--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="562">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46539163589478</t>
+    <t xml:space="preserve">2.46539187431335</t>
   </si>
   <si>
     <t xml:space="preserve">FPE.MI</t>
@@ -50,19 +50,19 @@
     <t xml:space="preserve">2.43408513069153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41060495376587</t>
+    <t xml:space="preserve">2.41060519218445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45756506919861</t>
+    <t xml:space="preserve">2.45756530761719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39495205879211</t>
+    <t xml:space="preserve">2.39495158195496</t>
   </si>
   <si>
     <t xml:space="preserve">2.33233880996704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41843199729919</t>
+    <t xml:space="preserve">2.41843175888062</t>
   </si>
   <si>
     <t xml:space="preserve">2.35581874847412</t>
@@ -71,22 +71,22 @@
     <t xml:space="preserve">2.37147188186646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50452470779419</t>
+    <t xml:space="preserve">2.50452494621277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36364531517029</t>
+    <t xml:space="preserve">2.36364579200745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44973850250244</t>
+    <t xml:space="preserve">2.44973826408386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37303733825684</t>
+    <t xml:space="preserve">2.37303757667542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34955763816833</t>
+    <t xml:space="preserve">2.34955739974976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46382665634155</t>
+    <t xml:space="preserve">2.46382641792297</t>
   </si>
   <si>
     <t xml:space="preserve">2.38712549209595</t>
@@ -104,22 +104,22 @@
     <t xml:space="preserve">2.37929844856262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38555979728699</t>
+    <t xml:space="preserve">2.38556003570557</t>
   </si>
   <si>
     <t xml:space="preserve">2.44191193580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78002238273621</t>
+    <t xml:space="preserve">2.78002309799194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36702084541321</t>
+    <t xml:space="preserve">3.36702060699463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62530016899109</t>
+    <t xml:space="preserve">3.62529993057251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31066918373108</t>
+    <t xml:space="preserve">3.3106689453125</t>
   </si>
   <si>
     <t xml:space="preserve">3.25588250160217</t>
@@ -128,79 +128,79 @@
     <t xml:space="preserve">3.20266103744507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05238962173462</t>
+    <t xml:space="preserve">3.0523898601532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09152293205261</t>
+    <t xml:space="preserve">3.09152317047119</t>
   </si>
   <si>
     <t xml:space="preserve">3.04456329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03673648834229</t>
+    <t xml:space="preserve">3.03673672676086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03830194473267</t>
+    <t xml:space="preserve">3.03830170631409</t>
   </si>
   <si>
     <t xml:space="preserve">3.15413618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30910348892212</t>
+    <t xml:space="preserve">3.30910396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30284214019775</t>
+    <t xml:space="preserve">3.30284190177917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35762858390808</t>
+    <t xml:space="preserve">3.35762882232666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57677459716797</t>
+    <t xml:space="preserve">3.57677507400513</t>
   </si>
   <si>
     <t xml:space="preserve">3.52198839187622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40458869934082</t>
+    <t xml:space="preserve">3.40458798408508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59242820739746</t>
+    <t xml:space="preserve">3.59242796897888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58460164070129</t>
+    <t xml:space="preserve">3.58460116386414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67852091789246</t>
+    <t xml:space="preserve">3.6785204410553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60025405883789</t>
+    <t xml:space="preserve">3.60025429725647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59555816650391</t>
+    <t xml:space="preserve">3.59555888175964</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632207870483</t>
+    <t xml:space="preserve">3.32632231712341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29501557350159</t>
+    <t xml:space="preserve">3.29501581192017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37484693527222</t>
+    <t xml:space="preserve">3.3748471736908</t>
   </si>
   <si>
     <t xml:space="preserve">3.38267397880554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44372153282166</t>
+    <t xml:space="preserve">3.44372200965881</t>
   </si>
   <si>
     <t xml:space="preserve">3.5908625125885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4797248840332</t>
+    <t xml:space="preserve">3.47972464561462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42650294303894</t>
+    <t xml:space="preserve">3.42650318145752</t>
   </si>
   <si>
     <t xml:space="preserve">3.41241550445557</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">3.24022912979126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21048831939697</t>
+    <t xml:space="preserve">3.21048808097839</t>
   </si>
   <si>
     <t xml:space="preserve">3.28405809402466</t>
@@ -218,19 +218,19 @@
     <t xml:space="preserve">3.16196274757385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20892238616943</t>
+    <t xml:space="preserve">3.20892262458801</t>
   </si>
   <si>
     <t xml:space="preserve">3.13848280906677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23240208625793</t>
+    <t xml:space="preserve">3.23240256309509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31849503517151</t>
+    <t xml:space="preserve">3.31849527359009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27623200416565</t>
+    <t xml:space="preserve">3.27623176574707</t>
   </si>
   <si>
     <t xml:space="preserve">3.18857312202454</t>
@@ -251,61 +251,61 @@
     <t xml:space="preserve">3.06021618843079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90368342399597</t>
+    <t xml:space="preserve">2.90368366241455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89585709571838</t>
+    <t xml:space="preserve">2.8958568572998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82854795455933</t>
+    <t xml:space="preserve">2.82854819297791</t>
   </si>
   <si>
     <t xml:space="preserve">2.83637452125549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90994501113892</t>
+    <t xml:space="preserve">2.90994477272034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491255760193</t>
+    <t xml:space="preserve">3.06491231918335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13065624237061</t>
+    <t xml:space="preserve">3.13065648078918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14474415779114</t>
+    <t xml:space="preserve">3.14474439620972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.213618516922</t>
+    <t xml:space="preserve">3.21361827850342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28562355041504</t>
+    <t xml:space="preserve">3.28562378883362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35919380187988</t>
+    <t xml:space="preserve">3.35919427871704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36388969421387</t>
+    <t xml:space="preserve">3.36389017105103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9133198261261</t>
+    <t xml:space="preserve">3.91332006454468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34378623962402</t>
+    <t xml:space="preserve">4.34378576278687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79381704330444</t>
+    <t xml:space="preserve">4.7938175201416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47864866256714</t>
+    <t xml:space="preserve">5.47864770889282</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09303998947144</t>
+    <t xml:space="preserve">6.09303903579712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41603565216064</t>
+    <t xml:space="preserve">5.41603517532349</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71344804763794</t>
+    <t xml:space="preserve">5.71344757080078</t>
   </si>
   <si>
     <t xml:space="preserve">5.56865453720093</t>
@@ -317,25 +317,25 @@
     <t xml:space="preserve">5.16558265686035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9464373588562</t>
+    <t xml:space="preserve">4.94643688201904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70381116867065</t>
+    <t xml:space="preserve">4.7038106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6764178276062</t>
+    <t xml:space="preserve">4.67641735076904</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00904941558838</t>
+    <t xml:space="preserve">5.00904989242554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55691480636597</t>
+    <t xml:space="preserve">5.55691385269165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30646228790283</t>
+    <t xml:space="preserve">5.30646276473999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22428274154663</t>
+    <t xml:space="preserve">5.22428226470947</t>
   </si>
   <si>
     <t xml:space="preserve">5.19688940048218</t>
@@ -347,28 +347,28 @@
     <t xml:space="preserve">5.47082138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36907529830933</t>
+    <t xml:space="preserve">5.36907577514648</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29080867767334</t>
+    <t xml:space="preserve">5.2908091545105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1734094619751</t>
+    <t xml:space="preserve">5.17340993881226</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09514331817627</t>
+    <t xml:space="preserve">5.09514284133911</t>
   </si>
   <si>
     <t xml:space="preserve">5.22036981582642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10296964645386</t>
+    <t xml:space="preserve">5.1029691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9933967590332</t>
+    <t xml:space="preserve">4.99339628219604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15384244918823</t>
+    <t xml:space="preserve">5.15384340286255</t>
   </si>
   <si>
     <t xml:space="preserve">4.98556995391846</t>
@@ -377,55 +377,55 @@
     <t xml:space="preserve">4.75859689712524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77033758163452</t>
+    <t xml:space="preserve">4.77033710479736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86425685882568</t>
+    <t xml:space="preserve">4.8642578125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88773679733276</t>
+    <t xml:space="preserve">4.88773727416992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83295011520386</t>
+    <t xml:space="preserve">4.83295059204102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75468397140503</t>
+    <t xml:space="preserve">4.75468444824219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82903671264648</t>
+    <t xml:space="preserve">4.8290376663208</t>
   </si>
   <si>
     <t xml:space="preserve">4.7233772277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68815803527832</t>
+    <t xml:space="preserve">4.688157081604</t>
   </si>
   <si>
     <t xml:space="preserve">4.78207731246948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8759970664978</t>
+    <t xml:space="preserve">4.87599658966064</t>
   </si>
   <si>
     <t xml:space="preserve">5.03644323348999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92687082290649</t>
+    <t xml:space="preserve">4.92687034606934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81338453292847</t>
+    <t xml:space="preserve">4.81338405609131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86034393310547</t>
+    <t xml:space="preserve">4.86034345626831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00122261047363</t>
+    <t xml:space="preserve">5.00122308731079</t>
   </si>
   <si>
     <t xml:space="preserve">4.77425098419189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82120990753174</t>
+    <t xml:space="preserve">4.8212103843689</t>
   </si>
   <si>
     <t xml:space="preserve">4.69989776611328</t>
@@ -434,22 +434,22 @@
     <t xml:space="preserve">4.69598484039307</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90730333328247</t>
+    <t xml:space="preserve">4.90730381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20471620559692</t>
+    <t xml:space="preserve">5.20471572875977</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43951559066772</t>
+    <t xml:space="preserve">5.43951463699341</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28298187255859</t>
+    <t xml:space="preserve">5.28298282623291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384927749634</t>
+    <t xml:space="preserve">5.24384880065918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36124801635742</t>
+    <t xml:space="preserve">5.36124897003174</t>
   </si>
   <si>
     <t xml:space="preserve">5.40038156509399</t>
@@ -458,70 +458,70 @@
     <t xml:space="preserve">5.51778173446655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63518047332764</t>
+    <t xml:space="preserve">5.63518095016479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96991682052612</t>
+    <t xml:space="preserve">4.96991634368896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93078327178955</t>
+    <t xml:space="preserve">4.93078374862671</t>
   </si>
   <si>
     <t xml:space="preserve">4.85251665115356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1264500617981</t>
+    <t xml:space="preserve">5.12644910812378</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04818296432495</t>
+    <t xml:space="preserve">5.04818248748779</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08731603622437</t>
+    <t xml:space="preserve">5.08731651306152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59604835510254</t>
+    <t xml:space="preserve">5.59604787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26159715652466</t>
+    <t xml:space="preserve">5.26159763336182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42103958129883</t>
+    <t xml:space="preserve">5.42104005813599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34131860733032</t>
+    <t xml:space="preserve">5.34131813049316</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22173738479614</t>
+    <t xml:space="preserve">5.22173643112183</t>
   </si>
   <si>
     <t xml:space="preserve">5.14201545715332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10215473175049</t>
+    <t xml:space="preserve">5.1021556854248</t>
   </si>
   <si>
     <t xml:space="preserve">5.18187618255615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.381178855896</t>
+    <t xml:space="preserve">5.38117933273315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30145835876465</t>
+    <t xml:space="preserve">5.30145788192749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9028525352478</t>
+    <t xml:space="preserve">4.90285205841064</t>
   </si>
   <si>
     <t xml:space="preserve">5.50076055526733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4608998298645</t>
+    <t xml:space="preserve">5.46090078353882</t>
   </si>
   <si>
     <t xml:space="preserve">5.58048248291016</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54062175750732</t>
+    <t xml:space="preserve">5.54062128067017</t>
   </si>
   <si>
     <t xml:space="preserve">5.62034273147583</t>
@@ -533,40 +533,40 @@
     <t xml:space="preserve">4.98257350921631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8231315612793</t>
+    <t xml:space="preserve">4.82313108444214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06229448318481</t>
+    <t xml:space="preserve">5.06229400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02243375778198</t>
+    <t xml:space="preserve">5.0224347114563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74340963363647</t>
+    <t xml:space="preserve">4.74340915679932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78327083587646</t>
+    <t xml:space="preserve">4.78326988220215</t>
   </si>
   <si>
     <t xml:space="preserve">4.86299180984497</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73992395401001</t>
+    <t xml:space="preserve">5.73992443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81964588165283</t>
+    <t xml:space="preserve">5.81964540481567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70006418228149</t>
+    <t xml:space="preserve">5.70006322860718</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66020345687866</t>
+    <t xml:space="preserve">5.66020250320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.77978515625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85950660705566</t>
+    <t xml:space="preserve">5.85950565338135</t>
   </si>
   <si>
     <t xml:space="preserve">5.97908782958984</t>
@@ -575,13 +575,13 @@
     <t xml:space="preserve">6.29797267913818</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13853025436401</t>
+    <t xml:space="preserve">6.13852977752686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05880928039551</t>
+    <t xml:space="preserve">6.05880880355835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825122833252</t>
+    <t xml:space="preserve">6.21825218200684</t>
   </si>
   <si>
     <t xml:space="preserve">6.09867000579834</t>
@@ -590,46 +590,46 @@
     <t xml:space="preserve">6.38518476486206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25998497009277</t>
+    <t xml:space="preserve">6.25998449325562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30171823501587</t>
+    <t xml:space="preserve">6.30171871185303</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17651844024658</t>
+    <t xml:space="preserve">6.17651796340942</t>
   </si>
   <si>
     <t xml:space="preserve">6.426917552948</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34345149993896</t>
+    <t xml:space="preserve">6.34345102310181</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46865081787109</t>
+    <t xml:space="preserve">6.46865129470825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96785259246826</t>
+    <t xml:space="preserve">5.9678521156311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00958490371704</t>
+    <t xml:space="preserve">6.0095853805542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13478565216064</t>
+    <t xml:space="preserve">6.13478422164917</t>
   </si>
   <si>
     <t xml:space="preserve">6.05131864547729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92611885070801</t>
+    <t xml:space="preserve">5.92611837387085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09305191040039</t>
+    <t xml:space="preserve">6.09305143356323</t>
   </si>
   <si>
     <t xml:space="preserve">6.21825170516968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51038408279419</t>
+    <t xml:space="preserve">6.51038503646851</t>
   </si>
   <si>
     <t xml:space="preserve">5.84265279769897</t>
@@ -638,22 +638,22 @@
     <t xml:space="preserve">5.88438606262207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05291604995728</t>
+    <t xml:space="preserve">7.05291557312012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09624671936035</t>
+    <t xml:space="preserve">8.09624767303467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.804114818573</t>
+    <t xml:space="preserve">7.80411338806152</t>
   </si>
   <si>
     <t xml:space="preserve">7.6371808052063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55371475219727</t>
+    <t xml:space="preserve">7.55371522903442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34504842758179</t>
+    <t xml:space="preserve">7.34504890441895</t>
   </si>
   <si>
     <t xml:space="preserve">7.17811584472656</t>
@@ -662,37 +662,37 @@
     <t xml:space="preserve">7.51198196411133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47024774551392</t>
+    <t xml:space="preserve">7.47024822235107</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30331611633301</t>
+    <t xml:space="preserve">7.30331516265869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851495742798</t>
+    <t xml:space="preserve">7.42851543426514</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26158237457275</t>
+    <t xml:space="preserve">7.2615818977356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38678169250488</t>
+    <t xml:space="preserve">7.3867826461792</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96944952011108</t>
+    <t xml:space="preserve">6.96944999694824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21984910964966</t>
+    <t xml:space="preserve">7.2198486328125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544849395752</t>
+    <t xml:space="preserve">7.59544897079468</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76238059997559</t>
+    <t xml:space="preserve">7.76238203048706</t>
   </si>
   <si>
     <t xml:space="preserve">7.84584712982178</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67891359329224</t>
+    <t xml:space="preserve">7.67891454696655</t>
   </si>
   <si>
     <t xml:space="preserve">7.01118278503418</t>
@@ -707,16 +707,16 @@
     <t xml:space="preserve">6.76078367233276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80251598358154</t>
+    <t xml:space="preserve">6.8025164604187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71905088424683</t>
+    <t xml:space="preserve">6.71904993057251</t>
   </si>
   <si>
     <t xml:space="preserve">6.8442497253418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59385061264038</t>
+    <t xml:space="preserve">6.59385108947754</t>
   </si>
   <si>
     <t xml:space="preserve">6.67731714248657</t>
@@ -728,13 +728,13 @@
     <t xml:space="preserve">5.75918579101562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71745204925537</t>
+    <t xml:space="preserve">5.71745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">5.80091905593872</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67571926116943</t>
+    <t xml:space="preserve">5.67571973800659</t>
   </si>
   <si>
     <t xml:space="preserve">5.59225273132324</t>
@@ -743,22 +743,22 @@
     <t xml:space="preserve">5.6339864730835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46705389022827</t>
+    <t xml:space="preserve">5.46705293655396</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55052042007446</t>
+    <t xml:space="preserve">5.55051946640015</t>
   </si>
   <si>
     <t xml:space="preserve">5.17492055892944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25838708877563</t>
+    <t xml:space="preserve">5.25838804244995</t>
   </si>
   <si>
     <t xml:space="preserve">5.38358688354492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13638353347778</t>
+    <t xml:space="preserve">7.13638257980347</t>
   </si>
   <si>
     <t xml:space="preserve">7.47247076034546</t>
@@ -767,10 +767,10 @@
     <t xml:space="preserve">7.25269222259521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2966480255127</t>
+    <t xml:space="preserve">7.29664754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20873641967773</t>
+    <t xml:space="preserve">7.20873594284058</t>
   </si>
   <si>
     <t xml:space="preserve">7.1647801399231</t>
@@ -779,16 +779,16 @@
     <t xml:space="preserve">7.07686996459961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98895835876465</t>
+    <t xml:space="preserve">6.98895788192749</t>
   </si>
   <si>
     <t xml:space="preserve">7.03291368484497</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94500255584717</t>
+    <t xml:space="preserve">6.94500207901001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85709142684937</t>
+    <t xml:space="preserve">6.85709095001221</t>
   </si>
   <si>
     <t xml:space="preserve">6.72522401809692</t>
@@ -812,22 +812,22 @@
     <t xml:space="preserve">7.34060382843018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51642751693726</t>
+    <t xml:space="preserve">7.5164270401001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56038236618042</t>
+    <t xml:space="preserve">7.56038284301758</t>
   </si>
   <si>
     <t xml:space="preserve">7.73620510101318</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69224977493286</t>
+    <t xml:space="preserve">7.6922492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829397201538</t>
+    <t xml:space="preserve">7.64829349517822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78247356414795</t>
+    <t xml:space="preserve">7.78247404098511</t>
   </si>
   <si>
     <t xml:space="preserve">7.8272008895874</t>
@@ -836,16 +836,16 @@
     <t xml:space="preserve">7.73774671554565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69302082061768</t>
+    <t xml:space="preserve">7.69302034378052</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60356664657593</t>
+    <t xml:space="preserve">7.60356712341309</t>
   </si>
   <si>
     <t xml:space="preserve">7.91665458679199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8719277381897</t>
+    <t xml:space="preserve">7.87192869186401</t>
   </si>
   <si>
     <t xml:space="preserve">7.96138143539429</t>
@@ -857,19 +857,19 @@
     <t xml:space="preserve">8.76646614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58755779266357</t>
+    <t xml:space="preserve">8.58755683898926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36392402648926</t>
+    <t xml:space="preserve">8.36392307281494</t>
   </si>
   <si>
     <t xml:space="preserve">8.63228416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54283046722412</t>
+    <t xml:space="preserve">8.54283142089844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40864944458008</t>
+    <t xml:space="preserve">8.40865039825439</t>
   </si>
   <si>
     <t xml:space="preserve">8.27446937561035</t>
@@ -878,40 +878,40 @@
     <t xml:space="preserve">8.45337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67701244354248</t>
+    <t xml:space="preserve">8.67701053619385</t>
   </si>
   <si>
     <t xml:space="preserve">8.49810409545898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81119251251221</t>
+    <t xml:space="preserve">8.81119155883789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7217378616333</t>
+    <t xml:space="preserve">8.72173881530762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85591983795166</t>
+    <t xml:space="preserve">8.85591888427734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03482532501221</t>
+    <t xml:space="preserve">9.03482627868652</t>
   </si>
   <si>
     <t xml:space="preserve">10.3766326904297</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4500780105591</t>
+    <t xml:space="preserve">11.4500770568848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.734447479248</t>
+    <t xml:space="preserve">10.7344465255737</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0922613143921</t>
+    <t xml:space="preserve">11.0922622680664</t>
   </si>
   <si>
     <t xml:space="preserve">10.9133539199829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1817150115967</t>
+    <t xml:space="preserve">11.181715965271</t>
   </si>
   <si>
     <t xml:space="preserve">11.3606224060059</t>
@@ -920,25 +920,25 @@
     <t xml:space="preserve">11.6289844512939</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5395307540894</t>
+    <t xml:space="preserve">11.539529800415</t>
   </si>
   <si>
     <t xml:space="preserve">11.2711696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5555391311646</t>
+    <t xml:space="preserve">10.5555400848389</t>
   </si>
   <si>
     <t xml:space="preserve">10.2871789932251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0028076171875</t>
+    <t xml:space="preserve">11.0028095245361</t>
   </si>
   <si>
     <t xml:space="preserve">10.6449928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4660863876343</t>
+    <t xml:space="preserve">10.46608543396</t>
   </si>
   <si>
     <t xml:space="preserve">10.1082715988159</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">9.75045585632324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.018816947937</t>
+    <t xml:space="preserve">10.0188159942627</t>
   </si>
   <si>
     <t xml:space="preserve">12.6129751205444</t>
@@ -959,13 +959,13 @@
     <t xml:space="preserve">12.9707899093628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0442342758179</t>
+    <t xml:space="preserve">14.0442333221436</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7758731842041</t>
+    <t xml:space="preserve">13.7758741378784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.507513999939</t>
+    <t xml:space="preserve">13.5075130462646</t>
   </si>
   <si>
     <t xml:space="preserve">13.2391519546509</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">13.0602445602417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4180593490601</t>
+    <t xml:space="preserve">13.4180583953857</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8813362121582</t>
+    <t xml:space="preserve">12.8813371658325</t>
   </si>
   <si>
     <t xml:space="preserve">12.7918834686279</t>
   </si>
   <si>
-    <t xml:space="preserve">12.702428817749</t>
+    <t xml:space="preserve">12.7024278640747</t>
   </si>
   <si>
     <t xml:space="preserve">13.149697303772</t>
@@ -992,46 +992,46 @@
     <t xml:space="preserve">13.3286046981812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547805786133</t>
+    <t xml:space="preserve">13.9547815322876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5969667434692</t>
+    <t xml:space="preserve">13.5969657897949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6864213943481</t>
+    <t xml:space="preserve">13.6864204406738</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8653268814087</t>
+    <t xml:space="preserve">13.865327835083</t>
   </si>
   <si>
     <t xml:space="preserve">14.4020500183105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2965879440308</t>
+    <t xml:space="preserve">15.2965869903564</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2071332931519</t>
+    <t xml:space="preserve">15.2071342468262</t>
   </si>
   <si>
     <t xml:space="preserve">14.5809564590454</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7598648071289</t>
+    <t xml:space="preserve">14.7598638534546</t>
   </si>
   <si>
     <t xml:space="preserve">14.4915046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5400876998901</t>
+    <t xml:space="preserve">14.5400886535645</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3560361862183</t>
+    <t xml:space="preserve">14.3560371398926</t>
   </si>
   <si>
     <t xml:space="preserve">14.2640104293823</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1719846725464</t>
+    <t xml:space="preserve">14.1719837188721</t>
   </si>
   <si>
     <t xml:space="preserve">14.8161659240723</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">14.6321144104004</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3683223724365</t>
+    <t xml:space="preserve">15.3683214187622</t>
   </si>
   <si>
     <t xml:space="preserve">15.5523738861084</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">15.9204750061035</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2088394165039</t>
+    <t xml:space="preserve">17.2088413238525</t>
   </si>
   <si>
     <t xml:space="preserve">17.3008632659912</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">18.4051742553711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1413803100586</t>
+    <t xml:space="preserve">19.1413822174072</t>
   </si>
   <si>
     <t xml:space="preserve">19.6935367584229</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">22.2702617645264</t>
   </si>
   <si>
-    <t xml:space="preserve">22.822416305542</t>
+    <t xml:space="preserve">22.8224182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6137962341309</t>
+    <t xml:space="preserve">20.6137943267822</t>
   </si>
   <si>
     <t xml:space="preserve">19.3254337310791</t>
@@ -1106,10 +1106,10 @@
     <t xml:space="preserve">22.0862102508545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0064678192139</t>
+    <t xml:space="preserve">23.0064697265625</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5586261749268</t>
+    <t xml:space="preserve">23.5586242675781</t>
   </si>
   <si>
     <t xml:space="preserve">23.74267578125</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">24.6629333496094</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8469886779785</t>
+    <t xml:space="preserve">24.8469867706299</t>
   </si>
   <si>
     <t xml:space="preserve">24.2948303222656</t>
@@ -1151,16 +1151,16 @@
     <t xml:space="preserve">27.975866317749</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9206943511963</t>
+    <t xml:space="preserve">30.9206924438477</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0801753997803</t>
+    <t xml:space="preserve">29.0801773071289</t>
   </si>
   <si>
-    <t xml:space="preserve">30.736644744873</t>
+    <t xml:space="preserve">30.7366428375244</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3685398101807</t>
+    <t xml:space="preserve">30.3685417175293</t>
   </si>
   <si>
     <t xml:space="preserve">29.2642288208008</t>
@@ -1172,10 +1172,10 @@
     <t xml:space="preserve">34.2336273193359</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7857780456543</t>
+    <t xml:space="preserve">34.7857818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8655204772949</t>
+    <t xml:space="preserve">33.8655166625977</t>
   </si>
   <si>
     <t xml:space="preserve">33.4974212646484</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">27.7918167114258</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8961238861084</t>
+    <t xml:space="preserve">28.896125793457</t>
   </si>
   <si>
     <t xml:space="preserve">29.4482803344727</t>
@@ -1208,19 +1208,19 @@
     <t xml:space="preserve">28.5280208587646</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7120723724365</t>
+    <t xml:space="preserve">28.7120742797852</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3439693450928</t>
+    <t xml:space="preserve">28.3439674377441</t>
   </si>
   <si>
     <t xml:space="preserve">27.055606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8715572357178</t>
+    <t xml:space="preserve">26.8715553283691</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3991413116455</t>
+    <t xml:space="preserve">25.3991432189941</t>
   </si>
   <si>
     <t xml:space="preserve">25.7672443389893</t>
@@ -1241,13 +1241,13 @@
     <t xml:space="preserve">30.0004329681396</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3931083679199</t>
+    <t xml:space="preserve">32.3931121826172</t>
   </si>
   <si>
     <t xml:space="preserve">32.209056854248</t>
   </si>
   <si>
-    <t xml:space="preserve">31.28879737854</t>
+    <t xml:space="preserve">31.2887954711914</t>
   </si>
   <si>
     <t xml:space="preserve">31.6569023132324</t>
@@ -1259,34 +1259,34 @@
     <t xml:space="preserve">32.0337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5990715026855</t>
+    <t xml:space="preserve">32.5990676879883</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1643714904785</t>
+    <t xml:space="preserve">33.1643753051758</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6569004058838</t>
+    <t xml:space="preserve">31.6568984985352</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4106369018555</t>
+    <t xml:space="preserve">32.4106407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7875022888184</t>
+    <t xml:space="preserve">32.7875061035156</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9759407043457</t>
+    <t xml:space="preserve">32.9759368896484</t>
   </si>
   <si>
     <t xml:space="preserve">30.9031639099121</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8453369140625</t>
+    <t xml:space="preserve">31.8453350067139</t>
   </si>
   <si>
     <t xml:space="preserve">30.714729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5262985229492</t>
+    <t xml:space="preserve">30.5263004302979</t>
   </si>
   <si>
     <t xml:space="preserve">31.2800331115723</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">30.1494293212891</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3378639221191</t>
+    <t xml:space="preserve">30.3378658294678</t>
   </si>
   <si>
     <t xml:space="preserve">29.395694732666</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">28.2650909423828</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6997890472412</t>
+    <t xml:space="preserve">27.6997871398926</t>
   </si>
   <si>
     <t xml:space="preserve">28.0766563415527</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">25.2501468658447</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3079776763916</t>
+    <t xml:space="preserve">24.307975769043</t>
   </si>
   <si>
     <t xml:space="preserve">23.9311103820801</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">23.7426776885986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.177375793457</t>
+    <t xml:space="preserve">23.1773738861084</t>
   </si>
   <si>
     <t xml:space="preserve">22.6120719909668</t>
@@ -1370,10 +1370,10 @@
     <t xml:space="preserve">22.2352046966553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0467700958252</t>
+    <t xml:space="preserve">22.0467720031738</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8005084991455</t>
+    <t xml:space="preserve">22.8005065917969</t>
   </si>
   <si>
     <t xml:space="preserve">22.988941192627</t>
@@ -1388,19 +1388,19 @@
     <t xml:space="preserve">25.6270160675049</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3807506561279</t>
+    <t xml:space="preserve">26.3807525634766</t>
   </si>
   <si>
-    <t xml:space="preserve">27.134485244751</t>
+    <t xml:space="preserve">27.1344871520996</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9460525512695</t>
+    <t xml:space="preserve">26.9460544586182</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3229198455811</t>
+    <t xml:space="preserve">27.3229217529297</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1923160552979</t>
+    <t xml:space="preserve">26.1923179626465</t>
   </si>
   <si>
     <t xml:space="preserve">26.7576179504395</t>
@@ -1695,6 +1695,9 @@
   </si>
   <si>
     <t xml:space="preserve">41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.2000007629395</t>
   </si>
 </sst>
 </file>
@@ -60611,7 +60614,7 @@
     </row>
     <row r="2254">
       <c r="A2254" s="1" t="n">
-        <v>45943.4603935185</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2254" t="n">
         <v>500</v>
@@ -60632,6 +60635,32 @@
         <v>534</v>
       </c>
       <c r="H2254" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" s="1" t="n">
+        <v>45944.5518055556</v>
+      </c>
+      <c r="B2255" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C2255" t="n">
+        <v>40.2000007629395</v>
+      </c>
+      <c r="D2255" t="n">
+        <v>38.5999984741211</v>
+      </c>
+      <c r="E2255" t="n">
+        <v>39</v>
+      </c>
+      <c r="F2255" t="n">
+        <v>40.2000007629395</v>
+      </c>
+      <c r="G2255" t="s">
+        <v>561</v>
+      </c>
+      <c r="H2255" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -44,49 +44,49 @@
     <t xml:space="preserve">FPE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4262580871582</t>
+    <t xml:space="preserve">2.42625832557678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43408513069153</t>
+    <t xml:space="preserve">2.43408489227295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41060519218445</t>
+    <t xml:space="preserve">2.41060495376587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45756506919861</t>
+    <t xml:space="preserve">2.45756530761719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39495158195496</t>
+    <t xml:space="preserve">2.39495182037354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233904838562</t>
+    <t xml:space="preserve">2.33233880996704</t>
   </si>
   <si>
     <t xml:space="preserve">2.41843199729919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35581874847412</t>
+    <t xml:space="preserve">2.3558189868927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37147235870361</t>
+    <t xml:space="preserve">2.37147212028503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50452494621277</t>
+    <t xml:space="preserve">2.50452518463135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36364531517029</t>
+    <t xml:space="preserve">2.36364555358887</t>
   </si>
   <si>
     <t xml:space="preserve">2.44973850250244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37303733825684</t>
+    <t xml:space="preserve">2.37303757667542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34955716133118</t>
+    <t xml:space="preserve">2.34955787658691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46382665634155</t>
+    <t xml:space="preserve">2.46382641792297</t>
   </si>
   <si>
     <t xml:space="preserve">2.38712525367737</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">2.45443439483643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34799218177795</t>
+    <t xml:space="preserve">2.34799194335938</t>
   </si>
   <si>
     <t xml:space="preserve">2.48104500770569</t>
@@ -104,88 +104,88 @@
     <t xml:space="preserve">2.3792986869812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38555979728699</t>
+    <t xml:space="preserve">2.38556027412415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4419116973877</t>
+    <t xml:space="preserve">2.44191193580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78002285957336</t>
+    <t xml:space="preserve">2.78002238273621</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36702060699463</t>
+    <t xml:space="preserve">3.36702084541321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62529945373535</t>
+    <t xml:space="preserve">3.62529969215393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31066918373108</t>
+    <t xml:space="preserve">3.31066846847534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25588250160217</t>
+    <t xml:space="preserve">3.25588226318359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20266103744507</t>
+    <t xml:space="preserve">3.20266127586365</t>
   </si>
   <si>
     <t xml:space="preserve">3.05239009857178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09152269363403</t>
+    <t xml:space="preserve">3.09152293205261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04456305503845</t>
+    <t xml:space="preserve">3.04456329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03673696517944</t>
+    <t xml:space="preserve">3.03673648834229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03830170631409</t>
+    <t xml:space="preserve">3.03830194473267</t>
   </si>
   <si>
     <t xml:space="preserve">3.15413618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30910325050354</t>
+    <t xml:space="preserve">3.30910396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30284190177917</t>
+    <t xml:space="preserve">3.30284237861633</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35762858390808</t>
+    <t xml:space="preserve">3.35762882232666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57677507400513</t>
+    <t xml:space="preserve">3.57677483558655</t>
   </si>
   <si>
     <t xml:space="preserve">3.52198839187622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40458846092224</t>
+    <t xml:space="preserve">3.40458869934082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59242820739746</t>
+    <t xml:space="preserve">3.59242844581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58460140228271</t>
+    <t xml:space="preserve">3.58460116386414</t>
   </si>
   <si>
     <t xml:space="preserve">3.67852115631104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60025429725647</t>
+    <t xml:space="preserve">3.60025453567505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59555864334106</t>
+    <t xml:space="preserve">3.59555888175964</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632231712341</t>
+    <t xml:space="preserve">3.32632255554199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29501557350159</t>
+    <t xml:space="preserve">3.29501581192017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3748471736908</t>
+    <t xml:space="preserve">3.37484765052795</t>
   </si>
   <si>
     <t xml:space="preserve">3.38267397880554</t>
@@ -194,40 +194,40 @@
     <t xml:space="preserve">3.44372200965881</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59086227416992</t>
+    <t xml:space="preserve">3.5908625125885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47972416877747</t>
+    <t xml:space="preserve">3.47972464561462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42650294303894</t>
+    <t xml:space="preserve">3.42650246620178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41241550445557</t>
+    <t xml:space="preserve">3.41241526603699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24022936820984</t>
+    <t xml:space="preserve">3.24022912979126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21048784255981</t>
+    <t xml:space="preserve">3.21048808097839</t>
   </si>
   <si>
     <t xml:space="preserve">3.28405857086182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16196274757385</t>
+    <t xml:space="preserve">3.16196250915527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20892262458801</t>
+    <t xml:space="preserve">3.20892238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13848280906677</t>
+    <t xml:space="preserve">3.13848304748535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23240232467651</t>
+    <t xml:space="preserve">3.23240280151367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31849503517151</t>
+    <t xml:space="preserve">3.31849527359009</t>
   </si>
   <si>
     <t xml:space="preserve">3.27623176574707</t>
@@ -236,16 +236,16 @@
     <t xml:space="preserve">3.18857312202454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14317846298218</t>
+    <t xml:space="preserve">3.14317893981934</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11500287055969</t>
+    <t xml:space="preserve">3.11500334739685</t>
   </si>
   <si>
     <t xml:space="preserve">3.00073409080505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97412347793579</t>
+    <t xml:space="preserve">2.97412323951721</t>
   </si>
   <si>
     <t xml:space="preserve">3.06021642684937</t>
@@ -260,49 +260,49 @@
     <t xml:space="preserve">2.82854819297791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83637499809265</t>
+    <t xml:space="preserve">2.83637452125549</t>
   </si>
   <si>
     <t xml:space="preserve">2.90994477272034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491255760193</t>
+    <t xml:space="preserve">3.06491208076477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13065648078918</t>
+    <t xml:space="preserve">3.13065600395203</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14474439620972</t>
+    <t xml:space="preserve">3.14474415779114</t>
   </si>
   <si>
     <t xml:space="preserve">3.21361827850342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2856240272522</t>
+    <t xml:space="preserve">3.28562355041504</t>
   </si>
   <si>
     <t xml:space="preserve">3.35919404029846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36389017105103</t>
+    <t xml:space="preserve">3.36388993263245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91331958770752</t>
+    <t xml:space="preserve">3.91332006454468</t>
   </si>
   <si>
     <t xml:space="preserve">4.34378576278687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79381704330444</t>
+    <t xml:space="preserve">4.7938175201416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47864818572998</t>
+    <t xml:space="preserve">5.47864866256714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09303998947144</t>
+    <t xml:space="preserve">6.09303951263428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41603469848633</t>
+    <t xml:space="preserve">5.41603517532349</t>
   </si>
   <si>
     <t xml:space="preserve">5.71344757080078</t>
@@ -320,70 +320,70 @@
     <t xml:space="preserve">4.94643640518188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70381116867065</t>
+    <t xml:space="preserve">4.7038106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67641735076904</t>
+    <t xml:space="preserve">4.6764178276062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00904989242554</t>
+    <t xml:space="preserve">5.0090503692627</t>
   </si>
   <si>
     <t xml:space="preserve">5.55691480636597</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30646181106567</t>
+    <t xml:space="preserve">5.30646276473999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22428274154663</t>
+    <t xml:space="preserve">5.22428226470947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19688940048218</t>
+    <t xml:space="preserve">5.19688844680786</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32211589813232</t>
+    <t xml:space="preserve">5.32211542129517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47082090377808</t>
+    <t xml:space="preserve">5.47082138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36907577514648</t>
+    <t xml:space="preserve">5.36907529830933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29080867767334</t>
+    <t xml:space="preserve">5.29080963134766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17340898513794</t>
+    <t xml:space="preserve">5.1734094619751</t>
   </si>
   <si>
     <t xml:space="preserve">5.09514331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22036981582642</t>
+    <t xml:space="preserve">5.2203688621521</t>
   </si>
   <si>
     <t xml:space="preserve">5.10296964645386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99339723587036</t>
+    <t xml:space="preserve">4.9933967590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15384292602539</t>
+    <t xml:space="preserve">5.15384244918823</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98556995391846</t>
+    <t xml:space="preserve">4.98557043075562</t>
   </si>
   <si>
     <t xml:space="preserve">4.7585973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77033710479736</t>
+    <t xml:space="preserve">4.77033758163452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86425733566284</t>
+    <t xml:space="preserve">4.86425685882568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88773679733276</t>
+    <t xml:space="preserve">4.88773632049561</t>
   </si>
   <si>
     <t xml:space="preserve">4.83295059204102</t>
@@ -395,28 +395,28 @@
     <t xml:space="preserve">4.82903718948364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72337770462036</t>
+    <t xml:space="preserve">4.7233772277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68815660476685</t>
+    <t xml:space="preserve">4.688157081604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78207778930664</t>
+    <t xml:space="preserve">4.78207731246948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87599754333496</t>
+    <t xml:space="preserve">4.87599658966064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03644371032715</t>
+    <t xml:space="preserve">5.03644275665283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92687082290649</t>
+    <t xml:space="preserve">4.92687034606934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81338405609131</t>
+    <t xml:space="preserve">4.81338357925415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86034345626831</t>
+    <t xml:space="preserve">4.86034393310547</t>
   </si>
   <si>
     <t xml:space="preserve">5.00122308731079</t>
@@ -425,172 +425,172 @@
     <t xml:space="preserve">4.77425050735474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8212103843689</t>
+    <t xml:space="preserve">4.82120990753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.69989728927612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69598436355591</t>
+    <t xml:space="preserve">4.69598388671875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90730381011963</t>
+    <t xml:space="preserve">4.90730333328247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20471620559692</t>
+    <t xml:space="preserve">5.20471572875977</t>
   </si>
   <si>
     <t xml:space="preserve">5.43951463699341</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28298234939575</t>
+    <t xml:space="preserve">5.28298187255859</t>
   </si>
   <si>
     <t xml:space="preserve">5.24384880065918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36124849319458</t>
+    <t xml:space="preserve">5.36124801635742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40038156509399</t>
+    <t xml:space="preserve">5.40038204193115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51778125762939</t>
+    <t xml:space="preserve">5.51778173446655</t>
   </si>
   <si>
     <t xml:space="preserve">5.63518095016479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96991682052612</t>
+    <t xml:space="preserve">4.96991729736328</t>
   </si>
   <si>
     <t xml:space="preserve">4.93078374862671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85251617431641</t>
+    <t xml:space="preserve">4.85251665115356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12644958496094</t>
+    <t xml:space="preserve">5.12645053863525</t>
   </si>
   <si>
     <t xml:space="preserve">5.04818296432495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08731651306152</t>
+    <t xml:space="preserve">5.08731603622437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59604835510254</t>
+    <t xml:space="preserve">5.59604787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26159715652466</t>
+    <t xml:space="preserve">5.26159763336182</t>
   </si>
   <si>
     <t xml:space="preserve">5.42103958129883</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34131813049316</t>
+    <t xml:space="preserve">5.34131860733032</t>
   </si>
   <si>
     <t xml:space="preserve">5.22173738479614</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14201593399048</t>
+    <t xml:space="preserve">5.14201545715332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10215520858765</t>
+    <t xml:space="preserve">5.1021556854248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18187618255615</t>
+    <t xml:space="preserve">5.18187570571899</t>
   </si>
   <si>
     <t xml:space="preserve">5.381178855896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30145788192749</t>
+    <t xml:space="preserve">5.30145740509033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9028525352478</t>
+    <t xml:space="preserve">4.90285205841064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50076150894165</t>
+    <t xml:space="preserve">5.50076103210449</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46090030670166</t>
+    <t xml:space="preserve">5.46089935302734</t>
   </si>
   <si>
-    <t xml:space="preserve">5.580482006073</t>
+    <t xml:space="preserve">5.58048248291016</t>
   </si>
   <si>
     <t xml:space="preserve">5.54062128067017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62034273147583</t>
+    <t xml:space="preserve">5.62034225463867</t>
   </si>
   <si>
     <t xml:space="preserve">4.94271278381348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98257303237915</t>
+    <t xml:space="preserve">4.98257350921631</t>
   </si>
   <si>
     <t xml:space="preserve">4.8231315612793</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06229448318481</t>
+    <t xml:space="preserve">5.06229496002197</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02243423461914</t>
+    <t xml:space="preserve">5.02243375778198</t>
   </si>
   <si>
     <t xml:space="preserve">4.74340963363647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78327083587646</t>
+    <t xml:space="preserve">4.78327035903931</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86299133300781</t>
+    <t xml:space="preserve">4.86299180984497</t>
   </si>
   <si>
     <t xml:space="preserve">5.73992443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81964492797852</t>
+    <t xml:space="preserve">5.81964588165283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70006370544434</t>
+    <t xml:space="preserve">5.70006418228149</t>
   </si>
   <si>
     <t xml:space="preserve">5.66020345687866</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77978467941284</t>
+    <t xml:space="preserve">5.77978563308716</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85950660705566</t>
+    <t xml:space="preserve">5.85950565338135</t>
   </si>
   <si>
     <t xml:space="preserve">5.97908782958984</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29797267913818</t>
+    <t xml:space="preserve">6.29797220230103</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13852977752686</t>
+    <t xml:space="preserve">6.13853025436401</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05880880355835</t>
+    <t xml:space="preserve">6.05880928039551</t>
   </si>
   <si>
     <t xml:space="preserve">6.21825122833252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09867000579834</t>
+    <t xml:space="preserve">6.09866952896118</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38518476486206</t>
+    <t xml:space="preserve">6.3851842880249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25998449325562</t>
+    <t xml:space="preserve">6.25998497009277</t>
   </si>
   <si>
     <t xml:space="preserve">6.30171775817871</t>
@@ -605,58 +605,58 @@
     <t xml:space="preserve">6.34345149993896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46865081787109</t>
+    <t xml:space="preserve">6.46865129470825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96785259246826</t>
+    <t xml:space="preserve">5.9678521156311</t>
   </si>
   <si>
     <t xml:space="preserve">6.0095853805542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13478517532349</t>
+    <t xml:space="preserve">6.13478469848633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05131816864014</t>
+    <t xml:space="preserve">6.05131912231445</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92611885070801</t>
+    <t xml:space="preserve">5.92611837387085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09305095672607</t>
+    <t xml:space="preserve">6.09305191040039</t>
   </si>
   <si>
     <t xml:space="preserve">6.51038408279419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84265232086182</t>
+    <t xml:space="preserve">5.84265279769897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88438606262207</t>
+    <t xml:space="preserve">5.88438558578491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05291604995728</t>
+    <t xml:space="preserve">7.05291652679443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09624767303467</t>
+    <t xml:space="preserve">8.09624671936035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80411529541016</t>
+    <t xml:space="preserve">7.804114818573</t>
   </si>
   <si>
     <t xml:space="preserve">7.63718032836914</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55371570587158</t>
+    <t xml:space="preserve">7.55371522903442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34504890441895</t>
+    <t xml:space="preserve">7.3450493812561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17811679840088</t>
+    <t xml:space="preserve">7.17811632156372</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51198244094849</t>
+    <t xml:space="preserve">7.51198196411133</t>
   </si>
   <si>
     <t xml:space="preserve">7.47024869918823</t>
@@ -665,19 +665,19 @@
     <t xml:space="preserve">7.30331516265869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851448059082</t>
+    <t xml:space="preserve">7.42851495742798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26158332824707</t>
+    <t xml:space="preserve">7.26158237457275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38678216934204</t>
+    <t xml:space="preserve">7.3867826461792</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96944952011108</t>
+    <t xml:space="preserve">6.96944999694824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21984958648682</t>
+    <t xml:space="preserve">7.2198486328125</t>
   </si>
   <si>
     <t xml:space="preserve">7.59544801712036</t>
@@ -686,19 +686,19 @@
     <t xml:space="preserve">7.7623815536499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84584712982178</t>
+    <t xml:space="preserve">7.84584808349609</t>
   </si>
   <si>
     <t xml:space="preserve">7.67891407012939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01118183135986</t>
+    <t xml:space="preserve">7.01118230819702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09464931488037</t>
+    <t xml:space="preserve">7.09464979171753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92771625518799</t>
+    <t xml:space="preserve">6.92771673202515</t>
   </si>
   <si>
     <t xml:space="preserve">6.76078367233276</t>
@@ -707,13 +707,13 @@
     <t xml:space="preserve">6.80251598358154</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71905040740967</t>
+    <t xml:space="preserve">6.71905088424683</t>
   </si>
   <si>
     <t xml:space="preserve">6.8442497253418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59385108947754</t>
+    <t xml:space="preserve">6.59385013580322</t>
   </si>
   <si>
     <t xml:space="preserve">6.67731666564941</t>
@@ -722,49 +722,49 @@
     <t xml:space="preserve">6.55211782455444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75918674468994</t>
+    <t xml:space="preserve">5.75918626785278</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71745252609253</t>
+    <t xml:space="preserve">5.71745204925537</t>
   </si>
   <si>
     <t xml:space="preserve">5.80091905593872</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67571926116943</t>
+    <t xml:space="preserve">5.67571973800659</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59225273132324</t>
+    <t xml:space="preserve">5.5922532081604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63398599624634</t>
+    <t xml:space="preserve">5.6339864730835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46705341339111</t>
+    <t xml:space="preserve">5.46705389022827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5505199432373</t>
+    <t xml:space="preserve">5.55051946640015</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1749210357666</t>
+    <t xml:space="preserve">5.17492055892944</t>
   </si>
   <si>
     <t xml:space="preserve">5.25838756561279</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38358688354492</t>
+    <t xml:space="preserve">5.38358640670776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13638353347778</t>
+    <t xml:space="preserve">7.13638257980347</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47247076034546</t>
+    <t xml:space="preserve">7.47247123718262</t>
   </si>
   <si>
     <t xml:space="preserve">7.25269222259521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29664754867554</t>
+    <t xml:space="preserve">7.2966480255127</t>
   </si>
   <si>
     <t xml:space="preserve">7.20873641967773</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">7.1647801399231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07686948776245</t>
+    <t xml:space="preserve">7.07686996459961</t>
   </si>
   <si>
     <t xml:space="preserve">6.98895788192749</t>
@@ -782,10 +782,10 @@
     <t xml:space="preserve">7.03291368484497</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94500255584717</t>
+    <t xml:space="preserve">6.94500160217285</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85709095001221</t>
+    <t xml:space="preserve">6.85709142684937</t>
   </si>
   <si>
     <t xml:space="preserve">6.72522401809692</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">7.12082529067993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34060335159302</t>
+    <t xml:space="preserve">7.34060430526733</t>
   </si>
   <si>
     <t xml:space="preserve">7.5164270401001</t>
@@ -815,22 +815,22 @@
     <t xml:space="preserve">7.56038284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851495742798</t>
+    <t xml:space="preserve">7.42851543426514</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73620510101318</t>
+    <t xml:space="preserve">7.73620557785034</t>
   </si>
   <si>
     <t xml:space="preserve">7.69224882125854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829444885254</t>
+    <t xml:space="preserve">7.64829397201538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78247404098511</t>
+    <t xml:space="preserve">7.78247451782227</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8272008895874</t>
+    <t xml:space="preserve">7.82720041275024</t>
   </si>
   <si>
     <t xml:space="preserve">7.73774671554565</t>
@@ -848,34 +848,34 @@
     <t xml:space="preserve">7.87192869186401</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96138048171997</t>
+    <t xml:space="preserve">7.96138143539429</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22974300384521</t>
+    <t xml:space="preserve">8.2297420501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76646518707275</t>
+    <t xml:space="preserve">8.76646614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58755683898926</t>
+    <t xml:space="preserve">8.58755779266357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36392307281494</t>
+    <t xml:space="preserve">8.36392402648926</t>
   </si>
   <si>
     <t xml:space="preserve">8.63228416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54283142089844</t>
+    <t xml:space="preserve">8.54283046722412</t>
   </si>
   <si>
     <t xml:space="preserve">8.40865039825439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27446937561035</t>
+    <t xml:space="preserve">8.27447032928467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45337677001953</t>
+    <t xml:space="preserve">8.45337772369385</t>
   </si>
   <si>
     <t xml:space="preserve">8.67701148986816</t>
@@ -884,31 +884,31 @@
     <t xml:space="preserve">8.49810314178467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81119155883789</t>
+    <t xml:space="preserve">8.81119251251221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72173881530762</t>
+    <t xml:space="preserve">8.7217378616333</t>
   </si>
   <si>
     <t xml:space="preserve">8.85591888427734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03482627868652</t>
+    <t xml:space="preserve">9.03482532501221</t>
   </si>
   <si>
-    <t xml:space="preserve">10.376633644104</t>
+    <t xml:space="preserve">10.3766326904297</t>
   </si>
   <si>
     <t xml:space="preserve">11.4500770568848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7344465255737</t>
+    <t xml:space="preserve">10.734447479248</t>
   </si>
   <si>
     <t xml:space="preserve">11.0922613143921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9133548736572</t>
+    <t xml:space="preserve">10.9133539199829</t>
   </si>
   <si>
     <t xml:space="preserve">11.181715965271</t>
@@ -920,10 +920,10 @@
     <t xml:space="preserve">11.6289844512939</t>
   </si>
   <si>
-    <t xml:space="preserve">11.539529800415</t>
+    <t xml:space="preserve">11.5395307540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2711687088013</t>
+    <t xml:space="preserve">11.2711696624756</t>
   </si>
   <si>
     <t xml:space="preserve">10.5555391311646</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">10.2871789932251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0028085708618</t>
+    <t xml:space="preserve">11.0028076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6449918746948</t>
+    <t xml:space="preserve">10.6449928283691</t>
   </si>
   <si>
     <t xml:space="preserve">10.4660863876343</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">10.1082706451416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1977243423462</t>
+    <t xml:space="preserve">10.1977233886719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75045680999756</t>
+    <t xml:space="preserve">9.75045585632324</t>
   </si>
   <si>
     <t xml:space="preserve">10.0188159942627</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">12.6129751205444</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9707908630371</t>
+    <t xml:space="preserve">12.9707899093628</t>
   </si>
   <si>
     <t xml:space="preserve">14.0442352294922</t>
@@ -968,46 +968,46 @@
     <t xml:space="preserve">13.507513999939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2391510009766</t>
+    <t xml:space="preserve">13.2391519546509</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0602445602417</t>
+    <t xml:space="preserve">13.0602436065674</t>
   </si>
   <si>
     <t xml:space="preserve">13.4180593490601</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8813371658325</t>
+    <t xml:space="preserve">12.8813362121582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7918825149536</t>
+    <t xml:space="preserve">12.7918834686279</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7024278640747</t>
+    <t xml:space="preserve">12.7024297714233</t>
   </si>
   <si>
     <t xml:space="preserve">13.149697303772</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3286037445068</t>
+    <t xml:space="preserve">13.3286046981812</t>
   </si>
   <si>
     <t xml:space="preserve">13.9547815322876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5969657897949</t>
+    <t xml:space="preserve">13.5969667434692</t>
   </si>
   <si>
     <t xml:space="preserve">13.6864204406738</t>
   </si>
   <si>
-    <t xml:space="preserve">13.865327835083</t>
+    <t xml:space="preserve">13.8653268814087</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4020500183105</t>
+    <t xml:space="preserve">14.4020509719849</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2965888977051</t>
+    <t xml:space="preserve">15.2965879440308</t>
   </si>
   <si>
     <t xml:space="preserve">15.2071342468262</t>
@@ -1016,10 +1016,10 @@
     <t xml:space="preserve">14.5809564590454</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7598638534546</t>
+    <t xml:space="preserve">14.7598648071289</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4915056228638</t>
+    <t xml:space="preserve">14.4915046691895</t>
   </si>
   <si>
     <t xml:space="preserve">14.5400876998901</t>
@@ -60692,7 +60692,7 @@
     </row>
     <row r="2257">
       <c r="A2257" s="1" t="n">
-        <v>45946.6493865741</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2257" t="n">
         <v>750</v>
@@ -60713,6 +60713,32 @@
         <v>543</v>
       </c>
       <c r="H2257" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="A2258" s="1" t="n">
+        <v>45947.3624537037</v>
+      </c>
+      <c r="B2258" t="n">
+        <v>750</v>
+      </c>
+      <c r="C2258" t="n">
+        <v>38.2000007629395</v>
+      </c>
+      <c r="D2258" t="n">
+        <v>38</v>
+      </c>
+      <c r="E2258" t="n">
+        <v>38.2000007629395</v>
+      </c>
+      <c r="F2258" t="n">
+        <v>38</v>
+      </c>
+      <c r="G2258" t="s">
+        <v>537</v>
+      </c>
+      <c r="H2258" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -44,46 +44,46 @@
     <t xml:space="preserve">FPE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42625832557678</t>
+    <t xml:space="preserve">2.42625856399536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43408489227295</t>
+    <t xml:space="preserve">2.43408536911011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41060495376587</t>
+    <t xml:space="preserve">2.41060519218445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45756530761719</t>
+    <t xml:space="preserve">2.45756506919861</t>
   </si>
   <si>
     <t xml:space="preserve">2.39495182037354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233880996704</t>
+    <t xml:space="preserve">2.33233904838562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41843199729919</t>
+    <t xml:space="preserve">2.41843175888062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3558189868927</t>
+    <t xml:space="preserve">2.35581874847412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37147212028503</t>
+    <t xml:space="preserve">2.37147188186646</t>
   </si>
   <si>
     <t xml:space="preserve">2.50452518463135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36364555358887</t>
+    <t xml:space="preserve">2.36364531517029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44973850250244</t>
+    <t xml:space="preserve">2.44973826408386</t>
   </si>
   <si>
     <t xml:space="preserve">2.37303757667542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34955787658691</t>
+    <t xml:space="preserve">2.34955763816833</t>
   </si>
   <si>
     <t xml:space="preserve">2.46382641792297</t>
@@ -95,19 +95,19 @@
     <t xml:space="preserve">2.45443439483643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34799194335938</t>
+    <t xml:space="preserve">2.34799242019653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48104500770569</t>
+    <t xml:space="preserve">2.48104476928711</t>
   </si>
   <si>
     <t xml:space="preserve">2.3792986869812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38556027412415</t>
+    <t xml:space="preserve">2.38556003570557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44191193580627</t>
+    <t xml:space="preserve">2.4419116973877</t>
   </si>
   <si>
     <t xml:space="preserve">2.78002238273621</t>
@@ -116,22 +116,22 @@
     <t xml:space="preserve">3.36702084541321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62529969215393</t>
+    <t xml:space="preserve">3.62529945373535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31066846847534</t>
+    <t xml:space="preserve">3.31066942214966</t>
   </si>
   <si>
     <t xml:space="preserve">3.25588226318359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20266127586365</t>
+    <t xml:space="preserve">3.20266103744507</t>
   </si>
   <si>
     <t xml:space="preserve">3.05239009857178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09152293205261</t>
+    <t xml:space="preserve">3.09152317047119</t>
   </si>
   <si>
     <t xml:space="preserve">3.04456329345703</t>
@@ -143,88 +143,88 @@
     <t xml:space="preserve">3.03830194473267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15413618087769</t>
+    <t xml:space="preserve">3.15413641929626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30910396575928</t>
+    <t xml:space="preserve">3.3091037273407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30284237861633</t>
+    <t xml:space="preserve">3.30284190177917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35762882232666</t>
+    <t xml:space="preserve">3.35762858390808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57677483558655</t>
+    <t xml:space="preserve">3.57677459716797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52198839187622</t>
+    <t xml:space="preserve">3.52198815345764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40458869934082</t>
+    <t xml:space="preserve">3.4045889377594</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59242844581604</t>
+    <t xml:space="preserve">3.59242820739746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58460116386414</t>
+    <t xml:space="preserve">3.58460187911987</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67852115631104</t>
+    <t xml:space="preserve">3.6785204410553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60025453567505</t>
+    <t xml:space="preserve">3.60025405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59555888175964</t>
+    <t xml:space="preserve">3.59555840492249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632255554199</t>
+    <t xml:space="preserve">3.32632231712341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29501581192017</t>
+    <t xml:space="preserve">3.29501557350159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37484765052795</t>
+    <t xml:space="preserve">3.3748471736908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38267397880554</t>
+    <t xml:space="preserve">3.38267350196838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44372200965881</t>
+    <t xml:space="preserve">3.44372177124023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5908625125885</t>
+    <t xml:space="preserve">3.59086275100708</t>
   </si>
   <si>
     <t xml:space="preserve">3.47972464561462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42650246620178</t>
+    <t xml:space="preserve">3.42650318145752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41241526603699</t>
+    <t xml:space="preserve">3.41241550445557</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24022912979126</t>
+    <t xml:space="preserve">3.24022936820984</t>
   </si>
   <si>
     <t xml:space="preserve">3.21048808097839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28405857086182</t>
+    <t xml:space="preserve">3.28405833244324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16196250915527</t>
+    <t xml:space="preserve">3.16196274757385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20892238616943</t>
+    <t xml:space="preserve">3.20892286300659</t>
   </si>
   <si>
     <t xml:space="preserve">3.13848304748535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23240280151367</t>
+    <t xml:space="preserve">3.23240232467651</t>
   </si>
   <si>
     <t xml:space="preserve">3.31849527359009</t>
@@ -233,22 +233,22 @@
     <t xml:space="preserve">3.27623176574707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18857312202454</t>
+    <t xml:space="preserve">3.18857288360596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14317893981934</t>
+    <t xml:space="preserve">3.14317846298218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11500334739685</t>
+    <t xml:space="preserve">3.11500263214111</t>
   </si>
   <si>
     <t xml:space="preserve">3.00073409080505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97412323951721</t>
+    <t xml:space="preserve">2.97412347793579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06021642684937</t>
+    <t xml:space="preserve">3.06021666526794</t>
   </si>
   <si>
     <t xml:space="preserve">2.90368366241455</t>
@@ -257,22 +257,22 @@
     <t xml:space="preserve">2.89585709571838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82854819297791</t>
+    <t xml:space="preserve">2.82854795455933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83637452125549</t>
+    <t xml:space="preserve">2.83637428283691</t>
   </si>
   <si>
     <t xml:space="preserve">2.90994477272034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491208076477</t>
+    <t xml:space="preserve">3.06491231918335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13065600395203</t>
+    <t xml:space="preserve">3.13065648078918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14474415779114</t>
+    <t xml:space="preserve">3.14474439620972</t>
   </si>
   <si>
     <t xml:space="preserve">3.21361827850342</t>
@@ -284,43 +284,43 @@
     <t xml:space="preserve">3.35919404029846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36388993263245</t>
+    <t xml:space="preserve">3.36388969421387</t>
   </si>
   <si>
     <t xml:space="preserve">3.91332006454468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34378576278687</t>
+    <t xml:space="preserve">4.34378528594971</t>
   </si>
   <si>
     <t xml:space="preserve">4.7938175201416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47864866256714</t>
+    <t xml:space="preserve">5.47864818572998</t>
   </si>
   <si>
     <t xml:space="preserve">6.09303951263428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41603517532349</t>
+    <t xml:space="preserve">5.41603469848633</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71344757080078</t>
+    <t xml:space="preserve">5.71344804763794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56865406036377</t>
+    <t xml:space="preserve">5.56865453720093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41994857788086</t>
+    <t xml:space="preserve">5.41994905471802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16558313369751</t>
+    <t xml:space="preserve">5.16558265686035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94643640518188</t>
+    <t xml:space="preserve">4.94643688201904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7038106918335</t>
+    <t xml:space="preserve">4.70381116867065</t>
   </si>
   <si>
     <t xml:space="preserve">4.6764178276062</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">5.55691480636597</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30646276473999</t>
+    <t xml:space="preserve">5.30646181106567</t>
   </si>
   <si>
     <t xml:space="preserve">5.22428226470947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19688844680786</t>
+    <t xml:space="preserve">5.19688940048218</t>
   </si>
   <si>
     <t xml:space="preserve">5.32211542129517</t>
@@ -350,40 +350,40 @@
     <t xml:space="preserve">5.36907529830933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29080963134766</t>
+    <t xml:space="preserve">5.2908091545105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1734094619751</t>
+    <t xml:space="preserve">5.17340993881226</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09514331817627</t>
+    <t xml:space="preserve">5.09514284133911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2203688621521</t>
+    <t xml:space="preserve">5.22036981582642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10296964645386</t>
+    <t xml:space="preserve">5.10296869277954</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9933967590332</t>
+    <t xml:space="preserve">4.99339723587036</t>
   </si>
   <si>
     <t xml:space="preserve">5.15384244918823</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98557043075562</t>
+    <t xml:space="preserve">4.98556995391846</t>
   </si>
   <si>
     <t xml:space="preserve">4.7585973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77033758163452</t>
+    <t xml:space="preserve">4.77033710479736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86425685882568</t>
+    <t xml:space="preserve">4.86425733566284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88773632049561</t>
+    <t xml:space="preserve">4.88773679733276</t>
   </si>
   <si>
     <t xml:space="preserve">4.83295059204102</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">4.7233772277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.688157081604</t>
+    <t xml:space="preserve">4.68815755844116</t>
   </si>
   <si>
     <t xml:space="preserve">4.78207731246948</t>
@@ -407,106 +407,106 @@
     <t xml:space="preserve">4.87599658966064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03644275665283</t>
+    <t xml:space="preserve">5.03644371032715</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92687034606934</t>
+    <t xml:space="preserve">4.92686986923218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81338357925415</t>
+    <t xml:space="preserve">4.81338405609131</t>
   </si>
   <si>
     <t xml:space="preserve">4.86034393310547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00122308731079</t>
+    <t xml:space="preserve">5.00122356414795</t>
   </si>
   <si>
     <t xml:space="preserve">4.77425050735474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82120990753174</t>
+    <t xml:space="preserve">4.8212103843689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69989728927612</t>
+    <t xml:space="preserve">4.69989824295044</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69598388671875</t>
+    <t xml:space="preserve">4.69598484039307</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90730333328247</t>
+    <t xml:space="preserve">4.90730381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20471572875977</t>
+    <t xml:space="preserve">5.20471620559692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43951463699341</t>
+    <t xml:space="preserve">5.43951511383057</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28298187255859</t>
+    <t xml:space="preserve">5.28298234939575</t>
   </si>
   <si>
     <t xml:space="preserve">5.24384880065918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36124801635742</t>
+    <t xml:space="preserve">5.36124897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40038204193115</t>
+    <t xml:space="preserve">5.40038251876831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51778173446655</t>
+    <t xml:space="preserve">5.51778125762939</t>
   </si>
   <si>
     <t xml:space="preserve">5.63518095016479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96991729736328</t>
+    <t xml:space="preserve">4.96991634368896</t>
   </si>
   <si>
     <t xml:space="preserve">4.93078374862671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85251665115356</t>
+    <t xml:space="preserve">4.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12645053863525</t>
+    <t xml:space="preserve">5.12644958496094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04818296432495</t>
+    <t xml:space="preserve">5.04818344116211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08731603622437</t>
+    <t xml:space="preserve">5.08731651306152</t>
   </si>
   <si>
     <t xml:space="preserve">5.59604787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26159763336182</t>
+    <t xml:space="preserve">5.26159715652466</t>
   </si>
   <si>
     <t xml:space="preserve">5.42103958129883</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34131860733032</t>
+    <t xml:space="preserve">5.34131813049316</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22173738479614</t>
+    <t xml:space="preserve">5.22173690795898</t>
   </si>
   <si>
     <t xml:space="preserve">5.14201545715332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1021556854248</t>
+    <t xml:space="preserve">5.10215520858765</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18187570571899</t>
+    <t xml:space="preserve">5.18187618255615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.381178855896</t>
+    <t xml:space="preserve">5.38117933273315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30145740509033</t>
+    <t xml:space="preserve">5.30145788192749</t>
   </si>
   <si>
     <t xml:space="preserve">4.90285205841064</t>
@@ -515,16 +515,16 @@
     <t xml:space="preserve">5.50076103210449</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46089935302734</t>
+    <t xml:space="preserve">5.46090030670166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58048248291016</t>
+    <t xml:space="preserve">5.580482006073</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54062128067017</t>
+    <t xml:space="preserve">5.54062175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62034225463867</t>
+    <t xml:space="preserve">5.62034320831299</t>
   </si>
   <si>
     <t xml:space="preserve">4.94271278381348</t>
@@ -533,46 +533,46 @@
     <t xml:space="preserve">4.98257350921631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8231315612793</t>
+    <t xml:space="preserve">4.82313108444214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06229496002197</t>
+    <t xml:space="preserve">5.06229448318481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02243375778198</t>
+    <t xml:space="preserve">5.02243423461914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74340963363647</t>
+    <t xml:space="preserve">4.74341011047363</t>
   </si>
   <si>
     <t xml:space="preserve">4.78327035903931</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86299180984497</t>
+    <t xml:space="preserve">4.86299133300781</t>
   </si>
   <si>
     <t xml:space="preserve">5.73992443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81964588165283</t>
+    <t xml:space="preserve">5.81964540481567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70006418228149</t>
+    <t xml:space="preserve">5.70006465911865</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66020345687866</t>
+    <t xml:space="preserve">5.6602029800415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77978563308716</t>
+    <t xml:space="preserve">5.77978467941284</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85950565338135</t>
+    <t xml:space="preserve">5.85950613021851</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97908782958984</t>
+    <t xml:space="preserve">5.979088306427</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29797220230103</t>
+    <t xml:space="preserve">6.29797315597534</t>
   </si>
   <si>
     <t xml:space="preserve">6.13853025436401</t>
@@ -584,19 +584,19 @@
     <t xml:space="preserve">6.21825122833252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09866952896118</t>
+    <t xml:space="preserve">6.09867000579834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3851842880249</t>
+    <t xml:space="preserve">6.38518476486206</t>
   </si>
   <si>
     <t xml:space="preserve">6.25998497009277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30171775817871</t>
+    <t xml:space="preserve">6.30171823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17651891708374</t>
+    <t xml:space="preserve">6.17651844024658</t>
   </si>
   <si>
     <t xml:space="preserve">6.426917552948</t>
@@ -605,115 +605,115 @@
     <t xml:space="preserve">6.34345149993896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46865129470825</t>
+    <t xml:space="preserve">6.46865081787109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9678521156311</t>
+    <t xml:space="preserve">5.96785306930542</t>
   </si>
   <si>
     <t xml:space="preserve">6.0095853805542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13478469848633</t>
+    <t xml:space="preserve">6.13478517532349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05131912231445</t>
+    <t xml:space="preserve">6.05131816864014</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92611837387085</t>
+    <t xml:space="preserve">5.92611885070801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09305191040039</t>
+    <t xml:space="preserve">6.09305143356323</t>
   </si>
   <si>
     <t xml:space="preserve">6.51038408279419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84265279769897</t>
+    <t xml:space="preserve">5.84265232086182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88438558578491</t>
+    <t xml:space="preserve">5.88438606262207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05291652679443</t>
+    <t xml:space="preserve">7.05291604995728</t>
   </si>
   <si>
     <t xml:space="preserve">8.09624671936035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.804114818573</t>
+    <t xml:space="preserve">7.80411529541016</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63718032836914</t>
+    <t xml:space="preserve">7.63718128204346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55371522903442</t>
+    <t xml:space="preserve">7.55371475219727</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3450493812561</t>
+    <t xml:space="preserve">7.34504842758179</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17811632156372</t>
+    <t xml:space="preserve">7.17811584472656</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51198196411133</t>
+    <t xml:space="preserve">7.51198148727417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47024869918823</t>
+    <t xml:space="preserve">7.47024774551392</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30331516265869</t>
+    <t xml:space="preserve">7.30331563949585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851495742798</t>
+    <t xml:space="preserve">7.42851448059082</t>
   </si>
   <si>
     <t xml:space="preserve">7.26158237457275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3867826461792</t>
+    <t xml:space="preserve">7.38678216934204</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96944999694824</t>
+    <t xml:space="preserve">6.9694504737854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2198486328125</t>
+    <t xml:space="preserve">7.21984910964966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544801712036</t>
+    <t xml:space="preserve">7.59544897079468</t>
   </si>
   <si>
     <t xml:space="preserve">7.7623815536499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84584808349609</t>
+    <t xml:space="preserve">7.84584712982178</t>
   </si>
   <si>
     <t xml:space="preserve">7.67891407012939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01118230819702</t>
+    <t xml:space="preserve">7.01118278503418</t>
   </si>
   <si>
     <t xml:space="preserve">7.09464979171753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92771673202515</t>
+    <t xml:space="preserve">6.92771625518799</t>
   </si>
   <si>
     <t xml:space="preserve">6.76078367233276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80251598358154</t>
+    <t xml:space="preserve">6.8025164604187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71905088424683</t>
+    <t xml:space="preserve">6.71905040740967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8442497253418</t>
+    <t xml:space="preserve">6.84424924850464</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59385013580322</t>
+    <t xml:space="preserve">6.59385108947754</t>
   </si>
   <si>
     <t xml:space="preserve">6.67731666564941</t>
@@ -725,37 +725,37 @@
     <t xml:space="preserve">5.75918626785278</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71745204925537</t>
+    <t xml:space="preserve">5.71745252609253</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80091905593872</t>
+    <t xml:space="preserve">5.80091953277588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67571973800659</t>
+    <t xml:space="preserve">5.67571926116943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5922532081604</t>
+    <t xml:space="preserve">5.59225273132324</t>
   </si>
   <si>
     <t xml:space="preserve">5.6339864730835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46705389022827</t>
+    <t xml:space="preserve">5.46705341339111</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55051946640015</t>
+    <t xml:space="preserve">5.5505199432373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17492055892944</t>
+    <t xml:space="preserve">5.1749210357666</t>
   </si>
   <si>
     <t xml:space="preserve">5.25838756561279</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38358640670776</t>
+    <t xml:space="preserve">5.38358688354492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13638257980347</t>
+    <t xml:space="preserve">7.13638353347778</t>
   </si>
   <si>
     <t xml:space="preserve">7.47247123718262</t>
@@ -764,28 +764,28 @@
     <t xml:space="preserve">7.25269222259521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2966480255127</t>
+    <t xml:space="preserve">7.29664754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20873641967773</t>
+    <t xml:space="preserve">7.20873594284058</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1647801399231</t>
+    <t xml:space="preserve">7.16478061676025</t>
   </si>
   <si>
     <t xml:space="preserve">7.07686996459961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98895788192749</t>
+    <t xml:space="preserve">6.98895835876465</t>
   </si>
   <si>
     <t xml:space="preserve">7.03291368484497</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94500160217285</t>
+    <t xml:space="preserve">6.94500255584717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85709142684937</t>
+    <t xml:space="preserve">6.85709095001221</t>
   </si>
   <si>
     <t xml:space="preserve">6.72522401809692</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">6.90104675292969</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63731241226196</t>
+    <t xml:space="preserve">6.63731288909912</t>
   </si>
   <si>
     <t xml:space="preserve">7.12082529067993</t>
@@ -812,25 +812,25 @@
     <t xml:space="preserve">7.5164270401001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56038284301758</t>
+    <t xml:space="preserve">7.56038188934326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851543426514</t>
+    <t xml:space="preserve">7.42851495742798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73620557785034</t>
+    <t xml:space="preserve">7.73620462417603</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69224882125854</t>
+    <t xml:space="preserve">7.69224977493286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829397201538</t>
+    <t xml:space="preserve">7.64829349517822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78247451782227</t>
+    <t xml:space="preserve">7.78247404098511</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82720041275024</t>
+    <t xml:space="preserve">7.82720184326172</t>
   </si>
   <si>
     <t xml:space="preserve">7.73774671554565</t>
@@ -839,10 +839,10 @@
     <t xml:space="preserve">7.69302082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60356712341309</t>
+    <t xml:space="preserve">7.60356616973877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91665554046631</t>
+    <t xml:space="preserve">7.91665458679199</t>
   </si>
   <si>
     <t xml:space="preserve">7.87192869186401</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">8.2297420501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76646614074707</t>
+    <t xml:space="preserve">8.76646518707275</t>
   </si>
   <si>
     <t xml:space="preserve">8.58755779266357</t>
@@ -869,10 +869,10 @@
     <t xml:space="preserve">8.54283046722412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40865039825439</t>
+    <t xml:space="preserve">8.40864944458008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27447032928467</t>
+    <t xml:space="preserve">8.27446937561035</t>
   </si>
   <si>
     <t xml:space="preserve">8.45337772369385</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">8.67701148986816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49810314178467</t>
+    <t xml:space="preserve">8.49810409545898</t>
   </si>
   <si>
     <t xml:space="preserve">8.81119251251221</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">8.85591888427734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03482532501221</t>
+    <t xml:space="preserve">9.03482627868652</t>
   </si>
   <si>
     <t xml:space="preserve">10.3766326904297</t>
@@ -902,19 +902,19 @@
     <t xml:space="preserve">11.4500770568848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.734447479248</t>
+    <t xml:space="preserve">10.7344465255737</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0922613143921</t>
+    <t xml:space="preserve">11.0922622680664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9133539199829</t>
+    <t xml:space="preserve">10.9133548736572</t>
   </si>
   <si>
     <t xml:space="preserve">11.181715965271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3606233596802</t>
+    <t xml:space="preserve">11.3606224060059</t>
   </si>
   <si>
     <t xml:space="preserve">11.6289844512939</t>
@@ -926,13 +926,13 @@
     <t xml:space="preserve">11.2711696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5555391311646</t>
+    <t xml:space="preserve">10.5555400848389</t>
   </si>
   <si>
     <t xml:space="preserve">10.2871789932251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0028076171875</t>
+    <t xml:space="preserve">11.0028085708618</t>
   </si>
   <si>
     <t xml:space="preserve">10.6449928283691</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">10.1082706451416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1977233886719</t>
+    <t xml:space="preserve">10.1977243423462</t>
   </si>
   <si>
     <t xml:space="preserve">9.75045585632324</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">12.6129751205444</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9707899093628</t>
+    <t xml:space="preserve">12.9707908630371</t>
   </si>
   <si>
     <t xml:space="preserve">14.0442352294922</t>
@@ -965,13 +965,13 @@
     <t xml:space="preserve">13.7758731842041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.507513999939</t>
+    <t xml:space="preserve">13.5075130462646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2391519546509</t>
+    <t xml:space="preserve">13.2391510009766</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0602436065674</t>
+    <t xml:space="preserve">13.0602445602417</t>
   </si>
   <si>
     <t xml:space="preserve">13.4180593490601</t>
@@ -980,10 +980,10 @@
     <t xml:space="preserve">12.8813362121582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7918834686279</t>
+    <t xml:space="preserve">12.7918825149536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7024297714233</t>
+    <t xml:space="preserve">12.702428817749</t>
   </si>
   <si>
     <t xml:space="preserve">13.149697303772</t>
@@ -995,34 +995,34 @@
     <t xml:space="preserve">13.9547815322876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5969667434692</t>
+    <t xml:space="preserve">13.5969657897949</t>
   </si>
   <si>
     <t xml:space="preserve">13.6864204406738</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8653268814087</t>
+    <t xml:space="preserve">13.865327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4020509719849</t>
+    <t xml:space="preserve">14.4020500183105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2965879440308</t>
+    <t xml:space="preserve">15.2965869903564</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2071342468262</t>
+    <t xml:space="preserve">15.2071323394775</t>
   </si>
   <si>
     <t xml:space="preserve">14.5809564590454</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7598648071289</t>
+    <t xml:space="preserve">14.7598657608032</t>
   </si>
   <si>
     <t xml:space="preserve">14.4915046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5400876998901</t>
+    <t xml:space="preserve">14.5400886535645</t>
   </si>
   <si>
     <t xml:space="preserve">14.3560371398926</t>
@@ -1031,22 +1031,22 @@
     <t xml:space="preserve">14.2640104293823</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1719846725464</t>
+    <t xml:space="preserve">14.1719837188721</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8161668777466</t>
+    <t xml:space="preserve">14.8161659240723</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6321134567261</t>
+    <t xml:space="preserve">14.6321144104004</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3683223724365</t>
+    <t xml:space="preserve">15.3683214187622</t>
   </si>
   <si>
     <t xml:space="preserve">15.5523738861084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1045265197754</t>
+    <t xml:space="preserve">16.104528427124</t>
   </si>
   <si>
     <t xml:space="preserve">16.3806056976318</t>
@@ -1055,16 +1055,16 @@
     <t xml:space="preserve">15.9204750061035</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2088394165039</t>
+    <t xml:space="preserve">17.2088413238525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3008651733398</t>
+    <t xml:space="preserve">17.3008632659912</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4849147796631</t>
+    <t xml:space="preserve">17.4849166870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5769424438477</t>
+    <t xml:space="preserve">17.576940536499</t>
   </si>
   <si>
     <t xml:space="preserve">17.6689682006836</t>
@@ -1085,13 +1085,13 @@
     <t xml:space="preserve">21.5340557098389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3745727539062</t>
+    <t xml:space="preserve">23.3745708465576</t>
   </si>
   <si>
-    <t xml:space="preserve">22.270263671875</t>
+    <t xml:space="preserve">22.2702617645264</t>
   </si>
   <si>
-    <t xml:space="preserve">22.822416305542</t>
+    <t xml:space="preserve">22.8224182128906</t>
   </si>
   <si>
     <t xml:space="preserve">20.6137943267822</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">23.9267272949219</t>
   </si>
   <si>
-    <t xml:space="preserve">24.662935256958</t>
+    <t xml:space="preserve">24.6629333496094</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8469848632812</t>
+    <t xml:space="preserve">24.8469867706299</t>
   </si>
   <si>
     <t xml:space="preserve">24.2948303222656</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">23.1905212402344</t>
   </si>
   <si>
-    <t xml:space="preserve">25.215087890625</t>
+    <t xml:space="preserve">25.2150897979736</t>
   </si>
   <si>
     <t xml:space="preserve">22.4543132781982</t>
@@ -1151,19 +1151,19 @@
     <t xml:space="preserve">27.975866317749</t>
   </si>
   <si>
-    <t xml:space="preserve">30.920690536499</t>
+    <t xml:space="preserve">30.9206924438477</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0801753997803</t>
+    <t xml:space="preserve">29.0801773071289</t>
   </si>
   <si>
-    <t xml:space="preserve">30.736644744873</t>
+    <t xml:space="preserve">30.7366428375244</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3685398101807</t>
+    <t xml:space="preserve">30.3685417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2642269134521</t>
+    <t xml:space="preserve">29.2642288208008</t>
   </si>
   <si>
     <t xml:space="preserve">31.4728507995605</t>
@@ -1175,13 +1175,13 @@
     <t xml:space="preserve">34.7857818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8655204772949</t>
+    <t xml:space="preserve">33.8655166625977</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4974174499512</t>
+    <t xml:space="preserve">33.4974212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1844844818115</t>
+    <t xml:space="preserve">30.1844863891602</t>
   </si>
   <si>
     <t xml:space="preserve">27.4237098693848</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">28.7120742797852</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3439693450928</t>
+    <t xml:space="preserve">28.3439674377441</t>
   </si>
   <si>
     <t xml:space="preserve">27.055606842041</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">25.3991432189941</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7672462463379</t>
+    <t xml:space="preserve">25.7672443389893</t>
   </si>
   <si>
     <t xml:space="preserve">25.0310382843018</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">27.6077632904053</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5525894165039</t>
+    <t xml:space="preserve">30.5525913238525</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6323337554932</t>
+    <t xml:space="preserve">29.6323318481445</t>
   </si>
   <si>
     <t xml:space="preserve">30.0004329681396</t>
@@ -1244,16 +1244,16 @@
     <t xml:space="preserve">32.3931121826172</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2090530395508</t>
+    <t xml:space="preserve">32.209056854248</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2887992858887</t>
+    <t xml:space="preserve">31.2887954711914</t>
   </si>
   <si>
     <t xml:space="preserve">31.6569023132324</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0250053405762</t>
+    <t xml:space="preserve">32.0250015258789</t>
   </si>
   <si>
     <t xml:space="preserve">32.0337677001953</t>
@@ -60718,7 +60718,7 @@
     </row>
     <row r="2258">
       <c r="A2258" s="1" t="n">
-        <v>45947.3624537037</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2258" t="n">
         <v>750</v>
@@ -60739,6 +60739,32 @@
         <v>537</v>
       </c>
       <c r="H2258" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="A2259" s="1" t="n">
+        <v>45950.4102083333</v>
+      </c>
+      <c r="B2259" t="n">
+        <v>750</v>
+      </c>
+      <c r="C2259" t="n">
+        <v>38.5999984741211</v>
+      </c>
+      <c r="D2259" t="n">
+        <v>38.5999984741211</v>
+      </c>
+      <c r="E2259" t="n">
+        <v>38.5999984741211</v>
+      </c>
+      <c r="F2259" t="n">
+        <v>38.5999984741211</v>
+      </c>
+      <c r="G2259" t="s">
+        <v>536</v>
+      </c>
+      <c r="H2259" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">FPE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42625832557678</t>
+    <t xml:space="preserve">2.4262580871582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43408513069153</t>
+    <t xml:space="preserve">2.43408536911011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41060495376587</t>
+    <t xml:space="preserve">2.41060519218445</t>
   </si>
   <si>
     <t xml:space="preserve">2.45756506919861</t>
@@ -59,34 +59,34 @@
     <t xml:space="preserve">2.39495205879211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233880996704</t>
+    <t xml:space="preserve">2.33233904838562</t>
   </si>
   <si>
     <t xml:space="preserve">2.41843175888062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35581874847412</t>
+    <t xml:space="preserve">2.35581851005554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37147188186646</t>
+    <t xml:space="preserve">2.37147212028503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50452518463135</t>
+    <t xml:space="preserve">2.50452494621277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36364531517029</t>
+    <t xml:space="preserve">2.36364555358887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44973874092102</t>
+    <t xml:space="preserve">2.44973850250244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37303733825684</t>
+    <t xml:space="preserve">2.37303709983826</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34955739974976</t>
+    <t xml:space="preserve">2.34955763816833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46382641792297</t>
+    <t xml:space="preserve">2.46382665634155</t>
   </si>
   <si>
     <t xml:space="preserve">2.38712525367737</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">2.34799218177795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48104500770569</t>
+    <t xml:space="preserve">2.48104548454285</t>
   </si>
   <si>
     <t xml:space="preserve">2.3792986869812</t>
@@ -107,34 +107,34 @@
     <t xml:space="preserve">2.38556003570557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44191193580627</t>
+    <t xml:space="preserve">2.4419116973877</t>
   </si>
   <si>
     <t xml:space="preserve">2.78002262115479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36702084541321</t>
+    <t xml:space="preserve">3.36702108383179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62529945373535</t>
+    <t xml:space="preserve">3.62530016899109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3106689453125</t>
+    <t xml:space="preserve">3.31066918373108</t>
   </si>
   <si>
     <t xml:space="preserve">3.25588226318359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20266103744507</t>
+    <t xml:space="preserve">3.20266127586365</t>
   </si>
   <si>
     <t xml:space="preserve">3.0523898601532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09152317047119</t>
+    <t xml:space="preserve">3.09152293205261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04456281661987</t>
+    <t xml:space="preserve">3.04456353187561</t>
   </si>
   <si>
     <t xml:space="preserve">3.03673672676086</t>
@@ -146,25 +146,25 @@
     <t xml:space="preserve">3.15413665771484</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3091037273407</t>
+    <t xml:space="preserve">3.30910396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30284214019775</t>
+    <t xml:space="preserve">3.30284190177917</t>
   </si>
   <si>
     <t xml:space="preserve">3.35762882232666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57677507400513</t>
+    <t xml:space="preserve">3.57677483558655</t>
   </si>
   <si>
     <t xml:space="preserve">3.52198815345764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40458798408508</t>
+    <t xml:space="preserve">3.40458846092224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59242820739746</t>
+    <t xml:space="preserve">3.5924277305603</t>
   </si>
   <si>
     <t xml:space="preserve">3.58460116386414</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">3.67852067947388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60025453567505</t>
+    <t xml:space="preserve">3.60025405883789</t>
   </si>
   <si>
     <t xml:space="preserve">3.59555864334106</t>
@@ -182,40 +182,40 @@
     <t xml:space="preserve">3.32632207870483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29501557350159</t>
+    <t xml:space="preserve">3.29501581192017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37484741210938</t>
+    <t xml:space="preserve">3.37484693527222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38267397880554</t>
+    <t xml:space="preserve">3.38267421722412</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44372177124023</t>
+    <t xml:space="preserve">3.44372224807739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59086203575134</t>
+    <t xml:space="preserve">3.59086227416992</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47972416877747</t>
+    <t xml:space="preserve">3.47972440719604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4265034198761</t>
+    <t xml:space="preserve">3.42650318145752</t>
   </si>
   <si>
     <t xml:space="preserve">3.41241526603699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24022912979126</t>
+    <t xml:space="preserve">3.24022889137268</t>
   </si>
   <si>
     <t xml:space="preserve">3.21048808097839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28405857086182</t>
+    <t xml:space="preserve">3.28405833244324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16196298599243</t>
+    <t xml:space="preserve">3.16196274757385</t>
   </si>
   <si>
     <t xml:space="preserve">3.20892262458801</t>
@@ -227,76 +227,76 @@
     <t xml:space="preserve">3.23240256309509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31849503517151</t>
+    <t xml:space="preserve">3.31849527359009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27623152732849</t>
+    <t xml:space="preserve">3.27623176574707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18857312202454</t>
+    <t xml:space="preserve">3.18857336044312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14317846298218</t>
+    <t xml:space="preserve">3.14317870140076</t>
   </si>
   <si>
     <t xml:space="preserve">3.11500287055969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00073385238647</t>
+    <t xml:space="preserve">3.00073409080505</t>
   </si>
   <si>
     <t xml:space="preserve">2.97412323951721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06021618843079</t>
+    <t xml:space="preserve">3.06021666526794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90368342399597</t>
+    <t xml:space="preserve">2.90368366241455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89585709571838</t>
+    <t xml:space="preserve">2.89585733413696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82854771614075</t>
+    <t xml:space="preserve">2.82854795455933</t>
   </si>
   <si>
     <t xml:space="preserve">2.83637452125549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90994477272034</t>
+    <t xml:space="preserve">2.90994453430176</t>
   </si>
   <si>
     <t xml:space="preserve">3.06491208076477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13065600395203</t>
+    <t xml:space="preserve">3.13065624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14474439620972</t>
+    <t xml:space="preserve">3.14474415779114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.213618516922</t>
+    <t xml:space="preserve">3.21361827850342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28562355041504</t>
+    <t xml:space="preserve">3.28562378883362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35919380187988</t>
+    <t xml:space="preserve">3.35919404029846</t>
   </si>
   <si>
     <t xml:space="preserve">3.36388969421387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91332030296326</t>
+    <t xml:space="preserve">3.91332006454468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34378576278687</t>
+    <t xml:space="preserve">4.34378623962402</t>
   </si>
   <si>
     <t xml:space="preserve">4.79381704330444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47864866256714</t>
+    <t xml:space="preserve">5.47864818572998</t>
   </si>
   <si>
     <t xml:space="preserve">6.09303951263428</t>
@@ -305,61 +305,61 @@
     <t xml:space="preserve">5.41603517532349</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71344804763794</t>
+    <t xml:space="preserve">5.71344709396362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56865501403809</t>
+    <t xml:space="preserve">5.56865453720093</t>
   </si>
   <si>
     <t xml:space="preserve">5.41994857788086</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16558313369751</t>
+    <t xml:space="preserve">5.16558265686035</t>
   </si>
   <si>
     <t xml:space="preserve">4.94643688201904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70381116867065</t>
+    <t xml:space="preserve">4.70381164550781</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6764178276062</t>
+    <t xml:space="preserve">4.67641735076904</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0090503692627</t>
+    <t xml:space="preserve">5.00904989242554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55691432952881</t>
+    <t xml:space="preserve">5.55691480636597</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30646276473999</t>
+    <t xml:space="preserve">5.30646181106567</t>
   </si>
   <si>
     <t xml:space="preserve">5.22428226470947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19688892364502</t>
+    <t xml:space="preserve">5.19688987731934</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32211589813232</t>
+    <t xml:space="preserve">5.32211542129517</t>
   </si>
   <si>
     <t xml:space="preserve">5.47082138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36907529830933</t>
+    <t xml:space="preserve">5.36907577514648</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29080867767334</t>
+    <t xml:space="preserve">5.29080963134766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17340993881226</t>
+    <t xml:space="preserve">5.1734094619751</t>
   </si>
   <si>
     <t xml:space="preserve">5.09514331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22036981582642</t>
+    <t xml:space="preserve">5.2203688621521</t>
   </si>
   <si>
     <t xml:space="preserve">5.10296964645386</t>
@@ -368,19 +368,19 @@
     <t xml:space="preserve">4.9933967590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15384340286255</t>
+    <t xml:space="preserve">5.15384292602539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98556995391846</t>
+    <t xml:space="preserve">4.9855694770813</t>
   </si>
   <si>
     <t xml:space="preserve">4.7585973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77033758163452</t>
+    <t xml:space="preserve">4.77033662796021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86425638198853</t>
+    <t xml:space="preserve">4.86425685882568</t>
   </si>
   <si>
     <t xml:space="preserve">4.88773679733276</t>
@@ -395,16 +395,16 @@
     <t xml:space="preserve">4.82903671264648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72337675094604</t>
+    <t xml:space="preserve">4.7233772277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68815755844116</t>
+    <t xml:space="preserve">4.68815660476685</t>
   </si>
   <si>
     <t xml:space="preserve">4.78207731246948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8759970664978</t>
+    <t xml:space="preserve">4.87599658966064</t>
   </si>
   <si>
     <t xml:space="preserve">5.03644323348999</t>
@@ -416,19 +416,19 @@
     <t xml:space="preserve">4.81338405609131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86034345626831</t>
+    <t xml:space="preserve">4.86034393310547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00122356414795</t>
+    <t xml:space="preserve">5.00122308731079</t>
   </si>
   <si>
     <t xml:space="preserve">4.77425050735474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82120990753174</t>
+    <t xml:space="preserve">4.8212103843689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69989728927612</t>
+    <t xml:space="preserve">4.69989776611328</t>
   </si>
   <si>
     <t xml:space="preserve">4.69598436355591</t>
@@ -437,61 +437,61 @@
     <t xml:space="preserve">4.90730333328247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20471525192261</t>
+    <t xml:space="preserve">5.20471572875977</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43951511383057</t>
+    <t xml:space="preserve">5.43951463699341</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28298187255859</t>
+    <t xml:space="preserve">5.28298234939575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384832382202</t>
+    <t xml:space="preserve">5.24384880065918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36124849319458</t>
+    <t xml:space="preserve">5.36124897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40038156509399</t>
+    <t xml:space="preserve">5.40038204193115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51778221130371</t>
+    <t xml:space="preserve">5.51778173446655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63518142700195</t>
+    <t xml:space="preserve">5.63518047332764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96991682052612</t>
+    <t xml:space="preserve">4.96991729736328</t>
   </si>
   <si>
     <t xml:space="preserve">4.93078374862671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85251665115356</t>
+    <t xml:space="preserve">4.85251617431641</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1264500617981</t>
+    <t xml:space="preserve">5.12644958496094</t>
   </si>
   <si>
     <t xml:space="preserve">5.04818296432495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08731651306152</t>
+    <t xml:space="preserve">5.08731555938721</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59604787826538</t>
+    <t xml:space="preserve">5.5960488319397</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26159763336182</t>
+    <t xml:space="preserve">5.26159715652466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42104005813599</t>
+    <t xml:space="preserve">5.42103958129883</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34131765365601</t>
+    <t xml:space="preserve">5.34131860733032</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22173738479614</t>
+    <t xml:space="preserve">5.22173690795898</t>
   </si>
   <si>
     <t xml:space="preserve">5.14201545715332</t>
@@ -500,10 +500,10 @@
     <t xml:space="preserve">5.1021556854248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18187665939331</t>
+    <t xml:space="preserve">5.18187570571899</t>
   </si>
   <si>
-    <t xml:space="preserve">5.381178855896</t>
+    <t xml:space="preserve">5.38117933273315</t>
   </si>
   <si>
     <t xml:space="preserve">5.30145740509033</t>
@@ -512,25 +512,25 @@
     <t xml:space="preserve">4.90285205841064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50076055526733</t>
+    <t xml:space="preserve">5.50076103210449</t>
   </si>
   <si>
     <t xml:space="preserve">5.46090030670166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58048248291016</t>
+    <t xml:space="preserve">5.580482006073</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54062128067017</t>
+    <t xml:space="preserve">5.54062175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62034320831299</t>
+    <t xml:space="preserve">5.62034273147583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94271230697632</t>
+    <t xml:space="preserve">4.94271183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98257303237915</t>
+    <t xml:space="preserve">4.98257350921631</t>
   </si>
   <si>
     <t xml:space="preserve">4.82313108444214</t>
@@ -542,37 +542,37 @@
     <t xml:space="preserve">5.02243423461914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74340915679932</t>
+    <t xml:space="preserve">4.74340963363647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78327035903931</t>
+    <t xml:space="preserve">4.78327083587646</t>
   </si>
   <si>
     <t xml:space="preserve">4.86299133300781</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73992490768433</t>
+    <t xml:space="preserve">5.73992395401001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81964588165283</t>
+    <t xml:space="preserve">5.81964540481567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70006370544434</t>
+    <t xml:space="preserve">5.70006465911865</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6602029800415</t>
+    <t xml:space="preserve">5.66020393371582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77978563308716</t>
+    <t xml:space="preserve">5.77978467941284</t>
   </si>
   <si>
     <t xml:space="preserve">5.85950565338135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97908782958984</t>
+    <t xml:space="preserve">5.979088306427</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29797315597534</t>
+    <t xml:space="preserve">6.29797220230103</t>
   </si>
   <si>
     <t xml:space="preserve">6.13853025436401</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">6.05880880355835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825170516968</t>
+    <t xml:space="preserve">6.21825122833252</t>
   </si>
   <si>
     <t xml:space="preserve">6.09867000579834</t>
@@ -593,13 +593,13 @@
     <t xml:space="preserve">6.25998449325562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30171775817871</t>
+    <t xml:space="preserve">6.30171823501587</t>
   </si>
   <si>
     <t xml:space="preserve">6.17651844024658</t>
   </si>
   <si>
-    <t xml:space="preserve">6.426917552948</t>
+    <t xml:space="preserve">6.42691707611084</t>
   </si>
   <si>
     <t xml:space="preserve">6.34345102310181</t>
@@ -608,52 +608,52 @@
     <t xml:space="preserve">6.46865081787109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9678521156311</t>
+    <t xml:space="preserve">5.96785259246826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00958585739136</t>
+    <t xml:space="preserve">6.0095853805542</t>
   </si>
   <si>
     <t xml:space="preserve">6.13478469848633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05131912231445</t>
+    <t xml:space="preserve">6.05131816864014</t>
   </si>
   <si>
     <t xml:space="preserve">5.92611885070801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09305191040039</t>
+    <t xml:space="preserve">6.09305238723755</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825122833252</t>
+    <t xml:space="preserve">6.21825075149536</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51038455963135</t>
+    <t xml:space="preserve">6.51038360595703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84265279769897</t>
+    <t xml:space="preserve">5.84265184402466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88438606262207</t>
+    <t xml:space="preserve">5.88438558578491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05291604995728</t>
+    <t xml:space="preserve">7.05291700363159</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09624767303467</t>
+    <t xml:space="preserve">8.09624671936035</t>
   </si>
   <si>
     <t xml:space="preserve">7.80411529541016</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63718032836914</t>
+    <t xml:space="preserve">7.63718128204346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55371522903442</t>
+    <t xml:space="preserve">7.55371475219727</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34504890441895</t>
+    <t xml:space="preserve">7.34504985809326</t>
   </si>
   <si>
     <t xml:space="preserve">7.17811632156372</t>
@@ -662,40 +662,40 @@
     <t xml:space="preserve">7.51198148727417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47024822235107</t>
+    <t xml:space="preserve">7.47024917602539</t>
   </si>
   <si>
     <t xml:space="preserve">7.30331611633301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851543426514</t>
+    <t xml:space="preserve">7.42851591110229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26158142089844</t>
+    <t xml:space="preserve">7.2615818977356</t>
   </si>
   <si>
     <t xml:space="preserve">7.3867826461792</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96944999694824</t>
+    <t xml:space="preserve">6.9694504737854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2198486328125</t>
+    <t xml:space="preserve">7.21984767913818</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544801712036</t>
+    <t xml:space="preserve">7.59544897079468</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76238059997559</t>
+    <t xml:space="preserve">7.76238107681274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84584712982178</t>
+    <t xml:space="preserve">7.84584665298462</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67891454696655</t>
+    <t xml:space="preserve">7.67891359329224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01118278503418</t>
+    <t xml:space="preserve">7.01118326187134</t>
   </si>
   <si>
     <t xml:space="preserve">7.09464931488037</t>
@@ -704,19 +704,19 @@
     <t xml:space="preserve">6.92771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76078367233276</t>
+    <t xml:space="preserve">6.76078414916992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80251693725586</t>
+    <t xml:space="preserve">6.8025164604187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71905040740967</t>
+    <t xml:space="preserve">6.71904993057251</t>
   </si>
   <si>
     <t xml:space="preserve">6.8442497253418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59385108947754</t>
+    <t xml:space="preserve">6.59385013580322</t>
   </si>
   <si>
     <t xml:space="preserve">6.67731714248657</t>
@@ -728,22 +728,22 @@
     <t xml:space="preserve">5.75918579101562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71745252609253</t>
+    <t xml:space="preserve">5.71745300292969</t>
   </si>
   <si>
     <t xml:space="preserve">5.80091905593872</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67571973800659</t>
+    <t xml:space="preserve">5.67572021484375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59225225448608</t>
+    <t xml:space="preserve">5.59225273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63398599624634</t>
+    <t xml:space="preserve">5.6339864730835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46705389022827</t>
+    <t xml:space="preserve">5.46705341339111</t>
   </si>
   <si>
     <t xml:space="preserve">5.55051946640015</t>
@@ -758,19 +758,19 @@
     <t xml:space="preserve">5.38358688354492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13638305664062</t>
+    <t xml:space="preserve">7.13638257980347</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47247171401978</t>
+    <t xml:space="preserve">7.47247076034546</t>
   </si>
   <si>
     <t xml:space="preserve">7.25269269943237</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29664850234985</t>
+    <t xml:space="preserve">7.2966480255127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20873689651489</t>
+    <t xml:space="preserve">7.20873641967773</t>
   </si>
   <si>
     <t xml:space="preserve">7.16478061676025</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">7.07686901092529</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98895740509033</t>
+    <t xml:space="preserve">6.98895788192749</t>
   </si>
   <si>
     <t xml:space="preserve">7.03291368484497</t>
@@ -788,37 +788,37 @@
     <t xml:space="preserve">6.94500207901001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85709095001221</t>
+    <t xml:space="preserve">6.85709047317505</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72522354125977</t>
+    <t xml:space="preserve">6.72522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81313467025757</t>
+    <t xml:space="preserve">6.81313514709473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76917934417725</t>
+    <t xml:space="preserve">6.76917886734009</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90104627609253</t>
+    <t xml:space="preserve">6.90104675292969</t>
   </si>
   <si>
     <t xml:space="preserve">6.63731241226196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12082529067993</t>
+    <t xml:space="preserve">7.12082576751709</t>
   </si>
   <si>
     <t xml:space="preserve">7.34060430526733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5164270401001</t>
+    <t xml:space="preserve">7.51642656326294</t>
   </si>
   <si>
     <t xml:space="preserve">7.56038284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73620557785034</t>
+    <t xml:space="preserve">7.7362060546875</t>
   </si>
   <si>
     <t xml:space="preserve">7.69224977493286</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">7.8272008895874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73774719238281</t>
+    <t xml:space="preserve">7.73774671554565</t>
   </si>
   <si>
     <t xml:space="preserve">7.69302082061768</t>
@@ -845,28 +845,28 @@
     <t xml:space="preserve">7.60356616973877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91665506362915</t>
+    <t xml:space="preserve">7.91665410995483</t>
   </si>
   <si>
     <t xml:space="preserve">7.87192821502686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96138000488281</t>
+    <t xml:space="preserve">7.96138095855713</t>
   </si>
   <si>
     <t xml:space="preserve">8.2297420501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76646518707275</t>
+    <t xml:space="preserve">8.76646614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58755874633789</t>
+    <t xml:space="preserve">8.58755779266357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36392307281494</t>
+    <t xml:space="preserve">8.36392402648926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63228416442871</t>
+    <t xml:space="preserve">8.63228511810303</t>
   </si>
   <si>
     <t xml:space="preserve">8.54283046722412</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">8.27446937561035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45337772369385</t>
+    <t xml:space="preserve">8.45337677001953</t>
   </si>
   <si>
     <t xml:space="preserve">8.67701148986816</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">8.85591888427734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03482723236084</t>
+    <t xml:space="preserve">9.03482627868652</t>
   </si>
   <si>
     <t xml:space="preserve">10.3766326904297</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4500770568848</t>
+    <t xml:space="preserve">11.4500780105591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7344465255737</t>
+    <t xml:space="preserve">10.734447479248</t>
   </si>
   <si>
     <t xml:space="preserve">11.0922622680664</t>
@@ -914,10 +914,10 @@
     <t xml:space="preserve">10.9133548736572</t>
   </si>
   <si>
-    <t xml:space="preserve">11.181715965271</t>
+    <t xml:space="preserve">11.1817150115967</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3606233596802</t>
+    <t xml:space="preserve">11.3606224060059</t>
   </si>
   <si>
     <t xml:space="preserve">11.6289844512939</t>
@@ -932,19 +932,19 @@
     <t xml:space="preserve">10.5555391311646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2871780395508</t>
+    <t xml:space="preserve">10.2871789932251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0028085708618</t>
+    <t xml:space="preserve">11.0028076171875</t>
   </si>
   <si>
     <t xml:space="preserve">10.6449928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.46608543396</t>
+    <t xml:space="preserve">10.4660863876343</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1082706451416</t>
+    <t xml:space="preserve">10.1082715988159</t>
   </si>
   <si>
     <t xml:space="preserve">10.1977243423462</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">12.9707908630371</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0442352294922</t>
+    <t xml:space="preserve">14.0442342758179</t>
   </si>
   <si>
     <t xml:space="preserve">13.7758731842041</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">13.2391519546509</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0602436065674</t>
+    <t xml:space="preserve">13.0602445602417</t>
   </si>
   <si>
     <t xml:space="preserve">13.4180593490601</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8813352584839</t>
+    <t xml:space="preserve">12.8813362121582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7918825149536</t>
+    <t xml:space="preserve">12.7918834686279</t>
   </si>
   <si>
     <t xml:space="preserve">12.702428817749</t>
@@ -992,7 +992,7 @@
     <t xml:space="preserve">13.149697303772</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3286056518555</t>
+    <t xml:space="preserve">13.3286037445068</t>
   </si>
   <si>
     <t xml:space="preserve">13.9547815322876</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">13.5969657897949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6864213943481</t>
+    <t xml:space="preserve">13.6864204406738</t>
   </si>
   <si>
     <t xml:space="preserve">13.865327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4020509719849</t>
+    <t xml:space="preserve">14.4020500183105</t>
   </si>
   <si>
     <t xml:space="preserve">15.2965879440308</t>
@@ -1025,10 +1025,10 @@
     <t xml:space="preserve">14.4915046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5400886535645</t>
+    <t xml:space="preserve">14.5400876998901</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3560371398926</t>
+    <t xml:space="preserve">14.3560361862183</t>
   </si>
   <si>
     <t xml:space="preserve">14.2640104293823</t>
@@ -1040,10 +1040,10 @@
     <t xml:space="preserve">14.8161659240723</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6321134567261</t>
+    <t xml:space="preserve">14.6321144104004</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3683233261108</t>
+    <t xml:space="preserve">15.3683223724365</t>
   </si>
   <si>
     <t xml:space="preserve">15.5523738861084</t>
@@ -1052,25 +1052,25 @@
     <t xml:space="preserve">16.104528427124</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3806037902832</t>
+    <t xml:space="preserve">16.3806056976318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9204759597778</t>
+    <t xml:space="preserve">15.9204750061035</t>
   </si>
   <si>
     <t xml:space="preserve">17.2088394165039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3008651733398</t>
+    <t xml:space="preserve">17.3008632659912</t>
   </si>
   <si>
     <t xml:space="preserve">17.4849166870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5769424438477</t>
+    <t xml:space="preserve">17.576940536499</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6689701080322</t>
+    <t xml:space="preserve">17.6689682006836</t>
   </si>
   <si>
     <t xml:space="preserve">18.4051742553711</t>
@@ -1085,13 +1085,13 @@
     <t xml:space="preserve">20.0616397857666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5340538024902</t>
+    <t xml:space="preserve">21.5340557098389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3745727539062</t>
+    <t xml:space="preserve">23.3745708465576</t>
   </si>
   <si>
-    <t xml:space="preserve">22.270263671875</t>
+    <t xml:space="preserve">22.2702617645264</t>
   </si>
   <si>
     <t xml:space="preserve">22.822416305542</t>
@@ -1106,13 +1106,13 @@
     <t xml:space="preserve">21.902156829834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0862083435059</t>
+    <t xml:space="preserve">22.0862102508545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0064697265625</t>
+    <t xml:space="preserve">23.0064678192139</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5586242675781</t>
+    <t xml:space="preserve">23.5586261749268</t>
   </si>
   <si>
     <t xml:space="preserve">23.74267578125</t>
@@ -1121,13 +1121,13 @@
     <t xml:space="preserve">23.9267272949219</t>
   </si>
   <si>
-    <t xml:space="preserve">24.662935256958</t>
+    <t xml:space="preserve">24.6629333496094</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8469867706299</t>
+    <t xml:space="preserve">24.8469886779785</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2948322296143</t>
+    <t xml:space="preserve">24.2948303222656</t>
   </si>
   <si>
     <t xml:space="preserve">24.1107807159424</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">23.1905212402344</t>
   </si>
   <si>
-    <t xml:space="preserve">25.215087890625</t>
+    <t xml:space="preserve">25.2150897979736</t>
   </si>
   <si>
     <t xml:space="preserve">22.4543132781982</t>
@@ -1148,31 +1148,31 @@
     <t xml:space="preserve">25.9512958526611</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5034503936768</t>
+    <t xml:space="preserve">26.5034523010254</t>
   </si>
   <si>
     <t xml:space="preserve">27.975866317749</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9206924438477</t>
+    <t xml:space="preserve">30.9206943511963</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0801773071289</t>
+    <t xml:space="preserve">29.0801753997803</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7366466522217</t>
+    <t xml:space="preserve">30.736644744873</t>
   </si>
   <si>
     <t xml:space="preserve">30.3685398101807</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2642269134521</t>
+    <t xml:space="preserve">29.2642288208008</t>
   </si>
   <si>
     <t xml:space="preserve">31.4728507995605</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2336235046387</t>
+    <t xml:space="preserve">34.2336273193359</t>
   </si>
   <si>
     <t xml:space="preserve">34.7857780456543</t>
@@ -1181,19 +1181,19 @@
     <t xml:space="preserve">33.8655204772949</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4974174499512</t>
+    <t xml:space="preserve">33.4974212646484</t>
   </si>
   <si>
     <t xml:space="preserve">30.1844863891602</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4237117767334</t>
+    <t xml:space="preserve">27.4237098693848</t>
   </si>
   <si>
     <t xml:space="preserve">26.6875038146973</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5831909179688</t>
+    <t xml:space="preserve">25.5831928253174</t>
   </si>
   <si>
     <t xml:space="preserve">26.3194007873535</t>
@@ -1211,16 +1211,16 @@
     <t xml:space="preserve">28.5280208587646</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7120742797852</t>
+    <t xml:space="preserve">28.7120723724365</t>
   </si>
   <si>
     <t xml:space="preserve">28.3439693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0556087493896</t>
+    <t xml:space="preserve">27.055606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8715553283691</t>
+    <t xml:space="preserve">26.8715572357178</t>
   </si>
   <si>
     <t xml:space="preserve">25.3991413116455</t>
@@ -60771,6 +60771,58 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2260">
+      <c r="A2260" s="1" t="n">
+        <v>45951.2916666667</v>
+      </c>
+      <c r="B2260" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2260" t="n">
+        <v>38.5999984741211</v>
+      </c>
+      <c r="D2260" t="n">
+        <v>38.5999984741211</v>
+      </c>
+      <c r="E2260" t="n">
+        <v>38.5999984741211</v>
+      </c>
+      <c r="F2260" t="n">
+        <v>38.5999984741211</v>
+      </c>
+      <c r="G2260" t="s">
+        <v>537</v>
+      </c>
+      <c r="H2260" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="A2261" s="1" t="n">
+        <v>45952.5840393519</v>
+      </c>
+      <c r="B2261" t="n">
+        <v>750</v>
+      </c>
+      <c r="C2261" t="n">
+        <v>39.5999984741211</v>
+      </c>
+      <c r="D2261" t="n">
+        <v>39.2000007629395</v>
+      </c>
+      <c r="E2261" t="n">
+        <v>39.2000007629395</v>
+      </c>
+      <c r="F2261" t="n">
+        <v>39.5999984741211</v>
+      </c>
+      <c r="G2261" t="s">
+        <v>532</v>
+      </c>
+      <c r="H2261" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -47,10 +47,10 @@
     <t xml:space="preserve">2.42625832557678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43408536911011</t>
+    <t xml:space="preserve">2.43408513069153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41060543060303</t>
+    <t xml:space="preserve">2.41060519218445</t>
   </si>
   <si>
     <t xml:space="preserve">2.45756530761719</t>
@@ -59,40 +59,40 @@
     <t xml:space="preserve">2.39495205879211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3323392868042</t>
+    <t xml:space="preserve">2.33233880996704</t>
   </si>
   <si>
     <t xml:space="preserve">2.41843199729919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35581874847412</t>
+    <t xml:space="preserve">2.3558189868927</t>
   </si>
   <si>
     <t xml:space="preserve">2.37147212028503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50452518463135</t>
+    <t xml:space="preserve">2.50452494621277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36364507675171</t>
+    <t xml:space="preserve">2.36364579200745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44973874092102</t>
+    <t xml:space="preserve">2.44973850250244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37303733825684</t>
+    <t xml:space="preserve">2.37303709983826</t>
   </si>
   <si>
     <t xml:space="preserve">2.34955763816833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46382617950439</t>
+    <t xml:space="preserve">2.46382665634155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38712501525879</t>
+    <t xml:space="preserve">2.38712549209595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45443415641785</t>
+    <t xml:space="preserve">2.45443439483643</t>
   </si>
   <si>
     <t xml:space="preserve">2.34799218177795</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">2.48104500770569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3792986869812</t>
+    <t xml:space="preserve">2.37929844856262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38556003570557</t>
+    <t xml:space="preserve">2.38556027412415</t>
   </si>
   <si>
     <t xml:space="preserve">2.4419116973877</t>
@@ -113,25 +113,25 @@
     <t xml:space="preserve">2.78002262115479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36702036857605</t>
+    <t xml:space="preserve">3.36702060699463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62529993057251</t>
+    <t xml:space="preserve">3.62529969215393</t>
   </si>
   <si>
     <t xml:space="preserve">3.31066918373108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25588226318359</t>
+    <t xml:space="preserve">3.25588250160217</t>
   </si>
   <si>
     <t xml:space="preserve">3.20266127586365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05238962173462</t>
+    <t xml:space="preserve">3.05239009857178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09152317047119</t>
+    <t xml:space="preserve">3.09152293205261</t>
   </si>
   <si>
     <t xml:space="preserve">3.04456329345703</t>
@@ -143,25 +143,25 @@
     <t xml:space="preserve">3.03830170631409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15413618087769</t>
+    <t xml:space="preserve">3.15413641929626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30910348892212</t>
+    <t xml:space="preserve">3.30910396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30284214019775</t>
+    <t xml:space="preserve">3.30284190177917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35762858390808</t>
+    <t xml:space="preserve">3.35762882232666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57677507400513</t>
+    <t xml:space="preserve">3.57677483558655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52198839187622</t>
+    <t xml:space="preserve">3.5219886302948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40458822250366</t>
+    <t xml:space="preserve">3.4045889377594</t>
   </si>
   <si>
     <t xml:space="preserve">3.5924277305603</t>
@@ -173,34 +173,34 @@
     <t xml:space="preserve">3.67852067947388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60025453567505</t>
+    <t xml:space="preserve">3.60025429725647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59555888175964</t>
+    <t xml:space="preserve">3.59555792808533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632184028625</t>
+    <t xml:space="preserve">3.32632255554199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29501533508301</t>
+    <t xml:space="preserve">3.29501581192017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3748471736908</t>
+    <t xml:space="preserve">3.37484741210938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3826744556427</t>
+    <t xml:space="preserve">3.38267374038696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44372177124023</t>
+    <t xml:space="preserve">3.44372200965881</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59086275100708</t>
+    <t xml:space="preserve">3.59086227416992</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47972464561462</t>
+    <t xml:space="preserve">3.47972512245178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42650365829468</t>
+    <t xml:space="preserve">3.42650294303894</t>
   </si>
   <si>
     <t xml:space="preserve">3.41241526603699</t>
@@ -209,31 +209,31 @@
     <t xml:space="preserve">3.24022889137268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21048784255981</t>
+    <t xml:space="preserve">3.21048808097839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28405857086182</t>
+    <t xml:space="preserve">3.28405809402466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16196298599243</t>
+    <t xml:space="preserve">3.16196250915527</t>
   </si>
   <si>
     <t xml:space="preserve">3.20892262458801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13848280906677</t>
+    <t xml:space="preserve">3.13848304748535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23240256309509</t>
+    <t xml:space="preserve">3.23240280151367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31849527359009</t>
+    <t xml:space="preserve">3.31849503517151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27623128890991</t>
+    <t xml:space="preserve">3.27623176574707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18857336044312</t>
+    <t xml:space="preserve">3.18857312202454</t>
   </si>
   <si>
     <t xml:space="preserve">3.14317870140076</t>
@@ -245,52 +245,52 @@
     <t xml:space="preserve">3.00073409080505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97412371635437</t>
+    <t xml:space="preserve">2.97412323951721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06021642684937</t>
+    <t xml:space="preserve">3.06021618843079</t>
   </si>
   <si>
     <t xml:space="preserve">2.90368366241455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89585709571838</t>
+    <t xml:space="preserve">2.8958568572998</t>
   </si>
   <si>
     <t xml:space="preserve">2.82854819297791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83637475967407</t>
+    <t xml:space="preserve">2.83637428283691</t>
   </si>
   <si>
     <t xml:space="preserve">2.90994477272034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491255760193</t>
+    <t xml:space="preserve">3.06491231918335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13065600395203</t>
+    <t xml:space="preserve">3.13065624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14474415779114</t>
+    <t xml:space="preserve">3.14474391937256</t>
   </si>
   <si>
     <t xml:space="preserve">3.21361827850342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28562378883362</t>
+    <t xml:space="preserve">3.28562355041504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35919380187988</t>
+    <t xml:space="preserve">3.35919427871704</t>
   </si>
   <si>
     <t xml:space="preserve">3.36388993263245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91332006454468</t>
+    <t xml:space="preserve">3.91332030296326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34378528594971</t>
+    <t xml:space="preserve">4.34378623962402</t>
   </si>
   <si>
     <t xml:space="preserve">4.7938175201416</t>
@@ -299,49 +299,49 @@
     <t xml:space="preserve">5.47864818572998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09303903579712</t>
+    <t xml:space="preserve">6.09303951263428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41603565216064</t>
+    <t xml:space="preserve">5.41603469848633</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71344804763794</t>
+    <t xml:space="preserve">5.71344709396362</t>
   </si>
   <si>
     <t xml:space="preserve">5.56865453720093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41994905471802</t>
+    <t xml:space="preserve">5.41994857788086</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16558265686035</t>
+    <t xml:space="preserve">5.16558218002319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94643688201904</t>
+    <t xml:space="preserve">4.9464373588562</t>
   </si>
   <si>
     <t xml:space="preserve">4.70381164550781</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6764178276062</t>
+    <t xml:space="preserve">4.67641687393188</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0090503692627</t>
+    <t xml:space="preserve">5.00904989242554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55691385269165</t>
+    <t xml:space="preserve">5.55691432952881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30646228790283</t>
+    <t xml:space="preserve">5.30646181106567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22428274154663</t>
+    <t xml:space="preserve">5.22428226470947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19688987731934</t>
+    <t xml:space="preserve">5.19688940048218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32211542129517</t>
+    <t xml:space="preserve">5.32211494445801</t>
   </si>
   <si>
     <t xml:space="preserve">5.47082138061523</t>
@@ -350,52 +350,52 @@
     <t xml:space="preserve">5.36907577514648</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2908091545105</t>
+    <t xml:space="preserve">5.29080963134766</t>
   </si>
   <si>
     <t xml:space="preserve">5.1734094619751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09514284133911</t>
+    <t xml:space="preserve">5.09514331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2203688621521</t>
+    <t xml:space="preserve">5.22036933898926</t>
   </si>
   <si>
     <t xml:space="preserve">5.1029691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9933967590332</t>
+    <t xml:space="preserve">4.99339723587036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15384244918823</t>
+    <t xml:space="preserve">5.15384292602539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9855694770813</t>
+    <t xml:space="preserve">4.98556900024414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7585973739624</t>
+    <t xml:space="preserve">4.75859689712524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77033710479736</t>
+    <t xml:space="preserve">4.77033758163452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86425733566284</t>
+    <t xml:space="preserve">4.86425638198853</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88773632049561</t>
+    <t xml:space="preserve">4.88773679733276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83295106887817</t>
+    <t xml:space="preserve">4.83295059204102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75468397140503</t>
+    <t xml:space="preserve">4.75468444824219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82903814315796</t>
+    <t xml:space="preserve">4.82903718948364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7233772277832</t>
+    <t xml:space="preserve">4.72337770462036</t>
   </si>
   <si>
     <t xml:space="preserve">4.68815755844116</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">4.78207731246948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87599754333496</t>
+    <t xml:space="preserve">4.87599658966064</t>
   </si>
   <si>
     <t xml:space="preserve">5.03644323348999</t>
@@ -413,19 +413,19 @@
     <t xml:space="preserve">4.92687034606934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81338405609131</t>
+    <t xml:space="preserve">4.81338453292847</t>
   </si>
   <si>
     <t xml:space="preserve">4.86034393310547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00122356414795</t>
+    <t xml:space="preserve">5.00122261047363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77425003051758</t>
+    <t xml:space="preserve">4.77425098419189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82121086120605</t>
+    <t xml:space="preserve">4.8212103843689</t>
   </si>
   <si>
     <t xml:space="preserve">4.69989728927612</t>
@@ -437,31 +437,31 @@
     <t xml:space="preserve">4.90730381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20471668243408</t>
+    <t xml:space="preserve">5.20471572875977</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43951511383057</t>
+    <t xml:space="preserve">5.43951463699341</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28298234939575</t>
+    <t xml:space="preserve">5.28298187255859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384927749634</t>
+    <t xml:space="preserve">5.24384880065918</t>
   </si>
   <si>
     <t xml:space="preserve">5.36124801635742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40038204193115</t>
+    <t xml:space="preserve">5.40038251876831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51778125762939</t>
+    <t xml:space="preserve">5.51778173446655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63518095016479</t>
+    <t xml:space="preserve">5.63518142700195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96991634368896</t>
+    <t xml:space="preserve">4.96991682052612</t>
   </si>
   <si>
     <t xml:space="preserve">4.93078374862671</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">4.85251665115356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1264500617981</t>
+    <t xml:space="preserve">5.12644958496094</t>
   </si>
   <si>
     <t xml:space="preserve">5.04818344116211</t>
@@ -479,61 +479,61 @@
     <t xml:space="preserve">5.08731651306152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59604787826538</t>
+    <t xml:space="preserve">5.59604740142822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26159763336182</t>
+    <t xml:space="preserve">5.26159715652466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42103958129883</t>
+    <t xml:space="preserve">5.42103910446167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34131860733032</t>
+    <t xml:space="preserve">5.34131813049316</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22173738479614</t>
+    <t xml:space="preserve">5.22173690795898</t>
   </si>
   <si>
     <t xml:space="preserve">5.14201545715332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1021556854248</t>
+    <t xml:space="preserve">5.10215520858765</t>
   </si>
   <si>
     <t xml:space="preserve">5.18187618255615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38117933273315</t>
+    <t xml:space="preserve">5.381178855896</t>
   </si>
   <si>
     <t xml:space="preserve">5.30145835876465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90285158157349</t>
+    <t xml:space="preserve">4.9028525352478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50076055526733</t>
+    <t xml:space="preserve">5.50076103210449</t>
   </si>
   <si>
     <t xml:space="preserve">5.46090030670166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58048152923584</t>
+    <t xml:space="preserve">5.580482006073</t>
   </si>
   <si>
     <t xml:space="preserve">5.54062128067017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62034225463867</t>
+    <t xml:space="preserve">5.62034320831299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94271230697632</t>
+    <t xml:space="preserve">4.94271278381348</t>
   </si>
   <si>
     <t xml:space="preserve">4.98257350921631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82313060760498</t>
+    <t xml:space="preserve">4.82313108444214</t>
   </si>
   <si>
     <t xml:space="preserve">5.06229448318481</t>
@@ -548,52 +548,52 @@
     <t xml:space="preserve">4.78327035903931</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86299085617065</t>
+    <t xml:space="preserve">4.86299180984497</t>
   </si>
   <si>
     <t xml:space="preserve">5.73992443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81964588165283</t>
+    <t xml:space="preserve">5.81964540481567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70006418228149</t>
+    <t xml:space="preserve">5.70006370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66020250320435</t>
+    <t xml:space="preserve">5.6602029800415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77978515625</t>
+    <t xml:space="preserve">5.77978467941284</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85950613021851</t>
+    <t xml:space="preserve">5.85950565338135</t>
   </si>
   <si>
     <t xml:space="preserve">5.979088306427</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29797220230103</t>
+    <t xml:space="preserve">6.29797267913818</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13853025436401</t>
+    <t xml:space="preserve">6.13852977752686</t>
   </si>
   <si>
     <t xml:space="preserve">6.05880928039551</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825122833252</t>
+    <t xml:space="preserve">6.21825170516968</t>
   </si>
   <si>
     <t xml:space="preserve">6.09867000579834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38518524169922</t>
+    <t xml:space="preserve">6.3851842880249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25998497009277</t>
+    <t xml:space="preserve">6.25998449325562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30171871185303</t>
+    <t xml:space="preserve">6.30171823501587</t>
   </si>
   <si>
     <t xml:space="preserve">6.17651844024658</t>
@@ -602,19 +602,19 @@
     <t xml:space="preserve">6.42691707611084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34345149993896</t>
+    <t xml:space="preserve">6.34345102310181</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46865081787109</t>
+    <t xml:space="preserve">6.46865034103394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96785259246826</t>
+    <t xml:space="preserve">5.9678521156311</t>
   </si>
   <si>
     <t xml:space="preserve">6.0095853805542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13478469848633</t>
+    <t xml:space="preserve">6.13478517532349</t>
   </si>
   <si>
     <t xml:space="preserve">6.05131816864014</t>
@@ -626,22 +626,25 @@
     <t xml:space="preserve">6.09305238723755</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51038360595703</t>
+    <t xml:space="preserve">6.21825122833252</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84265279769897</t>
+    <t xml:space="preserve">6.51038503646851</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88438558578491</t>
+    <t xml:space="preserve">5.84265232086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88438653945923</t>
   </si>
   <si>
     <t xml:space="preserve">7.05291652679443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09624767303467</t>
+    <t xml:space="preserve">8.09624671936035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.804114818573</t>
+    <t xml:space="preserve">7.80411434173584</t>
   </si>
   <si>
     <t xml:space="preserve">7.63718128204346</t>
@@ -650,16 +653,16 @@
     <t xml:space="preserve">7.55371475219727</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34504842758179</t>
+    <t xml:space="preserve">7.34504985809326</t>
   </si>
   <si>
     <t xml:space="preserve">7.17811632156372</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51198196411133</t>
+    <t xml:space="preserve">7.51198148727417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47024917602539</t>
+    <t xml:space="preserve">7.47024822235107</t>
   </si>
   <si>
     <t xml:space="preserve">7.30331563949585</t>
@@ -668,37 +671,37 @@
     <t xml:space="preserve">7.42851495742798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2615818977356</t>
+    <t xml:space="preserve">7.26158237457275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38678216934204</t>
+    <t xml:space="preserve">7.3867826461792</t>
   </si>
   <si>
     <t xml:space="preserve">6.96944999694824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2198486328125</t>
+    <t xml:space="preserve">7.21984958648682</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544849395752</t>
+    <t xml:space="preserve">7.59544897079468</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7623815536499</t>
+    <t xml:space="preserve">7.76238059997559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84584712982178</t>
+    <t xml:space="preserve">7.84584808349609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67891407012939</t>
+    <t xml:space="preserve">7.67891359329224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01118278503418</t>
+    <t xml:space="preserve">7.01118183135986</t>
   </si>
   <si>
     <t xml:space="preserve">7.09464931488037</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92771673202515</t>
+    <t xml:space="preserve">6.92771625518799</t>
   </si>
   <si>
     <t xml:space="preserve">6.76078414916992</t>
@@ -707,19 +710,19 @@
     <t xml:space="preserve">6.8025164604187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71905040740967</t>
+    <t xml:space="preserve">6.71905088424683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84425020217896</t>
+    <t xml:space="preserve">6.8442497253418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59385013580322</t>
+    <t xml:space="preserve">6.59385061264038</t>
   </si>
   <si>
     <t xml:space="preserve">6.67731714248657</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55211734771729</t>
+    <t xml:space="preserve">6.55211782455444</t>
   </si>
   <si>
     <t xml:space="preserve">5.75918579101562</t>
@@ -731,13 +734,13 @@
     <t xml:space="preserve">5.80091905593872</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67571926116943</t>
+    <t xml:space="preserve">5.67571973800659</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59225225448608</t>
+    <t xml:space="preserve">5.59225273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63398694992065</t>
+    <t xml:space="preserve">5.63398551940918</t>
   </si>
   <si>
     <t xml:space="preserve">5.46705389022827</t>
@@ -758,7 +761,7 @@
     <t xml:space="preserve">7.13638305664062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47247076034546</t>
+    <t xml:space="preserve">7.47247123718262</t>
   </si>
   <si>
     <t xml:space="preserve">7.25269222259521</t>
@@ -776,7 +779,7 @@
     <t xml:space="preserve">7.07686948776245</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98895835876465</t>
+    <t xml:space="preserve">6.98895740509033</t>
   </si>
   <si>
     <t xml:space="preserve">7.03291368484497</t>
@@ -785,25 +788,25 @@
     <t xml:space="preserve">6.94500207901001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85709047317505</t>
+    <t xml:space="preserve">6.85709142684937</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72522449493408</t>
+    <t xml:space="preserve">6.72522354125977</t>
   </si>
   <si>
     <t xml:space="preserve">6.81313467025757</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76917934417725</t>
+    <t xml:space="preserve">6.76917886734009</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90104627609253</t>
+    <t xml:space="preserve">6.90104675292969</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63731288909912</t>
+    <t xml:space="preserve">6.63731241226196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12082576751709</t>
+    <t xml:space="preserve">7.12082529067993</t>
   </si>
   <si>
     <t xml:space="preserve">7.34060430526733</t>
@@ -815,43 +818,40 @@
     <t xml:space="preserve">7.56038284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851543426514</t>
+    <t xml:space="preserve">7.42851591110229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73620510101318</t>
+    <t xml:space="preserve">7.7362060546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6922492980957</t>
+    <t xml:space="preserve">7.69224977493286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829301834106</t>
+    <t xml:space="preserve">7.64829397201538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78247356414795</t>
+    <t xml:space="preserve">7.78247404098511</t>
   </si>
   <si>
     <t xml:space="preserve">7.8272008895874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73774671554565</t>
+    <t xml:space="preserve">7.73774719238281</t>
   </si>
   <si>
     <t xml:space="preserve">7.69302082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829397201538</t>
+    <t xml:space="preserve">7.60356616973877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60356664657593</t>
+    <t xml:space="preserve">7.91665506362915</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91665458679199</t>
+    <t xml:space="preserve">7.87192821502686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8719277381897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96138143539429</t>
+    <t xml:space="preserve">7.96138095855713</t>
   </si>
   <si>
     <t xml:space="preserve">8.2297420501709</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">8.76646614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58755779266357</t>
+    <t xml:space="preserve">8.58755874633789</t>
   </si>
   <si>
     <t xml:space="preserve">8.36392402648926</t>
@@ -869,10 +869,10 @@
     <t xml:space="preserve">8.63228416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54283046722412</t>
+    <t xml:space="preserve">8.54283142089844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40864944458008</t>
+    <t xml:space="preserve">8.40865039825439</t>
   </si>
   <si>
     <t xml:space="preserve">8.27446937561035</t>
@@ -881,43 +881,43 @@
     <t xml:space="preserve">8.45337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67701244354248</t>
+    <t xml:space="preserve">8.67701148986816</t>
   </si>
   <si>
     <t xml:space="preserve">8.49810409545898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81119251251221</t>
+    <t xml:space="preserve">8.81119155883789</t>
   </si>
   <si>
     <t xml:space="preserve">8.7217378616333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85591983795166</t>
+    <t xml:space="preserve">8.85591888427734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03482532501221</t>
+    <t xml:space="preserve">9.03482723236084</t>
   </si>
   <si>
     <t xml:space="preserve">10.3766326904297</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4500780105591</t>
+    <t xml:space="preserve">11.4500770568848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.734447479248</t>
+    <t xml:space="preserve">10.7344465255737</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0922613143921</t>
+    <t xml:space="preserve">11.0922622680664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9133539199829</t>
+    <t xml:space="preserve">10.9133548736572</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1817150115967</t>
+    <t xml:space="preserve">11.181715965271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3606224060059</t>
+    <t xml:space="preserve">11.3606233596802</t>
   </si>
   <si>
     <t xml:space="preserve">11.6289844512939</t>
@@ -932,19 +932,19 @@
     <t xml:space="preserve">10.5555391311646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2871789932251</t>
+    <t xml:space="preserve">10.2871780395508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0028076171875</t>
+    <t xml:space="preserve">11.0028085708618</t>
   </si>
   <si>
     <t xml:space="preserve">10.6449928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4660863876343</t>
+    <t xml:space="preserve">10.46608543396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1082715988159</t>
+    <t xml:space="preserve">10.1082706451416</t>
   </si>
   <si>
     <t xml:space="preserve">10.1977243423462</t>
@@ -959,28 +959,28 @@
     <t xml:space="preserve">12.6129751205444</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9707899093628</t>
+    <t xml:space="preserve">12.9707908630371</t>
   </si>
   <si>
     <t xml:space="preserve">14.0442342758179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7758731842041</t>
+    <t xml:space="preserve">13.7758741378784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.507513999939</t>
+    <t xml:space="preserve">13.5075130462646</t>
   </si>
   <si>
     <t xml:space="preserve">13.2391519546509</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0602445602417</t>
+    <t xml:space="preserve">13.0602436065674</t>
   </si>
   <si>
     <t xml:space="preserve">13.4180593490601</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8813362121582</t>
+    <t xml:space="preserve">12.8813352584839</t>
   </si>
   <si>
     <t xml:space="preserve">12.7918834686279</t>
@@ -989,22 +989,22 @@
     <t xml:space="preserve">12.702428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.149697303772</t>
+    <t xml:space="preserve">13.1496982574463</t>
   </si>
   <si>
     <t xml:space="preserve">13.3286046981812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547805786133</t>
+    <t xml:space="preserve">13.9547824859619</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5969667434692</t>
+    <t xml:space="preserve">13.5969657897949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6864213943481</t>
+    <t xml:space="preserve">13.6864204406738</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8653268814087</t>
+    <t xml:space="preserve">13.865327835083</t>
   </si>
   <si>
     <t xml:space="preserve">14.4020500183105</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">15.2965879440308</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2071332931519</t>
+    <t xml:space="preserve">15.2071323394775</t>
   </si>
   <si>
     <t xml:space="preserve">14.5809564590454</t>
@@ -1025,10 +1025,10 @@
     <t xml:space="preserve">14.4915046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5400876998901</t>
+    <t xml:space="preserve">14.5400886535645</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3560361862183</t>
+    <t xml:space="preserve">14.3560371398926</t>
   </si>
   <si>
     <t xml:space="preserve">14.2640104293823</t>
@@ -1040,10 +1040,10 @@
     <t xml:space="preserve">14.8161659240723</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6321144104004</t>
+    <t xml:space="preserve">14.6321134567261</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3683223724365</t>
+    <t xml:space="preserve">15.3683233261108</t>
   </si>
   <si>
     <t xml:space="preserve">15.5523738861084</t>
@@ -1052,25 +1052,25 @@
     <t xml:space="preserve">16.104528427124</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3806056976318</t>
+    <t xml:space="preserve">16.3806037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9204750061035</t>
+    <t xml:space="preserve">15.9204759597778</t>
   </si>
   <si>
     <t xml:space="preserve">17.2088394165039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3008632659912</t>
+    <t xml:space="preserve">17.3008651733398</t>
   </si>
   <si>
     <t xml:space="preserve">17.4849166870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.576940536499</t>
+    <t xml:space="preserve">17.5769424438477</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6689682006836</t>
+    <t xml:space="preserve">17.6689701080322</t>
   </si>
   <si>
     <t xml:space="preserve">18.4051742553711</t>
@@ -1085,13 +1085,13 @@
     <t xml:space="preserve">20.0616397857666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5340557098389</t>
+    <t xml:space="preserve">21.5340538024902</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3745708465576</t>
+    <t xml:space="preserve">23.3745727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2702617645264</t>
+    <t xml:space="preserve">22.270263671875</t>
   </si>
   <si>
     <t xml:space="preserve">22.822416305542</t>
@@ -1106,13 +1106,13 @@
     <t xml:space="preserve">21.902156829834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0862102508545</t>
+    <t xml:space="preserve">22.0862083435059</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0064678192139</t>
+    <t xml:space="preserve">23.0064697265625</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5586261749268</t>
+    <t xml:space="preserve">23.5586242675781</t>
   </si>
   <si>
     <t xml:space="preserve">23.74267578125</t>
@@ -1121,13 +1121,13 @@
     <t xml:space="preserve">23.9267272949219</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6629333496094</t>
+    <t xml:space="preserve">24.662935256958</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8469886779785</t>
+    <t xml:space="preserve">24.8469867706299</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2948303222656</t>
+    <t xml:space="preserve">24.2948322296143</t>
   </si>
   <si>
     <t xml:space="preserve">24.1107807159424</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">23.1905212402344</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2150897979736</t>
+    <t xml:space="preserve">25.215087890625</t>
   </si>
   <si>
     <t xml:space="preserve">22.4543132781982</t>
@@ -1148,31 +1148,31 @@
     <t xml:space="preserve">25.9512958526611</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5034523010254</t>
+    <t xml:space="preserve">26.5034503936768</t>
   </si>
   <si>
     <t xml:space="preserve">27.975866317749</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9206943511963</t>
+    <t xml:space="preserve">30.9206924438477</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0801753997803</t>
+    <t xml:space="preserve">29.0801773071289</t>
   </si>
   <si>
-    <t xml:space="preserve">30.736644744873</t>
+    <t xml:space="preserve">30.7366466522217</t>
   </si>
   <si>
     <t xml:space="preserve">30.3685398101807</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2642288208008</t>
+    <t xml:space="preserve">29.2642269134521</t>
   </si>
   <si>
     <t xml:space="preserve">31.4728507995605</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2336273193359</t>
+    <t xml:space="preserve">34.2336235046387</t>
   </si>
   <si>
     <t xml:space="preserve">34.7857780456543</t>
@@ -1181,19 +1181,19 @@
     <t xml:space="preserve">33.8655204772949</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4974212646484</t>
+    <t xml:space="preserve">33.4974174499512</t>
   </si>
   <si>
     <t xml:space="preserve">30.1844863891602</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4237098693848</t>
+    <t xml:space="preserve">27.4237117767334</t>
   </si>
   <si>
     <t xml:space="preserve">26.6875038146973</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5831928253174</t>
+    <t xml:space="preserve">25.5831909179688</t>
   </si>
   <si>
     <t xml:space="preserve">26.3194007873535</t>
@@ -1211,16 +1211,16 @@
     <t xml:space="preserve">28.5280208587646</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7120723724365</t>
+    <t xml:space="preserve">28.7120742797852</t>
   </si>
   <si>
     <t xml:space="preserve">28.3439693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">27.055606842041</t>
+    <t xml:space="preserve">27.0556087493896</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8715572357178</t>
+    <t xml:space="preserve">26.8715553283691</t>
   </si>
   <si>
     <t xml:space="preserve">25.3991413116455</t>
@@ -18645,7 +18645,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G639" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19165,7 +19165,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G659" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -19191,7 +19191,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G660" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19295,7 +19295,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G664" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19503,7 +19503,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G672" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -19529,7 +19529,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G673" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20023,7 +20023,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G692" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20049,7 +20049,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G693" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20127,7 +20127,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G696" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20153,7 +20153,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G697" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -20283,7 +20283,7 @@
         <v>7</v>
       </c>
       <c r="G702" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -20309,7 +20309,7 @@
         <v>7</v>
       </c>
       <c r="G703" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -20335,7 +20335,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G704" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -20595,7 +20595,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G714" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -20621,7 +20621,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G715" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -20699,7 +20699,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G718" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -20751,7 +20751,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G720" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21011,7 +21011,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G730" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21037,7 +21037,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G731" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21063,7 +21063,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G732" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21089,7 +21089,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G733" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -21349,7 +21349,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G743" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -21375,7 +21375,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G744" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -21401,7 +21401,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G745" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -21427,7 +21427,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G746" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -21453,7 +21453,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G747" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -21479,7 +21479,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G748" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -21505,7 +21505,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G749" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -21531,7 +21531,7 @@
         <v>9</v>
       </c>
       <c r="G750" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -21557,7 +21557,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G751" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -21583,7 +21583,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G752" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -21609,7 +21609,7 @@
         <v>8.75</v>
       </c>
       <c r="G753" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -21635,7 +21635,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G754" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -21661,7 +21661,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G755" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -21687,7 +21687,7 @@
         <v>9</v>
       </c>
       <c r="G756" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -21713,7 +21713,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G757" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -21739,7 +21739,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G758" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -21765,7 +21765,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G759" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -21791,7 +21791,7 @@
         <v>9</v>
       </c>
       <c r="G760" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -21817,7 +21817,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G761" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -21843,7 +21843,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G762" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -21869,7 +21869,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G763" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -21895,7 +21895,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G764" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -21921,7 +21921,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G765" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -21947,7 +21947,7 @@
         <v>9</v>
       </c>
       <c r="G766" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -21973,7 +21973,7 @@
         <v>9</v>
       </c>
       <c r="G767" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -21999,7 +21999,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G768" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22025,7 +22025,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G769" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22051,7 +22051,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G770" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22077,7 +22077,7 @@
         <v>8.75</v>
       </c>
       <c r="G771" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22103,7 +22103,7 @@
         <v>8.75</v>
       </c>
       <c r="G772" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22129,7 +22129,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G773" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22155,7 +22155,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G774" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22181,7 +22181,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G775" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22207,7 +22207,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G776" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22233,7 +22233,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G777" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22259,7 +22259,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G778" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22285,7 +22285,7 @@
         <v>9</v>
       </c>
       <c r="G779" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -22311,7 +22311,7 @@
         <v>9</v>
       </c>
       <c r="G780" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -22337,7 +22337,7 @@
         <v>9</v>
       </c>
       <c r="G781" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -22363,7 +22363,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G782" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -22389,7 +22389,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G783" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -22415,7 +22415,7 @@
         <v>8.75</v>
       </c>
       <c r="G784" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -22441,7 +22441,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G785" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -22467,7 +22467,7 @@
         <v>8.75</v>
       </c>
       <c r="G786" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -22493,7 +22493,7 @@
         <v>8.75</v>
       </c>
       <c r="G787" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -22519,7 +22519,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G788" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -22545,7 +22545,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G789" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -22571,7 +22571,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G790" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -22597,7 +22597,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G791" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -22623,7 +22623,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G792" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -22649,7 +22649,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G793" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -22675,7 +22675,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G794" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -22701,7 +22701,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G795" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -22727,7 +22727,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G796" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -22753,7 +22753,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G797" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -22779,7 +22779,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G798" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -22805,7 +22805,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G799" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -22831,7 +22831,7 @@
         <v>8.75</v>
       </c>
       <c r="G800" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -22857,7 +22857,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G801" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -22883,7 +22883,7 @@
         <v>8.75</v>
       </c>
       <c r="G802" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -22909,7 +22909,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G803" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -22935,7 +22935,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G804" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -22961,7 +22961,7 @@
         <v>8.75</v>
       </c>
       <c r="G805" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -22987,7 +22987,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G806" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23013,7 +23013,7 @@
         <v>8.75</v>
       </c>
       <c r="G807" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23039,7 +23039,7 @@
         <v>8.75</v>
       </c>
       <c r="G808" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23065,7 +23065,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G809" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23091,7 +23091,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G810" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23117,7 +23117,7 @@
         <v>8.5</v>
       </c>
       <c r="G811" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23143,7 +23143,7 @@
         <v>8.5</v>
       </c>
       <c r="G812" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23169,7 +23169,7 @@
         <v>8.5</v>
       </c>
       <c r="G813" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23195,7 +23195,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G814" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23221,7 +23221,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G815" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23247,7 +23247,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G816" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23273,7 +23273,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G817" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23299,7 +23299,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G818" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -23325,7 +23325,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G819" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -23351,7 +23351,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G820" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -23377,7 +23377,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G821" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -23403,7 +23403,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G822" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -23429,7 +23429,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G823" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -23455,7 +23455,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G824" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -23481,7 +23481,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G825" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -23507,7 +23507,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G826" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -23533,7 +23533,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G827" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -23559,7 +23559,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G828" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -23585,7 +23585,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G829" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -23611,7 +23611,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G830" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -23637,7 +23637,7 @@
         <v>9</v>
       </c>
       <c r="G831" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -23663,7 +23663,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G832" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -23689,7 +23689,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G833" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -23715,7 +23715,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G834" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -23741,7 +23741,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G835" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -23767,7 +23767,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G836" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -23793,7 +23793,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G837" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -23819,7 +23819,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G838" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -23845,7 +23845,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G839" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -23871,7 +23871,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G840" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -23897,7 +23897,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G841" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -23923,7 +23923,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G842" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -23949,7 +23949,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G843" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -23975,7 +23975,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G844" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24001,7 +24001,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G845" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24027,7 +24027,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G846" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24053,7 +24053,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G847" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24079,7 +24079,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G848" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24105,7 +24105,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G849" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24131,7 +24131,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G850" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24157,7 +24157,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G851" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24183,7 +24183,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G852" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24209,7 +24209,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G853" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24235,7 +24235,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G854" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24261,7 +24261,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G855" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24287,7 +24287,7 @@
         <v>8</v>
       </c>
       <c r="G856" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24313,7 +24313,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G857" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24339,7 +24339,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G858" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -24417,7 +24417,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G861" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24495,7 +24495,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G864" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -24937,7 +24937,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G881" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25015,7 +25015,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G884" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25041,7 +25041,7 @@
         <v>7</v>
       </c>
       <c r="G885" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25249,7 +25249,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G893" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -25977,7 +25977,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G921" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26003,7 +26003,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G922" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26029,7 +26029,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G923" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -26055,7 +26055,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G924" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26159,7 +26159,7 @@
         <v>7</v>
       </c>
       <c r="G928" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26185,7 +26185,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G929" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26211,7 +26211,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G930" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26237,7 +26237,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G931" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26263,7 +26263,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G932" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26289,7 +26289,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G933" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26315,7 +26315,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G934" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26341,7 +26341,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G935" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26419,7 +26419,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G938" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26445,7 +26445,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G939" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26705,7 +26705,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G949" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26731,7 +26731,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G950" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26757,7 +26757,7 @@
         <v>7</v>
       </c>
       <c r="G951" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -26783,7 +26783,7 @@
         <v>7</v>
       </c>
       <c r="G952" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26809,7 +26809,7 @@
         <v>7</v>
       </c>
       <c r="G953" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26835,7 +26835,7 @@
         <v>7</v>
       </c>
       <c r="G954" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26861,7 +26861,7 @@
         <v>7</v>
       </c>
       <c r="G955" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26887,7 +26887,7 @@
         <v>7</v>
       </c>
       <c r="G956" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26913,7 +26913,7 @@
         <v>7</v>
       </c>
       <c r="G957" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26939,7 +26939,7 @@
         <v>7</v>
       </c>
       <c r="G958" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26965,7 +26965,7 @@
         <v>7</v>
       </c>
       <c r="G959" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -26991,7 +26991,7 @@
         <v>7</v>
       </c>
       <c r="G960" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27017,7 +27017,7 @@
         <v>7</v>
       </c>
       <c r="G961" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27043,7 +27043,7 @@
         <v>7</v>
       </c>
       <c r="G962" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27069,7 +27069,7 @@
         <v>7</v>
       </c>
       <c r="G963" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27095,7 +27095,7 @@
         <v>7</v>
       </c>
       <c r="G964" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27121,7 +27121,7 @@
         <v>7</v>
       </c>
       <c r="G965" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27147,7 +27147,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G966" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27173,7 +27173,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G967" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27199,7 +27199,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G968" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27225,7 +27225,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G969" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -27251,7 +27251,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G970" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27277,7 +27277,7 @@
         <v>6.75</v>
       </c>
       <c r="G971" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27303,7 +27303,7 @@
         <v>6.75</v>
       </c>
       <c r="G972" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27329,7 +27329,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G973" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27355,7 +27355,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G974" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27381,7 +27381,7 @@
         <v>6.75</v>
       </c>
       <c r="G975" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27407,7 +27407,7 @@
         <v>6.75</v>
       </c>
       <c r="G976" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27433,7 +27433,7 @@
         <v>6.75</v>
       </c>
       <c r="G977" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27459,7 +27459,7 @@
         <v>6.75</v>
       </c>
       <c r="G978" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -27485,7 +27485,7 @@
         <v>6.75</v>
       </c>
       <c r="G979" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27511,7 +27511,7 @@
         <v>6.75</v>
       </c>
       <c r="G980" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27537,7 +27537,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G981" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27563,7 +27563,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G982" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -27589,7 +27589,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G983" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -27615,7 +27615,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G984" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27641,7 +27641,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G985" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -27667,7 +27667,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G986" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -27693,7 +27693,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G987" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -27719,7 +27719,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G988" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -27745,7 +27745,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G989" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -27771,7 +27771,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G990" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -27797,7 +27797,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G991" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -27823,7 +27823,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G992" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -27849,7 +27849,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G993" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -27875,7 +27875,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G994" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -27901,7 +27901,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G995" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -27927,7 +27927,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G996" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -27953,7 +27953,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G997" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -27979,7 +27979,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G998" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28005,7 +28005,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G999" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28031,7 +28031,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1000" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28057,7 +28057,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1001" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28083,7 +28083,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1002" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28109,7 +28109,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1003" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28135,7 +28135,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1004" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28161,7 +28161,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1005" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28187,7 +28187,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1006" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28213,7 +28213,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1007" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28239,7 +28239,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1008" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28265,7 +28265,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1009" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28343,7 +28343,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1012" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28369,7 +28369,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1013" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28395,7 +28395,7 @@
         <v>8</v>
       </c>
       <c r="G1014" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28551,7 +28551,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1020" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28577,7 +28577,7 @@
         <v>8.5</v>
       </c>
       <c r="G1021" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28603,7 +28603,7 @@
         <v>8.5</v>
       </c>
       <c r="G1022" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -28629,7 +28629,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1023" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -28655,7 +28655,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1024" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28681,7 +28681,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1025" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28707,7 +28707,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1026" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28733,7 +28733,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1027" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28759,7 +28759,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1028" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28785,7 +28785,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1029" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28811,7 +28811,7 @@
         <v>8.75</v>
       </c>
       <c r="G1030" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28837,7 +28837,7 @@
         <v>8.75</v>
       </c>
       <c r="G1031" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28863,7 +28863,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1032" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28889,7 +28889,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1033" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28915,7 +28915,7 @@
         <v>8.5</v>
       </c>
       <c r="G1034" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28941,7 +28941,7 @@
         <v>8.25</v>
       </c>
       <c r="G1035" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28967,7 +28967,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1036" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -28993,7 +28993,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1037" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29019,7 +29019,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1038" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29045,7 +29045,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1039" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29071,7 +29071,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1040" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29097,7 +29097,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1041" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29123,7 +29123,7 @@
         <v>8</v>
       </c>
       <c r="G1042" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29149,7 +29149,7 @@
         <v>8</v>
       </c>
       <c r="G1043" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29175,7 +29175,7 @@
         <v>8</v>
       </c>
       <c r="G1044" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29201,7 +29201,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1045" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -29227,7 +29227,7 @@
         <v>8</v>
       </c>
       <c r="G1046" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29253,7 +29253,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1047" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -29279,7 +29279,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1048" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29305,7 +29305,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1049" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29331,7 +29331,7 @@
         <v>7.75</v>
       </c>
       <c r="G1050" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29357,7 +29357,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1051" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29383,7 +29383,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1052" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29409,7 +29409,7 @@
         <v>7.75</v>
       </c>
       <c r="G1053" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29435,7 +29435,7 @@
         <v>7.75</v>
       </c>
       <c r="G1054" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29461,7 +29461,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1055" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29487,7 +29487,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1056" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29513,7 +29513,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1057" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29539,7 +29539,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1058" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29565,7 +29565,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1059" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29591,7 +29591,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1060" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29617,7 +29617,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1061" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29643,7 +29643,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1062" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29669,7 +29669,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1063" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29695,7 +29695,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1064" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29721,7 +29721,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1065" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29747,7 +29747,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1066" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29773,7 +29773,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1067" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29799,7 +29799,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1068" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29825,7 +29825,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1069" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29851,7 +29851,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1070" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29877,7 +29877,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1071" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29903,7 +29903,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1072" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -29929,7 +29929,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1073" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -29955,7 +29955,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1074" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -29981,7 +29981,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1075" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30007,7 +30007,7 @@
         <v>8</v>
       </c>
       <c r="G1076" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30033,7 +30033,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1077" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30059,7 +30059,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1078" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30085,7 +30085,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1079" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -30111,7 +30111,7 @@
         <v>8.25</v>
       </c>
       <c r="G1080" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30137,7 +30137,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1081" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30163,7 +30163,7 @@
         <v>8.5</v>
       </c>
       <c r="G1082" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30189,7 +30189,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1083" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30215,7 +30215,7 @@
         <v>8.5</v>
       </c>
       <c r="G1084" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30241,7 +30241,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1085" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30267,7 +30267,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1086" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -30293,7 +30293,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1087" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30319,7 +30319,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1088" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30345,7 +30345,7 @@
         <v>8.5</v>
       </c>
       <c r="G1089" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30371,7 +30371,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1090" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30397,7 +30397,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1091" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30423,7 +30423,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1092" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30449,7 +30449,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1093" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30475,7 +30475,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1094" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30501,7 +30501,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1095" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30527,7 +30527,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1096" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30553,7 +30553,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1097" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30579,7 +30579,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1098" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30605,7 +30605,7 @@
         <v>8.75</v>
       </c>
       <c r="G1099" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30631,7 +30631,7 @@
         <v>8.75</v>
       </c>
       <c r="G1100" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30657,7 +30657,7 @@
         <v>8.75</v>
       </c>
       <c r="G1101" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -30683,7 +30683,7 @@
         <v>8.75</v>
       </c>
       <c r="G1102" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30709,7 +30709,7 @@
         <v>8.75</v>
       </c>
       <c r="G1103" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30735,7 +30735,7 @@
         <v>8.75</v>
       </c>
       <c r="G1104" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30761,7 +30761,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1105" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30787,7 +30787,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1106" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30813,7 +30813,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1107" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30839,7 +30839,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1108" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30865,7 +30865,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1109" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30891,7 +30891,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1110" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -30917,7 +30917,7 @@
         <v>8.75</v>
       </c>
       <c r="G1111" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30943,7 +30943,7 @@
         <v>8.75</v>
       </c>
       <c r="G1112" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -30969,7 +30969,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1113" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -30995,7 +30995,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1114" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31021,7 +31021,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31047,7 +31047,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1116" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31073,7 +31073,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1117" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31099,7 +31099,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1118" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31125,7 +31125,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1119" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31151,7 +31151,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1120" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31177,7 +31177,7 @@
         <v>8.75</v>
       </c>
       <c r="G1121" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31203,7 +31203,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1122" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31229,7 +31229,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1123" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31255,7 +31255,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1124" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31281,7 +31281,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1125" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31307,7 +31307,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1126" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31333,7 +31333,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1127" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31359,7 +31359,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1128" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31385,7 +31385,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1129" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31411,7 +31411,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1130" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31437,7 +31437,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1131" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31463,7 +31463,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1132" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31489,7 +31489,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1133" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31515,7 +31515,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1134" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31567,7 +31567,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1136" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31593,7 +31593,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1137" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31619,7 +31619,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1138" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31645,7 +31645,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1139" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31671,7 +31671,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1140" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31697,7 +31697,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1141" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31723,7 +31723,7 @@
         <v>8.75</v>
       </c>
       <c r="G1142" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31853,7 +31853,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1147" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31905,7 +31905,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1149" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32035,7 +32035,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1154" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32061,7 +32061,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1155" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32087,7 +32087,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1156" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -60851,7 +60851,7 @@
     </row>
     <row r="2263">
       <c r="A2263" s="1" t="n">
-        <v>45954.5039467593</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2263" t="n">
         <v>500</v>
@@ -60872,6 +60872,32 @@
         <v>545</v>
       </c>
       <c r="H2263" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="A2264" s="1" t="n">
+        <v>45957.6118865741</v>
+      </c>
+      <c r="B2264" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C2264" t="n">
+        <v>41</v>
+      </c>
+      <c r="D2264" t="n">
+        <v>39.4000015258789</v>
+      </c>
+      <c r="E2264" t="n">
+        <v>41</v>
+      </c>
+      <c r="F2264" t="n">
+        <v>39.7999992370605</v>
+      </c>
+      <c r="G2264" t="s">
+        <v>533</v>
+      </c>
+      <c r="H2264" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">FPE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42625832557678</t>
+    <t xml:space="preserve">2.42625856399536</t>
   </si>
   <si>
     <t xml:space="preserve">2.43408489227295</t>
@@ -53,25 +53,25 @@
     <t xml:space="preserve">2.41060519218445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45756506919861</t>
+    <t xml:space="preserve">2.45756530761719</t>
   </si>
   <si>
     <t xml:space="preserve">2.39495205879211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233904838562</t>
+    <t xml:space="preserve">2.33233880996704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41843199729919</t>
+    <t xml:space="preserve">2.41843175888062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35581874847412</t>
+    <t xml:space="preserve">2.3558189868927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37147188186646</t>
+    <t xml:space="preserve">2.37147235870361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50452542304993</t>
+    <t xml:space="preserve">2.50452518463135</t>
   </si>
   <si>
     <t xml:space="preserve">2.36364531517029</t>
@@ -83,55 +83,55 @@
     <t xml:space="preserve">2.37303757667542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34955739974976</t>
+    <t xml:space="preserve">2.34955763816833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46382689476013</t>
+    <t xml:space="preserve">2.46382665634155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38712573051453</t>
+    <t xml:space="preserve">2.38712525367737</t>
   </si>
   <si>
     <t xml:space="preserve">2.45443415641785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34799194335938</t>
+    <t xml:space="preserve">2.34799218177795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48104524612427</t>
+    <t xml:space="preserve">2.48104500770569</t>
   </si>
   <si>
     <t xml:space="preserve">2.37929844856262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38555979728699</t>
+    <t xml:space="preserve">2.38556003570557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44191193580627</t>
+    <t xml:space="preserve">2.4419116973877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78002285957336</t>
+    <t xml:space="preserve">2.78002262115479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36702060699463</t>
+    <t xml:space="preserve">3.36702036857605</t>
   </si>
   <si>
     <t xml:space="preserve">3.62529993057251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31066918373108</t>
+    <t xml:space="preserve">3.31066870689392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25588250160217</t>
+    <t xml:space="preserve">3.25588202476501</t>
   </si>
   <si>
     <t xml:space="preserve">3.20266127586365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0523898601532</t>
+    <t xml:space="preserve">3.05238962173462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09152317047119</t>
+    <t xml:space="preserve">3.09152293205261</t>
   </si>
   <si>
     <t xml:space="preserve">3.04456329345703</t>
@@ -140,19 +140,19 @@
     <t xml:space="preserve">3.03673672676086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03830218315125</t>
+    <t xml:space="preserve">3.03830170631409</t>
   </si>
   <si>
     <t xml:space="preserve">3.15413618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3091037273407</t>
+    <t xml:space="preserve">3.30910396575928</t>
   </si>
   <si>
     <t xml:space="preserve">3.30284214019775</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35762882232666</t>
+    <t xml:space="preserve">3.35762810707092</t>
   </si>
   <si>
     <t xml:space="preserve">3.57677483558655</t>
@@ -161,61 +161,61 @@
     <t xml:space="preserve">3.52198815345764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40458846092224</t>
+    <t xml:space="preserve">3.40458869934082</t>
   </si>
   <si>
     <t xml:space="preserve">3.59242820739746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58460164070129</t>
+    <t xml:space="preserve">3.58460140228271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6785204410553</t>
+    <t xml:space="preserve">3.67852067947388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60025453567505</t>
+    <t xml:space="preserve">3.60025405883789</t>
   </si>
   <si>
     <t xml:space="preserve">3.59555840492249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632207870483</t>
+    <t xml:space="preserve">3.32632231712341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29501557350159</t>
+    <t xml:space="preserve">3.29501581192017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3748471736908</t>
+    <t xml:space="preserve">3.37484693527222</t>
   </si>
   <si>
     <t xml:space="preserve">3.38267397880554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44372200965881</t>
+    <t xml:space="preserve">3.44372224807739</t>
   </si>
   <si>
     <t xml:space="preserve">3.59086227416992</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47972464561462</t>
+    <t xml:space="preserve">3.47972440719604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4265034198761</t>
+    <t xml:space="preserve">3.42650294303894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41241526603699</t>
+    <t xml:space="preserve">3.41241502761841</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24022912979126</t>
+    <t xml:space="preserve">3.24022936820984</t>
   </si>
   <si>
     <t xml:space="preserve">3.21048808097839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28405809402466</t>
+    <t xml:space="preserve">3.28405833244324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16196250915527</t>
+    <t xml:space="preserve">3.16196298599243</t>
   </si>
   <si>
     <t xml:space="preserve">3.20892262458801</t>
@@ -224,79 +224,79 @@
     <t xml:space="preserve">3.13848304748535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23240280151367</t>
+    <t xml:space="preserve">3.23240232467651</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31849503517151</t>
+    <t xml:space="preserve">3.31849551200867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27623200416565</t>
+    <t xml:space="preserve">3.27623152732849</t>
   </si>
   <si>
     <t xml:space="preserve">3.18857312202454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14317870140076</t>
+    <t xml:space="preserve">3.1431782245636</t>
   </si>
   <si>
     <t xml:space="preserve">3.11500310897827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00073432922363</t>
+    <t xml:space="preserve">3.0007336139679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97412347793579</t>
+    <t xml:space="preserve">2.97412323951721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06021642684937</t>
+    <t xml:space="preserve">3.06021666526794</t>
   </si>
   <si>
     <t xml:space="preserve">2.90368366241455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8958568572998</t>
+    <t xml:space="preserve">2.89585709571838</t>
   </si>
   <si>
     <t xml:space="preserve">2.82854795455933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83637475967407</t>
+    <t xml:space="preserve">2.83637452125549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9099452495575</t>
+    <t xml:space="preserve">2.90994453430176</t>
   </si>
   <si>
     <t xml:space="preserve">3.06491231918335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13065600395203</t>
+    <t xml:space="preserve">3.13065576553345</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14474439620972</t>
+    <t xml:space="preserve">3.14474415779114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21361827850342</t>
+    <t xml:space="preserve">3.21361875534058</t>
   </si>
   <si>
     <t xml:space="preserve">3.28562355041504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35919380187988</t>
+    <t xml:space="preserve">3.35919404029846</t>
   </si>
   <si>
     <t xml:space="preserve">3.36388993263245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91332030296326</t>
+    <t xml:space="preserve">3.91332054138184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34378576278687</t>
+    <t xml:space="preserve">4.34378623962402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7938175201416</t>
+    <t xml:space="preserve">4.79381704330444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47864866256714</t>
+    <t xml:space="preserve">5.47864818572998</t>
   </si>
   <si>
     <t xml:space="preserve">6.09303951263428</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">5.41603517532349</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71344757080078</t>
+    <t xml:space="preserve">5.71344804763794</t>
   </si>
   <si>
     <t xml:space="preserve">5.56865406036377</t>
@@ -317,61 +317,61 @@
     <t xml:space="preserve">5.16558265686035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94643688201904</t>
+    <t xml:space="preserve">4.9464373588562</t>
   </si>
   <si>
     <t xml:space="preserve">4.70381116867065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67641735076904</t>
+    <t xml:space="preserve">4.6764178276062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00905084609985</t>
+    <t xml:space="preserve">5.0090503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55691480636597</t>
+    <t xml:space="preserve">5.55691432952881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30646324157715</t>
+    <t xml:space="preserve">5.30646228790283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22428321838379</t>
+    <t xml:space="preserve">5.22428226470947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19688940048218</t>
+    <t xml:space="preserve">5.19688892364502</t>
   </si>
   <si>
     <t xml:space="preserve">5.32211589813232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47082138061523</t>
+    <t xml:space="preserve">5.47082090377808</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36907577514648</t>
+    <t xml:space="preserve">5.36907529830933</t>
   </si>
   <si>
     <t xml:space="preserve">5.2908091545105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1734094619751</t>
+    <t xml:space="preserve">5.17340993881226</t>
   </si>
   <si>
     <t xml:space="preserve">5.09514284133911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2203688621521</t>
+    <t xml:space="preserve">5.22036981582642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1029691696167</t>
+    <t xml:space="preserve">5.10296964645386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99339628219604</t>
+    <t xml:space="preserve">4.9933967590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15384244918823</t>
+    <t xml:space="preserve">5.15384292602539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98557043075562</t>
+    <t xml:space="preserve">4.98556995391846</t>
   </si>
   <si>
     <t xml:space="preserve">4.75859689712524</t>
@@ -380,16 +380,16 @@
     <t xml:space="preserve">4.77033758163452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86425733566284</t>
+    <t xml:space="preserve">4.86425685882568</t>
   </si>
   <si>
     <t xml:space="preserve">4.88773679733276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83295059204102</t>
+    <t xml:space="preserve">4.83295106887817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75468349456787</t>
+    <t xml:space="preserve">4.75468397140503</t>
   </si>
   <si>
     <t xml:space="preserve">4.82903718948364</t>
@@ -401,40 +401,40 @@
     <t xml:space="preserve">4.68815755844116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78207778930664</t>
+    <t xml:space="preserve">4.78207731246948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87599658966064</t>
+    <t xml:space="preserve">4.8759970664978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03644323348999</t>
+    <t xml:space="preserve">5.03644371032715</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92687034606934</t>
+    <t xml:space="preserve">4.92687082290649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81338357925415</t>
+    <t xml:space="preserve">4.81338453292847</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86034345626831</t>
+    <t xml:space="preserve">4.86034393310547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00122261047363</t>
+    <t xml:space="preserve">5.00122308731079</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77425146102905</t>
+    <t xml:space="preserve">4.77425050735474</t>
   </si>
   <si>
     <t xml:space="preserve">4.8212103843689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69989728927612</t>
+    <t xml:space="preserve">4.69989776611328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69598388671875</t>
+    <t xml:space="preserve">4.69598436355591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90730381011963</t>
+    <t xml:space="preserve">4.90730333328247</t>
   </si>
   <si>
     <t xml:space="preserve">5.20471620559692</t>
@@ -446,19 +446,19 @@
     <t xml:space="preserve">5.28298234939575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384880065918</t>
+    <t xml:space="preserve">5.24384927749634</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36124849319458</t>
+    <t xml:space="preserve">5.36124753952026</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40038204193115</t>
+    <t xml:space="preserve">5.40038251876831</t>
   </si>
   <si>
     <t xml:space="preserve">5.51778173446655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63518142700195</t>
+    <t xml:space="preserve">5.63518095016479</t>
   </si>
   <si>
     <t xml:space="preserve">4.96991682052612</t>
@@ -467,37 +467,37 @@
     <t xml:space="preserve">4.93078374862671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85251665115356</t>
+    <t xml:space="preserve">4.85251712799072</t>
   </si>
   <si>
     <t xml:space="preserve">5.12644958496094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04818296432495</t>
+    <t xml:space="preserve">5.04818248748779</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08731555938721</t>
+    <t xml:space="preserve">5.08731603622437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59604740142822</t>
+    <t xml:space="preserve">5.59604835510254</t>
   </si>
   <si>
     <t xml:space="preserve">5.26159715652466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42103958129883</t>
+    <t xml:space="preserve">5.42104005813599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34131813049316</t>
+    <t xml:space="preserve">5.34131860733032</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22173643112183</t>
+    <t xml:space="preserve">5.22173690795898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14201545715332</t>
+    <t xml:space="preserve">5.14201498031616</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10215520858765</t>
+    <t xml:space="preserve">5.1021556854248</t>
   </si>
   <si>
     <t xml:space="preserve">5.18187618255615</t>
@@ -509,19 +509,19 @@
     <t xml:space="preserve">5.30145835876465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90285205841064</t>
+    <t xml:space="preserve">4.9028525352478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50076055526733</t>
+    <t xml:space="preserve">5.50076150894165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4608998298645</t>
+    <t xml:space="preserve">5.46089935302734</t>
   </si>
   <si>
     <t xml:space="preserve">5.580482006073</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54062080383301</t>
+    <t xml:space="preserve">5.54062128067017</t>
   </si>
   <si>
     <t xml:space="preserve">5.62034273147583</t>
@@ -530,7 +530,7 @@
     <t xml:space="preserve">4.94271278381348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98257350921631</t>
+    <t xml:space="preserve">4.98257303237915</t>
   </si>
   <si>
     <t xml:space="preserve">4.82313108444214</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">5.06229448318481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02243375778198</t>
+    <t xml:space="preserve">5.02243423461914</t>
   </si>
   <si>
     <t xml:space="preserve">4.74341011047363</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">4.78327035903931</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86299180984497</t>
+    <t xml:space="preserve">4.86299133300781</t>
   </si>
   <si>
     <t xml:space="preserve">5.73992443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81964635848999</t>
+    <t xml:space="preserve">5.81964588165283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70006370544434</t>
+    <t xml:space="preserve">5.70006418228149</t>
   </si>
   <si>
     <t xml:space="preserve">5.6602029800415</t>
@@ -578,52 +578,52 @@
     <t xml:space="preserve">6.13853025436401</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05880928039551</t>
+    <t xml:space="preserve">6.05880880355835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825075149536</t>
+    <t xml:space="preserve">6.21825122833252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09867000579834</t>
+    <t xml:space="preserve">6.09866952896118</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38518476486206</t>
+    <t xml:space="preserve">6.3851842880249</t>
   </si>
   <si>
     <t xml:space="preserve">6.25998449325562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30171775817871</t>
+    <t xml:space="preserve">6.30171823501587</t>
   </si>
   <si>
     <t xml:space="preserve">6.17651844024658</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42691707611084</t>
+    <t xml:space="preserve">6.426917552948</t>
   </si>
   <si>
     <t xml:space="preserve">6.34345102310181</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46865081787109</t>
+    <t xml:space="preserve">6.46865034103394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96785163879395</t>
+    <t xml:space="preserve">5.96785259246826</t>
   </si>
   <si>
     <t xml:space="preserve">6.0095853805542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13478517532349</t>
+    <t xml:space="preserve">6.13478422164917</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05131864547729</t>
+    <t xml:space="preserve">6.05131816864014</t>
   </si>
   <si>
     <t xml:space="preserve">5.92611885070801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09305238723755</t>
+    <t xml:space="preserve">6.09305191040039</t>
   </si>
   <si>
     <t xml:space="preserve">6.51038408279419</t>
@@ -638,22 +638,22 @@
     <t xml:space="preserve">7.05291604995728</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09624767303467</t>
+    <t xml:space="preserve">8.09624671936035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80411529541016</t>
+    <t xml:space="preserve">7.80411338806152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6371808052063</t>
+    <t xml:space="preserve">7.63718032836914</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55371475219727</t>
+    <t xml:space="preserve">7.55371570587158</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3450493812561</t>
+    <t xml:space="preserve">7.34504985809326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17811632156372</t>
+    <t xml:space="preserve">7.17811584472656</t>
   </si>
   <si>
     <t xml:space="preserve">7.51198148727417</t>
@@ -665,64 +665,64 @@
     <t xml:space="preserve">7.30331611633301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851495742798</t>
+    <t xml:space="preserve">7.42851591110229</t>
   </si>
   <si>
     <t xml:space="preserve">7.26158237457275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38678216934204</t>
+    <t xml:space="preserve">7.3867826461792</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96944999694824</t>
+    <t xml:space="preserve">6.9694504737854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2198486328125</t>
+    <t xml:space="preserve">7.21984910964966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544849395752</t>
+    <t xml:space="preserve">7.59544801712036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7623815536499</t>
+    <t xml:space="preserve">7.76238203048706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84584712982178</t>
+    <t xml:space="preserve">7.84584665298462</t>
   </si>
   <si>
     <t xml:space="preserve">7.67891359329224</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01118230819702</t>
+    <t xml:space="preserve">7.01118278503418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09464931488037</t>
+    <t xml:space="preserve">7.09464979171753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92771625518799</t>
+    <t xml:space="preserve">6.9277172088623</t>
   </si>
   <si>
     <t xml:space="preserve">6.76078367233276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8025164604187</t>
+    <t xml:space="preserve">6.80251693725586</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71905040740967</t>
+    <t xml:space="preserve">6.71904993057251</t>
   </si>
   <si>
     <t xml:space="preserve">6.84425020217896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59385108947754</t>
+    <t xml:space="preserve">6.59385061264038</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67731714248657</t>
+    <t xml:space="preserve">6.67731666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55211734771729</t>
+    <t xml:space="preserve">6.55211639404297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75918579101562</t>
+    <t xml:space="preserve">5.75918626785278</t>
   </si>
   <si>
     <t xml:space="preserve">5.71745204925537</t>
@@ -731,13 +731,13 @@
     <t xml:space="preserve">5.80091905593872</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67571926116943</t>
+    <t xml:space="preserve">5.67572021484375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59225273132324</t>
+    <t xml:space="preserve">5.5922532081604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63398599624634</t>
+    <t xml:space="preserve">5.6339864730835</t>
   </si>
   <si>
     <t xml:space="preserve">5.46705341339111</t>
@@ -749,28 +749,28 @@
     <t xml:space="preserve">5.17492055892944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25838708877563</t>
+    <t xml:space="preserve">5.25838756561279</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38358688354492</t>
+    <t xml:space="preserve">5.38358640670776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13638257980347</t>
+    <t xml:space="preserve">7.13638305664062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47247076034546</t>
+    <t xml:space="preserve">7.47247123718262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25269317626953</t>
+    <t xml:space="preserve">7.25269269943237</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2966480255127</t>
+    <t xml:space="preserve">7.29664897918701</t>
   </si>
   <si>
     <t xml:space="preserve">7.20873689651489</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16478061676025</t>
+    <t xml:space="preserve">7.16478109359741</t>
   </si>
   <si>
     <t xml:space="preserve">7.07686901092529</t>
@@ -779,25 +779,25 @@
     <t xml:space="preserve">6.98895788192749</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03291368484497</t>
+    <t xml:space="preserve">7.03291320800781</t>
   </si>
   <si>
     <t xml:space="preserve">6.94500255584717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85709047317505</t>
+    <t xml:space="preserve">6.85709095001221</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72522401809692</t>
+    <t xml:space="preserve">6.72522354125977</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81313514709473</t>
+    <t xml:space="preserve">6.81313467025757</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76917886734009</t>
+    <t xml:space="preserve">6.76917934417725</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90104675292969</t>
+    <t xml:space="preserve">6.90104579925537</t>
   </si>
   <si>
     <t xml:space="preserve">6.63731241226196</t>
@@ -806,16 +806,16 @@
     <t xml:space="preserve">7.12082529067993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34060430526733</t>
+    <t xml:space="preserve">7.34060478210449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51642656326294</t>
+    <t xml:space="preserve">7.5164270401001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56038284301758</t>
+    <t xml:space="preserve">7.56038236618042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851543426514</t>
+    <t xml:space="preserve">7.42851495742798</t>
   </si>
   <si>
     <t xml:space="preserve">7.7362060546875</t>
@@ -836,16 +836,16 @@
     <t xml:space="preserve">7.73774671554565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69302082061768</t>
+    <t xml:space="preserve">7.69302034378052</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60356616973877</t>
+    <t xml:space="preserve">7.60356664657593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91665410995483</t>
+    <t xml:space="preserve">7.91665506362915</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87192821502686</t>
+    <t xml:space="preserve">7.87192916870117</t>
   </si>
   <si>
     <t xml:space="preserve">7.96138095855713</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">8.58755779266357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36392402648926</t>
+    <t xml:space="preserve">8.36392307281494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63228511810303</t>
+    <t xml:space="preserve">8.63228416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54283046722412</t>
+    <t xml:space="preserve">8.54283142089844</t>
   </si>
   <si>
     <t xml:space="preserve">8.40864944458008</t>
@@ -878,16 +878,16 @@
     <t xml:space="preserve">8.45337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67701148986816</t>
+    <t xml:space="preserve">8.67701053619385</t>
   </si>
   <si>
     <t xml:space="preserve">8.49810409545898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81119251251221</t>
+    <t xml:space="preserve">8.81119155883789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7217378616333</t>
+    <t xml:space="preserve">8.72173881530762</t>
   </si>
   <si>
     <t xml:space="preserve">8.85591888427734</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">9.03482627868652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3766326904297</t>
+    <t xml:space="preserve">10.376633644104</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4500780105591</t>
+    <t xml:space="preserve">11.4500770568848</t>
   </si>
   <si>
     <t xml:space="preserve">10.734447479248</t>
@@ -908,10 +908,10 @@
     <t xml:space="preserve">11.0922622680664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9133548736572</t>
+    <t xml:space="preserve">10.9133539199829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1817150115967</t>
+    <t xml:space="preserve">11.181715965271</t>
   </si>
   <si>
     <t xml:space="preserve">11.3606224060059</t>
@@ -926,19 +926,19 @@
     <t xml:space="preserve">11.2711696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5555391311646</t>
+    <t xml:space="preserve">10.5555400848389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2871789932251</t>
+    <t xml:space="preserve">10.2871780395508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0028076171875</t>
+    <t xml:space="preserve">11.0028085708618</t>
   </si>
   <si>
     <t xml:space="preserve">10.6449928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4660863876343</t>
+    <t xml:space="preserve">10.46608543396</t>
   </si>
   <si>
     <t xml:space="preserve">10.1082715988159</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">10.018816947937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6129751205444</t>
+    <t xml:space="preserve">12.6129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9707908630371</t>
+    <t xml:space="preserve">12.9707899093628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0442342758179</t>
+    <t xml:space="preserve">14.0442333221436</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7758731842041</t>
+    <t xml:space="preserve">13.7758741378784</t>
   </si>
   <si>
     <t xml:space="preserve">13.5075130462646</t>
@@ -986,16 +986,16 @@
     <t xml:space="preserve">12.702428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.149697303772</t>
+    <t xml:space="preserve">13.1496963500977</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3286037445068</t>
+    <t xml:space="preserve">13.3286046981812</t>
   </si>
   <si>
     <t xml:space="preserve">13.9547815322876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5969657897949</t>
+    <t xml:space="preserve">13.5969648361206</t>
   </si>
   <si>
     <t xml:space="preserve">13.6864204406738</t>
@@ -1010,16 +1010,16 @@
     <t xml:space="preserve">15.2965879440308</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2071323394775</t>
+    <t xml:space="preserve">15.2071332931519</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5809564590454</t>
+    <t xml:space="preserve">14.5809574127197</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7598648071289</t>
+    <t xml:space="preserve">14.7598638534546</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4915046691895</t>
+    <t xml:space="preserve">14.4915037155151</t>
   </si>
   <si>
     <t xml:space="preserve">14.5400876998901</t>
@@ -60898,6 +60898,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2265">
+      <c r="A2265" s="1" t="n">
+        <v>45958.3333333333</v>
+      </c>
+      <c r="B2265" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2265" t="n">
+        <v>39.7999992370605</v>
+      </c>
+      <c r="D2265" t="n">
+        <v>39.7999992370605</v>
+      </c>
+      <c r="E2265" t="n">
+        <v>39.7999992370605</v>
+      </c>
+      <c r="F2265" t="n">
+        <v>39.7999992370605</v>
+      </c>
+      <c r="G2265" t="s">
+        <v>532</v>
+      </c>
+      <c r="H2265" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46539187431335</t>
+    <t xml:space="preserve">2.46539163589478</t>
   </si>
   <si>
     <t xml:space="preserve">FPE.MI</t>
@@ -47,61 +47,61 @@
     <t xml:space="preserve">2.42625856399536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43408489227295</t>
+    <t xml:space="preserve">2.43408513069153</t>
   </si>
   <si>
     <t xml:space="preserve">2.41060519218445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45756530761719</t>
+    <t xml:space="preserve">2.45756506919861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39495205879211</t>
+    <t xml:space="preserve">2.39495229721069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233880996704</t>
+    <t xml:space="preserve">2.33233904838562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41843175888062</t>
+    <t xml:space="preserve">2.41843199729919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3558189868927</t>
+    <t xml:space="preserve">2.35581851005554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37147235870361</t>
+    <t xml:space="preserve">2.37147188186646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50452518463135</t>
+    <t xml:space="preserve">2.50452494621277</t>
   </si>
   <si>
     <t xml:space="preserve">2.36364531517029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44973874092102</t>
+    <t xml:space="preserve">2.44973826408386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37303757667542</t>
+    <t xml:space="preserve">2.37303733825684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34955763816833</t>
+    <t xml:space="preserve">2.34955739974976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46382665634155</t>
+    <t xml:space="preserve">2.46382641792297</t>
   </si>
   <si>
     <t xml:space="preserve">2.38712525367737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45443415641785</t>
+    <t xml:space="preserve">2.45443439483643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34799218177795</t>
+    <t xml:space="preserve">2.34799242019653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48104500770569</t>
+    <t xml:space="preserve">2.48104524612427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37929844856262</t>
+    <t xml:space="preserve">2.3792986869812</t>
   </si>
   <si>
     <t xml:space="preserve">2.38556003570557</t>
@@ -113,22 +113,22 @@
     <t xml:space="preserve">2.78002262115479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36702036857605</t>
+    <t xml:space="preserve">3.36702060699463</t>
   </si>
   <si>
     <t xml:space="preserve">3.62529993057251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31066870689392</t>
+    <t xml:space="preserve">3.31066918373108</t>
   </si>
   <si>
     <t xml:space="preserve">3.25588202476501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20266127586365</t>
+    <t xml:space="preserve">3.20266103744507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05238962173462</t>
+    <t xml:space="preserve">3.0523898601532</t>
   </si>
   <si>
     <t xml:space="preserve">3.09152293205261</t>
@@ -137,22 +137,22 @@
     <t xml:space="preserve">3.04456329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03673672676086</t>
+    <t xml:space="preserve">3.03673648834229</t>
   </si>
   <si>
     <t xml:space="preserve">3.03830170631409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15413618087769</t>
+    <t xml:space="preserve">3.15413665771484</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30910396575928</t>
+    <t xml:space="preserve">3.3091037273407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30284214019775</t>
+    <t xml:space="preserve">3.3028416633606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35762810707092</t>
+    <t xml:space="preserve">3.35762858390808</t>
   </si>
   <si>
     <t xml:space="preserve">3.57677483558655</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">3.52198815345764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40458869934082</t>
+    <t xml:space="preserve">3.4045889377594</t>
   </si>
   <si>
     <t xml:space="preserve">3.59242820739746</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">3.60025405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59555840492249</t>
+    <t xml:space="preserve">3.59555816650391</t>
   </si>
   <si>
     <t xml:space="preserve">3.32632231712341</t>
@@ -185,121 +185,121 @@
     <t xml:space="preserve">3.29501581192017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37484693527222</t>
+    <t xml:space="preserve">3.37484741210938</t>
   </si>
   <si>
     <t xml:space="preserve">3.38267397880554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44372224807739</t>
+    <t xml:space="preserve">3.44372177124023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59086227416992</t>
+    <t xml:space="preserve">3.5908625125885</t>
   </si>
   <si>
     <t xml:space="preserve">3.47972440719604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42650294303894</t>
+    <t xml:space="preserve">3.42650270462036</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41241502761841</t>
+    <t xml:space="preserve">3.41241526603699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24022936820984</t>
+    <t xml:space="preserve">3.24022912979126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21048808097839</t>
+    <t xml:space="preserve">3.21048784255981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28405833244324</t>
+    <t xml:space="preserve">3.28405857086182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16196298599243</t>
+    <t xml:space="preserve">3.16196250915527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20892262458801</t>
+    <t xml:space="preserve">3.20892238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13848304748535</t>
+    <t xml:space="preserve">3.13848328590393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23240232467651</t>
+    <t xml:space="preserve">3.23240280151367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31849551200867</t>
+    <t xml:space="preserve">3.31849527359009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27623152732849</t>
+    <t xml:space="preserve">3.27623176574707</t>
   </si>
   <si>
     <t xml:space="preserve">3.18857312202454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1431782245636</t>
+    <t xml:space="preserve">3.14317870140076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11500310897827</t>
+    <t xml:space="preserve">3.11500263214111</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0007336139679</t>
+    <t xml:space="preserve">3.00073409080505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97412323951721</t>
+    <t xml:space="preserve">2.97412347793579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06021666526794</t>
+    <t xml:space="preserve">3.06021642684937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90368366241455</t>
+    <t xml:space="preserve">2.90368342399597</t>
   </si>
   <si>
     <t xml:space="preserve">2.89585709571838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82854795455933</t>
+    <t xml:space="preserve">2.82854771614075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83637452125549</t>
+    <t xml:space="preserve">2.83637475967407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90994453430176</t>
+    <t xml:space="preserve">2.90994477272034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491231918335</t>
+    <t xml:space="preserve">3.06491279602051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13065576553345</t>
+    <t xml:space="preserve">3.13065600395203</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14474415779114</t>
+    <t xml:space="preserve">3.14474439620972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21361875534058</t>
+    <t xml:space="preserve">3.213618516922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28562355041504</t>
+    <t xml:space="preserve">3.28562378883362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35919404029846</t>
+    <t xml:space="preserve">3.35919427871704</t>
   </si>
   <si>
     <t xml:space="preserve">3.36388993263245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91332054138184</t>
+    <t xml:space="preserve">3.91332006454468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34378623962402</t>
+    <t xml:space="preserve">4.34378528594971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79381704330444</t>
+    <t xml:space="preserve">4.7938175201416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47864818572998</t>
+    <t xml:space="preserve">5.47864770889282</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09303951263428</t>
+    <t xml:space="preserve">6.09303903579712</t>
   </si>
   <si>
     <t xml:space="preserve">5.41603517532349</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">5.71344804763794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56865406036377</t>
+    <t xml:space="preserve">5.56865501403809</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41994857788086</t>
+    <t xml:space="preserve">5.41994905471802</t>
   </si>
   <si>
     <t xml:space="preserve">5.16558265686035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9464373588562</t>
+    <t xml:space="preserve">4.94643688201904</t>
   </si>
   <si>
     <t xml:space="preserve">4.70381116867065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6764178276062</t>
+    <t xml:space="preserve">4.67641735076904</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0090503692627</t>
+    <t xml:space="preserve">5.00904989242554</t>
   </si>
   <si>
     <t xml:space="preserve">5.55691432952881</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">5.30646228790283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22428226470947</t>
+    <t xml:space="preserve">5.22428274154663</t>
   </si>
   <si>
     <t xml:space="preserve">5.19688892364502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32211589813232</t>
+    <t xml:space="preserve">5.32211542129517</t>
   </si>
   <si>
     <t xml:space="preserve">5.47082090377808</t>
@@ -350,19 +350,19 @@
     <t xml:space="preserve">5.36907529830933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2908091545105</t>
+    <t xml:space="preserve">5.29080963134766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17340993881226</t>
+    <t xml:space="preserve">5.1734094619751</t>
   </si>
   <si>
     <t xml:space="preserve">5.09514284133911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22036981582642</t>
+    <t xml:space="preserve">5.22036933898926</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10296964645386</t>
+    <t xml:space="preserve">5.1029691696167</t>
   </si>
   <si>
     <t xml:space="preserve">4.9933967590332</t>
@@ -374,16 +374,16 @@
     <t xml:space="preserve">4.98556995391846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75859689712524</t>
+    <t xml:space="preserve">4.7585973739624</t>
   </si>
   <si>
     <t xml:space="preserve">4.77033758163452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86425685882568</t>
+    <t xml:space="preserve">4.86425733566284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88773679733276</t>
+    <t xml:space="preserve">4.88773727416992</t>
   </si>
   <si>
     <t xml:space="preserve">4.83295106887817</t>
@@ -395,13 +395,13 @@
     <t xml:space="preserve">4.82903718948364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72337770462036</t>
+    <t xml:space="preserve">4.72337818145752</t>
   </si>
   <si>
     <t xml:space="preserve">4.68815755844116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78207731246948</t>
+    <t xml:space="preserve">4.78207683563232</t>
   </si>
   <si>
     <t xml:space="preserve">4.8759970664978</t>
@@ -410,16 +410,16 @@
     <t xml:space="preserve">5.03644371032715</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92687082290649</t>
+    <t xml:space="preserve">4.92687034606934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81338453292847</t>
+    <t xml:space="preserve">4.81338405609131</t>
   </si>
   <si>
     <t xml:space="preserve">4.86034393310547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00122308731079</t>
+    <t xml:space="preserve">5.00122404098511</t>
   </si>
   <si>
     <t xml:space="preserve">4.77425050735474</t>
@@ -431,10 +431,10 @@
     <t xml:space="preserve">4.69989776611328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69598436355591</t>
+    <t xml:space="preserve">4.69598484039307</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90730333328247</t>
+    <t xml:space="preserve">4.90730381011963</t>
   </si>
   <si>
     <t xml:space="preserve">5.20471620559692</t>
@@ -449,10 +449,10 @@
     <t xml:space="preserve">5.24384927749634</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36124753952026</t>
+    <t xml:space="preserve">5.36124849319458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40038251876831</t>
+    <t xml:space="preserve">5.40038204193115</t>
   </si>
   <si>
     <t xml:space="preserve">5.51778173446655</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">5.63518095016479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96991682052612</t>
+    <t xml:space="preserve">4.96991634368896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93078374862671</t>
+    <t xml:space="preserve">4.93078327178955</t>
   </si>
   <si>
     <t xml:space="preserve">4.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12644958496094</t>
+    <t xml:space="preserve">5.1264500617981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04818248748779</t>
+    <t xml:space="preserve">5.04818296432495</t>
   </si>
   <si>
     <t xml:space="preserve">5.08731603622437</t>
@@ -485,43 +485,43 @@
     <t xml:space="preserve">5.26159715652466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42104005813599</t>
+    <t xml:space="preserve">5.42103910446167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34131860733032</t>
+    <t xml:space="preserve">5.34131813049316</t>
   </si>
   <si>
     <t xml:space="preserve">5.22173690795898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14201498031616</t>
+    <t xml:space="preserve">5.14201545715332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1021556854248</t>
+    <t xml:space="preserve">5.10215520858765</t>
   </si>
   <si>
     <t xml:space="preserve">5.18187618255615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38117933273315</t>
+    <t xml:space="preserve">5.381178855896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30145835876465</t>
+    <t xml:space="preserve">5.30145788192749</t>
   </si>
   <si>
     <t xml:space="preserve">4.9028525352478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50076150894165</t>
+    <t xml:space="preserve">5.50076103210449</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46089935302734</t>
+    <t xml:space="preserve">5.46090030670166</t>
   </si>
   <si>
     <t xml:space="preserve">5.580482006073</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54062128067017</t>
+    <t xml:space="preserve">5.54062175750732</t>
   </si>
   <si>
     <t xml:space="preserve">5.62034273147583</t>
@@ -533,19 +533,19 @@
     <t xml:space="preserve">4.98257303237915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82313108444214</t>
+    <t xml:space="preserve">4.82313060760498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06229448318481</t>
+    <t xml:space="preserve">5.06229400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02243423461914</t>
+    <t xml:space="preserve">5.02243375778198</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74341011047363</t>
+    <t xml:space="preserve">4.74340963363647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78327035903931</t>
+    <t xml:space="preserve">4.78327083587646</t>
   </si>
   <si>
     <t xml:space="preserve">4.86299133300781</t>
@@ -554,19 +554,19 @@
     <t xml:space="preserve">5.73992443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81964588165283</t>
+    <t xml:space="preserve">5.81964635848999</t>
   </si>
   <si>
     <t xml:space="preserve">5.70006418228149</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6602029800415</t>
+    <t xml:space="preserve">5.66020345687866</t>
   </si>
   <si>
     <t xml:space="preserve">5.77978467941284</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85950565338135</t>
+    <t xml:space="preserve">5.85950613021851</t>
   </si>
   <si>
     <t xml:space="preserve">5.97908782958984</t>
@@ -575,22 +575,22 @@
     <t xml:space="preserve">6.29797267913818</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13853025436401</t>
+    <t xml:space="preserve">6.13852977752686</t>
   </si>
   <si>
     <t xml:space="preserve">6.05880880355835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825122833252</t>
+    <t xml:space="preserve">6.21825170516968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09866952896118</t>
+    <t xml:space="preserve">6.09867000579834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3851842880249</t>
+    <t xml:space="preserve">6.38518476486206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25998449325562</t>
+    <t xml:space="preserve">6.25998544692993</t>
   </si>
   <si>
     <t xml:space="preserve">6.30171823501587</t>
@@ -602,10 +602,10 @@
     <t xml:space="preserve">6.426917552948</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34345102310181</t>
+    <t xml:space="preserve">6.34345149993896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46865034103394</t>
+    <t xml:space="preserve">6.46865081787109</t>
   </si>
   <si>
     <t xml:space="preserve">5.96785259246826</t>
@@ -614,19 +614,19 @@
     <t xml:space="preserve">6.0095853805542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13478422164917</t>
+    <t xml:space="preserve">6.13478469848633</t>
   </si>
   <si>
     <t xml:space="preserve">6.05131816864014</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92611885070801</t>
+    <t xml:space="preserve">5.92611932754517</t>
   </si>
   <si>
     <t xml:space="preserve">6.09305191040039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51038408279419</t>
+    <t xml:space="preserve">6.51038455963135</t>
   </si>
   <si>
     <t xml:space="preserve">5.84265232086182</t>
@@ -635,82 +635,82 @@
     <t xml:space="preserve">5.88438558578491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05291604995728</t>
+    <t xml:space="preserve">7.05291652679443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09624671936035</t>
+    <t xml:space="preserve">8.09624767303467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80411338806152</t>
+    <t xml:space="preserve">7.80411529541016</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63718032836914</t>
+    <t xml:space="preserve">7.6371808052063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55371570587158</t>
+    <t xml:space="preserve">7.55371522903442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34504985809326</t>
+    <t xml:space="preserve">7.34504890441895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17811584472656</t>
+    <t xml:space="preserve">7.17811679840088</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51198148727417</t>
+    <t xml:space="preserve">7.51198196411133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47024822235107</t>
+    <t xml:space="preserve">7.47024869918823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30331611633301</t>
+    <t xml:space="preserve">7.30331516265869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851591110229</t>
+    <t xml:space="preserve">7.42851448059082</t>
   </si>
   <si>
     <t xml:space="preserve">7.26158237457275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3867826461792</t>
+    <t xml:space="preserve">7.38678216934204</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9694504737854</t>
+    <t xml:space="preserve">6.96944952011108</t>
   </si>
   <si>
     <t xml:space="preserve">7.21984910964966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544801712036</t>
+    <t xml:space="preserve">7.59544897079468</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76238203048706</t>
+    <t xml:space="preserve">7.76238107681274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84584665298462</t>
+    <t xml:space="preserve">7.84584808349609</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67891359329224</t>
+    <t xml:space="preserve">7.67891454696655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01118278503418</t>
+    <t xml:space="preserve">7.01118183135986</t>
   </si>
   <si>
     <t xml:space="preserve">7.09464979171753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9277172088623</t>
+    <t xml:space="preserve">6.92771577835083</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76078367233276</t>
+    <t xml:space="preserve">6.76078319549561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80251693725586</t>
+    <t xml:space="preserve">6.80251598358154</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71904993057251</t>
+    <t xml:space="preserve">6.71905040740967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84425020217896</t>
+    <t xml:space="preserve">6.84424924850464</t>
   </si>
   <si>
     <t xml:space="preserve">6.59385061264038</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">6.67731666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55211639404297</t>
+    <t xml:space="preserve">6.55211782455444</t>
   </si>
   <si>
     <t xml:space="preserve">5.75918626785278</t>
@@ -731,73 +731,73 @@
     <t xml:space="preserve">5.80091905593872</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67572021484375</t>
+    <t xml:space="preserve">5.67571926116943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5922532081604</t>
+    <t xml:space="preserve">5.59225273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6339864730835</t>
+    <t xml:space="preserve">5.63398599624634</t>
   </si>
   <si>
     <t xml:space="preserve">5.46705341339111</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5505199432373</t>
+    <t xml:space="preserve">5.55051946640015</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17492055892944</t>
+    <t xml:space="preserve">5.1749210357666</t>
   </si>
   <si>
     <t xml:space="preserve">5.25838756561279</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38358640670776</t>
+    <t xml:space="preserve">5.38358688354492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13638305664062</t>
+    <t xml:space="preserve">7.13638353347778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47247123718262</t>
+    <t xml:space="preserve">7.47247076034546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25269269943237</t>
+    <t xml:space="preserve">7.25269222259521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29664897918701</t>
+    <t xml:space="preserve">7.29664754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20873689651489</t>
+    <t xml:space="preserve">7.20873594284058</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16478109359741</t>
+    <t xml:space="preserve">7.1647801399231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07686901092529</t>
+    <t xml:space="preserve">7.07686996459961</t>
   </si>
   <si>
     <t xml:space="preserve">6.98895788192749</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03291320800781</t>
+    <t xml:space="preserve">7.03291368484497</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94500255584717</t>
+    <t xml:space="preserve">6.94500207901001</t>
   </si>
   <si>
     <t xml:space="preserve">6.85709095001221</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72522354125977</t>
+    <t xml:space="preserve">6.72522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81313467025757</t>
+    <t xml:space="preserve">6.81313514709473</t>
   </si>
   <si>
     <t xml:space="preserve">6.76917934417725</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90104579925537</t>
+    <t xml:space="preserve">6.90104675292969</t>
   </si>
   <si>
     <t xml:space="preserve">6.63731241226196</t>
@@ -806,25 +806,25 @@
     <t xml:space="preserve">7.12082529067993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34060478210449</t>
+    <t xml:space="preserve">7.34060382843018</t>
   </si>
   <si>
     <t xml:space="preserve">7.5164270401001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56038236618042</t>
+    <t xml:space="preserve">7.56038284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851495742798</t>
+    <t xml:space="preserve">7.42851543426514</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7362060546875</t>
+    <t xml:space="preserve">7.73620510101318</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69224977493286</t>
+    <t xml:space="preserve">7.6922492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829397201538</t>
+    <t xml:space="preserve">7.64829349517822</t>
   </si>
   <si>
     <t xml:space="preserve">7.78247404098511</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">7.69302034378052</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60356664657593</t>
+    <t xml:space="preserve">7.60356712341309</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91665506362915</t>
+    <t xml:space="preserve">7.91665458679199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87192916870117</t>
+    <t xml:space="preserve">7.87192869186401</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96138095855713</t>
+    <t xml:space="preserve">7.96138143539429</t>
   </si>
   <si>
     <t xml:space="preserve">8.2297420501709</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">8.76646614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58755779266357</t>
+    <t xml:space="preserve">8.58755683898926</t>
   </si>
   <si>
     <t xml:space="preserve">8.36392307281494</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">8.54283142089844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40864944458008</t>
+    <t xml:space="preserve">8.40865039825439</t>
   </si>
   <si>
     <t xml:space="preserve">8.27446937561035</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">9.03482627868652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.376633644104</t>
+    <t xml:space="preserve">10.3766326904297</t>
   </si>
   <si>
     <t xml:space="preserve">11.4500770568848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.734447479248</t>
+    <t xml:space="preserve">10.7344465255737</t>
   </si>
   <si>
     <t xml:space="preserve">11.0922622680664</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">11.6289844512939</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5395307540894</t>
+    <t xml:space="preserve">11.539529800415</t>
   </si>
   <si>
     <t xml:space="preserve">11.2711696624756</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">10.5555400848389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2871780395508</t>
+    <t xml:space="preserve">10.2871789932251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0028085708618</t>
+    <t xml:space="preserve">11.0028095245361</t>
   </si>
   <si>
     <t xml:space="preserve">10.6449928283691</t>
@@ -950,10 +950,10 @@
     <t xml:space="preserve">9.75045585632324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.018816947937</t>
+    <t xml:space="preserve">10.0188159942627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6129760742188</t>
+    <t xml:space="preserve">12.6129751205444</t>
   </si>
   <si>
     <t xml:space="preserve">12.9707899093628</t>
@@ -974,19 +974,19 @@
     <t xml:space="preserve">13.0602445602417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4180593490601</t>
+    <t xml:space="preserve">13.4180583953857</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8813362121582</t>
+    <t xml:space="preserve">12.8813371658325</t>
   </si>
   <si>
     <t xml:space="preserve">12.7918834686279</t>
   </si>
   <si>
-    <t xml:space="preserve">12.702428817749</t>
+    <t xml:space="preserve">12.7024278640747</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1496963500977</t>
+    <t xml:space="preserve">13.149697303772</t>
   </si>
   <si>
     <t xml:space="preserve">13.3286046981812</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">13.9547815322876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5969648361206</t>
+    <t xml:space="preserve">13.5969657897949</t>
   </si>
   <si>
     <t xml:space="preserve">13.6864204406738</t>
@@ -1007,31 +1007,31 @@
     <t xml:space="preserve">14.4020500183105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2965879440308</t>
+    <t xml:space="preserve">15.2965869903564</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2071332931519</t>
+    <t xml:space="preserve">15.2071342468262</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5809574127197</t>
+    <t xml:space="preserve">14.5809564590454</t>
   </si>
   <si>
     <t xml:space="preserve">14.7598638534546</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4915037155151</t>
+    <t xml:space="preserve">14.4915046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5400876998901</t>
+    <t xml:space="preserve">14.5400886535645</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3560361862183</t>
+    <t xml:space="preserve">14.3560371398926</t>
   </si>
   <si>
     <t xml:space="preserve">14.2640104293823</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1719846725464</t>
+    <t xml:space="preserve">14.1719837188721</t>
   </si>
   <si>
     <t xml:space="preserve">14.8161659240723</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">14.6321144104004</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3683223724365</t>
+    <t xml:space="preserve">15.3683214187622</t>
   </si>
   <si>
     <t xml:space="preserve">15.5523738861084</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">15.9204750061035</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2088394165039</t>
+    <t xml:space="preserve">17.2088413238525</t>
   </si>
   <si>
     <t xml:space="preserve">17.3008632659912</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">18.4051742553711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1413803100586</t>
+    <t xml:space="preserve">19.1413822174072</t>
   </si>
   <si>
     <t xml:space="preserve">19.6935367584229</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">22.2702617645264</t>
   </si>
   <si>
-    <t xml:space="preserve">22.822416305542</t>
+    <t xml:space="preserve">22.8224182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6137962341309</t>
+    <t xml:space="preserve">20.6137943267822</t>
   </si>
   <si>
     <t xml:space="preserve">19.3254337310791</t>
@@ -1106,10 +1106,10 @@
     <t xml:space="preserve">22.0862102508545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0064678192139</t>
+    <t xml:space="preserve">23.0064697265625</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5586261749268</t>
+    <t xml:space="preserve">23.5586242675781</t>
   </si>
   <si>
     <t xml:space="preserve">23.74267578125</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">24.6629333496094</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8469886779785</t>
+    <t xml:space="preserve">24.8469867706299</t>
   </si>
   <si>
     <t xml:space="preserve">24.2948303222656</t>
@@ -1151,16 +1151,16 @@
     <t xml:space="preserve">27.975866317749</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9206943511963</t>
+    <t xml:space="preserve">30.9206924438477</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0801753997803</t>
+    <t xml:space="preserve">29.0801773071289</t>
   </si>
   <si>
-    <t xml:space="preserve">30.736644744873</t>
+    <t xml:space="preserve">30.7366428375244</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3685398101807</t>
+    <t xml:space="preserve">30.3685417175293</t>
   </si>
   <si>
     <t xml:space="preserve">29.2642288208008</t>
@@ -1172,10 +1172,10 @@
     <t xml:space="preserve">34.2336273193359</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7857780456543</t>
+    <t xml:space="preserve">34.7857818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8655204772949</t>
+    <t xml:space="preserve">33.8655166625977</t>
   </si>
   <si>
     <t xml:space="preserve">33.4974212646484</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">27.7918167114258</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8961238861084</t>
+    <t xml:space="preserve">28.896125793457</t>
   </si>
   <si>
     <t xml:space="preserve">29.4482803344727</t>
@@ -1208,19 +1208,19 @@
     <t xml:space="preserve">28.5280208587646</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7120723724365</t>
+    <t xml:space="preserve">28.7120742797852</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3439693450928</t>
+    <t xml:space="preserve">28.3439674377441</t>
   </si>
   <si>
     <t xml:space="preserve">27.055606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8715572357178</t>
+    <t xml:space="preserve">26.8715553283691</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3991413116455</t>
+    <t xml:space="preserve">25.3991432189941</t>
   </si>
   <si>
     <t xml:space="preserve">25.7672443389893</t>
@@ -1241,13 +1241,13 @@
     <t xml:space="preserve">30.0004329681396</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3931083679199</t>
+    <t xml:space="preserve">32.3931121826172</t>
   </si>
   <si>
     <t xml:space="preserve">32.209056854248</t>
   </si>
   <si>
-    <t xml:space="preserve">31.28879737854</t>
+    <t xml:space="preserve">31.2887954711914</t>
   </si>
   <si>
     <t xml:space="preserve">31.6569023132324</t>
@@ -1259,34 +1259,34 @@
     <t xml:space="preserve">32.0337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5990715026855</t>
+    <t xml:space="preserve">32.5990676879883</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1643714904785</t>
+    <t xml:space="preserve">33.1643753051758</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6569004058838</t>
+    <t xml:space="preserve">31.6568984985352</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4106369018555</t>
+    <t xml:space="preserve">32.4106407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7875022888184</t>
+    <t xml:space="preserve">32.7875061035156</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9759407043457</t>
+    <t xml:space="preserve">32.9759368896484</t>
   </si>
   <si>
     <t xml:space="preserve">30.9031639099121</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8453369140625</t>
+    <t xml:space="preserve">31.8453350067139</t>
   </si>
   <si>
     <t xml:space="preserve">30.714729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5262985229492</t>
+    <t xml:space="preserve">30.5263004302979</t>
   </si>
   <si>
     <t xml:space="preserve">31.2800331115723</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">30.1494293212891</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3378639221191</t>
+    <t xml:space="preserve">30.3378658294678</t>
   </si>
   <si>
     <t xml:space="preserve">29.395694732666</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">28.2650909423828</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6997890472412</t>
+    <t xml:space="preserve">27.6997871398926</t>
   </si>
   <si>
     <t xml:space="preserve">28.0766563415527</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">25.2501468658447</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3079776763916</t>
+    <t xml:space="preserve">24.307975769043</t>
   </si>
   <si>
     <t xml:space="preserve">23.9311103820801</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">23.7426776885986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.177375793457</t>
+    <t xml:space="preserve">23.1773738861084</t>
   </si>
   <si>
     <t xml:space="preserve">22.6120719909668</t>
@@ -1370,10 +1370,10 @@
     <t xml:space="preserve">22.2352046966553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0467700958252</t>
+    <t xml:space="preserve">22.0467720031738</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8005084991455</t>
+    <t xml:space="preserve">22.8005065917969</t>
   </si>
   <si>
     <t xml:space="preserve">22.988941192627</t>
@@ -1388,19 +1388,19 @@
     <t xml:space="preserve">25.6270160675049</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3807506561279</t>
+    <t xml:space="preserve">26.3807525634766</t>
   </si>
   <si>
-    <t xml:space="preserve">27.134485244751</t>
+    <t xml:space="preserve">27.1344871520996</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9460525512695</t>
+    <t xml:space="preserve">26.9460544586182</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3229198455811</t>
+    <t xml:space="preserve">27.3229217529297</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1923160552979</t>
+    <t xml:space="preserve">26.1923179626465</t>
   </si>
   <si>
     <t xml:space="preserve">26.7576179504395</t>
@@ -60924,6 +60924,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2266">
+      <c r="A2266" s="1" t="n">
+        <v>45959.3333333333</v>
+      </c>
+      <c r="B2266" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2266" t="n">
+        <v>39.7999992370605</v>
+      </c>
+      <c r="D2266" t="n">
+        <v>39.7999992370605</v>
+      </c>
+      <c r="E2266" t="n">
+        <v>39.7999992370605</v>
+      </c>
+      <c r="F2266" t="n">
+        <v>39.7999992370605</v>
+      </c>
+      <c r="G2266" t="s">
+        <v>532</v>
+      </c>
+      <c r="H2266" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46539163589478</t>
+    <t xml:space="preserve">2.46539211273193</t>
   </si>
   <si>
     <t xml:space="preserve">FPE.MI</t>
@@ -50,37 +50,37 @@
     <t xml:space="preserve">2.43408513069153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41060519218445</t>
+    <t xml:space="preserve">2.41060495376587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45756506919861</t>
+    <t xml:space="preserve">2.45756483078003</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39495229721069</t>
+    <t xml:space="preserve">2.39495205879211</t>
   </si>
   <si>
     <t xml:space="preserve">2.33233904838562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41843199729919</t>
+    <t xml:space="preserve">2.41843175888062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35581851005554</t>
+    <t xml:space="preserve">2.35581874847412</t>
   </si>
   <si>
     <t xml:space="preserve">2.37147188186646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50452494621277</t>
+    <t xml:space="preserve">2.50452518463135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36364531517029</t>
+    <t xml:space="preserve">2.36364555358887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44973826408386</t>
+    <t xml:space="preserve">2.44973850250244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37303733825684</t>
+    <t xml:space="preserve">2.37303757667542</t>
   </si>
   <si>
     <t xml:space="preserve">2.34955739974976</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">2.34799242019653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48104524612427</t>
+    <t xml:space="preserve">2.48104500770569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3792986869812</t>
+    <t xml:space="preserve">2.37929892539978</t>
   </si>
   <si>
     <t xml:space="preserve">2.38556003570557</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">3.36702060699463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62529993057251</t>
+    <t xml:space="preserve">3.62529969215393</t>
   </si>
   <si>
     <t xml:space="preserve">3.31066918373108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25588202476501</t>
+    <t xml:space="preserve">3.25588250160217</t>
   </si>
   <si>
     <t xml:space="preserve">3.20266103744507</t>
@@ -134,94 +134,94 @@
     <t xml:space="preserve">3.09152293205261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04456329345703</t>
+    <t xml:space="preserve">3.04456305503845</t>
   </si>
   <si>
     <t xml:space="preserve">3.03673648834229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03830170631409</t>
+    <t xml:space="preserve">3.03830146789551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15413665771484</t>
+    <t xml:space="preserve">3.15413641929626</t>
   </si>
   <si>
     <t xml:space="preserve">3.3091037273407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3028416633606</t>
+    <t xml:space="preserve">3.30284237861633</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35762858390808</t>
+    <t xml:space="preserve">3.35762882232666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57677483558655</t>
+    <t xml:space="preserve">3.57677507400513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52198815345764</t>
+    <t xml:space="preserve">3.52198839187622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4045889377594</t>
+    <t xml:space="preserve">3.40458822250366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59242820739746</t>
+    <t xml:space="preserve">3.59242796897888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58460140228271</t>
+    <t xml:space="preserve">3.58460164070129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67852067947388</t>
+    <t xml:space="preserve">3.67852115631104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60025405883789</t>
+    <t xml:space="preserve">3.60025453567505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59555816650391</t>
+    <t xml:space="preserve">3.59555864334106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632231712341</t>
+    <t xml:space="preserve">3.32632207870483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29501581192017</t>
+    <t xml:space="preserve">3.29501533508301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37484741210938</t>
+    <t xml:space="preserve">3.37484693527222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38267397880554</t>
+    <t xml:space="preserve">3.38267374038696</t>
   </si>
   <si>
     <t xml:space="preserve">3.44372177124023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5908625125885</t>
+    <t xml:space="preserve">3.59086227416992</t>
   </si>
   <si>
     <t xml:space="preserve">3.47972440719604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42650270462036</t>
+    <t xml:space="preserve">3.4265034198761</t>
   </si>
   <si>
     <t xml:space="preserve">3.41241526603699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24022912979126</t>
+    <t xml:space="preserve">3.2402286529541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21048784255981</t>
+    <t xml:space="preserve">3.21048808097839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28405857086182</t>
+    <t xml:space="preserve">3.28405833244324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16196250915527</t>
+    <t xml:space="preserve">3.16196298599243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20892238616943</t>
+    <t xml:space="preserve">3.20892286300659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13848328590393</t>
+    <t xml:space="preserve">3.13848304748535</t>
   </si>
   <si>
     <t xml:space="preserve">3.23240280151367</t>
@@ -230,88 +230,88 @@
     <t xml:space="preserve">3.31849527359009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27623176574707</t>
+    <t xml:space="preserve">3.27623152732849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18857312202454</t>
+    <t xml:space="preserve">3.18857336044312</t>
   </si>
   <si>
     <t xml:space="preserve">3.14317870140076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11500263214111</t>
+    <t xml:space="preserve">3.11500287055969</t>
   </si>
   <si>
     <t xml:space="preserve">3.00073409080505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97412347793579</t>
+    <t xml:space="preserve">2.97412323951721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06021642684937</t>
+    <t xml:space="preserve">3.06021666526794</t>
   </si>
   <si>
     <t xml:space="preserve">2.90368342399597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89585709571838</t>
+    <t xml:space="preserve">2.8958568572998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82854771614075</t>
+    <t xml:space="preserve">2.82854795455933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83637475967407</t>
+    <t xml:space="preserve">2.83637428283691</t>
   </si>
   <si>
     <t xml:space="preserve">2.90994477272034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491279602051</t>
+    <t xml:space="preserve">3.06491231918335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13065600395203</t>
+    <t xml:space="preserve">3.13065624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14474439620972</t>
+    <t xml:space="preserve">3.14474415779114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.213618516922</t>
+    <t xml:space="preserve">3.21361827850342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28562378883362</t>
+    <t xml:space="preserve">3.28562355041504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35919427871704</t>
+    <t xml:space="preserve">3.35919451713562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36388993263245</t>
+    <t xml:space="preserve">3.36389017105103</t>
   </si>
   <si>
     <t xml:space="preserve">3.91332006454468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34378528594971</t>
+    <t xml:space="preserve">4.34378576278687</t>
   </si>
   <si>
     <t xml:space="preserve">4.7938175201416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47864770889282</t>
+    <t xml:space="preserve">5.47864866256714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09303903579712</t>
+    <t xml:space="preserve">6.09303951263428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41603517532349</t>
+    <t xml:space="preserve">5.41603565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71344804763794</t>
+    <t xml:space="preserve">5.71344757080078</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56865501403809</t>
+    <t xml:space="preserve">5.56865453720093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41994905471802</t>
+    <t xml:space="preserve">5.41994857788086</t>
   </si>
   <si>
     <t xml:space="preserve">5.16558265686035</t>
@@ -326,31 +326,31 @@
     <t xml:space="preserve">4.67641735076904</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00904989242554</t>
+    <t xml:space="preserve">5.0090503692627</t>
   </si>
   <si>
     <t xml:space="preserve">5.55691432952881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30646228790283</t>
+    <t xml:space="preserve">5.30646276473999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22428274154663</t>
+    <t xml:space="preserve">5.22428178787231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19688892364502</t>
+    <t xml:space="preserve">5.19688940048218</t>
   </si>
   <si>
     <t xml:space="preserve">5.32211542129517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47082090377808</t>
+    <t xml:space="preserve">5.47082138061523</t>
   </si>
   <si>
     <t xml:space="preserve">5.36907529830933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29080963134766</t>
+    <t xml:space="preserve">5.29080867767334</t>
   </si>
   <si>
     <t xml:space="preserve">5.1734094619751</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">5.22036933898926</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1029691696167</t>
+    <t xml:space="preserve">5.10296964645386</t>
   </si>
   <si>
     <t xml:space="preserve">4.9933967590332</t>
@@ -374,7 +374,7 @@
     <t xml:space="preserve">4.98556995391846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7585973739624</t>
+    <t xml:space="preserve">4.75859785079956</t>
   </si>
   <si>
     <t xml:space="preserve">4.77033758163452</t>
@@ -383,10 +383,10 @@
     <t xml:space="preserve">4.86425733566284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88773727416992</t>
+    <t xml:space="preserve">4.88773679733276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83295106887817</t>
+    <t xml:space="preserve">4.83295059204102</t>
   </si>
   <si>
     <t xml:space="preserve">4.75468397140503</t>
@@ -395,40 +395,40 @@
     <t xml:space="preserve">4.82903718948364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72337818145752</t>
+    <t xml:space="preserve">4.7233772277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68815755844116</t>
+    <t xml:space="preserve">4.688157081604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78207683563232</t>
+    <t xml:space="preserve">4.78207731246948</t>
   </si>
   <si>
     <t xml:space="preserve">4.8759970664978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03644371032715</t>
+    <t xml:space="preserve">5.03644275665283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92687034606934</t>
+    <t xml:space="preserve">4.92686986923218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81338405609131</t>
+    <t xml:space="preserve">4.81338310241699</t>
   </si>
   <si>
     <t xml:space="preserve">4.86034393310547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00122404098511</t>
+    <t xml:space="preserve">5.00122356414795</t>
   </si>
   <si>
     <t xml:space="preserve">4.77425050735474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8212103843689</t>
+    <t xml:space="preserve">4.82120990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69989776611328</t>
+    <t xml:space="preserve">4.69989728927612</t>
   </si>
   <si>
     <t xml:space="preserve">4.69598484039307</t>
@@ -443,16 +443,16 @@
     <t xml:space="preserve">5.43951511383057</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28298234939575</t>
+    <t xml:space="preserve">5.28298282623291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384927749634</t>
+    <t xml:space="preserve">5.24384880065918</t>
   </si>
   <si>
     <t xml:space="preserve">5.36124849319458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40038204193115</t>
+    <t xml:space="preserve">5.40038156509399</t>
   </si>
   <si>
     <t xml:space="preserve">5.51778173446655</t>
@@ -464,85 +464,85 @@
     <t xml:space="preserve">4.96991634368896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93078327178955</t>
+    <t xml:space="preserve">4.93078422546387</t>
   </si>
   <si>
     <t xml:space="preserve">4.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1264500617981</t>
+    <t xml:space="preserve">5.12644910812378</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04818296432495</t>
+    <t xml:space="preserve">5.04818248748779</t>
   </si>
   <si>
     <t xml:space="preserve">5.08731603622437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59604835510254</t>
+    <t xml:space="preserve">5.59604787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26159715652466</t>
+    <t xml:space="preserve">5.26159763336182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42103910446167</t>
+    <t xml:space="preserve">5.42104005813599</t>
   </si>
   <si>
     <t xml:space="preserve">5.34131813049316</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22173690795898</t>
+    <t xml:space="preserve">5.22173643112183</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14201545715332</t>
+    <t xml:space="preserve">5.14201498031616</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10215520858765</t>
+    <t xml:space="preserve">5.1021556854248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18187618255615</t>
+    <t xml:space="preserve">5.18187570571899</t>
   </si>
   <si>
-    <t xml:space="preserve">5.381178855896</t>
+    <t xml:space="preserve">5.38117933273315</t>
   </si>
   <si>
     <t xml:space="preserve">5.30145788192749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9028525352478</t>
+    <t xml:space="preserve">4.90285158157349</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50076103210449</t>
+    <t xml:space="preserve">5.50076055526733</t>
   </si>
   <si>
     <t xml:space="preserve">5.46090030670166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.580482006073</t>
+    <t xml:space="preserve">5.58048248291016</t>
   </si>
   <si>
     <t xml:space="preserve">5.54062175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62034273147583</t>
+    <t xml:space="preserve">5.62034320831299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94271278381348</t>
+    <t xml:space="preserve">4.94271230697632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98257303237915</t>
+    <t xml:space="preserve">4.98257350921631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82313060760498</t>
+    <t xml:space="preserve">4.82313108444214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06229400634766</t>
+    <t xml:space="preserve">5.06229448318481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02243375778198</t>
+    <t xml:space="preserve">5.0224347114563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74340963363647</t>
+    <t xml:space="preserve">4.74341011047363</t>
   </si>
   <si>
     <t xml:space="preserve">4.78327083587646</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">4.86299133300781</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73992443084717</t>
+    <t xml:space="preserve">5.73992395401001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81964635848999</t>
+    <t xml:space="preserve">5.81964588165283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70006418228149</t>
+    <t xml:space="preserve">5.70006370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66020345687866</t>
+    <t xml:space="preserve">5.66020250320435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77978467941284</t>
+    <t xml:space="preserve">5.77978515625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85950613021851</t>
+    <t xml:space="preserve">5.85950660705566</t>
   </si>
   <si>
     <t xml:space="preserve">5.97908782958984</t>
@@ -575,7 +575,7 @@
     <t xml:space="preserve">6.29797267913818</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13852977752686</t>
+    <t xml:space="preserve">6.13853073120117</t>
   </si>
   <si>
     <t xml:space="preserve">6.05880880355835</t>
@@ -590,88 +590,91 @@
     <t xml:space="preserve">6.38518476486206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25998544692993</t>
+    <t xml:space="preserve">6.25998449325562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30171823501587</t>
+    <t xml:space="preserve">6.30171775817871</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17651844024658</t>
+    <t xml:space="preserve">6.17651796340942</t>
   </si>
   <si>
-    <t xml:space="preserve">6.426917552948</t>
+    <t xml:space="preserve">6.42691802978516</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34345149993896</t>
+    <t xml:space="preserve">6.34345102310181</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46865081787109</t>
+    <t xml:space="preserve">6.46865129470825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96785259246826</t>
+    <t xml:space="preserve">5.9678521156311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0095853805542</t>
+    <t xml:space="preserve">6.00958490371704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13478469848633</t>
+    <t xml:space="preserve">6.13478565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05131816864014</t>
+    <t xml:space="preserve">6.05131864547729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92611932754517</t>
+    <t xml:space="preserve">5.92611837387085</t>
   </si>
   <si>
     <t xml:space="preserve">6.09305191040039</t>
   </si>
   <si>
+    <t xml:space="preserve">6.21825122833252</t>
+  </si>
+  <si>
     <t xml:space="preserve">6.51038455963135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84265232086182</t>
+    <t xml:space="preserve">5.84265279769897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88438558578491</t>
+    <t xml:space="preserve">5.88438606262207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05291652679443</t>
+    <t xml:space="preserve">7.05291604995728</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09624767303467</t>
+    <t xml:space="preserve">8.09624671936035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80411529541016</t>
+    <t xml:space="preserve">7.804114818573</t>
   </si>
   <si>
     <t xml:space="preserve">7.6371808052063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55371522903442</t>
+    <t xml:space="preserve">7.55371570587158</t>
   </si>
   <si>
     <t xml:space="preserve">7.34504890441895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17811679840088</t>
+    <t xml:space="preserve">7.17811584472656</t>
   </si>
   <si>
     <t xml:space="preserve">7.51198196411133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47024869918823</t>
+    <t xml:space="preserve">7.47024822235107</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30331516265869</t>
+    <t xml:space="preserve">7.30331563949585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851448059082</t>
+    <t xml:space="preserve">7.42851543426514</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26158237457275</t>
+    <t xml:space="preserve">7.26158142089844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38678216934204</t>
+    <t xml:space="preserve">7.3867826461792</t>
   </si>
   <si>
     <t xml:space="preserve">6.96944952011108</t>
@@ -680,10 +683,10 @@
     <t xml:space="preserve">7.21984910964966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544897079468</t>
+    <t xml:space="preserve">7.59544849395752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76238107681274</t>
+    <t xml:space="preserve">7.76238203048706</t>
   </si>
   <si>
     <t xml:space="preserve">7.84584808349609</t>
@@ -692,82 +695,82 @@
     <t xml:space="preserve">7.67891454696655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01118183135986</t>
+    <t xml:space="preserve">7.01118278503418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09464979171753</t>
+    <t xml:space="preserve">7.09464931488037</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92771577835083</t>
+    <t xml:space="preserve">6.92771673202515</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76078319549561</t>
+    <t xml:space="preserve">6.76078414916992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80251598358154</t>
+    <t xml:space="preserve">6.8025164604187</t>
   </si>
   <si>
     <t xml:space="preserve">6.71905040740967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84424924850464</t>
+    <t xml:space="preserve">6.84425020217896</t>
   </si>
   <si>
     <t xml:space="preserve">6.59385061264038</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67731666564941</t>
+    <t xml:space="preserve">6.67731714248657</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55211782455444</t>
+    <t xml:space="preserve">6.55211687088013</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75918626785278</t>
+    <t xml:space="preserve">5.75918579101562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71745204925537</t>
+    <t xml:space="preserve">5.71745252609253</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80091905593872</t>
+    <t xml:space="preserve">5.80091953277588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67571926116943</t>
+    <t xml:space="preserve">5.67571973800659</t>
   </si>
   <si>
     <t xml:space="preserve">5.59225273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63398599624634</t>
+    <t xml:space="preserve">5.6339864730835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46705341339111</t>
+    <t xml:space="preserve">5.46705293655396</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55051946640015</t>
+    <t xml:space="preserve">5.5505199432373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1749210357666</t>
+    <t xml:space="preserve">5.17492055892944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25838756561279</t>
+    <t xml:space="preserve">5.25838804244995</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38358688354492</t>
+    <t xml:space="preserve">5.38358640670776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13638353347778</t>
+    <t xml:space="preserve">7.13638257980347</t>
   </si>
   <si>
     <t xml:space="preserve">7.47247076034546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25269222259521</t>
+    <t xml:space="preserve">7.25269174575806</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29664754867554</t>
+    <t xml:space="preserve">7.2966480255127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20873594284058</t>
+    <t xml:space="preserve">7.20873641967773</t>
   </si>
   <si>
     <t xml:space="preserve">7.1647801399231</t>
@@ -785,13 +788,13 @@
     <t xml:space="preserve">6.94500207901001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85709095001221</t>
+    <t xml:space="preserve">6.85709142684937</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72522401809692</t>
+    <t xml:space="preserve">6.72522354125977</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81313514709473</t>
+    <t xml:space="preserve">6.81313467025757</t>
   </si>
   <si>
     <t xml:space="preserve">6.76917934417725</t>
@@ -812,43 +815,40 @@
     <t xml:space="preserve">7.5164270401001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56038284301758</t>
+    <t xml:space="preserve">7.56038236618042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851543426514</t>
+    <t xml:space="preserve">7.7362060546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73620510101318</t>
+    <t xml:space="preserve">7.69224977493286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6922492980957</t>
+    <t xml:space="preserve">7.64829397201538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829349517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78247404098511</t>
+    <t xml:space="preserve">7.78247356414795</t>
   </si>
   <si>
     <t xml:space="preserve">7.8272008895874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73774671554565</t>
+    <t xml:space="preserve">7.73774719238281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69302034378052</t>
+    <t xml:space="preserve">7.69302082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60356712341309</t>
+    <t xml:space="preserve">7.60356664657593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91665458679199</t>
+    <t xml:space="preserve">7.91665554046631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87192869186401</t>
+    <t xml:space="preserve">7.8719277381897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96138143539429</t>
+    <t xml:space="preserve">7.96138048171997</t>
   </si>
   <si>
     <t xml:space="preserve">8.2297420501709</t>
@@ -857,16 +857,16 @@
     <t xml:space="preserve">8.76646614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58755683898926</t>
+    <t xml:space="preserve">8.58755874633789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36392307281494</t>
+    <t xml:space="preserve">8.36392402648926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63228416442871</t>
+    <t xml:space="preserve">8.63228321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54283142089844</t>
+    <t xml:space="preserve">8.54283046722412</t>
   </si>
   <si>
     <t xml:space="preserve">8.40865039825439</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">8.45337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67701053619385</t>
+    <t xml:space="preserve">8.67701244354248</t>
   </si>
   <si>
     <t xml:space="preserve">8.49810409545898</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">8.81119155883789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72173881530762</t>
+    <t xml:space="preserve">8.7217378616333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85591888427734</t>
+    <t xml:space="preserve">8.85591983795166</t>
   </si>
   <si>
     <t xml:space="preserve">9.03482627868652</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">10.7344465255737</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0922622680664</t>
+    <t xml:space="preserve">11.0922613143921</t>
   </si>
   <si>
     <t xml:space="preserve">10.9133539199829</t>
@@ -914,25 +914,25 @@
     <t xml:space="preserve">11.181715965271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3606224060059</t>
+    <t xml:space="preserve">11.3606233596802</t>
   </si>
   <si>
     <t xml:space="preserve">11.6289844512939</t>
   </si>
   <si>
-    <t xml:space="preserve">11.539529800415</t>
+    <t xml:space="preserve">11.5395307540894</t>
   </si>
   <si>
     <t xml:space="preserve">11.2711696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5555400848389</t>
+    <t xml:space="preserve">10.5555391311646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2871789932251</t>
+    <t xml:space="preserve">10.2871780395508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0028095245361</t>
+    <t xml:space="preserve">11.0028085708618</t>
   </si>
   <si>
     <t xml:space="preserve">10.6449928283691</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">10.46608543396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1082715988159</t>
+    <t xml:space="preserve">10.1082706451416</t>
   </si>
   <si>
     <t xml:space="preserve">10.1977243423462</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">9.75045585632324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0188159942627</t>
+    <t xml:space="preserve">10.018816947937</t>
   </si>
   <si>
     <t xml:space="preserve">12.6129751205444</t>
@@ -959,64 +959,64 @@
     <t xml:space="preserve">12.9707899093628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0442333221436</t>
+    <t xml:space="preserve">14.0442342758179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7758741378784</t>
+    <t xml:space="preserve">13.7758731842041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5075130462646</t>
+    <t xml:space="preserve">13.507513999939</t>
   </si>
   <si>
     <t xml:space="preserve">13.2391519546509</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0602445602417</t>
+    <t xml:space="preserve">13.0602436065674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4180583953857</t>
+    <t xml:space="preserve">13.4180593490601</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8813371658325</t>
+    <t xml:space="preserve">12.8813352584839</t>
   </si>
   <si>
     <t xml:space="preserve">12.7918834686279</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7024278640747</t>
+    <t xml:space="preserve">12.702428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.149697303772</t>
+    <t xml:space="preserve">13.1496982574463</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3286046981812</t>
+    <t xml:space="preserve">13.3286056518555</t>
   </si>
   <si>
     <t xml:space="preserve">13.9547815322876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5969657897949</t>
+    <t xml:space="preserve">13.5969667434692</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6864204406738</t>
+    <t xml:space="preserve">13.6864213943481</t>
   </si>
   <si>
-    <t xml:space="preserve">13.865327835083</t>
+    <t xml:space="preserve">13.8653268814087</t>
   </si>
   <si>
     <t xml:space="preserve">14.4020500183105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2965869903564</t>
+    <t xml:space="preserve">15.2965879440308</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2071342468262</t>
+    <t xml:space="preserve">15.2071332931519</t>
   </si>
   <si>
     <t xml:space="preserve">14.5809564590454</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7598638534546</t>
+    <t xml:space="preserve">14.7598648071289</t>
   </si>
   <si>
     <t xml:space="preserve">14.4915046691895</t>
@@ -1031,16 +1031,16 @@
     <t xml:space="preserve">14.2640104293823</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1719837188721</t>
+    <t xml:space="preserve">14.1719846725464</t>
   </si>
   <si>
     <t xml:space="preserve">14.8161659240723</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6321144104004</t>
+    <t xml:space="preserve">14.6321134567261</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3683214187622</t>
+    <t xml:space="preserve">15.3683233261108</t>
   </si>
   <si>
     <t xml:space="preserve">15.5523738861084</t>
@@ -1049,31 +1049,31 @@
     <t xml:space="preserve">16.104528427124</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3806056976318</t>
+    <t xml:space="preserve">16.3806037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9204750061035</t>
+    <t xml:space="preserve">15.9204759597778</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2088413238525</t>
+    <t xml:space="preserve">17.2088394165039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3008632659912</t>
+    <t xml:space="preserve">17.3008651733398</t>
   </si>
   <si>
     <t xml:space="preserve">17.4849166870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.576940536499</t>
+    <t xml:space="preserve">17.5769424438477</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6689682006836</t>
+    <t xml:space="preserve">17.6689701080322</t>
   </si>
   <si>
     <t xml:space="preserve">18.4051742553711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1413822174072</t>
+    <t xml:space="preserve">19.1413803100586</t>
   </si>
   <si>
     <t xml:space="preserve">19.6935367584229</t>
@@ -1082,19 +1082,19 @@
     <t xml:space="preserve">20.0616397857666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5340557098389</t>
+    <t xml:space="preserve">21.5340538024902</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3745708465576</t>
+    <t xml:space="preserve">23.3745727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2702617645264</t>
+    <t xml:space="preserve">22.270263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8224182128906</t>
+    <t xml:space="preserve">22.822416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6137943267822</t>
+    <t xml:space="preserve">20.6137962341309</t>
   </si>
   <si>
     <t xml:space="preserve">19.3254337310791</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">21.902156829834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0862102508545</t>
+    <t xml:space="preserve">22.0862083435059</t>
   </si>
   <si>
     <t xml:space="preserve">23.0064697265625</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">23.9267272949219</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6629333496094</t>
+    <t xml:space="preserve">24.662935256958</t>
   </si>
   <si>
     <t xml:space="preserve">24.8469867706299</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2948303222656</t>
+    <t xml:space="preserve">24.2948322296143</t>
   </si>
   <si>
     <t xml:space="preserve">24.1107807159424</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">23.1905212402344</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2150897979736</t>
+    <t xml:space="preserve">25.215087890625</t>
   </si>
   <si>
     <t xml:space="preserve">22.4543132781982</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">25.9512958526611</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5034523010254</t>
+    <t xml:space="preserve">26.5034503936768</t>
   </si>
   <si>
     <t xml:space="preserve">27.975866317749</t>
@@ -1157,40 +1157,40 @@
     <t xml:space="preserve">29.0801773071289</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7366428375244</t>
+    <t xml:space="preserve">30.7366466522217</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3685417175293</t>
+    <t xml:space="preserve">30.3685398101807</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2642288208008</t>
+    <t xml:space="preserve">29.2642269134521</t>
   </si>
   <si>
     <t xml:space="preserve">31.4728507995605</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2336273193359</t>
+    <t xml:space="preserve">34.2336235046387</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7857818603516</t>
+    <t xml:space="preserve">34.7857780456543</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8655166625977</t>
+    <t xml:space="preserve">33.8655204772949</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4974212646484</t>
+    <t xml:space="preserve">33.4974174499512</t>
   </si>
   <si>
     <t xml:space="preserve">30.1844863891602</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4237098693848</t>
+    <t xml:space="preserve">27.4237117767334</t>
   </si>
   <si>
     <t xml:space="preserve">26.6875038146973</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5831928253174</t>
+    <t xml:space="preserve">25.5831909179688</t>
   </si>
   <si>
     <t xml:space="preserve">26.3194007873535</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">27.7918167114258</t>
   </si>
   <si>
-    <t xml:space="preserve">28.896125793457</t>
+    <t xml:space="preserve">28.8961238861084</t>
   </si>
   <si>
     <t xml:space="preserve">29.4482803344727</t>
@@ -1211,16 +1211,16 @@
     <t xml:space="preserve">28.7120742797852</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3439674377441</t>
+    <t xml:space="preserve">28.3439693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">27.055606842041</t>
+    <t xml:space="preserve">27.0556087493896</t>
   </si>
   <si>
     <t xml:space="preserve">26.8715553283691</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3991432189941</t>
+    <t xml:space="preserve">25.3991413116455</t>
   </si>
   <si>
     <t xml:space="preserve">25.7672443389893</t>
@@ -1241,13 +1241,13 @@
     <t xml:space="preserve">30.0004329681396</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3931121826172</t>
+    <t xml:space="preserve">32.3931083679199</t>
   </si>
   <si>
     <t xml:space="preserve">32.209056854248</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2887954711914</t>
+    <t xml:space="preserve">31.28879737854</t>
   </si>
   <si>
     <t xml:space="preserve">31.6569023132324</t>
@@ -1259,34 +1259,34 @@
     <t xml:space="preserve">32.0337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5990676879883</t>
+    <t xml:space="preserve">32.5990715026855</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1643753051758</t>
+    <t xml:space="preserve">33.1643714904785</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6568984985352</t>
+    <t xml:space="preserve">31.6569004058838</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4106407165527</t>
+    <t xml:space="preserve">32.4106369018555</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7875061035156</t>
+    <t xml:space="preserve">32.7875022888184</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9759368896484</t>
+    <t xml:space="preserve">32.9759407043457</t>
   </si>
   <si>
     <t xml:space="preserve">30.9031639099121</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8453350067139</t>
+    <t xml:space="preserve">31.8453369140625</t>
   </si>
   <si>
     <t xml:space="preserve">30.714729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5263004302979</t>
+    <t xml:space="preserve">30.5262985229492</t>
   </si>
   <si>
     <t xml:space="preserve">31.2800331115723</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">30.1494293212891</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3378658294678</t>
+    <t xml:space="preserve">30.3378639221191</t>
   </si>
   <si>
     <t xml:space="preserve">29.395694732666</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">28.2650909423828</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6997871398926</t>
+    <t xml:space="preserve">27.6997890472412</t>
   </si>
   <si>
     <t xml:space="preserve">28.0766563415527</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">25.2501468658447</t>
   </si>
   <si>
-    <t xml:space="preserve">24.307975769043</t>
+    <t xml:space="preserve">24.3079776763916</t>
   </si>
   <si>
     <t xml:space="preserve">23.9311103820801</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">23.7426776885986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1773738861084</t>
+    <t xml:space="preserve">23.177375793457</t>
   </si>
   <si>
     <t xml:space="preserve">22.6120719909668</t>
@@ -1370,10 +1370,10 @@
     <t xml:space="preserve">22.2352046966553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0467720031738</t>
+    <t xml:space="preserve">22.0467700958252</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8005065917969</t>
+    <t xml:space="preserve">22.8005084991455</t>
   </si>
   <si>
     <t xml:space="preserve">22.988941192627</t>
@@ -1388,19 +1388,19 @@
     <t xml:space="preserve">25.6270160675049</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3807525634766</t>
+    <t xml:space="preserve">26.3807506561279</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1344871520996</t>
+    <t xml:space="preserve">27.134485244751</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9460544586182</t>
+    <t xml:space="preserve">26.9460525512695</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3229217529297</t>
+    <t xml:space="preserve">27.3229198455811</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1923179626465</t>
+    <t xml:space="preserve">26.1923160552979</t>
   </si>
   <si>
     <t xml:space="preserve">26.7576179504395</t>
@@ -18642,7 +18642,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G639" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19162,7 +19162,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G659" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -19188,7 +19188,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G660" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19292,7 +19292,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G664" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19500,7 +19500,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G672" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -19526,7 +19526,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G673" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20020,7 +20020,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G692" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20046,7 +20046,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G693" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20124,7 +20124,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G696" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20150,7 +20150,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G697" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -20280,7 +20280,7 @@
         <v>7</v>
       </c>
       <c r="G702" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -20306,7 +20306,7 @@
         <v>7</v>
       </c>
       <c r="G703" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -20332,7 +20332,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G704" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -20592,7 +20592,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G714" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -20618,7 +20618,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G715" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -20696,7 +20696,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G718" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -20748,7 +20748,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G720" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21008,7 +21008,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G730" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21034,7 +21034,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G731" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21060,7 +21060,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G732" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21086,7 +21086,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G733" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -21346,7 +21346,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G743" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -21372,7 +21372,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G744" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -21398,7 +21398,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G745" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -21424,7 +21424,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G746" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -21450,7 +21450,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G747" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -21476,7 +21476,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G748" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -21502,7 +21502,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G749" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -21528,7 +21528,7 @@
         <v>9</v>
       </c>
       <c r="G750" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -21554,7 +21554,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G751" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -21580,7 +21580,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G752" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -21606,7 +21606,7 @@
         <v>8.75</v>
       </c>
       <c r="G753" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -21632,7 +21632,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G754" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -21658,7 +21658,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G755" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -21684,7 +21684,7 @@
         <v>9</v>
       </c>
       <c r="G756" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -21710,7 +21710,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G757" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -21736,7 +21736,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G758" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -21762,7 +21762,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G759" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -21788,7 +21788,7 @@
         <v>9</v>
       </c>
       <c r="G760" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -21814,7 +21814,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G761" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -21840,7 +21840,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G762" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -21866,7 +21866,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G763" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -21892,7 +21892,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G764" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -21918,7 +21918,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G765" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -21944,7 +21944,7 @@
         <v>9</v>
       </c>
       <c r="G766" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -21970,7 +21970,7 @@
         <v>9</v>
       </c>
       <c r="G767" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -21996,7 +21996,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G768" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22022,7 +22022,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G769" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22048,7 +22048,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G770" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22074,7 +22074,7 @@
         <v>8.75</v>
       </c>
       <c r="G771" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22100,7 +22100,7 @@
         <v>8.75</v>
       </c>
       <c r="G772" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22126,7 +22126,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G773" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22152,7 +22152,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G774" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22178,7 +22178,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G775" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22204,7 +22204,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G776" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22230,7 +22230,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G777" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22256,7 +22256,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G778" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22282,7 +22282,7 @@
         <v>9</v>
       </c>
       <c r="G779" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -22308,7 +22308,7 @@
         <v>9</v>
       </c>
       <c r="G780" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -22334,7 +22334,7 @@
         <v>9</v>
       </c>
       <c r="G781" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -22360,7 +22360,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G782" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -22386,7 +22386,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G783" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -22412,7 +22412,7 @@
         <v>8.75</v>
       </c>
       <c r="G784" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -22438,7 +22438,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G785" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -22464,7 +22464,7 @@
         <v>8.75</v>
       </c>
       <c r="G786" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -22490,7 +22490,7 @@
         <v>8.75</v>
       </c>
       <c r="G787" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -22516,7 +22516,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G788" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -22542,7 +22542,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G789" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -22568,7 +22568,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G790" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -22594,7 +22594,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G791" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -22620,7 +22620,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G792" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -22646,7 +22646,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G793" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -22672,7 +22672,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G794" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -22698,7 +22698,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G795" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -22724,7 +22724,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G796" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -22750,7 +22750,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G797" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -22776,7 +22776,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G798" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -22802,7 +22802,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G799" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -22828,7 +22828,7 @@
         <v>8.75</v>
       </c>
       <c r="G800" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -22854,7 +22854,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G801" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -22880,7 +22880,7 @@
         <v>8.75</v>
       </c>
       <c r="G802" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -22906,7 +22906,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G803" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -22932,7 +22932,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G804" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -22958,7 +22958,7 @@
         <v>8.75</v>
       </c>
       <c r="G805" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -22984,7 +22984,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G806" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23010,7 +23010,7 @@
         <v>8.75</v>
       </c>
       <c r="G807" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23036,7 +23036,7 @@
         <v>8.75</v>
       </c>
       <c r="G808" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23062,7 +23062,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G809" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23088,7 +23088,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G810" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23114,7 +23114,7 @@
         <v>8.5</v>
       </c>
       <c r="G811" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23140,7 +23140,7 @@
         <v>8.5</v>
       </c>
       <c r="G812" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23166,7 +23166,7 @@
         <v>8.5</v>
       </c>
       <c r="G813" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23192,7 +23192,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G814" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23218,7 +23218,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G815" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23244,7 +23244,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G816" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23270,7 +23270,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G817" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23296,7 +23296,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G818" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -23322,7 +23322,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G819" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -23348,7 +23348,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G820" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -23374,7 +23374,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G821" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -23400,7 +23400,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G822" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -23426,7 +23426,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G823" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -23452,7 +23452,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G824" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -23478,7 +23478,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G825" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -23504,7 +23504,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G826" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -23530,7 +23530,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G827" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -23556,7 +23556,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G828" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -23582,7 +23582,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G829" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -23608,7 +23608,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G830" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -23634,7 +23634,7 @@
         <v>9</v>
       </c>
       <c r="G831" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -23660,7 +23660,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G832" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -23686,7 +23686,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G833" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -23712,7 +23712,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G834" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -23738,7 +23738,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G835" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -23764,7 +23764,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G836" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -23790,7 +23790,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G837" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -23816,7 +23816,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G838" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -23842,7 +23842,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G839" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -23868,7 +23868,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G840" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -23894,7 +23894,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G841" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -23920,7 +23920,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G842" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -23946,7 +23946,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G843" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -23972,7 +23972,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G844" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -23998,7 +23998,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G845" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24024,7 +24024,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G846" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24050,7 +24050,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G847" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24076,7 +24076,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G848" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24102,7 +24102,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G849" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24128,7 +24128,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G850" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24154,7 +24154,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G851" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24180,7 +24180,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G852" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24206,7 +24206,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G853" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24232,7 +24232,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G854" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24258,7 +24258,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G855" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24284,7 +24284,7 @@
         <v>8</v>
       </c>
       <c r="G856" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24310,7 +24310,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G857" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24336,7 +24336,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G858" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -24414,7 +24414,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G861" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24492,7 +24492,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G864" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -24934,7 +24934,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G881" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25012,7 +25012,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G884" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25038,7 +25038,7 @@
         <v>7</v>
       </c>
       <c r="G885" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25246,7 +25246,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G893" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -25974,7 +25974,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G921" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26000,7 +26000,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G922" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26026,7 +26026,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G923" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -26052,7 +26052,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G924" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26156,7 +26156,7 @@
         <v>7</v>
       </c>
       <c r="G928" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26182,7 +26182,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G929" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26208,7 +26208,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G930" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26234,7 +26234,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G931" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26260,7 +26260,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G932" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26286,7 +26286,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G933" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26312,7 +26312,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G934" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26338,7 +26338,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G935" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26416,7 +26416,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G938" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26442,7 +26442,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G939" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26702,7 +26702,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G949" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26728,7 +26728,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G950" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26754,7 +26754,7 @@
         <v>7</v>
       </c>
       <c r="G951" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -26780,7 +26780,7 @@
         <v>7</v>
       </c>
       <c r="G952" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26806,7 +26806,7 @@
         <v>7</v>
       </c>
       <c r="G953" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26832,7 +26832,7 @@
         <v>7</v>
       </c>
       <c r="G954" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26858,7 +26858,7 @@
         <v>7</v>
       </c>
       <c r="G955" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26884,7 +26884,7 @@
         <v>7</v>
       </c>
       <c r="G956" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26910,7 +26910,7 @@
         <v>7</v>
       </c>
       <c r="G957" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26936,7 +26936,7 @@
         <v>7</v>
       </c>
       <c r="G958" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26962,7 +26962,7 @@
         <v>7</v>
       </c>
       <c r="G959" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -26988,7 +26988,7 @@
         <v>7</v>
       </c>
       <c r="G960" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27014,7 +27014,7 @@
         <v>7</v>
       </c>
       <c r="G961" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27040,7 +27040,7 @@
         <v>7</v>
       </c>
       <c r="G962" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27066,7 +27066,7 @@
         <v>7</v>
       </c>
       <c r="G963" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27092,7 +27092,7 @@
         <v>7</v>
       </c>
       <c r="G964" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27118,7 +27118,7 @@
         <v>7</v>
       </c>
       <c r="G965" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27144,7 +27144,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G966" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27170,7 +27170,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G967" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27196,7 +27196,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G968" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27222,7 +27222,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G969" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -27248,7 +27248,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G970" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27274,7 +27274,7 @@
         <v>6.75</v>
       </c>
       <c r="G971" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27300,7 +27300,7 @@
         <v>6.75</v>
       </c>
       <c r="G972" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27326,7 +27326,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G973" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27352,7 +27352,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G974" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27378,7 +27378,7 @@
         <v>6.75</v>
       </c>
       <c r="G975" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27404,7 +27404,7 @@
         <v>6.75</v>
       </c>
       <c r="G976" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27430,7 +27430,7 @@
         <v>6.75</v>
       </c>
       <c r="G977" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27456,7 +27456,7 @@
         <v>6.75</v>
       </c>
       <c r="G978" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -27482,7 +27482,7 @@
         <v>6.75</v>
       </c>
       <c r="G979" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27508,7 +27508,7 @@
         <v>6.75</v>
       </c>
       <c r="G980" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27534,7 +27534,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G981" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27560,7 +27560,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G982" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -27586,7 +27586,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G983" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -27612,7 +27612,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G984" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27638,7 +27638,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G985" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -27664,7 +27664,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G986" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -27690,7 +27690,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G987" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -27716,7 +27716,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G988" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -27742,7 +27742,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G989" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -27768,7 +27768,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G990" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -27794,7 +27794,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G991" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -27820,7 +27820,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G992" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -27846,7 +27846,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G993" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -27872,7 +27872,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G994" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -27898,7 +27898,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G995" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -27924,7 +27924,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G996" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -27950,7 +27950,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G997" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -27976,7 +27976,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G998" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28002,7 +28002,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G999" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28028,7 +28028,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1000" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28054,7 +28054,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1001" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28080,7 +28080,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1002" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28106,7 +28106,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1003" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28132,7 +28132,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1004" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28158,7 +28158,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1005" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28184,7 +28184,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1006" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28210,7 +28210,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1007" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28236,7 +28236,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1008" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28262,7 +28262,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1009" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28340,7 +28340,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1012" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28366,7 +28366,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1013" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28392,7 +28392,7 @@
         <v>8</v>
       </c>
       <c r="G1014" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28548,7 +28548,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1020" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28574,7 +28574,7 @@
         <v>8.5</v>
       </c>
       <c r="G1021" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28600,7 +28600,7 @@
         <v>8.5</v>
       </c>
       <c r="G1022" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -28626,7 +28626,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1023" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -28652,7 +28652,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1024" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28678,7 +28678,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1025" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28704,7 +28704,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1026" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28730,7 +28730,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1027" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28756,7 +28756,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1028" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28782,7 +28782,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1029" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28808,7 +28808,7 @@
         <v>8.75</v>
       </c>
       <c r="G1030" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28834,7 +28834,7 @@
         <v>8.75</v>
       </c>
       <c r="G1031" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28860,7 +28860,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1032" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28886,7 +28886,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1033" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28912,7 +28912,7 @@
         <v>8.5</v>
       </c>
       <c r="G1034" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28938,7 +28938,7 @@
         <v>8.25</v>
       </c>
       <c r="G1035" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28964,7 +28964,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1036" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -28990,7 +28990,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1037" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29016,7 +29016,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1038" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29042,7 +29042,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1039" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29068,7 +29068,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1040" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29094,7 +29094,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1041" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29120,7 +29120,7 @@
         <v>8</v>
       </c>
       <c r="G1042" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29146,7 +29146,7 @@
         <v>8</v>
       </c>
       <c r="G1043" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29172,7 +29172,7 @@
         <v>8</v>
       </c>
       <c r="G1044" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29198,7 +29198,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1045" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -29224,7 +29224,7 @@
         <v>8</v>
       </c>
       <c r="G1046" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29250,7 +29250,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1047" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -29276,7 +29276,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1048" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29302,7 +29302,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1049" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29328,7 +29328,7 @@
         <v>7.75</v>
       </c>
       <c r="G1050" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29354,7 +29354,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1051" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29380,7 +29380,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1052" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29406,7 +29406,7 @@
         <v>7.75</v>
       </c>
       <c r="G1053" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29432,7 +29432,7 @@
         <v>7.75</v>
       </c>
       <c r="G1054" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29458,7 +29458,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1055" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29484,7 +29484,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1056" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29510,7 +29510,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1057" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29536,7 +29536,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1058" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29562,7 +29562,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1059" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29588,7 +29588,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1060" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29614,7 +29614,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1061" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29640,7 +29640,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1062" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29666,7 +29666,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1063" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29692,7 +29692,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1064" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29718,7 +29718,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1065" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29744,7 +29744,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1066" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29770,7 +29770,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1067" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29796,7 +29796,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1068" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29822,7 +29822,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1069" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29848,7 +29848,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1070" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29874,7 +29874,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1071" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29900,7 +29900,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1072" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -29926,7 +29926,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1073" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -29952,7 +29952,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1074" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -29978,7 +29978,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1075" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30004,7 +30004,7 @@
         <v>8</v>
       </c>
       <c r="G1076" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30030,7 +30030,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1077" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30056,7 +30056,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1078" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30082,7 +30082,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1079" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -30108,7 +30108,7 @@
         <v>8.25</v>
       </c>
       <c r="G1080" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30134,7 +30134,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1081" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30160,7 +30160,7 @@
         <v>8.5</v>
       </c>
       <c r="G1082" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30186,7 +30186,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1083" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30212,7 +30212,7 @@
         <v>8.5</v>
       </c>
       <c r="G1084" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30238,7 +30238,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1085" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30264,7 +30264,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1086" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -30290,7 +30290,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1087" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30316,7 +30316,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1088" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30342,7 +30342,7 @@
         <v>8.5</v>
       </c>
       <c r="G1089" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30368,7 +30368,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1090" t="s">
-        <v>267</v>
+        <v>218</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30394,7 +30394,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1091" t="s">
-        <v>267</v>
+        <v>218</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30420,7 +30420,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1092" t="s">
-        <v>267</v>
+        <v>218</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30446,7 +30446,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1093" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30472,7 +30472,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1094" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30498,7 +30498,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1095" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30784,7 +30784,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1106" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -60947,6 +60947,58 @@
         <v>532</v>
       </c>
       <c r="H2266" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" s="1" t="n">
+        <v>45960.3333333333</v>
+      </c>
+      <c r="B2267" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2267" t="n">
+        <v>39.7999992370605</v>
+      </c>
+      <c r="D2267" t="n">
+        <v>39.7999992370605</v>
+      </c>
+      <c r="E2267" t="n">
+        <v>39.7999992370605</v>
+      </c>
+      <c r="F2267" t="n">
+        <v>39.7999992370605</v>
+      </c>
+      <c r="G2267" t="s">
+        <v>532</v>
+      </c>
+      <c r="H2267" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" s="1" t="n">
+        <v>45961.5706597222</v>
+      </c>
+      <c r="B2268" t="n">
+        <v>250</v>
+      </c>
+      <c r="C2268" t="n">
+        <v>39.5999984741211</v>
+      </c>
+      <c r="D2268" t="n">
+        <v>39.5999984741211</v>
+      </c>
+      <c r="E2268" t="n">
+        <v>39.5999984741211</v>
+      </c>
+      <c r="F2268" t="n">
+        <v>39.5999984741211</v>
+      </c>
+      <c r="G2268" t="s">
+        <v>531</v>
+      </c>
+      <c r="H2268" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46539187431335</t>
+    <t xml:space="preserve">2.46539163589478</t>
   </si>
   <si>
     <t xml:space="preserve">FPE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42625856399536</t>
+    <t xml:space="preserve">2.42625832557678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43408536911011</t>
+    <t xml:space="preserve">2.43408513069153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41060519218445</t>
+    <t xml:space="preserve">2.41060566902161</t>
   </si>
   <si>
     <t xml:space="preserve">2.45756506919861</t>
@@ -59,13 +59,13 @@
     <t xml:space="preserve">2.39495205879211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233857154846</t>
+    <t xml:space="preserve">2.33233880996704</t>
   </si>
   <si>
     <t xml:space="preserve">2.41843175888062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3558189868927</t>
+    <t xml:space="preserve">2.35581874847412</t>
   </si>
   <si>
     <t xml:space="preserve">2.37147212028503</t>
@@ -74,25 +74,25 @@
     <t xml:space="preserve">2.50452518463135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36364555358887</t>
+    <t xml:space="preserve">2.36364531517029</t>
   </si>
   <si>
     <t xml:space="preserve">2.44973826408386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37303757667542</t>
+    <t xml:space="preserve">2.37303733825684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34955763816833</t>
+    <t xml:space="preserve">2.34955787658691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46382617950439</t>
+    <t xml:space="preserve">2.46382641792297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38712525367737</t>
+    <t xml:space="preserve">2.38712549209595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45443415641785</t>
+    <t xml:space="preserve">2.45443439483643</t>
   </si>
   <si>
     <t xml:space="preserve">2.34799218177795</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">2.48104500770569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3792986869812</t>
+    <t xml:space="preserve">2.37929892539978</t>
   </si>
   <si>
     <t xml:space="preserve">2.38556003570557</t>
@@ -119,13 +119,13 @@
     <t xml:space="preserve">3.62529969215393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31066846847534</t>
+    <t xml:space="preserve">3.3106689453125</t>
   </si>
   <si>
     <t xml:space="preserve">3.25588226318359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20266103744507</t>
+    <t xml:space="preserve">3.20266151428223</t>
   </si>
   <si>
     <t xml:space="preserve">3.0523898601532</t>
@@ -134,13 +134,13 @@
     <t xml:space="preserve">3.09152293205261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04456305503845</t>
+    <t xml:space="preserve">3.04456329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03673648834229</t>
+    <t xml:space="preserve">3.03673696517944</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03830170631409</t>
+    <t xml:space="preserve">3.03830194473267</t>
   </si>
   <si>
     <t xml:space="preserve">3.15413618087769</t>
@@ -152,16 +152,16 @@
     <t xml:space="preserve">3.30284214019775</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35762858390808</t>
+    <t xml:space="preserve">3.35762882232666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57677459716797</t>
+    <t xml:space="preserve">3.57677483558655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52198767662048</t>
+    <t xml:space="preserve">3.52198839187622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40458846092224</t>
+    <t xml:space="preserve">3.40458822250366</t>
   </si>
   <si>
     <t xml:space="preserve">3.59242820739746</t>
@@ -176,19 +176,19 @@
     <t xml:space="preserve">3.60025453567505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59555912017822</t>
+    <t xml:space="preserve">3.59555888175964</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632231712341</t>
+    <t xml:space="preserve">3.32632207870483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29501557350159</t>
+    <t xml:space="preserve">3.29501581192017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37484741210938</t>
+    <t xml:space="preserve">3.3748471736908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38267421722412</t>
+    <t xml:space="preserve">3.3826744556427</t>
   </si>
   <si>
     <t xml:space="preserve">3.44372200965881</t>
@@ -197,31 +197,31 @@
     <t xml:space="preserve">3.59086227416992</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47972416877747</t>
+    <t xml:space="preserve">3.47972440719604</t>
   </si>
   <si>
     <t xml:space="preserve">3.42650294303894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41241526603699</t>
+    <t xml:space="preserve">3.41241550445557</t>
   </si>
   <si>
     <t xml:space="preserve">3.24022889137268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21048855781555</t>
+    <t xml:space="preserve">3.21048808097839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28405857086182</t>
+    <t xml:space="preserve">3.28405833244324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16196274757385</t>
+    <t xml:space="preserve">3.16196298599243</t>
   </si>
   <si>
     <t xml:space="preserve">3.20892238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13848280906677</t>
+    <t xml:space="preserve">3.13848257064819</t>
   </si>
   <si>
     <t xml:space="preserve">3.23240256309509</t>
@@ -233,7 +233,7 @@
     <t xml:space="preserve">3.27623152732849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18857288360596</t>
+    <t xml:space="preserve">3.18857312202454</t>
   </si>
   <si>
     <t xml:space="preserve">3.14317870140076</t>
@@ -245,34 +245,34 @@
     <t xml:space="preserve">3.00073385238647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97412323951721</t>
+    <t xml:space="preserve">2.97412347793579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06021642684937</t>
+    <t xml:space="preserve">3.06021690368652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90368390083313</t>
+    <t xml:space="preserve">2.90368366241455</t>
   </si>
   <si>
     <t xml:space="preserve">2.89585733413696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82854771614075</t>
+    <t xml:space="preserve">2.82854819297791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83637475967407</t>
+    <t xml:space="preserve">2.83637452125549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90994501113892</t>
+    <t xml:space="preserve">2.90994477272034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491231918335</t>
+    <t xml:space="preserve">3.06491255760193</t>
   </si>
   <si>
     <t xml:space="preserve">3.13065624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14474439620972</t>
+    <t xml:space="preserve">3.14474415779114</t>
   </si>
   <si>
     <t xml:space="preserve">3.21361827850342</t>
@@ -290,40 +290,40 @@
     <t xml:space="preserve">3.91332006454468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34378528594971</t>
+    <t xml:space="preserve">4.34378576278687</t>
   </si>
   <si>
     <t xml:space="preserve">4.79381704330444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47864770889282</t>
+    <t xml:space="preserve">5.47864818572998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09303903579712</t>
+    <t xml:space="preserve">6.09303951263428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41603517532349</t>
+    <t xml:space="preserve">5.41603565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71344709396362</t>
+    <t xml:space="preserve">5.71344757080078</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56865501403809</t>
+    <t xml:space="preserve">5.56865453720093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41994905471802</t>
+    <t xml:space="preserve">5.41994857788086</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16558265686035</t>
+    <t xml:space="preserve">5.16558218002319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94643592834473</t>
+    <t xml:space="preserve">4.94643688201904</t>
   </si>
   <si>
     <t xml:space="preserve">4.70381116867065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67641735076904</t>
+    <t xml:space="preserve">4.67641830444336</t>
   </si>
   <si>
     <t xml:space="preserve">5.0090503692627</t>
@@ -335,31 +335,31 @@
     <t xml:space="preserve">5.30646276473999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22428321838379</t>
+    <t xml:space="preserve">5.22428274154663</t>
   </si>
   <si>
     <t xml:space="preserve">5.19688940048218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32211542129517</t>
+    <t xml:space="preserve">5.32211589813232</t>
   </si>
   <si>
     <t xml:space="preserve">5.47082138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36907482147217</t>
+    <t xml:space="preserve">5.36907529830933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2908091545105</t>
+    <t xml:space="preserve">5.29080963134766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1734094619751</t>
+    <t xml:space="preserve">5.17340993881226</t>
   </si>
   <si>
     <t xml:space="preserve">5.09514284133911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22036981582642</t>
+    <t xml:space="preserve">5.22036933898926</t>
   </si>
   <si>
     <t xml:space="preserve">5.1029691696167</t>
@@ -368,22 +368,22 @@
     <t xml:space="preserve">4.9933967590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15384292602539</t>
+    <t xml:space="preserve">5.15384244918823</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98556995391846</t>
+    <t xml:space="preserve">4.9855694770813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7585973739624</t>
+    <t xml:space="preserve">4.75859785079956</t>
   </si>
   <si>
     <t xml:space="preserve">4.77033710479736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86425828933716</t>
+    <t xml:space="preserve">4.8642578125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88773727416992</t>
+    <t xml:space="preserve">4.88773679733276</t>
   </si>
   <si>
     <t xml:space="preserve">4.83295059204102</t>
@@ -398,34 +398,34 @@
     <t xml:space="preserve">4.7233772277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.688157081604</t>
+    <t xml:space="preserve">4.68815803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78207778930664</t>
+    <t xml:space="preserve">4.78207731246948</t>
   </si>
   <si>
     <t xml:space="preserve">4.8759970664978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03644275665283</t>
+    <t xml:space="preserve">5.03644323348999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92686986923218</t>
+    <t xml:space="preserve">4.92687034606934</t>
   </si>
   <si>
     <t xml:space="preserve">4.81338453292847</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86034393310547</t>
+    <t xml:space="preserve">4.86034345626831</t>
   </si>
   <si>
     <t xml:space="preserve">5.00122308731079</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77425050735474</t>
+    <t xml:space="preserve">4.77425098419189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8212103843689</t>
+    <t xml:space="preserve">4.82121133804321</t>
   </si>
   <si>
     <t xml:space="preserve">4.69989728927612</t>
@@ -443,7 +443,7 @@
     <t xml:space="preserve">5.43951511383057</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28298187255859</t>
+    <t xml:space="preserve">5.28298234939575</t>
   </si>
   <si>
     <t xml:space="preserve">5.24384927749634</t>
@@ -452,22 +452,22 @@
     <t xml:space="preserve">5.36124801635742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40038204193115</t>
+    <t xml:space="preserve">5.40038156509399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51778078079224</t>
+    <t xml:space="preserve">5.51778125762939</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63518095016479</t>
+    <t xml:space="preserve">5.63518047332764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96991682052612</t>
+    <t xml:space="preserve">4.96991634368896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93078374862671</t>
+    <t xml:space="preserve">4.93078327178955</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85251712799072</t>
+    <t xml:space="preserve">4.85251665115356</t>
   </si>
   <si>
     <t xml:space="preserve">5.12644958496094</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">5.08731603622437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59604787826538</t>
+    <t xml:space="preserve">5.59604835510254</t>
   </si>
   <si>
     <t xml:space="preserve">5.26159763336182</t>
@@ -494,10 +494,10 @@
     <t xml:space="preserve">5.22173690795898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14201545715332</t>
+    <t xml:space="preserve">5.14201498031616</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10215520858765</t>
+    <t xml:space="preserve">5.1021556854248</t>
   </si>
   <si>
     <t xml:space="preserve">5.18187618255615</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">5.30145835876465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9028525352478</t>
+    <t xml:space="preserve">4.90285205841064</t>
   </si>
   <si>
     <t xml:space="preserve">5.50076055526733</t>
@@ -518,31 +518,31 @@
     <t xml:space="preserve">5.4608998298645</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58048152923584</t>
+    <t xml:space="preserve">5.580482006073</t>
   </si>
   <si>
     <t xml:space="preserve">5.54062128067017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62034225463867</t>
+    <t xml:space="preserve">5.62034273147583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94271230697632</t>
+    <t xml:space="preserve">4.94271183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98257303237915</t>
+    <t xml:space="preserve">4.98257350921631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8231315612793</t>
+    <t xml:space="preserve">4.82313108444214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06229496002197</t>
+    <t xml:space="preserve">5.06229448318481</t>
   </si>
   <si>
     <t xml:space="preserve">5.02243423461914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74340963363647</t>
+    <t xml:space="preserve">4.74341011047363</t>
   </si>
   <si>
     <t xml:space="preserve">4.78327035903931</t>
@@ -554,10 +554,10 @@
     <t xml:space="preserve">5.73992395401001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81964540481567</t>
+    <t xml:space="preserve">5.81964588165283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70006370544434</t>
+    <t xml:space="preserve">5.70006418228149</t>
   </si>
   <si>
     <t xml:space="preserve">5.66020345687866</t>
@@ -572,61 +572,61 @@
     <t xml:space="preserve">5.979088306427</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29797220230103</t>
+    <t xml:space="preserve">6.29797267913818</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13853073120117</t>
+    <t xml:space="preserve">6.13853025436401</t>
   </si>
   <si>
     <t xml:space="preserve">6.05880880355835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825170516968</t>
+    <t xml:space="preserve">6.21825218200684</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09867000579834</t>
+    <t xml:space="preserve">6.09866952896118</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38518476486206</t>
+    <t xml:space="preserve">6.38518524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25998449325562</t>
+    <t xml:space="preserve">6.25998497009277</t>
   </si>
   <si>
     <t xml:space="preserve">6.30171871185303</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17651891708374</t>
+    <t xml:space="preserve">6.17651844024658</t>
   </si>
   <si>
     <t xml:space="preserve">6.42691707611084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34345102310181</t>
+    <t xml:space="preserve">6.34345149993896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46865129470825</t>
+    <t xml:space="preserve">6.46865081787109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9678521156311</t>
+    <t xml:space="preserve">5.96785259246826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00958585739136</t>
+    <t xml:space="preserve">6.00958490371704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13478469848633</t>
+    <t xml:space="preserve">6.13478517532349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05131864547729</t>
+    <t xml:space="preserve">6.05131816864014</t>
   </si>
   <si>
     <t xml:space="preserve">5.92611885070801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09305143356323</t>
+    <t xml:space="preserve">6.09305191040039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825122833252</t>
+    <t xml:space="preserve">6.21825170516968</t>
   </si>
   <si>
     <t xml:space="preserve">6.51038408279419</t>
@@ -638,64 +638,64 @@
     <t xml:space="preserve">5.88438558578491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05291604995728</t>
+    <t xml:space="preserve">7.05291652679443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09624671936035</t>
+    <t xml:space="preserve">8.09624767303467</t>
   </si>
   <si>
     <t xml:space="preserve">7.804114818573</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63718032836914</t>
+    <t xml:space="preserve">7.63718128204346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55371570587158</t>
+    <t xml:space="preserve">7.55371475219727</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34504890441895</t>
+    <t xml:space="preserve">7.34504842758179</t>
   </si>
   <si>
     <t xml:space="preserve">7.17811632156372</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51198148727417</t>
+    <t xml:space="preserve">7.51198196411133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47024822235107</t>
+    <t xml:space="preserve">7.47024917602539</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30331516265869</t>
+    <t xml:space="preserve">7.30331563949585</t>
   </si>
   <si>
     <t xml:space="preserve">7.42851400375366</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26158237457275</t>
+    <t xml:space="preserve">7.2615818977356</t>
   </si>
   <si>
     <t xml:space="preserve">7.3867826461792</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96944999694824</t>
+    <t xml:space="preserve">6.9694504737854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2198486328125</t>
+    <t xml:space="preserve">7.21984910964966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544849395752</t>
+    <t xml:space="preserve">7.5954475402832</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76238107681274</t>
+    <t xml:space="preserve">7.76238059997559</t>
   </si>
   <si>
     <t xml:space="preserve">7.84584760665894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67891502380371</t>
+    <t xml:space="preserve">7.67891407012939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01118183135986</t>
+    <t xml:space="preserve">7.01118230819702</t>
   </si>
   <si>
     <t xml:space="preserve">7.09464931488037</t>
@@ -704,16 +704,16 @@
     <t xml:space="preserve">6.92771673202515</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76078462600708</t>
+    <t xml:space="preserve">6.76078414916992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80251598358154</t>
+    <t xml:space="preserve">6.8025164604187</t>
   </si>
   <si>
     <t xml:space="preserve">6.71905040740967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8442497253418</t>
+    <t xml:space="preserve">6.84425020217896</t>
   </si>
   <si>
     <t xml:space="preserve">6.59385061264038</t>
@@ -728,10 +728,10 @@
     <t xml:space="preserve">5.75918579101562</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71745300292969</t>
+    <t xml:space="preserve">5.71745204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80091905593872</t>
+    <t xml:space="preserve">5.80091857910156</t>
   </si>
   <si>
     <t xml:space="preserve">5.67571926116943</t>
@@ -740,43 +740,43 @@
     <t xml:space="preserve">5.59225273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63398599624634</t>
+    <t xml:space="preserve">5.6339864730835</t>
   </si>
   <si>
     <t xml:space="preserve">5.46705389022827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55052042007446</t>
+    <t xml:space="preserve">5.5505199432373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17492008209229</t>
+    <t xml:space="preserve">5.17492055892944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25838804244995</t>
+    <t xml:space="preserve">5.25838756561279</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38358640670776</t>
+    <t xml:space="preserve">5.38358736038208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13638353347778</t>
+    <t xml:space="preserve">7.13638305664062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4724702835083</t>
+    <t xml:space="preserve">7.47247076034546</t>
   </si>
   <si>
     <t xml:space="preserve">7.25269222259521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29664754867554</t>
+    <t xml:space="preserve">7.2966480255127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20873594284058</t>
+    <t xml:space="preserve">7.20873641967773</t>
   </si>
   <si>
     <t xml:space="preserve">7.16478061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07686996459961</t>
+    <t xml:space="preserve">7.07686948776245</t>
   </si>
   <si>
     <t xml:space="preserve">6.98895788192749</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">6.85709095001221</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72522401809692</t>
+    <t xml:space="preserve">6.72522449493408</t>
   </si>
   <si>
     <t xml:space="preserve">6.81313467025757</t>
@@ -800,58 +800,58 @@
     <t xml:space="preserve">6.76917934417725</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90104675292969</t>
+    <t xml:space="preserve">6.90104627609253</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63731241226196</t>
+    <t xml:space="preserve">6.63731288909912</t>
   </si>
   <si>
     <t xml:space="preserve">7.12082576751709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34060430526733</t>
+    <t xml:space="preserve">7.34060478210449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51642751693726</t>
+    <t xml:space="preserve">7.5164270401001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56038331985474</t>
+    <t xml:space="preserve">7.56038284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851495742798</t>
+    <t xml:space="preserve">7.42851543426514</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7362060546875</t>
+    <t xml:space="preserve">7.73620510101318</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69224882125854</t>
+    <t xml:space="preserve">7.6922492980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64829301834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78247356414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8272008895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73774719238281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69302082061768</t>
   </si>
   <si>
     <t xml:space="preserve">7.64829397201538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78247451782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82720041275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73774671554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69302129745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64829444885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60356616973877</t>
+    <t xml:space="preserve">7.60356664657593</t>
   </si>
   <si>
     <t xml:space="preserve">7.91665554046631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87192869186401</t>
+    <t xml:space="preserve">7.8719277381897</t>
   </si>
   <si>
     <t xml:space="preserve">7.96138048171997</t>
@@ -860,31 +860,31 @@
     <t xml:space="preserve">8.2297420501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76646518707275</t>
+    <t xml:space="preserve">8.76646614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58755779266357</t>
+    <t xml:space="preserve">8.58755874633789</t>
   </si>
   <si>
     <t xml:space="preserve">8.36392402648926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63228416442871</t>
+    <t xml:space="preserve">8.63228321075439</t>
   </si>
   <si>
     <t xml:space="preserve">8.54283046722412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40864944458008</t>
+    <t xml:space="preserve">8.40865039825439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27447032928467</t>
+    <t xml:space="preserve">8.27446937561035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45337772369385</t>
+    <t xml:space="preserve">8.45337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67701148986816</t>
+    <t xml:space="preserve">8.67701244354248</t>
   </si>
   <si>
     <t xml:space="preserve">8.49810409545898</t>
@@ -908,16 +908,16 @@
     <t xml:space="preserve">11.4500770568848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.734447479248</t>
+    <t xml:space="preserve">10.7344465255737</t>
   </si>
   <si>
     <t xml:space="preserve">11.0922613143921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9133548736572</t>
+    <t xml:space="preserve">10.9133539199829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1817150115967</t>
+    <t xml:space="preserve">11.181715965271</t>
   </si>
   <si>
     <t xml:space="preserve">11.3606233596802</t>
@@ -926,25 +926,25 @@
     <t xml:space="preserve">11.6289844512939</t>
   </si>
   <si>
-    <t xml:space="preserve">11.539529800415</t>
+    <t xml:space="preserve">11.5395307540894</t>
   </si>
   <si>
     <t xml:space="preserve">11.2711696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5555400848389</t>
+    <t xml:space="preserve">10.5555391311646</t>
   </si>
   <si>
     <t xml:space="preserve">10.2871780395508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0028076171875</t>
+    <t xml:space="preserve">11.0028085708618</t>
   </si>
   <si>
     <t xml:space="preserve">10.6449928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4660863876343</t>
+    <t xml:space="preserve">10.46608543396</t>
   </si>
   <si>
     <t xml:space="preserve">10.1082706451416</t>
@@ -956,22 +956,22 @@
     <t xml:space="preserve">9.75045585632324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0188159942627</t>
+    <t xml:space="preserve">10.018816947937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6129760742188</t>
+    <t xml:space="preserve">12.6129751205444</t>
   </si>
   <si>
     <t xml:space="preserve">12.9707899093628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0442352294922</t>
+    <t xml:space="preserve">14.0442342758179</t>
   </si>
   <si>
     <t xml:space="preserve">13.7758731842041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5075130462646</t>
+    <t xml:space="preserve">13.507513999939</t>
   </si>
   <si>
     <t xml:space="preserve">13.2391519546509</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">13.4180593490601</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8813362121582</t>
+    <t xml:space="preserve">12.8813352584839</t>
   </si>
   <si>
     <t xml:space="preserve">12.7918834686279</t>
@@ -992,10 +992,10 @@
     <t xml:space="preserve">12.702428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1496963500977</t>
+    <t xml:space="preserve">13.1496982574463</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3286046981812</t>
+    <t xml:space="preserve">13.3286056518555</t>
   </si>
   <si>
     <t xml:space="preserve">13.9547815322876</t>
@@ -1004,19 +1004,19 @@
     <t xml:space="preserve">13.5969667434692</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6864204406738</t>
+    <t xml:space="preserve">13.6864213943481</t>
   </si>
   <si>
     <t xml:space="preserve">13.8653268814087</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4020509719849</t>
+    <t xml:space="preserve">14.4020500183105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2965888977051</t>
+    <t xml:space="preserve">15.2965879440308</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2071323394775</t>
+    <t xml:space="preserve">15.2071332931519</t>
   </si>
   <si>
     <t xml:space="preserve">14.5809564590454</t>
@@ -1040,31 +1040,31 @@
     <t xml:space="preserve">14.1719846725464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8161668777466</t>
+    <t xml:space="preserve">14.8161659240723</t>
   </si>
   <si>
     <t xml:space="preserve">14.6321134567261</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3683223724365</t>
+    <t xml:space="preserve">15.3683233261108</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5523729324341</t>
+    <t xml:space="preserve">15.5523738861084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1045265197754</t>
+    <t xml:space="preserve">16.104528427124</t>
   </si>
   <si>
     <t xml:space="preserve">16.3806037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9204750061035</t>
+    <t xml:space="preserve">15.9204759597778</t>
   </si>
   <si>
     <t xml:space="preserve">17.2088394165039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3008632659912</t>
+    <t xml:space="preserve">17.3008651733398</t>
   </si>
   <si>
     <t xml:space="preserve">17.4849166870117</t>
@@ -1073,13 +1073,13 @@
     <t xml:space="preserve">17.5769424438477</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6689682006836</t>
+    <t xml:space="preserve">17.6689701080322</t>
   </si>
   <si>
     <t xml:space="preserve">18.4051742553711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1413822174072</t>
+    <t xml:space="preserve">19.1413803100586</t>
   </si>
   <si>
     <t xml:space="preserve">19.6935367584229</t>
@@ -1088,49 +1088,49 @@
     <t xml:space="preserve">20.0616397857666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5340557098389</t>
+    <t xml:space="preserve">21.5340538024902</t>
   </si>
   <si>
     <t xml:space="preserve">23.3745727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2702617645264</t>
+    <t xml:space="preserve">22.270263671875</t>
   </si>
   <si>
     <t xml:space="preserve">22.822416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6137943267822</t>
+    <t xml:space="preserve">20.6137962341309</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3254356384277</t>
+    <t xml:space="preserve">19.3254337310791</t>
   </si>
   <si>
     <t xml:space="preserve">21.902156829834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0862102508545</t>
+    <t xml:space="preserve">22.0862083435059</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0064678192139</t>
+    <t xml:space="preserve">23.0064697265625</t>
   </si>
   <si>
     <t xml:space="preserve">23.5586242675781</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7426738739014</t>
+    <t xml:space="preserve">23.74267578125</t>
   </si>
   <si>
     <t xml:space="preserve">23.9267272949219</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6629333496094</t>
+    <t xml:space="preserve">24.662935256958</t>
   </si>
   <si>
     <t xml:space="preserve">24.8469867706299</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2948303222656</t>
+    <t xml:space="preserve">24.2948322296143</t>
   </si>
   <si>
     <t xml:space="preserve">24.1107807159424</t>
@@ -1139,31 +1139,31 @@
     <t xml:space="preserve">23.1905212402344</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2150897979736</t>
+    <t xml:space="preserve">25.215087890625</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4543151855469</t>
+    <t xml:space="preserve">22.4543132781982</t>
   </si>
   <si>
     <t xml:space="preserve">24.4788837432861</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9512977600098</t>
+    <t xml:space="preserve">25.9512958526611</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5034523010254</t>
+    <t xml:space="preserve">26.5034503936768</t>
   </si>
   <si>
     <t xml:space="preserve">27.975866317749</t>
   </si>
   <si>
-    <t xml:space="preserve">30.920690536499</t>
+    <t xml:space="preserve">30.9206924438477</t>
   </si>
   <si>
     <t xml:space="preserve">29.0801773071289</t>
   </si>
   <si>
-    <t xml:space="preserve">30.736644744873</t>
+    <t xml:space="preserve">30.7366466522217</t>
   </si>
   <si>
     <t xml:space="preserve">30.3685398101807</t>
@@ -1172,40 +1172,40 @@
     <t xml:space="preserve">29.2642269134521</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4728527069092</t>
+    <t xml:space="preserve">31.4728507995605</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2336273193359</t>
+    <t xml:space="preserve">34.2336235046387</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7857818603516</t>
+    <t xml:space="preserve">34.7857780456543</t>
   </si>
   <si>
     <t xml:space="preserve">33.8655204772949</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4974212646484</t>
+    <t xml:space="preserve">33.4974174499512</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1844844818115</t>
+    <t xml:space="preserve">30.1844863891602</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4237098693848</t>
+    <t xml:space="preserve">27.4237117767334</t>
   </si>
   <si>
     <t xml:space="preserve">26.6875038146973</t>
   </si>
   <si>
-    <t xml:space="preserve">25.583194732666</t>
+    <t xml:space="preserve">25.5831909179688</t>
   </si>
   <si>
     <t xml:space="preserve">26.3194007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7918148040771</t>
+    <t xml:space="preserve">27.7918167114258</t>
   </si>
   <si>
-    <t xml:space="preserve">28.896125793457</t>
+    <t xml:space="preserve">28.8961238861084</t>
   </si>
   <si>
     <t xml:space="preserve">29.4482803344727</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">28.3439693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0556049346924</t>
+    <t xml:space="preserve">27.0556087493896</t>
   </si>
   <si>
     <t xml:space="preserve">26.8715553283691</t>
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">25.3991413116455</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7672462463379</t>
+    <t xml:space="preserve">25.7672443389893</t>
   </si>
   <si>
     <t xml:space="preserve">25.0310382843018</t>
@@ -1238,61 +1238,61 @@
     <t xml:space="preserve">27.6077632904053</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5525894165039</t>
+    <t xml:space="preserve">30.5525913238525</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6323337554932</t>
+    <t xml:space="preserve">29.6323318481445</t>
   </si>
   <si>
     <t xml:space="preserve">30.0004329681396</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3931121826172</t>
+    <t xml:space="preserve">32.3931083679199</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2090530395508</t>
+    <t xml:space="preserve">32.209056854248</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2887954711914</t>
+    <t xml:space="preserve">31.28879737854</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6569042205811</t>
+    <t xml:space="preserve">31.6569023132324</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0250053405762</t>
+    <t xml:space="preserve">32.0250015258789</t>
   </si>
   <si>
     <t xml:space="preserve">32.0337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5990676879883</t>
+    <t xml:space="preserve">32.5990715026855</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1643753051758</t>
+    <t xml:space="preserve">33.1643714904785</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6568984985352</t>
+    <t xml:space="preserve">31.6569004058838</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4106407165527</t>
+    <t xml:space="preserve">32.4106369018555</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7875061035156</t>
+    <t xml:space="preserve">32.7875022888184</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9759368896484</t>
+    <t xml:space="preserve">32.9759407043457</t>
   </si>
   <si>
     <t xml:space="preserve">30.9031639099121</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8453350067139</t>
+    <t xml:space="preserve">31.8453369140625</t>
   </si>
   <si>
     <t xml:space="preserve">30.714729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5263004302979</t>
+    <t xml:space="preserve">30.5262985229492</t>
   </si>
   <si>
     <t xml:space="preserve">31.2800331115723</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">30.1494293212891</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3378658294678</t>
+    <t xml:space="preserve">30.3378639221191</t>
   </si>
   <si>
     <t xml:space="preserve">29.395694732666</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">28.2650909423828</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6997871398926</t>
+    <t xml:space="preserve">27.6997890472412</t>
   </si>
   <si>
     <t xml:space="preserve">28.0766563415527</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">25.2501468658447</t>
   </si>
   <si>
-    <t xml:space="preserve">24.307975769043</t>
+    <t xml:space="preserve">24.3079776763916</t>
   </si>
   <si>
     <t xml:space="preserve">23.9311103820801</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">23.7426776885986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1773738861084</t>
+    <t xml:space="preserve">23.177375793457</t>
   </si>
   <si>
     <t xml:space="preserve">22.6120719909668</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">22.2352046966553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0467720031738</t>
+    <t xml:space="preserve">22.0467700958252</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8005065917969</t>
+    <t xml:space="preserve">22.8005084991455</t>
   </si>
   <si>
     <t xml:space="preserve">22.988941192627</t>
@@ -1394,19 +1394,19 @@
     <t xml:space="preserve">25.6270160675049</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3807525634766</t>
+    <t xml:space="preserve">26.3807506561279</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1344871520996</t>
+    <t xml:space="preserve">27.134485244751</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9460544586182</t>
+    <t xml:space="preserve">26.9460525512695</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3229217529297</t>
+    <t xml:space="preserve">27.3229198455811</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1923179626465</t>
+    <t xml:space="preserve">26.1923160552979</t>
   </si>
   <si>
     <t xml:space="preserve">26.7576179504395</t>
@@ -61140,7 +61140,7 @@
     </row>
     <row r="2274">
       <c r="A2274" s="1" t="n">
-        <v>45971.6725231481</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2274" t="n">
         <v>1750</v>
@@ -61161,6 +61161,32 @@
         <v>537</v>
       </c>
       <c r="H2274" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" s="1" t="n">
+        <v>45972.6359490741</v>
+      </c>
+      <c r="B2275" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C2275" t="n">
+        <v>39.5999984741211</v>
+      </c>
+      <c r="D2275" t="n">
+        <v>39.4000015258789</v>
+      </c>
+      <c r="E2275" t="n">
+        <v>39.4000015258789</v>
+      </c>
+      <c r="F2275" t="n">
+        <v>39.4000015258789</v>
+      </c>
+      <c r="G2275" t="s">
+        <v>547</v>
+      </c>
+      <c r="H2275" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="561">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="562">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46539163589478</t>
+    <t xml:space="preserve">2.46539187431335</t>
   </si>
   <si>
     <t xml:space="preserve">FPE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42625856399536</t>
+    <t xml:space="preserve">2.42625832557678</t>
   </si>
   <si>
     <t xml:space="preserve">2.43408513069153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41060543060303</t>
+    <t xml:space="preserve">2.41060519218445</t>
   </si>
   <si>
     <t xml:space="preserve">2.45756530761719</t>
@@ -59,28 +59,28 @@
     <t xml:space="preserve">2.39495182037354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233904838562</t>
+    <t xml:space="preserve">2.33233880996704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41843175888062</t>
+    <t xml:space="preserve">2.41843199729919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35581874847412</t>
+    <t xml:space="preserve">2.35581851005554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37147188186646</t>
+    <t xml:space="preserve">2.37147212028503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50452518463135</t>
+    <t xml:space="preserve">2.50452494621277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36364555358887</t>
+    <t xml:space="preserve">2.36364531517029</t>
   </si>
   <si>
     <t xml:space="preserve">2.44973850250244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37303781509399</t>
+    <t xml:space="preserve">2.37303757667542</t>
   </si>
   <si>
     <t xml:space="preserve">2.34955763816833</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">2.46382641792297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38712525367737</t>
+    <t xml:space="preserve">2.38712549209595</t>
   </si>
   <si>
     <t xml:space="preserve">2.45443439483643</t>
@@ -101,58 +101,58 @@
     <t xml:space="preserve">2.48104524612427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3792986869812</t>
+    <t xml:space="preserve">2.37929892539978</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38555979728699</t>
+    <t xml:space="preserve">2.38556027412415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4419116973877</t>
+    <t xml:space="preserve">2.44191145896912</t>
   </si>
   <si>
     <t xml:space="preserve">2.78002285957336</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36702060699463</t>
+    <t xml:space="preserve">3.36702108383179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62529993057251</t>
+    <t xml:space="preserve">3.62530040740967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31066942214966</t>
+    <t xml:space="preserve">3.31066918373108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25588250160217</t>
+    <t xml:space="preserve">3.25588274002075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20266151428223</t>
+    <t xml:space="preserve">3.20266103744507</t>
   </si>
   <si>
     <t xml:space="preserve">3.0523898601532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09152317047119</t>
+    <t xml:space="preserve">3.09152293205261</t>
   </si>
   <si>
     <t xml:space="preserve">3.04456305503845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03673696517944</t>
+    <t xml:space="preserve">3.03673672676086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03830194473267</t>
+    <t xml:space="preserve">3.03830146789551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15413641929626</t>
+    <t xml:space="preserve">3.15413665771484</t>
   </si>
   <si>
     <t xml:space="preserve">3.30910348892212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30284214019775</t>
+    <t xml:space="preserve">3.30284190177917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3576283454895</t>
+    <t xml:space="preserve">3.35762858390808</t>
   </si>
   <si>
     <t xml:space="preserve">3.57677483558655</t>
@@ -164,37 +164,37 @@
     <t xml:space="preserve">3.40458869934082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59242844581604</t>
+    <t xml:space="preserve">3.59242820739746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58460140228271</t>
+    <t xml:space="preserve">3.58460116386414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6785204410553</t>
+    <t xml:space="preserve">3.67852091789246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60025405883789</t>
+    <t xml:space="preserve">3.60025429725647</t>
   </si>
   <si>
     <t xml:space="preserve">3.59555864334106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632207870483</t>
+    <t xml:space="preserve">3.32632184028625</t>
   </si>
   <si>
     <t xml:space="preserve">3.29501557350159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3748471736908</t>
+    <t xml:space="preserve">3.37484669685364</t>
   </si>
   <si>
     <t xml:space="preserve">3.38267397880554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44372177124023</t>
+    <t xml:space="preserve">3.44372200965881</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59086227416992</t>
+    <t xml:space="preserve">3.59086298942566</t>
   </si>
   <si>
     <t xml:space="preserve">3.47972440719604</t>
@@ -203,40 +203,40 @@
     <t xml:space="preserve">3.42650294303894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41241502761841</t>
+    <t xml:space="preserve">3.41241550445557</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24022889137268</t>
+    <t xml:space="preserve">3.2402286529541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21048808097839</t>
+    <t xml:space="preserve">3.21048784255981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28405833244324</t>
+    <t xml:space="preserve">3.28405857086182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16196274757385</t>
+    <t xml:space="preserve">3.16196250915527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20892238616943</t>
+    <t xml:space="preserve">3.20892262458801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13848328590393</t>
+    <t xml:space="preserve">3.13848304748535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23240256309509</t>
+    <t xml:space="preserve">3.23240280151367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31849527359009</t>
+    <t xml:space="preserve">3.31849551200867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27623200416565</t>
+    <t xml:space="preserve">3.27623176574707</t>
   </si>
   <si>
     <t xml:space="preserve">3.18857336044312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14317870140076</t>
+    <t xml:space="preserve">3.14317846298218</t>
   </si>
   <si>
     <t xml:space="preserve">3.11500310897827</t>
@@ -245,19 +245,19 @@
     <t xml:space="preserve">3.00073385238647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97412347793579</t>
+    <t xml:space="preserve">2.97412323951721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06021618843079</t>
+    <t xml:space="preserve">3.06021666526794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90368366241455</t>
+    <t xml:space="preserve">2.90368342399597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8958568572998</t>
+    <t xml:space="preserve">2.89585709571838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82854819297791</t>
+    <t xml:space="preserve">2.82854795455933</t>
   </si>
   <si>
     <t xml:space="preserve">2.83637452125549</t>
@@ -269,10 +269,10 @@
     <t xml:space="preserve">3.06491231918335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13065600395203</t>
+    <t xml:space="preserve">3.13065624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14474415779114</t>
+    <t xml:space="preserve">3.1447446346283</t>
   </si>
   <si>
     <t xml:space="preserve">3.213618516922</t>
@@ -287,16 +287,16 @@
     <t xml:space="preserve">3.36388969421387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91332054138184</t>
+    <t xml:space="preserve">3.91332006454468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34378576278687</t>
+    <t xml:space="preserve">4.34378528594971</t>
   </si>
   <si>
     <t xml:space="preserve">4.7938175201416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47864818572998</t>
+    <t xml:space="preserve">5.47864866256714</t>
   </si>
   <si>
     <t xml:space="preserve">6.09303951263428</t>
@@ -308,34 +308,34 @@
     <t xml:space="preserve">5.71344804763794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56865501403809</t>
+    <t xml:space="preserve">5.56865406036377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41994905471802</t>
+    <t xml:space="preserve">5.41994857788086</t>
   </si>
   <si>
     <t xml:space="preserve">5.16558265686035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94643640518188</t>
+    <t xml:space="preserve">4.94643688201904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7038106918335</t>
+    <t xml:space="preserve">4.70381116867065</t>
   </si>
   <si>
     <t xml:space="preserve">4.6764178276062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0090503692627</t>
+    <t xml:space="preserve">5.00904989242554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55691432952881</t>
+    <t xml:space="preserve">5.55691528320312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30646181106567</t>
+    <t xml:space="preserve">5.30646228790283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22428274154663</t>
+    <t xml:space="preserve">5.22428226470947</t>
   </si>
   <si>
     <t xml:space="preserve">5.19688940048218</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">5.47082138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36907577514648</t>
+    <t xml:space="preserve">5.36907482147217</t>
   </si>
   <si>
     <t xml:space="preserve">5.29080963134766</t>
@@ -362,58 +362,58 @@
     <t xml:space="preserve">5.2203688621521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10296964645386</t>
+    <t xml:space="preserve">5.10297012329102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99339628219604</t>
+    <t xml:space="preserve">4.9933967590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15384244918823</t>
+    <t xml:space="preserve">5.15384340286255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9855694770813</t>
+    <t xml:space="preserve">4.98556995391846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7585973739624</t>
+    <t xml:space="preserve">4.75859785079956</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77033758163452</t>
+    <t xml:space="preserve">4.77033805847168</t>
   </si>
   <si>
     <t xml:space="preserve">4.86425685882568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88773727416992</t>
+    <t xml:space="preserve">4.88773679733276</t>
   </si>
   <si>
     <t xml:space="preserve">4.83295059204102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75468349456787</t>
+    <t xml:space="preserve">4.75468397140503</t>
   </si>
   <si>
     <t xml:space="preserve">4.82903671264648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7233772277832</t>
+    <t xml:space="preserve">4.72337770462036</t>
   </si>
   <si>
     <t xml:space="preserve">4.688157081604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78207778930664</t>
+    <t xml:space="preserve">4.78207731246948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8759970664978</t>
+    <t xml:space="preserve">4.87599658966064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03644323348999</t>
+    <t xml:space="preserve">5.03644371032715</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92687082290649</t>
+    <t xml:space="preserve">4.92687034606934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81338405609131</t>
+    <t xml:space="preserve">4.81338310241699</t>
   </si>
   <si>
     <t xml:space="preserve">4.86034393310547</t>
@@ -422,10 +422,10 @@
     <t xml:space="preserve">5.00122308731079</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77425050735474</t>
+    <t xml:space="preserve">4.77425098419189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82121086120605</t>
+    <t xml:space="preserve">4.8212103843689</t>
   </si>
   <si>
     <t xml:space="preserve">4.69989776611328</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">4.90730381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20471668243408</t>
+    <t xml:space="preserve">5.20471525192261</t>
   </si>
   <si>
     <t xml:space="preserve">5.43951511383057</t>
@@ -446,49 +446,49 @@
     <t xml:space="preserve">5.28298234939575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384880065918</t>
+    <t xml:space="preserve">5.24384832382202</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36124897003174</t>
+    <t xml:space="preserve">5.36124849319458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40038204193115</t>
+    <t xml:space="preserve">5.40038156509399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51778221130371</t>
+    <t xml:space="preserve">5.51778173446655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63518047332764</t>
+    <t xml:space="preserve">5.63518095016479</t>
   </si>
   <si>
     <t xml:space="preserve">4.96991682052612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93078327178955</t>
+    <t xml:space="preserve">4.93078374862671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85251712799072</t>
+    <t xml:space="preserve">4.85251665115356</t>
   </si>
   <si>
     <t xml:space="preserve">5.12644958496094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04818344116211</t>
+    <t xml:space="preserve">5.04818248748779</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08731603622437</t>
+    <t xml:space="preserve">5.08731555938721</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59604740142822</t>
+    <t xml:space="preserve">5.59604787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26159763336182</t>
+    <t xml:space="preserve">5.2615966796875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42104053497314</t>
+    <t xml:space="preserve">5.42103958129883</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34131860733032</t>
+    <t xml:space="preserve">5.34131813049316</t>
   </si>
   <si>
     <t xml:space="preserve">5.22173690795898</t>
@@ -500,40 +500,40 @@
     <t xml:space="preserve">5.10215520858765</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18187618255615</t>
+    <t xml:space="preserve">5.18187522888184</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38117933273315</t>
+    <t xml:space="preserve">5.381178855896</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30145835876465</t>
+    <t xml:space="preserve">5.30145740509033</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90285205841064</t>
+    <t xml:space="preserve">4.90285158157349</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50076150894165</t>
+    <t xml:space="preserve">5.50076055526733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4608998298645</t>
+    <t xml:space="preserve">5.46090030670166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.580482006073</t>
+    <t xml:space="preserve">5.58048248291016</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54062128067017</t>
+    <t xml:space="preserve">5.54062175750732</t>
   </si>
   <si>
     <t xml:space="preserve">5.62034273147583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94271278381348</t>
+    <t xml:space="preserve">4.94271230697632</t>
   </si>
   <si>
     <t xml:space="preserve">4.98257350921631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8231315612793</t>
+    <t xml:space="preserve">4.82313060760498</t>
   </si>
   <si>
     <t xml:space="preserve">5.06229400634766</t>
@@ -542,64 +542,64 @@
     <t xml:space="preserve">5.02243375778198</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74340915679932</t>
+    <t xml:space="preserve">4.74341011047363</t>
   </si>
   <si>
     <t xml:space="preserve">4.78327035903931</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86299133300781</t>
+    <t xml:space="preserve">4.86299180984497</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73992395401001</t>
+    <t xml:space="preserve">5.73992443084717</t>
   </si>
   <si>
     <t xml:space="preserve">5.81964588165283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70006322860718</t>
+    <t xml:space="preserve">5.70006370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6602029800415</t>
+    <t xml:space="preserve">5.66020393371582</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77978467941284</t>
+    <t xml:space="preserve">5.77978515625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85950660705566</t>
+    <t xml:space="preserve">5.85950613021851</t>
   </si>
   <si>
-    <t xml:space="preserve">5.979088306427</t>
+    <t xml:space="preserve">5.97908782958984</t>
   </si>
   <si>
     <t xml:space="preserve">6.29797267913818</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13853025436401</t>
+    <t xml:space="preserve">6.13853073120117</t>
   </si>
   <si>
     <t xml:space="preserve">6.05880880355835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825170516968</t>
+    <t xml:space="preserve">6.21825122833252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0986704826355</t>
+    <t xml:space="preserve">6.09866952896118</t>
   </si>
   <si>
     <t xml:space="preserve">6.38518476486206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25998497009277</t>
+    <t xml:space="preserve">6.25998449325562</t>
   </si>
   <si>
     <t xml:space="preserve">6.30171823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17651844024658</t>
+    <t xml:space="preserve">6.17651891708374</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42691802978516</t>
+    <t xml:space="preserve">6.426917552948</t>
   </si>
   <si>
     <t xml:space="preserve">6.34345149993896</t>
@@ -608,10 +608,10 @@
     <t xml:space="preserve">6.46865081787109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96785163879395</t>
+    <t xml:space="preserve">5.9678521156311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00958490371704</t>
+    <t xml:space="preserve">6.0095853805542</t>
   </si>
   <si>
     <t xml:space="preserve">6.13478469848633</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">6.05131864547729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92611885070801</t>
+    <t xml:space="preserve">5.92611837387085</t>
   </si>
   <si>
     <t xml:space="preserve">6.09305191040039</t>
@@ -629,10 +629,10 @@
     <t xml:space="preserve">6.51038360595703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84265232086182</t>
+    <t xml:space="preserve">5.84265279769897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88438606262207</t>
+    <t xml:space="preserve">5.88438558578491</t>
   </si>
   <si>
     <t xml:space="preserve">7.05291604995728</t>
@@ -641,76 +641,76 @@
     <t xml:space="preserve">8.09624671936035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80411434173584</t>
+    <t xml:space="preserve">7.804114818573</t>
   </si>
   <si>
     <t xml:space="preserve">7.63718128204346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55371570587158</t>
+    <t xml:space="preserve">7.55371522903442</t>
   </si>
   <si>
     <t xml:space="preserve">7.34504890441895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17811632156372</t>
+    <t xml:space="preserve">7.17811584472656</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51198196411133</t>
+    <t xml:space="preserve">7.51198148727417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47024822235107</t>
+    <t xml:space="preserve">7.47024869918823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30331611633301</t>
+    <t xml:space="preserve">7.30331563949585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851400375366</t>
+    <t xml:space="preserve">7.42851591110229</t>
   </si>
   <si>
     <t xml:space="preserve">7.2615818977356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38678312301636</t>
+    <t xml:space="preserve">7.38678121566772</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9694504737854</t>
+    <t xml:space="preserve">6.96944999694824</t>
   </si>
   <si>
     <t xml:space="preserve">7.2198486328125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544801712036</t>
+    <t xml:space="preserve">7.59544849395752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76238012313843</t>
+    <t xml:space="preserve">7.76238203048706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84584760665894</t>
+    <t xml:space="preserve">7.84584617614746</t>
   </si>
   <si>
     <t xml:space="preserve">7.67891454696655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01118278503418</t>
+    <t xml:space="preserve">7.01118326187134</t>
   </si>
   <si>
     <t xml:space="preserve">7.09464883804321</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92771625518799</t>
+    <t xml:space="preserve">6.92771673202515</t>
   </si>
   <si>
     <t xml:space="preserve">6.76078414916992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8025164604187</t>
+    <t xml:space="preserve">6.80251598358154</t>
   </si>
   <si>
     <t xml:space="preserve">6.71905088424683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84424924850464</t>
+    <t xml:space="preserve">6.8442497253418</t>
   </si>
   <si>
     <t xml:space="preserve">6.59385061264038</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">6.55211734771729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75918579101562</t>
+    <t xml:space="preserve">5.75918626785278</t>
   </si>
   <si>
     <t xml:space="preserve">5.71745252609253</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">5.80091905593872</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67572021484375</t>
+    <t xml:space="preserve">5.67571973800659</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59225273132324</t>
+    <t xml:space="preserve">5.59225225448608</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6339864730835</t>
+    <t xml:space="preserve">5.63398694992065</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46705341339111</t>
+    <t xml:space="preserve">5.46705389022827</t>
   </si>
   <si>
     <t xml:space="preserve">5.5505199432373</t>
@@ -755,37 +755,37 @@
     <t xml:space="preserve">5.38358688354492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13638257980347</t>
+    <t xml:space="preserve">7.13638305664062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4724702835083</t>
+    <t xml:space="preserve">7.47247076034546</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25269269943237</t>
+    <t xml:space="preserve">7.25269222259521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2966480255127</t>
+    <t xml:space="preserve">7.29664850234985</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20873594284058</t>
+    <t xml:space="preserve">7.20873641967773</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16478061676025</t>
+    <t xml:space="preserve">7.1647801399231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07686996459961</t>
+    <t xml:space="preserve">7.07686948776245</t>
   </si>
   <si>
     <t xml:space="preserve">6.98895835876465</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03291320800781</t>
+    <t xml:space="preserve">7.03291368484497</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94500255584717</t>
+    <t xml:space="preserve">6.94500207901001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85709047317505</t>
+    <t xml:space="preserve">6.85709095001221</t>
   </si>
   <si>
     <t xml:space="preserve">6.72522401809692</t>
@@ -794,82 +794,82 @@
     <t xml:space="preserve">6.81313514709473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7691798210144</t>
+    <t xml:space="preserve">6.76917934417725</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90104675292969</t>
+    <t xml:space="preserve">6.90104627609253</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63731241226196</t>
+    <t xml:space="preserve">6.63731288909912</t>
   </si>
   <si>
     <t xml:space="preserve">7.12082576751709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34060478210449</t>
+    <t xml:space="preserve">7.34060430526733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51642656326294</t>
+    <t xml:space="preserve">7.5164270401001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56038284301758</t>
+    <t xml:space="preserve">7.56038236618042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851495742798</t>
+    <t xml:space="preserve">7.73620557785034</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73620510101318</t>
+    <t xml:space="preserve">7.6922492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69224977493286</t>
+    <t xml:space="preserve">7.64829301834106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829349517822</t>
+    <t xml:space="preserve">7.78247356414795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78247404098511</t>
+    <t xml:space="preserve">7.8272008895874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82720136642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73774719238281</t>
+    <t xml:space="preserve">7.73774671554565</t>
   </si>
   <si>
     <t xml:space="preserve">7.69302082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60356616973877</t>
+    <t xml:space="preserve">7.64829397201538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91665554046631</t>
+    <t xml:space="preserve">7.60356664657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91665458679199</t>
   </si>
   <si>
     <t xml:space="preserve">7.8719277381897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96138048171997</t>
+    <t xml:space="preserve">7.96138143539429</t>
   </si>
   <si>
     <t xml:space="preserve">8.2297420501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76646518707275</t>
+    <t xml:space="preserve">8.76646614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58755874633789</t>
+    <t xml:space="preserve">8.58755779266357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36392307281494</t>
+    <t xml:space="preserve">8.36392402648926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63228321075439</t>
+    <t xml:space="preserve">8.63228416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54283142089844</t>
+    <t xml:space="preserve">8.54283046722412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40865039825439</t>
+    <t xml:space="preserve">8.40864944458008</t>
   </si>
   <si>
     <t xml:space="preserve">8.27446937561035</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">8.45337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67701148986816</t>
+    <t xml:space="preserve">8.67701244354248</t>
   </si>
   <si>
     <t xml:space="preserve">8.49810409545898</t>
@@ -890,28 +890,28 @@
     <t xml:space="preserve">8.7217378616333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85591888427734</t>
+    <t xml:space="preserve">8.85591983795166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03482723236084</t>
+    <t xml:space="preserve">9.03482532501221</t>
   </si>
   <si>
     <t xml:space="preserve">10.3766326904297</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4500770568848</t>
+    <t xml:space="preserve">11.4500780105591</t>
   </si>
   <si>
     <t xml:space="preserve">10.734447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0922622680664</t>
+    <t xml:space="preserve">11.0922613143921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9133548736572</t>
+    <t xml:space="preserve">10.9133539199829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.181715965271</t>
+    <t xml:space="preserve">11.1817150115967</t>
   </si>
   <si>
     <t xml:space="preserve">11.3606224060059</t>
@@ -923,22 +923,22 @@
     <t xml:space="preserve">11.5395307540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2711706161499</t>
+    <t xml:space="preserve">11.2711696624756</t>
   </si>
   <si>
     <t xml:space="preserve">10.5555391311646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2871780395508</t>
+    <t xml:space="preserve">10.2871789932251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0028085708618</t>
+    <t xml:space="preserve">11.0028076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6449918746948</t>
+    <t xml:space="preserve">10.6449928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.46608543396</t>
+    <t xml:space="preserve">10.4660863876343</t>
   </si>
   <si>
     <t xml:space="preserve">10.1082715988159</t>
@@ -953,19 +953,19 @@
     <t xml:space="preserve">10.018816947937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6129760742188</t>
+    <t xml:space="preserve">12.6129751205444</t>
   </si>
   <si>
     <t xml:space="preserve">12.9707899093628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0442352294922</t>
+    <t xml:space="preserve">14.0442342758179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7758741378784</t>
+    <t xml:space="preserve">13.7758731842041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5075130462646</t>
+    <t xml:space="preserve">13.507513999939</t>
   </si>
   <si>
     <t xml:space="preserve">13.2391519546509</t>
@@ -977,10 +977,10 @@
     <t xml:space="preserve">13.4180593490601</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8813352584839</t>
+    <t xml:space="preserve">12.8813362121582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7918815612793</t>
+    <t xml:space="preserve">12.7918834686279</t>
   </si>
   <si>
     <t xml:space="preserve">12.702428817749</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">13.149697303772</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3286056518555</t>
+    <t xml:space="preserve">13.3286046981812</t>
   </si>
   <si>
     <t xml:space="preserve">13.9547805786133</t>
@@ -998,34 +998,34 @@
     <t xml:space="preserve">13.5969667434692</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6864204406738</t>
+    <t xml:space="preserve">13.6864213943481</t>
   </si>
   <si>
-    <t xml:space="preserve">13.865327835083</t>
+    <t xml:space="preserve">13.8653268814087</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4020509719849</t>
+    <t xml:space="preserve">14.4020500183105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2965869903564</t>
+    <t xml:space="preserve">15.2965879440308</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2071323394775</t>
+    <t xml:space="preserve">15.2071332931519</t>
   </si>
   <si>
     <t xml:space="preserve">14.5809564590454</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7598657608032</t>
+    <t xml:space="preserve">14.7598648071289</t>
   </si>
   <si>
     <t xml:space="preserve">14.4915046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5400886535645</t>
+    <t xml:space="preserve">14.5400876998901</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3560371398926</t>
+    <t xml:space="preserve">14.3560361862183</t>
   </si>
   <si>
     <t xml:space="preserve">14.2640104293823</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">14.8161659240723</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6321134567261</t>
+    <t xml:space="preserve">14.6321144104004</t>
   </si>
   <si>
     <t xml:space="preserve">15.3683223724365</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">16.104528427124</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3806037902832</t>
+    <t xml:space="preserve">16.3806056976318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9204769134521</t>
+    <t xml:space="preserve">15.9204750061035</t>
   </si>
   <si>
     <t xml:space="preserve">17.2088394165039</t>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve">17.4849166870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5769424438477</t>
+    <t xml:space="preserve">17.576940536499</t>
   </si>
   <si>
     <t xml:space="preserve">17.6689682006836</t>
@@ -1073,31 +1073,31 @@
     <t xml:space="preserve">18.4051742553711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1413822174072</t>
+    <t xml:space="preserve">19.1413803100586</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6935386657715</t>
+    <t xml:space="preserve">19.6935367584229</t>
   </si>
   <si>
     <t xml:space="preserve">20.0616397857666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5340538024902</t>
+    <t xml:space="preserve">21.5340557098389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3745727539062</t>
+    <t xml:space="preserve">23.3745708465576</t>
   </si>
   <si>
-    <t xml:space="preserve">22.270263671875</t>
+    <t xml:space="preserve">22.2702617645264</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8224182128906</t>
+    <t xml:space="preserve">22.822416305542</t>
   </si>
   <si>
     <t xml:space="preserve">20.6137962341309</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3254356384277</t>
+    <t xml:space="preserve">19.3254337310791</t>
   </si>
   <si>
     <t xml:space="preserve">21.902156829834</t>
@@ -1106,10 +1106,10 @@
     <t xml:space="preserve">22.0862102508545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0064697265625</t>
+    <t xml:space="preserve">23.0064678192139</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5586242675781</t>
+    <t xml:space="preserve">23.5586261749268</t>
   </si>
   <si>
     <t xml:space="preserve">23.74267578125</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">24.6629333496094</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8469867706299</t>
+    <t xml:space="preserve">24.8469886779785</t>
   </si>
   <si>
     <t xml:space="preserve">24.2948303222656</t>
@@ -1136,25 +1136,25 @@
     <t xml:space="preserve">25.2150897979736</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4543151855469</t>
+    <t xml:space="preserve">22.4543132781982</t>
   </si>
   <si>
     <t xml:space="preserve">24.4788837432861</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9512977600098</t>
+    <t xml:space="preserve">25.9512958526611</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5034503936768</t>
+    <t xml:space="preserve">26.5034523010254</t>
   </si>
   <si>
     <t xml:space="preserve">27.975866317749</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9206924438477</t>
+    <t xml:space="preserve">30.9206943511963</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0801773071289</t>
+    <t xml:space="preserve">29.0801753997803</t>
   </si>
   <si>
     <t xml:space="preserve">30.736644744873</t>
@@ -1163,31 +1163,31 @@
     <t xml:space="preserve">30.3685398101807</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2642269134521</t>
+    <t xml:space="preserve">29.2642288208008</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4728527069092</t>
+    <t xml:space="preserve">31.4728507995605</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2336235046387</t>
+    <t xml:space="preserve">34.2336273193359</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7857818603516</t>
+    <t xml:space="preserve">34.7857780456543</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8655166625977</t>
+    <t xml:space="preserve">33.8655204772949</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4974174499512</t>
+    <t xml:space="preserve">33.4974212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1844844818115</t>
+    <t xml:space="preserve">30.1844863891602</t>
   </si>
   <si>
     <t xml:space="preserve">27.4237098693848</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6875019073486</t>
+    <t xml:space="preserve">26.6875038146973</t>
   </si>
   <si>
     <t xml:space="preserve">25.5831928253174</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">26.3194007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7918148040771</t>
+    <t xml:space="preserve">27.7918167114258</t>
   </si>
   <si>
     <t xml:space="preserve">28.8961238861084</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">28.5280208587646</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7120742797852</t>
+    <t xml:space="preserve">28.7120723724365</t>
   </si>
   <si>
     <t xml:space="preserve">28.3439693450928</t>
@@ -1217,7 +1217,7 @@
     <t xml:space="preserve">27.055606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8715553283691</t>
+    <t xml:space="preserve">26.8715572357178</t>
   </si>
   <si>
     <t xml:space="preserve">25.3991413116455</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">27.6077632904053</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5525894165039</t>
+    <t xml:space="preserve">30.5525913238525</t>
   </si>
   <si>
     <t xml:space="preserve">29.6323318481445</t>
@@ -1247,10 +1247,10 @@
     <t xml:space="preserve">32.209056854248</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2887954711914</t>
+    <t xml:space="preserve">31.28879737854</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6569004058838</t>
+    <t xml:space="preserve">31.6569023132324</t>
   </si>
   <si>
     <t xml:space="preserve">32.0250015258789</t>
@@ -1263,6 +1263,9 @@
   </si>
   <si>
     <t xml:space="preserve">33.1643714904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6569004058838</t>
   </si>
   <si>
     <t xml:space="preserve">32.4106369018555</t>
@@ -30365,7 +30368,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1090" t="s">
-        <v>267</v>
+        <v>217</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30391,7 +30394,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1091" t="s">
-        <v>267</v>
+        <v>217</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30417,7 +30420,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1092" t="s">
-        <v>267</v>
+        <v>217</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30521,7 +30524,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1096" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30547,7 +30550,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1097" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30573,7 +30576,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1098" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30599,7 +30602,7 @@
         <v>8.75</v>
       </c>
       <c r="G1099" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30625,7 +30628,7 @@
         <v>8.75</v>
       </c>
       <c r="G1100" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30651,7 +30654,7 @@
         <v>8.75</v>
       </c>
       <c r="G1101" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -30677,7 +30680,7 @@
         <v>8.75</v>
       </c>
       <c r="G1102" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30703,7 +30706,7 @@
         <v>8.75</v>
       </c>
       <c r="G1103" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30729,7 +30732,7 @@
         <v>8.75</v>
       </c>
       <c r="G1104" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30755,7 +30758,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1105" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30807,7 +30810,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1107" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30833,7 +30836,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1108" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30859,7 +30862,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1109" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30885,7 +30888,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1110" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -30911,7 +30914,7 @@
         <v>8.75</v>
       </c>
       <c r="G1111" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30937,7 +30940,7 @@
         <v>8.75</v>
       </c>
       <c r="G1112" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -30963,7 +30966,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1113" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -30989,7 +30992,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1114" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31015,7 +31018,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31041,7 +31044,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1116" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31067,7 +31070,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1117" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31093,7 +31096,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1118" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31119,7 +31122,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1119" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31145,7 +31148,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1120" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31171,7 +31174,7 @@
         <v>8.75</v>
       </c>
       <c r="G1121" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31197,7 +31200,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1122" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31223,7 +31226,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1123" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31249,7 +31252,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1124" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31275,7 +31278,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1125" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31301,7 +31304,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1126" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31327,7 +31330,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1127" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31353,7 +31356,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1128" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31379,7 +31382,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1129" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31405,7 +31408,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1130" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31431,7 +31434,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1131" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31457,7 +31460,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1132" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31483,7 +31486,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1133" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31509,7 +31512,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1134" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31561,7 +31564,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1136" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31587,7 +31590,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1137" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31613,7 +31616,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1138" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31639,7 +31642,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1139" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31665,7 +31668,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1140" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31691,7 +31694,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1141" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31717,7 +31720,7 @@
         <v>8.75</v>
       </c>
       <c r="G1142" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31847,7 +31850,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1147" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31899,7 +31902,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1149" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32029,7 +32032,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1154" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32055,7 +32058,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1155" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32081,7 +32084,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1156" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -44665,7 +44668,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1640" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44717,7 +44720,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1642" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44743,7 +44746,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1643" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44925,7 +44928,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1650" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44951,7 +44954,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1651" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44977,7 +44980,7 @@
         <v>35</v>
       </c>
       <c r="G1652" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45003,7 +45006,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1653" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45029,7 +45032,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1654" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45055,7 +45058,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1655" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45081,7 +45084,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1656" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45107,7 +45110,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1657" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45133,7 +45136,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1658" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45159,7 +45162,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1659" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45185,7 +45188,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1660" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45211,7 +45214,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1661" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45237,7 +45240,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1662" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45263,7 +45266,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1663" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45289,7 +45292,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1664" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45315,7 +45318,7 @@
         <v>32</v>
       </c>
       <c r="G1665" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45341,7 +45344,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1666" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45367,7 +45370,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1667" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45393,7 +45396,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1668" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45419,7 +45422,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1669" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45445,7 +45448,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1670" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45471,7 +45474,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1671" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45497,7 +45500,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1672" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45523,7 +45526,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1673" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45549,7 +45552,7 @@
         <v>32</v>
       </c>
       <c r="G1674" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45575,7 +45578,7 @@
         <v>32</v>
       </c>
       <c r="G1675" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45601,7 +45604,7 @@
         <v>32</v>
       </c>
       <c r="G1676" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45627,7 +45630,7 @@
         <v>32</v>
       </c>
       <c r="G1677" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45653,7 +45656,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1678" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45679,7 +45682,7 @@
         <v>33</v>
       </c>
       <c r="G1679" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45705,7 +45708,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1680" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45731,7 +45734,7 @@
         <v>33</v>
       </c>
       <c r="G1681" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45757,7 +45760,7 @@
         <v>32</v>
       </c>
       <c r="G1682" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45783,7 +45786,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1683" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45809,7 +45812,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1684" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45835,7 +45838,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1685" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45861,7 +45864,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1686" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45887,7 +45890,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1687" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45913,7 +45916,7 @@
         <v>33</v>
       </c>
       <c r="G1688" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45939,7 +45942,7 @@
         <v>33</v>
       </c>
       <c r="G1689" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45965,7 +45968,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1690" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45991,7 +45994,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1691" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46017,7 +46020,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1692" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46121,7 +46124,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1696" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46147,7 +46150,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1697" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46173,7 +46176,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1698" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46199,7 +46202,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1699" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46225,7 +46228,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1700" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46251,7 +46254,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1701" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46277,7 +46280,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1702" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46303,7 +46306,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1703" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46329,7 +46332,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1704" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46381,7 +46384,7 @@
         <v>33</v>
       </c>
       <c r="G1706" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46407,7 +46410,7 @@
         <v>33</v>
       </c>
       <c r="G1707" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46433,7 +46436,7 @@
         <v>33</v>
       </c>
       <c r="G1708" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46459,7 +46462,7 @@
         <v>33</v>
       </c>
       <c r="G1709" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46485,7 +46488,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1710" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46511,7 +46514,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1711" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46537,7 +46540,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1712" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46563,7 +46566,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1713" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46589,7 +46592,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1714" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46615,7 +46618,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1715" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46641,7 +46644,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1716" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46667,7 +46670,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1717" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46693,7 +46696,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1718" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46719,7 +46722,7 @@
         <v>32</v>
       </c>
       <c r="G1719" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46745,7 +46748,7 @@
         <v>32</v>
       </c>
       <c r="G1720" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46771,7 +46774,7 @@
         <v>32</v>
       </c>
       <c r="G1721" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46797,7 +46800,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1722" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46823,7 +46826,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1723" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46849,7 +46852,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1724" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46875,7 +46878,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1725" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46901,7 +46904,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1726" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46927,7 +46930,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1727" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46953,7 +46956,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1728" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46979,7 +46982,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1729" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47005,7 +47008,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1730" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47031,7 +47034,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1731" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47057,7 +47060,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1732" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47083,7 +47086,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1733" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47109,7 +47112,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1734" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47135,7 +47138,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1735" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47161,7 +47164,7 @@
         <v>30</v>
       </c>
       <c r="G1736" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47187,7 +47190,7 @@
         <v>30</v>
       </c>
       <c r="G1737" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47213,7 +47216,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1738" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47239,7 +47242,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1739" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47265,7 +47268,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1740" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47291,7 +47294,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1741" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47317,7 +47320,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1742" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47343,7 +47346,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1743" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47369,7 +47372,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1744" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47395,7 +47398,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1745" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47421,7 +47424,7 @@
         <v>26</v>
       </c>
       <c r="G1746" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47447,7 +47450,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1747" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47473,7 +47476,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1748" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47499,7 +47502,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1749" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47525,7 +47528,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1750" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47551,7 +47554,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1751" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47577,7 +47580,7 @@
         <v>27</v>
       </c>
       <c r="G1752" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47603,7 +47606,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1753" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47629,7 +47632,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1754" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47655,7 +47658,7 @@
         <v>26</v>
       </c>
       <c r="G1755" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47681,7 +47684,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1756" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47707,7 +47710,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1757" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47733,7 +47736,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1758" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47759,7 +47762,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1759" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47785,7 +47788,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1760" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47811,7 +47814,7 @@
         <v>24</v>
       </c>
       <c r="G1761" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47837,7 +47840,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1762" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47863,7 +47866,7 @@
         <v>23</v>
       </c>
       <c r="G1763" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47889,7 +47892,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1764" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47915,7 +47918,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1765" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47941,7 +47944,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1766" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47967,7 +47970,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1767" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47993,7 +47996,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1768" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48019,7 +48022,7 @@
         <v>24</v>
       </c>
       <c r="G1769" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48045,7 +48048,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1770" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48071,7 +48074,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1771" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48097,7 +48100,7 @@
         <v>24</v>
       </c>
       <c r="G1772" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48123,7 +48126,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48149,7 +48152,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1774" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48175,7 +48178,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1775" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48201,7 +48204,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1776" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48227,7 +48230,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1777" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48253,7 +48256,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1778" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48279,7 +48282,7 @@
         <v>28</v>
       </c>
       <c r="G1779" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48305,7 +48308,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1780" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48331,7 +48334,7 @@
         <v>28</v>
       </c>
       <c r="G1781" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48357,7 +48360,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1782" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48383,7 +48386,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1783" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48409,7 +48412,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1784" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48435,7 +48438,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1785" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48461,7 +48464,7 @@
         <v>28</v>
       </c>
       <c r="G1786" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48487,7 +48490,7 @@
         <v>28</v>
       </c>
       <c r="G1787" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48513,7 +48516,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1788" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48539,7 +48542,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1789" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48565,7 +48568,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1790" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -48591,7 +48594,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1791" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48617,7 +48620,7 @@
         <v>28</v>
       </c>
       <c r="G1792" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48643,7 +48646,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1793" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48669,7 +48672,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1794" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -48695,7 +48698,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1795" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48721,7 +48724,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1796" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48747,7 +48750,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1797" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48773,7 +48776,7 @@
         <v>29</v>
       </c>
       <c r="G1798" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48799,7 +48802,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1799" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48825,7 +48828,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1800" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48851,7 +48854,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1801" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48877,7 +48880,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1802" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48903,7 +48906,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1803" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48929,7 +48932,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1804" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48955,7 +48958,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1805" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48981,7 +48984,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1806" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49007,7 +49010,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1807" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49033,7 +49036,7 @@
         <v>28</v>
       </c>
       <c r="G1808" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49059,7 +49062,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1809" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49085,7 +49088,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1810" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49111,7 +49114,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1811" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49137,7 +49140,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1812" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49163,7 +49166,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1813" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49189,7 +49192,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1814" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49215,7 +49218,7 @@
         <v>27</v>
       </c>
       <c r="G1815" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49241,7 +49244,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1816" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49267,7 +49270,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1817" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49293,7 +49296,7 @@
         <v>26</v>
       </c>
       <c r="G1818" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49319,7 +49322,7 @@
         <v>26</v>
       </c>
       <c r="G1819" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49345,7 +49348,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1820" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49371,7 +49374,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1821" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49397,7 +49400,7 @@
         <v>26</v>
       </c>
       <c r="G1822" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49423,7 +49426,7 @@
         <v>26</v>
       </c>
       <c r="G1823" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49449,7 +49452,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49475,7 +49478,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1825" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49501,7 +49504,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1826" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49527,7 +49530,7 @@
         <v>29</v>
       </c>
       <c r="G1827" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49553,7 +49556,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1828" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49579,7 +49582,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1829" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49605,7 +49608,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49631,7 +49634,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1831" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49657,7 +49660,7 @@
         <v>29</v>
       </c>
       <c r="G1832" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49683,7 +49686,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1833" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49709,7 +49712,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1834" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49735,7 +49738,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1835" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49761,7 +49764,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1836" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49787,7 +49790,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1837" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49813,7 +49816,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1838" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49839,7 +49842,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1839" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49865,7 +49868,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1840" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49891,7 +49894,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1841" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49917,7 +49920,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1842" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49943,7 +49946,7 @@
         <v>30</v>
       </c>
       <c r="G1843" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49969,7 +49972,7 @@
         <v>30</v>
       </c>
       <c r="G1844" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49995,7 +49998,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1845" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50021,7 +50024,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1846" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50047,7 +50050,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1847" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50073,7 +50076,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1848" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50099,7 +50102,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1849" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50125,7 +50128,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1850" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50151,7 +50154,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1851" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50177,7 +50180,7 @@
         <v>29</v>
       </c>
       <c r="G1852" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50203,7 +50206,7 @@
         <v>29</v>
       </c>
       <c r="G1853" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50229,7 +50232,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1854" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50255,7 +50258,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1855" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50281,7 +50284,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1856" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50307,7 +50310,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1857" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50333,7 +50336,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1858" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50359,7 +50362,7 @@
         <v>29</v>
       </c>
       <c r="G1859" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50385,7 +50388,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50411,7 +50414,7 @@
         <v>30</v>
       </c>
       <c r="G1861" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50437,7 +50440,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1862" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50463,7 +50466,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1863" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50489,7 +50492,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1864" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50515,7 +50518,7 @@
         <v>27</v>
       </c>
       <c r="G1865" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50541,7 +50544,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1866" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50567,7 +50570,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1867" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50593,7 +50596,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1868" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50619,7 +50622,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1869" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50645,7 +50648,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1870" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50671,7 +50674,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1871" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50697,7 +50700,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1872" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50723,7 +50726,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1873" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50749,7 +50752,7 @@
         <v>27</v>
       </c>
       <c r="G1874" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50775,7 +50778,7 @@
         <v>27</v>
       </c>
       <c r="G1875" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50801,7 +50804,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1876" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50827,7 +50830,7 @@
         <v>27</v>
       </c>
       <c r="G1877" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50853,7 +50856,7 @@
         <v>27</v>
       </c>
       <c r="G1878" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50879,7 +50882,7 @@
         <v>27</v>
       </c>
       <c r="G1879" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50905,7 +50908,7 @@
         <v>27</v>
       </c>
       <c r="G1880" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50931,7 +50934,7 @@
         <v>28</v>
       </c>
       <c r="G1881" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50957,7 +50960,7 @@
         <v>28</v>
       </c>
       <c r="G1882" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50983,7 +50986,7 @@
         <v>28</v>
       </c>
       <c r="G1883" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51009,7 +51012,7 @@
         <v>28</v>
       </c>
       <c r="G1884" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51035,7 +51038,7 @@
         <v>28</v>
       </c>
       <c r="G1885" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51061,7 +51064,7 @@
         <v>28</v>
       </c>
       <c r="G1886" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51087,7 +51090,7 @@
         <v>27</v>
       </c>
       <c r="G1887" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51113,7 +51116,7 @@
         <v>27</v>
       </c>
       <c r="G1888" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51139,7 +51142,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1889" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51165,7 +51168,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1890" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51191,7 +51194,7 @@
         <v>28</v>
       </c>
       <c r="G1891" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51217,7 +51220,7 @@
         <v>28</v>
       </c>
       <c r="G1892" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51243,7 +51246,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1893" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51269,7 +51272,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1894" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51295,7 +51298,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1895" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51321,7 +51324,7 @@
         <v>28</v>
       </c>
       <c r="G1896" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51347,7 +51350,7 @@
         <v>28</v>
       </c>
       <c r="G1897" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51373,7 +51376,7 @@
         <v>28</v>
       </c>
       <c r="G1898" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51399,7 +51402,7 @@
         <v>28</v>
       </c>
       <c r="G1899" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51425,7 +51428,7 @@
         <v>28</v>
       </c>
       <c r="G1900" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51451,7 +51454,7 @@
         <v>28</v>
       </c>
       <c r="G1901" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51477,7 +51480,7 @@
         <v>28</v>
       </c>
       <c r="G1902" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51503,7 +51506,7 @@
         <v>28</v>
       </c>
       <c r="G1903" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51529,7 +51532,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51555,7 +51558,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51581,7 +51584,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51607,7 +51610,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51633,7 +51636,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1908" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51659,7 +51662,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1909" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51685,7 +51688,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1910" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51711,7 +51714,7 @@
         <v>29</v>
       </c>
       <c r="G1911" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51737,7 +51740,7 @@
         <v>29</v>
       </c>
       <c r="G1912" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51763,7 +51766,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1913" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51789,7 +51792,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1914" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51815,7 +51818,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51841,7 +51844,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1916" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51867,7 +51870,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1917" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51893,7 +51896,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1918" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51919,7 +51922,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1919" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51945,7 +51948,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1920" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51971,7 +51974,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1921" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51997,7 +52000,7 @@
         <v>27</v>
       </c>
       <c r="G1922" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52023,7 +52026,7 @@
         <v>27</v>
       </c>
       <c r="G1923" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52049,7 +52052,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1924" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52075,7 +52078,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1925" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52101,7 +52104,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1926" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52127,7 +52130,7 @@
         <v>28</v>
       </c>
       <c r="G1927" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52153,7 +52156,7 @@
         <v>28</v>
       </c>
       <c r="G1928" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52179,7 +52182,7 @@
         <v>28</v>
       </c>
       <c r="G1929" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52205,7 +52208,7 @@
         <v>28</v>
       </c>
       <c r="G1930" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52231,7 +52234,7 @@
         <v>28</v>
       </c>
       <c r="G1931" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52257,7 +52260,7 @@
         <v>28</v>
       </c>
       <c r="G1932" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52283,7 +52286,7 @@
         <v>28</v>
       </c>
       <c r="G1933" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52309,7 +52312,7 @@
         <v>28</v>
       </c>
       <c r="G1934" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52335,7 +52338,7 @@
         <v>28</v>
       </c>
       <c r="G1935" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52361,7 +52364,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1936" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52387,7 +52390,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1937" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52413,7 +52416,7 @@
         <v>28</v>
       </c>
       <c r="G1938" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52439,7 +52442,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1939" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52465,7 +52468,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1940" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52491,7 +52494,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1941" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52517,7 +52520,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1942" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52543,7 +52546,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1943" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52569,7 +52572,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1944" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52595,7 +52598,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1945" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52621,7 +52624,7 @@
         <v>28</v>
       </c>
       <c r="G1946" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52647,7 +52650,7 @@
         <v>28</v>
       </c>
       <c r="G1947" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52673,7 +52676,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1948" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52699,7 +52702,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1949" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52725,7 +52728,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1950" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52751,7 +52754,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1951" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52777,7 +52780,7 @@
         <v>28</v>
       </c>
       <c r="G1952" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52803,7 +52806,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1953" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52829,7 +52832,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1954" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52855,7 +52858,7 @@
         <v>27</v>
       </c>
       <c r="G1955" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52881,7 +52884,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1956" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52907,7 +52910,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1957" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -52933,7 +52936,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1958" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -52959,7 +52962,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1959" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -52985,7 +52988,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1960" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53011,7 +53014,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1961" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53037,7 +53040,7 @@
         <v>28</v>
       </c>
       <c r="G1962" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53063,7 +53066,7 @@
         <v>28</v>
       </c>
       <c r="G1963" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53089,7 +53092,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1964" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53115,7 +53118,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1965" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53141,7 +53144,7 @@
         <v>27</v>
       </c>
       <c r="G1966" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53167,7 +53170,7 @@
         <v>27</v>
       </c>
       <c r="G1967" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53193,7 +53196,7 @@
         <v>27</v>
       </c>
       <c r="G1968" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53219,7 +53222,7 @@
         <v>27</v>
       </c>
       <c r="G1969" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53245,7 +53248,7 @@
         <v>27</v>
       </c>
       <c r="G1970" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53271,7 +53274,7 @@
         <v>27</v>
       </c>
       <c r="G1971" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53297,7 +53300,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1972" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53323,7 +53326,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1973" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53349,7 +53352,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1974" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53375,7 +53378,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1975" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53401,7 +53404,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1976" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53427,7 +53430,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1977" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53453,7 +53456,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1978" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53479,7 +53482,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1979" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53505,7 +53508,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1980" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53531,7 +53534,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1981" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53557,7 +53560,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1982" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53583,7 +53586,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1983" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53609,7 +53612,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1984" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53635,7 +53638,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1985" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53661,7 +53664,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1986" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53687,7 +53690,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1987" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53713,7 +53716,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1988" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53739,7 +53742,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1989" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53765,7 +53768,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1990" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53791,7 +53794,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1991" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53817,7 +53820,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1992" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53843,7 +53846,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1993" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53869,7 +53872,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1994" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53895,7 +53898,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1995" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -53921,7 +53924,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1996" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -53947,7 +53950,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1997" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -53973,7 +53976,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1998" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -53999,7 +54002,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1999" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54025,7 +54028,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2000" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54051,7 +54054,7 @@
         <v>25</v>
       </c>
       <c r="G2001" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54077,7 +54080,7 @@
         <v>25</v>
       </c>
       <c r="G2002" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54103,7 +54106,7 @@
         <v>25</v>
       </c>
       <c r="G2003" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54129,7 +54132,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2004" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54155,7 +54158,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2005" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54181,7 +54184,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G2006" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54207,7 +54210,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G2007" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54233,7 +54236,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G2008" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54259,7 +54262,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G2009" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54285,7 +54288,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G2010" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54311,7 +54314,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G2011" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54337,7 +54340,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G2012" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54363,7 +54366,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G2013" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54389,7 +54392,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2014" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54415,7 +54418,7 @@
         <v>24</v>
       </c>
       <c r="G2015" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54441,7 +54444,7 @@
         <v>24</v>
       </c>
       <c r="G2016" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54467,7 +54470,7 @@
         <v>24</v>
       </c>
       <c r="G2017" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54493,7 +54496,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G2018" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54519,7 +54522,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G2019" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54545,7 +54548,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2020" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54571,7 +54574,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G2021" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54597,7 +54600,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G2022" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54623,7 +54626,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G2023" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54649,7 +54652,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G2024" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54675,7 +54678,7 @@
         <v>24</v>
       </c>
       <c r="G2025" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54701,7 +54704,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G2026" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54727,7 +54730,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2027" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54753,7 +54756,7 @@
         <v>23</v>
       </c>
       <c r="G2028" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54779,7 +54782,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2029" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54805,7 +54808,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2030" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54831,7 +54834,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2031" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54857,7 +54860,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2032" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54883,7 +54886,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2033" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54909,7 +54912,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2034" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -54935,7 +54938,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2035" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -54961,7 +54964,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2036" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -54987,7 +54990,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2037" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55013,7 +55016,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2038" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55039,7 +55042,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2039" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55065,7 +55068,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2040" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55091,7 +55094,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2041" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55117,7 +55120,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G2042" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55143,7 +55146,7 @@
         <v>22</v>
       </c>
       <c r="G2043" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55169,7 +55172,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2044" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55195,7 +55198,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G2045" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55221,7 +55224,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2046" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55247,7 +55250,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2047" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55273,7 +55276,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2048" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55299,7 +55302,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2049" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55325,7 +55328,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2050" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55351,7 +55354,7 @@
         <v>24</v>
       </c>
       <c r="G2051" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55377,7 +55380,7 @@
         <v>24</v>
       </c>
       <c r="G2052" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55403,7 +55406,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G2053" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55429,7 +55432,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G2054" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55455,7 +55458,7 @@
         <v>24</v>
       </c>
       <c r="G2055" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55481,7 +55484,7 @@
         <v>24</v>
       </c>
       <c r="G2056" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55507,7 +55510,7 @@
         <v>24</v>
       </c>
       <c r="G2057" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55533,7 +55536,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2058" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55559,7 +55562,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2059" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55585,7 +55588,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2060" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55611,7 +55614,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2061" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55637,7 +55640,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2062" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55663,7 +55666,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2063" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55689,7 +55692,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2064" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55715,7 +55718,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2065" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55741,7 +55744,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2066" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55767,7 +55770,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2067" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55793,7 +55796,7 @@
         <v>25</v>
       </c>
       <c r="G2068" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55819,7 +55822,7 @@
         <v>25</v>
       </c>
       <c r="G2069" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55845,7 +55848,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2070" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55871,7 +55874,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2071" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55897,7 +55900,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2072" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -55923,7 +55926,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G2073" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -55949,7 +55952,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G2074" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -55975,7 +55978,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2075" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56001,7 +56004,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2076" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56027,7 +56030,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2077" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56053,7 +56056,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2078" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56079,7 +56082,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2079" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56105,7 +56108,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2080" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56131,7 +56134,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2081" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56157,7 +56160,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2082" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56183,7 +56186,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2083" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56209,7 +56212,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2084" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56235,7 +56238,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2085" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56261,7 +56264,7 @@
         <v>25</v>
       </c>
       <c r="G2086" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56287,7 +56290,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2087" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56313,7 +56316,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2088" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56339,7 +56342,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2089" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56365,7 +56368,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2090" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56391,7 +56394,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2091" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56417,7 +56420,7 @@
         <v>25</v>
       </c>
       <c r="G2092" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56443,7 +56446,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2093" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56469,7 +56472,7 @@
         <v>25</v>
       </c>
       <c r="G2094" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56495,7 +56498,7 @@
         <v>25</v>
       </c>
       <c r="G2095" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56521,7 +56524,7 @@
         <v>25</v>
       </c>
       <c r="G2096" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56547,7 +56550,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2097" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56573,7 +56576,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2098" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56599,7 +56602,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2099" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56625,7 +56628,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2100" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56651,7 +56654,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G2101" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56677,7 +56680,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G2102" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56703,7 +56706,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G2103" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56729,7 +56732,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G2104" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56755,7 +56758,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G2105" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56781,7 +56784,7 @@
         <v>32</v>
       </c>
       <c r="G2106" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56807,7 +56810,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G2107" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56833,7 +56836,7 @@
         <v>32</v>
       </c>
       <c r="G2108" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56859,7 +56862,7 @@
         <v>31</v>
       </c>
       <c r="G2109" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56885,7 +56888,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G2110" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56911,7 +56914,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G2111" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -56937,7 +56940,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G2112" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -56963,7 +56966,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G2113" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -56989,7 +56992,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G2114" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57015,7 +57018,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G2115" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57041,7 +57044,7 @@
         <v>31</v>
       </c>
       <c r="G2116" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57067,7 +57070,7 @@
         <v>31</v>
       </c>
       <c r="G2117" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57093,7 +57096,7 @@
         <v>31</v>
       </c>
       <c r="G2118" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57119,7 +57122,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G2119" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57145,7 +57148,7 @@
         <v>30</v>
       </c>
       <c r="G2120" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57171,7 +57174,7 @@
         <v>30</v>
       </c>
       <c r="G2121" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57197,7 +57200,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2122" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57223,7 +57226,7 @@
         <v>29</v>
       </c>
       <c r="G2123" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57249,7 +57252,7 @@
         <v>29</v>
       </c>
       <c r="G2124" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57275,7 +57278,7 @@
         <v>29</v>
       </c>
       <c r="G2125" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57301,7 +57304,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G2126" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57327,7 +57330,7 @@
         <v>29</v>
       </c>
       <c r="G2127" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57353,7 +57356,7 @@
         <v>29</v>
       </c>
       <c r="G2128" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57379,7 +57382,7 @@
         <v>29</v>
       </c>
       <c r="G2129" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57405,7 +57408,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2130" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57431,7 +57434,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2131" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57457,7 +57460,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2132" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57483,7 +57486,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G2133" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57509,7 +57512,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G2134" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57535,7 +57538,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G2135" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57561,7 +57564,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G2136" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57587,7 +57590,7 @@
         <v>31</v>
       </c>
       <c r="G2137" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57613,7 +57616,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G2138" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57639,7 +57642,7 @@
         <v>30</v>
       </c>
       <c r="G2139" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57665,7 +57668,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G2140" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57691,7 +57694,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G2141" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57717,7 +57720,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G2142" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57743,7 +57746,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G2143" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57769,7 +57772,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G2144" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57795,7 +57798,7 @@
         <v>31</v>
       </c>
       <c r="G2145" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57821,7 +57824,7 @@
         <v>31</v>
       </c>
       <c r="G2146" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57847,7 +57850,7 @@
         <v>31</v>
       </c>
       <c r="G2147" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57873,7 +57876,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G2148" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57899,7 +57902,7 @@
         <v>32</v>
       </c>
       <c r="G2149" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -57925,7 +57928,7 @@
         <v>32</v>
       </c>
       <c r="G2150" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -57951,7 +57954,7 @@
         <v>32</v>
       </c>
       <c r="G2151" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -57977,7 +57980,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G2152" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58003,7 +58006,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G2153" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58029,7 +58032,7 @@
         <v>34</v>
       </c>
       <c r="G2154" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58055,7 +58058,7 @@
         <v>34</v>
       </c>
       <c r="G2155" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58081,7 +58084,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G2156" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -58107,7 +58110,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G2157" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -58133,7 +58136,7 @@
         <v>39</v>
       </c>
       <c r="G2158" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58159,7 +58162,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2159" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58185,7 +58188,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2160" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58211,7 +58214,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2161" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58237,7 +58240,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2162" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58263,7 +58266,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2163" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58289,7 +58292,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2164" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -58315,7 +58318,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2165" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58341,7 +58344,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2166" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58367,7 +58370,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G2167" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58393,7 +58396,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G2168" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58419,7 +58422,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2169" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58445,7 +58448,7 @@
         <v>40</v>
       </c>
       <c r="G2170" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58471,7 +58474,7 @@
         <v>40</v>
       </c>
       <c r="G2171" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58497,7 +58500,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2172" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58523,7 +58526,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2173" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58549,7 +58552,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G2174" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58575,7 +58578,7 @@
         <v>38</v>
       </c>
       <c r="G2175" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58601,7 +58604,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G2176" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58627,7 +58630,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G2177" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58653,7 +58656,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G2178" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58679,7 +58682,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G2179" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58705,7 +58708,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G2180" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58731,7 +58734,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G2181" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58757,7 +58760,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2182" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58783,7 +58786,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2183" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58809,7 +58812,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2184" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58835,7 +58838,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2185" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58861,7 +58864,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2186" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58887,7 +58890,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2187" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58913,7 +58916,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2188" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -58939,7 +58942,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2189" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -58965,7 +58968,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2190" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -58991,7 +58994,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2191" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59017,7 +59020,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2192" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59043,7 +59046,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2193" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59069,7 +59072,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2194" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59095,7 +59098,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G2195" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -59121,7 +59124,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G2196" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59147,7 +59150,7 @@
         <v>40</v>
       </c>
       <c r="G2197" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59173,7 +59176,7 @@
         <v>40</v>
       </c>
       <c r="G2198" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59199,7 +59202,7 @@
         <v>40</v>
       </c>
       <c r="G2199" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59225,7 +59228,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G2200" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59251,7 +59254,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G2201" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59277,7 +59280,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G2202" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59303,7 +59306,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G2203" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59329,7 +59332,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G2204" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59355,7 +59358,7 @@
         <v>44</v>
       </c>
       <c r="G2205" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59381,7 +59384,7 @@
         <v>44</v>
       </c>
       <c r="G2206" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59407,7 +59410,7 @@
         <v>44</v>
       </c>
       <c r="G2207" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59433,7 +59436,7 @@
         <v>44.5999984741211</v>
       </c>
       <c r="G2208" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59459,7 +59462,7 @@
         <v>44</v>
       </c>
       <c r="G2209" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59485,7 +59488,7 @@
         <v>44</v>
       </c>
       <c r="G2210" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59511,7 +59514,7 @@
         <v>44</v>
       </c>
       <c r="G2211" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59537,7 +59540,7 @@
         <v>44</v>
       </c>
       <c r="G2212" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59563,7 +59566,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2213" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59589,7 +59592,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2214" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59615,7 +59618,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2215" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59641,7 +59644,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2216" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59667,7 +59670,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2217" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59693,7 +59696,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2218" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59719,7 +59722,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G2219" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59745,7 +59748,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G2220" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59771,7 +59774,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G2221" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59797,7 +59800,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2222" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59823,7 +59826,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2223" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59849,7 +59852,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2224" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59875,7 +59878,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2225" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59901,7 +59904,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G2226" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -59927,7 +59930,7 @@
         <v>39</v>
       </c>
       <c r="G2227" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -59953,7 +59956,7 @@
         <v>39</v>
       </c>
       <c r="G2228" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -59979,7 +59982,7 @@
         <v>39</v>
       </c>
       <c r="G2229" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60005,7 +60008,7 @@
         <v>39</v>
       </c>
       <c r="G2230" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60031,7 +60034,7 @@
         <v>39</v>
       </c>
       <c r="G2231" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60057,7 +60060,7 @@
         <v>39</v>
       </c>
       <c r="G2232" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60083,7 +60086,7 @@
         <v>39</v>
       </c>
       <c r="G2233" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60109,7 +60112,7 @@
         <v>37</v>
       </c>
       <c r="G2234" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60135,7 +60138,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2235" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60161,7 +60164,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G2236" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60187,7 +60190,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2237" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60213,7 +60216,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2238" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60239,7 +60242,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G2239" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60265,7 +60268,7 @@
         <v>38</v>
       </c>
       <c r="G2240" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60291,7 +60294,7 @@
         <v>39</v>
       </c>
       <c r="G2241" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60317,7 +60320,7 @@
         <v>42</v>
       </c>
       <c r="G2242" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60343,7 +60346,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G2243" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60369,7 +60372,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G2244" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60395,7 +60398,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G2245" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60421,7 +60424,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G2246" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60447,7 +60450,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G2247" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60473,7 +60476,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G2248" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60499,7 +60502,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G2249" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60525,7 +60528,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G2250" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60551,7 +60554,7 @@
         <v>41</v>
       </c>
       <c r="G2251" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60577,7 +60580,7 @@
         <v>41</v>
       </c>
       <c r="G2252" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60603,7 +60606,7 @@
         <v>40</v>
       </c>
       <c r="G2253" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60629,7 +60632,7 @@
         <v>40</v>
       </c>
       <c r="G2254" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60655,7 +60658,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G2255" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60681,7 +60684,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2256" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60707,7 +60710,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2257" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60733,7 +60736,7 @@
         <v>38</v>
       </c>
       <c r="G2258" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60759,7 +60762,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G2259" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60785,7 +60788,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G2260" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60811,7 +60814,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2261" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60837,7 +60840,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2262" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60863,7 +60866,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G2263" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60889,7 +60892,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2264" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60915,7 +60918,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2265" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -60941,7 +60944,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2266" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -60967,7 +60970,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2267" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -60993,7 +60996,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2268" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61019,7 +61022,7 @@
         <v>40</v>
       </c>
       <c r="G2269" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61045,7 +61048,7 @@
         <v>40</v>
       </c>
       <c r="G2270" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -61071,7 +61074,7 @@
         <v>40</v>
       </c>
       <c r="G2271" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61097,7 +61100,7 @@
         <v>40</v>
       </c>
       <c r="G2272" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61123,7 +61126,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G2273" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61149,7 +61152,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2274" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61175,7 +61178,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G2275" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61201,7 +61204,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2276" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61227,7 +61230,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G2277" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61235,7 +61238,7 @@
     </row>
     <row r="2278">
       <c r="A2278" s="1" t="n">
-        <v>45975.6593055556</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2278" t="n">
         <v>500</v>
@@ -61253,7 +61256,7 @@
         <v>38</v>
       </c>
       <c r="G2278" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46539187431335</t>
+    <t xml:space="preserve">2.46539163589478</t>
   </si>
   <si>
     <t xml:space="preserve">FPE.MI</t>
@@ -47,25 +47,25 @@
     <t xml:space="preserve">2.42625832557678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43408513069153</t>
+    <t xml:space="preserve">2.43408536911011</t>
   </si>
   <si>
     <t xml:space="preserve">2.41060519218445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45756530761719</t>
+    <t xml:space="preserve">2.45756554603577</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39495182037354</t>
+    <t xml:space="preserve">2.39495205879211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233880996704</t>
+    <t xml:space="preserve">2.33233904838562</t>
   </si>
   <si>
     <t xml:space="preserve">2.41843199729919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35581851005554</t>
+    <t xml:space="preserve">2.3558189868927</t>
   </si>
   <si>
     <t xml:space="preserve">2.37147212028503</t>
@@ -77,19 +77,19 @@
     <t xml:space="preserve">2.36364531517029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44973850250244</t>
+    <t xml:space="preserve">2.44973874092102</t>
   </si>
   <si>
     <t xml:space="preserve">2.37303757667542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34955763816833</t>
+    <t xml:space="preserve">2.34955739974976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46382641792297</t>
+    <t xml:space="preserve">2.46382665634155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38712549209595</t>
+    <t xml:space="preserve">2.38712525367737</t>
   </si>
   <si>
     <t xml:space="preserve">2.45443439483643</t>
@@ -101,100 +101,100 @@
     <t xml:space="preserve">2.48104524612427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37929892539978</t>
+    <t xml:space="preserve">2.37929844856262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38556027412415</t>
+    <t xml:space="preserve">2.38556003570557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44191145896912</t>
+    <t xml:space="preserve">2.4419116973877</t>
   </si>
   <si>
     <t xml:space="preserve">2.78002285957336</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36702108383179</t>
+    <t xml:space="preserve">3.36702036857605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62530040740967</t>
+    <t xml:space="preserve">3.62530016899109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31066918373108</t>
+    <t xml:space="preserve">3.3106689453125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25588274002075</t>
+    <t xml:space="preserve">3.25588250160217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20266103744507</t>
+    <t xml:space="preserve">3.20266127586365</t>
   </si>
   <si>
     <t xml:space="preserve">3.0523898601532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09152293205261</t>
+    <t xml:space="preserve">3.09152317047119</t>
   </si>
   <si>
     <t xml:space="preserve">3.04456305503845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03673672676086</t>
+    <t xml:space="preserve">3.03673648834229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03830146789551</t>
+    <t xml:space="preserve">3.03830170631409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15413665771484</t>
+    <t xml:space="preserve">3.15413641929626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30910348892212</t>
+    <t xml:space="preserve">3.3091037273407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30284190177917</t>
+    <t xml:space="preserve">3.30284214019775</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35762858390808</t>
+    <t xml:space="preserve">3.35762810707092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57677483558655</t>
+    <t xml:space="preserve">3.57677531242371</t>
   </si>
   <si>
     <t xml:space="preserve">3.52198815345764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40458869934082</t>
+    <t xml:space="preserve">3.40458822250366</t>
   </si>
   <si>
     <t xml:space="preserve">3.59242820739746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58460116386414</t>
+    <t xml:space="preserve">3.58460092544556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67852091789246</t>
+    <t xml:space="preserve">3.67852067947388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60025429725647</t>
+    <t xml:space="preserve">3.60025453567505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59555864334106</t>
+    <t xml:space="preserve">3.59555816650391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632184028625</t>
+    <t xml:space="preserve">3.32632231712341</t>
   </si>
   <si>
     <t xml:space="preserve">3.29501557350159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37484669685364</t>
+    <t xml:space="preserve">3.37484693527222</t>
   </si>
   <si>
     <t xml:space="preserve">3.38267397880554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44372200965881</t>
+    <t xml:space="preserve">3.44372177124023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59086298942566</t>
+    <t xml:space="preserve">3.5908625125885</t>
   </si>
   <si>
     <t xml:space="preserve">3.47972440719604</t>
@@ -203,16 +203,16 @@
     <t xml:space="preserve">3.42650294303894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41241550445557</t>
+    <t xml:space="preserve">3.41241502761841</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2402286529541</t>
+    <t xml:space="preserve">3.24022936820984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21048784255981</t>
+    <t xml:space="preserve">3.21048831939697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28405857086182</t>
+    <t xml:space="preserve">3.28405833244324</t>
   </si>
   <si>
     <t xml:space="preserve">3.16196250915527</t>
@@ -224,19 +224,19 @@
     <t xml:space="preserve">3.13848304748535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23240280151367</t>
+    <t xml:space="preserve">3.23240256309509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31849551200867</t>
+    <t xml:space="preserve">3.31849527359009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27623176574707</t>
+    <t xml:space="preserve">3.27623224258423</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18857336044312</t>
+    <t xml:space="preserve">3.18857312202454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14317846298218</t>
+    <t xml:space="preserve">3.1431782245636</t>
   </si>
   <si>
     <t xml:space="preserve">3.11500310897827</t>
@@ -248,58 +248,58 @@
     <t xml:space="preserve">2.97412323951721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06021666526794</t>
+    <t xml:space="preserve">3.06021642684937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90368342399597</t>
+    <t xml:space="preserve">2.90368366241455</t>
   </si>
   <si>
     <t xml:space="preserve">2.89585709571838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82854795455933</t>
+    <t xml:space="preserve">2.82854771614075</t>
   </si>
   <si>
     <t xml:space="preserve">2.83637452125549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90994477272034</t>
+    <t xml:space="preserve">2.9099452495575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491231918335</t>
+    <t xml:space="preserve">3.06491255760193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13065624237061</t>
+    <t xml:space="preserve">3.13065648078918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1447446346283</t>
+    <t xml:space="preserve">3.14474439620972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.213618516922</t>
+    <t xml:space="preserve">3.21361875534058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28562355041504</t>
+    <t xml:space="preserve">3.28562378883362</t>
   </si>
   <si>
     <t xml:space="preserve">3.35919404029846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36388969421387</t>
+    <t xml:space="preserve">3.36388945579529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91332006454468</t>
+    <t xml:space="preserve">3.91332030296326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34378528594971</t>
+    <t xml:space="preserve">4.34378623962402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7938175201416</t>
+    <t xml:space="preserve">4.79381704330444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47864866256714</t>
+    <t xml:space="preserve">5.47864818572998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09303951263428</t>
+    <t xml:space="preserve">6.09303998947144</t>
   </si>
   <si>
     <t xml:space="preserve">5.41603517532349</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">5.71344804763794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56865406036377</t>
+    <t xml:space="preserve">5.56865453720093</t>
   </si>
   <si>
     <t xml:space="preserve">5.41994857788086</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">4.94643688201904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70381116867065</t>
+    <t xml:space="preserve">4.7038106918335</t>
   </si>
   <si>
     <t xml:space="preserve">4.6764178276062</t>
@@ -329,58 +329,58 @@
     <t xml:space="preserve">5.00904989242554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55691528320312</t>
+    <t xml:space="preserve">5.55691432952881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30646228790283</t>
+    <t xml:space="preserve">5.30646276473999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22428226470947</t>
+    <t xml:space="preserve">5.22428321838379</t>
   </si>
   <si>
     <t xml:space="preserve">5.19688940048218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32211542129517</t>
+    <t xml:space="preserve">5.32211494445801</t>
   </si>
   <si>
     <t xml:space="preserve">5.47082138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36907482147217</t>
+    <t xml:space="preserve">5.36907529830933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29080963134766</t>
+    <t xml:space="preserve">5.2908091545105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1734094619751</t>
+    <t xml:space="preserve">5.17340993881226</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09514331817627</t>
+    <t xml:space="preserve">5.09514284133911</t>
   </si>
   <si>
     <t xml:space="preserve">5.2203688621521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10297012329102</t>
+    <t xml:space="preserve">5.1029691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9933967590332</t>
+    <t xml:space="preserve">4.99339723587036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15384340286255</t>
+    <t xml:space="preserve">5.15384292602539</t>
   </si>
   <si>
     <t xml:space="preserve">4.98556995391846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75859785079956</t>
+    <t xml:space="preserve">4.75859689712524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77033805847168</t>
+    <t xml:space="preserve">4.77033758163452</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86425685882568</t>
+    <t xml:space="preserve">4.86425733566284</t>
   </si>
   <si>
     <t xml:space="preserve">4.88773679733276</t>
@@ -389,16 +389,16 @@
     <t xml:space="preserve">4.83295059204102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75468397140503</t>
+    <t xml:space="preserve">4.75468444824219</t>
   </si>
   <si>
     <t xml:space="preserve">4.82903671264648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72337770462036</t>
+    <t xml:space="preserve">4.7233772277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.688157081604</t>
+    <t xml:space="preserve">4.68815803527832</t>
   </si>
   <si>
     <t xml:space="preserve">4.78207731246948</t>
@@ -407,22 +407,22 @@
     <t xml:space="preserve">4.87599658966064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03644371032715</t>
+    <t xml:space="preserve">5.03644323348999</t>
   </si>
   <si>
     <t xml:space="preserve">4.92687034606934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81338310241699</t>
+    <t xml:space="preserve">4.81338405609131</t>
   </si>
   <si>
     <t xml:space="preserve">4.86034393310547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00122308731079</t>
+    <t xml:space="preserve">5.00122261047363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77425098419189</t>
+    <t xml:space="preserve">4.77425050735474</t>
   </si>
   <si>
     <t xml:space="preserve">4.8212103843689</t>
@@ -434,13 +434,13 @@
     <t xml:space="preserve">4.69598436355591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90730381011963</t>
+    <t xml:space="preserve">4.90730333328247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20471525192261</t>
+    <t xml:space="preserve">5.20471572875977</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43951511383057</t>
+    <t xml:space="preserve">5.43951606750488</t>
   </si>
   <si>
     <t xml:space="preserve">5.28298234939575</t>
@@ -449,13 +449,13 @@
     <t xml:space="preserve">5.24384832382202</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36124849319458</t>
+    <t xml:space="preserve">5.36124897003174</t>
   </si>
   <si>
     <t xml:space="preserve">5.40038156509399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51778173446655</t>
+    <t xml:space="preserve">5.51778125762939</t>
   </si>
   <si>
     <t xml:space="preserve">5.63518095016479</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">4.96991682052612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93078374862671</t>
+    <t xml:space="preserve">4.93078327178955</t>
   </si>
   <si>
     <t xml:space="preserve">4.85251665115356</t>
@@ -473,22 +473,22 @@
     <t xml:space="preserve">5.12644958496094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04818248748779</t>
+    <t xml:space="preserve">5.04818296432495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08731555938721</t>
+    <t xml:space="preserve">5.08731603622437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59604787826538</t>
+    <t xml:space="preserve">5.59604740142822</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2615966796875</t>
+    <t xml:space="preserve">5.26159715652466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42103958129883</t>
+    <t xml:space="preserve">5.42103910446167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34131813049316</t>
+    <t xml:space="preserve">5.34131765365601</t>
   </si>
   <si>
     <t xml:space="preserve">5.22173690795898</t>
@@ -500,31 +500,31 @@
     <t xml:space="preserve">5.10215520858765</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18187522888184</t>
+    <t xml:space="preserve">5.18187618255615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.381178855896</t>
+    <t xml:space="preserve">5.38117933273315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30145740509033</t>
+    <t xml:space="preserve">5.30145788192749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90285158157349</t>
+    <t xml:space="preserve">4.90285205841064</t>
   </si>
   <si>
     <t xml:space="preserve">5.50076055526733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46090030670166</t>
+    <t xml:space="preserve">5.46090078353882</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58048248291016</t>
+    <t xml:space="preserve">5.580482006073</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54062175750732</t>
+    <t xml:space="preserve">5.54062223434448</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62034273147583</t>
+    <t xml:space="preserve">5.62034225463867</t>
   </si>
   <si>
     <t xml:space="preserve">4.94271230697632</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">4.82313060760498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06229400634766</t>
+    <t xml:space="preserve">5.06229448318481</t>
   </si>
   <si>
     <t xml:space="preserve">5.02243375778198</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">4.78327035903931</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86299180984497</t>
+    <t xml:space="preserve">4.86299133300781</t>
   </si>
   <si>
     <t xml:space="preserve">5.73992443084717</t>
@@ -557,46 +557,46 @@
     <t xml:space="preserve">5.81964588165283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70006370544434</t>
+    <t xml:space="preserve">5.70006322860718</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66020393371582</t>
+    <t xml:space="preserve">5.6602029800415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77978515625</t>
+    <t xml:space="preserve">5.77978467941284</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85950613021851</t>
+    <t xml:space="preserve">5.85950565338135</t>
   </si>
   <si>
     <t xml:space="preserve">5.97908782958984</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29797267913818</t>
+    <t xml:space="preserve">6.29797315597534</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13853073120117</t>
+    <t xml:space="preserve">6.13852977752686</t>
   </si>
   <si>
     <t xml:space="preserve">6.05880880355835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825122833252</t>
+    <t xml:space="preserve">6.21825170516968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09866952896118</t>
+    <t xml:space="preserve">6.09867000579834</t>
   </si>
   <si>
     <t xml:space="preserve">6.38518476486206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25998449325562</t>
+    <t xml:space="preserve">6.25998497009277</t>
   </si>
   <si>
     <t xml:space="preserve">6.30171823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17651891708374</t>
+    <t xml:space="preserve">6.17651844024658</t>
   </si>
   <si>
     <t xml:space="preserve">6.426917552948</t>
@@ -605,46 +605,46 @@
     <t xml:space="preserve">6.34345149993896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46865081787109</t>
+    <t xml:space="preserve">6.46865129470825</t>
   </si>
   <si>
     <t xml:space="preserve">5.9678521156311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0095853805542</t>
+    <t xml:space="preserve">6.00958490371704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13478469848633</t>
+    <t xml:space="preserve">6.13478422164917</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05131864547729</t>
+    <t xml:space="preserve">6.05131816864014</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92611837387085</t>
+    <t xml:space="preserve">5.92611885070801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09305191040039</t>
+    <t xml:space="preserve">6.09305143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51038360595703</t>
+    <t xml:space="preserve">6.51038455963135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84265279769897</t>
+    <t xml:space="preserve">5.84265232086182</t>
   </si>
   <si>
     <t xml:space="preserve">5.88438558578491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05291604995728</t>
+    <t xml:space="preserve">7.05291652679443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09624671936035</t>
+    <t xml:space="preserve">8.09624767303467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.804114818573</t>
+    <t xml:space="preserve">7.80411434173584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63718128204346</t>
+    <t xml:space="preserve">7.63718175888062</t>
   </si>
   <si>
     <t xml:space="preserve">7.55371522903442</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">7.34504890441895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17811584472656</t>
+    <t xml:space="preserve">7.17811679840088</t>
   </si>
   <si>
     <t xml:space="preserve">7.51198148727417</t>
@@ -662,31 +662,31 @@
     <t xml:space="preserve">7.47024869918823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30331563949585</t>
+    <t xml:space="preserve">7.30331516265869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851591110229</t>
+    <t xml:space="preserve">7.42851495742798</t>
   </si>
   <si>
     <t xml:space="preserve">7.2615818977356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38678121566772</t>
+    <t xml:space="preserve">7.38678216934204</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96944999694824</t>
+    <t xml:space="preserve">6.96944952011108</t>
   </si>
   <si>
     <t xml:space="preserve">7.2198486328125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544849395752</t>
+    <t xml:space="preserve">7.59544801712036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76238203048706</t>
+    <t xml:space="preserve">7.76238107681274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84584617614746</t>
+    <t xml:space="preserve">7.84584712982178</t>
   </si>
   <si>
     <t xml:space="preserve">7.67891454696655</t>
@@ -695,10 +695,10 @@
     <t xml:space="preserve">7.01118326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09464883804321</t>
+    <t xml:space="preserve">7.09464931488037</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92771673202515</t>
+    <t xml:space="preserve">6.92771625518799</t>
   </si>
   <si>
     <t xml:space="preserve">6.76078414916992</t>
@@ -707,16 +707,16 @@
     <t xml:space="preserve">6.80251598358154</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71905088424683</t>
+    <t xml:space="preserve">6.71904993057251</t>
   </si>
   <si>
     <t xml:space="preserve">6.8442497253418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59385061264038</t>
+    <t xml:space="preserve">6.5938515663147</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67731666564941</t>
+    <t xml:space="preserve">6.67731714248657</t>
   </si>
   <si>
     <t xml:space="preserve">6.55211734771729</t>
@@ -728,19 +728,19 @@
     <t xml:space="preserve">5.71745252609253</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80091905593872</t>
+    <t xml:space="preserve">5.80091953277588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67571973800659</t>
+    <t xml:space="preserve">5.67571926116943</t>
   </si>
   <si>
     <t xml:space="preserve">5.59225225448608</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63398694992065</t>
+    <t xml:space="preserve">5.6339864730835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46705389022827</t>
+    <t xml:space="preserve">5.46705341339111</t>
   </si>
   <si>
     <t xml:space="preserve">5.5505199432373</t>
@@ -755,16 +755,16 @@
     <t xml:space="preserve">5.38358688354492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13638305664062</t>
+    <t xml:space="preserve">7.13638257980347</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47247076034546</t>
+    <t xml:space="preserve">7.4724702835083</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25269222259521</t>
+    <t xml:space="preserve">7.25269269943237</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29664850234985</t>
+    <t xml:space="preserve">7.29664754867554</t>
   </si>
   <si>
     <t xml:space="preserve">7.20873641967773</t>
@@ -776,13 +776,13 @@
     <t xml:space="preserve">7.07686948776245</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98895835876465</t>
+    <t xml:space="preserve">6.98895788192749</t>
   </si>
   <si>
     <t xml:space="preserve">7.03291368484497</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94500207901001</t>
+    <t xml:space="preserve">6.94500255584717</t>
   </si>
   <si>
     <t xml:space="preserve">6.85709095001221</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">6.72522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81313514709473</t>
+    <t xml:space="preserve">6.81313562393188</t>
   </si>
   <si>
     <t xml:space="preserve">6.76917934417725</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">6.90104627609253</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63731288909912</t>
+    <t xml:space="preserve">6.63731241226196</t>
   </si>
   <si>
     <t xml:space="preserve">7.12082576751709</t>
@@ -809,22 +809,25 @@
     <t xml:space="preserve">7.34060430526733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5164270401001</t>
+    <t xml:space="preserve">7.51642656326294</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56038236618042</t>
+    <t xml:space="preserve">7.56038284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73620557785034</t>
+    <t xml:space="preserve">7.42851591110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7362060546875</t>
   </si>
   <si>
     <t xml:space="preserve">7.6922492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829301834106</t>
+    <t xml:space="preserve">7.64829349517822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78247356414795</t>
+    <t xml:space="preserve">7.78247404098511</t>
   </si>
   <si>
     <t xml:space="preserve">7.8272008895874</t>
@@ -833,19 +836,16 @@
     <t xml:space="preserve">7.73774671554565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69302082061768</t>
+    <t xml:space="preserve">7.69302129745483</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829397201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60356664657593</t>
+    <t xml:space="preserve">7.60356616973877</t>
   </si>
   <si>
     <t xml:space="preserve">7.91665458679199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8719277381897</t>
+    <t xml:space="preserve">7.87192869186401</t>
   </si>
   <si>
     <t xml:space="preserve">7.96138143539429</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">8.2297420501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76646614074707</t>
+    <t xml:space="preserve">8.76646518707275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58755779266357</t>
+    <t xml:space="preserve">8.58755683898926</t>
   </si>
   <si>
     <t xml:space="preserve">8.36392402648926</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">8.54283046722412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40864944458008</t>
+    <t xml:space="preserve">8.40865039825439</t>
   </si>
   <si>
     <t xml:space="preserve">8.27446937561035</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">8.45337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67701244354248</t>
+    <t xml:space="preserve">8.67701148986816</t>
   </si>
   <si>
     <t xml:space="preserve">8.49810409545898</t>
@@ -890,28 +890,28 @@
     <t xml:space="preserve">8.7217378616333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85591983795166</t>
+    <t xml:space="preserve">8.85591888427734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03482532501221</t>
+    <t xml:space="preserve">9.03482627868652</t>
   </si>
   <si>
     <t xml:space="preserve">10.3766326904297</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4500780105591</t>
+    <t xml:space="preserve">11.4500770568848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.734447479248</t>
+    <t xml:space="preserve">10.7344465255737</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0922613143921</t>
+    <t xml:space="preserve">11.0922622680664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9133539199829</t>
+    <t xml:space="preserve">10.9133548736572</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1817150115967</t>
+    <t xml:space="preserve">11.181715965271</t>
   </si>
   <si>
     <t xml:space="preserve">11.3606224060059</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">11.6289844512939</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5395307540894</t>
+    <t xml:space="preserve">11.539529800415</t>
   </si>
   <si>
     <t xml:space="preserve">11.2711696624756</t>
@@ -932,16 +932,16 @@
     <t xml:space="preserve">10.2871789932251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0028076171875</t>
+    <t xml:space="preserve">11.0028085708618</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6449928283691</t>
+    <t xml:space="preserve">10.6449937820435</t>
   </si>
   <si>
     <t xml:space="preserve">10.4660863876343</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1082715988159</t>
+    <t xml:space="preserve">10.1082706451416</t>
   </si>
   <si>
     <t xml:space="preserve">10.1977243423462</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">9.75045585632324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.018816947937</t>
+    <t xml:space="preserve">10.0188159942627</t>
   </si>
   <si>
     <t xml:space="preserve">12.6129751205444</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">13.7758731842041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.507513999939</t>
+    <t xml:space="preserve">13.5075130462646</t>
   </si>
   <si>
     <t xml:space="preserve">13.2391519546509</t>
@@ -977,40 +977,40 @@
     <t xml:space="preserve">13.4180593490601</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8813362121582</t>
+    <t xml:space="preserve">12.8813371658325</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7918834686279</t>
+    <t xml:space="preserve">12.7918825149536</t>
   </si>
   <si>
     <t xml:space="preserve">12.702428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.149697303772</t>
+    <t xml:space="preserve">13.1496982574463</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3286046981812</t>
+    <t xml:space="preserve">13.3286037445068</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547805786133</t>
+    <t xml:space="preserve">13.9547815322876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5969667434692</t>
+    <t xml:space="preserve">13.5969657897949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6864213943481</t>
+    <t xml:space="preserve">13.6864204406738</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8653268814087</t>
+    <t xml:space="preserve">13.8653287887573</t>
   </si>
   <si>
     <t xml:space="preserve">14.4020500183105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2965879440308</t>
+    <t xml:space="preserve">15.2965869903564</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2071332931519</t>
+    <t xml:space="preserve">15.2071323394775</t>
   </si>
   <si>
     <t xml:space="preserve">14.5809564590454</t>
@@ -1022,16 +1022,16 @@
     <t xml:space="preserve">14.4915046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5400876998901</t>
+    <t xml:space="preserve">14.5400886535645</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3560361862183</t>
+    <t xml:space="preserve">14.3560371398926</t>
   </si>
   <si>
     <t xml:space="preserve">14.2640104293823</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1719846725464</t>
+    <t xml:space="preserve">14.1719837188721</t>
   </si>
   <si>
     <t xml:space="preserve">14.8161659240723</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">14.6321144104004</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3683223724365</t>
+    <t xml:space="preserve">15.3683214187622</t>
   </si>
   <si>
     <t xml:space="preserve">15.5523738861084</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">15.9204750061035</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2088394165039</t>
+    <t xml:space="preserve">17.2088413238525</t>
   </si>
   <si>
     <t xml:space="preserve">17.3008632659912</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">18.4051742553711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1413803100586</t>
+    <t xml:space="preserve">19.1413822174072</t>
   </si>
   <si>
     <t xml:space="preserve">19.6935367584229</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">22.2702617645264</t>
   </si>
   <si>
-    <t xml:space="preserve">22.822416305542</t>
+    <t xml:space="preserve">22.8224182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6137962341309</t>
+    <t xml:space="preserve">20.6137943267822</t>
   </si>
   <si>
     <t xml:space="preserve">19.3254337310791</t>
@@ -1106,10 +1106,10 @@
     <t xml:space="preserve">22.0862102508545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0064678192139</t>
+    <t xml:space="preserve">23.0064697265625</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5586261749268</t>
+    <t xml:space="preserve">23.5586242675781</t>
   </si>
   <si>
     <t xml:space="preserve">23.74267578125</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">24.6629333496094</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8469886779785</t>
+    <t xml:space="preserve">24.8469867706299</t>
   </si>
   <si>
     <t xml:space="preserve">24.2948303222656</t>
@@ -1151,16 +1151,16 @@
     <t xml:space="preserve">27.975866317749</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9206943511963</t>
+    <t xml:space="preserve">30.9206924438477</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0801753997803</t>
+    <t xml:space="preserve">29.0801773071289</t>
   </si>
   <si>
-    <t xml:space="preserve">30.736644744873</t>
+    <t xml:space="preserve">30.7366428375244</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3685398101807</t>
+    <t xml:space="preserve">30.3685417175293</t>
   </si>
   <si>
     <t xml:space="preserve">29.2642288208008</t>
@@ -1172,10 +1172,10 @@
     <t xml:space="preserve">34.2336273193359</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7857780456543</t>
+    <t xml:space="preserve">34.7857818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8655204772949</t>
+    <t xml:space="preserve">33.8655166625977</t>
   </si>
   <si>
     <t xml:space="preserve">33.4974212646484</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">27.7918167114258</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8961238861084</t>
+    <t xml:space="preserve">28.896125793457</t>
   </si>
   <si>
     <t xml:space="preserve">29.4482803344727</t>
@@ -1208,19 +1208,19 @@
     <t xml:space="preserve">28.5280208587646</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7120723724365</t>
+    <t xml:space="preserve">28.7120742797852</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3439693450928</t>
+    <t xml:space="preserve">28.3439674377441</t>
   </si>
   <si>
     <t xml:space="preserve">27.055606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8715572357178</t>
+    <t xml:space="preserve">26.8715553283691</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3991413116455</t>
+    <t xml:space="preserve">25.3991432189941</t>
   </si>
   <si>
     <t xml:space="preserve">25.7672443389893</t>
@@ -1241,13 +1241,13 @@
     <t xml:space="preserve">30.0004329681396</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3931083679199</t>
+    <t xml:space="preserve">32.3931121826172</t>
   </si>
   <si>
     <t xml:space="preserve">32.209056854248</t>
   </si>
   <si>
-    <t xml:space="preserve">31.28879737854</t>
+    <t xml:space="preserve">31.2887954711914</t>
   </si>
   <si>
     <t xml:space="preserve">31.6569023132324</t>
@@ -1259,34 +1259,34 @@
     <t xml:space="preserve">32.0337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5990715026855</t>
+    <t xml:space="preserve">32.5990676879883</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1643714904785</t>
+    <t xml:space="preserve">33.1643753051758</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6569004058838</t>
+    <t xml:space="preserve">31.6568984985352</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4106369018555</t>
+    <t xml:space="preserve">32.4106407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7875022888184</t>
+    <t xml:space="preserve">32.7875061035156</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9759407043457</t>
+    <t xml:space="preserve">32.9759368896484</t>
   </si>
   <si>
     <t xml:space="preserve">30.9031639099121</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8453369140625</t>
+    <t xml:space="preserve">31.8453350067139</t>
   </si>
   <si>
     <t xml:space="preserve">30.714729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5262985229492</t>
+    <t xml:space="preserve">30.5263004302979</t>
   </si>
   <si>
     <t xml:space="preserve">31.2800331115723</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">30.1494293212891</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3378639221191</t>
+    <t xml:space="preserve">30.3378658294678</t>
   </si>
   <si>
     <t xml:space="preserve">29.395694732666</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">28.2650909423828</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6997890472412</t>
+    <t xml:space="preserve">27.6997871398926</t>
   </si>
   <si>
     <t xml:space="preserve">28.0766563415527</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">25.2501468658447</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3079776763916</t>
+    <t xml:space="preserve">24.307975769043</t>
   </si>
   <si>
     <t xml:space="preserve">23.9311103820801</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">23.7426776885986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.177375793457</t>
+    <t xml:space="preserve">23.1773738861084</t>
   </si>
   <si>
     <t xml:space="preserve">22.6120719909668</t>
@@ -1370,10 +1370,10 @@
     <t xml:space="preserve">22.2352046966553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0467700958252</t>
+    <t xml:space="preserve">22.0467720031738</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8005084991455</t>
+    <t xml:space="preserve">22.8005065917969</t>
   </si>
   <si>
     <t xml:space="preserve">22.988941192627</t>
@@ -1388,19 +1388,19 @@
     <t xml:space="preserve">25.6270160675049</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3807506561279</t>
+    <t xml:space="preserve">26.3807525634766</t>
   </si>
   <si>
-    <t xml:space="preserve">27.134485244751</t>
+    <t xml:space="preserve">27.1344871520996</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9460525512695</t>
+    <t xml:space="preserve">26.9460544586182</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3229198455811</t>
+    <t xml:space="preserve">27.3229217529297</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1923160552979</t>
+    <t xml:space="preserve">26.1923179626465</t>
   </si>
   <si>
     <t xml:space="preserve">26.7576179504395</t>
@@ -30368,7 +30368,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1090" t="s">
-        <v>217</v>
+        <v>267</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30394,7 +30394,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1091" t="s">
-        <v>217</v>
+        <v>267</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30420,7 +30420,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1092" t="s">
-        <v>217</v>
+        <v>267</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30524,7 +30524,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1096" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30550,7 +30550,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1097" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30576,7 +30576,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1098" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30602,7 +30602,7 @@
         <v>8.75</v>
       </c>
       <c r="G1099" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30628,7 +30628,7 @@
         <v>8.75</v>
       </c>
       <c r="G1100" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30654,7 +30654,7 @@
         <v>8.75</v>
       </c>
       <c r="G1101" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -30680,7 +30680,7 @@
         <v>8.75</v>
       </c>
       <c r="G1102" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30706,7 +30706,7 @@
         <v>8.75</v>
       </c>
       <c r="G1103" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30732,7 +30732,7 @@
         <v>8.75</v>
       </c>
       <c r="G1104" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30758,7 +30758,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1105" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30810,7 +30810,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1107" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30836,7 +30836,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1108" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30862,7 +30862,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1109" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30888,7 +30888,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1110" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -30914,7 +30914,7 @@
         <v>8.75</v>
       </c>
       <c r="G1111" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30940,7 +30940,7 @@
         <v>8.75</v>
       </c>
       <c r="G1112" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -30966,7 +30966,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1113" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -30992,7 +30992,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1114" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31018,7 +31018,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31044,7 +31044,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1116" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31070,7 +31070,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1117" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31096,7 +31096,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1118" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31122,7 +31122,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1119" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31148,7 +31148,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1120" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31174,7 +31174,7 @@
         <v>8.75</v>
       </c>
       <c r="G1121" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31200,7 +31200,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1122" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31226,7 +31226,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1123" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31252,7 +31252,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1124" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31278,7 +31278,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1125" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31304,7 +31304,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1126" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31330,7 +31330,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1127" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31356,7 +31356,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1128" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31382,7 +31382,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1129" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31408,7 +31408,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1130" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31434,7 +31434,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1131" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31460,7 +31460,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1132" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31486,7 +31486,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1133" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31512,7 +31512,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1134" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31564,7 +31564,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1136" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31590,7 +31590,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1137" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31616,7 +31616,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1138" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31642,7 +31642,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1139" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31668,7 +31668,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1140" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31694,7 +31694,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1141" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31720,7 +31720,7 @@
         <v>8.75</v>
       </c>
       <c r="G1142" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31850,7 +31850,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1147" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31902,7 +31902,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1149" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32032,7 +32032,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1154" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32058,7 +32058,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1155" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32084,7 +32084,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1156" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -61259,6 +61259,58 @@
         <v>537</v>
       </c>
       <c r="H2278" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" s="1" t="n">
+        <v>45978.3333333333</v>
+      </c>
+      <c r="B2279" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2279" t="n">
+        <v>38</v>
+      </c>
+      <c r="D2279" t="n">
+        <v>38</v>
+      </c>
+      <c r="E2279" t="n">
+        <v>38</v>
+      </c>
+      <c r="F2279" t="n">
+        <v>38</v>
+      </c>
+      <c r="G2279" t="s">
+        <v>537</v>
+      </c>
+      <c r="H2279" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" s="1" t="n">
+        <v>45979.3876388889</v>
+      </c>
+      <c r="B2280" t="n">
+        <v>250</v>
+      </c>
+      <c r="C2280" t="n">
+        <v>38.7999992370605</v>
+      </c>
+      <c r="D2280" t="n">
+        <v>38.7999992370605</v>
+      </c>
+      <c r="E2280" t="n">
+        <v>38.7999992370605</v>
+      </c>
+      <c r="F2280" t="n">
+        <v>38.7999992370605</v>
+      </c>
+      <c r="G2280" t="s">
+        <v>533</v>
+      </c>
+      <c r="H2280" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46539163589478</t>
+    <t xml:space="preserve">2.46539187431335</t>
   </si>
   <si>
     <t xml:space="preserve">FPE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42625832557678</t>
+    <t xml:space="preserve">2.42625856399536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43408536911011</t>
+    <t xml:space="preserve">2.43408513069153</t>
   </si>
   <si>
     <t xml:space="preserve">2.41060519218445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45756554603577</t>
+    <t xml:space="preserve">2.45756506919861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39495205879211</t>
+    <t xml:space="preserve">2.39495182037354</t>
   </si>
   <si>
     <t xml:space="preserve">2.33233904838562</t>
@@ -65,31 +65,31 @@
     <t xml:space="preserve">2.41843199729919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3558189868927</t>
+    <t xml:space="preserve">2.35581851005554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37147212028503</t>
+    <t xml:space="preserve">2.37147188186646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50452494621277</t>
+    <t xml:space="preserve">2.50452518463135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36364531517029</t>
+    <t xml:space="preserve">2.36364555358887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44973874092102</t>
+    <t xml:space="preserve">2.44973850250244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37303757667542</t>
+    <t xml:space="preserve">2.37303733825684</t>
   </si>
   <si>
     <t xml:space="preserve">2.34955739974976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46382665634155</t>
+    <t xml:space="preserve">2.46382641792297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38712525367737</t>
+    <t xml:space="preserve">2.38712549209595</t>
   </si>
   <si>
     <t xml:space="preserve">2.45443439483643</t>
@@ -98,25 +98,25 @@
     <t xml:space="preserve">2.34799218177795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48104524612427</t>
+    <t xml:space="preserve">2.48104476928711</t>
   </si>
   <si>
     <t xml:space="preserve">2.37929844856262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38556003570557</t>
+    <t xml:space="preserve">2.38556027412415</t>
   </si>
   <si>
     <t xml:space="preserve">2.4419116973877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78002285957336</t>
+    <t xml:space="preserve">2.78002262115479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36702036857605</t>
+    <t xml:space="preserve">3.36702084541321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62530016899109</t>
+    <t xml:space="preserve">3.62529969215393</t>
   </si>
   <si>
     <t xml:space="preserve">3.3106689453125</t>
@@ -134,16 +134,16 @@
     <t xml:space="preserve">3.09152317047119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04456305503845</t>
+    <t xml:space="preserve">3.04456329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03673648834229</t>
+    <t xml:space="preserve">3.03673672676086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03830170631409</t>
+    <t xml:space="preserve">3.03830194473267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15413641929626</t>
+    <t xml:space="preserve">3.15413594245911</t>
   </si>
   <si>
     <t xml:space="preserve">3.3091037273407</t>
@@ -152,31 +152,31 @@
     <t xml:space="preserve">3.30284214019775</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35762810707092</t>
+    <t xml:space="preserve">3.35762858390808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57677531242371</t>
+    <t xml:space="preserve">3.57677507400513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52198815345764</t>
+    <t xml:space="preserve">3.52198767662048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40458822250366</t>
+    <t xml:space="preserve">3.40458869934082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59242820739746</t>
+    <t xml:space="preserve">3.59242844581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58460092544556</t>
+    <t xml:space="preserve">3.58460140228271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67852067947388</t>
+    <t xml:space="preserve">3.67852091789246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60025453567505</t>
+    <t xml:space="preserve">3.60025405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59555816650391</t>
+    <t xml:space="preserve">3.59555864334106</t>
   </si>
   <si>
     <t xml:space="preserve">3.32632231712341</t>
@@ -185,7 +185,7 @@
     <t xml:space="preserve">3.29501557350159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37484693527222</t>
+    <t xml:space="preserve">3.37484741210938</t>
   </si>
   <si>
     <t xml:space="preserve">3.38267397880554</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">3.44372177124023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5908625125885</t>
+    <t xml:space="preserve">3.59086227416992</t>
   </si>
   <si>
     <t xml:space="preserve">3.47972440719604</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">3.42650294303894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41241502761841</t>
+    <t xml:space="preserve">3.41241550445557</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24022936820984</t>
+    <t xml:space="preserve">3.2402286529541</t>
   </si>
   <si>
     <t xml:space="preserve">3.21048831939697</t>
@@ -218,37 +218,37 @@
     <t xml:space="preserve">3.16196250915527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20892262458801</t>
+    <t xml:space="preserve">3.20892238616943</t>
   </si>
   <si>
     <t xml:space="preserve">3.13848304748535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23240256309509</t>
+    <t xml:space="preserve">3.23240280151367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31849527359009</t>
+    <t xml:space="preserve">3.31849551200867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27623224258423</t>
+    <t xml:space="preserve">3.27623176574707</t>
   </si>
   <si>
     <t xml:space="preserve">3.18857312202454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1431782245636</t>
+    <t xml:space="preserve">3.14317870140076</t>
   </si>
   <si>
     <t xml:space="preserve">3.11500310897827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00073385238647</t>
+    <t xml:space="preserve">3.0007336139679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97412323951721</t>
+    <t xml:space="preserve">2.97412347793579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06021642684937</t>
+    <t xml:space="preserve">3.06021618843079</t>
   </si>
   <si>
     <t xml:space="preserve">2.90368366241455</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">2.89585709571838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82854771614075</t>
+    <t xml:space="preserve">2.82854795455933</t>
   </si>
   <si>
     <t xml:space="preserve">2.83637452125549</t>
@@ -266,49 +266,49 @@
     <t xml:space="preserve">2.9099452495575</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491255760193</t>
+    <t xml:space="preserve">3.06491208076477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13065648078918</t>
+    <t xml:space="preserve">3.13065624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14474439620972</t>
+    <t xml:space="preserve">3.14474415779114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21361875534058</t>
+    <t xml:space="preserve">3.21361827850342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28562378883362</t>
+    <t xml:space="preserve">3.28562331199646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35919404029846</t>
+    <t xml:space="preserve">3.35919380187988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36388945579529</t>
+    <t xml:space="preserve">3.36389017105103</t>
   </si>
   <si>
     <t xml:space="preserve">3.91332030296326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34378623962402</t>
+    <t xml:space="preserve">4.34378576278687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79381704330444</t>
+    <t xml:space="preserve">4.7938175201416</t>
   </si>
   <si>
     <t xml:space="preserve">5.47864818572998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09303998947144</t>
+    <t xml:space="preserve">6.09303903579712</t>
   </si>
   <si>
     <t xml:space="preserve">5.41603517532349</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71344804763794</t>
+    <t xml:space="preserve">5.71344757080078</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56865453720093</t>
+    <t xml:space="preserve">5.56865501403809</t>
   </si>
   <si>
     <t xml:space="preserve">5.41994857788086</t>
@@ -326,25 +326,25 @@
     <t xml:space="preserve">4.6764178276062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00904989242554</t>
+    <t xml:space="preserve">5.0090503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55691432952881</t>
+    <t xml:space="preserve">5.55691480636597</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30646276473999</t>
+    <t xml:space="preserve">5.30646228790283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22428321838379</t>
+    <t xml:space="preserve">5.22428274154663</t>
   </si>
   <si>
     <t xml:space="preserve">5.19688940048218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32211494445801</t>
+    <t xml:space="preserve">5.32211542129517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47082138061523</t>
+    <t xml:space="preserve">5.47082185745239</t>
   </si>
   <si>
     <t xml:space="preserve">5.36907529830933</t>
@@ -353,22 +353,22 @@
     <t xml:space="preserve">5.2908091545105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17340993881226</t>
+    <t xml:space="preserve">5.17340898513794</t>
   </si>
   <si>
     <t xml:space="preserve">5.09514284133911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2203688621521</t>
+    <t xml:space="preserve">5.22036933898926</t>
   </si>
   <si>
     <t xml:space="preserve">5.1029691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99339723587036</t>
+    <t xml:space="preserve">4.99339628219604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15384292602539</t>
+    <t xml:space="preserve">5.15384244918823</t>
   </si>
   <si>
     <t xml:space="preserve">4.98556995391846</t>
@@ -377,25 +377,25 @@
     <t xml:space="preserve">4.75859689712524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77033758163452</t>
+    <t xml:space="preserve">4.77033710479736</t>
   </si>
   <si>
     <t xml:space="preserve">4.86425733566284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88773679733276</t>
+    <t xml:space="preserve">4.88773727416992</t>
   </si>
   <si>
     <t xml:space="preserve">4.83295059204102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75468444824219</t>
+    <t xml:space="preserve">4.75468397140503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82903671264648</t>
+    <t xml:space="preserve">4.82903718948364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7233772277832</t>
+    <t xml:space="preserve">4.72337770462036</t>
   </si>
   <si>
     <t xml:space="preserve">4.68815803527832</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">4.78207731246948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87599658966064</t>
+    <t xml:space="preserve">4.8759970664978</t>
   </si>
   <si>
     <t xml:space="preserve">5.03644323348999</t>
@@ -416,13 +416,13 @@
     <t xml:space="preserve">4.81338405609131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86034393310547</t>
+    <t xml:space="preserve">4.86034440994263</t>
   </si>
   <si>
     <t xml:space="preserve">5.00122261047363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77425050735474</t>
+    <t xml:space="preserve">4.77425098419189</t>
   </si>
   <si>
     <t xml:space="preserve">4.8212103843689</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">4.90730333328247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20471572875977</t>
+    <t xml:space="preserve">5.20471620559692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43951606750488</t>
+    <t xml:space="preserve">5.43951511383057</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28298234939575</t>
+    <t xml:space="preserve">5.28298187255859</t>
   </si>
   <si>
     <t xml:space="preserve">5.24384832382202</t>
@@ -452,22 +452,22 @@
     <t xml:space="preserve">5.36124897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40038156509399</t>
+    <t xml:space="preserve">5.40038251876831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51778125762939</t>
+    <t xml:space="preserve">5.51778221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63518095016479</t>
+    <t xml:space="preserve">5.63518047332764</t>
   </si>
   <si>
     <t xml:space="preserve">4.96991682052612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93078327178955</t>
+    <t xml:space="preserve">4.93078374862671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85251665115356</t>
+    <t xml:space="preserve">4.85251712799072</t>
   </si>
   <si>
     <t xml:space="preserve">5.12644958496094</t>
@@ -476,25 +476,25 @@
     <t xml:space="preserve">5.04818296432495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08731603622437</t>
+    <t xml:space="preserve">5.08731651306152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59604740142822</t>
+    <t xml:space="preserve">5.59604787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26159715652466</t>
+    <t xml:space="preserve">5.26159763336182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42103910446167</t>
+    <t xml:space="preserve">5.42104053497314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34131765365601</t>
+    <t xml:space="preserve">5.34131813049316</t>
   </si>
   <si>
     <t xml:space="preserve">5.22173690795898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14201545715332</t>
+    <t xml:space="preserve">5.14201498031616</t>
   </si>
   <si>
     <t xml:space="preserve">5.10215520858765</t>
@@ -515,19 +515,19 @@
     <t xml:space="preserve">5.50076055526733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46090078353882</t>
+    <t xml:space="preserve">5.4608998298645</t>
   </si>
   <si>
     <t xml:space="preserve">5.580482006073</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54062223434448</t>
+    <t xml:space="preserve">5.54062175750732</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62034225463867</t>
+    <t xml:space="preserve">5.62034273147583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94271230697632</t>
+    <t xml:space="preserve">4.94271278381348</t>
   </si>
   <si>
     <t xml:space="preserve">4.98257350921631</t>
@@ -539,52 +539,52 @@
     <t xml:space="preserve">5.06229448318481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02243375778198</t>
+    <t xml:space="preserve">5.02243423461914</t>
   </si>
   <si>
     <t xml:space="preserve">4.74341011047363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78327035903931</t>
+    <t xml:space="preserve">4.78326988220215</t>
   </si>
   <si>
     <t xml:space="preserve">4.86299133300781</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73992443084717</t>
+    <t xml:space="preserve">5.73992490768433</t>
   </si>
   <si>
     <t xml:space="preserve">5.81964588165283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70006322860718</t>
+    <t xml:space="preserve">5.70006418228149</t>
   </si>
   <si>
     <t xml:space="preserve">5.6602029800415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77978467941284</t>
+    <t xml:space="preserve">5.77978515625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85950565338135</t>
+    <t xml:space="preserve">5.85950613021851</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97908782958984</t>
+    <t xml:space="preserve">5.979088306427</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29797315597534</t>
+    <t xml:space="preserve">6.29797267913818</t>
   </si>
   <si>
     <t xml:space="preserve">6.13852977752686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05880880355835</t>
+    <t xml:space="preserve">6.05880928039551</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825170516968</t>
+    <t xml:space="preserve">6.21825122833252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09867000579834</t>
+    <t xml:space="preserve">6.09866952896118</t>
   </si>
   <si>
     <t xml:space="preserve">6.38518476486206</t>
@@ -599,22 +599,22 @@
     <t xml:space="preserve">6.17651844024658</t>
   </si>
   <si>
-    <t xml:space="preserve">6.426917552948</t>
+    <t xml:space="preserve">6.42691707611084</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34345149993896</t>
+    <t xml:space="preserve">6.34345102310181</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46865129470825</t>
+    <t xml:space="preserve">6.46865177154541</t>
   </si>
   <si>
     <t xml:space="preserve">5.9678521156311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00958490371704</t>
+    <t xml:space="preserve">6.00958585739136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13478422164917</t>
+    <t xml:space="preserve">6.13478517532349</t>
   </si>
   <si>
     <t xml:space="preserve">6.05131816864014</t>
@@ -623,13 +623,13 @@
     <t xml:space="preserve">5.92611885070801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09305143356323</t>
+    <t xml:space="preserve">6.09305238723755</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51038455963135</t>
+    <t xml:space="preserve">6.51038408279419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84265232086182</t>
+    <t xml:space="preserve">5.84265279769897</t>
   </si>
   <si>
     <t xml:space="preserve">5.88438558578491</t>
@@ -638,64 +638,64 @@
     <t xml:space="preserve">7.05291652679443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09624767303467</t>
+    <t xml:space="preserve">8.09624671936035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80411434173584</t>
+    <t xml:space="preserve">7.804114818573</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63718175888062</t>
+    <t xml:space="preserve">7.63718032836914</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55371522903442</t>
+    <t xml:space="preserve">7.55371570587158</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34504890441895</t>
+    <t xml:space="preserve">7.3450493812561</t>
   </si>
   <si>
     <t xml:space="preserve">7.17811679840088</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51198148727417</t>
+    <t xml:space="preserve">7.51198101043701</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47024869918823</t>
+    <t xml:space="preserve">7.47024917602539</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30331516265869</t>
+    <t xml:space="preserve">7.30331563949585</t>
   </si>
   <si>
     <t xml:space="preserve">7.42851495742798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2615818977356</t>
+    <t xml:space="preserve">7.26158237457275</t>
   </si>
   <si>
     <t xml:space="preserve">7.38678216934204</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96944952011108</t>
+    <t xml:space="preserve">6.96944999694824</t>
   </si>
   <si>
     <t xml:space="preserve">7.2198486328125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544801712036</t>
+    <t xml:space="preserve">7.59544944763184</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76238107681274</t>
+    <t xml:space="preserve">7.7623815536499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84584712982178</t>
+    <t xml:space="preserve">7.84584760665894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67891454696655</t>
+    <t xml:space="preserve">7.67891407012939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01118326187134</t>
+    <t xml:space="preserve">7.01118278503418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09464931488037</t>
+    <t xml:space="preserve">7.09464883804321</t>
   </si>
   <si>
     <t xml:space="preserve">6.92771625518799</t>
@@ -704,16 +704,16 @@
     <t xml:space="preserve">6.76078414916992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80251598358154</t>
+    <t xml:space="preserve">6.8025164604187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71904993057251</t>
+    <t xml:space="preserve">6.71905040740967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8442497253418</t>
+    <t xml:space="preserve">6.84425020217896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5938515663147</t>
+    <t xml:space="preserve">6.59385061264038</t>
   </si>
   <si>
     <t xml:space="preserve">6.67731714248657</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">6.55211734771729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75918626785278</t>
+    <t xml:space="preserve">5.75918579101562</t>
   </si>
   <si>
     <t xml:space="preserve">5.71745252609253</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">5.80091953277588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67571926116943</t>
+    <t xml:space="preserve">5.67571973800659</t>
   </si>
   <si>
     <t xml:space="preserve">5.59225225448608</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">5.6339864730835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46705341339111</t>
+    <t xml:space="preserve">5.46705389022827</t>
   </si>
   <si>
     <t xml:space="preserve">5.5505199432373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17492055892944</t>
+    <t xml:space="preserve">5.1749210357666</t>
   </si>
   <si>
     <t xml:space="preserve">5.25838756561279</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">7.4724702835083</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25269269943237</t>
+    <t xml:space="preserve">7.25269222259521</t>
   </si>
   <si>
     <t xml:space="preserve">7.29664754867554</t>
@@ -770,13 +770,13 @@
     <t xml:space="preserve">7.20873641967773</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1647801399231</t>
+    <t xml:space="preserve">7.16478061676025</t>
   </si>
   <si>
     <t xml:space="preserve">7.07686948776245</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98895788192749</t>
+    <t xml:space="preserve">6.98895835876465</t>
   </si>
   <si>
     <t xml:space="preserve">7.03291368484497</t>
@@ -812,10 +812,10 @@
     <t xml:space="preserve">7.51642656326294</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56038284301758</t>
+    <t xml:space="preserve">7.56038331985474</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851591110229</t>
+    <t xml:space="preserve">7.42851543426514</t>
   </si>
   <si>
     <t xml:space="preserve">7.7362060546875</t>
@@ -61290,7 +61290,7 @@
     </row>
     <row r="2280">
       <c r="A2280" s="1" t="n">
-        <v>45979.3876388889</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2280" t="n">
         <v>250</v>
@@ -61311,6 +61311,32 @@
         <v>533</v>
       </c>
       <c r="H2280" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" s="1" t="n">
+        <v>45980.6063657407</v>
+      </c>
+      <c r="B2281" t="n">
+        <v>250</v>
+      </c>
+      <c r="C2281" t="n">
+        <v>38</v>
+      </c>
+      <c r="D2281" t="n">
+        <v>38</v>
+      </c>
+      <c r="E2281" t="n">
+        <v>38</v>
+      </c>
+      <c r="F2281" t="n">
+        <v>38</v>
+      </c>
+      <c r="G2281" t="s">
+        <v>537</v>
+      </c>
+      <c r="H2281" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -44,61 +44,61 @@
     <t xml:space="preserve">FPE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42625832557678</t>
+    <t xml:space="preserve">2.42625856399536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43408489227295</t>
+    <t xml:space="preserve">2.43408513069153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41060543060303</t>
+    <t xml:space="preserve">2.41060495376587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45756506919861</t>
+    <t xml:space="preserve">2.45756530761719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39495158195496</t>
+    <t xml:space="preserve">2.39495182037354</t>
   </si>
   <si>
     <t xml:space="preserve">2.3323392868042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41843199729919</t>
+    <t xml:space="preserve">2.41843175888062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35581922531128</t>
+    <t xml:space="preserve">2.3558189868927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37147164344788</t>
+    <t xml:space="preserve">2.37147188186646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50452518463135</t>
+    <t xml:space="preserve">2.50452494621277</t>
   </si>
   <si>
     <t xml:space="preserve">2.36364531517029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44973850250244</t>
+    <t xml:space="preserve">2.44973874092102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37303757667542</t>
+    <t xml:space="preserve">2.37303781509399</t>
   </si>
   <si>
     <t xml:space="preserve">2.34955763816833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46382641792297</t>
+    <t xml:space="preserve">2.46382617950439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38712549209595</t>
+    <t xml:space="preserve">2.38712501525879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45443439483643</t>
+    <t xml:space="preserve">2.45443415641785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34799194335938</t>
+    <t xml:space="preserve">2.34799218177795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48104476928711</t>
+    <t xml:space="preserve">2.48104500770569</t>
   </si>
   <si>
     <t xml:space="preserve">2.3792986869812</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">2.38556003570557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44191193580627</t>
+    <t xml:space="preserve">2.4419116973877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78002238273621</t>
+    <t xml:space="preserve">2.78002262115479</t>
   </si>
   <si>
     <t xml:space="preserve">3.36702084541321</t>
@@ -119,16 +119,16 @@
     <t xml:space="preserve">3.62529969215393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31066870689392</t>
+    <t xml:space="preserve">3.3106689453125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25588274002075</t>
+    <t xml:space="preserve">3.25588202476501</t>
   </si>
   <si>
     <t xml:space="preserve">3.20266127586365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0523898601532</t>
+    <t xml:space="preserve">3.05238962173462</t>
   </si>
   <si>
     <t xml:space="preserve">3.09152317047119</t>
@@ -137,37 +137,37 @@
     <t xml:space="preserve">3.04456329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03673648834229</t>
+    <t xml:space="preserve">3.03673672676086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03830194473267</t>
+    <t xml:space="preserve">3.03830170631409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15413594245911</t>
+    <t xml:space="preserve">3.15413618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3091037273407</t>
+    <t xml:space="preserve">3.30910348892212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30284190177917</t>
+    <t xml:space="preserve">3.3028416633606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35762882232666</t>
+    <t xml:space="preserve">3.3576283454895</t>
   </si>
   <si>
     <t xml:space="preserve">3.57677507400513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5219874382019</t>
+    <t xml:space="preserve">3.52198839187622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40458869934082</t>
+    <t xml:space="preserve">3.40458846092224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59242844581604</t>
+    <t xml:space="preserve">3.59242820739746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58460092544556</t>
+    <t xml:space="preserve">3.58460140228271</t>
   </si>
   <si>
     <t xml:space="preserve">3.67852091789246</t>
@@ -185,34 +185,34 @@
     <t xml:space="preserve">3.29501581192017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37484765052795</t>
+    <t xml:space="preserve">3.37484741210938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38267374038696</t>
+    <t xml:space="preserve">3.38267421722412</t>
   </si>
   <si>
     <t xml:space="preserve">3.44372200965881</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59086275100708</t>
+    <t xml:space="preserve">3.59086298942566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47972440719604</t>
+    <t xml:space="preserve">3.47972393035889</t>
   </si>
   <si>
     <t xml:space="preserve">3.42650294303894</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41241478919983</t>
+    <t xml:space="preserve">3.41241526603699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24022889137268</t>
+    <t xml:space="preserve">3.24022912979126</t>
   </si>
   <si>
     <t xml:space="preserve">3.21048831939697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28405833244324</t>
+    <t xml:space="preserve">3.28405809402466</t>
   </si>
   <si>
     <t xml:space="preserve">3.16196298599243</t>
@@ -221,37 +221,37 @@
     <t xml:space="preserve">3.20892238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13848328590393</t>
+    <t xml:space="preserve">3.13848304748535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23240280151367</t>
+    <t xml:space="preserve">3.23240232467651</t>
   </si>
   <si>
     <t xml:space="preserve">3.31849527359009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27623200416565</t>
+    <t xml:space="preserve">3.27623105049133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18857336044312</t>
+    <t xml:space="preserve">3.18857312202454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14317870140076</t>
+    <t xml:space="preserve">3.14317846298218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11500334739685</t>
+    <t xml:space="preserve">3.11500310897827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00073409080505</t>
+    <t xml:space="preserve">3.00073385238647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97412347793579</t>
+    <t xml:space="preserve">2.97412323951721</t>
   </si>
   <si>
     <t xml:space="preserve">3.06021618843079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90368366241455</t>
+    <t xml:space="preserve">2.90368342399597</t>
   </si>
   <si>
     <t xml:space="preserve">2.89585709571838</t>
@@ -263,25 +263,25 @@
     <t xml:space="preserve">2.83637452125549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90994501113892</t>
+    <t xml:space="preserve">2.90994477272034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491208076477</t>
+    <t xml:space="preserve">3.06491255760193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13065576553345</t>
+    <t xml:space="preserve">3.13065600395203</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14474439620972</t>
+    <t xml:space="preserve">3.14474415779114</t>
   </si>
   <si>
     <t xml:space="preserve">3.21361827850342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28562355041504</t>
+    <t xml:space="preserve">3.28562331199646</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35919332504272</t>
+    <t xml:space="preserve">3.35919404029846</t>
   </si>
   <si>
     <t xml:space="preserve">3.36388969421387</t>
@@ -290,19 +290,19 @@
     <t xml:space="preserve">3.91332006454468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34378623962402</t>
+    <t xml:space="preserve">4.34378528594971</t>
   </si>
   <si>
     <t xml:space="preserve">4.79381704330444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47864818572998</t>
+    <t xml:space="preserve">5.47864770889282</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09303951263428</t>
+    <t xml:space="preserve">6.09303903579712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41603565216064</t>
+    <t xml:space="preserve">5.41603517532349</t>
   </si>
   <si>
     <t xml:space="preserve">5.71344757080078</t>
@@ -314,25 +314,25 @@
     <t xml:space="preserve">5.41994905471802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16558313369751</t>
+    <t xml:space="preserve">5.16558218002319</t>
   </si>
   <si>
     <t xml:space="preserve">4.94643688201904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7038106918335</t>
+    <t xml:space="preserve">4.70381164550781</t>
   </si>
   <si>
     <t xml:space="preserve">4.6764178276062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0090503692627</t>
+    <t xml:space="preserve">5.00904989242554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55691480636597</t>
+    <t xml:space="preserve">5.55691385269165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30646228790283</t>
+    <t xml:space="preserve">5.30646276473999</t>
   </si>
   <si>
     <t xml:space="preserve">5.22428274154663</t>
@@ -341,19 +341,19 @@
     <t xml:space="preserve">5.19688940048218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32211542129517</t>
+    <t xml:space="preserve">5.32211494445801</t>
   </si>
   <si>
     <t xml:space="preserve">5.47082138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36907482147217</t>
+    <t xml:space="preserve">5.36907529830933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2908091545105</t>
+    <t xml:space="preserve">5.29080963134766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1734094619751</t>
+    <t xml:space="preserve">5.17340898513794</t>
   </si>
   <si>
     <t xml:space="preserve">5.09514331817627</t>
@@ -362,16 +362,16 @@
     <t xml:space="preserve">5.22036933898926</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1029691696167</t>
+    <t xml:space="preserve">5.10297012329102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9933967590332</t>
+    <t xml:space="preserve">4.99339723587036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15384244918823</t>
+    <t xml:space="preserve">5.15384340286255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98556995391846</t>
+    <t xml:space="preserve">4.9855694770813</t>
   </si>
   <si>
     <t xml:space="preserve">4.7585973739624</t>
@@ -380,76 +380,76 @@
     <t xml:space="preserve">4.77033662796021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86425733566284</t>
+    <t xml:space="preserve">4.86425685882568</t>
   </si>
   <si>
     <t xml:space="preserve">4.88773727416992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83295059204102</t>
+    <t xml:space="preserve">4.83295106887817</t>
   </si>
   <si>
     <t xml:space="preserve">4.75468397140503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82903718948364</t>
+    <t xml:space="preserve">4.8290376663208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72337770462036</t>
+    <t xml:space="preserve">4.7233772277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68815803527832</t>
+    <t xml:space="preserve">4.68815755844116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78207683563232</t>
+    <t xml:space="preserve">4.78207731246948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87599658966064</t>
+    <t xml:space="preserve">4.8759970664978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03644323348999</t>
+    <t xml:space="preserve">5.03644275665283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92686986923218</t>
+    <t xml:space="preserve">4.92687034606934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81338405609131</t>
+    <t xml:space="preserve">4.81338453292847</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86034393310547</t>
+    <t xml:space="preserve">4.86034345626831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00122308731079</t>
+    <t xml:space="preserve">5.00122356414795</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77425098419189</t>
+    <t xml:space="preserve">4.77425003051758</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82121086120605</t>
+    <t xml:space="preserve">4.82120990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69989824295044</t>
+    <t xml:space="preserve">4.69989776611328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69598388671875</t>
+    <t xml:space="preserve">4.69598436355591</t>
   </si>
   <si>
     <t xml:space="preserve">4.90730381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20471620559692</t>
+    <t xml:space="preserve">5.20471668243408</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43951511383057</t>
+    <t xml:space="preserve">5.43951559066772</t>
   </si>
   <si>
     <t xml:space="preserve">5.28298187255859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384880065918</t>
+    <t xml:space="preserve">5.2438497543335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36124801635742</t>
+    <t xml:space="preserve">5.36124849319458</t>
   </si>
   <si>
     <t xml:space="preserve">5.40038251876831</t>
@@ -467,16 +467,16 @@
     <t xml:space="preserve">4.93078374862671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85251665115356</t>
+    <t xml:space="preserve">4.85251712799072</t>
   </si>
   <si>
     <t xml:space="preserve">5.12644958496094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04818248748779</t>
+    <t xml:space="preserve">5.04818296432495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08731603622437</t>
+    <t xml:space="preserve">5.08731555938721</t>
   </si>
   <si>
     <t xml:space="preserve">5.59604835510254</t>
@@ -485,7 +485,7 @@
     <t xml:space="preserve">5.26159715652466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42104005813599</t>
+    <t xml:space="preserve">5.42103958129883</t>
   </si>
   <si>
     <t xml:space="preserve">5.34131908416748</t>
@@ -497,28 +497,28 @@
     <t xml:space="preserve">5.14201498031616</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10215520858765</t>
+    <t xml:space="preserve">5.10215473175049</t>
   </si>
   <si>
     <t xml:space="preserve">5.18187570571899</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38117933273315</t>
+    <t xml:space="preserve">5.381178855896</t>
   </si>
   <si>
     <t xml:space="preserve">5.30145835876465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90285205841064</t>
+    <t xml:space="preserve">4.9028525352478</t>
   </si>
   <si>
     <t xml:space="preserve">5.50076103210449</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4608998298645</t>
+    <t xml:space="preserve">5.46090030670166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.580482006073</t>
+    <t xml:space="preserve">5.58048152923584</t>
   </si>
   <si>
     <t xml:space="preserve">5.54062175750732</t>
@@ -527,40 +527,40 @@
     <t xml:space="preserve">5.62034273147583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94271278381348</t>
+    <t xml:space="preserve">4.94271230697632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98257303237915</t>
+    <t xml:space="preserve">4.98257350921631</t>
   </si>
   <si>
     <t xml:space="preserve">4.82313108444214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06229496002197</t>
+    <t xml:space="preserve">5.06229448318481</t>
   </si>
   <si>
     <t xml:space="preserve">5.02243423461914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74340963363647</t>
+    <t xml:space="preserve">4.74341011047363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78326988220215</t>
+    <t xml:space="preserve">4.78327035903931</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86299133300781</t>
+    <t xml:space="preserve">4.86299085617065</t>
   </si>
   <si>
     <t xml:space="preserve">5.73992443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81964540481567</t>
+    <t xml:space="preserve">5.81964588165283</t>
   </si>
   <si>
     <t xml:space="preserve">5.70006418228149</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6602029800415</t>
+    <t xml:space="preserve">5.66020250320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.77978515625</t>
@@ -569,34 +569,34 @@
     <t xml:space="preserve">5.85950613021851</t>
   </si>
   <si>
-    <t xml:space="preserve">5.979088306427</t>
+    <t xml:space="preserve">5.97908782958984</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29797220230103</t>
+    <t xml:space="preserve">6.29797267913818</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13853025436401</t>
+    <t xml:space="preserve">6.13853073120117</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05880928039551</t>
+    <t xml:space="preserve">6.05880880355835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825170516968</t>
+    <t xml:space="preserve">6.21825122833252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09866952896118</t>
+    <t xml:space="preserve">6.09867000579834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3851842880249</t>
+    <t xml:space="preserve">6.38518476486206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25998497009277</t>
+    <t xml:space="preserve">6.25998449325562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30171871185303</t>
+    <t xml:space="preserve">6.30171823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17651796340942</t>
+    <t xml:space="preserve">6.17651844024658</t>
   </si>
   <si>
     <t xml:space="preserve">6.426917552948</t>
@@ -605,49 +605,49 @@
     <t xml:space="preserve">6.34345102310181</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46865081787109</t>
+    <t xml:space="preserve">6.46865129470825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9678521156311</t>
+    <t xml:space="preserve">5.96785259246826</t>
   </si>
   <si>
     <t xml:space="preserve">6.0095853805542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13478517532349</t>
+    <t xml:space="preserve">6.13478469848633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05131864547729</t>
+    <t xml:space="preserve">6.05131816864014</t>
   </si>
   <si>
     <t xml:space="preserve">5.92611885070801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09305191040039</t>
+    <t xml:space="preserve">6.09305238723755</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825122833252</t>
+    <t xml:space="preserve">6.21825170516968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51038455963135</t>
+    <t xml:space="preserve">6.51038360595703</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84265279769897</t>
+    <t xml:space="preserve">5.84265232086182</t>
   </si>
   <si>
     <t xml:space="preserve">5.88438558578491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05291604995728</t>
+    <t xml:space="preserve">7.05291557312012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09624671936035</t>
+    <t xml:space="preserve">8.09624576568604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.804114818573</t>
+    <t xml:space="preserve">7.80411386489868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6371808052063</t>
+    <t xml:space="preserve">7.63718128204346</t>
   </si>
   <si>
     <t xml:space="preserve">7.55371475219727</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">7.3450493812561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17811632156372</t>
+    <t xml:space="preserve">7.1781153678894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51198101043701</t>
+    <t xml:space="preserve">7.51198196411133</t>
   </si>
   <si>
     <t xml:space="preserve">7.47024822235107</t>
@@ -668,10 +668,10 @@
     <t xml:space="preserve">7.30331611633301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4285135269165</t>
+    <t xml:space="preserve">7.42851495742798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26158237457275</t>
+    <t xml:space="preserve">7.2615818977356</t>
   </si>
   <si>
     <t xml:space="preserve">7.38678216934204</t>
@@ -683,31 +683,31 @@
     <t xml:space="preserve">7.2198486328125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544944763184</t>
+    <t xml:space="preserve">7.59544849395752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76238107681274</t>
+    <t xml:space="preserve">7.7623815536499</t>
   </si>
   <si>
     <t xml:space="preserve">7.84584760665894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67891550064087</t>
+    <t xml:space="preserve">7.67891407012939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01118230819702</t>
+    <t xml:space="preserve">7.01118278503418</t>
   </si>
   <si>
     <t xml:space="preserve">7.09464979171753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92771625518799</t>
+    <t xml:space="preserve">6.9277172088623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76078462600708</t>
+    <t xml:space="preserve">6.76078414916992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8025164604187</t>
+    <t xml:space="preserve">6.80251693725586</t>
   </si>
   <si>
     <t xml:space="preserve">6.71905040740967</t>
@@ -716,13 +716,13 @@
     <t xml:space="preserve">6.8442497253418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59385013580322</t>
+    <t xml:space="preserve">6.59385108947754</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67731666564941</t>
+    <t xml:space="preserve">6.67731714248657</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55211782455444</t>
+    <t xml:space="preserve">6.55211734771729</t>
   </si>
   <si>
     <t xml:space="preserve">5.75918626785278</t>
@@ -737,25 +737,25 @@
     <t xml:space="preserve">5.67571926116943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5922532081604</t>
+    <t xml:space="preserve">5.59225273132324</t>
   </si>
   <si>
     <t xml:space="preserve">5.6339864730835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46705389022827</t>
+    <t xml:space="preserve">5.46705341339111</t>
   </si>
   <si>
     <t xml:space="preserve">5.55052042007446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1749210357666</t>
+    <t xml:space="preserve">5.17492055892944</t>
   </si>
   <si>
     <t xml:space="preserve">5.25838756561279</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38358688354492</t>
+    <t xml:space="preserve">5.38358736038208</t>
   </si>
   <si>
     <t xml:space="preserve">7.13638353347778</t>
@@ -767,13 +767,13 @@
     <t xml:space="preserve">7.25269222259521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29664754867554</t>
+    <t xml:space="preserve">7.29664850234985</t>
   </si>
   <si>
     <t xml:space="preserve">7.20873594284058</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16478061676025</t>
+    <t xml:space="preserve">7.16478109359741</t>
   </si>
   <si>
     <t xml:space="preserve">7.07686948776245</t>
@@ -785,28 +785,28 @@
     <t xml:space="preserve">7.03291320800781</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94500255584717</t>
+    <t xml:space="preserve">6.94500303268433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85709095001221</t>
+    <t xml:space="preserve">6.85709047317505</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72522354125977</t>
+    <t xml:space="preserve">6.72522401809692</t>
   </si>
   <si>
     <t xml:space="preserve">6.81313514709473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76917934417725</t>
+    <t xml:space="preserve">6.7691798210144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90104675292969</t>
+    <t xml:space="preserve">6.90104627609253</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63731288909912</t>
+    <t xml:space="preserve">6.63731241226196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12082624435425</t>
+    <t xml:space="preserve">7.12082576751709</t>
   </si>
   <si>
     <t xml:space="preserve">7.34060430526733</t>
@@ -815,10 +815,10 @@
     <t xml:space="preserve">7.51642751693726</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56038284301758</t>
+    <t xml:space="preserve">7.56038188934326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851495742798</t>
+    <t xml:space="preserve">7.42851448059082</t>
   </si>
   <si>
     <t xml:space="preserve">7.7362060546875</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">7.69224977493286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829397201538</t>
+    <t xml:space="preserve">7.64829301834106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78247451782227</t>
+    <t xml:space="preserve">7.78247356414795</t>
   </si>
   <si>
     <t xml:space="preserve">7.82720136642456</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">7.73774671554565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69302082061768</t>
+    <t xml:space="preserve">7.69301986694336</t>
   </si>
   <si>
     <t xml:space="preserve">7.64829444885254</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">7.87192869186401</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96138048171997</t>
+    <t xml:space="preserve">7.96138143539429</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22974300384521</t>
+    <t xml:space="preserve">8.2297420501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.76646518707275</t>
@@ -884,10 +884,10 @@
     <t xml:space="preserve">8.45337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67701148986816</t>
+    <t xml:space="preserve">8.67701053619385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49810314178467</t>
+    <t xml:space="preserve">8.49810409545898</t>
   </si>
   <si>
     <t xml:space="preserve">8.81119251251221</t>
@@ -914,43 +914,43 @@
     <t xml:space="preserve">11.0922613143921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9133548736572</t>
+    <t xml:space="preserve">10.9133539199829</t>
   </si>
   <si>
     <t xml:space="preserve">11.1817150115967</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3606233596802</t>
+    <t xml:space="preserve">11.3606224060059</t>
   </si>
   <si>
     <t xml:space="preserve">11.6289844512939</t>
   </si>
   <si>
-    <t xml:space="preserve">11.539529800415</t>
+    <t xml:space="preserve">11.5395307540894</t>
   </si>
   <si>
     <t xml:space="preserve">11.2711696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5555391311646</t>
+    <t xml:space="preserve">10.5555400848389</t>
   </si>
   <si>
     <t xml:space="preserve">10.2871789932251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0028085708618</t>
+    <t xml:space="preserve">11.0028095245361</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6449928283691</t>
+    <t xml:space="preserve">10.6449937820435</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4660863876343</t>
+    <t xml:space="preserve">10.46608543396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1082706451416</t>
+    <t xml:space="preserve">10.1082715988159</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1977243423462</t>
+    <t xml:space="preserve">10.1977252960205</t>
   </si>
   <si>
     <t xml:space="preserve">9.75045585632324</t>
@@ -962,31 +962,31 @@
     <t xml:space="preserve">12.6129751205444</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9707908630371</t>
+    <t xml:space="preserve">12.9707899093628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0442352294922</t>
+    <t xml:space="preserve">14.0442342758179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7758731842041</t>
+    <t xml:space="preserve">13.7758741378784</t>
   </si>
   <si>
-    <t xml:space="preserve">13.507513999939</t>
+    <t xml:space="preserve">13.5075130462646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2391510009766</t>
+    <t xml:space="preserve">13.2391519546509</t>
   </si>
   <si>
     <t xml:space="preserve">13.0602445602417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4180593490601</t>
+    <t xml:space="preserve">13.4180583953857</t>
   </si>
   <si>
     <t xml:space="preserve">12.8813362121582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7918825149536</t>
+    <t xml:space="preserve">12.7918834686279</t>
   </si>
   <si>
     <t xml:space="preserve">12.702428817749</t>
@@ -995,16 +995,16 @@
     <t xml:space="preserve">13.149697303772</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3286046981812</t>
+    <t xml:space="preserve">13.3286056518555</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547815322876</t>
+    <t xml:space="preserve">13.9547805786133</t>
   </si>
   <si>
     <t xml:space="preserve">13.5969657897949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6864194869995</t>
+    <t xml:space="preserve">13.6864204406738</t>
   </si>
   <si>
     <t xml:space="preserve">13.865327835083</t>
@@ -1019,13 +1019,13 @@
     <t xml:space="preserve">15.2071342468262</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5809564590454</t>
+    <t xml:space="preserve">14.5809574127197</t>
   </si>
   <si>
     <t xml:space="preserve">14.7598648071289</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4915056228638</t>
+    <t xml:space="preserve">14.4915046691895</t>
   </si>
   <si>
     <t xml:space="preserve">14.5400886535645</t>
@@ -61348,7 +61348,7 @@
     </row>
     <row r="2282">
       <c r="A2282" s="1" t="n">
-        <v>45981.644537037</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2282" t="n">
         <v>500</v>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="562">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,136 +44,136 @@
     <t xml:space="preserve">FPE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42625856399536</t>
+    <t xml:space="preserve">2.42625832557678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43408536911011</t>
+    <t xml:space="preserve">2.43408513069153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41060543060303</t>
+    <t xml:space="preserve">2.41060495376587</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45756506919861</t>
+    <t xml:space="preserve">2.45756530761719</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39495205879211</t>
+    <t xml:space="preserve">2.39495182037354</t>
   </si>
   <si>
     <t xml:space="preserve">2.33233904838562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41843175888062</t>
+    <t xml:space="preserve">2.41843223571777</t>
   </si>
   <si>
     <t xml:space="preserve">2.35581874847412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37147212028503</t>
+    <t xml:space="preserve">2.37147188186646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50452518463135</t>
+    <t xml:space="preserve">2.50452470779419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36364531517029</t>
+    <t xml:space="preserve">2.36364555358887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44973850250244</t>
+    <t xml:space="preserve">2.44973826408386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37303733825684</t>
+    <t xml:space="preserve">2.37303757667542</t>
   </si>
   <si>
     <t xml:space="preserve">2.34955763816833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46382641792297</t>
+    <t xml:space="preserve">2.46382617950439</t>
   </si>
   <si>
     <t xml:space="preserve">2.38712525367737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45443439483643</t>
+    <t xml:space="preserve">2.45443415641785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34799218177795</t>
+    <t xml:space="preserve">2.34799194335938</t>
   </si>
   <si>
     <t xml:space="preserve">2.48104500770569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3792986869812</t>
+    <t xml:space="preserve">2.37929844856262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38556027412415</t>
+    <t xml:space="preserve">2.38556003570557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44191193580627</t>
+    <t xml:space="preserve">2.44191145896912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78002285957336</t>
+    <t xml:space="preserve">2.78002262115479</t>
   </si>
   <si>
     <t xml:space="preserve">3.36702084541321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62529993057251</t>
+    <t xml:space="preserve">3.62529969215393</t>
   </si>
   <si>
     <t xml:space="preserve">3.31066870689392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25588226318359</t>
+    <t xml:space="preserve">3.25588250160217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20266127586365</t>
+    <t xml:space="preserve">3.20266103744507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05238962173462</t>
+    <t xml:space="preserve">3.0523898601532</t>
   </si>
   <si>
     <t xml:space="preserve">3.09152293205261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04456305503845</t>
+    <t xml:space="preserve">3.04456281661987</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03673648834229</t>
+    <t xml:space="preserve">3.03673672676086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03830170631409</t>
+    <t xml:space="preserve">3.03830194473267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15413665771484</t>
+    <t xml:space="preserve">3.15413641929626</t>
   </si>
   <si>
     <t xml:space="preserve">3.3091037273407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30284190177917</t>
+    <t xml:space="preserve">3.30284214019775</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35762906074524</t>
+    <t xml:space="preserve">3.35762882232666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57677483558655</t>
+    <t xml:space="preserve">3.57677459716797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52198815345764</t>
+    <t xml:space="preserve">3.52198839187622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40458869934082</t>
+    <t xml:space="preserve">3.4045889377594</t>
   </si>
   <si>
     <t xml:space="preserve">3.59242796897888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58460116386414</t>
+    <t xml:space="preserve">3.58460164070129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67852067947388</t>
+    <t xml:space="preserve">3.67852115631104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60025477409363</t>
+    <t xml:space="preserve">3.60025429725647</t>
   </si>
   <si>
     <t xml:space="preserve">3.59555864334106</t>
@@ -182,22 +182,22 @@
     <t xml:space="preserve">3.32632184028625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29501557350159</t>
+    <t xml:space="preserve">3.29501533508301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37484741210938</t>
+    <t xml:space="preserve">3.3748471736908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38267397880554</t>
+    <t xml:space="preserve">3.38267374038696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44372200965881</t>
+    <t xml:space="preserve">3.44372177124023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59086227416992</t>
+    <t xml:space="preserve">3.59086275100708</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47972440719604</t>
+    <t xml:space="preserve">3.47972464561462</t>
   </si>
   <si>
     <t xml:space="preserve">3.4265034198761</t>
@@ -212,31 +212,31 @@
     <t xml:space="preserve">3.21048831939697</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28405857086182</t>
+    <t xml:space="preserve">3.28405833244324</t>
   </si>
   <si>
     <t xml:space="preserve">3.16196274757385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20892262458801</t>
+    <t xml:space="preserve">3.20892238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13848304748535</t>
+    <t xml:space="preserve">3.13848328590393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23240280151367</t>
+    <t xml:space="preserve">3.23240256309509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31849527359009</t>
+    <t xml:space="preserve">3.31849551200867</t>
   </si>
   <si>
     <t xml:space="preserve">3.27623176574707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18857312202454</t>
+    <t xml:space="preserve">3.18857336044312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14317893981934</t>
+    <t xml:space="preserve">3.14317846298218</t>
   </si>
   <si>
     <t xml:space="preserve">3.11500287055969</t>
@@ -248,22 +248,22 @@
     <t xml:space="preserve">2.97412347793579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06021618843079</t>
+    <t xml:space="preserve">3.06021642684937</t>
   </si>
   <si>
     <t xml:space="preserve">2.90368366241455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8958568572998</t>
+    <t xml:space="preserve">2.89585709571838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82854819297791</t>
+    <t xml:space="preserve">2.82854795455933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83637452125549</t>
+    <t xml:space="preserve">2.83637428283691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90994477272034</t>
+    <t xml:space="preserve">2.90994501113892</t>
   </si>
   <si>
     <t xml:space="preserve">3.06491231918335</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">3.14474439620972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.213618516922</t>
+    <t xml:space="preserve">3.21361827850342</t>
   </si>
   <si>
     <t xml:space="preserve">3.28562378883362</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">3.35919380187988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36388969421387</t>
+    <t xml:space="preserve">3.36389017105103</t>
   </si>
   <si>
     <t xml:space="preserve">3.91332030296326</t>
@@ -302,43 +302,43 @@
     <t xml:space="preserve">6.09303951263428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41603517532349</t>
+    <t xml:space="preserve">5.41603469848633</t>
   </si>
   <si>
     <t xml:space="preserve">5.71344709396362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56865406036377</t>
+    <t xml:space="preserve">5.56865453720093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41994905471802</t>
+    <t xml:space="preserve">5.41994857788086</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16558218002319</t>
+    <t xml:space="preserve">5.16558265686035</t>
   </si>
   <si>
     <t xml:space="preserve">4.94643640518188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7038106918335</t>
+    <t xml:space="preserve">4.70381116867065</t>
   </si>
   <si>
     <t xml:space="preserve">4.6764178276062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0090503692627</t>
+    <t xml:space="preserve">5.00904941558838</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55691528320312</t>
+    <t xml:space="preserve">5.55691480636597</t>
   </si>
   <si>
     <t xml:space="preserve">5.30646276473999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22428226470947</t>
+    <t xml:space="preserve">5.22428274154663</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19688987731934</t>
+    <t xml:space="preserve">5.19688940048218</t>
   </si>
   <si>
     <t xml:space="preserve">5.32211542129517</t>
@@ -347,70 +347,70 @@
     <t xml:space="preserve">5.47082185745239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36907482147217</t>
+    <t xml:space="preserve">5.36907529830933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29080963134766</t>
+    <t xml:space="preserve">5.2908091545105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17340898513794</t>
+    <t xml:space="preserve">5.1734094619751</t>
   </si>
   <si>
     <t xml:space="preserve">5.09514284133911</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22036981582642</t>
+    <t xml:space="preserve">5.2203688621521</t>
   </si>
   <si>
     <t xml:space="preserve">5.1029691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99339628219604</t>
+    <t xml:space="preserve">4.99339723587036</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15384292602539</t>
+    <t xml:space="preserve">5.15384244918823</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9855694770813</t>
+    <t xml:space="preserve">4.98556995391846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7585973739624</t>
+    <t xml:space="preserve">4.75859689712524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77033615112305</t>
+    <t xml:space="preserve">4.77033710479736</t>
   </si>
   <si>
     <t xml:space="preserve">4.86425733566284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88773727416992</t>
+    <t xml:space="preserve">4.88773679733276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83295106887817</t>
+    <t xml:space="preserve">4.83295011520386</t>
   </si>
   <si>
     <t xml:space="preserve">4.75468397140503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8290376663208</t>
+    <t xml:space="preserve">4.82903671264648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72337675094604</t>
+    <t xml:space="preserve">4.7233772277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68815755844116</t>
+    <t xml:space="preserve">4.68815803527832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78207731246948</t>
+    <t xml:space="preserve">4.78207683563232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8759970664978</t>
+    <t xml:space="preserve">4.87599754333496</t>
   </si>
   <si>
     <t xml:space="preserve">5.03644323348999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92687034606934</t>
+    <t xml:space="preserve">4.92686986923218</t>
   </si>
   <si>
     <t xml:space="preserve">4.81338405609131</t>
@@ -425,31 +425,31 @@
     <t xml:space="preserve">4.77425050735474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82121086120605</t>
+    <t xml:space="preserve">4.82120990753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.69989776611328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69598436355591</t>
+    <t xml:space="preserve">4.69598388671875</t>
   </si>
   <si>
     <t xml:space="preserve">4.90730381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20471620559692</t>
+    <t xml:space="preserve">5.20471572875977</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43951511383057</t>
+    <t xml:space="preserve">5.43951559066772</t>
   </si>
   <si>
     <t xml:space="preserve">5.28298234939575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384927749634</t>
+    <t xml:space="preserve">5.24384880065918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36124801635742</t>
+    <t xml:space="preserve">5.3612494468689</t>
   </si>
   <si>
     <t xml:space="preserve">5.40038204193115</t>
@@ -467,25 +467,25 @@
     <t xml:space="preserve">4.93078374862671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85251712799072</t>
+    <t xml:space="preserve">4.85251665115356</t>
   </si>
   <si>
     <t xml:space="preserve">5.12644910812378</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04818344116211</t>
+    <t xml:space="preserve">5.04818248748779</t>
   </si>
   <si>
     <t xml:space="preserve">5.08731603622437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59604835510254</t>
+    <t xml:space="preserve">5.59604787826538</t>
   </si>
   <si>
     <t xml:space="preserve">5.26159715652466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42104005813599</t>
+    <t xml:space="preserve">5.42103910446167</t>
   </si>
   <si>
     <t xml:space="preserve">5.34131813049316</t>
@@ -494,25 +494,25 @@
     <t xml:space="preserve">5.22173690795898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14201593399048</t>
+    <t xml:space="preserve">5.14201545715332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1021556854248</t>
+    <t xml:space="preserve">5.10215473175049</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18187570571899</t>
+    <t xml:space="preserve">5.18187618255615</t>
   </si>
   <si>
     <t xml:space="preserve">5.38117933273315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30145740509033</t>
+    <t xml:space="preserve">5.30145788192749</t>
   </si>
   <si>
     <t xml:space="preserve">4.9028525352478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50076007843018</t>
+    <t xml:space="preserve">5.50076055526733</t>
   </si>
   <si>
     <t xml:space="preserve">5.4608998298645</t>
@@ -530,46 +530,46 @@
     <t xml:space="preserve">4.94271230697632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98257350921631</t>
+    <t xml:space="preserve">4.98257303237915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8231315612793</t>
+    <t xml:space="preserve">4.82313060760498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06229448318481</t>
+    <t xml:space="preserve">5.06229400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02243423461914</t>
+    <t xml:space="preserve">5.02243375778198</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74340963363647</t>
+    <t xml:space="preserve">4.74340867996216</t>
   </si>
   <si>
     <t xml:space="preserve">4.78327035903931</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86299133300781</t>
+    <t xml:space="preserve">4.86299180984497</t>
   </si>
   <si>
     <t xml:space="preserve">5.73992395401001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81964588165283</t>
+    <t xml:space="preserve">5.81964540481567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70006465911865</t>
+    <t xml:space="preserve">5.70006322860718</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66020345687866</t>
+    <t xml:space="preserve">5.6602029800415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77978467941284</t>
+    <t xml:space="preserve">5.77978515625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85950565338135</t>
+    <t xml:space="preserve">5.85950660705566</t>
   </si>
   <si>
-    <t xml:space="preserve">5.979088306427</t>
+    <t xml:space="preserve">5.97908782958984</t>
   </si>
   <si>
     <t xml:space="preserve">6.29797267913818</t>
@@ -581,40 +581,40 @@
     <t xml:space="preserve">6.05880928039551</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825122833252</t>
+    <t xml:space="preserve">6.21825170516968</t>
   </si>
   <si>
     <t xml:space="preserve">6.09866952896118</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38518476486206</t>
+    <t xml:space="preserve">6.38518524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25998497009277</t>
+    <t xml:space="preserve">6.25998449325562</t>
   </si>
   <si>
     <t xml:space="preserve">6.30171871185303</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17651844024658</t>
+    <t xml:space="preserve">6.17651891708374</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42691707611084</t>
+    <t xml:space="preserve">6.426917552948</t>
   </si>
   <si>
     <t xml:space="preserve">6.34345102310181</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46865081787109</t>
+    <t xml:space="preserve">6.46865129470825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96785259246826</t>
+    <t xml:space="preserve">5.9678521156311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00958585739136</t>
+    <t xml:space="preserve">6.00958490371704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13478469848633</t>
+    <t xml:space="preserve">6.13478565216064</t>
   </si>
   <si>
     <t xml:space="preserve">6.05131864547729</t>
@@ -632,25 +632,25 @@
     <t xml:space="preserve">5.84265232086182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88438558578491</t>
+    <t xml:space="preserve">5.88438653945923</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05291604995728</t>
+    <t xml:space="preserve">7.05291652679443</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09624767303467</t>
+    <t xml:space="preserve">8.09624671936035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80411577224731</t>
+    <t xml:space="preserve">7.804114818573</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63718175888062</t>
+    <t xml:space="preserve">7.6371808052063</t>
   </si>
   <si>
     <t xml:space="preserve">7.55371522903442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34504890441895</t>
+    <t xml:space="preserve">7.34504842758179</t>
   </si>
   <si>
     <t xml:space="preserve">7.17811632156372</t>
@@ -659,49 +659,49 @@
     <t xml:space="preserve">7.51198148727417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47024917602539</t>
+    <t xml:space="preserve">7.47024822235107</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30331563949585</t>
+    <t xml:space="preserve">7.30331611633301</t>
   </si>
   <si>
     <t xml:space="preserve">7.42851448059082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2615818977356</t>
+    <t xml:space="preserve">7.26158142089844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38678169250488</t>
+    <t xml:space="preserve">7.38678312301636</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96944999694824</t>
+    <t xml:space="preserve">6.9694504737854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2198486328125</t>
+    <t xml:space="preserve">7.21984910964966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544849395752</t>
+    <t xml:space="preserve">7.5954475402832</t>
   </si>
   <si>
     <t xml:space="preserve">7.76238107681274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84584712982178</t>
+    <t xml:space="preserve">7.84584760665894</t>
   </si>
   <si>
     <t xml:space="preserve">7.67891407012939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01118278503418</t>
+    <t xml:space="preserve">7.01118230819702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09464883804321</t>
+    <t xml:space="preserve">7.09464931488037</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92771673202515</t>
+    <t xml:space="preserve">6.92771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76078414916992</t>
+    <t xml:space="preserve">6.76078367233276</t>
   </si>
   <si>
     <t xml:space="preserve">6.80251598358154</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">6.71905040740967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8442497253418</t>
+    <t xml:space="preserve">6.84424924850464</t>
   </si>
   <si>
     <t xml:space="preserve">6.59385061264038</t>
@@ -722,28 +722,28 @@
     <t xml:space="preserve">6.55211734771729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75918531417847</t>
+    <t xml:space="preserve">5.75918626785278</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71745300292969</t>
+    <t xml:space="preserve">5.71745252609253</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80091905593872</t>
+    <t xml:space="preserve">5.80091953277588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67571973800659</t>
+    <t xml:space="preserve">5.67571926116943</t>
   </si>
   <si>
     <t xml:space="preserve">5.59225273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63398694992065</t>
+    <t xml:space="preserve">5.6339864730835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46705341339111</t>
+    <t xml:space="preserve">5.46705293655396</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5505199432373</t>
+    <t xml:space="preserve">5.55051946640015</t>
   </si>
   <si>
     <t xml:space="preserve">5.17492055892944</t>
@@ -752,13 +752,13 @@
     <t xml:space="preserve">5.25838756561279</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38358736038208</t>
+    <t xml:space="preserve">5.38358640670776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13638305664062</t>
+    <t xml:space="preserve">7.13638353347778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4724702835083</t>
+    <t xml:space="preserve">7.47247123718262</t>
   </si>
   <si>
     <t xml:space="preserve">7.25269222259521</t>
@@ -767,25 +767,25 @@
     <t xml:space="preserve">7.2966480255127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20873594284058</t>
+    <t xml:space="preserve">7.20873641967773</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16478061676025</t>
+    <t xml:space="preserve">7.16478109359741</t>
   </si>
   <si>
     <t xml:space="preserve">7.07686948776245</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98895835876465</t>
+    <t xml:space="preserve">6.98895740509033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03291368484497</t>
+    <t xml:space="preserve">7.03291416168213</t>
   </si>
   <si>
     <t xml:space="preserve">6.94500255584717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85709095001221</t>
+    <t xml:space="preserve">6.85709047317505</t>
   </si>
   <si>
     <t xml:space="preserve">6.72522401809692</t>
@@ -794,88 +794,88 @@
     <t xml:space="preserve">6.81313514709473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76917934417725</t>
+    <t xml:space="preserve">6.7691798210144</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90104627609253</t>
+    <t xml:space="preserve">6.90104675292969</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63731241226196</t>
+    <t xml:space="preserve">6.63731288909912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12082576751709</t>
+    <t xml:space="preserve">7.12082481384277</t>
   </si>
   <si>
     <t xml:space="preserve">7.34060430526733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5164270401001</t>
+    <t xml:space="preserve">7.51642656326294</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56038284301758</t>
+    <t xml:space="preserve">7.56038236618042</t>
   </si>
   <si>
     <t xml:space="preserve">7.42851543426514</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73620557785034</t>
+    <t xml:space="preserve">7.73620510101318</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6922492980957</t>
+    <t xml:space="preserve">7.69224977493286</t>
   </si>
   <si>
     <t xml:space="preserve">7.64829349517822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78247404098511</t>
+    <t xml:space="preserve">7.78247356414795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8272008895874</t>
+    <t xml:space="preserve">7.82720136642456</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73774671554565</t>
+    <t xml:space="preserve">7.73774719238281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69302082061768</t>
+    <t xml:space="preserve">7.69302034378052</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829397201538</t>
+    <t xml:space="preserve">7.64829444885254</t>
   </si>
   <si>
     <t xml:space="preserve">7.60356616973877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91665410995483</t>
+    <t xml:space="preserve">7.91665554046631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87192821502686</t>
+    <t xml:space="preserve">7.8719277381897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96138095855713</t>
+    <t xml:space="preserve">7.96138048171997</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2297420501709</t>
+    <t xml:space="preserve">8.22974109649658</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76646614074707</t>
+    <t xml:space="preserve">8.76646518707275</t>
   </si>
   <si>
     <t xml:space="preserve">8.58755779266357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36392402648926</t>
+    <t xml:space="preserve">8.36392307281494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63228511810303</t>
+    <t xml:space="preserve">8.63228416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54283046722412</t>
+    <t xml:space="preserve">8.54283142089844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40864944458008</t>
+    <t xml:space="preserve">8.40865039825439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27446937561035</t>
+    <t xml:space="preserve">8.27447032928467</t>
   </si>
   <si>
     <t xml:space="preserve">8.45337677001953</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">8.67701148986816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49810409545898</t>
+    <t xml:space="preserve">8.49810314178467</t>
   </si>
   <si>
     <t xml:space="preserve">8.81119251251221</t>
@@ -893,49 +893,49 @@
     <t xml:space="preserve">8.7217378616333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85591888427734</t>
+    <t xml:space="preserve">8.85591793060303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03482627868652</t>
+    <t xml:space="preserve">9.03482723236084</t>
   </si>
   <si>
     <t xml:space="preserve">10.3766326904297</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4500780105591</t>
+    <t xml:space="preserve">11.4500770568848</t>
   </si>
   <si>
     <t xml:space="preserve">10.734447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0922622680664</t>
+    <t xml:space="preserve">11.0922613143921</t>
   </si>
   <si>
     <t xml:space="preserve">10.9133548736572</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1817150115967</t>
+    <t xml:space="preserve">11.181715965271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3606224060059</t>
+    <t xml:space="preserve">11.3606233596802</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6289844512939</t>
+    <t xml:space="preserve">11.6289854049683</t>
   </si>
   <si>
     <t xml:space="preserve">11.5395307540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2711696624756</t>
+    <t xml:space="preserve">11.2711706161499</t>
   </si>
   <si>
     <t xml:space="preserve">10.5555391311646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2871789932251</t>
+    <t xml:space="preserve">10.2871780395508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0028076171875</t>
+    <t xml:space="preserve">11.0028095245361</t>
   </si>
   <si>
     <t xml:space="preserve">10.6449928283691</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">10.1082715988159</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1977243423462</t>
+    <t xml:space="preserve">10.1977252960205</t>
   </si>
   <si>
     <t xml:space="preserve">9.75045585632324</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">12.6129751205444</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9707908630371</t>
+    <t xml:space="preserve">12.9707899093628</t>
   </si>
   <si>
     <t xml:space="preserve">14.0442342758179</t>
@@ -977,13 +977,13 @@
     <t xml:space="preserve">13.0602445602417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4180593490601</t>
+    <t xml:space="preserve">13.4180583953857</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8813362121582</t>
+    <t xml:space="preserve">12.8813352584839</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7918834686279</t>
+    <t xml:space="preserve">12.7918825149536</t>
   </si>
   <si>
     <t xml:space="preserve">12.702428817749</t>
@@ -992,16 +992,16 @@
     <t xml:space="preserve">13.149697303772</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3286037445068</t>
+    <t xml:space="preserve">13.3286056518555</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547815322876</t>
+    <t xml:space="preserve">13.9547805786133</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5969657897949</t>
+    <t xml:space="preserve">13.5969667434692</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6864204406738</t>
+    <t xml:space="preserve">13.6864194869995</t>
   </si>
   <si>
     <t xml:space="preserve">13.865327835083</t>
@@ -1010,25 +1010,25 @@
     <t xml:space="preserve">14.4020500183105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2965879440308</t>
+    <t xml:space="preserve">15.2965888977051</t>
   </si>
   <si>
     <t xml:space="preserve">15.2071323394775</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5809564590454</t>
+    <t xml:space="preserve">14.5809555053711</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7598648071289</t>
+    <t xml:space="preserve">14.7598657608032</t>
   </si>
   <si>
     <t xml:space="preserve">14.4915046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5400876998901</t>
+    <t xml:space="preserve">14.5400886535645</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3560361862183</t>
+    <t xml:space="preserve">14.3560371398926</t>
   </si>
   <si>
     <t xml:space="preserve">14.2640104293823</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">14.8161659240723</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6321144104004</t>
+    <t xml:space="preserve">14.6321134567261</t>
   </si>
   <si>
     <t xml:space="preserve">15.3683223724365</t>
@@ -1052,10 +1052,10 @@
     <t xml:space="preserve">16.104528427124</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3806056976318</t>
+    <t xml:space="preserve">16.3806037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9204750061035</t>
+    <t xml:space="preserve">15.9204769134521</t>
   </si>
   <si>
     <t xml:space="preserve">17.2088394165039</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">17.4849166870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.576940536499</t>
+    <t xml:space="preserve">17.5769424438477</t>
   </si>
   <si>
     <t xml:space="preserve">17.6689682006836</t>
@@ -1076,31 +1076,31 @@
     <t xml:space="preserve">18.4051742553711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1413803100586</t>
+    <t xml:space="preserve">19.1413822174072</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6935367584229</t>
+    <t xml:space="preserve">19.6935386657715</t>
   </si>
   <si>
     <t xml:space="preserve">20.0616397857666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5340557098389</t>
+    <t xml:space="preserve">21.5340538024902</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3745708465576</t>
+    <t xml:space="preserve">23.3745727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2702617645264</t>
+    <t xml:space="preserve">22.270263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">22.822416305542</t>
+    <t xml:space="preserve">22.8224182128906</t>
   </si>
   <si>
     <t xml:space="preserve">20.6137962341309</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3254337310791</t>
+    <t xml:space="preserve">19.3254356384277</t>
   </si>
   <si>
     <t xml:space="preserve">21.902156829834</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">22.0862102508545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0064678192139</t>
+    <t xml:space="preserve">23.0064697265625</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5586261749268</t>
+    <t xml:space="preserve">23.5586242675781</t>
   </si>
   <si>
     <t xml:space="preserve">23.74267578125</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">24.6629333496094</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8469886779785</t>
+    <t xml:space="preserve">24.8469867706299</t>
   </si>
   <si>
     <t xml:space="preserve">24.2948303222656</t>
@@ -1139,25 +1139,25 @@
     <t xml:space="preserve">25.2150897979736</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4543132781982</t>
+    <t xml:space="preserve">22.4543151855469</t>
   </si>
   <si>
     <t xml:space="preserve">24.4788837432861</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9512958526611</t>
+    <t xml:space="preserve">25.9512977600098</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5034523010254</t>
+    <t xml:space="preserve">26.5034503936768</t>
   </si>
   <si>
     <t xml:space="preserve">27.975866317749</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9206943511963</t>
+    <t xml:space="preserve">30.9206924438477</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0801753997803</t>
+    <t xml:space="preserve">29.0801773071289</t>
   </si>
   <si>
     <t xml:space="preserve">30.736644744873</t>
@@ -1166,31 +1166,31 @@
     <t xml:space="preserve">30.3685398101807</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2642288208008</t>
+    <t xml:space="preserve">29.2642269134521</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4728507995605</t>
+    <t xml:space="preserve">31.4728527069092</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2336273193359</t>
+    <t xml:space="preserve">34.2336235046387</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7857780456543</t>
+    <t xml:space="preserve">34.7857818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8655204772949</t>
+    <t xml:space="preserve">33.8655166625977</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4974212646484</t>
+    <t xml:space="preserve">33.4974174499512</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1844863891602</t>
+    <t xml:space="preserve">30.1844844818115</t>
   </si>
   <si>
     <t xml:space="preserve">27.4237098693848</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6875038146973</t>
+    <t xml:space="preserve">26.6875019073486</t>
   </si>
   <si>
     <t xml:space="preserve">25.5831928253174</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">26.3194007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7918167114258</t>
+    <t xml:space="preserve">27.7918148040771</t>
   </si>
   <si>
     <t xml:space="preserve">28.8961238861084</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">28.5280208587646</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7120723724365</t>
+    <t xml:space="preserve">28.7120742797852</t>
   </si>
   <si>
     <t xml:space="preserve">28.3439693450928</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">27.055606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8715572357178</t>
+    <t xml:space="preserve">26.8715553283691</t>
   </si>
   <si>
     <t xml:space="preserve">25.3991413116455</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">27.6077632904053</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5525913238525</t>
+    <t xml:space="preserve">30.5525894165039</t>
   </si>
   <si>
     <t xml:space="preserve">29.6323318481445</t>
@@ -1250,10 +1250,10 @@
     <t xml:space="preserve">32.209056854248</t>
   </si>
   <si>
-    <t xml:space="preserve">31.28879737854</t>
+    <t xml:space="preserve">31.2887954711914</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6569023132324</t>
+    <t xml:space="preserve">31.6569004058838</t>
   </si>
   <si>
     <t xml:space="preserve">32.0250015258789</t>
@@ -1266,9 +1266,6 @@
   </si>
   <si>
     <t xml:space="preserve">33.1643714904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6569004058838</t>
   </si>
   <si>
     <t xml:space="preserve">32.4106369018555</t>
@@ -44671,7 +44668,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1640" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44723,7 +44720,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1642" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44749,7 +44746,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1643" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44931,7 +44928,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1650" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44957,7 +44954,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1651" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44983,7 +44980,7 @@
         <v>35</v>
       </c>
       <c r="G1652" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45009,7 +45006,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1653" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45035,7 +45032,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1654" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45061,7 +45058,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1655" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45087,7 +45084,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1656" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45113,7 +45110,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1657" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45139,7 +45136,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1658" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45165,7 +45162,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1659" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45191,7 +45188,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1660" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45217,7 +45214,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1661" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45243,7 +45240,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1662" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45269,7 +45266,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1663" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45295,7 +45292,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1664" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45321,7 +45318,7 @@
         <v>32</v>
       </c>
       <c r="G1665" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45347,7 +45344,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1666" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45373,7 +45370,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1667" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45399,7 +45396,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1668" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45425,7 +45422,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1669" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45451,7 +45448,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1670" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45477,7 +45474,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1671" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45503,7 +45500,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1672" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45529,7 +45526,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1673" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45555,7 +45552,7 @@
         <v>32</v>
       </c>
       <c r="G1674" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45581,7 +45578,7 @@
         <v>32</v>
       </c>
       <c r="G1675" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45607,7 +45604,7 @@
         <v>32</v>
       </c>
       <c r="G1676" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45633,7 +45630,7 @@
         <v>32</v>
       </c>
       <c r="G1677" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45659,7 +45656,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1678" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45685,7 +45682,7 @@
         <v>33</v>
       </c>
       <c r="G1679" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45711,7 +45708,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1680" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45737,7 +45734,7 @@
         <v>33</v>
       </c>
       <c r="G1681" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45763,7 +45760,7 @@
         <v>32</v>
       </c>
       <c r="G1682" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45789,7 +45786,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1683" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45815,7 +45812,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1684" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45841,7 +45838,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1685" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45867,7 +45864,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1686" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45893,7 +45890,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1687" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45919,7 +45916,7 @@
         <v>33</v>
       </c>
       <c r="G1688" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45945,7 +45942,7 @@
         <v>33</v>
       </c>
       <c r="G1689" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45971,7 +45968,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1690" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45997,7 +45994,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1691" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46023,7 +46020,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1692" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46127,7 +46124,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1696" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46153,7 +46150,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1697" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46179,7 +46176,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1698" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46205,7 +46202,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1699" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46231,7 +46228,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1700" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46257,7 +46254,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1701" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46283,7 +46280,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1702" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46309,7 +46306,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1703" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46335,7 +46332,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1704" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46387,7 +46384,7 @@
         <v>33</v>
       </c>
       <c r="G1706" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46413,7 +46410,7 @@
         <v>33</v>
       </c>
       <c r="G1707" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46439,7 +46436,7 @@
         <v>33</v>
       </c>
       <c r="G1708" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46465,7 +46462,7 @@
         <v>33</v>
       </c>
       <c r="G1709" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46491,7 +46488,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1710" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46517,7 +46514,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1711" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46543,7 +46540,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1712" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46569,7 +46566,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1713" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46595,7 +46592,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1714" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46621,7 +46618,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1715" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46647,7 +46644,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1716" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46673,7 +46670,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1717" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46699,7 +46696,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1718" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46725,7 +46722,7 @@
         <v>32</v>
       </c>
       <c r="G1719" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46751,7 +46748,7 @@
         <v>32</v>
       </c>
       <c r="G1720" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46777,7 +46774,7 @@
         <v>32</v>
       </c>
       <c r="G1721" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46803,7 +46800,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1722" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46829,7 +46826,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1723" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46855,7 +46852,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1724" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46881,7 +46878,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1725" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46907,7 +46904,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1726" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46933,7 +46930,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1727" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46959,7 +46956,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1728" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46985,7 +46982,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1729" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47011,7 +47008,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1730" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47037,7 +47034,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1731" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47063,7 +47060,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1732" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47089,7 +47086,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1733" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47115,7 +47112,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1734" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47141,7 +47138,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1735" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47167,7 +47164,7 @@
         <v>30</v>
       </c>
       <c r="G1736" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47193,7 +47190,7 @@
         <v>30</v>
       </c>
       <c r="G1737" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47219,7 +47216,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1738" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47245,7 +47242,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1739" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47271,7 +47268,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1740" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47297,7 +47294,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1741" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47323,7 +47320,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1742" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47349,7 +47346,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1743" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47375,7 +47372,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1744" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47401,7 +47398,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1745" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47427,7 +47424,7 @@
         <v>26</v>
       </c>
       <c r="G1746" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47453,7 +47450,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1747" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47479,7 +47476,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1748" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47505,7 +47502,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1749" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47531,7 +47528,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1750" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47557,7 +47554,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1751" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47583,7 +47580,7 @@
         <v>27</v>
       </c>
       <c r="G1752" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47609,7 +47606,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1753" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47635,7 +47632,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1754" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47661,7 +47658,7 @@
         <v>26</v>
       </c>
       <c r="G1755" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47687,7 +47684,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1756" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47713,7 +47710,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1757" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47739,7 +47736,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1758" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47765,7 +47762,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1759" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47791,7 +47788,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1760" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47817,7 +47814,7 @@
         <v>24</v>
       </c>
       <c r="G1761" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47843,7 +47840,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1762" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47869,7 +47866,7 @@
         <v>23</v>
       </c>
       <c r="G1763" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47895,7 +47892,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1764" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47921,7 +47918,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1765" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47947,7 +47944,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1766" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47973,7 +47970,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1767" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47999,7 +47996,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1768" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48025,7 +48022,7 @@
         <v>24</v>
       </c>
       <c r="G1769" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48051,7 +48048,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1770" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48077,7 +48074,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1771" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48103,7 +48100,7 @@
         <v>24</v>
       </c>
       <c r="G1772" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48129,7 +48126,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48155,7 +48152,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1774" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48181,7 +48178,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1775" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48207,7 +48204,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1776" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48233,7 +48230,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1777" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48259,7 +48256,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1778" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48285,7 +48282,7 @@
         <v>28</v>
       </c>
       <c r="G1779" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48311,7 +48308,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1780" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48337,7 +48334,7 @@
         <v>28</v>
       </c>
       <c r="G1781" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48363,7 +48360,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1782" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48389,7 +48386,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1783" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48415,7 +48412,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1784" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48441,7 +48438,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1785" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48467,7 +48464,7 @@
         <v>28</v>
       </c>
       <c r="G1786" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48493,7 +48490,7 @@
         <v>28</v>
       </c>
       <c r="G1787" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48519,7 +48516,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1788" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48545,7 +48542,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1789" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48571,7 +48568,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1790" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -48597,7 +48594,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1791" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48623,7 +48620,7 @@
         <v>28</v>
       </c>
       <c r="G1792" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48649,7 +48646,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1793" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48675,7 +48672,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1794" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -48701,7 +48698,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1795" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48727,7 +48724,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1796" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48753,7 +48750,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1797" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48779,7 +48776,7 @@
         <v>29</v>
       </c>
       <c r="G1798" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48805,7 +48802,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1799" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48831,7 +48828,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1800" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48857,7 +48854,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1801" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48883,7 +48880,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1802" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48909,7 +48906,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1803" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48935,7 +48932,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1804" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48961,7 +48958,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1805" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48987,7 +48984,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1806" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49013,7 +49010,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1807" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49039,7 +49036,7 @@
         <v>28</v>
       </c>
       <c r="G1808" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49065,7 +49062,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1809" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49091,7 +49088,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1810" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49117,7 +49114,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1811" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49143,7 +49140,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1812" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49169,7 +49166,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1813" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49195,7 +49192,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1814" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49221,7 +49218,7 @@
         <v>27</v>
       </c>
       <c r="G1815" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49247,7 +49244,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1816" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49273,7 +49270,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1817" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49299,7 +49296,7 @@
         <v>26</v>
       </c>
       <c r="G1818" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49325,7 +49322,7 @@
         <v>26</v>
       </c>
       <c r="G1819" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49351,7 +49348,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1820" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49377,7 +49374,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1821" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49403,7 +49400,7 @@
         <v>26</v>
       </c>
       <c r="G1822" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49429,7 +49426,7 @@
         <v>26</v>
       </c>
       <c r="G1823" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49455,7 +49452,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49481,7 +49478,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1825" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49507,7 +49504,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1826" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49533,7 +49530,7 @@
         <v>29</v>
       </c>
       <c r="G1827" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49559,7 +49556,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1828" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49585,7 +49582,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1829" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49611,7 +49608,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49637,7 +49634,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1831" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49663,7 +49660,7 @@
         <v>29</v>
       </c>
       <c r="G1832" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49689,7 +49686,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1833" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49715,7 +49712,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1834" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49741,7 +49738,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1835" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49767,7 +49764,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1836" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49793,7 +49790,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1837" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49819,7 +49816,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1838" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49845,7 +49842,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1839" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49871,7 +49868,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1840" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49897,7 +49894,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1841" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49923,7 +49920,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1842" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49949,7 +49946,7 @@
         <v>30</v>
       </c>
       <c r="G1843" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49975,7 +49972,7 @@
         <v>30</v>
       </c>
       <c r="G1844" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50001,7 +49998,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1845" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50027,7 +50024,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1846" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50053,7 +50050,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1847" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50079,7 +50076,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1848" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50105,7 +50102,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1849" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50131,7 +50128,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1850" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50157,7 +50154,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1851" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50183,7 +50180,7 @@
         <v>29</v>
       </c>
       <c r="G1852" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50209,7 +50206,7 @@
         <v>29</v>
       </c>
       <c r="G1853" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50235,7 +50232,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1854" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50261,7 +50258,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1855" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50287,7 +50284,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1856" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50313,7 +50310,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1857" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50339,7 +50336,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1858" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50365,7 +50362,7 @@
         <v>29</v>
       </c>
       <c r="G1859" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50391,7 +50388,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50417,7 +50414,7 @@
         <v>30</v>
       </c>
       <c r="G1861" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50443,7 +50440,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1862" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50469,7 +50466,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1863" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50495,7 +50492,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1864" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50521,7 +50518,7 @@
         <v>27</v>
       </c>
       <c r="G1865" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50547,7 +50544,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1866" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50573,7 +50570,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1867" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50599,7 +50596,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1868" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50625,7 +50622,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1869" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50651,7 +50648,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1870" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50677,7 +50674,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1871" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50703,7 +50700,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1872" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50729,7 +50726,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1873" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50755,7 +50752,7 @@
         <v>27</v>
       </c>
       <c r="G1874" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50781,7 +50778,7 @@
         <v>27</v>
       </c>
       <c r="G1875" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50807,7 +50804,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1876" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50833,7 +50830,7 @@
         <v>27</v>
       </c>
       <c r="G1877" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50859,7 +50856,7 @@
         <v>27</v>
       </c>
       <c r="G1878" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50885,7 +50882,7 @@
         <v>27</v>
       </c>
       <c r="G1879" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50911,7 +50908,7 @@
         <v>27</v>
       </c>
       <c r="G1880" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50937,7 +50934,7 @@
         <v>28</v>
       </c>
       <c r="G1881" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50963,7 +50960,7 @@
         <v>28</v>
       </c>
       <c r="G1882" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50989,7 +50986,7 @@
         <v>28</v>
       </c>
       <c r="G1883" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51015,7 +51012,7 @@
         <v>28</v>
       </c>
       <c r="G1884" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51041,7 +51038,7 @@
         <v>28</v>
       </c>
       <c r="G1885" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51067,7 +51064,7 @@
         <v>28</v>
       </c>
       <c r="G1886" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51093,7 +51090,7 @@
         <v>27</v>
       </c>
       <c r="G1887" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51119,7 +51116,7 @@
         <v>27</v>
       </c>
       <c r="G1888" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51145,7 +51142,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1889" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51171,7 +51168,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1890" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51197,7 +51194,7 @@
         <v>28</v>
       </c>
       <c r="G1891" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51223,7 +51220,7 @@
         <v>28</v>
       </c>
       <c r="G1892" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51249,7 +51246,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1893" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51275,7 +51272,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1894" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51301,7 +51298,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1895" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51327,7 +51324,7 @@
         <v>28</v>
       </c>
       <c r="G1896" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51353,7 +51350,7 @@
         <v>28</v>
       </c>
       <c r="G1897" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51379,7 +51376,7 @@
         <v>28</v>
       </c>
       <c r="G1898" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51405,7 +51402,7 @@
         <v>28</v>
       </c>
       <c r="G1899" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51431,7 +51428,7 @@
         <v>28</v>
       </c>
       <c r="G1900" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51457,7 +51454,7 @@
         <v>28</v>
       </c>
       <c r="G1901" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51483,7 +51480,7 @@
         <v>28</v>
       </c>
       <c r="G1902" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51509,7 +51506,7 @@
         <v>28</v>
       </c>
       <c r="G1903" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51535,7 +51532,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51561,7 +51558,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51587,7 +51584,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51613,7 +51610,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51639,7 +51636,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1908" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51665,7 +51662,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1909" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51691,7 +51688,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1910" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51717,7 +51714,7 @@
         <v>29</v>
       </c>
       <c r="G1911" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51743,7 +51740,7 @@
         <v>29</v>
       </c>
       <c r="G1912" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51769,7 +51766,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1913" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51795,7 +51792,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1914" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51821,7 +51818,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51847,7 +51844,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1916" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51873,7 +51870,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1917" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51899,7 +51896,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1918" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51925,7 +51922,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1919" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51951,7 +51948,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1920" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51977,7 +51974,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1921" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52003,7 +52000,7 @@
         <v>27</v>
       </c>
       <c r="G1922" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52029,7 +52026,7 @@
         <v>27</v>
       </c>
       <c r="G1923" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52055,7 +52052,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1924" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52081,7 +52078,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1925" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52107,7 +52104,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1926" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52133,7 +52130,7 @@
         <v>28</v>
       </c>
       <c r="G1927" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52159,7 +52156,7 @@
         <v>28</v>
       </c>
       <c r="G1928" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52185,7 +52182,7 @@
         <v>28</v>
       </c>
       <c r="G1929" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52211,7 +52208,7 @@
         <v>28</v>
       </c>
       <c r="G1930" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52237,7 +52234,7 @@
         <v>28</v>
       </c>
       <c r="G1931" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52263,7 +52260,7 @@
         <v>28</v>
       </c>
       <c r="G1932" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52289,7 +52286,7 @@
         <v>28</v>
       </c>
       <c r="G1933" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52315,7 +52312,7 @@
         <v>28</v>
       </c>
       <c r="G1934" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52341,7 +52338,7 @@
         <v>28</v>
       </c>
       <c r="G1935" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52367,7 +52364,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1936" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52393,7 +52390,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1937" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52419,7 +52416,7 @@
         <v>28</v>
       </c>
       <c r="G1938" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52445,7 +52442,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1939" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52471,7 +52468,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1940" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52497,7 +52494,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1941" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52523,7 +52520,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1942" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52549,7 +52546,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1943" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52575,7 +52572,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1944" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52601,7 +52598,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1945" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52627,7 +52624,7 @@
         <v>28</v>
       </c>
       <c r="G1946" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52653,7 +52650,7 @@
         <v>28</v>
       </c>
       <c r="G1947" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52679,7 +52676,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1948" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52705,7 +52702,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1949" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52731,7 +52728,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1950" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52757,7 +52754,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1951" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52783,7 +52780,7 @@
         <v>28</v>
       </c>
       <c r="G1952" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52809,7 +52806,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1953" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52835,7 +52832,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1954" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52861,7 +52858,7 @@
         <v>27</v>
       </c>
       <c r="G1955" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52887,7 +52884,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1956" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52913,7 +52910,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1957" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -52939,7 +52936,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1958" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -52965,7 +52962,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1959" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -52991,7 +52988,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1960" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53017,7 +53014,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1961" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53043,7 +53040,7 @@
         <v>28</v>
       </c>
       <c r="G1962" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53069,7 +53066,7 @@
         <v>28</v>
       </c>
       <c r="G1963" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53095,7 +53092,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1964" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53121,7 +53118,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1965" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53147,7 +53144,7 @@
         <v>27</v>
       </c>
       <c r="G1966" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53173,7 +53170,7 @@
         <v>27</v>
       </c>
       <c r="G1967" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53199,7 +53196,7 @@
         <v>27</v>
       </c>
       <c r="G1968" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53225,7 +53222,7 @@
         <v>27</v>
       </c>
       <c r="G1969" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53251,7 +53248,7 @@
         <v>27</v>
       </c>
       <c r="G1970" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53277,7 +53274,7 @@
         <v>27</v>
       </c>
       <c r="G1971" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53303,7 +53300,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1972" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53329,7 +53326,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1973" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53355,7 +53352,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1974" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53381,7 +53378,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1975" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53407,7 +53404,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1976" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53433,7 +53430,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1977" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53459,7 +53456,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1978" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53485,7 +53482,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1979" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53511,7 +53508,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1980" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53537,7 +53534,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1981" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53563,7 +53560,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1982" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53589,7 +53586,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1983" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53615,7 +53612,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1984" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53641,7 +53638,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1985" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53667,7 +53664,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1986" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53693,7 +53690,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1987" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53719,7 +53716,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1988" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53745,7 +53742,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1989" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53771,7 +53768,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1990" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53797,7 +53794,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1991" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53823,7 +53820,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1992" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53849,7 +53846,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1993" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53875,7 +53872,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1994" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53901,7 +53898,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1995" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -53927,7 +53924,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1996" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -53953,7 +53950,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1997" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -53979,7 +53976,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1998" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54005,7 +54002,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1999" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54031,7 +54028,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2000" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54057,7 +54054,7 @@
         <v>25</v>
       </c>
       <c r="G2001" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54083,7 +54080,7 @@
         <v>25</v>
       </c>
       <c r="G2002" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54109,7 +54106,7 @@
         <v>25</v>
       </c>
       <c r="G2003" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54135,7 +54132,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2004" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54161,7 +54158,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2005" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54187,7 +54184,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G2006" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54213,7 +54210,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G2007" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54239,7 +54236,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G2008" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54265,7 +54262,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G2009" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54291,7 +54288,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G2010" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54317,7 +54314,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G2011" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54343,7 +54340,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G2012" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54369,7 +54366,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G2013" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54395,7 +54392,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2014" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54421,7 +54418,7 @@
         <v>24</v>
       </c>
       <c r="G2015" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54447,7 +54444,7 @@
         <v>24</v>
       </c>
       <c r="G2016" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54473,7 +54470,7 @@
         <v>24</v>
       </c>
       <c r="G2017" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54499,7 +54496,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G2018" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54525,7 +54522,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G2019" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54551,7 +54548,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2020" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54577,7 +54574,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G2021" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54603,7 +54600,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G2022" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54629,7 +54626,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G2023" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54655,7 +54652,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G2024" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54681,7 +54678,7 @@
         <v>24</v>
       </c>
       <c r="G2025" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54707,7 +54704,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G2026" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54733,7 +54730,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2027" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54759,7 +54756,7 @@
         <v>23</v>
       </c>
       <c r="G2028" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54785,7 +54782,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2029" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54811,7 +54808,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2030" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54837,7 +54834,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2031" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54863,7 +54860,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2032" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54889,7 +54886,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2033" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54915,7 +54912,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2034" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -54941,7 +54938,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2035" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -54967,7 +54964,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2036" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -54993,7 +54990,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2037" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55019,7 +55016,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2038" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55045,7 +55042,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2039" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55071,7 +55068,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2040" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55097,7 +55094,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2041" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55123,7 +55120,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G2042" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55149,7 +55146,7 @@
         <v>22</v>
       </c>
       <c r="G2043" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55175,7 +55172,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2044" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55201,7 +55198,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G2045" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55227,7 +55224,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2046" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55253,7 +55250,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2047" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55279,7 +55276,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2048" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55305,7 +55302,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2049" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55331,7 +55328,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2050" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55357,7 +55354,7 @@
         <v>24</v>
       </c>
       <c r="G2051" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55383,7 +55380,7 @@
         <v>24</v>
       </c>
       <c r="G2052" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55409,7 +55406,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G2053" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55435,7 +55432,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G2054" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55461,7 +55458,7 @@
         <v>24</v>
       </c>
       <c r="G2055" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55487,7 +55484,7 @@
         <v>24</v>
       </c>
       <c r="G2056" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55513,7 +55510,7 @@
         <v>24</v>
       </c>
       <c r="G2057" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55539,7 +55536,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2058" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55565,7 +55562,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2059" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55591,7 +55588,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2060" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55617,7 +55614,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2061" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55643,7 +55640,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2062" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55669,7 +55666,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2063" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55695,7 +55692,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2064" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55721,7 +55718,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2065" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55747,7 +55744,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2066" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55773,7 +55770,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2067" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55799,7 +55796,7 @@
         <v>25</v>
       </c>
       <c r="G2068" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55825,7 +55822,7 @@
         <v>25</v>
       </c>
       <c r="G2069" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55851,7 +55848,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2070" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55877,7 +55874,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2071" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55903,7 +55900,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2072" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -55929,7 +55926,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G2073" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -55955,7 +55952,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G2074" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -55981,7 +55978,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2075" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56007,7 +56004,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2076" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56033,7 +56030,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2077" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56059,7 +56056,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2078" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56085,7 +56082,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2079" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56111,7 +56108,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2080" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56137,7 +56134,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2081" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56163,7 +56160,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2082" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56189,7 +56186,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2083" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56215,7 +56212,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2084" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56241,7 +56238,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2085" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56267,7 +56264,7 @@
         <v>25</v>
       </c>
       <c r="G2086" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56293,7 +56290,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2087" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56319,7 +56316,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2088" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56345,7 +56342,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2089" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56371,7 +56368,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2090" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56397,7 +56394,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2091" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56423,7 +56420,7 @@
         <v>25</v>
       </c>
       <c r="G2092" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56449,7 +56446,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2093" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56475,7 +56472,7 @@
         <v>25</v>
       </c>
       <c r="G2094" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56501,7 +56498,7 @@
         <v>25</v>
       </c>
       <c r="G2095" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56527,7 +56524,7 @@
         <v>25</v>
       </c>
       <c r="G2096" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56553,7 +56550,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2097" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56579,7 +56576,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2098" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56605,7 +56602,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2099" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56631,7 +56628,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2100" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56657,7 +56654,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G2101" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56683,7 +56680,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G2102" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56709,7 +56706,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G2103" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56735,7 +56732,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G2104" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56761,7 +56758,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G2105" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56787,7 +56784,7 @@
         <v>32</v>
       </c>
       <c r="G2106" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56813,7 +56810,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G2107" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56839,7 +56836,7 @@
         <v>32</v>
       </c>
       <c r="G2108" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56865,7 +56862,7 @@
         <v>31</v>
       </c>
       <c r="G2109" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56891,7 +56888,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G2110" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56917,7 +56914,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G2111" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -56943,7 +56940,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G2112" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -56969,7 +56966,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G2113" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -56995,7 +56992,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G2114" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57021,7 +57018,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G2115" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57047,7 +57044,7 @@
         <v>31</v>
       </c>
       <c r="G2116" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57073,7 +57070,7 @@
         <v>31</v>
       </c>
       <c r="G2117" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57099,7 +57096,7 @@
         <v>31</v>
       </c>
       <c r="G2118" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57125,7 +57122,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G2119" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57151,7 +57148,7 @@
         <v>30</v>
       </c>
       <c r="G2120" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57177,7 +57174,7 @@
         <v>30</v>
       </c>
       <c r="G2121" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57203,7 +57200,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2122" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57229,7 +57226,7 @@
         <v>29</v>
       </c>
       <c r="G2123" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57255,7 +57252,7 @@
         <v>29</v>
       </c>
       <c r="G2124" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57281,7 +57278,7 @@
         <v>29</v>
       </c>
       <c r="G2125" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57307,7 +57304,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G2126" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57333,7 +57330,7 @@
         <v>29</v>
       </c>
       <c r="G2127" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57359,7 +57356,7 @@
         <v>29</v>
       </c>
       <c r="G2128" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57385,7 +57382,7 @@
         <v>29</v>
       </c>
       <c r="G2129" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57411,7 +57408,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2130" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57437,7 +57434,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2131" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57463,7 +57460,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2132" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57489,7 +57486,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G2133" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57515,7 +57512,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G2134" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57541,7 +57538,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G2135" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57567,7 +57564,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G2136" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57593,7 +57590,7 @@
         <v>31</v>
       </c>
       <c r="G2137" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57619,7 +57616,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G2138" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57645,7 +57642,7 @@
         <v>30</v>
       </c>
       <c r="G2139" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57671,7 +57668,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G2140" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57697,7 +57694,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G2141" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57723,7 +57720,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G2142" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57749,7 +57746,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G2143" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57775,7 +57772,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G2144" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57801,7 +57798,7 @@
         <v>31</v>
       </c>
       <c r="G2145" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57827,7 +57824,7 @@
         <v>31</v>
       </c>
       <c r="G2146" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57853,7 +57850,7 @@
         <v>31</v>
       </c>
       <c r="G2147" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57879,7 +57876,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G2148" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57905,7 +57902,7 @@
         <v>32</v>
       </c>
       <c r="G2149" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -57931,7 +57928,7 @@
         <v>32</v>
       </c>
       <c r="G2150" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -57957,7 +57954,7 @@
         <v>32</v>
       </c>
       <c r="G2151" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -57983,7 +57980,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G2152" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58009,7 +58006,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G2153" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58035,7 +58032,7 @@
         <v>34</v>
       </c>
       <c r="G2154" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58061,7 +58058,7 @@
         <v>34</v>
       </c>
       <c r="G2155" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58087,7 +58084,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G2156" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -58113,7 +58110,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G2157" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -58139,7 +58136,7 @@
         <v>39</v>
       </c>
       <c r="G2158" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58165,7 +58162,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2159" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58191,7 +58188,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2160" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58217,7 +58214,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2161" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58243,7 +58240,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2162" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58269,7 +58266,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2163" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58295,7 +58292,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2164" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -58321,7 +58318,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2165" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58347,7 +58344,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2166" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58373,7 +58370,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G2167" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58399,7 +58396,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G2168" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58425,7 +58422,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2169" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58451,7 +58448,7 @@
         <v>40</v>
       </c>
       <c r="G2170" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58477,7 +58474,7 @@
         <v>40</v>
       </c>
       <c r="G2171" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58503,7 +58500,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2172" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58529,7 +58526,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2173" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58555,7 +58552,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G2174" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58581,7 +58578,7 @@
         <v>38</v>
       </c>
       <c r="G2175" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58607,7 +58604,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G2176" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58633,7 +58630,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G2177" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58659,7 +58656,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G2178" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58685,7 +58682,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G2179" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58711,7 +58708,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G2180" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58737,7 +58734,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G2181" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58763,7 +58760,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2182" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58789,7 +58786,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2183" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58815,7 +58812,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2184" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58841,7 +58838,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2185" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58867,7 +58864,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2186" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58893,7 +58890,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2187" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58919,7 +58916,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2188" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -58945,7 +58942,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2189" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -58971,7 +58968,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2190" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -58997,7 +58994,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2191" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59023,7 +59020,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2192" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59049,7 +59046,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2193" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59075,7 +59072,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2194" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59101,7 +59098,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G2195" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -59127,7 +59124,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G2196" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59153,7 +59150,7 @@
         <v>40</v>
       </c>
       <c r="G2197" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59179,7 +59176,7 @@
         <v>40</v>
       </c>
       <c r="G2198" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59205,7 +59202,7 @@
         <v>40</v>
       </c>
       <c r="G2199" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59231,7 +59228,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G2200" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59257,7 +59254,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G2201" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59283,7 +59280,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G2202" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59309,7 +59306,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G2203" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59335,7 +59332,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G2204" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59361,7 +59358,7 @@
         <v>44</v>
       </c>
       <c r="G2205" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59387,7 +59384,7 @@
         <v>44</v>
       </c>
       <c r="G2206" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59413,7 +59410,7 @@
         <v>44</v>
       </c>
       <c r="G2207" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59439,7 +59436,7 @@
         <v>44.5999984741211</v>
       </c>
       <c r="G2208" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59465,7 +59462,7 @@
         <v>44</v>
       </c>
       <c r="G2209" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59491,7 +59488,7 @@
         <v>44</v>
       </c>
       <c r="G2210" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59517,7 +59514,7 @@
         <v>44</v>
       </c>
       <c r="G2211" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59543,7 +59540,7 @@
         <v>44</v>
       </c>
       <c r="G2212" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59569,7 +59566,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2213" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59595,7 +59592,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2214" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59621,7 +59618,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2215" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59647,7 +59644,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2216" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59673,7 +59670,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2217" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59699,7 +59696,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2218" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59725,7 +59722,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G2219" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59751,7 +59748,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G2220" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59777,7 +59774,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G2221" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59803,7 +59800,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2222" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59829,7 +59826,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2223" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59855,7 +59852,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2224" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59881,7 +59878,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2225" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59907,7 +59904,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G2226" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -59933,7 +59930,7 @@
         <v>39</v>
       </c>
       <c r="G2227" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -59959,7 +59956,7 @@
         <v>39</v>
       </c>
       <c r="G2228" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -59985,7 +59982,7 @@
         <v>39</v>
       </c>
       <c r="G2229" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60011,7 +60008,7 @@
         <v>39</v>
       </c>
       <c r="G2230" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60037,7 +60034,7 @@
         <v>39</v>
       </c>
       <c r="G2231" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60063,7 +60060,7 @@
         <v>39</v>
       </c>
       <c r="G2232" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60089,7 +60086,7 @@
         <v>39</v>
       </c>
       <c r="G2233" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60115,7 +60112,7 @@
         <v>37</v>
       </c>
       <c r="G2234" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60141,7 +60138,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2235" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60167,7 +60164,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G2236" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60193,7 +60190,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2237" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60219,7 +60216,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2238" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60245,7 +60242,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G2239" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60271,7 +60268,7 @@
         <v>38</v>
       </c>
       <c r="G2240" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60297,7 +60294,7 @@
         <v>39</v>
       </c>
       <c r="G2241" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60323,7 +60320,7 @@
         <v>42</v>
       </c>
       <c r="G2242" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60349,7 +60346,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G2243" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60375,7 +60372,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G2244" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60401,7 +60398,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G2245" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60427,7 +60424,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G2246" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60453,7 +60450,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G2247" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60479,7 +60476,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G2248" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60505,7 +60502,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G2249" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60531,7 +60528,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G2250" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60557,7 +60554,7 @@
         <v>41</v>
       </c>
       <c r="G2251" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60583,7 +60580,7 @@
         <v>41</v>
       </c>
       <c r="G2252" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60609,7 +60606,7 @@
         <v>40</v>
       </c>
       <c r="G2253" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60635,7 +60632,7 @@
         <v>40</v>
       </c>
       <c r="G2254" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60661,7 +60658,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G2255" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60687,7 +60684,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2256" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60713,7 +60710,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2257" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60739,7 +60736,7 @@
         <v>38</v>
       </c>
       <c r="G2258" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60765,7 +60762,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G2259" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60791,7 +60788,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G2260" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60817,7 +60814,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2261" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60843,7 +60840,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2262" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60869,7 +60866,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G2263" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60895,7 +60892,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2264" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60921,7 +60918,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2265" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -60947,7 +60944,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2266" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -60973,7 +60970,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2267" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -60999,7 +60996,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2268" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61025,7 +61022,7 @@
         <v>40</v>
       </c>
       <c r="G2269" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61051,7 +61048,7 @@
         <v>40</v>
       </c>
       <c r="G2270" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -61077,7 +61074,7 @@
         <v>40</v>
       </c>
       <c r="G2271" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61103,7 +61100,7 @@
         <v>40</v>
       </c>
       <c r="G2272" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61129,7 +61126,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G2273" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61155,7 +61152,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2274" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61181,7 +61178,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G2275" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61207,7 +61204,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2276" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61233,7 +61230,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G2277" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61259,7 +61256,7 @@
         <v>38</v>
       </c>
       <c r="G2278" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61285,7 +61282,7 @@
         <v>38</v>
       </c>
       <c r="G2279" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61311,7 +61308,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G2280" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61337,7 +61334,7 @@
         <v>38</v>
       </c>
       <c r="G2281" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61363,7 +61360,7 @@
         <v>38</v>
       </c>
       <c r="G2282" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61389,7 +61386,7 @@
         <v>38</v>
       </c>
       <c r="G2283" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61397,7 +61394,7 @@
     </row>
     <row r="2284">
       <c r="A2284" s="1" t="n">
-        <v>45985.6834837963</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2284" t="n">
         <v>1000</v>
@@ -61415,9 +61412,35 @@
         <v>38</v>
       </c>
       <c r="G2284" t="s">
+        <v>537</v>
+      </c>
+      <c r="H2284" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" s="1" t="n">
+        <v>45986.6611574074</v>
+      </c>
+      <c r="B2285" t="n">
+        <v>250</v>
+      </c>
+      <c r="C2285" t="n">
+        <v>37.5999984741211</v>
+      </c>
+      <c r="D2285" t="n">
+        <v>37.5999984741211</v>
+      </c>
+      <c r="E2285" t="n">
+        <v>37.5999984741211</v>
+      </c>
+      <c r="F2285" t="n">
+        <v>37.5999984741211</v>
+      </c>
+      <c r="G2285" t="s">
         <v>538</v>
       </c>
-      <c r="H2284" t="s">
+      <c r="H2285" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46539187431335</t>
+    <t xml:space="preserve">2.46539163589478</t>
   </si>
   <si>
     <t xml:space="preserve">FPE.MI</t>
@@ -50,34 +50,34 @@
     <t xml:space="preserve">2.43408513069153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41060495376587</t>
+    <t xml:space="preserve">2.41060543060303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45756530761719</t>
+    <t xml:space="preserve">2.45756506919861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39495182037354</t>
+    <t xml:space="preserve">2.39495205879211</t>
   </si>
   <si>
     <t xml:space="preserve">2.33233904838562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41843223571777</t>
+    <t xml:space="preserve">2.41843152046204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35581874847412</t>
+    <t xml:space="preserve">2.3558189868927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37147188186646</t>
+    <t xml:space="preserve">2.37147212028503</t>
   </si>
   <si>
     <t xml:space="preserve">2.50452470779419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36364555358887</t>
+    <t xml:space="preserve">2.36364531517029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44973826408386</t>
+    <t xml:space="preserve">2.44973850250244</t>
   </si>
   <si>
     <t xml:space="preserve">2.37303757667542</t>
@@ -86,28 +86,28 @@
     <t xml:space="preserve">2.34955763816833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46382617950439</t>
+    <t xml:space="preserve">2.46382665634155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38712525367737</t>
+    <t xml:space="preserve">2.38712549209595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45443415641785</t>
+    <t xml:space="preserve">2.454434633255</t>
   </si>
   <si>
     <t xml:space="preserve">2.34799194335938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48104500770569</t>
+    <t xml:space="preserve">2.48104524612427</t>
   </si>
   <si>
     <t xml:space="preserve">2.37929844856262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38556003570557</t>
+    <t xml:space="preserve">2.38556027412415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44191145896912</t>
+    <t xml:space="preserve">2.4419116973877</t>
   </si>
   <si>
     <t xml:space="preserve">2.78002262115479</t>
@@ -116,31 +116,31 @@
     <t xml:space="preserve">3.36702084541321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62529969215393</t>
+    <t xml:space="preserve">3.62530016899109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31066870689392</t>
+    <t xml:space="preserve">3.3106689453125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25588250160217</t>
+    <t xml:space="preserve">3.25588226318359</t>
   </si>
   <si>
     <t xml:space="preserve">3.20266103744507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0523898601532</t>
+    <t xml:space="preserve">3.05239009857178</t>
   </si>
   <si>
     <t xml:space="preserve">3.09152293205261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04456281661987</t>
+    <t xml:space="preserve">3.04456329345703</t>
   </si>
   <si>
     <t xml:space="preserve">3.03673672676086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03830194473267</t>
+    <t xml:space="preserve">3.03830170631409</t>
   </si>
   <si>
     <t xml:space="preserve">3.15413641929626</t>
@@ -158,22 +158,22 @@
     <t xml:space="preserve">3.57677459716797</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52198839187622</t>
+    <t xml:space="preserve">3.52198815345764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4045889377594</t>
+    <t xml:space="preserve">3.40458846092224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59242796897888</t>
+    <t xml:space="preserve">3.59242820739746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58460164070129</t>
+    <t xml:space="preserve">3.58460068702698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67852115631104</t>
+    <t xml:space="preserve">3.67852067947388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60025429725647</t>
+    <t xml:space="preserve">3.60025453567505</t>
   </si>
   <si>
     <t xml:space="preserve">3.59555864334106</t>
@@ -182,7 +182,7 @@
     <t xml:space="preserve">3.32632184028625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29501533508301</t>
+    <t xml:space="preserve">3.29501557350159</t>
   </si>
   <si>
     <t xml:space="preserve">3.3748471736908</t>
@@ -191,13 +191,13 @@
     <t xml:space="preserve">3.38267374038696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44372177124023</t>
+    <t xml:space="preserve">3.44372200965881</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59086275100708</t>
+    <t xml:space="preserve">3.59086227416992</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47972464561462</t>
+    <t xml:space="preserve">3.47972440719604</t>
   </si>
   <si>
     <t xml:space="preserve">3.4265034198761</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">3.28405833244324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16196274757385</t>
+    <t xml:space="preserve">3.16196250915527</t>
   </si>
   <si>
     <t xml:space="preserve">3.20892238616943</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">3.23240256309509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31849551200867</t>
+    <t xml:space="preserve">3.31849527359009</t>
   </si>
   <si>
     <t xml:space="preserve">3.27623176574707</t>
@@ -236,58 +236,58 @@
     <t xml:space="preserve">3.18857336044312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14317846298218</t>
+    <t xml:space="preserve">3.14317870140076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11500287055969</t>
+    <t xml:space="preserve">3.11500310897827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00073385238647</t>
+    <t xml:space="preserve">3.0007336139679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97412347793579</t>
+    <t xml:space="preserve">2.97412300109863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06021642684937</t>
+    <t xml:space="preserve">3.06021666526794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90368366241455</t>
+    <t xml:space="preserve">2.90368390083313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89585709571838</t>
+    <t xml:space="preserve">2.8958568572998</t>
   </si>
   <si>
     <t xml:space="preserve">2.82854795455933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83637428283691</t>
+    <t xml:space="preserve">2.83637452125549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90994501113892</t>
+    <t xml:space="preserve">2.90994477272034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491231918335</t>
+    <t xml:space="preserve">3.06491255760193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13065600395203</t>
+    <t xml:space="preserve">3.13065624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14474439620972</t>
+    <t xml:space="preserve">3.14474391937256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21361827850342</t>
+    <t xml:space="preserve">3.21361804008484</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28562378883362</t>
+    <t xml:space="preserve">3.2856240272522</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35919380187988</t>
+    <t xml:space="preserve">3.35919427871704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36389017105103</t>
+    <t xml:space="preserve">3.36388945579529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91332030296326</t>
+    <t xml:space="preserve">3.91332006454468</t>
   </si>
   <si>
     <t xml:space="preserve">4.34378528594971</t>
@@ -299,52 +299,52 @@
     <t xml:space="preserve">5.47864818572998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09303951263428</t>
+    <t xml:space="preserve">6.09303903579712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41603469848633</t>
+    <t xml:space="preserve">5.41603517532349</t>
   </si>
   <si>
     <t xml:space="preserve">5.71344709396362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56865453720093</t>
+    <t xml:space="preserve">5.56865406036377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41994857788086</t>
+    <t xml:space="preserve">5.41994905471802</t>
   </si>
   <si>
     <t xml:space="preserve">5.16558265686035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94643640518188</t>
+    <t xml:space="preserve">4.94643688201904</t>
   </si>
   <si>
     <t xml:space="preserve">4.70381116867065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6764178276062</t>
+    <t xml:space="preserve">4.67641735076904</t>
   </si>
   <si>
     <t xml:space="preserve">5.00904941558838</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55691480636597</t>
+    <t xml:space="preserve">5.55691432952881</t>
   </si>
   <si>
     <t xml:space="preserve">5.30646276473999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22428274154663</t>
+    <t xml:space="preserve">5.22428178787231</t>
   </si>
   <si>
     <t xml:space="preserve">5.19688940048218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32211542129517</t>
+    <t xml:space="preserve">5.32211589813232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47082185745239</t>
+    <t xml:space="preserve">5.47082138061523</t>
   </si>
   <si>
     <t xml:space="preserve">5.36907529830933</t>
@@ -353,19 +353,19 @@
     <t xml:space="preserve">5.2908091545105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1734094619751</t>
+    <t xml:space="preserve">5.17340898513794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09514284133911</t>
+    <t xml:space="preserve">5.09514236450195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2203688621521</t>
+    <t xml:space="preserve">5.22036933898926</t>
   </si>
   <si>
     <t xml:space="preserve">5.1029691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99339723587036</t>
+    <t xml:space="preserve">4.9933967590332</t>
   </si>
   <si>
     <t xml:space="preserve">5.15384244918823</t>
@@ -383,13 +383,13 @@
     <t xml:space="preserve">4.86425733566284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88773679733276</t>
+    <t xml:space="preserve">4.88773727416992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83295011520386</t>
+    <t xml:space="preserve">4.83295059204102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75468397140503</t>
+    <t xml:space="preserve">4.75468349456787</t>
   </si>
   <si>
     <t xml:space="preserve">4.82903671264648</t>
@@ -398,34 +398,34 @@
     <t xml:space="preserve">4.7233772277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68815803527832</t>
+    <t xml:space="preserve">4.688157081604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78207683563232</t>
+    <t xml:space="preserve">4.78207731246948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87599754333496</t>
+    <t xml:space="preserve">4.8759970664978</t>
   </si>
   <si>
     <t xml:space="preserve">5.03644323348999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92686986923218</t>
+    <t xml:space="preserve">4.92687082290649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81338405609131</t>
+    <t xml:space="preserve">4.81338453292847</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86034393310547</t>
+    <t xml:space="preserve">4.86034345626831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00122356414795</t>
+    <t xml:space="preserve">5.00122308731079</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77425050735474</t>
+    <t xml:space="preserve">4.77425098419189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82120990753174</t>
+    <t xml:space="preserve">4.82121086120605</t>
   </si>
   <si>
     <t xml:space="preserve">4.69989776611328</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">5.20471572875977</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43951559066772</t>
+    <t xml:space="preserve">5.43951463699341</t>
   </si>
   <si>
     <t xml:space="preserve">5.28298234939575</t>
@@ -449,46 +449,46 @@
     <t xml:space="preserve">5.24384880065918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3612494468689</t>
+    <t xml:space="preserve">5.36124849319458</t>
   </si>
   <si>
     <t xml:space="preserve">5.40038204193115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51778173446655</t>
+    <t xml:space="preserve">5.51778125762939</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63518095016479</t>
+    <t xml:space="preserve">5.63518047332764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96991634368896</t>
+    <t xml:space="preserve">4.96991682052612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93078374862671</t>
+    <t xml:space="preserve">4.93078327178955</t>
   </si>
   <si>
     <t xml:space="preserve">4.85251665115356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12644910812378</t>
+    <t xml:space="preserve">5.12644958496094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04818248748779</t>
+    <t xml:space="preserve">5.04818296432495</t>
   </si>
   <si>
     <t xml:space="preserve">5.08731603622437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59604787826538</t>
+    <t xml:space="preserve">5.59604835510254</t>
   </si>
   <si>
     <t xml:space="preserve">5.26159715652466</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42103910446167</t>
+    <t xml:space="preserve">5.42104053497314</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34131813049316</t>
+    <t xml:space="preserve">5.34131860733032</t>
   </si>
   <si>
     <t xml:space="preserve">5.22173690795898</t>
@@ -497,13 +497,13 @@
     <t xml:space="preserve">5.14201545715332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10215473175049</t>
+    <t xml:space="preserve">5.10215520858765</t>
   </si>
   <si>
     <t xml:space="preserve">5.18187618255615</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38117933273315</t>
+    <t xml:space="preserve">5.381178855896</t>
   </si>
   <si>
     <t xml:space="preserve">5.30145788192749</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">4.9028525352478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50076055526733</t>
+    <t xml:space="preserve">5.50076103210449</t>
   </si>
   <si>
     <t xml:space="preserve">5.4608998298645</t>
@@ -527,22 +527,22 @@
     <t xml:space="preserve">5.62034273147583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94271230697632</t>
+    <t xml:space="preserve">4.94271278381348</t>
   </si>
   <si>
     <t xml:space="preserve">4.98257303237915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82313060760498</t>
+    <t xml:space="preserve">4.82313203811646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06229400634766</t>
+    <t xml:space="preserve">5.06229448318481</t>
   </si>
   <si>
     <t xml:space="preserve">5.02243375778198</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74340867996216</t>
+    <t xml:space="preserve">4.74340963363647</t>
   </si>
   <si>
     <t xml:space="preserve">4.78327035903931</t>
@@ -551,67 +551,67 @@
     <t xml:space="preserve">4.86299180984497</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73992395401001</t>
+    <t xml:space="preserve">5.73992443084717</t>
   </si>
   <si>
     <t xml:space="preserve">5.81964540481567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70006322860718</t>
+    <t xml:space="preserve">5.70006370544434</t>
   </si>
   <si>
     <t xml:space="preserve">5.6602029800415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77978515625</t>
+    <t xml:space="preserve">5.77978467941284</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85950660705566</t>
+    <t xml:space="preserve">5.85950613021851</t>
   </si>
   <si>
     <t xml:space="preserve">5.97908782958984</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29797267913818</t>
+    <t xml:space="preserve">6.29797220230103</t>
   </si>
   <si>
     <t xml:space="preserve">6.13853025436401</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05880928039551</t>
+    <t xml:space="preserve">6.05880880355835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825170516968</t>
+    <t xml:space="preserve">6.21825218200684</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09866952896118</t>
+    <t xml:space="preserve">6.0986704826355</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38518524169922</t>
+    <t xml:space="preserve">6.38518476486206</t>
   </si>
   <si>
     <t xml:space="preserve">6.25998449325562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30171871185303</t>
+    <t xml:space="preserve">6.30171823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17651891708374</t>
+    <t xml:space="preserve">6.17651844024658</t>
   </si>
   <si>
     <t xml:space="preserve">6.426917552948</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34345102310181</t>
+    <t xml:space="preserve">6.34345149993896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46865129470825</t>
+    <t xml:space="preserve">6.46865081787109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9678521156311</t>
+    <t xml:space="preserve">5.96785259246826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00958490371704</t>
+    <t xml:space="preserve">6.0095853805542</t>
   </si>
   <si>
     <t xml:space="preserve">6.13478565216064</t>
@@ -626,70 +626,73 @@
     <t xml:space="preserve">6.09305191040039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51038408279419</t>
+    <t xml:space="preserve">6.21825170516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51038455963135</t>
   </si>
   <si>
     <t xml:space="preserve">5.84265232086182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88438653945923</t>
+    <t xml:space="preserve">5.88438558578491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05291652679443</t>
+    <t xml:space="preserve">7.05291604995728</t>
   </si>
   <si>
     <t xml:space="preserve">8.09624671936035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.804114818573</t>
+    <t xml:space="preserve">7.80411529541016</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6371808052063</t>
+    <t xml:space="preserve">7.63718128204346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55371522903442</t>
+    <t xml:space="preserve">7.55371475219727</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34504842758179</t>
+    <t xml:space="preserve">7.34504890441895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17811632156372</t>
+    <t xml:space="preserve">7.17811584472656</t>
   </si>
   <si>
     <t xml:space="preserve">7.51198148727417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47024822235107</t>
+    <t xml:space="preserve">7.47024774551392</t>
   </si>
   <si>
     <t xml:space="preserve">7.30331611633301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851448059082</t>
+    <t xml:space="preserve">7.42851495742798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26158142089844</t>
+    <t xml:space="preserve">7.26158237457275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38678312301636</t>
+    <t xml:space="preserve">7.38678169250488</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9694504737854</t>
+    <t xml:space="preserve">6.96944999694824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21984910964966</t>
+    <t xml:space="preserve">7.2198486328125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5954475402832</t>
+    <t xml:space="preserve">7.59544849395752</t>
   </si>
   <si>
     <t xml:space="preserve">7.76238107681274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84584760665894</t>
+    <t xml:space="preserve">7.84584665298462</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67891407012939</t>
+    <t xml:space="preserve">7.67891359329224</t>
   </si>
   <si>
     <t xml:space="preserve">7.01118230819702</t>
@@ -707,10 +710,10 @@
     <t xml:space="preserve">6.80251598358154</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71905040740967</t>
+    <t xml:space="preserve">6.71905088424683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84424924850464</t>
+    <t xml:space="preserve">6.8442497253418</t>
   </si>
   <si>
     <t xml:space="preserve">6.59385061264038</t>
@@ -722,43 +725,43 @@
     <t xml:space="preserve">6.55211734771729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75918626785278</t>
+    <t xml:space="preserve">5.75918579101562</t>
   </si>
   <si>
     <t xml:space="preserve">5.71745252609253</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80091953277588</t>
+    <t xml:space="preserve">5.80091905593872</t>
   </si>
   <si>
     <t xml:space="preserve">5.67571926116943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59225273132324</t>
+    <t xml:space="preserve">5.5922532081604</t>
   </si>
   <si>
     <t xml:space="preserve">5.6339864730835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46705293655396</t>
+    <t xml:space="preserve">5.46705341339111</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55051946640015</t>
+    <t xml:space="preserve">5.5505199432373</t>
   </si>
   <si>
     <t xml:space="preserve">5.17492055892944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25838756561279</t>
+    <t xml:space="preserve">5.25838708877563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38358640670776</t>
+    <t xml:space="preserve">5.38358736038208</t>
   </si>
   <si>
     <t xml:space="preserve">7.13638353347778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47247123718262</t>
+    <t xml:space="preserve">7.47247076034546</t>
   </si>
   <si>
     <t xml:space="preserve">7.25269222259521</t>
@@ -770,22 +773,22 @@
     <t xml:space="preserve">7.20873641967773</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16478109359741</t>
+    <t xml:space="preserve">7.1647801399231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07686948776245</t>
+    <t xml:space="preserve">7.07686996459961</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98895740509033</t>
+    <t xml:space="preserve">6.98895835876465</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03291416168213</t>
+    <t xml:space="preserve">7.03291368484497</t>
   </si>
   <si>
     <t xml:space="preserve">6.94500255584717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85709047317505</t>
+    <t xml:space="preserve">6.85709142684937</t>
   </si>
   <si>
     <t xml:space="preserve">6.72522401809692</t>
@@ -794,28 +797,25 @@
     <t xml:space="preserve">6.81313514709473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7691798210144</t>
+    <t xml:space="preserve">6.76917934417725</t>
   </si>
   <si>
     <t xml:space="preserve">6.90104675292969</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63731288909912</t>
+    <t xml:space="preserve">6.63731241226196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12082481384277</t>
+    <t xml:space="preserve">7.12082529067993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34060430526733</t>
+    <t xml:space="preserve">7.34060382843018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51642656326294</t>
+    <t xml:space="preserve">7.51642751693726</t>
   </si>
   <si>
     <t xml:space="preserve">7.56038236618042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42851543426514</t>
   </si>
   <si>
     <t xml:space="preserve">7.73620510101318</t>
@@ -824,67 +824,64 @@
     <t xml:space="preserve">7.69224977493286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829349517822</t>
+    <t xml:space="preserve">7.64829397201538</t>
   </si>
   <si>
     <t xml:space="preserve">7.78247356414795</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82720136642456</t>
+    <t xml:space="preserve">7.8272008895874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73774719238281</t>
+    <t xml:space="preserve">7.73774671554565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69302034378052</t>
+    <t xml:space="preserve">7.69302082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829444885254</t>
+    <t xml:space="preserve">7.60356664657593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60356616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91665554046631</t>
+    <t xml:space="preserve">7.91665458679199</t>
   </si>
   <si>
     <t xml:space="preserve">7.8719277381897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96138048171997</t>
+    <t xml:space="preserve">7.96138143539429</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22974109649658</t>
+    <t xml:space="preserve">8.2297420501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76646518707275</t>
+    <t xml:space="preserve">8.76646614074707</t>
   </si>
   <si>
     <t xml:space="preserve">8.58755779266357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36392307281494</t>
+    <t xml:space="preserve">8.36392402648926</t>
   </si>
   <si>
     <t xml:space="preserve">8.63228416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54283142089844</t>
+    <t xml:space="preserve">8.54283046722412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40865039825439</t>
+    <t xml:space="preserve">8.40864944458008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27447032928467</t>
+    <t xml:space="preserve">8.27446937561035</t>
   </si>
   <si>
     <t xml:space="preserve">8.45337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67701148986816</t>
+    <t xml:space="preserve">8.67701244354248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49810314178467</t>
+    <t xml:space="preserve">8.49810409545898</t>
   </si>
   <si>
     <t xml:space="preserve">8.81119251251221</t>
@@ -893,16 +890,16 @@
     <t xml:space="preserve">8.7217378616333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85591793060303</t>
+    <t xml:space="preserve">8.85591983795166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03482723236084</t>
+    <t xml:space="preserve">9.03482532501221</t>
   </si>
   <si>
     <t xml:space="preserve">10.3766326904297</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4500770568848</t>
+    <t xml:space="preserve">11.4500780105591</t>
   </si>
   <si>
     <t xml:space="preserve">10.734447479248</t>
@@ -911,31 +908,31 @@
     <t xml:space="preserve">11.0922613143921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9133548736572</t>
+    <t xml:space="preserve">10.9133539199829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.181715965271</t>
+    <t xml:space="preserve">11.1817150115967</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3606233596802</t>
+    <t xml:space="preserve">11.3606224060059</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6289854049683</t>
+    <t xml:space="preserve">11.6289844512939</t>
   </si>
   <si>
     <t xml:space="preserve">11.5395307540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2711706161499</t>
+    <t xml:space="preserve">11.2711696624756</t>
   </si>
   <si>
     <t xml:space="preserve">10.5555391311646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2871780395508</t>
+    <t xml:space="preserve">10.2871789932251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0028095245361</t>
+    <t xml:space="preserve">11.0028076171875</t>
   </si>
   <si>
     <t xml:space="preserve">10.6449928283691</t>
@@ -947,7 +944,7 @@
     <t xml:space="preserve">10.1082715988159</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1977252960205</t>
+    <t xml:space="preserve">10.1977243423462</t>
   </si>
   <si>
     <t xml:space="preserve">9.75045585632324</t>
@@ -968,7 +965,7 @@
     <t xml:space="preserve">13.7758731842041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5075130462646</t>
+    <t xml:space="preserve">13.507513999939</t>
   </si>
   <si>
     <t xml:space="preserve">13.2391519546509</t>
@@ -977,13 +974,13 @@
     <t xml:space="preserve">13.0602445602417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4180583953857</t>
+    <t xml:space="preserve">13.4180593490601</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8813352584839</t>
+    <t xml:space="preserve">12.8813362121582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7918825149536</t>
+    <t xml:space="preserve">12.7918834686279</t>
   </si>
   <si>
     <t xml:space="preserve">12.702428817749</t>
@@ -992,7 +989,7 @@
     <t xml:space="preserve">13.149697303772</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3286056518555</t>
+    <t xml:space="preserve">13.3286046981812</t>
   </si>
   <si>
     <t xml:space="preserve">13.9547805786133</t>
@@ -1001,34 +998,34 @@
     <t xml:space="preserve">13.5969667434692</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6864194869995</t>
+    <t xml:space="preserve">13.6864213943481</t>
   </si>
   <si>
-    <t xml:space="preserve">13.865327835083</t>
+    <t xml:space="preserve">13.8653268814087</t>
   </si>
   <si>
     <t xml:space="preserve">14.4020500183105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2965888977051</t>
+    <t xml:space="preserve">15.2965879440308</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2071323394775</t>
+    <t xml:space="preserve">15.2071332931519</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5809555053711</t>
+    <t xml:space="preserve">14.5809564590454</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7598657608032</t>
+    <t xml:space="preserve">14.7598648071289</t>
   </si>
   <si>
     <t xml:space="preserve">14.4915046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5400886535645</t>
+    <t xml:space="preserve">14.5400876998901</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3560371398926</t>
+    <t xml:space="preserve">14.3560361862183</t>
   </si>
   <si>
     <t xml:space="preserve">14.2640104293823</t>
@@ -1040,7 +1037,7 @@
     <t xml:space="preserve">14.8161659240723</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6321134567261</t>
+    <t xml:space="preserve">14.6321144104004</t>
   </si>
   <si>
     <t xml:space="preserve">15.3683223724365</t>
@@ -1052,10 +1049,10 @@
     <t xml:space="preserve">16.104528427124</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3806037902832</t>
+    <t xml:space="preserve">16.3806056976318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9204769134521</t>
+    <t xml:space="preserve">15.9204750061035</t>
   </si>
   <si>
     <t xml:space="preserve">17.2088394165039</t>
@@ -1067,7 +1064,7 @@
     <t xml:space="preserve">17.4849166870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5769424438477</t>
+    <t xml:space="preserve">17.576940536499</t>
   </si>
   <si>
     <t xml:space="preserve">17.6689682006836</t>
@@ -1076,31 +1073,31 @@
     <t xml:space="preserve">18.4051742553711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1413822174072</t>
+    <t xml:space="preserve">19.1413803100586</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6935386657715</t>
+    <t xml:space="preserve">19.6935367584229</t>
   </si>
   <si>
     <t xml:space="preserve">20.0616397857666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5340538024902</t>
+    <t xml:space="preserve">21.5340557098389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3745727539062</t>
+    <t xml:space="preserve">23.3745708465576</t>
   </si>
   <si>
-    <t xml:space="preserve">22.270263671875</t>
+    <t xml:space="preserve">22.2702617645264</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8224182128906</t>
+    <t xml:space="preserve">22.822416305542</t>
   </si>
   <si>
     <t xml:space="preserve">20.6137962341309</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3254356384277</t>
+    <t xml:space="preserve">19.3254337310791</t>
   </si>
   <si>
     <t xml:space="preserve">21.902156829834</t>
@@ -1109,10 +1106,10 @@
     <t xml:space="preserve">22.0862102508545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0064697265625</t>
+    <t xml:space="preserve">23.0064678192139</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5586242675781</t>
+    <t xml:space="preserve">23.5586261749268</t>
   </si>
   <si>
     <t xml:space="preserve">23.74267578125</t>
@@ -1124,7 +1121,7 @@
     <t xml:space="preserve">24.6629333496094</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8469867706299</t>
+    <t xml:space="preserve">24.8469886779785</t>
   </si>
   <si>
     <t xml:space="preserve">24.2948303222656</t>
@@ -1139,25 +1136,25 @@
     <t xml:space="preserve">25.2150897979736</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4543151855469</t>
+    <t xml:space="preserve">22.4543132781982</t>
   </si>
   <si>
     <t xml:space="preserve">24.4788837432861</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9512977600098</t>
+    <t xml:space="preserve">25.9512958526611</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5034503936768</t>
+    <t xml:space="preserve">26.5034523010254</t>
   </si>
   <si>
     <t xml:space="preserve">27.975866317749</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9206924438477</t>
+    <t xml:space="preserve">30.9206943511963</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0801773071289</t>
+    <t xml:space="preserve">29.0801753997803</t>
   </si>
   <si>
     <t xml:space="preserve">30.736644744873</t>
@@ -1166,31 +1163,31 @@
     <t xml:space="preserve">30.3685398101807</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2642269134521</t>
+    <t xml:space="preserve">29.2642288208008</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4728527069092</t>
+    <t xml:space="preserve">31.4728507995605</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2336235046387</t>
+    <t xml:space="preserve">34.2336273193359</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7857818603516</t>
+    <t xml:space="preserve">34.7857780456543</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8655166625977</t>
+    <t xml:space="preserve">33.8655204772949</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4974174499512</t>
+    <t xml:space="preserve">33.4974212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1844844818115</t>
+    <t xml:space="preserve">30.1844863891602</t>
   </si>
   <si>
     <t xml:space="preserve">27.4237098693848</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6875019073486</t>
+    <t xml:space="preserve">26.6875038146973</t>
   </si>
   <si>
     <t xml:space="preserve">25.5831928253174</t>
@@ -1199,7 +1196,7 @@
     <t xml:space="preserve">26.3194007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7918148040771</t>
+    <t xml:space="preserve">27.7918167114258</t>
   </si>
   <si>
     <t xml:space="preserve">28.8961238861084</t>
@@ -1211,7 +1208,7 @@
     <t xml:space="preserve">28.5280208587646</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7120742797852</t>
+    <t xml:space="preserve">28.7120723724365</t>
   </si>
   <si>
     <t xml:space="preserve">28.3439693450928</t>
@@ -1220,7 +1217,7 @@
     <t xml:space="preserve">27.055606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8715553283691</t>
+    <t xml:space="preserve">26.8715572357178</t>
   </si>
   <si>
     <t xml:space="preserve">25.3991413116455</t>
@@ -1235,7 +1232,7 @@
     <t xml:space="preserve">27.6077632904053</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5525894165039</t>
+    <t xml:space="preserve">30.5525913238525</t>
   </si>
   <si>
     <t xml:space="preserve">29.6323318481445</t>
@@ -1250,10 +1247,10 @@
     <t xml:space="preserve">32.209056854248</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2887954711914</t>
+    <t xml:space="preserve">31.28879737854</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6569004058838</t>
+    <t xml:space="preserve">31.6569023132324</t>
   </si>
   <si>
     <t xml:space="preserve">32.0250015258789</t>
@@ -1266,6 +1263,9 @@
   </si>
   <si>
     <t xml:space="preserve">33.1643714904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6569004058838</t>
   </si>
   <si>
     <t xml:space="preserve">32.4106369018555</t>
@@ -18642,7 +18642,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G639" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19162,7 +19162,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G659" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -19188,7 +19188,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G660" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19292,7 +19292,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G664" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19500,7 +19500,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G672" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -19526,7 +19526,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G673" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20020,7 +20020,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G692" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20046,7 +20046,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G693" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20124,7 +20124,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G696" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20150,7 +20150,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G697" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -20280,7 +20280,7 @@
         <v>7</v>
       </c>
       <c r="G702" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -20306,7 +20306,7 @@
         <v>7</v>
       </c>
       <c r="G703" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -20332,7 +20332,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G704" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -20592,7 +20592,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G714" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -20618,7 +20618,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G715" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -20696,7 +20696,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G718" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -20748,7 +20748,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G720" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21008,7 +21008,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G730" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21034,7 +21034,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G731" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21060,7 +21060,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G732" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21086,7 +21086,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G733" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -21346,7 +21346,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G743" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -21372,7 +21372,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G744" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -21398,7 +21398,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G745" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -21424,7 +21424,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G746" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -21450,7 +21450,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G747" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -21476,7 +21476,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G748" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -21502,7 +21502,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G749" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -21528,7 +21528,7 @@
         <v>9</v>
       </c>
       <c r="G750" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -21554,7 +21554,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G751" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -21580,7 +21580,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G752" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -21606,7 +21606,7 @@
         <v>8.75</v>
       </c>
       <c r="G753" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -21632,7 +21632,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G754" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -21658,7 +21658,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G755" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -21684,7 +21684,7 @@
         <v>9</v>
       </c>
       <c r="G756" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -21710,7 +21710,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G757" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -21736,7 +21736,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G758" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -21762,7 +21762,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G759" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -21788,7 +21788,7 @@
         <v>9</v>
       </c>
       <c r="G760" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -21814,7 +21814,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G761" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -21840,7 +21840,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G762" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -21866,7 +21866,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G763" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -21892,7 +21892,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G764" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -21918,7 +21918,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G765" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -21944,7 +21944,7 @@
         <v>9</v>
       </c>
       <c r="G766" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -21970,7 +21970,7 @@
         <v>9</v>
       </c>
       <c r="G767" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -21996,7 +21996,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G768" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22022,7 +22022,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G769" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22048,7 +22048,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G770" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22074,7 +22074,7 @@
         <v>8.75</v>
       </c>
       <c r="G771" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22100,7 +22100,7 @@
         <v>8.75</v>
       </c>
       <c r="G772" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22126,7 +22126,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G773" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22152,7 +22152,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G774" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22178,7 +22178,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G775" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22204,7 +22204,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G776" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22230,7 +22230,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G777" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22256,7 +22256,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G778" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22282,7 +22282,7 @@
         <v>9</v>
       </c>
       <c r="G779" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -22308,7 +22308,7 @@
         <v>9</v>
       </c>
       <c r="G780" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -22334,7 +22334,7 @@
         <v>9</v>
       </c>
       <c r="G781" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -22360,7 +22360,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G782" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -22386,7 +22386,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G783" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -22412,7 +22412,7 @@
         <v>8.75</v>
       </c>
       <c r="G784" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -22438,7 +22438,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G785" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -22464,7 +22464,7 @@
         <v>8.75</v>
       </c>
       <c r="G786" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -22490,7 +22490,7 @@
         <v>8.75</v>
       </c>
       <c r="G787" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -22516,7 +22516,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G788" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -22542,7 +22542,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G789" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -22568,7 +22568,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G790" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -22594,7 +22594,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G791" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -22620,7 +22620,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G792" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -22646,7 +22646,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G793" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -22672,7 +22672,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G794" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -22698,7 +22698,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G795" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -22724,7 +22724,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G796" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -22750,7 +22750,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G797" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -22776,7 +22776,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G798" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -22802,7 +22802,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G799" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -22828,7 +22828,7 @@
         <v>8.75</v>
       </c>
       <c r="G800" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -22854,7 +22854,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G801" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -22880,7 +22880,7 @@
         <v>8.75</v>
       </c>
       <c r="G802" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -22906,7 +22906,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G803" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -22932,7 +22932,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G804" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -22958,7 +22958,7 @@
         <v>8.75</v>
       </c>
       <c r="G805" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -22984,7 +22984,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G806" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23010,7 +23010,7 @@
         <v>8.75</v>
       </c>
       <c r="G807" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23036,7 +23036,7 @@
         <v>8.75</v>
       </c>
       <c r="G808" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23062,7 +23062,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G809" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23088,7 +23088,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G810" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23114,7 +23114,7 @@
         <v>8.5</v>
       </c>
       <c r="G811" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23140,7 +23140,7 @@
         <v>8.5</v>
       </c>
       <c r="G812" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23166,7 +23166,7 @@
         <v>8.5</v>
       </c>
       <c r="G813" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23192,7 +23192,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G814" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23218,7 +23218,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G815" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23244,7 +23244,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G816" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23270,7 +23270,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G817" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23296,7 +23296,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G818" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -23322,7 +23322,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G819" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -23348,7 +23348,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G820" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -23374,7 +23374,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G821" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -23400,7 +23400,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G822" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -23426,7 +23426,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G823" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -23452,7 +23452,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G824" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -23478,7 +23478,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G825" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -23504,7 +23504,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G826" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -23530,7 +23530,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G827" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -23556,7 +23556,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G828" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -23582,7 +23582,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G829" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -23608,7 +23608,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G830" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -23634,7 +23634,7 @@
         <v>9</v>
       </c>
       <c r="G831" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -23660,7 +23660,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G832" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -23686,7 +23686,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G833" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -23712,7 +23712,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G834" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -23738,7 +23738,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G835" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -23764,7 +23764,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G836" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -23790,7 +23790,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G837" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -23816,7 +23816,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G838" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -23842,7 +23842,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G839" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -23868,7 +23868,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G840" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -23894,7 +23894,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G841" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -23920,7 +23920,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G842" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -23946,7 +23946,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G843" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -23972,7 +23972,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G844" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -23998,7 +23998,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G845" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24024,7 +24024,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G846" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24050,7 +24050,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G847" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24076,7 +24076,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G848" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24102,7 +24102,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G849" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24128,7 +24128,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G850" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24154,7 +24154,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G851" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24180,7 +24180,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G852" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24206,7 +24206,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G853" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24232,7 +24232,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G854" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24258,7 +24258,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G855" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24284,7 +24284,7 @@
         <v>8</v>
       </c>
       <c r="G856" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24310,7 +24310,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G857" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24336,7 +24336,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G858" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -24414,7 +24414,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G861" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24492,7 +24492,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G864" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -24934,7 +24934,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G881" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25012,7 +25012,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G884" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25038,7 +25038,7 @@
         <v>7</v>
       </c>
       <c r="G885" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25246,7 +25246,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G893" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -25974,7 +25974,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G921" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26000,7 +26000,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G922" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26026,7 +26026,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G923" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -26052,7 +26052,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G924" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26156,7 +26156,7 @@
         <v>7</v>
       </c>
       <c r="G928" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26182,7 +26182,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G929" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26208,7 +26208,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G930" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26234,7 +26234,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G931" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26260,7 +26260,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G932" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26286,7 +26286,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G933" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26312,7 +26312,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G934" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26338,7 +26338,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G935" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26416,7 +26416,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G938" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26442,7 +26442,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G939" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26702,7 +26702,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G949" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26728,7 +26728,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G950" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26754,7 +26754,7 @@
         <v>7</v>
       </c>
       <c r="G951" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -26780,7 +26780,7 @@
         <v>7</v>
       </c>
       <c r="G952" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26806,7 +26806,7 @@
         <v>7</v>
       </c>
       <c r="G953" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26832,7 +26832,7 @@
         <v>7</v>
       </c>
       <c r="G954" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26858,7 +26858,7 @@
         <v>7</v>
       </c>
       <c r="G955" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26884,7 +26884,7 @@
         <v>7</v>
       </c>
       <c r="G956" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26910,7 +26910,7 @@
         <v>7</v>
       </c>
       <c r="G957" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26936,7 +26936,7 @@
         <v>7</v>
       </c>
       <c r="G958" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26962,7 +26962,7 @@
         <v>7</v>
       </c>
       <c r="G959" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -26988,7 +26988,7 @@
         <v>7</v>
       </c>
       <c r="G960" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27014,7 +27014,7 @@
         <v>7</v>
       </c>
       <c r="G961" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27040,7 +27040,7 @@
         <v>7</v>
       </c>
       <c r="G962" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27066,7 +27066,7 @@
         <v>7</v>
       </c>
       <c r="G963" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27092,7 +27092,7 @@
         <v>7</v>
       </c>
       <c r="G964" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27118,7 +27118,7 @@
         <v>7</v>
       </c>
       <c r="G965" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27144,7 +27144,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G966" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27170,7 +27170,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G967" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27196,7 +27196,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G968" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27222,7 +27222,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G969" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -27248,7 +27248,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G970" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27274,7 +27274,7 @@
         <v>6.75</v>
       </c>
       <c r="G971" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27300,7 +27300,7 @@
         <v>6.75</v>
       </c>
       <c r="G972" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27326,7 +27326,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G973" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27352,7 +27352,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G974" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27378,7 +27378,7 @@
         <v>6.75</v>
       </c>
       <c r="G975" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27404,7 +27404,7 @@
         <v>6.75</v>
       </c>
       <c r="G976" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27430,7 +27430,7 @@
         <v>6.75</v>
       </c>
       <c r="G977" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27456,7 +27456,7 @@
         <v>6.75</v>
       </c>
       <c r="G978" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -27482,7 +27482,7 @@
         <v>6.75</v>
       </c>
       <c r="G979" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27508,7 +27508,7 @@
         <v>6.75</v>
       </c>
       <c r="G980" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27534,7 +27534,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G981" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27560,7 +27560,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G982" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -27586,7 +27586,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G983" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -27612,7 +27612,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G984" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27638,7 +27638,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G985" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -27664,7 +27664,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G986" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -27690,7 +27690,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G987" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -27716,7 +27716,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G988" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -27742,7 +27742,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G989" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -27768,7 +27768,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G990" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -27794,7 +27794,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G991" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -27820,7 +27820,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G992" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -27846,7 +27846,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G993" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -27872,7 +27872,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G994" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -27898,7 +27898,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G995" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -27924,7 +27924,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G996" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -27950,7 +27950,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G997" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -27976,7 +27976,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G998" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28002,7 +28002,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G999" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28028,7 +28028,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1000" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28054,7 +28054,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1001" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28080,7 +28080,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1002" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28106,7 +28106,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1003" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28132,7 +28132,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1004" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28158,7 +28158,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1005" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28184,7 +28184,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1006" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28210,7 +28210,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1007" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28236,7 +28236,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1008" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28262,7 +28262,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1009" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28340,7 +28340,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1012" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28366,7 +28366,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1013" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28392,7 +28392,7 @@
         <v>8</v>
       </c>
       <c r="G1014" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28548,7 +28548,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1020" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28574,7 +28574,7 @@
         <v>8.5</v>
       </c>
       <c r="G1021" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28600,7 +28600,7 @@
         <v>8.5</v>
       </c>
       <c r="G1022" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -28626,7 +28626,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1023" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -28652,7 +28652,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1024" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28678,7 +28678,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1025" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28704,7 +28704,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1026" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28730,7 +28730,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1027" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28756,7 +28756,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1028" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28782,7 +28782,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1029" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28808,7 +28808,7 @@
         <v>8.75</v>
       </c>
       <c r="G1030" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28834,7 +28834,7 @@
         <v>8.75</v>
       </c>
       <c r="G1031" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28860,7 +28860,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1032" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28886,7 +28886,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1033" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28912,7 +28912,7 @@
         <v>8.5</v>
       </c>
       <c r="G1034" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28938,7 +28938,7 @@
         <v>8.25</v>
       </c>
       <c r="G1035" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28964,7 +28964,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1036" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -28990,7 +28990,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1037" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29016,7 +29016,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1038" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29042,7 +29042,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1039" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29068,7 +29068,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1040" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29094,7 +29094,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1041" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29120,7 +29120,7 @@
         <v>8</v>
       </c>
       <c r="G1042" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29146,7 +29146,7 @@
         <v>8</v>
       </c>
       <c r="G1043" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29172,7 +29172,7 @@
         <v>8</v>
       </c>
       <c r="G1044" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29198,7 +29198,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1045" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -29224,7 +29224,7 @@
         <v>8</v>
       </c>
       <c r="G1046" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29250,7 +29250,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1047" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -29276,7 +29276,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1048" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29302,7 +29302,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1049" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29328,7 +29328,7 @@
         <v>7.75</v>
       </c>
       <c r="G1050" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29354,7 +29354,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1051" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29380,7 +29380,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1052" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29406,7 +29406,7 @@
         <v>7.75</v>
       </c>
       <c r="G1053" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29432,7 +29432,7 @@
         <v>7.75</v>
       </c>
       <c r="G1054" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29458,7 +29458,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1055" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29484,7 +29484,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1056" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29510,7 +29510,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1057" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29536,7 +29536,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1058" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29562,7 +29562,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1059" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29588,7 +29588,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1060" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29614,7 +29614,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1061" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29640,7 +29640,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1062" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29666,7 +29666,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1063" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29692,7 +29692,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1064" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29718,7 +29718,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1065" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29744,7 +29744,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1066" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29770,7 +29770,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1067" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29796,7 +29796,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1068" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29822,7 +29822,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1069" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29848,7 +29848,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1070" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29874,7 +29874,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1071" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29900,7 +29900,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1072" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -29926,7 +29926,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1073" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -29952,7 +29952,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1074" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -29978,7 +29978,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1075" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30004,7 +30004,7 @@
         <v>8</v>
       </c>
       <c r="G1076" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30030,7 +30030,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1077" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30056,7 +30056,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1078" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30082,7 +30082,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1079" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -30108,7 +30108,7 @@
         <v>8.25</v>
       </c>
       <c r="G1080" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30134,7 +30134,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1081" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30160,7 +30160,7 @@
         <v>8.5</v>
       </c>
       <c r="G1082" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30186,7 +30186,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1083" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30212,7 +30212,7 @@
         <v>8.5</v>
       </c>
       <c r="G1084" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30238,7 +30238,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1085" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30264,7 +30264,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1086" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -30290,7 +30290,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1087" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30316,7 +30316,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1088" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30342,7 +30342,7 @@
         <v>8.5</v>
       </c>
       <c r="G1089" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30368,7 +30368,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1090" t="s">
-        <v>267</v>
+        <v>218</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30394,7 +30394,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1091" t="s">
-        <v>267</v>
+        <v>218</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30420,7 +30420,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1092" t="s">
-        <v>267</v>
+        <v>218</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30446,7 +30446,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1093" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30472,7 +30472,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1094" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30498,7 +30498,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1095" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30784,7 +30784,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1106" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -31486,7 +31486,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1133" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31512,7 +31512,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1134" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31538,7 +31538,7 @@
         <v>8.5</v>
       </c>
       <c r="G1135" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -31564,7 +31564,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1136" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31590,7 +31590,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1137" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31616,7 +31616,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1138" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31642,7 +31642,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1139" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31668,7 +31668,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1140" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31694,7 +31694,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1141" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31746,7 +31746,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1143" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -31772,7 +31772,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1144" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -31798,7 +31798,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1145" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -31824,7 +31824,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1146" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -31876,7 +31876,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G1148" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -31928,7 +31928,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1150" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -31954,7 +31954,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1151" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -31980,7 +31980,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1152" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -32006,7 +32006,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1153" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -32110,7 +32110,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1157" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -32136,7 +32136,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G1158" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -32162,7 +32162,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1159" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -32188,7 +32188,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1160" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -32214,7 +32214,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1161" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -32240,7 +32240,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1162" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -32266,7 +32266,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1163" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -32292,7 +32292,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1164" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -32318,7 +32318,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G1165" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -32344,7 +32344,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1166" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -32370,7 +32370,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G1167" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -32396,7 +32396,7 @@
         <v>9.25</v>
       </c>
       <c r="G1168" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -32422,7 +32422,7 @@
         <v>9.25</v>
       </c>
       <c r="G1169" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -32448,7 +32448,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1170" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -32474,7 +32474,7 @@
         <v>9.55000019073486</v>
       </c>
       <c r="G1171" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -32500,7 +32500,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1172" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -32526,7 +32526,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1173" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -32552,7 +32552,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1174" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -32578,7 +32578,7 @@
         <v>9.44999980926514</v>
       </c>
       <c r="G1175" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -32604,7 +32604,7 @@
         <v>9.5</v>
       </c>
       <c r="G1176" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -32630,7 +32630,7 @@
         <v>9.64999961853027</v>
       </c>
       <c r="G1177" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -32656,7 +32656,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1178" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -32682,7 +32682,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G1179" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -32708,7 +32708,7 @@
         <v>9.75</v>
       </c>
       <c r="G1180" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -32734,7 +32734,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1181" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -32760,7 +32760,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1182" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -32786,7 +32786,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G1183" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -32812,7 +32812,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G1184" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -32838,7 +32838,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1185" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -32864,7 +32864,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1186" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -32890,7 +32890,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1187" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -32916,7 +32916,7 @@
         <v>12</v>
       </c>
       <c r="G1188" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -32942,7 +32942,7 @@
         <v>12</v>
       </c>
       <c r="G1189" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -32968,7 +32968,7 @@
         <v>12</v>
       </c>
       <c r="G1190" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -32994,7 +32994,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1191" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -33020,7 +33020,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1192" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -33046,7 +33046,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1193" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -33072,7 +33072,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1194" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -33098,7 +33098,7 @@
         <v>12.5</v>
       </c>
       <c r="G1195" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -33124,7 +33124,7 @@
         <v>12.5</v>
       </c>
       <c r="G1196" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -33150,7 +33150,7 @@
         <v>12.5</v>
       </c>
       <c r="G1197" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -33176,7 +33176,7 @@
         <v>12.5</v>
       </c>
       <c r="G1198" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -33202,7 +33202,7 @@
         <v>12.5</v>
       </c>
       <c r="G1199" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -33228,7 +33228,7 @@
         <v>12.5</v>
       </c>
       <c r="G1200" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -33254,7 +33254,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1201" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -33280,7 +33280,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G1202" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -33306,7 +33306,7 @@
         <v>12.5</v>
       </c>
       <c r="G1203" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -33332,7 +33332,7 @@
         <v>12.5</v>
       </c>
       <c r="G1204" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -33358,7 +33358,7 @@
         <v>12.5</v>
       </c>
       <c r="G1205" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -33384,7 +33384,7 @@
         <v>12.5</v>
       </c>
       <c r="G1206" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -33410,7 +33410,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1207" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -33436,7 +33436,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1208" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -33462,7 +33462,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1209" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -33488,7 +33488,7 @@
         <v>12.5</v>
       </c>
       <c r="G1210" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -33514,7 +33514,7 @@
         <v>13</v>
       </c>
       <c r="G1211" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -33540,7 +33540,7 @@
         <v>13</v>
       </c>
       <c r="G1212" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -33566,7 +33566,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1213" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -33592,7 +33592,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1214" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -33618,7 +33618,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G1215" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -33644,7 +33644,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1216" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -33670,7 +33670,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1217" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -33696,7 +33696,7 @@
         <v>12</v>
       </c>
       <c r="G1218" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -33722,7 +33722,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1219" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -33748,7 +33748,7 @@
         <v>11.5</v>
       </c>
       <c r="G1220" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -33774,7 +33774,7 @@
         <v>11.5</v>
       </c>
       <c r="G1221" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -33800,7 +33800,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1222" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -33826,7 +33826,7 @@
         <v>12.5</v>
       </c>
       <c r="G1223" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -33852,7 +33852,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1224" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -33878,7 +33878,7 @@
         <v>12.5</v>
       </c>
       <c r="G1225" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -33904,7 +33904,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1226" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -33930,7 +33930,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1227" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -33956,7 +33956,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1228" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -33982,7 +33982,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1229" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -34008,7 +34008,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1230" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -34034,7 +34034,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1231" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -34060,7 +34060,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1232" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -34086,7 +34086,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1233" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -34112,7 +34112,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1234" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -34138,7 +34138,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1235" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -34164,7 +34164,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1236" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -34190,7 +34190,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1237" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -34216,7 +34216,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1238" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -34242,7 +34242,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1239" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -34268,7 +34268,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1240" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -34294,7 +34294,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1241" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -34320,7 +34320,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1242" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -34346,7 +34346,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1243" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -34372,7 +34372,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1244" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -34398,7 +34398,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1245" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -34424,7 +34424,7 @@
         <v>12</v>
       </c>
       <c r="G1246" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -34450,7 +34450,7 @@
         <v>12</v>
       </c>
       <c r="G1247" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -34476,7 +34476,7 @@
         <v>12</v>
       </c>
       <c r="G1248" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -34502,7 +34502,7 @@
         <v>12</v>
       </c>
       <c r="G1249" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -34528,7 +34528,7 @@
         <v>12</v>
       </c>
       <c r="G1250" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -34554,7 +34554,7 @@
         <v>12</v>
       </c>
       <c r="G1251" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -34580,7 +34580,7 @@
         <v>12</v>
       </c>
       <c r="G1252" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -34606,7 +34606,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1253" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -34632,7 +34632,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1254" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -34658,7 +34658,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1255" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -34684,7 +34684,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1256" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -34710,7 +34710,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1257" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -34736,7 +34736,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1258" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -34762,7 +34762,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1259" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -34788,7 +34788,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1260" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -34814,7 +34814,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1261" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -34840,7 +34840,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1262" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -34866,7 +34866,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1263" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -34892,7 +34892,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1264" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -34918,7 +34918,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1265" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -34944,7 +34944,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1266" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -34970,7 +34970,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1267" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1267" t="s">
         <v>9</v>
@@ -34996,7 +34996,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1268" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1268" t="s">
         <v>9</v>
@@ -35022,7 +35022,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1269" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1269" t="s">
         <v>9</v>
@@ -35048,7 +35048,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1270" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1270" t="s">
         <v>9</v>
@@ -35074,7 +35074,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1271" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1271" t="s">
         <v>9</v>
@@ -35100,7 +35100,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1272" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1272" t="s">
         <v>9</v>
@@ -35126,7 +35126,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1273" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1273" t="s">
         <v>9</v>
@@ -35152,7 +35152,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1274" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1274" t="s">
         <v>9</v>
@@ -35178,7 +35178,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1275" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1275" t="s">
         <v>9</v>
@@ -35204,7 +35204,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1276" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1276" t="s">
         <v>9</v>
@@ -35230,7 +35230,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1277" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1277" t="s">
         <v>9</v>
@@ -35256,7 +35256,7 @@
         <v>11.5</v>
       </c>
       <c r="G1278" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1278" t="s">
         <v>9</v>
@@ -35282,7 +35282,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1279" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1279" t="s">
         <v>9</v>
@@ -35308,7 +35308,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1280" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1280" t="s">
         <v>9</v>
@@ -35334,7 +35334,7 @@
         <v>11.5</v>
       </c>
       <c r="G1281" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1281" t="s">
         <v>9</v>
@@ -35360,7 +35360,7 @@
         <v>11.5</v>
       </c>
       <c r="G1282" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1282" t="s">
         <v>9</v>
@@ -35386,7 +35386,7 @@
         <v>11.5</v>
       </c>
       <c r="G1283" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1283" t="s">
         <v>9</v>
@@ -35412,7 +35412,7 @@
         <v>11.5</v>
       </c>
       <c r="G1284" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1284" t="s">
         <v>9</v>
@@ -35438,7 +35438,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1285" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1285" t="s">
         <v>9</v>
@@ -35464,7 +35464,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1286" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1286" t="s">
         <v>9</v>
@@ -35490,7 +35490,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1287" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1287" t="s">
         <v>9</v>
@@ -35516,7 +35516,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1288" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1288" t="s">
         <v>9</v>
@@ -35542,7 +35542,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1289" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1289" t="s">
         <v>9</v>
@@ -35568,7 +35568,7 @@
         <v>11.5</v>
       </c>
       <c r="G1290" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1290" t="s">
         <v>9</v>
@@ -35594,7 +35594,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1291" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1291" t="s">
         <v>9</v>
@@ -35620,7 +35620,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1292" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1292" t="s">
         <v>9</v>
@@ -35646,7 +35646,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1293" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1293" t="s">
         <v>9</v>
@@ -35672,7 +35672,7 @@
         <v>12</v>
       </c>
       <c r="G1294" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1294" t="s">
         <v>9</v>
@@ -35698,7 +35698,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G1295" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1295" t="s">
         <v>9</v>
@@ -35724,7 +35724,7 @@
         <v>12</v>
       </c>
       <c r="G1296" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1296" t="s">
         <v>9</v>
@@ -35750,7 +35750,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G1297" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1297" t="s">
         <v>9</v>
@@ -35776,7 +35776,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1298" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1298" t="s">
         <v>9</v>
@@ -35802,7 +35802,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G1299" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1299" t="s">
         <v>9</v>
@@ -35828,7 +35828,7 @@
         <v>13</v>
       </c>
       <c r="G1300" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1300" t="s">
         <v>9</v>
@@ -35854,7 +35854,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1301" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1301" t="s">
         <v>9</v>
@@ -35880,7 +35880,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G1302" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1302" t="s">
         <v>9</v>
@@ -35906,7 +35906,7 @@
         <v>14.5</v>
       </c>
       <c r="G1303" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1303" t="s">
         <v>9</v>
@@ -35932,7 +35932,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1304" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1304" t="s">
         <v>9</v>
@@ -35958,7 +35958,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1305" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1305" t="s">
         <v>9</v>
@@ -35984,7 +35984,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1306" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1306" t="s">
         <v>9</v>
@@ -36010,7 +36010,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1307" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1307" t="s">
         <v>9</v>
@@ -36036,7 +36036,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1308" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1308" t="s">
         <v>9</v>
@@ -36062,7 +36062,7 @@
         <v>14.5</v>
       </c>
       <c r="G1309" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1309" t="s">
         <v>9</v>
@@ -36088,7 +36088,7 @@
         <v>15</v>
       </c>
       <c r="G1310" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1310" t="s">
         <v>9</v>
@@ -36114,7 +36114,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1311" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1311" t="s">
         <v>9</v>
@@ -36140,7 +36140,7 @@
         <v>15</v>
       </c>
       <c r="G1312" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1312" t="s">
         <v>9</v>
@@ -36166,7 +36166,7 @@
         <v>14.5</v>
       </c>
       <c r="G1313" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1313" t="s">
         <v>9</v>
@@ -36192,7 +36192,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1314" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1314" t="s">
         <v>9</v>
@@ -36218,7 +36218,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1315" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1315" t="s">
         <v>9</v>
@@ -36244,7 +36244,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1316" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1316" t="s">
         <v>9</v>
@@ -36270,7 +36270,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1317" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H1317" t="s">
         <v>9</v>
@@ -36296,7 +36296,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1318" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1318" t="s">
         <v>9</v>
@@ -36322,7 +36322,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1319" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1319" t="s">
         <v>9</v>
@@ -36348,7 +36348,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1320" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1320" t="s">
         <v>9</v>
@@ -36374,7 +36374,7 @@
         <v>14.5</v>
       </c>
       <c r="G1321" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1321" t="s">
         <v>9</v>
@@ -36400,7 +36400,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1322" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1322" t="s">
         <v>9</v>
@@ -36426,7 +36426,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1323" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1323" t="s">
         <v>9</v>
@@ -36452,7 +36452,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1324" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1324" t="s">
         <v>9</v>
@@ -36478,7 +36478,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1325" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1325" t="s">
         <v>9</v>
@@ -36504,7 +36504,7 @@
         <v>14.5</v>
       </c>
       <c r="G1326" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1326" t="s">
         <v>9</v>
@@ -36530,7 +36530,7 @@
         <v>14.5</v>
       </c>
       <c r="G1327" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1327" t="s">
         <v>9</v>
@@ -36556,7 +36556,7 @@
         <v>14.5</v>
       </c>
       <c r="G1328" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1328" t="s">
         <v>9</v>
@@ -36582,7 +36582,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1329" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1329" t="s">
         <v>9</v>
@@ -36608,7 +36608,7 @@
         <v>14.5</v>
       </c>
       <c r="G1330" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1330" t="s">
         <v>9</v>
@@ -36634,7 +36634,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1331" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1331" t="s">
         <v>9</v>
@@ -36660,7 +36660,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1332" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1332" t="s">
         <v>9</v>
@@ -36686,7 +36686,7 @@
         <v>15</v>
       </c>
       <c r="G1333" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1333" t="s">
         <v>9</v>
@@ -36712,7 +36712,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1334" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1334" t="s">
         <v>9</v>
@@ -36738,7 +36738,7 @@
         <v>15</v>
       </c>
       <c r="G1335" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1335" t="s">
         <v>9</v>
@@ -36764,7 +36764,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1336" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1336" t="s">
         <v>9</v>
@@ -36790,7 +36790,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1337" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1337" t="s">
         <v>9</v>
@@ -36816,7 +36816,7 @@
         <v>14.5</v>
       </c>
       <c r="G1338" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1338" t="s">
         <v>9</v>
@@ -36842,7 +36842,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1339" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1339" t="s">
         <v>9</v>
@@ -36868,7 +36868,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1340" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1340" t="s">
         <v>9</v>
@@ -36894,7 +36894,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1341" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1341" t="s">
         <v>9</v>
@@ -36920,7 +36920,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1342" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1342" t="s">
         <v>9</v>
@@ -36946,7 +36946,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1343" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1343" t="s">
         <v>9</v>
@@ -36972,7 +36972,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1344" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1344" t="s">
         <v>9</v>
@@ -36998,7 +36998,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1345" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1345" t="s">
         <v>9</v>
@@ -37024,7 +37024,7 @@
         <v>14.8999996185303</v>
       </c>
       <c r="G1346" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1346" t="s">
         <v>9</v>
@@ -37050,7 +37050,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1347" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1347" t="s">
         <v>9</v>
@@ -37076,7 +37076,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1348" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1348" t="s">
         <v>9</v>
@@ -37102,7 +37102,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1349" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1349" t="s">
         <v>9</v>
@@ -37128,7 +37128,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1350" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1350" t="s">
         <v>9</v>
@@ -37154,7 +37154,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1351" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1351" t="s">
         <v>9</v>
@@ -37180,7 +37180,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1352" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1352" t="s">
         <v>9</v>
@@ -37206,7 +37206,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1353" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1353" t="s">
         <v>9</v>
@@ -37232,7 +37232,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1354" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1354" t="s">
         <v>9</v>
@@ -37258,7 +37258,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1355" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1355" t="s">
         <v>9</v>
@@ -37284,7 +37284,7 @@
         <v>15.5</v>
       </c>
       <c r="G1356" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1356" t="s">
         <v>9</v>
@@ -37310,7 +37310,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1357" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1357" t="s">
         <v>9</v>
@@ -37336,7 +37336,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1358" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1358" t="s">
         <v>9</v>
@@ -37362,7 +37362,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1359" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1359" t="s">
         <v>9</v>
@@ -37388,7 +37388,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1360" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1360" t="s">
         <v>9</v>
@@ -37414,7 +37414,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1361" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1361" t="s">
         <v>9</v>
@@ -37440,7 +37440,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1362" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1362" t="s">
         <v>9</v>
@@ -37466,7 +37466,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1363" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1363" t="s">
         <v>9</v>
@@ -37492,7 +37492,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1364" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1364" t="s">
         <v>9</v>
@@ -37518,7 +37518,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1365" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1365" t="s">
         <v>9</v>
@@ -37544,7 +37544,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1366" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1366" t="s">
         <v>9</v>
@@ -37570,7 +37570,7 @@
         <v>17</v>
       </c>
       <c r="G1367" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1367" t="s">
         <v>9</v>
@@ -37596,7 +37596,7 @@
         <v>17</v>
       </c>
       <c r="G1368" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1368" t="s">
         <v>9</v>
@@ -37622,7 +37622,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1369" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1369" t="s">
         <v>9</v>
@@ -37648,7 +37648,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1370" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1370" t="s">
         <v>9</v>
@@ -37674,7 +37674,7 @@
         <v>16.5</v>
       </c>
       <c r="G1371" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H1371" t="s">
         <v>9</v>
@@ -37700,7 +37700,7 @@
         <v>16.5</v>
       </c>
       <c r="G1372" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H1372" t="s">
         <v>9</v>
@@ -37726,7 +37726,7 @@
         <v>16.5</v>
       </c>
       <c r="G1373" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H1373" t="s">
         <v>9</v>
@@ -37752,7 +37752,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1374" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H1374" t="s">
         <v>9</v>
@@ -37778,7 +37778,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1375" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1375" t="s">
         <v>9</v>
@@ -37804,7 +37804,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1376" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1376" t="s">
         <v>9</v>
@@ -37830,7 +37830,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1377" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1377" t="s">
         <v>9</v>
@@ -37856,7 +37856,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1378" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1378" t="s">
         <v>9</v>
@@ -37882,7 +37882,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1379" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1379" t="s">
         <v>9</v>
@@ -37908,7 +37908,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1380" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H1380" t="s">
         <v>9</v>
@@ -37934,7 +37934,7 @@
         <v>15.5</v>
       </c>
       <c r="G1381" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H1381" t="s">
         <v>9</v>
@@ -37960,7 +37960,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1382" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1382" t="s">
         <v>9</v>
@@ -37986,7 +37986,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1383" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1383" t="s">
         <v>9</v>
@@ -38012,7 +38012,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1384" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1384" t="s">
         <v>9</v>
@@ -38038,7 +38038,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1385" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1385" t="s">
         <v>9</v>
@@ -38064,7 +38064,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1386" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1386" t="s">
         <v>9</v>
@@ -38090,7 +38090,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1387" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1387" t="s">
         <v>9</v>
@@ -38116,7 +38116,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1388" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1388" t="s">
         <v>9</v>
@@ -38142,7 +38142,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1389" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1389" t="s">
         <v>9</v>
@@ -38168,7 +38168,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1390" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1390" t="s">
         <v>9</v>
@@ -38194,7 +38194,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1391" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1391" t="s">
         <v>9</v>
@@ -38220,7 +38220,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1392" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1392" t="s">
         <v>9</v>
@@ -38246,7 +38246,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1393" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1393" t="s">
         <v>9</v>
@@ -38272,7 +38272,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1394" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1394" t="s">
         <v>9</v>
@@ -38298,7 +38298,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1395" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1395" t="s">
         <v>9</v>
@@ -38324,7 +38324,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1396" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1396" t="s">
         <v>9</v>
@@ -38350,7 +38350,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1397" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1397" t="s">
         <v>9</v>
@@ -38376,7 +38376,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1398" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1398" t="s">
         <v>9</v>
@@ -38402,7 +38402,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1399" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1399" t="s">
         <v>9</v>
@@ -38428,7 +38428,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1400" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1400" t="s">
         <v>9</v>
@@ -38454,7 +38454,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1401" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1401" t="s">
         <v>9</v>
@@ -38480,7 +38480,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1402" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1402" t="s">
         <v>9</v>
@@ -38506,7 +38506,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1403" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1403" t="s">
         <v>9</v>
@@ -38532,7 +38532,7 @@
         <v>17.5</v>
       </c>
       <c r="G1404" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1404" t="s">
         <v>9</v>
@@ -38558,7 +38558,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1405" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1405" t="s">
         <v>9</v>
@@ -38584,7 +38584,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1406" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1406" t="s">
         <v>9</v>
@@ -38610,7 +38610,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1407" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1407" t="s">
         <v>9</v>
@@ -38636,7 +38636,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1408" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1408" t="s">
         <v>9</v>
@@ -38662,7 +38662,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G1409" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1409" t="s">
         <v>9</v>
@@ -38688,7 +38688,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1410" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1410" t="s">
         <v>9</v>
@@ -38714,7 +38714,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1411" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1411" t="s">
         <v>9</v>
@@ -38740,7 +38740,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1412" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1412" t="s">
         <v>9</v>
@@ -38766,7 +38766,7 @@
         <v>19</v>
       </c>
       <c r="G1413" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1413" t="s">
         <v>9</v>
@@ -38792,7 +38792,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1414" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1414" t="s">
         <v>9</v>
@@ -38818,7 +38818,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1415" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1415" t="s">
         <v>9</v>
@@ -38844,7 +38844,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1416" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1416" t="s">
         <v>9</v>
@@ -38870,7 +38870,7 @@
         <v>20</v>
       </c>
       <c r="G1417" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1417" t="s">
         <v>9</v>
@@ -38896,7 +38896,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1418" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1418" t="s">
         <v>9</v>
@@ -38922,7 +38922,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1419" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1419" t="s">
         <v>9</v>
@@ -38948,7 +38948,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1420" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1420" t="s">
         <v>9</v>
@@ -38974,7 +38974,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1421" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -39000,7 +39000,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1422" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -39026,7 +39026,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1423" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -39052,7 +39052,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1424" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -39078,7 +39078,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1425" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1425" t="s">
         <v>9</v>
@@ -39104,7 +39104,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1426" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1426" t="s">
         <v>9</v>
@@ -39130,7 +39130,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1427" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39156,7 +39156,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1428" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39182,7 +39182,7 @@
         <v>21</v>
       </c>
       <c r="G1429" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39208,7 +39208,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1430" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39234,7 +39234,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1431" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1431" t="s">
         <v>9</v>
@@ -39260,7 +39260,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1432" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1432" t="s">
         <v>9</v>
@@ -39286,7 +39286,7 @@
         <v>24</v>
       </c>
       <c r="G1433" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39312,7 +39312,7 @@
         <v>24</v>
       </c>
       <c r="G1434" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39338,7 +39338,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G1435" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1435" t="s">
         <v>9</v>
@@ -39364,7 +39364,7 @@
         <v>25</v>
       </c>
       <c r="G1436" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1436" t="s">
         <v>9</v>
@@ -39390,7 +39390,7 @@
         <v>25</v>
       </c>
       <c r="G1437" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39416,7 +39416,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1438" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39442,7 +39442,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1439" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39468,7 +39468,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1440" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39494,7 +39494,7 @@
         <v>25</v>
       </c>
       <c r="G1441" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39520,7 +39520,7 @@
         <v>25</v>
       </c>
       <c r="G1442" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39546,7 +39546,7 @@
         <v>25</v>
       </c>
       <c r="G1443" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39572,7 +39572,7 @@
         <v>25</v>
       </c>
       <c r="G1444" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39598,7 +39598,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1445" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39624,7 +39624,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1446" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39650,7 +39650,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1447" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39676,7 +39676,7 @@
         <v>26</v>
       </c>
       <c r="G1448" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -39702,7 +39702,7 @@
         <v>26</v>
       </c>
       <c r="G1449" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39728,7 +39728,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1450" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39754,7 +39754,7 @@
         <v>27</v>
       </c>
       <c r="G1451" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39780,7 +39780,7 @@
         <v>27</v>
       </c>
       <c r="G1452" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1452" t="s">
         <v>9</v>
@@ -39806,7 +39806,7 @@
         <v>26</v>
       </c>
       <c r="G1453" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39832,7 +39832,7 @@
         <v>26</v>
       </c>
       <c r="G1454" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39858,7 +39858,7 @@
         <v>26</v>
       </c>
       <c r="G1455" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1455" t="s">
         <v>9</v>
@@ -39884,7 +39884,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1456" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39910,7 +39910,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1457" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39936,7 +39936,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1458" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39962,7 +39962,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1459" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39988,7 +39988,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1460" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1460" t="s">
         <v>9</v>
@@ -40014,7 +40014,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1461" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -40040,7 +40040,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1462" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -40066,7 +40066,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1463" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -40092,7 +40092,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1464" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -40118,7 +40118,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1465" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40144,7 +40144,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1466" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40170,7 +40170,7 @@
         <v>25</v>
       </c>
       <c r="G1467" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40196,7 +40196,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1468" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40222,7 +40222,7 @@
         <v>25</v>
       </c>
       <c r="G1469" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40248,7 +40248,7 @@
         <v>26</v>
       </c>
       <c r="G1470" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40274,7 +40274,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1471" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40300,7 +40300,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1472" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40326,7 +40326,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1473" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40352,7 +40352,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1474" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40378,7 +40378,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1475" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40404,7 +40404,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1476" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40430,7 +40430,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1477" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40456,7 +40456,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1478" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40482,7 +40482,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1479" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1479" t="s">
         <v>9</v>
@@ -40508,7 +40508,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1480" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -40534,7 +40534,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1481" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -40560,7 +40560,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1482" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -40586,7 +40586,7 @@
         <v>25</v>
       </c>
       <c r="G1483" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -40612,7 +40612,7 @@
         <v>25</v>
       </c>
       <c r="G1484" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -40638,7 +40638,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1485" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -40664,7 +40664,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1486" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -40690,7 +40690,7 @@
         <v>26</v>
       </c>
       <c r="G1487" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -40716,7 +40716,7 @@
         <v>26</v>
       </c>
       <c r="G1488" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40742,7 +40742,7 @@
         <v>26</v>
       </c>
       <c r="G1489" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40768,7 +40768,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1490" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40794,7 +40794,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1491" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40820,7 +40820,7 @@
         <v>27</v>
       </c>
       <c r="G1492" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1492" t="s">
         <v>9</v>
@@ -40846,7 +40846,7 @@
         <v>27</v>
       </c>
       <c r="G1493" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40872,7 +40872,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1494" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40898,7 +40898,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1495" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40924,7 +40924,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1496" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40950,7 +40950,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1497" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40976,7 +40976,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1498" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -41002,7 +41002,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1499" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -41028,7 +41028,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1500" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -41054,7 +41054,7 @@
         <v>33</v>
       </c>
       <c r="G1501" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -41080,7 +41080,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1502" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -41106,7 +41106,7 @@
         <v>33</v>
       </c>
       <c r="G1503" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -41132,7 +41132,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1504" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41158,7 +41158,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1505" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41184,7 +41184,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G1506" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41210,7 +41210,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G1507" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41236,7 +41236,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G1508" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41262,7 +41262,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G1509" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41288,7 +41288,7 @@
         <v>36.4000015258789</v>
       </c>
       <c r="G1510" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41314,7 +41314,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1511" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41340,7 +41340,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1512" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41366,7 +41366,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1513" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41392,7 +41392,7 @@
         <v>29</v>
       </c>
       <c r="G1514" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41418,7 +41418,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1515" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41444,7 +41444,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1516" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41470,7 +41470,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1517" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41496,7 +41496,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1518" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41522,7 +41522,7 @@
         <v>29</v>
       </c>
       <c r="G1519" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41548,7 +41548,7 @@
         <v>29</v>
       </c>
       <c r="G1520" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41574,7 +41574,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1521" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41600,7 +41600,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1522" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41626,7 +41626,7 @@
         <v>32</v>
       </c>
       <c r="G1523" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -41652,7 +41652,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1524" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -41678,7 +41678,7 @@
         <v>32</v>
       </c>
       <c r="G1525" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -41704,7 +41704,7 @@
         <v>31</v>
       </c>
       <c r="G1526" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41730,7 +41730,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1527" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41756,7 +41756,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1528" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41782,7 +41782,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1529" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41808,7 +41808,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1530" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41834,7 +41834,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1531" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41860,7 +41860,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1532" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41886,7 +41886,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1533" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41912,7 +41912,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1534" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41938,7 +41938,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1535" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41964,7 +41964,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1536" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41990,7 +41990,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1537" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -42016,7 +42016,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1538" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -42042,7 +42042,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1539" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -42068,7 +42068,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1540" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -42094,7 +42094,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1541" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -42120,7 +42120,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1542" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42146,7 +42146,7 @@
         <v>28</v>
       </c>
       <c r="G1543" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42172,7 +42172,7 @@
         <v>28</v>
       </c>
       <c r="G1544" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42198,7 +42198,7 @@
         <v>28</v>
       </c>
       <c r="G1545" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42224,7 +42224,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1546" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42250,7 +42250,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1547" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42276,7 +42276,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1548" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42302,7 +42302,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1549" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42328,7 +42328,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1550" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42354,7 +42354,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1551" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42380,7 +42380,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1552" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42406,7 +42406,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1553" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42432,7 +42432,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1554" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42458,7 +42458,7 @@
         <v>30</v>
       </c>
       <c r="G1555" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42484,7 +42484,7 @@
         <v>30</v>
       </c>
       <c r="G1556" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42510,7 +42510,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1557" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42536,7 +42536,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1558" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42562,7 +42562,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1559" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42588,7 +42588,7 @@
         <v>30</v>
       </c>
       <c r="G1560" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42614,7 +42614,7 @@
         <v>30</v>
       </c>
       <c r="G1561" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42640,7 +42640,7 @@
         <v>30</v>
       </c>
       <c r="G1562" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42666,7 +42666,7 @@
         <v>30</v>
       </c>
       <c r="G1563" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -42692,7 +42692,7 @@
         <v>29</v>
       </c>
       <c r="G1564" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42718,7 +42718,7 @@
         <v>29</v>
       </c>
       <c r="G1565" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42744,7 +42744,7 @@
         <v>29</v>
       </c>
       <c r="G1566" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42770,7 +42770,7 @@
         <v>30</v>
       </c>
       <c r="G1567" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42796,7 +42796,7 @@
         <v>30</v>
       </c>
       <c r="G1568" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42822,7 +42822,7 @@
         <v>31</v>
       </c>
       <c r="G1569" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42848,7 +42848,7 @@
         <v>31</v>
       </c>
       <c r="G1570" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42874,7 +42874,7 @@
         <v>31</v>
       </c>
       <c r="G1571" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42900,7 +42900,7 @@
         <v>32</v>
       </c>
       <c r="G1572" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42926,7 +42926,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1573" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42952,7 +42952,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1574" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42978,7 +42978,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1575" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -43004,7 +43004,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1576" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -43030,7 +43030,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1577" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -43056,7 +43056,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1578" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -43082,7 +43082,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1579" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -43108,7 +43108,7 @@
         <v>31</v>
       </c>
       <c r="G1580" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -43134,7 +43134,7 @@
         <v>31</v>
       </c>
       <c r="G1581" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43160,7 +43160,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1582" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43186,7 +43186,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1583" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43212,7 +43212,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1584" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43238,7 +43238,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1585" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43264,7 +43264,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1586" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43290,7 +43290,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1587" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43316,7 +43316,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1588" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43342,7 +43342,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1589" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43368,7 +43368,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1590" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43394,7 +43394,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1591" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43420,7 +43420,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1592" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43446,7 +43446,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1593" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43472,7 +43472,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1594" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43498,7 +43498,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1595" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43524,7 +43524,7 @@
         <v>33</v>
       </c>
       <c r="G1596" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43550,7 +43550,7 @@
         <v>33</v>
       </c>
       <c r="G1597" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43576,7 +43576,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1598" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -43602,7 +43602,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1599" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43628,7 +43628,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1600" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -43654,7 +43654,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1601" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -43680,7 +43680,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1602" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -43706,7 +43706,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G1603" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43732,7 +43732,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1604" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43758,7 +43758,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1605" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43784,7 +43784,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1606" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43810,7 +43810,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1607" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43836,7 +43836,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1608" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43862,7 +43862,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1609" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43888,7 +43888,7 @@
         <v>32</v>
       </c>
       <c r="G1610" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43914,7 +43914,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1611" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43940,7 +43940,7 @@
         <v>35</v>
       </c>
       <c r="G1612" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43966,7 +43966,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1613" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43992,7 +43992,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1614" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -44018,7 +44018,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1615" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -44044,7 +44044,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1616" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -44070,7 +44070,7 @@
         <v>33</v>
       </c>
       <c r="G1617" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -44096,7 +44096,7 @@
         <v>34</v>
       </c>
       <c r="G1618" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -44122,7 +44122,7 @@
         <v>34</v>
       </c>
       <c r="G1619" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44148,7 +44148,7 @@
         <v>34</v>
       </c>
       <c r="G1620" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44174,7 +44174,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1621" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44200,7 +44200,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1622" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44226,7 +44226,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1623" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44252,7 +44252,7 @@
         <v>33</v>
       </c>
       <c r="G1624" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44278,7 +44278,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1625" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44304,7 +44304,7 @@
         <v>34</v>
       </c>
       <c r="G1626" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44330,7 +44330,7 @@
         <v>34</v>
       </c>
       <c r="G1627" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44356,7 +44356,7 @@
         <v>34</v>
       </c>
       <c r="G1628" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44382,7 +44382,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1629" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44408,7 +44408,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1630" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44434,7 +44434,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1631" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44460,7 +44460,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1632" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44486,7 +44486,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1633" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44512,7 +44512,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1634" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44538,7 +44538,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1635" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44564,7 +44564,7 @@
         <v>34</v>
       </c>
       <c r="G1636" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44590,7 +44590,7 @@
         <v>34</v>
       </c>
       <c r="G1637" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44616,7 +44616,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1638" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44642,7 +44642,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1639" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44668,7 +44668,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1640" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44694,7 +44694,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1641" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44772,7 +44772,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1644" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44798,7 +44798,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1645" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44824,7 +44824,7 @@
         <v>34</v>
       </c>
       <c r="G1646" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44850,7 +44850,7 @@
         <v>34</v>
       </c>
       <c r="G1647" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44876,7 +44876,7 @@
         <v>34</v>
       </c>
       <c r="G1648" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44902,7 +44902,7 @@
         <v>34</v>
       </c>
       <c r="G1649" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -45344,7 +45344,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1666" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45994,7 +45994,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1691" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46020,7 +46020,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1692" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46046,7 +46046,7 @@
         <v>34</v>
       </c>
       <c r="G1693" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -46072,7 +46072,7 @@
         <v>34</v>
       </c>
       <c r="G1694" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -46098,7 +46098,7 @@
         <v>34</v>
       </c>
       <c r="G1695" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -46254,7 +46254,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1701" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46280,7 +46280,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1702" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46306,7 +46306,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1703" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46358,7 +46358,7 @@
         <v>34</v>
       </c>
       <c r="G1705" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -61420,7 +61420,7 @@
     </row>
     <row r="2285">
       <c r="A2285" s="1" t="n">
-        <v>45986.6611574074</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2285" t="n">
         <v>250</v>
@@ -61441,6 +61441,32 @@
         <v>538</v>
       </c>
       <c r="H2285" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" s="1" t="n">
+        <v>45987.6634837963</v>
+      </c>
+      <c r="B2286" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C2286" t="n">
+        <v>37.4000015258789</v>
+      </c>
+      <c r="D2286" t="n">
+        <v>37</v>
+      </c>
+      <c r="E2286" t="n">
+        <v>37.4000015258789</v>
+      </c>
+      <c r="F2286" t="n">
+        <v>37</v>
+      </c>
+      <c r="G2286" t="s">
+        <v>554</v>
+      </c>
+      <c r="H2286" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46539187431335</t>
+    <t xml:space="preserve">2.46539163589478</t>
   </si>
   <si>
     <t xml:space="preserve">FPE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42625856399536</t>
+    <t xml:space="preserve">2.42625832557678</t>
   </si>
   <si>
     <t xml:space="preserve">2.43408489227295</t>
@@ -53,52 +53,52 @@
     <t xml:space="preserve">2.41060543060303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45756530761719</t>
+    <t xml:space="preserve">2.45756506919861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39495182037354</t>
+    <t xml:space="preserve">2.39495158195496</t>
   </si>
   <si>
     <t xml:space="preserve">2.33233880996704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41843199729919</t>
+    <t xml:space="preserve">2.41843175888062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35581851005554</t>
+    <t xml:space="preserve">2.35581874847412</t>
   </si>
   <si>
     <t xml:space="preserve">2.37147212028503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50452494621277</t>
+    <t xml:space="preserve">2.50452518463135</t>
   </si>
   <si>
     <t xml:space="preserve">2.36364531517029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44973874092102</t>
+    <t xml:space="preserve">2.44973850250244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37303781509399</t>
+    <t xml:space="preserve">2.37303733825684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34955739974976</t>
+    <t xml:space="preserve">2.34955763816833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46382689476013</t>
+    <t xml:space="preserve">2.46382641792297</t>
   </si>
   <si>
     <t xml:space="preserve">2.38712525367737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45443439483643</t>
+    <t xml:space="preserve">2.45443415641785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34799194335938</t>
+    <t xml:space="preserve">2.34799218177795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48104524612427</t>
+    <t xml:space="preserve">2.48104500770569</t>
   </si>
   <si>
     <t xml:space="preserve">2.3792986869812</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">2.38556003570557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4419116973877</t>
+    <t xml:space="preserve">2.44191145896912</t>
   </si>
   <si>
     <t xml:space="preserve">2.78002262115479</t>
@@ -116,31 +116,31 @@
     <t xml:space="preserve">3.36702084541321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62530016899109</t>
+    <t xml:space="preserve">3.62529993057251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3106689453125</t>
+    <t xml:space="preserve">3.31066918373108</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25588226318359</t>
+    <t xml:space="preserve">3.25588250160217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20266103744507</t>
+    <t xml:space="preserve">3.20266151428223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05238962173462</t>
+    <t xml:space="preserve">3.05238938331604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09152269363403</t>
+    <t xml:space="preserve">3.09152317047119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04456305503845</t>
+    <t xml:space="preserve">3.04456329345703</t>
   </si>
   <si>
     <t xml:space="preserve">3.03673672676086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03830146789551</t>
+    <t xml:space="preserve">3.03830194473267</t>
   </si>
   <si>
     <t xml:space="preserve">3.15413618087769</t>
@@ -158,37 +158,37 @@
     <t xml:space="preserve">3.57677507400513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5219886302948</t>
+    <t xml:space="preserve">3.52198815345764</t>
   </si>
   <si>
     <t xml:space="preserve">3.40458869934082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59242820739746</t>
+    <t xml:space="preserve">3.5924277305603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58460116386414</t>
+    <t xml:space="preserve">3.58460092544556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67852139472961</t>
+    <t xml:space="preserve">3.67852091789246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60025501251221</t>
+    <t xml:space="preserve">3.60025453567505</t>
   </si>
   <si>
     <t xml:space="preserve">3.59555888175964</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632231712341</t>
+    <t xml:space="preserve">3.32632207870483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29501581192017</t>
+    <t xml:space="preserve">3.29501533508301</t>
   </si>
   <si>
     <t xml:space="preserve">3.37484693527222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38267374038696</t>
+    <t xml:space="preserve">3.38267397880554</t>
   </si>
   <si>
     <t xml:space="preserve">3.44372224807739</t>
@@ -200,43 +200,43 @@
     <t xml:space="preserve">3.47972440719604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42650294303894</t>
+    <t xml:space="preserve">3.4265034198761</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41241550445557</t>
+    <t xml:space="preserve">3.41241526603699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24022889137268</t>
+    <t xml:space="preserve">3.2402286529541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21048831939697</t>
+    <t xml:space="preserve">3.21048808097839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28405833244324</t>
+    <t xml:space="preserve">3.28405857086182</t>
   </si>
   <si>
     <t xml:space="preserve">3.16196274757385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20892262458801</t>
+    <t xml:space="preserve">3.20892238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13848328590393</t>
+    <t xml:space="preserve">3.13848304748535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23240280151367</t>
+    <t xml:space="preserve">3.23240256309509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31849551200867</t>
+    <t xml:space="preserve">3.31849527359009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27623176574707</t>
+    <t xml:space="preserve">3.27623152732849</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18857336044312</t>
+    <t xml:space="preserve">3.18857288360596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14317870140076</t>
+    <t xml:space="preserve">3.14317846298218</t>
   </si>
   <si>
     <t xml:space="preserve">3.11500287055969</t>
@@ -251,34 +251,34 @@
     <t xml:space="preserve">3.06021642684937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90368390083313</t>
+    <t xml:space="preserve">2.90368366241455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8958568572998</t>
+    <t xml:space="preserve">2.89585709571838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82854819297791</t>
+    <t xml:space="preserve">2.82854795455933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83637452125549</t>
+    <t xml:space="preserve">2.83637475967407</t>
   </si>
   <si>
     <t xml:space="preserve">2.90994477272034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491208076477</t>
+    <t xml:space="preserve">3.06491231918335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13065600395203</t>
+    <t xml:space="preserve">3.13065648078918</t>
   </si>
   <si>
     <t xml:space="preserve">3.14474415779114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.213618516922</t>
+    <t xml:space="preserve">3.21361827850342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2856240272522</t>
+    <t xml:space="preserve">3.28562355041504</t>
   </si>
   <si>
     <t xml:space="preserve">3.35919380187988</t>
@@ -287,28 +287,28 @@
     <t xml:space="preserve">3.36388993263245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91331958770752</t>
+    <t xml:space="preserve">3.91332006454468</t>
   </si>
   <si>
     <t xml:space="preserve">4.34378528594971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79381704330444</t>
+    <t xml:space="preserve">4.7938175201416</t>
   </si>
   <si>
     <t xml:space="preserve">5.47864818572998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09303951263428</t>
+    <t xml:space="preserve">6.09303903579712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41603517532349</t>
+    <t xml:space="preserve">5.41603565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71344709396362</t>
+    <t xml:space="preserve">5.71344804763794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56865406036377</t>
+    <t xml:space="preserve">5.56865453720093</t>
   </si>
   <si>
     <t xml:space="preserve">5.41994905471802</t>
@@ -317,46 +317,46 @@
     <t xml:space="preserve">5.16558265686035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94643688201904</t>
+    <t xml:space="preserve">4.94643640518188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70381164550781</t>
+    <t xml:space="preserve">4.70381116867065</t>
   </si>
   <si>
     <t xml:space="preserve">4.67641735076904</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00904989242554</t>
+    <t xml:space="preserve">5.0090503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55691432952881</t>
+    <t xml:space="preserve">5.55691480636597</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30646133422852</t>
+    <t xml:space="preserve">5.30646276473999</t>
   </si>
   <si>
     <t xml:space="preserve">5.22428274154663</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19688892364502</t>
+    <t xml:space="preserve">5.19688940048218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32211589813232</t>
+    <t xml:space="preserve">5.32211542129517</t>
   </si>
   <si>
     <t xml:space="preserve">5.47082138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36907577514648</t>
+    <t xml:space="preserve">5.36907529830933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29080963134766</t>
+    <t xml:space="preserve">5.2908091545105</t>
   </si>
   <si>
     <t xml:space="preserve">5.1734094619751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09514331817627</t>
+    <t xml:space="preserve">5.09514284133911</t>
   </si>
   <si>
     <t xml:space="preserve">5.22036933898926</t>
@@ -365,10 +365,10 @@
     <t xml:space="preserve">5.10296964645386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9933967590332</t>
+    <t xml:space="preserve">4.99339628219604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15384292602539</t>
+    <t xml:space="preserve">5.15384340286255</t>
   </si>
   <si>
     <t xml:space="preserve">4.9855694770813</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">4.7585973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77033710479736</t>
+    <t xml:space="preserve">4.77033758163452</t>
   </si>
   <si>
     <t xml:space="preserve">4.86425733566284</t>
@@ -386,28 +386,28 @@
     <t xml:space="preserve">4.88773727416992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83295059204102</t>
+    <t xml:space="preserve">4.83295154571533</t>
   </si>
   <si>
     <t xml:space="preserve">4.75468397140503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82903671264648</t>
+    <t xml:space="preserve">4.8290376663208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72337770462036</t>
+    <t xml:space="preserve">4.7233772277832</t>
   </si>
   <si>
     <t xml:space="preserve">4.68815755844116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78207731246948</t>
+    <t xml:space="preserve">4.78207778930664</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87599754333496</t>
+    <t xml:space="preserve">4.8759970664978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03644275665283</t>
+    <t xml:space="preserve">5.03644323348999</t>
   </si>
   <si>
     <t xml:space="preserve">4.92687034606934</t>
@@ -428,19 +428,19 @@
     <t xml:space="preserve">4.82121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69989824295044</t>
+    <t xml:space="preserve">4.69989728927612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69598388671875</t>
+    <t xml:space="preserve">4.69598436355591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90730333328247</t>
+    <t xml:space="preserve">4.90730381011963</t>
   </si>
   <si>
     <t xml:space="preserve">5.20471668243408</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43951463699341</t>
+    <t xml:space="preserve">5.43951559066772</t>
   </si>
   <si>
     <t xml:space="preserve">5.28298234939575</t>
@@ -449,10 +449,10 @@
     <t xml:space="preserve">5.24384880065918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36124849319458</t>
+    <t xml:space="preserve">5.36124801635742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40038204193115</t>
+    <t xml:space="preserve">5.40038251876831</t>
   </si>
   <si>
     <t xml:space="preserve">5.51778125762939</t>
@@ -461,13 +461,13 @@
     <t xml:space="preserve">5.63518095016479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96991634368896</t>
+    <t xml:space="preserve">4.96991682052612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93078374862671</t>
+    <t xml:space="preserve">4.93078327178955</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85251712799072</t>
+    <t xml:space="preserve">4.85251665115356</t>
   </si>
   <si>
     <t xml:space="preserve">5.12644958496094</t>
@@ -476,52 +476,52 @@
     <t xml:space="preserve">5.04818296432495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08731603622437</t>
+    <t xml:space="preserve">5.08731555938721</t>
   </si>
   <si>
     <t xml:space="preserve">5.59604787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26159715652466</t>
+    <t xml:space="preserve">5.26159763336182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42103910446167</t>
+    <t xml:space="preserve">5.42103958129883</t>
   </si>
   <si>
     <t xml:space="preserve">5.34131813049316</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22173643112183</t>
+    <t xml:space="preserve">5.22173690795898</t>
   </si>
   <si>
     <t xml:space="preserve">5.14201545715332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10215520858765</t>
+    <t xml:space="preserve">5.1021556854248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18187618255615</t>
+    <t xml:space="preserve">5.18187570571899</t>
   </si>
   <si>
     <t xml:space="preserve">5.38117933273315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30145835876465</t>
+    <t xml:space="preserve">5.30145788192749</t>
   </si>
   <si>
     <t xml:space="preserve">4.90285158157349</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50076103210449</t>
+    <t xml:space="preserve">5.50076150894165</t>
   </si>
   <si>
     <t xml:space="preserve">5.46090030670166</t>
   </si>
   <si>
-    <t xml:space="preserve">5.580482006073</t>
+    <t xml:space="preserve">5.58048152923584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54062128067017</t>
+    <t xml:space="preserve">5.54062175750732</t>
   </si>
   <si>
     <t xml:space="preserve">5.62034273147583</t>
@@ -530,16 +530,16 @@
     <t xml:space="preserve">4.94271278381348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98257255554199</t>
+    <t xml:space="preserve">4.98257350921631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82313108444214</t>
+    <t xml:space="preserve">4.82313060760498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06229448318481</t>
+    <t xml:space="preserve">5.06229496002197</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02243423461914</t>
+    <t xml:space="preserve">5.02243375778198</t>
   </si>
   <si>
     <t xml:space="preserve">4.74340963363647</t>
@@ -548,19 +548,19 @@
     <t xml:space="preserve">4.78326988220215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86299180984497</t>
+    <t xml:space="preserve">4.86299133300781</t>
   </si>
   <si>
     <t xml:space="preserve">5.73992443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81964540481567</t>
+    <t xml:space="preserve">5.81964588165283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70006370544434</t>
+    <t xml:space="preserve">5.70006418228149</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66020250320435</t>
+    <t xml:space="preserve">5.6602029800415</t>
   </si>
   <si>
     <t xml:space="preserve">5.77978467941284</t>
@@ -569,13 +569,13 @@
     <t xml:space="preserve">5.85950565338135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97908782958984</t>
+    <t xml:space="preserve">5.979088306427</t>
   </si>
   <si>
     <t xml:space="preserve">6.29797220230103</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13852977752686</t>
+    <t xml:space="preserve">6.13853073120117</t>
   </si>
   <si>
     <t xml:space="preserve">6.05880880355835</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">6.21825122833252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09866952896118</t>
+    <t xml:space="preserve">6.09867000579834</t>
   </si>
   <si>
     <t xml:space="preserve">6.38518476486206</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">6.30171823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17651844024658</t>
+    <t xml:space="preserve">6.17651891708374</t>
   </si>
   <si>
     <t xml:space="preserve">6.42691707611084</t>
@@ -608,70 +608,67 @@
     <t xml:space="preserve">6.46865129470825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96785259246826</t>
+    <t xml:space="preserve">5.9678521156311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00958490371704</t>
+    <t xml:space="preserve">6.00958585739136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13478469848633</t>
+    <t xml:space="preserve">6.13478517532349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05131864547729</t>
+    <t xml:space="preserve">6.05131816864014</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92611885070801</t>
+    <t xml:space="preserve">5.92611932754517</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09305143356323</t>
+    <t xml:space="preserve">6.09305238723755</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825075149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51038455963135</t>
+    <t xml:space="preserve">6.51038408279419</t>
   </si>
   <si>
     <t xml:space="preserve">5.84265279769897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88438558578491</t>
+    <t xml:space="preserve">5.88438606262207</t>
   </si>
   <si>
     <t xml:space="preserve">7.05291604995728</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09624671936035</t>
+    <t xml:space="preserve">8.09624767303467</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80411434173584</t>
+    <t xml:space="preserve">7.804114818573</t>
   </si>
   <si>
     <t xml:space="preserve">7.6371808052063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55371475219727</t>
+    <t xml:space="preserve">7.55371522903442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34504985809326</t>
+    <t xml:space="preserve">7.3450493812561</t>
   </si>
   <si>
     <t xml:space="preserve">7.17811679840088</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51198244094849</t>
+    <t xml:space="preserve">7.51198101043701</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47024869918823</t>
+    <t xml:space="preserve">7.47024917602539</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30331516265869</t>
+    <t xml:space="preserve">7.30331563949585</t>
   </si>
   <si>
     <t xml:space="preserve">7.42851495742798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26158285140991</t>
+    <t xml:space="preserve">7.26158237457275</t>
   </si>
   <si>
     <t xml:space="preserve">7.38678216934204</t>
@@ -683,40 +680,40 @@
     <t xml:space="preserve">7.2198486328125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544801712036</t>
+    <t xml:space="preserve">7.59544944763184</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76238203048706</t>
+    <t xml:space="preserve">7.7623815536499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84584903717041</t>
+    <t xml:space="preserve">7.84584760665894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67891502380371</t>
+    <t xml:space="preserve">7.67891454696655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01118326187134</t>
+    <t xml:space="preserve">7.01118278503418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09464979171753</t>
+    <t xml:space="preserve">7.09464836120605</t>
   </si>
   <si>
     <t xml:space="preserve">6.92771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76078367233276</t>
+    <t xml:space="preserve">6.76078414916992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8025164604187</t>
+    <t xml:space="preserve">6.80251598358154</t>
   </si>
   <si>
     <t xml:space="preserve">6.71905040740967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84424924850464</t>
+    <t xml:space="preserve">6.84425020217896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59385108947754</t>
+    <t xml:space="preserve">6.59385061264038</t>
   </si>
   <si>
     <t xml:space="preserve">6.67731714248657</t>
@@ -725,7 +722,7 @@
     <t xml:space="preserve">6.55211734771729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75918626785278</t>
+    <t xml:space="preserve">5.75918531417847</t>
   </si>
   <si>
     <t xml:space="preserve">5.71745252609253</t>
@@ -734,16 +731,16 @@
     <t xml:space="preserve">5.80091905593872</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67571926116943</t>
+    <t xml:space="preserve">5.67571973800659</t>
   </si>
   <si>
     <t xml:space="preserve">5.59225273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63398599624634</t>
+    <t xml:space="preserve">5.6339864730835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46705341339111</t>
+    <t xml:space="preserve">5.46705389022827</t>
   </si>
   <si>
     <t xml:space="preserve">5.5505199432373</t>
@@ -758,10 +755,10 @@
     <t xml:space="preserve">5.38358688354492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13638353347778</t>
+    <t xml:space="preserve">7.13638305664062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47247076034546</t>
+    <t xml:space="preserve">7.4724702835083</t>
   </si>
   <si>
     <t xml:space="preserve">7.25269222259521</t>
@@ -773,19 +770,19 @@
     <t xml:space="preserve">7.20873641967773</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1647801399231</t>
+    <t xml:space="preserve">7.16478061676025</t>
   </si>
   <si>
     <t xml:space="preserve">7.07686948776245</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98895788192749</t>
+    <t xml:space="preserve">6.98895835876465</t>
   </si>
   <si>
     <t xml:space="preserve">7.03291368484497</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94500207901001</t>
+    <t xml:space="preserve">6.94500255584717</t>
   </si>
   <si>
     <t xml:space="preserve">6.85709095001221</t>
@@ -794,37 +791,40 @@
     <t xml:space="preserve">6.72522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81313514709473</t>
+    <t xml:space="preserve">6.81313562393188</t>
   </si>
   <si>
     <t xml:space="preserve">6.76917934417725</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90104675292969</t>
+    <t xml:space="preserve">6.90104627609253</t>
   </si>
   <si>
     <t xml:space="preserve">6.63731241226196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12082529067993</t>
+    <t xml:space="preserve">7.12082576751709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34060382843018</t>
+    <t xml:space="preserve">7.34060430526733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5164270401001</t>
+    <t xml:space="preserve">7.51642656326294</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56038284301758</t>
+    <t xml:space="preserve">7.56038331985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42851543426514</t>
   </si>
   <si>
     <t xml:space="preserve">7.7362060546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69224882125854</t>
+    <t xml:space="preserve">7.6922492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829444885254</t>
+    <t xml:space="preserve">7.64829349517822</t>
   </si>
   <si>
     <t xml:space="preserve">7.78247404098511</t>
@@ -836,22 +836,22 @@
     <t xml:space="preserve">7.73774671554565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69302082061768</t>
+    <t xml:space="preserve">7.69302129745483</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60356712341309</t>
+    <t xml:space="preserve">7.60356616973877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91665554046631</t>
+    <t xml:space="preserve">7.91665458679199</t>
   </si>
   <si>
     <t xml:space="preserve">7.87192869186401</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96138048171997</t>
+    <t xml:space="preserve">7.96138143539429</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22974300384521</t>
+    <t xml:space="preserve">8.2297420501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.76646518707275</t>
@@ -860,13 +860,13 @@
     <t xml:space="preserve">8.58755683898926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36392307281494</t>
+    <t xml:space="preserve">8.36392402648926</t>
   </si>
   <si>
     <t xml:space="preserve">8.63228416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54283142089844</t>
+    <t xml:space="preserve">8.54283046722412</t>
   </si>
   <si>
     <t xml:space="preserve">8.40865039825439</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">8.67701148986816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49810314178467</t>
+    <t xml:space="preserve">8.49810409545898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81119155883789</t>
+    <t xml:space="preserve">8.81119251251221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72173881530762</t>
+    <t xml:space="preserve">8.7217378616333</t>
   </si>
   <si>
     <t xml:space="preserve">8.85591888427734</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">9.03482627868652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.376633644104</t>
+    <t xml:space="preserve">10.3766326904297</t>
   </si>
   <si>
     <t xml:space="preserve">11.4500770568848</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">10.7344465255737</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0922613143921</t>
+    <t xml:space="preserve">11.0922622680664</t>
   </si>
   <si>
     <t xml:space="preserve">10.9133548736572</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">11.181715965271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3606233596802</t>
+    <t xml:space="preserve">11.3606224060059</t>
   </si>
   <si>
     <t xml:space="preserve">11.6289844512939</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">11.539529800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2711687088013</t>
+    <t xml:space="preserve">11.2711696624756</t>
   </si>
   <si>
     <t xml:space="preserve">10.5555391311646</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">11.0028085708618</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6449918746948</t>
+    <t xml:space="preserve">10.6449937820435</t>
   </si>
   <si>
     <t xml:space="preserve">10.4660863876343</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">10.1977243423462</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75045680999756</t>
+    <t xml:space="preserve">9.75045585632324</t>
   </si>
   <si>
     <t xml:space="preserve">10.0188159942627</t>
@@ -956,19 +956,19 @@
     <t xml:space="preserve">12.6129751205444</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9707908630371</t>
+    <t xml:space="preserve">12.9707899093628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0442352294922</t>
+    <t xml:space="preserve">14.0442342758179</t>
   </si>
   <si>
     <t xml:space="preserve">13.7758731842041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.507513999939</t>
+    <t xml:space="preserve">13.5075130462646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2391510009766</t>
+    <t xml:space="preserve">13.2391519546509</t>
   </si>
   <si>
     <t xml:space="preserve">13.0602445602417</t>
@@ -983,10 +983,10 @@
     <t xml:space="preserve">12.7918825149536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7024278640747</t>
+    <t xml:space="preserve">12.702428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.149697303772</t>
+    <t xml:space="preserve">13.1496982574463</t>
   </si>
   <si>
     <t xml:space="preserve">13.3286037445068</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">13.6864204406738</t>
   </si>
   <si>
-    <t xml:space="preserve">13.865327835083</t>
+    <t xml:space="preserve">13.8653287887573</t>
   </si>
   <si>
     <t xml:space="preserve">14.4020500183105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2965888977051</t>
+    <t xml:space="preserve">15.2965869903564</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2071342468262</t>
+    <t xml:space="preserve">15.2071323394775</t>
   </si>
   <si>
     <t xml:space="preserve">14.5809564590454</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7598638534546</t>
+    <t xml:space="preserve">14.7598648071289</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4915056228638</t>
+    <t xml:space="preserve">14.4915046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5400876998901</t>
+    <t xml:space="preserve">14.5400886535645</t>
   </si>
   <si>
     <t xml:space="preserve">14.3560371398926</t>
@@ -1031,22 +1031,22 @@
     <t xml:space="preserve">14.2640104293823</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1719846725464</t>
+    <t xml:space="preserve">14.1719837188721</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8161668777466</t>
+    <t xml:space="preserve">14.8161659240723</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6321134567261</t>
+    <t xml:space="preserve">14.6321144104004</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3683223724365</t>
+    <t xml:space="preserve">15.3683214187622</t>
   </si>
   <si>
     <t xml:space="preserve">15.5523738861084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1045265197754</t>
+    <t xml:space="preserve">16.104528427124</t>
   </si>
   <si>
     <t xml:space="preserve">16.3806056976318</t>
@@ -1055,16 +1055,16 @@
     <t xml:space="preserve">15.9204750061035</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2088394165039</t>
+    <t xml:space="preserve">17.2088413238525</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3008651733398</t>
+    <t xml:space="preserve">17.3008632659912</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4849147796631</t>
+    <t xml:space="preserve">17.4849166870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5769424438477</t>
+    <t xml:space="preserve">17.576940536499</t>
   </si>
   <si>
     <t xml:space="preserve">17.6689682006836</t>
@@ -1085,13 +1085,13 @@
     <t xml:space="preserve">21.5340557098389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3745727539062</t>
+    <t xml:space="preserve">23.3745708465576</t>
   </si>
   <si>
-    <t xml:space="preserve">22.270263671875</t>
+    <t xml:space="preserve">22.2702617645264</t>
   </si>
   <si>
-    <t xml:space="preserve">22.822416305542</t>
+    <t xml:space="preserve">22.8224182128906</t>
   </si>
   <si>
     <t xml:space="preserve">20.6137943267822</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">23.9267272949219</t>
   </si>
   <si>
-    <t xml:space="preserve">24.662935256958</t>
+    <t xml:space="preserve">24.6629333496094</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8469848632812</t>
+    <t xml:space="preserve">24.8469867706299</t>
   </si>
   <si>
     <t xml:space="preserve">24.2948303222656</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">23.1905212402344</t>
   </si>
   <si>
-    <t xml:space="preserve">25.215087890625</t>
+    <t xml:space="preserve">25.2150897979736</t>
   </si>
   <si>
     <t xml:space="preserve">22.4543132781982</t>
@@ -1151,19 +1151,19 @@
     <t xml:space="preserve">27.975866317749</t>
   </si>
   <si>
-    <t xml:space="preserve">30.920690536499</t>
+    <t xml:space="preserve">30.9206924438477</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0801753997803</t>
+    <t xml:space="preserve">29.0801773071289</t>
   </si>
   <si>
-    <t xml:space="preserve">30.736644744873</t>
+    <t xml:space="preserve">30.7366428375244</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3685398101807</t>
+    <t xml:space="preserve">30.3685417175293</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2642269134521</t>
+    <t xml:space="preserve">29.2642288208008</t>
   </si>
   <si>
     <t xml:space="preserve">31.4728507995605</t>
@@ -1175,13 +1175,13 @@
     <t xml:space="preserve">34.7857818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8655204772949</t>
+    <t xml:space="preserve">33.8655166625977</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4974174499512</t>
+    <t xml:space="preserve">33.4974212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1844844818115</t>
+    <t xml:space="preserve">30.1844863891602</t>
   </si>
   <si>
     <t xml:space="preserve">27.4237098693848</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">28.7120742797852</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3439693450928</t>
+    <t xml:space="preserve">28.3439674377441</t>
   </si>
   <si>
     <t xml:space="preserve">27.055606842041</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">25.3991432189941</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7672462463379</t>
+    <t xml:space="preserve">25.7672443389893</t>
   </si>
   <si>
     <t xml:space="preserve">25.0310382843018</t>
@@ -1232,10 +1232,10 @@
     <t xml:space="preserve">27.6077632904053</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5525894165039</t>
+    <t xml:space="preserve">30.5525913238525</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6323337554932</t>
+    <t xml:space="preserve">29.6323318481445</t>
   </si>
   <si>
     <t xml:space="preserve">30.0004329681396</t>
@@ -1244,16 +1244,16 @@
     <t xml:space="preserve">32.3931121826172</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2090530395508</t>
+    <t xml:space="preserve">32.209056854248</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2887992858887</t>
+    <t xml:space="preserve">31.2887954711914</t>
   </si>
   <si>
     <t xml:space="preserve">31.6569023132324</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0250053405762</t>
+    <t xml:space="preserve">32.0250015258789</t>
   </si>
   <si>
     <t xml:space="preserve">32.0337677001953</t>
@@ -18642,7 +18642,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G639" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19162,7 +19162,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G659" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -19188,7 +19188,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G660" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19292,7 +19292,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G664" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19500,7 +19500,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G672" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -19526,7 +19526,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G673" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20020,7 +20020,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G692" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20046,7 +20046,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G693" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20124,7 +20124,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G696" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20150,7 +20150,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G697" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -20280,7 +20280,7 @@
         <v>7</v>
       </c>
       <c r="G702" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -20306,7 +20306,7 @@
         <v>7</v>
       </c>
       <c r="G703" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -20332,7 +20332,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G704" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -20592,7 +20592,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G714" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -20618,7 +20618,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G715" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -20696,7 +20696,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G718" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -20748,7 +20748,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G720" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21008,7 +21008,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G730" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21034,7 +21034,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G731" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21060,7 +21060,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G732" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21086,7 +21086,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G733" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -21346,7 +21346,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G743" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -21372,7 +21372,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G744" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -21398,7 +21398,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G745" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -21424,7 +21424,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G746" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -21450,7 +21450,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G747" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -21476,7 +21476,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G748" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -21502,7 +21502,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G749" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -21528,7 +21528,7 @@
         <v>9</v>
       </c>
       <c r="G750" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -21554,7 +21554,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G751" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -21580,7 +21580,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G752" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -21606,7 +21606,7 @@
         <v>8.75</v>
       </c>
       <c r="G753" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -21632,7 +21632,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G754" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -21658,7 +21658,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G755" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -21684,7 +21684,7 @@
         <v>9</v>
       </c>
       <c r="G756" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -21710,7 +21710,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G757" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -21736,7 +21736,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G758" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -21762,7 +21762,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G759" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -21788,7 +21788,7 @@
         <v>9</v>
       </c>
       <c r="G760" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -21814,7 +21814,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G761" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -21840,7 +21840,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G762" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -21866,7 +21866,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G763" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -21892,7 +21892,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G764" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -21918,7 +21918,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G765" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -21944,7 +21944,7 @@
         <v>9</v>
       </c>
       <c r="G766" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -21970,7 +21970,7 @@
         <v>9</v>
       </c>
       <c r="G767" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -21996,7 +21996,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G768" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22022,7 +22022,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G769" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22048,7 +22048,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G770" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22074,7 +22074,7 @@
         <v>8.75</v>
       </c>
       <c r="G771" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22100,7 +22100,7 @@
         <v>8.75</v>
       </c>
       <c r="G772" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22126,7 +22126,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G773" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22152,7 +22152,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G774" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22178,7 +22178,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G775" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22204,7 +22204,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G776" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22230,7 +22230,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G777" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22256,7 +22256,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G778" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22282,7 +22282,7 @@
         <v>9</v>
       </c>
       <c r="G779" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -22308,7 +22308,7 @@
         <v>9</v>
       </c>
       <c r="G780" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -22334,7 +22334,7 @@
         <v>9</v>
       </c>
       <c r="G781" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -22360,7 +22360,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G782" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -22386,7 +22386,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G783" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -22412,7 +22412,7 @@
         <v>8.75</v>
       </c>
       <c r="G784" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -22438,7 +22438,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G785" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -22464,7 +22464,7 @@
         <v>8.75</v>
       </c>
       <c r="G786" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -22490,7 +22490,7 @@
         <v>8.75</v>
       </c>
       <c r="G787" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -22516,7 +22516,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G788" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -22542,7 +22542,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G789" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -22568,7 +22568,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G790" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -22594,7 +22594,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G791" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -22620,7 +22620,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G792" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -22646,7 +22646,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G793" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -22672,7 +22672,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G794" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -22698,7 +22698,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G795" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -22724,7 +22724,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G796" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -22750,7 +22750,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G797" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -22776,7 +22776,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G798" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -22802,7 +22802,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G799" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -22828,7 +22828,7 @@
         <v>8.75</v>
       </c>
       <c r="G800" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -22854,7 +22854,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G801" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -22880,7 +22880,7 @@
         <v>8.75</v>
       </c>
       <c r="G802" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -22906,7 +22906,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G803" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -22932,7 +22932,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G804" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -22958,7 +22958,7 @@
         <v>8.75</v>
       </c>
       <c r="G805" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -22984,7 +22984,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G806" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23010,7 +23010,7 @@
         <v>8.75</v>
       </c>
       <c r="G807" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23036,7 +23036,7 @@
         <v>8.75</v>
       </c>
       <c r="G808" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23062,7 +23062,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G809" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23088,7 +23088,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G810" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23114,7 +23114,7 @@
         <v>8.5</v>
       </c>
       <c r="G811" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23140,7 +23140,7 @@
         <v>8.5</v>
       </c>
       <c r="G812" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23166,7 +23166,7 @@
         <v>8.5</v>
       </c>
       <c r="G813" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23192,7 +23192,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G814" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23218,7 +23218,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G815" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23244,7 +23244,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G816" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23270,7 +23270,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G817" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23296,7 +23296,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G818" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -23322,7 +23322,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G819" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -23348,7 +23348,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G820" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -23374,7 +23374,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G821" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -23400,7 +23400,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G822" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -23426,7 +23426,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G823" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -23452,7 +23452,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G824" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -23478,7 +23478,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G825" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -23504,7 +23504,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G826" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -23530,7 +23530,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G827" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -23556,7 +23556,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G828" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -23582,7 +23582,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G829" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -23608,7 +23608,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G830" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -23634,7 +23634,7 @@
         <v>9</v>
       </c>
       <c r="G831" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -23660,7 +23660,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G832" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -23686,7 +23686,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G833" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -23712,7 +23712,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G834" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -23738,7 +23738,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G835" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -23764,7 +23764,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G836" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -23790,7 +23790,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G837" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -23816,7 +23816,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G838" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -23842,7 +23842,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G839" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -23868,7 +23868,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G840" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -23894,7 +23894,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G841" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -23920,7 +23920,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G842" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -23946,7 +23946,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G843" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -23972,7 +23972,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G844" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -23998,7 +23998,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G845" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24024,7 +24024,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G846" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24050,7 +24050,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G847" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24076,7 +24076,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G848" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24102,7 +24102,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G849" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24128,7 +24128,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G850" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24154,7 +24154,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G851" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24180,7 +24180,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G852" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24206,7 +24206,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G853" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24232,7 +24232,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G854" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24258,7 +24258,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G855" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24284,7 +24284,7 @@
         <v>8</v>
       </c>
       <c r="G856" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24310,7 +24310,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G857" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24336,7 +24336,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G858" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -24414,7 +24414,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G861" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24492,7 +24492,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G864" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -24934,7 +24934,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G881" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25012,7 +25012,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G884" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25038,7 +25038,7 @@
         <v>7</v>
       </c>
       <c r="G885" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25246,7 +25246,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G893" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -25974,7 +25974,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G921" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26000,7 +26000,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G922" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26026,7 +26026,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G923" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -26052,7 +26052,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G924" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26156,7 +26156,7 @@
         <v>7</v>
       </c>
       <c r="G928" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26182,7 +26182,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G929" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26208,7 +26208,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G930" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26234,7 +26234,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G931" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26260,7 +26260,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G932" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26286,7 +26286,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G933" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26312,7 +26312,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G934" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26338,7 +26338,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G935" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26416,7 +26416,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G938" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26442,7 +26442,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G939" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26702,7 +26702,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G949" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26728,7 +26728,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G950" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26754,7 +26754,7 @@
         <v>7</v>
       </c>
       <c r="G951" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -26780,7 +26780,7 @@
         <v>7</v>
       </c>
       <c r="G952" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26806,7 +26806,7 @@
         <v>7</v>
       </c>
       <c r="G953" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26832,7 +26832,7 @@
         <v>7</v>
       </c>
       <c r="G954" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26858,7 +26858,7 @@
         <v>7</v>
       </c>
       <c r="G955" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26884,7 +26884,7 @@
         <v>7</v>
       </c>
       <c r="G956" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26910,7 +26910,7 @@
         <v>7</v>
       </c>
       <c r="G957" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26936,7 +26936,7 @@
         <v>7</v>
       </c>
       <c r="G958" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26962,7 +26962,7 @@
         <v>7</v>
       </c>
       <c r="G959" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -26988,7 +26988,7 @@
         <v>7</v>
       </c>
       <c r="G960" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27014,7 +27014,7 @@
         <v>7</v>
       </c>
       <c r="G961" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27040,7 +27040,7 @@
         <v>7</v>
       </c>
       <c r="G962" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27066,7 +27066,7 @@
         <v>7</v>
       </c>
       <c r="G963" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27092,7 +27092,7 @@
         <v>7</v>
       </c>
       <c r="G964" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27118,7 +27118,7 @@
         <v>7</v>
       </c>
       <c r="G965" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27144,7 +27144,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G966" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27170,7 +27170,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G967" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27196,7 +27196,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G968" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27222,7 +27222,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G969" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -27248,7 +27248,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G970" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27274,7 +27274,7 @@
         <v>6.75</v>
       </c>
       <c r="G971" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27300,7 +27300,7 @@
         <v>6.75</v>
       </c>
       <c r="G972" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27326,7 +27326,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G973" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27352,7 +27352,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G974" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27378,7 +27378,7 @@
         <v>6.75</v>
       </c>
       <c r="G975" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27404,7 +27404,7 @@
         <v>6.75</v>
       </c>
       <c r="G976" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27430,7 +27430,7 @@
         <v>6.75</v>
       </c>
       <c r="G977" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27456,7 +27456,7 @@
         <v>6.75</v>
       </c>
       <c r="G978" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -27482,7 +27482,7 @@
         <v>6.75</v>
       </c>
       <c r="G979" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27508,7 +27508,7 @@
         <v>6.75</v>
       </c>
       <c r="G980" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27534,7 +27534,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G981" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27560,7 +27560,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G982" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -27586,7 +27586,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G983" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -27612,7 +27612,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G984" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27638,7 +27638,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G985" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -27664,7 +27664,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G986" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -27690,7 +27690,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G987" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -27716,7 +27716,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G988" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -27742,7 +27742,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G989" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -27768,7 +27768,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G990" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -27794,7 +27794,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G991" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -27820,7 +27820,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G992" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -27846,7 +27846,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G993" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -27872,7 +27872,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G994" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -27898,7 +27898,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G995" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -27924,7 +27924,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G996" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -27950,7 +27950,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G997" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -27976,7 +27976,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G998" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28002,7 +28002,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G999" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28028,7 +28028,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1000" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28054,7 +28054,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1001" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28080,7 +28080,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1002" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28106,7 +28106,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1003" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28132,7 +28132,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1004" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28158,7 +28158,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1005" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28184,7 +28184,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1006" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28210,7 +28210,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1007" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28236,7 +28236,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1008" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28262,7 +28262,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1009" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28340,7 +28340,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1012" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28366,7 +28366,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1013" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28392,7 +28392,7 @@
         <v>8</v>
       </c>
       <c r="G1014" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28548,7 +28548,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1020" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28574,7 +28574,7 @@
         <v>8.5</v>
       </c>
       <c r="G1021" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28600,7 +28600,7 @@
         <v>8.5</v>
       </c>
       <c r="G1022" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -28626,7 +28626,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1023" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -28652,7 +28652,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1024" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28678,7 +28678,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1025" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28704,7 +28704,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1026" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28730,7 +28730,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1027" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28756,7 +28756,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1028" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28782,7 +28782,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1029" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28808,7 +28808,7 @@
         <v>8.75</v>
       </c>
       <c r="G1030" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28834,7 +28834,7 @@
         <v>8.75</v>
       </c>
       <c r="G1031" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28860,7 +28860,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1032" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28886,7 +28886,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1033" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28912,7 +28912,7 @@
         <v>8.5</v>
       </c>
       <c r="G1034" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28938,7 +28938,7 @@
         <v>8.25</v>
       </c>
       <c r="G1035" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28964,7 +28964,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1036" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -28990,7 +28990,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1037" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29016,7 +29016,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1038" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29042,7 +29042,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1039" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29068,7 +29068,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1040" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29094,7 +29094,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1041" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29120,7 +29120,7 @@
         <v>8</v>
       </c>
       <c r="G1042" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29146,7 +29146,7 @@
         <v>8</v>
       </c>
       <c r="G1043" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29172,7 +29172,7 @@
         <v>8</v>
       </c>
       <c r="G1044" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29198,7 +29198,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1045" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -29224,7 +29224,7 @@
         <v>8</v>
       </c>
       <c r="G1046" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29250,7 +29250,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1047" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -29276,7 +29276,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1048" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29302,7 +29302,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1049" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29328,7 +29328,7 @@
         <v>7.75</v>
       </c>
       <c r="G1050" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29354,7 +29354,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1051" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29380,7 +29380,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1052" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29406,7 +29406,7 @@
         <v>7.75</v>
       </c>
       <c r="G1053" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29432,7 +29432,7 @@
         <v>7.75</v>
       </c>
       <c r="G1054" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29458,7 +29458,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1055" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29484,7 +29484,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1056" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29510,7 +29510,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1057" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29536,7 +29536,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1058" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29562,7 +29562,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1059" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29588,7 +29588,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1060" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29614,7 +29614,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1061" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29640,7 +29640,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1062" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29666,7 +29666,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1063" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29692,7 +29692,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1064" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29718,7 +29718,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1065" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29744,7 +29744,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1066" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29770,7 +29770,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1067" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29796,7 +29796,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1068" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29822,7 +29822,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1069" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29848,7 +29848,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1070" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29874,7 +29874,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1071" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29900,7 +29900,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1072" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -29926,7 +29926,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1073" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -29952,7 +29952,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1074" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -29978,7 +29978,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1075" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30004,7 +30004,7 @@
         <v>8</v>
       </c>
       <c r="G1076" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30030,7 +30030,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1077" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30056,7 +30056,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1078" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30082,7 +30082,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1079" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -30108,7 +30108,7 @@
         <v>8.25</v>
       </c>
       <c r="G1080" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30134,7 +30134,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1081" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30160,7 +30160,7 @@
         <v>8.5</v>
       </c>
       <c r="G1082" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30186,7 +30186,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1083" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30212,7 +30212,7 @@
         <v>8.5</v>
       </c>
       <c r="G1084" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30238,7 +30238,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1085" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30264,7 +30264,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1086" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -30290,7 +30290,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1087" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30316,7 +30316,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1088" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30342,7 +30342,7 @@
         <v>8.5</v>
       </c>
       <c r="G1089" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30368,7 +30368,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1090" t="s">
-        <v>218</v>
+        <v>267</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30394,7 +30394,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1091" t="s">
-        <v>218</v>
+        <v>267</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30420,7 +30420,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1092" t="s">
-        <v>218</v>
+        <v>267</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30446,7 +30446,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1093" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30472,7 +30472,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1094" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30498,7 +30498,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1095" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30784,7 +30784,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1106" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -61602,7 +61602,7 @@
     </row>
     <row r="2292">
       <c r="A2292" s="1" t="n">
-        <v>45995.6459143519</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B2292" t="n">
         <v>6250</v>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -44,22 +44,22 @@
     <t xml:space="preserve">FPE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42625832557678</t>
+    <t xml:space="preserve">2.42625856399536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43408489227295</t>
+    <t xml:space="preserve">2.43408536911011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41060543060303</t>
+    <t xml:space="preserve">2.41060495376587</t>
   </si>
   <si>
     <t xml:space="preserve">2.45756506919861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39495158195496</t>
+    <t xml:space="preserve">2.39495182037354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233880996704</t>
+    <t xml:space="preserve">2.33233904838562</t>
   </si>
   <si>
     <t xml:space="preserve">2.41843175888062</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">2.35581874847412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37147212028503</t>
+    <t xml:space="preserve">2.37147188186646</t>
   </si>
   <si>
     <t xml:space="preserve">2.50452518463135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36364531517029</t>
+    <t xml:space="preserve">2.36364507675171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44973850250244</t>
+    <t xml:space="preserve">2.44973874092102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37303733825684</t>
+    <t xml:space="preserve">2.37303757667542</t>
   </si>
   <si>
     <t xml:space="preserve">2.34955763816833</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">2.46382641792297</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38712525367737</t>
+    <t xml:space="preserve">2.38712501525879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45443415641785</t>
+    <t xml:space="preserve">2.45443439483643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34799218177795</t>
+    <t xml:space="preserve">2.34799242019653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48104500770569</t>
+    <t xml:space="preserve">2.48104476928711</t>
   </si>
   <si>
     <t xml:space="preserve">2.3792986869812</t>
@@ -107,28 +107,28 @@
     <t xml:space="preserve">2.38556003570557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44191145896912</t>
+    <t xml:space="preserve">2.4419116973877</t>
   </si>
   <si>
     <t xml:space="preserve">2.78002262115479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36702084541321</t>
+    <t xml:space="preserve">3.36702060699463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62529993057251</t>
+    <t xml:space="preserve">3.62530016899109</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31066918373108</t>
+    <t xml:space="preserve">3.3106689453125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25588250160217</t>
+    <t xml:space="preserve">3.25588202476501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20266151428223</t>
+    <t xml:space="preserve">3.20266127586365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05238938331604</t>
+    <t xml:space="preserve">3.0523898601532</t>
   </si>
   <si>
     <t xml:space="preserve">3.09152317047119</t>
@@ -140,13 +140,13 @@
     <t xml:space="preserve">3.03673672676086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03830194473267</t>
+    <t xml:space="preserve">3.03830170631409</t>
   </si>
   <si>
     <t xml:space="preserve">3.15413618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3091037273407</t>
+    <t xml:space="preserve">3.30910396575928</t>
   </si>
   <si>
     <t xml:space="preserve">3.30284190177917</t>
@@ -155,88 +155,88 @@
     <t xml:space="preserve">3.35762882232666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57677507400513</t>
+    <t xml:space="preserve">3.57677531242371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52198815345764</t>
+    <t xml:space="preserve">3.52198839187622</t>
   </si>
   <si>
     <t xml:space="preserve">3.40458869934082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5924277305603</t>
+    <t xml:space="preserve">3.59242844581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58460092544556</t>
+    <t xml:space="preserve">3.58460164070129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67852091789246</t>
+    <t xml:space="preserve">3.67852115631104</t>
   </si>
   <si>
     <t xml:space="preserve">3.60025453567505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59555888175964</t>
+    <t xml:space="preserve">3.59555840492249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632207870483</t>
+    <t xml:space="preserve">3.32632255554199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29501533508301</t>
+    <t xml:space="preserve">3.29501581192017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37484693527222</t>
+    <t xml:space="preserve">3.37484741210938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38267397880554</t>
+    <t xml:space="preserve">3.3826744556427</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44372224807739</t>
+    <t xml:space="preserve">3.44372200965881</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59086275100708</t>
+    <t xml:space="preserve">3.5908625125885</t>
   </si>
   <si>
     <t xml:space="preserve">3.47972440719604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4265034198761</t>
+    <t xml:space="preserve">3.42650318145752</t>
   </si>
   <si>
     <t xml:space="preserve">3.41241526603699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2402286529541</t>
+    <t xml:space="preserve">3.24022912979126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21048808097839</t>
+    <t xml:space="preserve">3.21048784255981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28405857086182</t>
+    <t xml:space="preserve">3.28405809402466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16196274757385</t>
+    <t xml:space="preserve">3.16196298599243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20892238616943</t>
+    <t xml:space="preserve">3.20892262458801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13848304748535</t>
+    <t xml:space="preserve">3.13848280906677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23240256309509</t>
+    <t xml:space="preserve">3.23240232467651</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31849527359009</t>
+    <t xml:space="preserve">3.31849551200867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27623152732849</t>
+    <t xml:space="preserve">3.27623128890991</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18857288360596</t>
+    <t xml:space="preserve">3.18857312202454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14317846298218</t>
+    <t xml:space="preserve">3.14317893981934</t>
   </si>
   <si>
     <t xml:space="preserve">3.11500287055969</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">2.97412347793579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06021642684937</t>
+    <t xml:space="preserve">3.06021618843079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90368366241455</t>
+    <t xml:space="preserve">2.90368342399597</t>
   </si>
   <si>
     <t xml:space="preserve">2.89585709571838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82854795455933</t>
+    <t xml:space="preserve">2.82854819297791</t>
   </si>
   <si>
     <t xml:space="preserve">2.83637475967407</t>
@@ -266,52 +266,52 @@
     <t xml:space="preserve">2.90994477272034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491231918335</t>
+    <t xml:space="preserve">3.06491255760193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13065648078918</t>
+    <t xml:space="preserve">3.13065600395203</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14474415779114</t>
+    <t xml:space="preserve">3.14474439620972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21361827850342</t>
+    <t xml:space="preserve">3.213618516922</t>
   </si>
   <si>
     <t xml:space="preserve">3.28562355041504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35919380187988</t>
+    <t xml:space="preserve">3.3591935634613</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36388993263245</t>
+    <t xml:space="preserve">3.36388969421387</t>
   </si>
   <si>
     <t xml:space="preserve">3.91332006454468</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34378528594971</t>
+    <t xml:space="preserve">4.34378576278687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7938175201416</t>
+    <t xml:space="preserve">4.79381704330444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47864818572998</t>
+    <t xml:space="preserve">5.47864866256714</t>
   </si>
   <si>
     <t xml:space="preserve">6.09303903579712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41603565216064</t>
+    <t xml:space="preserve">5.41603469848633</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71344804763794</t>
+    <t xml:space="preserve">5.71344757080078</t>
   </si>
   <si>
     <t xml:space="preserve">5.56865453720093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41994905471802</t>
+    <t xml:space="preserve">5.41994857788086</t>
   </si>
   <si>
     <t xml:space="preserve">5.16558265686035</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">4.70381116867065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67641735076904</t>
+    <t xml:space="preserve">4.6764178276062</t>
   </si>
   <si>
     <t xml:space="preserve">5.0090503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55691480636597</t>
+    <t xml:space="preserve">5.55691432952881</t>
   </si>
   <si>
     <t xml:space="preserve">5.30646276473999</t>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">5.19688940048218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32211542129517</t>
+    <t xml:space="preserve">5.32211589813232</t>
   </si>
   <si>
     <t xml:space="preserve">5.47082138061523</t>
@@ -350,13 +350,13 @@
     <t xml:space="preserve">5.36907529830933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2908091545105</t>
+    <t xml:space="preserve">5.29080963134766</t>
   </si>
   <si>
     <t xml:space="preserve">5.1734094619751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09514284133911</t>
+    <t xml:space="preserve">5.09514331817627</t>
   </si>
   <si>
     <t xml:space="preserve">5.22036933898926</t>
@@ -365,19 +365,19 @@
     <t xml:space="preserve">5.10296964645386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99339628219604</t>
+    <t xml:space="preserve">4.9933967590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15384340286255</t>
+    <t xml:space="preserve">5.15384292602539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9855694770813</t>
+    <t xml:space="preserve">4.98556995391846</t>
   </si>
   <si>
     <t xml:space="preserve">4.7585973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77033758163452</t>
+    <t xml:space="preserve">4.77033710479736</t>
   </si>
   <si>
     <t xml:space="preserve">4.86425733566284</t>
@@ -386,22 +386,22 @@
     <t xml:space="preserve">4.88773727416992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83295154571533</t>
+    <t xml:space="preserve">4.83295106887817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75468397140503</t>
+    <t xml:space="preserve">4.75468349456787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8290376663208</t>
+    <t xml:space="preserve">4.82903718948364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7233772277832</t>
+    <t xml:space="preserve">4.72337675094604</t>
   </si>
   <si>
     <t xml:space="preserve">4.68815755844116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78207778930664</t>
+    <t xml:space="preserve">4.78207683563232</t>
   </si>
   <si>
     <t xml:space="preserve">4.8759970664978</t>
@@ -410,10 +410,10 @@
     <t xml:space="preserve">5.03644323348999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92687034606934</t>
+    <t xml:space="preserve">4.92686986923218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81338405609131</t>
+    <t xml:space="preserve">4.81338453292847</t>
   </si>
   <si>
     <t xml:space="preserve">4.86034393310547</t>
@@ -422,16 +422,16 @@
     <t xml:space="preserve">5.00122308731079</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77425050735474</t>
+    <t xml:space="preserve">4.77425003051758</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82121086120605</t>
+    <t xml:space="preserve">4.82120990753174</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69989728927612</t>
+    <t xml:space="preserve">4.69989776611328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69598436355591</t>
+    <t xml:space="preserve">4.69598484039307</t>
   </si>
   <si>
     <t xml:space="preserve">4.90730381011963</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">5.43951559066772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28298234939575</t>
+    <t xml:space="preserve">5.28298282623291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384880065918</t>
+    <t xml:space="preserve">5.24384927749634</t>
   </si>
   <si>
     <t xml:space="preserve">5.36124801635742</t>
@@ -455,31 +455,31 @@
     <t xml:space="preserve">5.40038251876831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51778125762939</t>
+    <t xml:space="preserve">5.51778173446655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63518095016479</t>
+    <t xml:space="preserve">5.63518142700195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96991682052612</t>
+    <t xml:space="preserve">4.96991586685181</t>
   </si>
   <si>
     <t xml:space="preserve">4.93078327178955</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85251665115356</t>
+    <t xml:space="preserve">4.85251712799072</t>
   </si>
   <si>
     <t xml:space="preserve">5.12644958496094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04818296432495</t>
+    <t xml:space="preserve">5.04818344116211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08731555938721</t>
+    <t xml:space="preserve">5.08731651306152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59604787826538</t>
+    <t xml:space="preserve">5.59604835510254</t>
   </si>
   <si>
     <t xml:space="preserve">5.26159763336182</t>
@@ -488,37 +488,37 @@
     <t xml:space="preserve">5.42103958129883</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34131813049316</t>
+    <t xml:space="preserve">5.34131860733032</t>
   </si>
   <si>
     <t xml:space="preserve">5.22173690795898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14201545715332</t>
+    <t xml:space="preserve">5.14201498031616</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1021556854248</t>
+    <t xml:space="preserve">5.10215520858765</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18187570571899</t>
+    <t xml:space="preserve">5.18187618255615</t>
   </si>
   <si>
     <t xml:space="preserve">5.38117933273315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30145788192749</t>
+    <t xml:space="preserve">5.30145835876465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90285158157349</t>
+    <t xml:space="preserve">4.9028525352478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50076150894165</t>
+    <t xml:space="preserve">5.50076055526733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46090030670166</t>
+    <t xml:space="preserve">5.4608998298645</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58048152923584</t>
+    <t xml:space="preserve">5.580482006073</t>
   </si>
   <si>
     <t xml:space="preserve">5.54062175750732</t>
@@ -527,31 +527,31 @@
     <t xml:space="preserve">5.62034273147583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94271278381348</t>
+    <t xml:space="preserve">4.94271230697632</t>
   </si>
   <si>
     <t xml:space="preserve">4.98257350921631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82313060760498</t>
+    <t xml:space="preserve">4.82313108444214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06229496002197</t>
+    <t xml:space="preserve">5.06229448318481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02243375778198</t>
+    <t xml:space="preserve">5.02243423461914</t>
   </si>
   <si>
     <t xml:space="preserve">4.74340963363647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78326988220215</t>
+    <t xml:space="preserve">4.78327035903931</t>
   </si>
   <si>
     <t xml:space="preserve">4.86299133300781</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73992443084717</t>
+    <t xml:space="preserve">5.73992395401001</t>
   </si>
   <si>
     <t xml:space="preserve">5.81964588165283</t>
@@ -560,34 +560,34 @@
     <t xml:space="preserve">5.70006418228149</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6602029800415</t>
+    <t xml:space="preserve">5.66020250320435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77978467941284</t>
+    <t xml:space="preserve">5.77978515625</t>
   </si>
   <si>
     <t xml:space="preserve">5.85950565338135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.979088306427</t>
+    <t xml:space="preserve">5.97908782958984</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29797220230103</t>
+    <t xml:space="preserve">6.29797315597534</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13853073120117</t>
+    <t xml:space="preserve">6.13852977752686</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05880880355835</t>
+    <t xml:space="preserve">6.05880928039551</t>
   </si>
   <si>
     <t xml:space="preserve">6.21825122833252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09867000579834</t>
+    <t xml:space="preserve">6.09866952896118</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38518476486206</t>
+    <t xml:space="preserve">6.38518524169922</t>
   </si>
   <si>
     <t xml:space="preserve">6.25998497009277</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">6.30171823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17651891708374</t>
+    <t xml:space="preserve">6.17651844024658</t>
   </si>
   <si>
     <t xml:space="preserve">6.42691707611084</t>
@@ -608,22 +608,22 @@
     <t xml:space="preserve">6.46865129470825</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9678521156311</t>
+    <t xml:space="preserve">5.96785259246826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00958585739136</t>
+    <t xml:space="preserve">6.0095853805542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13478517532349</t>
+    <t xml:space="preserve">6.13478422164917</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05131816864014</t>
+    <t xml:space="preserve">6.05131864547729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92611932754517</t>
+    <t xml:space="preserve">5.92611885070801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09305238723755</t>
+    <t xml:space="preserve">6.09305191040039</t>
   </si>
   <si>
     <t xml:space="preserve">6.51038408279419</t>
@@ -632,79 +632,79 @@
     <t xml:space="preserve">5.84265279769897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88438606262207</t>
+    <t xml:space="preserve">5.88438558578491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05291604995728</t>
+    <t xml:space="preserve">7.05291557312012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09624767303467</t>
+    <t xml:space="preserve">8.09624576568604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.804114818573</t>
+    <t xml:space="preserve">7.80411386489868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6371808052063</t>
+    <t xml:space="preserve">7.63718128204346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55371522903442</t>
+    <t xml:space="preserve">7.55371570587158</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3450493812561</t>
+    <t xml:space="preserve">7.34504985809326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17811679840088</t>
+    <t xml:space="preserve">7.17811632156372</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51198101043701</t>
+    <t xml:space="preserve">7.51198196411133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47024917602539</t>
+    <t xml:space="preserve">7.47024822235107</t>
   </si>
   <si>
     <t xml:space="preserve">7.30331563949585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851495742798</t>
+    <t xml:space="preserve">7.42851448059082</t>
   </si>
   <si>
     <t xml:space="preserve">7.26158237457275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38678216934204</t>
+    <t xml:space="preserve">7.3867826461792</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96944999694824</t>
+    <t xml:space="preserve">6.96944952011108</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2198486328125</t>
+    <t xml:space="preserve">7.21984910964966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544944763184</t>
+    <t xml:space="preserve">7.59544849395752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7623815536499</t>
+    <t xml:space="preserve">7.76238250732422</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84584760665894</t>
+    <t xml:space="preserve">7.84584712982178</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67891454696655</t>
+    <t xml:space="preserve">7.67891407012939</t>
   </si>
   <si>
     <t xml:space="preserve">7.01118278503418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09464836120605</t>
+    <t xml:space="preserve">7.09464979171753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92771625518799</t>
+    <t xml:space="preserve">6.92771768569946</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76078414916992</t>
+    <t xml:space="preserve">6.76078367233276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80251598358154</t>
+    <t xml:space="preserve">6.80251693725586</t>
   </si>
   <si>
     <t xml:space="preserve">6.71905040740967</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">6.84425020217896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59385061264038</t>
+    <t xml:space="preserve">6.59385108947754</t>
   </si>
   <si>
     <t xml:space="preserve">6.67731714248657</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">6.55211734771729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75918531417847</t>
+    <t xml:space="preserve">5.75918626785278</t>
   </si>
   <si>
     <t xml:space="preserve">5.71745252609253</t>
@@ -731,67 +731,67 @@
     <t xml:space="preserve">5.80091905593872</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67571973800659</t>
+    <t xml:space="preserve">5.67571926116943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59225273132324</t>
+    <t xml:space="preserve">5.59225225448608</t>
   </si>
   <si>
     <t xml:space="preserve">5.6339864730835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46705389022827</t>
+    <t xml:space="preserve">5.46705341339111</t>
   </si>
   <si>
     <t xml:space="preserve">5.5505199432373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17492055892944</t>
+    <t xml:space="preserve">5.1749210357666</t>
   </si>
   <si>
     <t xml:space="preserve">5.25838756561279</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38358688354492</t>
+    <t xml:space="preserve">5.38358736038208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13638305664062</t>
+    <t xml:space="preserve">7.13638353347778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4724702835083</t>
+    <t xml:space="preserve">7.47247123718262</t>
   </si>
   <si>
     <t xml:space="preserve">7.25269222259521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29664754867554</t>
+    <t xml:space="preserve">7.29664897918701</t>
   </si>
   <si>
     <t xml:space="preserve">7.20873641967773</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16478061676025</t>
+    <t xml:space="preserve">7.16478109359741</t>
   </si>
   <si>
     <t xml:space="preserve">7.07686948776245</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98895835876465</t>
+    <t xml:space="preserve">6.98895788192749</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03291368484497</t>
+    <t xml:space="preserve">7.03291320800781</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94500255584717</t>
+    <t xml:space="preserve">6.94500303268433</t>
   </si>
   <si>
     <t xml:space="preserve">6.85709095001221</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72522401809692</t>
+    <t xml:space="preserve">6.72522449493408</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81313562393188</t>
+    <t xml:space="preserve">6.81313514709473</t>
   </si>
   <si>
     <t xml:space="preserve">6.76917934417725</t>
@@ -803,22 +803,19 @@
     <t xml:space="preserve">6.63731241226196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12082576751709</t>
+    <t xml:space="preserve">7.12082529067993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34060430526733</t>
+    <t xml:space="preserve">7.34060382843018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51642656326294</t>
+    <t xml:space="preserve">7.51642751693726</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56038331985474</t>
+    <t xml:space="preserve">7.56038284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851543426514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7362060546875</t>
+    <t xml:space="preserve">7.73620653152466</t>
   </si>
   <si>
     <t xml:space="preserve">7.6922492980957</t>
@@ -833,34 +830,37 @@
     <t xml:space="preserve">7.8272008895874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73774671554565</t>
+    <t xml:space="preserve">7.73774719238281</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69302129745483</t>
+    <t xml:space="preserve">7.69302082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60356616973877</t>
+    <t xml:space="preserve">7.64829444885254</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91665458679199</t>
+    <t xml:space="preserve">7.60356712341309</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87192869186401</t>
+    <t xml:space="preserve">7.91665506362915</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96138143539429</t>
+    <t xml:space="preserve">7.87192916870117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96138095855713</t>
   </si>
   <si>
     <t xml:space="preserve">8.2297420501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76646518707275</t>
+    <t xml:space="preserve">8.76646614074707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58755683898926</t>
+    <t xml:space="preserve">8.58755779266357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36392402648926</t>
+    <t xml:space="preserve">8.36392307281494</t>
   </si>
   <si>
     <t xml:space="preserve">8.63228416442871</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">8.54283046722412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40865039825439</t>
+    <t xml:space="preserve">8.40864944458008</t>
   </si>
   <si>
     <t xml:space="preserve">8.27446937561035</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">8.45337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67701148986816</t>
+    <t xml:space="preserve">8.67701053619385</t>
   </si>
   <si>
     <t xml:space="preserve">8.49810409545898</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">8.85591888427734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03482627868652</t>
+    <t xml:space="preserve">9.03482723236084</t>
   </si>
   <si>
     <t xml:space="preserve">10.3766326904297</t>
@@ -908,28 +908,28 @@
     <t xml:space="preserve">11.0922622680664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9133548736572</t>
+    <t xml:space="preserve">10.9133539199829</t>
   </si>
   <si>
     <t xml:space="preserve">11.181715965271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3606224060059</t>
+    <t xml:space="preserve">11.3606233596802</t>
   </si>
   <si>
     <t xml:space="preserve">11.6289844512939</t>
   </si>
   <si>
-    <t xml:space="preserve">11.539529800415</t>
+    <t xml:space="preserve">11.5395307540894</t>
   </si>
   <si>
     <t xml:space="preserve">11.2711696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5555391311646</t>
+    <t xml:space="preserve">10.5555400848389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2871789932251</t>
+    <t xml:space="preserve">10.2871780395508</t>
   </si>
   <si>
     <t xml:space="preserve">11.0028085708618</t>
@@ -938,25 +938,25 @@
     <t xml:space="preserve">10.6449937820435</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4660863876343</t>
+    <t xml:space="preserve">10.46608543396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1082706451416</t>
+    <t xml:space="preserve">10.1082715988159</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1977243423462</t>
+    <t xml:space="preserve">10.1977252960205</t>
   </si>
   <si>
     <t xml:space="preserve">9.75045585632324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0188159942627</t>
+    <t xml:space="preserve">10.018816947937</t>
   </si>
   <si>
     <t xml:space="preserve">12.6129751205444</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9707899093628</t>
+    <t xml:space="preserve">12.9707908630371</t>
   </si>
   <si>
     <t xml:space="preserve">14.0442342758179</t>
@@ -971,25 +971,25 @@
     <t xml:space="preserve">13.2391519546509</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0602445602417</t>
+    <t xml:space="preserve">13.0602436065674</t>
   </si>
   <si>
     <t xml:space="preserve">13.4180593490601</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8813371658325</t>
+    <t xml:space="preserve">12.8813362121582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7918825149536</t>
+    <t xml:space="preserve">12.7918834686279</t>
   </si>
   <si>
     <t xml:space="preserve">12.702428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1496982574463</t>
+    <t xml:space="preserve">13.1496963500977</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3286037445068</t>
+    <t xml:space="preserve">13.3286046981812</t>
   </si>
   <si>
     <t xml:space="preserve">13.9547815322876</t>
@@ -998,28 +998,28 @@
     <t xml:space="preserve">13.5969657897949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6864204406738</t>
+    <t xml:space="preserve">13.6864213943481</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8653287887573</t>
+    <t xml:space="preserve">13.865327835083</t>
   </si>
   <si>
     <t xml:space="preserve">14.4020500183105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2965869903564</t>
+    <t xml:space="preserve">15.2965888977051</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2071323394775</t>
+    <t xml:space="preserve">15.2071342468262</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5809564590454</t>
+    <t xml:space="preserve">14.5809574127197</t>
   </si>
   <si>
     <t xml:space="preserve">14.7598648071289</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4915046691895</t>
+    <t xml:space="preserve">14.4915037155151</t>
   </si>
   <si>
     <t xml:space="preserve">14.5400886535645</t>
@@ -1031,16 +1031,16 @@
     <t xml:space="preserve">14.2640104293823</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1719837188721</t>
+    <t xml:space="preserve">14.1719846725464</t>
   </si>
   <si>
     <t xml:space="preserve">14.8161659240723</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6321144104004</t>
+    <t xml:space="preserve">14.6321134567261</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3683214187622</t>
+    <t xml:space="preserve">15.3683233261108</t>
   </si>
   <si>
     <t xml:space="preserve">15.5523738861084</t>
@@ -1049,31 +1049,31 @@
     <t xml:space="preserve">16.104528427124</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3806056976318</t>
+    <t xml:space="preserve">16.3806037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9204750061035</t>
+    <t xml:space="preserve">15.9204759597778</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2088413238525</t>
+    <t xml:space="preserve">17.2088394165039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3008632659912</t>
+    <t xml:space="preserve">17.3008651733398</t>
   </si>
   <si>
     <t xml:space="preserve">17.4849166870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.576940536499</t>
+    <t xml:space="preserve">17.5769424438477</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6689682006836</t>
+    <t xml:space="preserve">17.6689701080322</t>
   </si>
   <si>
     <t xml:space="preserve">18.4051742553711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1413822174072</t>
+    <t xml:space="preserve">19.1413803100586</t>
   </si>
   <si>
     <t xml:space="preserve">19.6935367584229</t>
@@ -1082,19 +1082,19 @@
     <t xml:space="preserve">20.0616397857666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5340557098389</t>
+    <t xml:space="preserve">21.5340538024902</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3745708465576</t>
+    <t xml:space="preserve">23.3745727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2702617645264</t>
+    <t xml:space="preserve">22.270263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8224182128906</t>
+    <t xml:space="preserve">22.822416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6137943267822</t>
+    <t xml:space="preserve">20.6137962341309</t>
   </si>
   <si>
     <t xml:space="preserve">19.3254337310791</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">21.902156829834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0862102508545</t>
+    <t xml:space="preserve">22.0862083435059</t>
   </si>
   <si>
     <t xml:space="preserve">23.0064697265625</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">23.9267272949219</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6629333496094</t>
+    <t xml:space="preserve">24.662935256958</t>
   </si>
   <si>
     <t xml:space="preserve">24.8469867706299</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2948303222656</t>
+    <t xml:space="preserve">24.2948322296143</t>
   </si>
   <si>
     <t xml:space="preserve">24.1107807159424</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">23.1905212402344</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2150897979736</t>
+    <t xml:space="preserve">25.215087890625</t>
   </si>
   <si>
     <t xml:space="preserve">22.4543132781982</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">25.9512958526611</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5034523010254</t>
+    <t xml:space="preserve">26.5034503936768</t>
   </si>
   <si>
     <t xml:space="preserve">27.975866317749</t>
@@ -1157,40 +1157,40 @@
     <t xml:space="preserve">29.0801773071289</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7366428375244</t>
+    <t xml:space="preserve">30.7366466522217</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3685417175293</t>
+    <t xml:space="preserve">30.3685398101807</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2642288208008</t>
+    <t xml:space="preserve">29.2642269134521</t>
   </si>
   <si>
     <t xml:space="preserve">31.4728507995605</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2336273193359</t>
+    <t xml:space="preserve">34.2336235046387</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7857818603516</t>
+    <t xml:space="preserve">34.7857780456543</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8655166625977</t>
+    <t xml:space="preserve">33.8655204772949</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4974212646484</t>
+    <t xml:space="preserve">33.4974174499512</t>
   </si>
   <si>
     <t xml:space="preserve">30.1844863891602</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4237098693848</t>
+    <t xml:space="preserve">27.4237117767334</t>
   </si>
   <si>
     <t xml:space="preserve">26.6875038146973</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5831928253174</t>
+    <t xml:space="preserve">25.5831909179688</t>
   </si>
   <si>
     <t xml:space="preserve">26.3194007873535</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">27.7918167114258</t>
   </si>
   <si>
-    <t xml:space="preserve">28.896125793457</t>
+    <t xml:space="preserve">28.8961238861084</t>
   </si>
   <si>
     <t xml:space="preserve">29.4482803344727</t>
@@ -1211,16 +1211,16 @@
     <t xml:space="preserve">28.7120742797852</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3439674377441</t>
+    <t xml:space="preserve">28.3439693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">27.055606842041</t>
+    <t xml:space="preserve">27.0556087493896</t>
   </si>
   <si>
     <t xml:space="preserve">26.8715553283691</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3991432189941</t>
+    <t xml:space="preserve">25.3991413116455</t>
   </si>
   <si>
     <t xml:space="preserve">25.7672443389893</t>
@@ -1241,13 +1241,13 @@
     <t xml:space="preserve">30.0004329681396</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3931121826172</t>
+    <t xml:space="preserve">32.3931083679199</t>
   </si>
   <si>
     <t xml:space="preserve">32.209056854248</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2887954711914</t>
+    <t xml:space="preserve">31.28879737854</t>
   </si>
   <si>
     <t xml:space="preserve">31.6569023132324</t>
@@ -1259,34 +1259,34 @@
     <t xml:space="preserve">32.0337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5990676879883</t>
+    <t xml:space="preserve">32.5990715026855</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1643753051758</t>
+    <t xml:space="preserve">33.1643714904785</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6568984985352</t>
+    <t xml:space="preserve">31.6569004058838</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4106407165527</t>
+    <t xml:space="preserve">32.4106369018555</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7875061035156</t>
+    <t xml:space="preserve">32.7875022888184</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9759368896484</t>
+    <t xml:space="preserve">32.9759407043457</t>
   </si>
   <si>
     <t xml:space="preserve">30.9031639099121</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8453350067139</t>
+    <t xml:space="preserve">31.8453369140625</t>
   </si>
   <si>
     <t xml:space="preserve">30.714729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5263004302979</t>
+    <t xml:space="preserve">30.5262985229492</t>
   </si>
   <si>
     <t xml:space="preserve">31.2800331115723</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">30.1494293212891</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3378658294678</t>
+    <t xml:space="preserve">30.3378639221191</t>
   </si>
   <si>
     <t xml:space="preserve">29.395694732666</t>
@@ -1322,7 +1322,7 @@
     <t xml:space="preserve">28.2650909423828</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6997871398926</t>
+    <t xml:space="preserve">27.6997890472412</t>
   </si>
   <si>
     <t xml:space="preserve">28.0766563415527</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">25.2501468658447</t>
   </si>
   <si>
-    <t xml:space="preserve">24.307975769043</t>
+    <t xml:space="preserve">24.3079776763916</t>
   </si>
   <si>
     <t xml:space="preserve">23.9311103820801</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">23.7426776885986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1773738861084</t>
+    <t xml:space="preserve">23.177375793457</t>
   </si>
   <si>
     <t xml:space="preserve">22.6120719909668</t>
@@ -1370,10 +1370,10 @@
     <t xml:space="preserve">22.2352046966553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0467720031738</t>
+    <t xml:space="preserve">22.0467700958252</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8005065917969</t>
+    <t xml:space="preserve">22.8005084991455</t>
   </si>
   <si>
     <t xml:space="preserve">22.988941192627</t>
@@ -1388,19 +1388,19 @@
     <t xml:space="preserve">25.6270160675049</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3807525634766</t>
+    <t xml:space="preserve">26.3807506561279</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1344871520996</t>
+    <t xml:space="preserve">27.134485244751</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9460544586182</t>
+    <t xml:space="preserve">26.9460525512695</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3229217529297</t>
+    <t xml:space="preserve">27.3229198455811</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1923179626465</t>
+    <t xml:space="preserve">26.1923160552979</t>
   </si>
   <si>
     <t xml:space="preserve">26.7576179504395</t>
@@ -30368,7 +30368,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1090" t="s">
-        <v>267</v>
+        <v>217</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30394,7 +30394,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1091" t="s">
-        <v>267</v>
+        <v>217</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30420,7 +30420,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1092" t="s">
-        <v>267</v>
+        <v>217</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30524,7 +30524,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1096" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30550,7 +30550,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1097" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30576,7 +30576,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1098" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30602,7 +30602,7 @@
         <v>8.75</v>
       </c>
       <c r="G1099" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30628,7 +30628,7 @@
         <v>8.75</v>
       </c>
       <c r="G1100" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30654,7 +30654,7 @@
         <v>8.75</v>
       </c>
       <c r="G1101" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -30680,7 +30680,7 @@
         <v>8.75</v>
       </c>
       <c r="G1102" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30706,7 +30706,7 @@
         <v>8.75</v>
       </c>
       <c r="G1103" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30732,7 +30732,7 @@
         <v>8.75</v>
       </c>
       <c r="G1104" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30758,7 +30758,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1105" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30810,7 +30810,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1107" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30836,7 +30836,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1108" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30862,7 +30862,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1109" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30888,7 +30888,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1110" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -30914,7 +30914,7 @@
         <v>8.75</v>
       </c>
       <c r="G1111" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30940,7 +30940,7 @@
         <v>8.75</v>
       </c>
       <c r="G1112" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -30966,7 +30966,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1113" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -30992,7 +30992,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1114" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31018,7 +31018,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31044,7 +31044,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1116" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31070,7 +31070,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1117" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31096,7 +31096,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1118" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31122,7 +31122,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1119" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31148,7 +31148,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1120" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31174,7 +31174,7 @@
         <v>8.75</v>
       </c>
       <c r="G1121" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31200,7 +31200,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1122" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31226,7 +31226,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1123" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31252,7 +31252,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1124" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31278,7 +31278,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1125" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31304,7 +31304,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1126" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31330,7 +31330,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1127" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31356,7 +31356,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1128" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31382,7 +31382,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1129" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31408,7 +31408,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1130" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31434,7 +31434,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1131" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31460,7 +31460,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1132" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31486,7 +31486,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1133" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31512,7 +31512,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1134" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31564,7 +31564,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1136" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31590,7 +31590,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1137" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31616,7 +31616,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1138" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31642,7 +31642,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1139" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31668,7 +31668,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1140" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31694,7 +31694,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1141" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31720,7 +31720,7 @@
         <v>8.75</v>
       </c>
       <c r="G1142" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31850,7 +31850,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1147" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31902,7 +31902,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1149" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32032,7 +32032,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1154" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32058,7 +32058,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1155" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32084,7 +32084,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1156" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -61623,6 +61623,32 @@
         <v>555</v>
       </c>
       <c r="H2292" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" s="1" t="n">
+        <v>45996.3333333333</v>
+      </c>
+      <c r="B2293" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2293" t="n">
+        <v>37.4000015258789</v>
+      </c>
+      <c r="D2293" t="n">
+        <v>37.4000015258789</v>
+      </c>
+      <c r="E2293" t="n">
+        <v>37.4000015258789</v>
+      </c>
+      <c r="F2293" t="n">
+        <v>37.4000015258789</v>
+      </c>
+      <c r="G2293" t="s">
+        <v>555</v>
+      </c>
+      <c r="H2293" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46539163589478</t>
+    <t xml:space="preserve">2.46539187431335</t>
   </si>
   <si>
     <t xml:space="preserve">FPE.MI</t>
@@ -47,58 +47,58 @@
     <t xml:space="preserve">2.42625856399536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43408536911011</t>
+    <t xml:space="preserve">2.43408513069153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41060495376587</t>
+    <t xml:space="preserve">2.41060519218445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45756506919861</t>
+    <t xml:space="preserve">2.45756554603577</t>
   </si>
   <si>
     <t xml:space="preserve">2.39495182037354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233904838562</t>
+    <t xml:space="preserve">2.33233880996704</t>
   </si>
   <si>
     <t xml:space="preserve">2.41843175888062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35581874847412</t>
+    <t xml:space="preserve">2.3558189868927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37147188186646</t>
+    <t xml:space="preserve">2.37147212028503</t>
   </si>
   <si>
     <t xml:space="preserve">2.50452518463135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36364507675171</t>
+    <t xml:space="preserve">2.36364555358887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44973874092102</t>
+    <t xml:space="preserve">2.44973826408386</t>
   </si>
   <si>
     <t xml:space="preserve">2.37303757667542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34955763816833</t>
+    <t xml:space="preserve">2.34955739974976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46382641792297</t>
+    <t xml:space="preserve">2.46382617950439</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38712501525879</t>
+    <t xml:space="preserve">2.38712525367737</t>
   </si>
   <si>
     <t xml:space="preserve">2.45443439483643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34799242019653</t>
+    <t xml:space="preserve">2.34799218177795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48104476928711</t>
+    <t xml:space="preserve">2.48104524612427</t>
   </si>
   <si>
     <t xml:space="preserve">2.3792986869812</t>
@@ -107,79 +107,79 @@
     <t xml:space="preserve">2.38556003570557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4419116973877</t>
+    <t xml:space="preserve">2.44191145896912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78002262115479</t>
+    <t xml:space="preserve">2.78002285957336</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36702060699463</t>
+    <t xml:space="preserve">3.36702084541321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62530016899109</t>
+    <t xml:space="preserve">3.62529993057251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3106689453125</t>
+    <t xml:space="preserve">3.31066942214966</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25588202476501</t>
+    <t xml:space="preserve">3.25588250160217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20266127586365</t>
+    <t xml:space="preserve">3.20266151428223</t>
   </si>
   <si>
     <t xml:space="preserve">3.0523898601532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09152317047119</t>
+    <t xml:space="preserve">3.09152269363403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04456329345703</t>
+    <t xml:space="preserve">3.04456377029419</t>
   </si>
   <si>
     <t xml:space="preserve">3.03673672676086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03830170631409</t>
+    <t xml:space="preserve">3.03830194473267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15413618087769</t>
+    <t xml:space="preserve">3.15413641929626</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30910396575928</t>
+    <t xml:space="preserve">3.3091037273407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30284190177917</t>
+    <t xml:space="preserve">3.30284214019775</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35762882232666</t>
+    <t xml:space="preserve">3.3576283454895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57677531242371</t>
+    <t xml:space="preserve">3.57677507400513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52198839187622</t>
+    <t xml:space="preserve">3.52198815345764</t>
   </si>
   <si>
     <t xml:space="preserve">3.40458869934082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59242844581604</t>
+    <t xml:space="preserve">3.59242820739746</t>
   </si>
   <si>
     <t xml:space="preserve">3.58460164070129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67852115631104</t>
+    <t xml:space="preserve">3.67852091789246</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60025453567505</t>
+    <t xml:space="preserve">3.60025429725647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59555840492249</t>
+    <t xml:space="preserve">3.59555864334106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632255554199</t>
+    <t xml:space="preserve">3.32632207870483</t>
   </si>
   <si>
     <t xml:space="preserve">3.29501581192017</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">3.37484741210938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3826744556427</t>
+    <t xml:space="preserve">3.38267397880554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44372200965881</t>
+    <t xml:space="preserve">3.44372224807739</t>
   </si>
   <si>
     <t xml:space="preserve">3.5908625125885</t>
@@ -206,58 +206,58 @@
     <t xml:space="preserve">3.41241526603699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24022912979126</t>
+    <t xml:space="preserve">3.24022889137268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21048784255981</t>
+    <t xml:space="preserve">3.21048808097839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28405809402466</t>
+    <t xml:space="preserve">3.28405857086182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16196298599243</t>
+    <t xml:space="preserve">3.16196250915527</t>
   </si>
   <si>
     <t xml:space="preserve">3.20892262458801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13848280906677</t>
+    <t xml:space="preserve">3.13848304748535</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23240232467651</t>
+    <t xml:space="preserve">3.23240280151367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31849551200867</t>
+    <t xml:space="preserve">3.31849527359009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27623128890991</t>
+    <t xml:space="preserve">3.27623176574707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18857312202454</t>
+    <t xml:space="preserve">3.18857336044312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14317893981934</t>
+    <t xml:space="preserve">3.14317870140076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11500287055969</t>
+    <t xml:space="preserve">3.11500310897827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00073385238647</t>
+    <t xml:space="preserve">3.00073409080505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97412347793579</t>
+    <t xml:space="preserve">2.97412323951721</t>
   </si>
   <si>
     <t xml:space="preserve">3.06021618843079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90368342399597</t>
+    <t xml:space="preserve">2.90368366241455</t>
   </si>
   <si>
     <t xml:space="preserve">2.89585709571838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82854819297791</t>
+    <t xml:space="preserve">2.82854795455933</t>
   </si>
   <si>
     <t xml:space="preserve">2.83637475967407</t>
@@ -266,13 +266,13 @@
     <t xml:space="preserve">2.90994477272034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491255760193</t>
+    <t xml:space="preserve">3.06491279602051</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13065600395203</t>
+    <t xml:space="preserve">3.13065624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14474439620972</t>
+    <t xml:space="preserve">3.14474415779114</t>
   </si>
   <si>
     <t xml:space="preserve">3.213618516922</t>
@@ -281,34 +281,34 @@
     <t xml:space="preserve">3.28562355041504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3591935634613</t>
+    <t xml:space="preserve">3.35919404029846</t>
   </si>
   <si>
     <t xml:space="preserve">3.36388969421387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91332006454468</t>
+    <t xml:space="preserve">3.91332054138184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34378576278687</t>
+    <t xml:space="preserve">4.34378528594971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79381704330444</t>
+    <t xml:space="preserve">4.7938175201416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47864866256714</t>
+    <t xml:space="preserve">5.47864818572998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09303903579712</t>
+    <t xml:space="preserve">6.09303951263428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41603469848633</t>
+    <t xml:space="preserve">5.41603517532349</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71344757080078</t>
+    <t xml:space="preserve">5.71344804763794</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56865453720093</t>
+    <t xml:space="preserve">5.56865406036377</t>
   </si>
   <si>
     <t xml:space="preserve">5.41994857788086</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">4.94643640518188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70381116867065</t>
+    <t xml:space="preserve">4.7038106918335</t>
   </si>
   <si>
     <t xml:space="preserve">4.6764178276062</t>
@@ -329,19 +329,19 @@
     <t xml:space="preserve">5.0090503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55691432952881</t>
+    <t xml:space="preserve">5.55691480636597</t>
   </si>
   <si>
     <t xml:space="preserve">5.30646276473999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22428274154663</t>
+    <t xml:space="preserve">5.22428226470947</t>
   </si>
   <si>
     <t xml:space="preserve">5.19688940048218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32211589813232</t>
+    <t xml:space="preserve">5.32211542129517</t>
   </si>
   <si>
     <t xml:space="preserve">5.47082138061523</t>
@@ -353,13 +353,13 @@
     <t xml:space="preserve">5.29080963134766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1734094619751</t>
+    <t xml:space="preserve">5.17340898513794</t>
   </si>
   <si>
     <t xml:space="preserve">5.09514331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22036933898926</t>
+    <t xml:space="preserve">5.2203688621521</t>
   </si>
   <si>
     <t xml:space="preserve">5.10296964645386</t>
@@ -368,40 +368,40 @@
     <t xml:space="preserve">4.9933967590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15384292602539</t>
+    <t xml:space="preserve">5.15384244918823</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98556995391846</t>
+    <t xml:space="preserve">4.98557043075562</t>
   </si>
   <si>
     <t xml:space="preserve">4.7585973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77033710479736</t>
+    <t xml:space="preserve">4.77033758163452</t>
   </si>
   <si>
     <t xml:space="preserve">4.86425733566284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88773727416992</t>
+    <t xml:space="preserve">4.88773632049561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83295106887817</t>
+    <t xml:space="preserve">4.83295059204102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75468349456787</t>
+    <t xml:space="preserve">4.75468397140503</t>
   </si>
   <si>
     <t xml:space="preserve">4.82903718948364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72337675094604</t>
+    <t xml:space="preserve">4.72337770462036</t>
   </si>
   <si>
     <t xml:space="preserve">4.68815755844116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78207683563232</t>
+    <t xml:space="preserve">4.78207778930664</t>
   </si>
   <si>
     <t xml:space="preserve">4.8759970664978</t>
@@ -410,10 +410,10 @@
     <t xml:space="preserve">5.03644323348999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92686986923218</t>
+    <t xml:space="preserve">4.92687082290649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81338453292847</t>
+    <t xml:space="preserve">4.81338357925415</t>
   </si>
   <si>
     <t xml:space="preserve">4.86034393310547</t>
@@ -422,64 +422,64 @@
     <t xml:space="preserve">5.00122308731079</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77425003051758</t>
+    <t xml:space="preserve">4.77425050735474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82120990753174</t>
+    <t xml:space="preserve">4.8212103843689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69989776611328</t>
+    <t xml:space="preserve">4.69989728927612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69598484039307</t>
+    <t xml:space="preserve">4.69598436355591</t>
   </si>
   <si>
     <t xml:space="preserve">4.90730381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20471668243408</t>
+    <t xml:space="preserve">5.20471620559692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43951559066772</t>
+    <t xml:space="preserve">5.43951463699341</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28298282623291</t>
+    <t xml:space="preserve">5.28298234939575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384927749634</t>
+    <t xml:space="preserve">5.24384880065918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36124801635742</t>
+    <t xml:space="preserve">5.36124897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40038251876831</t>
+    <t xml:space="preserve">5.40038204193115</t>
   </si>
   <si>
     <t xml:space="preserve">5.51778173446655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63518142700195</t>
+    <t xml:space="preserve">5.63518095016479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96991586685181</t>
+    <t xml:space="preserve">4.96991634368896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93078327178955</t>
+    <t xml:space="preserve">4.93078374862671</t>
   </si>
   <si>
     <t xml:space="preserve">4.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12644958496094</t>
+    <t xml:space="preserve">5.1264500617981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04818344116211</t>
+    <t xml:space="preserve">5.04818248748779</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08731651306152</t>
+    <t xml:space="preserve">5.08731603622437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59604835510254</t>
+    <t xml:space="preserve">5.59604787826538</t>
   </si>
   <si>
     <t xml:space="preserve">5.26159763336182</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">5.42103958129883</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34131860733032</t>
+    <t xml:space="preserve">5.34131813049316</t>
   </si>
   <si>
     <t xml:space="preserve">5.22173690795898</t>
@@ -497,43 +497,43 @@
     <t xml:space="preserve">5.14201498031616</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10215520858765</t>
+    <t xml:space="preserve">5.1021556854248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18187618255615</t>
+    <t xml:space="preserve">5.18187570571899</t>
   </si>
   <si>
     <t xml:space="preserve">5.38117933273315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30145835876465</t>
+    <t xml:space="preserve">5.30145788192749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9028525352478</t>
+    <t xml:space="preserve">4.90285205841064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50076055526733</t>
+    <t xml:space="preserve">5.50076150894165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4608998298645</t>
+    <t xml:space="preserve">5.46090030670166</t>
   </si>
   <si>
     <t xml:space="preserve">5.580482006073</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54062175750732</t>
+    <t xml:space="preserve">5.54062128067017</t>
   </si>
   <si>
     <t xml:space="preserve">5.62034273147583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94271230697632</t>
+    <t xml:space="preserve">4.94271278381348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98257350921631</t>
+    <t xml:space="preserve">4.98257303237915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82313108444214</t>
+    <t xml:space="preserve">4.82313060760498</t>
   </si>
   <si>
     <t xml:space="preserve">5.06229448318481</t>
@@ -542,25 +542,25 @@
     <t xml:space="preserve">5.02243423461914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74340963363647</t>
+    <t xml:space="preserve">4.74341011047363</t>
   </si>
   <si>
     <t xml:space="preserve">4.78327035903931</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86299133300781</t>
+    <t xml:space="preserve">4.86299180984497</t>
   </si>
   <si>
     <t xml:space="preserve">5.73992395401001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81964588165283</t>
+    <t xml:space="preserve">5.81964635848999</t>
   </si>
   <si>
     <t xml:space="preserve">5.70006418228149</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66020250320435</t>
+    <t xml:space="preserve">5.66020345687866</t>
   </si>
   <si>
     <t xml:space="preserve">5.77978515625</t>
@@ -569,13 +569,13 @@
     <t xml:space="preserve">5.85950565338135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97908782958984</t>
+    <t xml:space="preserve">5.97908735275269</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29797315597534</t>
+    <t xml:space="preserve">6.29797220230103</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13852977752686</t>
+    <t xml:space="preserve">6.13853025436401</t>
   </si>
   <si>
     <t xml:space="preserve">6.05880928039551</t>
@@ -584,37 +584,37 @@
     <t xml:space="preserve">6.21825122833252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09866952896118</t>
+    <t xml:space="preserve">6.09866905212402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38518524169922</t>
+    <t xml:space="preserve">6.3851842880249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25998497009277</t>
+    <t xml:space="preserve">6.25998449325562</t>
   </si>
   <si>
     <t xml:space="preserve">6.30171823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17651844024658</t>
+    <t xml:space="preserve">6.17651891708374</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42691707611084</t>
+    <t xml:space="preserve">6.426917552948</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34345102310181</t>
+    <t xml:space="preserve">6.34345149993896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46865129470825</t>
+    <t xml:space="preserve">6.46865081787109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96785259246826</t>
+    <t xml:space="preserve">5.9678521156311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0095853805542</t>
+    <t xml:space="preserve">6.00958490371704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13478422164917</t>
+    <t xml:space="preserve">6.13478517532349</t>
   </si>
   <si>
     <t xml:space="preserve">6.05131864547729</t>
@@ -623,7 +623,10 @@
     <t xml:space="preserve">5.92611885070801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09305191040039</t>
+    <t xml:space="preserve">6.09305238723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21825075149536</t>
   </si>
   <si>
     <t xml:space="preserve">6.51038408279419</t>
@@ -635,91 +638,91 @@
     <t xml:space="preserve">5.88438558578491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05291557312012</t>
+    <t xml:space="preserve">7.05291604995728</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09624576568604</t>
+    <t xml:space="preserve">8.09624671936035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80411386489868</t>
+    <t xml:space="preserve">7.804114818573</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63718128204346</t>
+    <t xml:space="preserve">7.63718175888062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55371570587158</t>
+    <t xml:space="preserve">7.55371475219727</t>
   </si>
   <si>
     <t xml:space="preserve">7.34504985809326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17811632156372</t>
+    <t xml:space="preserve">7.17811584472656</t>
   </si>
   <si>
     <t xml:space="preserve">7.51198196411133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47024822235107</t>
+    <t xml:space="preserve">7.47024869918823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30331563949585</t>
+    <t xml:space="preserve">7.30331611633301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851448059082</t>
+    <t xml:space="preserve">7.42851495742798</t>
   </si>
   <si>
     <t xml:space="preserve">7.26158237457275</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3867826461792</t>
+    <t xml:space="preserve">7.38678169250488</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96944952011108</t>
+    <t xml:space="preserve">6.96944999694824</t>
   </si>
   <si>
     <t xml:space="preserve">7.21984910964966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544849395752</t>
+    <t xml:space="preserve">7.59544801712036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76238250732422</t>
+    <t xml:space="preserve">7.76238203048706</t>
   </si>
   <si>
     <t xml:space="preserve">7.84584712982178</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67891407012939</t>
+    <t xml:space="preserve">7.67891359329224</t>
   </si>
   <si>
     <t xml:space="preserve">7.01118278503418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09464979171753</t>
+    <t xml:space="preserve">7.09464883804321</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92771768569946</t>
+    <t xml:space="preserve">6.92771673202515</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76078367233276</t>
+    <t xml:space="preserve">6.76078414916992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80251693725586</t>
+    <t xml:space="preserve">6.80251598358154</t>
   </si>
   <si>
     <t xml:space="preserve">6.71905040740967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84425020217896</t>
+    <t xml:space="preserve">6.8442497253418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59385108947754</t>
+    <t xml:space="preserve">6.59385013580322</t>
   </si>
   <si>
     <t xml:space="preserve">6.67731714248657</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55211734771729</t>
+    <t xml:space="preserve">6.55211782455444</t>
   </si>
   <si>
     <t xml:space="preserve">5.75918626785278</t>
@@ -734,7 +737,7 @@
     <t xml:space="preserve">5.67571926116943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59225225448608</t>
+    <t xml:space="preserve">5.59225273132324</t>
   </si>
   <si>
     <t xml:space="preserve">5.6339864730835</t>
@@ -743,52 +746,52 @@
     <t xml:space="preserve">5.46705341339111</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5505199432373</t>
+    <t xml:space="preserve">5.55052042007446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1749210357666</t>
+    <t xml:space="preserve">5.17492055892944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25838756561279</t>
+    <t xml:space="preserve">5.25838804244995</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38358736038208</t>
+    <t xml:space="preserve">5.38358640670776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13638353347778</t>
+    <t xml:space="preserve">7.13638257980347</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47247123718262</t>
+    <t xml:space="preserve">7.4724702835083</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25269222259521</t>
+    <t xml:space="preserve">7.25269269943237</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29664897918701</t>
+    <t xml:space="preserve">7.2966480255127</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20873641967773</t>
+    <t xml:space="preserve">7.20873689651489</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16478109359741</t>
+    <t xml:space="preserve">7.1647801399231</t>
   </si>
   <si>
     <t xml:space="preserve">7.07686948776245</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98895788192749</t>
+    <t xml:space="preserve">6.98895835876465</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03291320800781</t>
+    <t xml:space="preserve">7.03291368484497</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94500303268433</t>
+    <t xml:space="preserve">6.94500255584717</t>
   </si>
   <si>
     <t xml:space="preserve">6.85709095001221</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72522449493408</t>
+    <t xml:space="preserve">6.72522401809692</t>
   </si>
   <si>
     <t xml:space="preserve">6.81313514709473</t>
@@ -797,7 +800,7 @@
     <t xml:space="preserve">6.76917934417725</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90104627609253</t>
+    <t xml:space="preserve">6.90104675292969</t>
   </si>
   <si>
     <t xml:space="preserve">6.63731241226196</t>
@@ -809,46 +812,43 @@
     <t xml:space="preserve">7.34060382843018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51642751693726</t>
+    <t xml:space="preserve">7.51642656326294</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56038284301758</t>
+    <t xml:space="preserve">7.56038236618042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73620653152466</t>
+    <t xml:space="preserve">7.7362060546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6922492980957</t>
+    <t xml:space="preserve">7.69224977493286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829349517822</t>
+    <t xml:space="preserve">7.64829397201538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78247404098511</t>
+    <t xml:space="preserve">7.78247356414795</t>
   </si>
   <si>
     <t xml:space="preserve">7.8272008895874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73774719238281</t>
+    <t xml:space="preserve">7.73774671554565</t>
   </si>
   <si>
     <t xml:space="preserve">7.69302082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829444885254</t>
+    <t xml:space="preserve">7.60356664657593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60356712341309</t>
+    <t xml:space="preserve">7.91665458679199</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91665506362915</t>
+    <t xml:space="preserve">7.8719277381897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87192916870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96138095855713</t>
+    <t xml:space="preserve">7.96138143539429</t>
   </si>
   <si>
     <t xml:space="preserve">8.2297420501709</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">8.58755779266357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36392307281494</t>
+    <t xml:space="preserve">8.36392402648926</t>
   </si>
   <si>
     <t xml:space="preserve">8.63228416442871</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">8.45337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67701053619385</t>
+    <t xml:space="preserve">8.67701244354248</t>
   </si>
   <si>
     <t xml:space="preserve">8.49810409545898</t>
@@ -890,31 +890,31 @@
     <t xml:space="preserve">8.7217378616333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85591888427734</t>
+    <t xml:space="preserve">8.85591983795166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03482723236084</t>
+    <t xml:space="preserve">9.03482532501221</t>
   </si>
   <si>
     <t xml:space="preserve">10.3766326904297</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4500770568848</t>
+    <t xml:space="preserve">11.4500780105591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7344465255737</t>
+    <t xml:space="preserve">10.734447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0922622680664</t>
+    <t xml:space="preserve">11.0922613143921</t>
   </si>
   <si>
     <t xml:space="preserve">10.9133539199829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.181715965271</t>
+    <t xml:space="preserve">11.1817150115967</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3606233596802</t>
+    <t xml:space="preserve">11.3606224060059</t>
   </si>
   <si>
     <t xml:space="preserve">11.6289844512939</t>
@@ -926,25 +926,25 @@
     <t xml:space="preserve">11.2711696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5555400848389</t>
+    <t xml:space="preserve">10.5555391311646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2871780395508</t>
+    <t xml:space="preserve">10.2871789932251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0028085708618</t>
+    <t xml:space="preserve">11.0028076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6449937820435</t>
+    <t xml:space="preserve">10.6449928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.46608543396</t>
+    <t xml:space="preserve">10.4660863876343</t>
   </si>
   <si>
     <t xml:space="preserve">10.1082715988159</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1977252960205</t>
+    <t xml:space="preserve">10.1977243423462</t>
   </si>
   <si>
     <t xml:space="preserve">9.75045585632324</t>
@@ -956,7 +956,7 @@
     <t xml:space="preserve">12.6129751205444</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9707908630371</t>
+    <t xml:space="preserve">12.9707899093628</t>
   </si>
   <si>
     <t xml:space="preserve">14.0442342758179</t>
@@ -965,13 +965,13 @@
     <t xml:space="preserve">13.7758731842041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5075130462646</t>
+    <t xml:space="preserve">13.507513999939</t>
   </si>
   <si>
     <t xml:space="preserve">13.2391519546509</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0602436065674</t>
+    <t xml:space="preserve">13.0602445602417</t>
   </si>
   <si>
     <t xml:space="preserve">13.4180593490601</t>
@@ -986,46 +986,46 @@
     <t xml:space="preserve">12.702428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1496963500977</t>
+    <t xml:space="preserve">13.149697303772</t>
   </si>
   <si>
     <t xml:space="preserve">13.3286046981812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547815322876</t>
+    <t xml:space="preserve">13.9547805786133</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5969657897949</t>
+    <t xml:space="preserve">13.5969667434692</t>
   </si>
   <si>
     <t xml:space="preserve">13.6864213943481</t>
   </si>
   <si>
-    <t xml:space="preserve">13.865327835083</t>
+    <t xml:space="preserve">13.8653268814087</t>
   </si>
   <si>
     <t xml:space="preserve">14.4020500183105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2965888977051</t>
+    <t xml:space="preserve">15.2965879440308</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2071342468262</t>
+    <t xml:space="preserve">15.2071332931519</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5809574127197</t>
+    <t xml:space="preserve">14.5809564590454</t>
   </si>
   <si>
     <t xml:space="preserve">14.7598648071289</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4915037155151</t>
+    <t xml:space="preserve">14.4915046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5400886535645</t>
+    <t xml:space="preserve">14.5400876998901</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3560371398926</t>
+    <t xml:space="preserve">14.3560361862183</t>
   </si>
   <si>
     <t xml:space="preserve">14.2640104293823</t>
@@ -1037,10 +1037,10 @@
     <t xml:space="preserve">14.8161659240723</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6321134567261</t>
+    <t xml:space="preserve">14.6321144104004</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3683233261108</t>
+    <t xml:space="preserve">15.3683223724365</t>
   </si>
   <si>
     <t xml:space="preserve">15.5523738861084</t>
@@ -1049,25 +1049,25 @@
     <t xml:space="preserve">16.104528427124</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3806037902832</t>
+    <t xml:space="preserve">16.3806056976318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9204759597778</t>
+    <t xml:space="preserve">15.9204750061035</t>
   </si>
   <si>
     <t xml:space="preserve">17.2088394165039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3008651733398</t>
+    <t xml:space="preserve">17.3008632659912</t>
   </si>
   <si>
     <t xml:space="preserve">17.4849166870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5769424438477</t>
+    <t xml:space="preserve">17.576940536499</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6689701080322</t>
+    <t xml:space="preserve">17.6689682006836</t>
   </si>
   <si>
     <t xml:space="preserve">18.4051742553711</t>
@@ -1082,13 +1082,13 @@
     <t xml:space="preserve">20.0616397857666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5340538024902</t>
+    <t xml:space="preserve">21.5340557098389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3745727539062</t>
+    <t xml:space="preserve">23.3745708465576</t>
   </si>
   <si>
-    <t xml:space="preserve">22.270263671875</t>
+    <t xml:space="preserve">22.2702617645264</t>
   </si>
   <si>
     <t xml:space="preserve">22.822416305542</t>
@@ -1103,13 +1103,13 @@
     <t xml:space="preserve">21.902156829834</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0862083435059</t>
+    <t xml:space="preserve">22.0862102508545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0064697265625</t>
+    <t xml:space="preserve">23.0064678192139</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5586242675781</t>
+    <t xml:space="preserve">23.5586261749268</t>
   </si>
   <si>
     <t xml:space="preserve">23.74267578125</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">23.9267272949219</t>
   </si>
   <si>
-    <t xml:space="preserve">24.662935256958</t>
+    <t xml:space="preserve">24.6629333496094</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8469867706299</t>
+    <t xml:space="preserve">24.8469886779785</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2948322296143</t>
+    <t xml:space="preserve">24.2948303222656</t>
   </si>
   <si>
     <t xml:space="preserve">24.1107807159424</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">23.1905212402344</t>
   </si>
   <si>
-    <t xml:space="preserve">25.215087890625</t>
+    <t xml:space="preserve">25.2150897979736</t>
   </si>
   <si>
     <t xml:space="preserve">22.4543132781982</t>
@@ -1145,31 +1145,31 @@
     <t xml:space="preserve">25.9512958526611</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5034503936768</t>
+    <t xml:space="preserve">26.5034523010254</t>
   </si>
   <si>
     <t xml:space="preserve">27.975866317749</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9206924438477</t>
+    <t xml:space="preserve">30.9206943511963</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0801773071289</t>
+    <t xml:space="preserve">29.0801753997803</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7366466522217</t>
+    <t xml:space="preserve">30.736644744873</t>
   </si>
   <si>
     <t xml:space="preserve">30.3685398101807</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2642269134521</t>
+    <t xml:space="preserve">29.2642288208008</t>
   </si>
   <si>
     <t xml:space="preserve">31.4728507995605</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2336235046387</t>
+    <t xml:space="preserve">34.2336273193359</t>
   </si>
   <si>
     <t xml:space="preserve">34.7857780456543</t>
@@ -1178,19 +1178,19 @@
     <t xml:space="preserve">33.8655204772949</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4974174499512</t>
+    <t xml:space="preserve">33.4974212646484</t>
   </si>
   <si>
     <t xml:space="preserve">30.1844863891602</t>
   </si>
   <si>
-    <t xml:space="preserve">27.4237117767334</t>
+    <t xml:space="preserve">27.4237098693848</t>
   </si>
   <si>
     <t xml:space="preserve">26.6875038146973</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5831909179688</t>
+    <t xml:space="preserve">25.5831928253174</t>
   </si>
   <si>
     <t xml:space="preserve">26.3194007873535</t>
@@ -1208,16 +1208,16 @@
     <t xml:space="preserve">28.5280208587646</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7120742797852</t>
+    <t xml:space="preserve">28.7120723724365</t>
   </si>
   <si>
     <t xml:space="preserve">28.3439693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0556087493896</t>
+    <t xml:space="preserve">27.055606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8715553283691</t>
+    <t xml:space="preserve">26.8715572357178</t>
   </si>
   <si>
     <t xml:space="preserve">25.3991413116455</t>
@@ -18642,7 +18642,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G639" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19162,7 +19162,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G659" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -19188,7 +19188,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G660" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19292,7 +19292,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G664" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19500,7 +19500,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G672" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -19526,7 +19526,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G673" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20020,7 +20020,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G692" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20046,7 +20046,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G693" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20124,7 +20124,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G696" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20150,7 +20150,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G697" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -20280,7 +20280,7 @@
         <v>7</v>
       </c>
       <c r="G702" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -20306,7 +20306,7 @@
         <v>7</v>
       </c>
       <c r="G703" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -20332,7 +20332,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G704" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -20592,7 +20592,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G714" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -20618,7 +20618,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G715" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -20696,7 +20696,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G718" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -20748,7 +20748,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G720" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21008,7 +21008,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G730" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21034,7 +21034,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G731" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21060,7 +21060,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G732" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21086,7 +21086,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G733" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -21346,7 +21346,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G743" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -21372,7 +21372,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G744" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -21398,7 +21398,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G745" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -21424,7 +21424,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G746" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -21450,7 +21450,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G747" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -21476,7 +21476,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G748" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -21502,7 +21502,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G749" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -21528,7 +21528,7 @@
         <v>9</v>
       </c>
       <c r="G750" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -21554,7 +21554,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G751" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -21580,7 +21580,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G752" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -21606,7 +21606,7 @@
         <v>8.75</v>
       </c>
       <c r="G753" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -21632,7 +21632,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G754" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -21658,7 +21658,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G755" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -21684,7 +21684,7 @@
         <v>9</v>
       </c>
       <c r="G756" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -21710,7 +21710,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G757" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -21736,7 +21736,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G758" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -21762,7 +21762,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G759" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -21788,7 +21788,7 @@
         <v>9</v>
       </c>
       <c r="G760" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -21814,7 +21814,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G761" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -21840,7 +21840,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G762" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -21866,7 +21866,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G763" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -21892,7 +21892,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G764" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -21918,7 +21918,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G765" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -21944,7 +21944,7 @@
         <v>9</v>
       </c>
       <c r="G766" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -21970,7 +21970,7 @@
         <v>9</v>
       </c>
       <c r="G767" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -21996,7 +21996,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G768" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22022,7 +22022,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G769" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22048,7 +22048,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G770" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22074,7 +22074,7 @@
         <v>8.75</v>
       </c>
       <c r="G771" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22100,7 +22100,7 @@
         <v>8.75</v>
       </c>
       <c r="G772" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22126,7 +22126,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G773" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22152,7 +22152,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G774" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22178,7 +22178,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G775" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22204,7 +22204,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G776" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22230,7 +22230,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G777" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22256,7 +22256,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G778" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22282,7 +22282,7 @@
         <v>9</v>
       </c>
       <c r="G779" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -22308,7 +22308,7 @@
         <v>9</v>
       </c>
       <c r="G780" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -22334,7 +22334,7 @@
         <v>9</v>
       </c>
       <c r="G781" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -22360,7 +22360,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G782" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -22386,7 +22386,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G783" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -22412,7 +22412,7 @@
         <v>8.75</v>
       </c>
       <c r="G784" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -22438,7 +22438,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G785" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -22464,7 +22464,7 @@
         <v>8.75</v>
       </c>
       <c r="G786" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -22490,7 +22490,7 @@
         <v>8.75</v>
       </c>
       <c r="G787" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -22516,7 +22516,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G788" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -22542,7 +22542,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G789" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -22568,7 +22568,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G790" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -22594,7 +22594,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G791" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -22620,7 +22620,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G792" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -22646,7 +22646,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G793" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -22672,7 +22672,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G794" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -22698,7 +22698,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G795" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -22724,7 +22724,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G796" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -22750,7 +22750,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G797" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -22776,7 +22776,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G798" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -22802,7 +22802,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G799" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -22828,7 +22828,7 @@
         <v>8.75</v>
       </c>
       <c r="G800" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -22854,7 +22854,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G801" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -22880,7 +22880,7 @@
         <v>8.75</v>
       </c>
       <c r="G802" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -22906,7 +22906,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G803" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -22932,7 +22932,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G804" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -22958,7 +22958,7 @@
         <v>8.75</v>
       </c>
       <c r="G805" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -22984,7 +22984,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G806" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23010,7 +23010,7 @@
         <v>8.75</v>
       </c>
       <c r="G807" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23036,7 +23036,7 @@
         <v>8.75</v>
       </c>
       <c r="G808" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23062,7 +23062,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G809" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23088,7 +23088,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G810" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23114,7 +23114,7 @@
         <v>8.5</v>
       </c>
       <c r="G811" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23140,7 +23140,7 @@
         <v>8.5</v>
       </c>
       <c r="G812" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23166,7 +23166,7 @@
         <v>8.5</v>
       </c>
       <c r="G813" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23192,7 +23192,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G814" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23218,7 +23218,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G815" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23244,7 +23244,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G816" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23270,7 +23270,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G817" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23296,7 +23296,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G818" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -23322,7 +23322,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G819" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -23348,7 +23348,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G820" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -23374,7 +23374,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G821" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -23400,7 +23400,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G822" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -23426,7 +23426,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G823" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -23452,7 +23452,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G824" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -23478,7 +23478,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G825" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -23504,7 +23504,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G826" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -23530,7 +23530,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G827" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -23556,7 +23556,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G828" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -23582,7 +23582,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G829" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -23608,7 +23608,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G830" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -23634,7 +23634,7 @@
         <v>9</v>
       </c>
       <c r="G831" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -23660,7 +23660,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G832" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -23686,7 +23686,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G833" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -23712,7 +23712,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G834" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -23738,7 +23738,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G835" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -23764,7 +23764,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G836" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -23790,7 +23790,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G837" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -23816,7 +23816,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G838" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -23842,7 +23842,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G839" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -23868,7 +23868,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G840" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -23894,7 +23894,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G841" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -23920,7 +23920,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G842" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -23946,7 +23946,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G843" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -23972,7 +23972,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G844" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -23998,7 +23998,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G845" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24024,7 +24024,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G846" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24050,7 +24050,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G847" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24076,7 +24076,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G848" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24102,7 +24102,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G849" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24128,7 +24128,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G850" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24154,7 +24154,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G851" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24180,7 +24180,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G852" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24206,7 +24206,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G853" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24232,7 +24232,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G854" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24258,7 +24258,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G855" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24284,7 +24284,7 @@
         <v>8</v>
       </c>
       <c r="G856" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24310,7 +24310,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G857" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24336,7 +24336,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G858" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -24414,7 +24414,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G861" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24492,7 +24492,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G864" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -24934,7 +24934,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G881" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25012,7 +25012,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G884" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25038,7 +25038,7 @@
         <v>7</v>
       </c>
       <c r="G885" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25246,7 +25246,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G893" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -25974,7 +25974,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G921" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26000,7 +26000,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G922" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26026,7 +26026,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G923" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -26052,7 +26052,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G924" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26156,7 +26156,7 @@
         <v>7</v>
       </c>
       <c r="G928" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26182,7 +26182,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G929" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26208,7 +26208,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G930" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26234,7 +26234,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G931" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26260,7 +26260,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G932" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26286,7 +26286,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G933" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26312,7 +26312,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G934" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26338,7 +26338,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G935" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26416,7 +26416,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G938" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26442,7 +26442,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G939" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26702,7 +26702,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G949" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26728,7 +26728,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G950" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26754,7 +26754,7 @@
         <v>7</v>
       </c>
       <c r="G951" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -26780,7 +26780,7 @@
         <v>7</v>
       </c>
       <c r="G952" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26806,7 +26806,7 @@
         <v>7</v>
       </c>
       <c r="G953" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26832,7 +26832,7 @@
         <v>7</v>
       </c>
       <c r="G954" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26858,7 +26858,7 @@
         <v>7</v>
       </c>
       <c r="G955" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26884,7 +26884,7 @@
         <v>7</v>
       </c>
       <c r="G956" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26910,7 +26910,7 @@
         <v>7</v>
       </c>
       <c r="G957" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26936,7 +26936,7 @@
         <v>7</v>
       </c>
       <c r="G958" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26962,7 +26962,7 @@
         <v>7</v>
       </c>
       <c r="G959" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -26988,7 +26988,7 @@
         <v>7</v>
       </c>
       <c r="G960" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27014,7 +27014,7 @@
         <v>7</v>
       </c>
       <c r="G961" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27040,7 +27040,7 @@
         <v>7</v>
       </c>
       <c r="G962" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27066,7 +27066,7 @@
         <v>7</v>
       </c>
       <c r="G963" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27092,7 +27092,7 @@
         <v>7</v>
       </c>
       <c r="G964" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27118,7 +27118,7 @@
         <v>7</v>
       </c>
       <c r="G965" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27144,7 +27144,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G966" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27170,7 +27170,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G967" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27196,7 +27196,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G968" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27222,7 +27222,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G969" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -27248,7 +27248,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G970" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27274,7 +27274,7 @@
         <v>6.75</v>
       </c>
       <c r="G971" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27300,7 +27300,7 @@
         <v>6.75</v>
       </c>
       <c r="G972" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27326,7 +27326,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G973" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27352,7 +27352,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G974" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27378,7 +27378,7 @@
         <v>6.75</v>
       </c>
       <c r="G975" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27404,7 +27404,7 @@
         <v>6.75</v>
       </c>
       <c r="G976" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27430,7 +27430,7 @@
         <v>6.75</v>
       </c>
       <c r="G977" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27456,7 +27456,7 @@
         <v>6.75</v>
       </c>
       <c r="G978" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -27482,7 +27482,7 @@
         <v>6.75</v>
       </c>
       <c r="G979" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27508,7 +27508,7 @@
         <v>6.75</v>
       </c>
       <c r="G980" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27534,7 +27534,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G981" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27560,7 +27560,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G982" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -27586,7 +27586,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G983" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -27612,7 +27612,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G984" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27638,7 +27638,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G985" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -27664,7 +27664,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G986" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -27690,7 +27690,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G987" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -27716,7 +27716,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G988" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -27742,7 +27742,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G989" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -27768,7 +27768,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G990" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -27794,7 +27794,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G991" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -27820,7 +27820,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G992" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -27846,7 +27846,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G993" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -27872,7 +27872,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G994" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -27898,7 +27898,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G995" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -27924,7 +27924,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G996" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -27950,7 +27950,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G997" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -27976,7 +27976,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G998" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28002,7 +28002,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G999" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28028,7 +28028,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1000" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28054,7 +28054,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1001" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28080,7 +28080,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1002" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28106,7 +28106,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1003" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28132,7 +28132,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1004" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28158,7 +28158,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1005" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28184,7 +28184,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1006" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28210,7 +28210,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1007" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28236,7 +28236,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1008" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28262,7 +28262,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1009" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28340,7 +28340,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1012" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28366,7 +28366,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1013" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28392,7 +28392,7 @@
         <v>8</v>
       </c>
       <c r="G1014" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28548,7 +28548,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1020" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28574,7 +28574,7 @@
         <v>8.5</v>
       </c>
       <c r="G1021" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28600,7 +28600,7 @@
         <v>8.5</v>
       </c>
       <c r="G1022" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -28626,7 +28626,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1023" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -28652,7 +28652,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1024" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28678,7 +28678,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1025" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28704,7 +28704,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1026" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28730,7 +28730,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1027" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28756,7 +28756,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1028" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28782,7 +28782,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1029" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28808,7 +28808,7 @@
         <v>8.75</v>
       </c>
       <c r="G1030" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28834,7 +28834,7 @@
         <v>8.75</v>
       </c>
       <c r="G1031" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28860,7 +28860,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1032" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28886,7 +28886,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1033" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28912,7 +28912,7 @@
         <v>8.5</v>
       </c>
       <c r="G1034" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28938,7 +28938,7 @@
         <v>8.25</v>
       </c>
       <c r="G1035" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28964,7 +28964,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1036" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -28990,7 +28990,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1037" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29016,7 +29016,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1038" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29042,7 +29042,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1039" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29068,7 +29068,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1040" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29094,7 +29094,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1041" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29120,7 +29120,7 @@
         <v>8</v>
       </c>
       <c r="G1042" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29146,7 +29146,7 @@
         <v>8</v>
       </c>
       <c r="G1043" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29172,7 +29172,7 @@
         <v>8</v>
       </c>
       <c r="G1044" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29198,7 +29198,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1045" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -29224,7 +29224,7 @@
         <v>8</v>
       </c>
       <c r="G1046" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29250,7 +29250,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1047" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -29276,7 +29276,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1048" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29302,7 +29302,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1049" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29328,7 +29328,7 @@
         <v>7.75</v>
       </c>
       <c r="G1050" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29354,7 +29354,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1051" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29380,7 +29380,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1052" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29406,7 +29406,7 @@
         <v>7.75</v>
       </c>
       <c r="G1053" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29432,7 +29432,7 @@
         <v>7.75</v>
       </c>
       <c r="G1054" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29458,7 +29458,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1055" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29484,7 +29484,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1056" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29510,7 +29510,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1057" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29536,7 +29536,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1058" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29562,7 +29562,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1059" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29588,7 +29588,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1060" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29614,7 +29614,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1061" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29640,7 +29640,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1062" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29666,7 +29666,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1063" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29692,7 +29692,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1064" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29718,7 +29718,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1065" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29744,7 +29744,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1066" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29770,7 +29770,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1067" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29796,7 +29796,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1068" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29822,7 +29822,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1069" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29848,7 +29848,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1070" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29874,7 +29874,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1071" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29900,7 +29900,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1072" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -29926,7 +29926,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1073" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -29952,7 +29952,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1074" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -29978,7 +29978,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1075" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30004,7 +30004,7 @@
         <v>8</v>
       </c>
       <c r="G1076" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30030,7 +30030,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1077" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30056,7 +30056,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1078" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30082,7 +30082,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1079" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -30108,7 +30108,7 @@
         <v>8.25</v>
       </c>
       <c r="G1080" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30134,7 +30134,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1081" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30160,7 +30160,7 @@
         <v>8.5</v>
       </c>
       <c r="G1082" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30186,7 +30186,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1083" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30212,7 +30212,7 @@
         <v>8.5</v>
       </c>
       <c r="G1084" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30238,7 +30238,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1085" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30264,7 +30264,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1086" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -30290,7 +30290,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1087" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30316,7 +30316,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1088" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30342,7 +30342,7 @@
         <v>8.5</v>
       </c>
       <c r="G1089" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30368,7 +30368,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1090" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30394,7 +30394,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1091" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30420,7 +30420,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1092" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30446,7 +30446,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1093" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30472,7 +30472,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1094" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30498,7 +30498,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1095" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30524,7 +30524,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1096" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30550,7 +30550,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1097" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30576,7 +30576,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1098" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30602,7 +30602,7 @@
         <v>8.75</v>
       </c>
       <c r="G1099" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30628,7 +30628,7 @@
         <v>8.75</v>
       </c>
       <c r="G1100" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30654,7 +30654,7 @@
         <v>8.75</v>
       </c>
       <c r="G1101" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -30680,7 +30680,7 @@
         <v>8.75</v>
       </c>
       <c r="G1102" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30706,7 +30706,7 @@
         <v>8.75</v>
       </c>
       <c r="G1103" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30732,7 +30732,7 @@
         <v>8.75</v>
       </c>
       <c r="G1104" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30758,7 +30758,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1105" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30784,7 +30784,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1106" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30810,7 +30810,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1107" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30836,7 +30836,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1108" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30862,7 +30862,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1109" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30888,7 +30888,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1110" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -30914,7 +30914,7 @@
         <v>8.75</v>
       </c>
       <c r="G1111" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30940,7 +30940,7 @@
         <v>8.75</v>
       </c>
       <c r="G1112" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -30966,7 +30966,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1113" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -30992,7 +30992,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1114" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31018,7 +31018,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31044,7 +31044,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1116" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31070,7 +31070,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1117" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31096,7 +31096,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1118" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31122,7 +31122,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1119" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31148,7 +31148,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1120" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31174,7 +31174,7 @@
         <v>8.75</v>
       </c>
       <c r="G1121" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31200,7 +31200,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1122" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31226,7 +31226,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1123" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31252,7 +31252,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1124" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31278,7 +31278,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1125" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31304,7 +31304,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1126" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31330,7 +31330,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1127" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31356,7 +31356,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1128" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31382,7 +31382,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1129" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31408,7 +31408,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1130" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31434,7 +31434,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1131" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31460,7 +31460,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1132" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31486,7 +31486,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1133" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31512,7 +31512,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1134" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31564,7 +31564,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1136" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31590,7 +31590,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1137" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31616,7 +31616,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1138" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31642,7 +31642,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1139" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31668,7 +31668,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1140" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31694,7 +31694,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1141" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31720,7 +31720,7 @@
         <v>8.75</v>
       </c>
       <c r="G1142" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31850,7 +31850,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1147" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31902,7 +31902,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1149" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32032,7 +32032,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1154" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32058,7 +32058,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1155" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32084,7 +32084,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1156" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -61649,6 +61649,58 @@
         <v>555</v>
       </c>
       <c r="H2293" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" s="1" t="n">
+        <v>45999.3333333333</v>
+      </c>
+      <c r="B2294" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2294" t="n">
+        <v>37.4000015258789</v>
+      </c>
+      <c r="D2294" t="n">
+        <v>37.4000015258789</v>
+      </c>
+      <c r="E2294" t="n">
+        <v>37.4000015258789</v>
+      </c>
+      <c r="F2294" t="n">
+        <v>37.4000015258789</v>
+      </c>
+      <c r="G2294" t="s">
+        <v>555</v>
+      </c>
+      <c r="H2294" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" s="1" t="n">
+        <v>46000.458599537</v>
+      </c>
+      <c r="B2295" t="n">
+        <v>500</v>
+      </c>
+      <c r="C2295" t="n">
+        <v>38</v>
+      </c>
+      <c r="D2295" t="n">
+        <v>37.7999992370605</v>
+      </c>
+      <c r="E2295" t="n">
+        <v>37.7999992370605</v>
+      </c>
+      <c r="F2295" t="n">
+        <v>38</v>
+      </c>
+      <c r="G2295" t="s">
+        <v>537</v>
+      </c>
+      <c r="H2295" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">FPE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42625832557678</t>
+    <t xml:space="preserve">2.4262580871582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43408513069153</t>
+    <t xml:space="preserve">2.43408489227295</t>
   </si>
   <si>
     <t xml:space="preserve">2.41060519218445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45756530761719</t>
+    <t xml:space="preserve">2.45756506919861</t>
   </si>
   <si>
     <t xml:space="preserve">2.39495182037354</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">2.41843199729919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35581922531128</t>
+    <t xml:space="preserve">2.35581874847412</t>
   </si>
   <si>
     <t xml:space="preserve">2.37147212028503</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">2.50452518463135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36364555358887</t>
+    <t xml:space="preserve">2.36364507675171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44973874092102</t>
+    <t xml:space="preserve">2.44973826408386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37303781509399</t>
+    <t xml:space="preserve">2.37303757667542</t>
   </si>
   <si>
     <t xml:space="preserve">2.34955763816833</t>
@@ -89,37 +89,37 @@
     <t xml:space="preserve">2.46382665634155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38712549209595</t>
+    <t xml:space="preserve">2.38712525367737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45443415641785</t>
+    <t xml:space="preserve">2.45443439483643</t>
   </si>
   <si>
     <t xml:space="preserve">2.34799218177795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48104524612427</t>
+    <t xml:space="preserve">2.48104500770569</t>
   </si>
   <si>
     <t xml:space="preserve">2.37929844856262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38555979728699</t>
+    <t xml:space="preserve">2.38556003570557</t>
   </si>
   <si>
     <t xml:space="preserve">2.4419116973877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78002285957336</t>
+    <t xml:space="preserve">2.78002262115479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36702060699463</t>
+    <t xml:space="preserve">3.36702108383179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62530016899109</t>
+    <t xml:space="preserve">3.62529993057251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3106689453125</t>
+    <t xml:space="preserve">3.31066870689392</t>
   </si>
   <si>
     <t xml:space="preserve">3.25588250160217</t>
@@ -131,13 +131,13 @@
     <t xml:space="preserve">3.0523898601532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09152317047119</t>
+    <t xml:space="preserve">3.09152293205261</t>
   </si>
   <si>
     <t xml:space="preserve">3.04456329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03673648834229</t>
+    <t xml:space="preserve">3.03673672676086</t>
   </si>
   <si>
     <t xml:space="preserve">3.03830194473267</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">3.15413618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3091037273407</t>
+    <t xml:space="preserve">3.30910396575928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30284190177917</t>
+    <t xml:space="preserve">3.30284214019775</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35762858390808</t>
+    <t xml:space="preserve">3.35762906074524</t>
   </si>
   <si>
     <t xml:space="preserve">3.57677507400513</t>
@@ -161,52 +161,52 @@
     <t xml:space="preserve">3.52198815345764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40458822250366</t>
+    <t xml:space="preserve">3.40458869934082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59242796897888</t>
+    <t xml:space="preserve">3.59242844581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58460092544556</t>
+    <t xml:space="preserve">3.58460140228271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67852067947388</t>
+    <t xml:space="preserve">3.67852091789246</t>
   </si>
   <si>
     <t xml:space="preserve">3.60025429725647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59555840492249</t>
+    <t xml:space="preserve">3.59555864334106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632231712341</t>
+    <t xml:space="preserve">3.32632207870483</t>
   </si>
   <si>
     <t xml:space="preserve">3.29501557350159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37484693527222</t>
+    <t xml:space="preserve">3.3748471736908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38267397880554</t>
+    <t xml:space="preserve">3.38267350196838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44372200965881</t>
+    <t xml:space="preserve">3.44372224807739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5908625125885</t>
+    <t xml:space="preserve">3.59086298942566</t>
   </si>
   <si>
     <t xml:space="preserve">3.47972440719604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42650318145752</t>
+    <t xml:space="preserve">3.42650270462036</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41241526603699</t>
+    <t xml:space="preserve">3.41241502761841</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24022936820984</t>
+    <t xml:space="preserve">3.2402286529541</t>
   </si>
   <si>
     <t xml:space="preserve">3.21048808097839</t>
@@ -218,28 +218,28 @@
     <t xml:space="preserve">3.16196250915527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20892262458801</t>
+    <t xml:space="preserve">3.20892238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13848304748535</t>
+    <t xml:space="preserve">3.13848328590393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23240280151367</t>
+    <t xml:space="preserve">3.23240256309509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31849527359009</t>
+    <t xml:space="preserve">3.31849551200867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27623224258423</t>
+    <t xml:space="preserve">3.27623152732849</t>
   </si>
   <si>
     <t xml:space="preserve">3.18857312202454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14317846298218</t>
+    <t xml:space="preserve">3.14317870140076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11500310897827</t>
+    <t xml:space="preserve">3.11500287055969</t>
   </si>
   <si>
     <t xml:space="preserve">3.00073409080505</t>
@@ -248,73 +248,73 @@
     <t xml:space="preserve">2.97412323951721</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06021666526794</t>
+    <t xml:space="preserve">3.06021618843079</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90368342399597</t>
+    <t xml:space="preserve">2.90368366241455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8958568572998</t>
+    <t xml:space="preserve">2.89585709571838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82854771614075</t>
+    <t xml:space="preserve">2.82854819297791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83637452125549</t>
+    <t xml:space="preserve">2.83637475967407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90994501113892</t>
+    <t xml:space="preserve">2.90994477272034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491231918335</t>
+    <t xml:space="preserve">3.06491208076477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13065648078918</t>
+    <t xml:space="preserve">3.13065624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14474439620972</t>
+    <t xml:space="preserve">3.14474415779114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21361827850342</t>
+    <t xml:space="preserve">3.21361875534058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28562355041504</t>
+    <t xml:space="preserve">3.28562378883362</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35919404029846</t>
+    <t xml:space="preserve">3.35919380187988</t>
   </si>
   <si>
     <t xml:space="preserve">3.36388969421387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91332030296326</t>
+    <t xml:space="preserve">3.9133198261261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34378623962402</t>
+    <t xml:space="preserve">4.34378576278687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7938175201416</t>
+    <t xml:space="preserve">4.79381799697876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47864818572998</t>
+    <t xml:space="preserve">5.47864866256714</t>
   </si>
   <si>
     <t xml:space="preserve">6.09303951263428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41603517532349</t>
+    <t xml:space="preserve">5.41603469848633</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71344709396362</t>
+    <t xml:space="preserve">5.71344757080078</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56865453720093</t>
+    <t xml:space="preserve">5.56865406036377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41994905471802</t>
+    <t xml:space="preserve">5.41994857788086</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16558218002319</t>
+    <t xml:space="preserve">5.16558265686035</t>
   </si>
   <si>
     <t xml:space="preserve">4.9464373588562</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">4.7038106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67641687393188</t>
+    <t xml:space="preserve">4.6764178276062</t>
   </si>
   <si>
     <t xml:space="preserve">5.0090503692627</t>
@@ -332,19 +332,19 @@
     <t xml:space="preserve">5.55691480636597</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30646276473999</t>
+    <t xml:space="preserve">5.30646228790283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22428321838379</t>
+    <t xml:space="preserve">5.22428226470947</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19688987731934</t>
+    <t xml:space="preserve">5.19688940048218</t>
   </si>
   <si>
     <t xml:space="preserve">5.32211542129517</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47082138061523</t>
+    <t xml:space="preserve">5.47082185745239</t>
   </si>
   <si>
     <t xml:space="preserve">5.36907577514648</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">5.2908091545105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1734094619751</t>
+    <t xml:space="preserve">5.17340898513794</t>
   </si>
   <si>
     <t xml:space="preserve">5.09514284133911</t>
@@ -362,13 +362,13 @@
     <t xml:space="preserve">5.2203688621521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10296964645386</t>
+    <t xml:space="preserve">5.10297012329102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99339723587036</t>
+    <t xml:space="preserve">4.99339628219604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15384244918823</t>
+    <t xml:space="preserve">5.15384292602539</t>
   </si>
   <si>
     <t xml:space="preserve">4.9855694770813</t>
@@ -380,85 +380,85 @@
     <t xml:space="preserve">4.77033710479736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86425733566284</t>
+    <t xml:space="preserve">4.86425685882568</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88773727416992</t>
+    <t xml:space="preserve">4.88773679733276</t>
   </si>
   <si>
     <t xml:space="preserve">4.83295059204102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75468349456787</t>
+    <t xml:space="preserve">4.75468397140503</t>
   </si>
   <si>
     <t xml:space="preserve">4.82903718948364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7233772277832</t>
+    <t xml:space="preserve">4.72337675094604</t>
   </si>
   <si>
     <t xml:space="preserve">4.68815755844116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78207778930664</t>
+    <t xml:space="preserve">4.78207731246948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87599658966064</t>
+    <t xml:space="preserve">4.8759970664978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03644323348999</t>
+    <t xml:space="preserve">5.03644275665283</t>
   </si>
   <si>
     <t xml:space="preserve">4.92686986923218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81338357925415</t>
+    <t xml:space="preserve">4.81338405609131</t>
   </si>
   <si>
     <t xml:space="preserve">4.86034393310547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00122261047363</t>
+    <t xml:space="preserve">5.00122308731079</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77425098419189</t>
+    <t xml:space="preserve">4.77425050735474</t>
   </si>
   <si>
     <t xml:space="preserve">4.8212103843689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69989728927612</t>
+    <t xml:space="preserve">4.69989824295044</t>
   </si>
   <si>
     <t xml:space="preserve">4.69598436355591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90730285644531</t>
+    <t xml:space="preserve">4.90730381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20471572875977</t>
+    <t xml:space="preserve">5.20471620559692</t>
   </si>
   <si>
     <t xml:space="preserve">5.43951559066772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28298234939575</t>
+    <t xml:space="preserve">5.28298187255859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384832382202</t>
+    <t xml:space="preserve">5.24384927749634</t>
   </si>
   <si>
     <t xml:space="preserve">5.36124897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40038156509399</t>
+    <t xml:space="preserve">5.40038204193115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51778125762939</t>
+    <t xml:space="preserve">5.51778173446655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63518095016479</t>
+    <t xml:space="preserve">5.63518142700195</t>
   </si>
   <si>
     <t xml:space="preserve">4.96991682052612</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">4.93078374862671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85251665115356</t>
+    <t xml:space="preserve">4.85251617431641</t>
   </si>
   <si>
     <t xml:space="preserve">5.12644958496094</t>
@@ -476,13 +476,13 @@
     <t xml:space="preserve">5.04818296432495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08731651306152</t>
+    <t xml:space="preserve">5.08731603622437</t>
   </si>
   <si>
     <t xml:space="preserve">5.59604787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2615966796875</t>
+    <t xml:space="preserve">5.26159715652466</t>
   </si>
   <si>
     <t xml:space="preserve">5.42103958129883</t>
@@ -503,28 +503,28 @@
     <t xml:space="preserve">5.18187570571899</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38117980957031</t>
+    <t xml:space="preserve">5.381178855896</t>
   </si>
   <si>
     <t xml:space="preserve">5.30145788192749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90285158157349</t>
+    <t xml:space="preserve">4.90285205841064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50076055526733</t>
+    <t xml:space="preserve">5.50076103210449</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46090078353882</t>
+    <t xml:space="preserve">5.46090030670166</t>
   </si>
   <si>
     <t xml:space="preserve">5.580482006073</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54062175750732</t>
+    <t xml:space="preserve">5.54062128067017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62034273147583</t>
+    <t xml:space="preserve">5.62034225463867</t>
   </si>
   <si>
     <t xml:space="preserve">4.94271230697632</t>
@@ -536,28 +536,28 @@
     <t xml:space="preserve">4.82313060760498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06229448318481</t>
+    <t xml:space="preserve">5.06229400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02243375778198</t>
+    <t xml:space="preserve">5.02243423461914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74341011047363</t>
+    <t xml:space="preserve">4.74340915679932</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78327035903931</t>
+    <t xml:space="preserve">4.78327083587646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86299133300781</t>
+    <t xml:space="preserve">4.86299085617065</t>
   </si>
   <si>
     <t xml:space="preserve">5.73992443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81964588165283</t>
+    <t xml:space="preserve">5.81964540481567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70006370544434</t>
+    <t xml:space="preserve">5.70006418228149</t>
   </si>
   <si>
     <t xml:space="preserve">5.6602029800415</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">5.77978515625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85950565338135</t>
+    <t xml:space="preserve">5.85950613021851</t>
   </si>
   <si>
     <t xml:space="preserve">5.979088306427</t>
@@ -578,13 +578,13 @@
     <t xml:space="preserve">6.13853025436401</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05880928039551</t>
+    <t xml:space="preserve">6.05880832672119</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825122833252</t>
+    <t xml:space="preserve">6.21825170516968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09866952896118</t>
+    <t xml:space="preserve">6.09867000579834</t>
   </si>
   <si>
     <t xml:space="preserve">6.38518476486206</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">6.426917552948</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34345102310181</t>
+    <t xml:space="preserve">6.34345054626465</t>
   </si>
   <si>
     <t xml:space="preserve">6.46865081787109</t>
@@ -620,10 +620,13 @@
     <t xml:space="preserve">6.05131864547729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92611885070801</t>
+    <t xml:space="preserve">5.92611837387085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09305191040039</t>
+    <t xml:space="preserve">6.09305143356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21825075149536</t>
   </si>
   <si>
     <t xml:space="preserve">6.51038408279419</t>
@@ -635,13 +638,13 @@
     <t xml:space="preserve">5.88438558578491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05291604995728</t>
+    <t xml:space="preserve">7.05291557312012</t>
   </si>
   <si>
     <t xml:space="preserve">8.09624671936035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80411434173584</t>
+    <t xml:space="preserve">7.804114818573</t>
   </si>
   <si>
     <t xml:space="preserve">7.6371808052063</t>
@@ -656,43 +659,43 @@
     <t xml:space="preserve">7.17811679840088</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51198148727417</t>
+    <t xml:space="preserve">7.51198244094849</t>
   </si>
   <si>
     <t xml:space="preserve">7.47024869918823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30331563949585</t>
+    <t xml:space="preserve">7.30331468582153</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851495742798</t>
+    <t xml:space="preserve">7.42851591110229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2615818977356</t>
+    <t xml:space="preserve">7.26158285140991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38678216934204</t>
+    <t xml:space="preserve">7.3867826461792</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96944952011108</t>
+    <t xml:space="preserve">6.9694504737854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2198486328125</t>
+    <t xml:space="preserve">7.21984910964966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544849395752</t>
+    <t xml:space="preserve">7.59544801712036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76238059997559</t>
+    <t xml:space="preserve">7.76238203048706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84584712982178</t>
+    <t xml:space="preserve">7.84584760665894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67891407012939</t>
+    <t xml:space="preserve">7.67891454696655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01118326187134</t>
+    <t xml:space="preserve">7.01118278503418</t>
   </si>
   <si>
     <t xml:space="preserve">7.09464931488037</t>
@@ -701,22 +704,22 @@
     <t xml:space="preserve">6.92771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76078414916992</t>
+    <t xml:space="preserve">6.76078367233276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8025164604187</t>
+    <t xml:space="preserve">6.80251598358154</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71905088424683</t>
+    <t xml:space="preserve">6.71905040740967</t>
   </si>
   <si>
     <t xml:space="preserve">6.8442497253418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59385108947754</t>
+    <t xml:space="preserve">6.59385061264038</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67731761932373</t>
+    <t xml:space="preserve">6.67731714248657</t>
   </si>
   <si>
     <t xml:space="preserve">6.55211734771729</t>
@@ -725,49 +728,49 @@
     <t xml:space="preserve">5.75918626785278</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71745252609253</t>
+    <t xml:space="preserve">5.71745300292969</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80091953277588</t>
+    <t xml:space="preserve">5.80091905593872</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67571926116943</t>
+    <t xml:space="preserve">5.67571973800659</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59225225448608</t>
+    <t xml:space="preserve">5.59225273132324</t>
   </si>
   <si>
     <t xml:space="preserve">5.63398599624634</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46705389022827</t>
+    <t xml:space="preserve">5.46705341339111</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55051946640015</t>
+    <t xml:space="preserve">5.5505199432373</t>
   </si>
   <si>
     <t xml:space="preserve">5.17492055892944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25838708877563</t>
+    <t xml:space="preserve">5.25838756561279</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38358688354492</t>
+    <t xml:space="preserve">5.38358640670776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13638257980347</t>
+    <t xml:space="preserve">7.13638353347778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4724702835083</t>
+    <t xml:space="preserve">7.47247123718262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25269269943237</t>
+    <t xml:space="preserve">7.25269222259521</t>
   </si>
   <si>
     <t xml:space="preserve">7.29664754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20873689651489</t>
+    <t xml:space="preserve">7.20873641967773</t>
   </si>
   <si>
     <t xml:space="preserve">7.16478061676025</t>
@@ -776,10 +779,10 @@
     <t xml:space="preserve">7.07686948776245</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98895788192749</t>
+    <t xml:space="preserve">6.98895740509033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03291320800781</t>
+    <t xml:space="preserve">7.03291368484497</t>
   </si>
   <si>
     <t xml:space="preserve">6.94500255584717</t>
@@ -788,16 +791,16 @@
     <t xml:space="preserve">6.85709095001221</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72522354125977</t>
+    <t xml:space="preserve">6.72522401809692</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81313562393188</t>
+    <t xml:space="preserve">6.81313514709473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76917886734009</t>
+    <t xml:space="preserve">6.76917934417725</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90104627609253</t>
+    <t xml:space="preserve">6.90104675292969</t>
   </si>
   <si>
     <t xml:space="preserve">6.63731241226196</t>
@@ -812,46 +815,43 @@
     <t xml:space="preserve">7.5164270401001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56038331985474</t>
+    <t xml:space="preserve">7.56038284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851591110229</t>
+    <t xml:space="preserve">7.42851495742798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73620653152466</t>
+    <t xml:space="preserve">7.7362060546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69224977493286</t>
+    <t xml:space="preserve">7.69224882125854</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829349517822</t>
+    <t xml:space="preserve">7.64829444885254</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78247404098511</t>
+    <t xml:space="preserve">7.78247451782227</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8272008895874</t>
+    <t xml:space="preserve">7.82720041275024</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73774671554565</t>
+    <t xml:space="preserve">7.7377462387085</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69302129745483</t>
+    <t xml:space="preserve">7.69302082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829397201538</t>
+    <t xml:space="preserve">7.60356616973877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60356569290161</t>
+    <t xml:space="preserve">7.91665554046631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91665506362915</t>
+    <t xml:space="preserve">7.87192869186401</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87192916870117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96138095855713</t>
+    <t xml:space="preserve">7.96138048171997</t>
   </si>
   <si>
     <t xml:space="preserve">8.2297420501709</t>
@@ -863,19 +863,19 @@
     <t xml:space="preserve">8.58755779266357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36392402648926</t>
+    <t xml:space="preserve">8.36392307281494</t>
   </si>
   <si>
     <t xml:space="preserve">8.63228416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54283046722412</t>
+    <t xml:space="preserve">8.54283142089844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40864944458008</t>
+    <t xml:space="preserve">8.40865039825439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27446937561035</t>
+    <t xml:space="preserve">8.27447032928467</t>
   </si>
   <si>
     <t xml:space="preserve">8.45337677001953</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">8.67701148986816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49810409545898</t>
+    <t xml:space="preserve">8.49810314178467</t>
   </si>
   <si>
     <t xml:space="preserve">8.81119251251221</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">8.85591888427734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03482627868652</t>
+    <t xml:space="preserve">9.03482723236084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.376633644104</t>
+    <t xml:space="preserve">10.3766326904297</t>
   </si>
   <si>
     <t xml:space="preserve">11.4500770568848</t>
@@ -908,25 +908,25 @@
     <t xml:space="preserve">10.734447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0922622680664</t>
+    <t xml:space="preserve">11.0922603607178</t>
   </si>
   <si>
     <t xml:space="preserve">10.9133548736572</t>
   </si>
   <si>
-    <t xml:space="preserve">11.181715965271</t>
+    <t xml:space="preserve">11.1817150115967</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3606224060059</t>
+    <t xml:space="preserve">11.3606233596802</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6289844512939</t>
+    <t xml:space="preserve">11.6289854049683</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5395307540894</t>
+    <t xml:space="preserve">11.539529800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2711696624756</t>
+    <t xml:space="preserve">11.2711706161499</t>
   </si>
   <si>
     <t xml:space="preserve">10.5555391311646</t>
@@ -935,34 +935,34 @@
     <t xml:space="preserve">10.2871780395508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0028076171875</t>
+    <t xml:space="preserve">11.0028085708618</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6449937820435</t>
+    <t xml:space="preserve">10.6449928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4660863876343</t>
+    <t xml:space="preserve">10.4660873413086</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1082706451416</t>
+    <t xml:space="preserve">10.1082715988159</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1977243423462</t>
+    <t xml:space="preserve">10.1977252960205</t>
   </si>
   <si>
     <t xml:space="preserve">9.75045585632324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.018816947937</t>
+    <t xml:space="preserve">10.0188159942627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6129760742188</t>
+    <t xml:space="preserve">12.6129751205444</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9707899093628</t>
+    <t xml:space="preserve">12.9707908630371</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0442342758179</t>
+    <t xml:space="preserve">14.0442352294922</t>
   </si>
   <si>
     <t xml:space="preserve">13.7758731842041</t>
@@ -977,58 +977,58 @@
     <t xml:space="preserve">13.0602445602417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4180603027344</t>
+    <t xml:space="preserve">13.4180583953857</t>
   </si>
   <si>
     <t xml:space="preserve">12.8813362121582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7918825149536</t>
+    <t xml:space="preserve">12.7918834686279</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7024297714233</t>
+    <t xml:space="preserve">12.702428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.149697303772</t>
+    <t xml:space="preserve">13.1496963500977</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3286037445068</t>
+    <t xml:space="preserve">13.3286056518555</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547815322876</t>
+    <t xml:space="preserve">13.9547805786133</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5969648361206</t>
+    <t xml:space="preserve">13.5969667434692</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6864204406738</t>
+    <t xml:space="preserve">13.6864194869995</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8653287887573</t>
+    <t xml:space="preserve">13.865327835083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4020500183105</t>
+    <t xml:space="preserve">14.4020509719849</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2965879440308</t>
+    <t xml:space="preserve">15.2965888977051</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2071313858032</t>
+    <t xml:space="preserve">15.2071323394775</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5809564590454</t>
+    <t xml:space="preserve">14.5809555053711</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7598648071289</t>
+    <t xml:space="preserve">14.7598657608032</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4915037155151</t>
+    <t xml:space="preserve">14.4915056228638</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5400876998901</t>
+    <t xml:space="preserve">14.5400886535645</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3560361862183</t>
+    <t xml:space="preserve">14.3560371398926</t>
   </si>
   <si>
     <t xml:space="preserve">14.2640104293823</t>
@@ -1037,22 +1037,22 @@
     <t xml:space="preserve">14.1719846725464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8161659240723</t>
+    <t xml:space="preserve">14.8161668777466</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6321144104004</t>
+    <t xml:space="preserve">14.6321134567261</t>
   </si>
   <si>
     <t xml:space="preserve">15.3683223724365</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5523738861084</t>
+    <t xml:space="preserve">15.5523729324341</t>
   </si>
   <si>
-    <t xml:space="preserve">16.104528427124</t>
+    <t xml:space="preserve">16.1045265197754</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3806056976318</t>
+    <t xml:space="preserve">16.3806037902832</t>
   </si>
   <si>
     <t xml:space="preserve">15.9204750061035</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">17.4849166870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.576940536499</t>
+    <t xml:space="preserve">17.5769424438477</t>
   </si>
   <si>
     <t xml:space="preserve">17.6689682006836</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">18.4051742553711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1413803100586</t>
+    <t xml:space="preserve">19.1413822174072</t>
   </si>
   <si>
     <t xml:space="preserve">19.6935367584229</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">21.5340557098389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3745708465576</t>
+    <t xml:space="preserve">23.3745727539062</t>
   </si>
   <si>
     <t xml:space="preserve">22.2702617645264</t>
@@ -1097,10 +1097,10 @@
     <t xml:space="preserve">22.822416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6137962341309</t>
+    <t xml:space="preserve">20.6137943267822</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3254337310791</t>
+    <t xml:space="preserve">19.3254356384277</t>
   </si>
   <si>
     <t xml:space="preserve">21.902156829834</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">23.0064678192139</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5586261749268</t>
+    <t xml:space="preserve">23.5586242675781</t>
   </si>
   <si>
-    <t xml:space="preserve">23.74267578125</t>
+    <t xml:space="preserve">23.7426738739014</t>
   </si>
   <si>
     <t xml:space="preserve">23.9267272949219</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">24.6629333496094</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8469886779785</t>
+    <t xml:space="preserve">24.8469867706299</t>
   </si>
   <si>
     <t xml:space="preserve">24.2948303222656</t>
@@ -1139,13 +1139,13 @@
     <t xml:space="preserve">25.2150897979736</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4543132781982</t>
+    <t xml:space="preserve">22.4543151855469</t>
   </si>
   <si>
     <t xml:space="preserve">24.4788837432861</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9512958526611</t>
+    <t xml:space="preserve">25.9512977600098</t>
   </si>
   <si>
     <t xml:space="preserve">26.5034523010254</t>
@@ -1154,10 +1154,10 @@
     <t xml:space="preserve">27.975866317749</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9206943511963</t>
+    <t xml:space="preserve">30.920690536499</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0801753997803</t>
+    <t xml:space="preserve">29.0801773071289</t>
   </si>
   <si>
     <t xml:space="preserve">30.736644744873</t>
@@ -1166,16 +1166,16 @@
     <t xml:space="preserve">30.3685398101807</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2642288208008</t>
+    <t xml:space="preserve">29.2642269134521</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4728507995605</t>
+    <t xml:space="preserve">31.4728527069092</t>
   </si>
   <si>
     <t xml:space="preserve">34.2336273193359</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7857780456543</t>
+    <t xml:space="preserve">34.7857818603516</t>
   </si>
   <si>
     <t xml:space="preserve">33.8655204772949</t>
@@ -1184,7 +1184,7 @@
     <t xml:space="preserve">33.4974212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1844863891602</t>
+    <t xml:space="preserve">30.1844844818115</t>
   </si>
   <si>
     <t xml:space="preserve">27.4237098693848</t>
@@ -1193,16 +1193,16 @@
     <t xml:space="preserve">26.6875038146973</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5831928253174</t>
+    <t xml:space="preserve">25.583194732666</t>
   </si>
   <si>
     <t xml:space="preserve">26.3194007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7918167114258</t>
+    <t xml:space="preserve">27.7918148040771</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8961238861084</t>
+    <t xml:space="preserve">28.896125793457</t>
   </si>
   <si>
     <t xml:space="preserve">29.4482803344727</t>
@@ -1211,22 +1211,22 @@
     <t xml:space="preserve">28.5280208587646</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7120723724365</t>
+    <t xml:space="preserve">28.7120742797852</t>
   </si>
   <si>
     <t xml:space="preserve">28.3439693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">27.055606842041</t>
+    <t xml:space="preserve">27.0556049346924</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8715572357178</t>
+    <t xml:space="preserve">26.8715553283691</t>
   </si>
   <si>
     <t xml:space="preserve">25.3991413116455</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7672443389893</t>
+    <t xml:space="preserve">25.7672462463379</t>
   </si>
   <si>
     <t xml:space="preserve">25.0310382843018</t>
@@ -1235,61 +1235,61 @@
     <t xml:space="preserve">27.6077632904053</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5525913238525</t>
+    <t xml:space="preserve">30.5525894165039</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6323318481445</t>
+    <t xml:space="preserve">29.6323337554932</t>
   </si>
   <si>
     <t xml:space="preserve">30.0004329681396</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3931083679199</t>
+    <t xml:space="preserve">32.3931121826172</t>
   </si>
   <si>
-    <t xml:space="preserve">32.209056854248</t>
+    <t xml:space="preserve">32.2090530395508</t>
   </si>
   <si>
-    <t xml:space="preserve">31.28879737854</t>
+    <t xml:space="preserve">31.2887954711914</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6569023132324</t>
+    <t xml:space="preserve">31.6569042205811</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0250015258789</t>
+    <t xml:space="preserve">32.0250053405762</t>
   </si>
   <si>
     <t xml:space="preserve">32.0337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5990715026855</t>
+    <t xml:space="preserve">32.5990676879883</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1643714904785</t>
+    <t xml:space="preserve">33.1643753051758</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6569004058838</t>
+    <t xml:space="preserve">31.6568984985352</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4106369018555</t>
+    <t xml:space="preserve">32.4106407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7875022888184</t>
+    <t xml:space="preserve">32.7875061035156</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9759407043457</t>
+    <t xml:space="preserve">32.9759368896484</t>
   </si>
   <si>
     <t xml:space="preserve">30.9031639099121</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8453369140625</t>
+    <t xml:space="preserve">31.8453350067139</t>
   </si>
   <si>
     <t xml:space="preserve">30.714729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5262985229492</t>
+    <t xml:space="preserve">30.5263004302979</t>
   </si>
   <si>
     <t xml:space="preserve">31.2800331115723</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">30.1494293212891</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3378639221191</t>
+    <t xml:space="preserve">30.3378658294678</t>
   </si>
   <si>
     <t xml:space="preserve">29.395694732666</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">28.2650909423828</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6997890472412</t>
+    <t xml:space="preserve">27.6997871398926</t>
   </si>
   <si>
     <t xml:space="preserve">28.0766563415527</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">25.2501468658447</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3079776763916</t>
+    <t xml:space="preserve">24.307975769043</t>
   </si>
   <si>
     <t xml:space="preserve">23.9311103820801</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">23.7426776885986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.177375793457</t>
+    <t xml:space="preserve">23.1773738861084</t>
   </si>
   <si>
     <t xml:space="preserve">22.6120719909668</t>
@@ -1373,10 +1373,10 @@
     <t xml:space="preserve">22.2352046966553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0467700958252</t>
+    <t xml:space="preserve">22.0467720031738</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8005084991455</t>
+    <t xml:space="preserve">22.8005065917969</t>
   </si>
   <si>
     <t xml:space="preserve">22.988941192627</t>
@@ -1391,19 +1391,19 @@
     <t xml:space="preserve">25.6270160675049</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3807506561279</t>
+    <t xml:space="preserve">26.3807525634766</t>
   </si>
   <si>
-    <t xml:space="preserve">27.134485244751</t>
+    <t xml:space="preserve">27.1344871520996</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9460525512695</t>
+    <t xml:space="preserve">26.9460544586182</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3229198455811</t>
+    <t xml:space="preserve">27.3229217529297</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1923160552979</t>
+    <t xml:space="preserve">26.1923179626465</t>
   </si>
   <si>
     <t xml:space="preserve">26.7576179504395</t>
@@ -18645,7 +18645,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G639" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19165,7 +19165,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G659" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -19191,7 +19191,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G660" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19295,7 +19295,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G664" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19503,7 +19503,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G672" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -19529,7 +19529,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G673" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20023,7 +20023,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G692" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20049,7 +20049,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G693" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20127,7 +20127,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G696" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20153,7 +20153,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G697" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -20283,7 +20283,7 @@
         <v>7</v>
       </c>
       <c r="G702" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -20309,7 +20309,7 @@
         <v>7</v>
       </c>
       <c r="G703" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -20335,7 +20335,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G704" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -20595,7 +20595,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G714" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -20621,7 +20621,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G715" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -20699,7 +20699,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G718" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -20751,7 +20751,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G720" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21011,7 +21011,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G730" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21037,7 +21037,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G731" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21063,7 +21063,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G732" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21089,7 +21089,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G733" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -21349,7 +21349,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G743" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -21375,7 +21375,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G744" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -21401,7 +21401,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G745" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -21427,7 +21427,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G746" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -21453,7 +21453,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G747" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -21479,7 +21479,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G748" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -21505,7 +21505,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G749" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -21531,7 +21531,7 @@
         <v>9</v>
       </c>
       <c r="G750" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -21557,7 +21557,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G751" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -21583,7 +21583,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G752" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -21609,7 +21609,7 @@
         <v>8.75</v>
       </c>
       <c r="G753" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -21635,7 +21635,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G754" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -21661,7 +21661,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G755" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -21687,7 +21687,7 @@
         <v>9</v>
       </c>
       <c r="G756" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -21713,7 +21713,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G757" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -21739,7 +21739,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G758" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -21765,7 +21765,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G759" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -21791,7 +21791,7 @@
         <v>9</v>
       </c>
       <c r="G760" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -21817,7 +21817,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G761" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -21843,7 +21843,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G762" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -21869,7 +21869,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G763" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -21895,7 +21895,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G764" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -21921,7 +21921,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G765" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -21947,7 +21947,7 @@
         <v>9</v>
       </c>
       <c r="G766" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -21973,7 +21973,7 @@
         <v>9</v>
       </c>
       <c r="G767" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -21999,7 +21999,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G768" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22025,7 +22025,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G769" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22051,7 +22051,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G770" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22077,7 +22077,7 @@
         <v>8.75</v>
       </c>
       <c r="G771" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22103,7 +22103,7 @@
         <v>8.75</v>
       </c>
       <c r="G772" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22129,7 +22129,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G773" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22155,7 +22155,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G774" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22181,7 +22181,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G775" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22207,7 +22207,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G776" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22233,7 +22233,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G777" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22259,7 +22259,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G778" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22285,7 +22285,7 @@
         <v>9</v>
       </c>
       <c r="G779" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -22311,7 +22311,7 @@
         <v>9</v>
       </c>
       <c r="G780" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -22337,7 +22337,7 @@
         <v>9</v>
       </c>
       <c r="G781" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -22363,7 +22363,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G782" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -22389,7 +22389,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G783" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -22415,7 +22415,7 @@
         <v>8.75</v>
       </c>
       <c r="G784" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -22441,7 +22441,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G785" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -22467,7 +22467,7 @@
         <v>8.75</v>
       </c>
       <c r="G786" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -22493,7 +22493,7 @@
         <v>8.75</v>
       </c>
       <c r="G787" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -22519,7 +22519,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G788" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -22545,7 +22545,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G789" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -22571,7 +22571,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G790" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -22597,7 +22597,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G791" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -22623,7 +22623,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G792" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -22649,7 +22649,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G793" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -22675,7 +22675,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G794" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -22701,7 +22701,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G795" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -22727,7 +22727,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G796" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -22753,7 +22753,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G797" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -22779,7 +22779,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G798" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -22805,7 +22805,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G799" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -22831,7 +22831,7 @@
         <v>8.75</v>
       </c>
       <c r="G800" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -22857,7 +22857,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G801" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -22883,7 +22883,7 @@
         <v>8.75</v>
       </c>
       <c r="G802" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -22909,7 +22909,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G803" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -22935,7 +22935,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G804" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -22961,7 +22961,7 @@
         <v>8.75</v>
       </c>
       <c r="G805" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -22987,7 +22987,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G806" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23013,7 +23013,7 @@
         <v>8.75</v>
       </c>
       <c r="G807" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23039,7 +23039,7 @@
         <v>8.75</v>
       </c>
       <c r="G808" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23065,7 +23065,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G809" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23091,7 +23091,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G810" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23117,7 +23117,7 @@
         <v>8.5</v>
       </c>
       <c r="G811" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23143,7 +23143,7 @@
         <v>8.5</v>
       </c>
       <c r="G812" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23169,7 +23169,7 @@
         <v>8.5</v>
       </c>
       <c r="G813" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23195,7 +23195,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G814" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23221,7 +23221,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G815" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23247,7 +23247,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G816" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23273,7 +23273,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G817" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23299,7 +23299,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G818" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -23325,7 +23325,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G819" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -23351,7 +23351,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G820" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -23377,7 +23377,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G821" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -23403,7 +23403,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G822" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -23429,7 +23429,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G823" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -23455,7 +23455,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G824" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -23481,7 +23481,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G825" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -23507,7 +23507,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G826" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -23533,7 +23533,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G827" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -23559,7 +23559,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G828" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -23585,7 +23585,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G829" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -23611,7 +23611,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G830" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -23637,7 +23637,7 @@
         <v>9</v>
       </c>
       <c r="G831" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -23663,7 +23663,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G832" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -23689,7 +23689,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G833" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -23715,7 +23715,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G834" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -23741,7 +23741,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G835" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -23767,7 +23767,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G836" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -23793,7 +23793,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G837" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -23819,7 +23819,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G838" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -23845,7 +23845,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G839" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -23871,7 +23871,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G840" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -23897,7 +23897,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G841" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -23923,7 +23923,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G842" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -23949,7 +23949,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G843" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -23975,7 +23975,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G844" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24001,7 +24001,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G845" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24027,7 +24027,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G846" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24053,7 +24053,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G847" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24079,7 +24079,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G848" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24105,7 +24105,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G849" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24131,7 +24131,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G850" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24157,7 +24157,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G851" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24183,7 +24183,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G852" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24209,7 +24209,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G853" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24235,7 +24235,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G854" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24261,7 +24261,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G855" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24287,7 +24287,7 @@
         <v>8</v>
       </c>
       <c r="G856" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24313,7 +24313,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G857" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24339,7 +24339,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G858" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -24417,7 +24417,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G861" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24495,7 +24495,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G864" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -24937,7 +24937,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G881" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25015,7 +25015,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G884" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25041,7 +25041,7 @@
         <v>7</v>
       </c>
       <c r="G885" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25249,7 +25249,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G893" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -25977,7 +25977,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G921" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26003,7 +26003,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G922" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26029,7 +26029,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G923" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -26055,7 +26055,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G924" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26159,7 +26159,7 @@
         <v>7</v>
       </c>
       <c r="G928" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26185,7 +26185,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G929" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26211,7 +26211,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G930" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26237,7 +26237,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G931" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26263,7 +26263,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G932" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26289,7 +26289,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G933" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26315,7 +26315,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G934" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26341,7 +26341,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G935" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26419,7 +26419,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G938" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26445,7 +26445,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G939" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26705,7 +26705,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G949" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26731,7 +26731,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G950" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26757,7 +26757,7 @@
         <v>7</v>
       </c>
       <c r="G951" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -26783,7 +26783,7 @@
         <v>7</v>
       </c>
       <c r="G952" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26809,7 +26809,7 @@
         <v>7</v>
       </c>
       <c r="G953" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26835,7 +26835,7 @@
         <v>7</v>
       </c>
       <c r="G954" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26861,7 +26861,7 @@
         <v>7</v>
       </c>
       <c r="G955" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26887,7 +26887,7 @@
         <v>7</v>
       </c>
       <c r="G956" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26913,7 +26913,7 @@
         <v>7</v>
       </c>
       <c r="G957" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26939,7 +26939,7 @@
         <v>7</v>
       </c>
       <c r="G958" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26965,7 +26965,7 @@
         <v>7</v>
       </c>
       <c r="G959" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -26991,7 +26991,7 @@
         <v>7</v>
       </c>
       <c r="G960" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27017,7 +27017,7 @@
         <v>7</v>
       </c>
       <c r="G961" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27043,7 +27043,7 @@
         <v>7</v>
       </c>
       <c r="G962" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27069,7 +27069,7 @@
         <v>7</v>
       </c>
       <c r="G963" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27095,7 +27095,7 @@
         <v>7</v>
       </c>
       <c r="G964" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27121,7 +27121,7 @@
         <v>7</v>
       </c>
       <c r="G965" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27147,7 +27147,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G966" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27173,7 +27173,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G967" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27199,7 +27199,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G968" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27225,7 +27225,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G969" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -27251,7 +27251,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G970" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27277,7 +27277,7 @@
         <v>6.75</v>
       </c>
       <c r="G971" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27303,7 +27303,7 @@
         <v>6.75</v>
       </c>
       <c r="G972" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27329,7 +27329,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G973" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27355,7 +27355,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G974" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27381,7 +27381,7 @@
         <v>6.75</v>
       </c>
       <c r="G975" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27407,7 +27407,7 @@
         <v>6.75</v>
       </c>
       <c r="G976" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27433,7 +27433,7 @@
         <v>6.75</v>
       </c>
       <c r="G977" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27459,7 +27459,7 @@
         <v>6.75</v>
       </c>
       <c r="G978" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -27485,7 +27485,7 @@
         <v>6.75</v>
       </c>
       <c r="G979" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27511,7 +27511,7 @@
         <v>6.75</v>
       </c>
       <c r="G980" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27537,7 +27537,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G981" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27563,7 +27563,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G982" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -27589,7 +27589,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G983" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -27615,7 +27615,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G984" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27641,7 +27641,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G985" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -27667,7 +27667,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G986" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -27693,7 +27693,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G987" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -27719,7 +27719,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G988" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -27745,7 +27745,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G989" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -27771,7 +27771,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G990" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -27797,7 +27797,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G991" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -27823,7 +27823,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G992" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -27849,7 +27849,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G993" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -27875,7 +27875,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G994" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -27901,7 +27901,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G995" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -27927,7 +27927,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G996" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -27953,7 +27953,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G997" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -27979,7 +27979,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G998" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28005,7 +28005,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G999" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28031,7 +28031,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1000" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28057,7 +28057,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1001" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28083,7 +28083,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1002" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28109,7 +28109,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1003" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28135,7 +28135,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1004" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28161,7 +28161,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1005" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28187,7 +28187,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1006" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28213,7 +28213,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1007" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28239,7 +28239,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1008" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28265,7 +28265,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1009" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28343,7 +28343,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1012" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28369,7 +28369,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1013" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28395,7 +28395,7 @@
         <v>8</v>
       </c>
       <c r="G1014" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28551,7 +28551,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1020" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28577,7 +28577,7 @@
         <v>8.5</v>
       </c>
       <c r="G1021" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28603,7 +28603,7 @@
         <v>8.5</v>
       </c>
       <c r="G1022" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -28629,7 +28629,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1023" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -28655,7 +28655,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1024" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28681,7 +28681,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1025" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28707,7 +28707,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1026" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28733,7 +28733,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1027" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28759,7 +28759,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1028" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28785,7 +28785,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1029" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28811,7 +28811,7 @@
         <v>8.75</v>
       </c>
       <c r="G1030" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28837,7 +28837,7 @@
         <v>8.75</v>
       </c>
       <c r="G1031" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28863,7 +28863,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1032" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28889,7 +28889,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1033" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28915,7 +28915,7 @@
         <v>8.5</v>
       </c>
       <c r="G1034" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28941,7 +28941,7 @@
         <v>8.25</v>
       </c>
       <c r="G1035" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28967,7 +28967,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1036" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -28993,7 +28993,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1037" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29019,7 +29019,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1038" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29045,7 +29045,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1039" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29071,7 +29071,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1040" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29097,7 +29097,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1041" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29123,7 +29123,7 @@
         <v>8</v>
       </c>
       <c r="G1042" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29149,7 +29149,7 @@
         <v>8</v>
       </c>
       <c r="G1043" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29175,7 +29175,7 @@
         <v>8</v>
       </c>
       <c r="G1044" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29201,7 +29201,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1045" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -29227,7 +29227,7 @@
         <v>8</v>
       </c>
       <c r="G1046" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29253,7 +29253,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1047" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -29279,7 +29279,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1048" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29305,7 +29305,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1049" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29331,7 +29331,7 @@
         <v>7.75</v>
       </c>
       <c r="G1050" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29357,7 +29357,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1051" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29383,7 +29383,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1052" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29409,7 +29409,7 @@
         <v>7.75</v>
       </c>
       <c r="G1053" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29435,7 +29435,7 @@
         <v>7.75</v>
       </c>
       <c r="G1054" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29461,7 +29461,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1055" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29487,7 +29487,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1056" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29513,7 +29513,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1057" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29539,7 +29539,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1058" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29565,7 +29565,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1059" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29591,7 +29591,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1060" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29617,7 +29617,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1061" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29643,7 +29643,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1062" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29669,7 +29669,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1063" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29695,7 +29695,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1064" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29721,7 +29721,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1065" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29747,7 +29747,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1066" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29773,7 +29773,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1067" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29799,7 +29799,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1068" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29825,7 +29825,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1069" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29851,7 +29851,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1070" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29877,7 +29877,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1071" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29903,7 +29903,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1072" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -29929,7 +29929,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1073" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -29955,7 +29955,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1074" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -29981,7 +29981,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1075" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30007,7 +30007,7 @@
         <v>8</v>
       </c>
       <c r="G1076" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30033,7 +30033,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1077" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30059,7 +30059,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1078" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30085,7 +30085,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1079" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -30111,7 +30111,7 @@
         <v>8.25</v>
       </c>
       <c r="G1080" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30137,7 +30137,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1081" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30163,7 +30163,7 @@
         <v>8.5</v>
       </c>
       <c r="G1082" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30189,7 +30189,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1083" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30215,7 +30215,7 @@
         <v>8.5</v>
       </c>
       <c r="G1084" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30241,7 +30241,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1085" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30267,7 +30267,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1086" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -30293,7 +30293,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1087" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30319,7 +30319,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1088" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30345,7 +30345,7 @@
         <v>8.5</v>
       </c>
       <c r="G1089" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30371,7 +30371,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1090" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30397,7 +30397,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1091" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30423,7 +30423,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1092" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30449,7 +30449,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1093" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30475,7 +30475,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1094" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30501,7 +30501,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1095" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30527,7 +30527,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1096" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30553,7 +30553,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1097" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30579,7 +30579,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1098" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30605,7 +30605,7 @@
         <v>8.75</v>
       </c>
       <c r="G1099" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30631,7 +30631,7 @@
         <v>8.75</v>
       </c>
       <c r="G1100" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30657,7 +30657,7 @@
         <v>8.75</v>
       </c>
       <c r="G1101" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -30683,7 +30683,7 @@
         <v>8.75</v>
       </c>
       <c r="G1102" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30709,7 +30709,7 @@
         <v>8.75</v>
       </c>
       <c r="G1103" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30735,7 +30735,7 @@
         <v>8.75</v>
       </c>
       <c r="G1104" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30761,7 +30761,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1105" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30787,7 +30787,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1106" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30813,7 +30813,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1107" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30839,7 +30839,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1108" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30865,7 +30865,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1109" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30891,7 +30891,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1110" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -30917,7 +30917,7 @@
         <v>8.75</v>
       </c>
       <c r="G1111" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30943,7 +30943,7 @@
         <v>8.75</v>
       </c>
       <c r="G1112" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -30969,7 +30969,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1113" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -30995,7 +30995,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1114" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31021,7 +31021,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31047,7 +31047,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1116" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31073,7 +31073,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1117" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31099,7 +31099,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1118" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31125,7 +31125,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1119" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31151,7 +31151,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1120" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31177,7 +31177,7 @@
         <v>8.75</v>
       </c>
       <c r="G1121" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31203,7 +31203,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1122" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31229,7 +31229,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1123" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31255,7 +31255,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1124" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31281,7 +31281,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1125" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31307,7 +31307,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1126" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31333,7 +31333,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1127" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31359,7 +31359,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1128" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31385,7 +31385,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1129" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31411,7 +31411,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1130" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31437,7 +31437,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1131" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31463,7 +31463,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1132" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31489,7 +31489,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1133" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31515,7 +31515,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1134" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31567,7 +31567,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1136" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31593,7 +31593,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1137" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31619,7 +31619,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1138" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31645,7 +31645,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1139" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31671,7 +31671,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1140" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31697,7 +31697,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1141" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31723,7 +31723,7 @@
         <v>8.75</v>
       </c>
       <c r="G1142" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31853,7 +31853,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1147" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31905,7 +31905,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1149" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32035,7 +32035,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1154" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32061,7 +32061,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1155" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32087,7 +32087,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1156" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -61756,6 +61756,58 @@
         <v>555</v>
       </c>
       <c r="H2297" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" s="1" t="n">
+        <v>46003.3333333333</v>
+      </c>
+      <c r="B2298" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2298" t="n">
+        <v>37</v>
+      </c>
+      <c r="D2298" t="n">
+        <v>37</v>
+      </c>
+      <c r="E2298" t="n">
+        <v>37</v>
+      </c>
+      <c r="F2298" t="n">
+        <v>37</v>
+      </c>
+      <c r="G2298" t="s">
+        <v>555</v>
+      </c>
+      <c r="H2298" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" s="1" t="n">
+        <v>46006.591875</v>
+      </c>
+      <c r="B2299" t="n">
+        <v>250</v>
+      </c>
+      <c r="C2299" t="n">
+        <v>37.7999992370605</v>
+      </c>
+      <c r="D2299" t="n">
+        <v>37.7999992370605</v>
+      </c>
+      <c r="E2299" t="n">
+        <v>37.7999992370605</v>
+      </c>
+      <c r="F2299" t="n">
+        <v>37.7999992370605</v>
+      </c>
+      <c r="G2299" t="s">
+        <v>543</v>
+      </c>
+      <c r="H2299" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46539163589478</t>
+    <t xml:space="preserve">2.46539187431335</t>
   </si>
   <si>
     <t xml:space="preserve">FPE.MI</t>
@@ -47,22 +47,22 @@
     <t xml:space="preserve">2.42625832557678</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43408536911011</t>
+    <t xml:space="preserve">2.43408513069153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41060543060303</t>
+    <t xml:space="preserve">2.41060519218445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45756483078003</t>
+    <t xml:space="preserve">2.45756506919861</t>
   </si>
   <si>
     <t xml:space="preserve">2.39495182037354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233880996704</t>
+    <t xml:space="preserve">2.33233904838562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41843152046204</t>
+    <t xml:space="preserve">2.41843175888062</t>
   </si>
   <si>
     <t xml:space="preserve">2.3558189868927</t>
@@ -71,61 +71,61 @@
     <t xml:space="preserve">2.37147212028503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50452470779419</t>
+    <t xml:space="preserve">2.50452518463135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36364555358887</t>
+    <t xml:space="preserve">2.36364531517029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44973850250244</t>
+    <t xml:space="preserve">2.44973874092102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37303733825684</t>
+    <t xml:space="preserve">2.37303757667542</t>
   </si>
   <si>
     <t xml:space="preserve">2.34955763816833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46382641792297</t>
+    <t xml:space="preserve">2.46382665634155</t>
   </si>
   <si>
     <t xml:space="preserve">2.38712525367737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45443439483643</t>
+    <t xml:space="preserve">2.45443415641785</t>
   </si>
   <si>
     <t xml:space="preserve">2.34799194335938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48104500770569</t>
+    <t xml:space="preserve">2.48104524612427</t>
   </si>
   <si>
     <t xml:space="preserve">2.3792986869812</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38556051254272</t>
+    <t xml:space="preserve">2.38556003570557</t>
   </si>
   <si>
     <t xml:space="preserve">2.4419116973877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78002262115479</t>
+    <t xml:space="preserve">2.78002285957336</t>
   </si>
   <si>
     <t xml:space="preserve">3.36702084541321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62529969215393</t>
+    <t xml:space="preserve">3.62530016899109</t>
   </si>
   <si>
     <t xml:space="preserve">3.31066870689392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25588202476501</t>
+    <t xml:space="preserve">3.25588226318359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20266127586365</t>
+    <t xml:space="preserve">3.20266151428223</t>
   </si>
   <si>
     <t xml:space="preserve">3.0523898601532</t>
@@ -137,28 +137,28 @@
     <t xml:space="preserve">3.04456329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03673696517944</t>
+    <t xml:space="preserve">3.03673624992371</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03830170631409</t>
+    <t xml:space="preserve">3.03830194473267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15413641929626</t>
+    <t xml:space="preserve">3.15413618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30910396575928</t>
+    <t xml:space="preserve">3.3091037273407</t>
   </si>
   <si>
     <t xml:space="preserve">3.30284190177917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3576283454895</t>
+    <t xml:space="preserve">3.35762882232666</t>
   </si>
   <si>
     <t xml:space="preserve">3.57677507400513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52198767662048</t>
+    <t xml:space="preserve">3.52198815345764</t>
   </si>
   <si>
     <t xml:space="preserve">3.40458822250366</t>
@@ -167,37 +167,37 @@
     <t xml:space="preserve">3.59242796897888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58460092544556</t>
+    <t xml:space="preserve">3.58460116386414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67852091789246</t>
+    <t xml:space="preserve">3.67852067947388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60025453567505</t>
+    <t xml:space="preserve">3.60025429725647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59555888175964</t>
+    <t xml:space="preserve">3.59555840492249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632207870483</t>
+    <t xml:space="preserve">3.32632231712341</t>
   </si>
   <si>
     <t xml:space="preserve">3.29501557350159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3748471736908</t>
+    <t xml:space="preserve">3.37484693527222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38267421722412</t>
+    <t xml:space="preserve">3.38267397880554</t>
   </si>
   <si>
     <t xml:space="preserve">3.44372200965881</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5908625125885</t>
+    <t xml:space="preserve">3.59086275100708</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47972440719604</t>
+    <t xml:space="preserve">3.47972464561462</t>
   </si>
   <si>
     <t xml:space="preserve">3.42650318145752</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">3.41241526603699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24022889137268</t>
+    <t xml:space="preserve">3.24022912979126</t>
   </si>
   <si>
     <t xml:space="preserve">3.21048808097839</t>
@@ -218,31 +218,31 @@
     <t xml:space="preserve">3.16196250915527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20892238616943</t>
+    <t xml:space="preserve">3.20892262458801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13848280906677</t>
+    <t xml:space="preserve">3.13848304748535</t>
   </si>
   <si>
     <t xml:space="preserve">3.23240280151367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31849551200867</t>
+    <t xml:space="preserve">3.31849527359009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27623176574707</t>
+    <t xml:space="preserve">3.27623200416565</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18857336044312</t>
+    <t xml:space="preserve">3.18857312202454</t>
   </si>
   <si>
     <t xml:space="preserve">3.14317870140076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11500310897827</t>
+    <t xml:space="preserve">3.11500287055969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00073385238647</t>
+    <t xml:space="preserve">3.00073409080505</t>
   </si>
   <si>
     <t xml:space="preserve">2.97412323951721</t>
@@ -254,19 +254,19 @@
     <t xml:space="preserve">2.90368366241455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89585709571838</t>
+    <t xml:space="preserve">2.8958568572998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82854819297791</t>
+    <t xml:space="preserve">2.82854747772217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83637452125549</t>
+    <t xml:space="preserve">2.83637475967407</t>
   </si>
   <si>
     <t xml:space="preserve">2.90994501113892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491184234619</t>
+    <t xml:space="preserve">3.06491255760193</t>
   </si>
   <si>
     <t xml:space="preserve">3.13065624237061</t>
@@ -275,31 +275,31 @@
     <t xml:space="preserve">3.14474415779114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.213618516922</t>
+    <t xml:space="preserve">3.21361827850342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2856240272522</t>
+    <t xml:space="preserve">3.28562355041504</t>
   </si>
   <si>
     <t xml:space="preserve">3.35919404029846</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36388993263245</t>
+    <t xml:space="preserve">3.36388969421387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91332006454468</t>
+    <t xml:space="preserve">3.9133198261261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34378528594971</t>
+    <t xml:space="preserve">4.34378576278687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79381704330444</t>
+    <t xml:space="preserve">4.7938175201416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47864770889282</t>
+    <t xml:space="preserve">5.47864818572998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09303951263428</t>
+    <t xml:space="preserve">6.09303903579712</t>
   </si>
   <si>
     <t xml:space="preserve">5.41603517532349</t>
@@ -308,67 +308,67 @@
     <t xml:space="preserve">5.71344757080078</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56865501403809</t>
+    <t xml:space="preserve">5.56865453720093</t>
   </si>
   <si>
     <t xml:space="preserve">5.41994905471802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16558265686035</t>
+    <t xml:space="preserve">5.16558218002319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94643688201904</t>
+    <t xml:space="preserve">4.9464373588562</t>
   </si>
   <si>
     <t xml:space="preserve">4.70381116867065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6764178276062</t>
+    <t xml:space="preserve">4.67641735076904</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00904941558838</t>
+    <t xml:space="preserve">5.0090503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55691528320312</t>
+    <t xml:space="preserve">5.55691480636597</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30646228790283</t>
+    <t xml:space="preserve">5.30646181106567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22428226470947</t>
+    <t xml:space="preserve">5.22428274154663</t>
   </si>
   <si>
     <t xml:space="preserve">5.19688940048218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32211637496948</t>
+    <t xml:space="preserve">5.32211589813232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47082090377808</t>
+    <t xml:space="preserve">5.47082138061523</t>
   </si>
   <si>
     <t xml:space="preserve">5.36907529830933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29080963134766</t>
+    <t xml:space="preserve">5.2908091545105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1734094619751</t>
+    <t xml:space="preserve">5.17340993881226</t>
   </si>
   <si>
     <t xml:space="preserve">5.09514331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22036933898926</t>
+    <t xml:space="preserve">5.2203688621521</t>
   </si>
   <si>
     <t xml:space="preserve">5.10296964645386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99339723587036</t>
+    <t xml:space="preserve">4.9933967590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15384244918823</t>
+    <t xml:space="preserve">5.15384292602539</t>
   </si>
   <si>
     <t xml:space="preserve">4.98556995391846</t>
@@ -377,25 +377,25 @@
     <t xml:space="preserve">4.7585973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77033710479736</t>
+    <t xml:space="preserve">4.77033758163452</t>
   </si>
   <si>
     <t xml:space="preserve">4.86425733566284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88773775100708</t>
+    <t xml:space="preserve">4.88773679733276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83295059204102</t>
+    <t xml:space="preserve">4.83295106887817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75468349456787</t>
+    <t xml:space="preserve">4.75468301773071</t>
   </si>
   <si>
     <t xml:space="preserve">4.82903718948364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72337770462036</t>
+    <t xml:space="preserve">4.7233772277832</t>
   </si>
   <si>
     <t xml:space="preserve">4.68815755844116</t>
@@ -404,13 +404,13 @@
     <t xml:space="preserve">4.78207731246948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87599754333496</t>
+    <t xml:space="preserve">4.87599658966064</t>
   </si>
   <si>
     <t xml:space="preserve">5.03644275665283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92687034606934</t>
+    <t xml:space="preserve">4.92687082290649</t>
   </si>
   <si>
     <t xml:space="preserve">4.81338405609131</t>
@@ -419,13 +419,13 @@
     <t xml:space="preserve">4.86034345626831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00122308731079</t>
+    <t xml:space="preserve">5.00122261047363</t>
   </si>
   <si>
     <t xml:space="preserve">4.77425050735474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82121086120605</t>
+    <t xml:space="preserve">4.8212103843689</t>
   </si>
   <si>
     <t xml:space="preserve">4.69989728927612</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">4.90730285644531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20471668243408</t>
+    <t xml:space="preserve">5.20471620559692</t>
   </si>
   <si>
     <t xml:space="preserve">5.43951511383057</t>
@@ -455,22 +455,22 @@
     <t xml:space="preserve">5.40038156509399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51778173446655</t>
+    <t xml:space="preserve">5.51778125762939</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63518047332764</t>
+    <t xml:space="preserve">5.63518095016479</t>
   </si>
   <si>
     <t xml:space="preserve">4.96991682052612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93078327178955</t>
+    <t xml:space="preserve">4.93078374862671</t>
   </si>
   <si>
     <t xml:space="preserve">4.85251665115356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12644910812378</t>
+    <t xml:space="preserve">5.12644958496094</t>
   </si>
   <si>
     <t xml:space="preserve">5.04818296432495</t>
@@ -482,46 +482,46 @@
     <t xml:space="preserve">5.59604787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26159763336182</t>
+    <t xml:space="preserve">5.2615966796875</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42104053497314</t>
+    <t xml:space="preserve">5.42104005813599</t>
   </si>
   <si>
     <t xml:space="preserve">5.34131813049316</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22173643112183</t>
+    <t xml:space="preserve">5.22173690795898</t>
   </si>
   <si>
     <t xml:space="preserve">5.14201545715332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10215473175049</t>
+    <t xml:space="preserve">5.10215520858765</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18187618255615</t>
+    <t xml:space="preserve">5.18187522888184</t>
   </si>
   <si>
     <t xml:space="preserve">5.38117980957031</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30145835876465</t>
+    <t xml:space="preserve">5.30145788192749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9028525352478</t>
+    <t xml:space="preserve">4.90285205841064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50076103210449</t>
+    <t xml:space="preserve">5.50076055526733</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4608998298645</t>
+    <t xml:space="preserve">5.46090126037598</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58048152923584</t>
+    <t xml:space="preserve">5.580482006073</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54062128067017</t>
+    <t xml:space="preserve">5.54062175750732</t>
   </si>
   <si>
     <t xml:space="preserve">5.62034273147583</t>
@@ -533,16 +533,16 @@
     <t xml:space="preserve">4.98257303237915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82313108444214</t>
+    <t xml:space="preserve">4.82313060760498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06229448318481</t>
+    <t xml:space="preserve">5.06229400634766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02243375778198</t>
+    <t xml:space="preserve">5.02243423461914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74340963363647</t>
+    <t xml:space="preserve">4.74341011047363</t>
   </si>
   <si>
     <t xml:space="preserve">4.78327035903931</t>
@@ -551,31 +551,31 @@
     <t xml:space="preserve">4.86299133300781</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73992395401001</t>
+    <t xml:space="preserve">5.73992443084717</t>
   </si>
   <si>
     <t xml:space="preserve">5.81964588165283</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70006370544434</t>
+    <t xml:space="preserve">5.70006418228149</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66020393371582</t>
+    <t xml:space="preserve">5.6602029800415</t>
   </si>
   <si>
     <t xml:space="preserve">5.77978515625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85950660705566</t>
+    <t xml:space="preserve">5.85950565338135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.979088306427</t>
+    <t xml:space="preserve">5.97908782958984</t>
   </si>
   <si>
     <t xml:space="preserve">6.29797267913818</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13853025436401</t>
+    <t xml:space="preserve">6.13853073120117</t>
   </si>
   <si>
     <t xml:space="preserve">6.05880880355835</t>
@@ -584,19 +584,19 @@
     <t xml:space="preserve">6.21825170516968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09867000579834</t>
+    <t xml:space="preserve">6.09866952896118</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3851842880249</t>
+    <t xml:space="preserve">6.38518476486206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25998497009277</t>
+    <t xml:space="preserve">6.25998449325562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30171871185303</t>
+    <t xml:space="preserve">6.30171823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17651796340942</t>
+    <t xml:space="preserve">6.17651844024658</t>
   </si>
   <si>
     <t xml:space="preserve">6.426917552948</t>
@@ -614,10 +614,10 @@
     <t xml:space="preserve">6.0095853805542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13478469848633</t>
+    <t xml:space="preserve">6.13478517532349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05131912231445</t>
+    <t xml:space="preserve">6.05131864547729</t>
   </si>
   <si>
     <t xml:space="preserve">5.92611885070801</t>
@@ -647,79 +647,79 @@
     <t xml:space="preserve">7.80411434173584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63718128204346</t>
+    <t xml:space="preserve">7.6371808052063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55371475219727</t>
+    <t xml:space="preserve">7.55371522903442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34504985809326</t>
+    <t xml:space="preserve">7.3450493812561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17811632156372</t>
+    <t xml:space="preserve">7.17811679840088</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51198101043701</t>
+    <t xml:space="preserve">7.51198148727417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47024822235107</t>
+    <t xml:space="preserve">7.47024869918823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30331611633301</t>
+    <t xml:space="preserve">7.30331563949585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851400375366</t>
+    <t xml:space="preserve">7.42851495742798</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26158237457275</t>
+    <t xml:space="preserve">7.2615818977356</t>
   </si>
   <si>
     <t xml:space="preserve">7.38678216934204</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9694504737854</t>
+    <t xml:space="preserve">6.96944952011108</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21984815597534</t>
+    <t xml:space="preserve">7.2198486328125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544897079468</t>
+    <t xml:space="preserve">7.59544849395752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76238107681274</t>
+    <t xml:space="preserve">7.76238059997559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84584760665894</t>
+    <t xml:space="preserve">7.84584712982178</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67891550064087</t>
+    <t xml:space="preserve">7.67891407012939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01118278503418</t>
+    <t xml:space="preserve">7.01118326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09464979171753</t>
+    <t xml:space="preserve">7.09464931488037</t>
   </si>
   <si>
     <t xml:space="preserve">6.92771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76078462600708</t>
+    <t xml:space="preserve">6.76078414916992</t>
   </si>
   <si>
     <t xml:space="preserve">6.8025164604187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71905040740967</t>
+    <t xml:space="preserve">6.71905088424683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84424924850464</t>
+    <t xml:space="preserve">6.8442497253418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59385061264038</t>
+    <t xml:space="preserve">6.59385108947754</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67731666564941</t>
+    <t xml:space="preserve">6.67731761932373</t>
   </si>
   <si>
     <t xml:space="preserve">6.55211734771729</t>
@@ -734,43 +734,43 @@
     <t xml:space="preserve">5.80091953277588</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67571973800659</t>
+    <t xml:space="preserve">5.67571926116943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5922532081604</t>
+    <t xml:space="preserve">5.59225225448608</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6339864730835</t>
+    <t xml:space="preserve">5.63398599624634</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46705341339111</t>
+    <t xml:space="preserve">5.46705389022827</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5505199432373</t>
+    <t xml:space="preserve">5.55051946640015</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17492008209229</t>
+    <t xml:space="preserve">5.17492055892944</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25838756561279</t>
+    <t xml:space="preserve">5.25838708877563</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38358640670776</t>
+    <t xml:space="preserve">5.38358688354492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13638353347778</t>
+    <t xml:space="preserve">7.13638257980347</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47247123718262</t>
+    <t xml:space="preserve">7.4724702835083</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25269222259521</t>
+    <t xml:space="preserve">7.25269269943237</t>
   </si>
   <si>
     <t xml:space="preserve">7.29664754867554</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20873594284058</t>
+    <t xml:space="preserve">7.20873689651489</t>
   </si>
   <si>
     <t xml:space="preserve">7.16478061676025</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">7.07686948776245</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98895835876465</t>
+    <t xml:space="preserve">6.98895788192749</t>
   </si>
   <si>
     <t xml:space="preserve">7.03291320800781</t>
@@ -794,70 +794,70 @@
     <t xml:space="preserve">6.72522354125977</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81313514709473</t>
+    <t xml:space="preserve">6.81313562393188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76917934417725</t>
+    <t xml:space="preserve">6.76917886734009</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90104675292969</t>
+    <t xml:space="preserve">6.90104627609253</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63731288909912</t>
+    <t xml:space="preserve">6.63731241226196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12082624435425</t>
+    <t xml:space="preserve">7.12082529067993</t>
   </si>
   <si>
     <t xml:space="preserve">7.34060430526733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51642751693726</t>
+    <t xml:space="preserve">7.5164270401001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56038284301758</t>
+    <t xml:space="preserve">7.56038331985474</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851495742798</t>
+    <t xml:space="preserve">7.42851591110229</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7362060546875</t>
+    <t xml:space="preserve">7.73620653152466</t>
   </si>
   <si>
     <t xml:space="preserve">7.69224977493286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829397201538</t>
+    <t xml:space="preserve">7.64829349517822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78247451782227</t>
+    <t xml:space="preserve">7.78247404098511</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82720136642456</t>
+    <t xml:space="preserve">7.8272008895874</t>
   </si>
   <si>
     <t xml:space="preserve">7.73774671554565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69302082061768</t>
+    <t xml:space="preserve">7.69302129745483</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829444885254</t>
+    <t xml:space="preserve">7.64829397201538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60356712341309</t>
+    <t xml:space="preserve">7.60356569290161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91665458679199</t>
+    <t xml:space="preserve">7.91665506362915</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87192869186401</t>
+    <t xml:space="preserve">7.87192916870117</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96138048171997</t>
+    <t xml:space="preserve">7.96138095855713</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22974300384521</t>
+    <t xml:space="preserve">8.2297420501709</t>
   </si>
   <si>
     <t xml:space="preserve">8.76646518707275</t>
@@ -866,16 +866,16 @@
     <t xml:space="preserve">8.58755779266357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36392307281494</t>
+    <t xml:space="preserve">8.36392402648926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63228321075439</t>
+    <t xml:space="preserve">8.63228416442871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54283142089844</t>
+    <t xml:space="preserve">8.54283046722412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40865039825439</t>
+    <t xml:space="preserve">8.40864944458008</t>
   </si>
   <si>
     <t xml:space="preserve">8.27446937561035</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">8.67701148986816</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49810314178467</t>
+    <t xml:space="preserve">8.49810409545898</t>
   </si>
   <si>
     <t xml:space="preserve">8.81119251251221</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">9.03482627868652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3766326904297</t>
+    <t xml:space="preserve">10.376633644104</t>
   </si>
   <si>
     <t xml:space="preserve">11.4500770568848</t>
@@ -911,22 +911,22 @@
     <t xml:space="preserve">10.734447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0922613143921</t>
+    <t xml:space="preserve">11.0922622680664</t>
   </si>
   <si>
     <t xml:space="preserve">10.9133548736572</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1817150115967</t>
+    <t xml:space="preserve">11.181715965271</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3606233596802</t>
+    <t xml:space="preserve">11.3606224060059</t>
   </si>
   <si>
     <t xml:space="preserve">11.6289844512939</t>
   </si>
   <si>
-    <t xml:space="preserve">11.539529800415</t>
+    <t xml:space="preserve">11.5395307540894</t>
   </si>
   <si>
     <t xml:space="preserve">11.2711696624756</t>
@@ -935,13 +935,13 @@
     <t xml:space="preserve">10.5555391311646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2871789932251</t>
+    <t xml:space="preserve">10.2871780395508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0028085708618</t>
+    <t xml:space="preserve">11.0028076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6449928283691</t>
+    <t xml:space="preserve">10.6449937820435</t>
   </si>
   <si>
     <t xml:space="preserve">10.4660863876343</t>
@@ -959,28 +959,28 @@
     <t xml:space="preserve">10.018816947937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6129751205444</t>
+    <t xml:space="preserve">12.6129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9707908630371</t>
+    <t xml:space="preserve">12.9707899093628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0442352294922</t>
+    <t xml:space="preserve">14.0442342758179</t>
   </si>
   <si>
     <t xml:space="preserve">13.7758731842041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.507513999939</t>
+    <t xml:space="preserve">13.5075130462646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2391510009766</t>
+    <t xml:space="preserve">13.2391519546509</t>
   </si>
   <si>
     <t xml:space="preserve">13.0602445602417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4180593490601</t>
+    <t xml:space="preserve">13.4180603027344</t>
   </si>
   <si>
     <t xml:space="preserve">12.8813362121582</t>
@@ -989,34 +989,34 @@
     <t xml:space="preserve">12.7918825149536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.702428817749</t>
+    <t xml:space="preserve">12.7024297714233</t>
   </si>
   <si>
     <t xml:space="preserve">13.149697303772</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3286046981812</t>
+    <t xml:space="preserve">13.3286037445068</t>
   </si>
   <si>
     <t xml:space="preserve">13.9547815322876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5969657897949</t>
+    <t xml:space="preserve">13.5969648361206</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6864194869995</t>
+    <t xml:space="preserve">13.6864204406738</t>
   </si>
   <si>
-    <t xml:space="preserve">13.865327835083</t>
+    <t xml:space="preserve">13.8653287887573</t>
   </si>
   <si>
     <t xml:space="preserve">14.4020500183105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2965888977051</t>
+    <t xml:space="preserve">15.2965879440308</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2071342468262</t>
+    <t xml:space="preserve">15.2071313858032</t>
   </si>
   <si>
     <t xml:space="preserve">14.5809564590454</t>
@@ -1025,13 +1025,13 @@
     <t xml:space="preserve">14.7598648071289</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4915056228638</t>
+    <t xml:space="preserve">14.4915037155151</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5400886535645</t>
+    <t xml:space="preserve">14.5400876998901</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3560371398926</t>
+    <t xml:space="preserve">14.3560361862183</t>
   </si>
   <si>
     <t xml:space="preserve">14.2640104293823</t>
@@ -1040,22 +1040,22 @@
     <t xml:space="preserve">14.1719846725464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8161668777466</t>
+    <t xml:space="preserve">14.8161659240723</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6321134567261</t>
+    <t xml:space="preserve">14.6321144104004</t>
   </si>
   <si>
     <t xml:space="preserve">15.3683223724365</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5523729324341</t>
+    <t xml:space="preserve">15.5523738861084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1045265197754</t>
+    <t xml:space="preserve">16.104528427124</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3806037902832</t>
+    <t xml:space="preserve">16.3806056976318</t>
   </si>
   <si>
     <t xml:space="preserve">15.9204750061035</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">17.4849166870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5769424438477</t>
+    <t xml:space="preserve">17.576940536499</t>
   </si>
   <si>
     <t xml:space="preserve">17.6689682006836</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">18.4051742553711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1413822174072</t>
+    <t xml:space="preserve">19.1413803100586</t>
   </si>
   <si>
     <t xml:space="preserve">19.6935367584229</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">21.5340557098389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3745727539062</t>
+    <t xml:space="preserve">23.3745708465576</t>
   </si>
   <si>
     <t xml:space="preserve">22.2702617645264</t>
@@ -1100,10 +1100,10 @@
     <t xml:space="preserve">22.822416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6137943267822</t>
+    <t xml:space="preserve">20.6137962341309</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3254356384277</t>
+    <t xml:space="preserve">19.3254337310791</t>
   </si>
   <si>
     <t xml:space="preserve">21.902156829834</t>
@@ -1115,10 +1115,10 @@
     <t xml:space="preserve">23.0064678192139</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5586242675781</t>
+    <t xml:space="preserve">23.5586261749268</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7426738739014</t>
+    <t xml:space="preserve">23.74267578125</t>
   </si>
   <si>
     <t xml:space="preserve">23.9267272949219</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">24.6629333496094</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8469867706299</t>
+    <t xml:space="preserve">24.8469886779785</t>
   </si>
   <si>
     <t xml:space="preserve">24.2948303222656</t>
@@ -1142,13 +1142,13 @@
     <t xml:space="preserve">25.2150897979736</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4543151855469</t>
+    <t xml:space="preserve">22.4543132781982</t>
   </si>
   <si>
     <t xml:space="preserve">24.4788837432861</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9512977600098</t>
+    <t xml:space="preserve">25.9512958526611</t>
   </si>
   <si>
     <t xml:space="preserve">26.5034523010254</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">27.975866317749</t>
   </si>
   <si>
-    <t xml:space="preserve">30.920690536499</t>
+    <t xml:space="preserve">30.9206943511963</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0801773071289</t>
+    <t xml:space="preserve">29.0801753997803</t>
   </si>
   <si>
     <t xml:space="preserve">30.736644744873</t>
@@ -1169,16 +1169,16 @@
     <t xml:space="preserve">30.3685398101807</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2642269134521</t>
+    <t xml:space="preserve">29.2642288208008</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4728527069092</t>
+    <t xml:space="preserve">31.4728507995605</t>
   </si>
   <si>
     <t xml:space="preserve">34.2336273193359</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7857818603516</t>
+    <t xml:space="preserve">34.7857780456543</t>
   </si>
   <si>
     <t xml:space="preserve">33.8655204772949</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">33.4974212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1844844818115</t>
+    <t xml:space="preserve">30.1844863891602</t>
   </si>
   <si>
     <t xml:space="preserve">27.4237098693848</t>
@@ -1196,16 +1196,16 @@
     <t xml:space="preserve">26.6875038146973</t>
   </si>
   <si>
-    <t xml:space="preserve">25.583194732666</t>
+    <t xml:space="preserve">25.5831928253174</t>
   </si>
   <si>
     <t xml:space="preserve">26.3194007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7918148040771</t>
+    <t xml:space="preserve">27.7918167114258</t>
   </si>
   <si>
-    <t xml:space="preserve">28.896125793457</t>
+    <t xml:space="preserve">28.8961238861084</t>
   </si>
   <si>
     <t xml:space="preserve">29.4482803344727</t>
@@ -1214,22 +1214,22 @@
     <t xml:space="preserve">28.5280208587646</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7120742797852</t>
+    <t xml:space="preserve">28.7120723724365</t>
   </si>
   <si>
     <t xml:space="preserve">28.3439693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0556049346924</t>
+    <t xml:space="preserve">27.055606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8715553283691</t>
+    <t xml:space="preserve">26.8715572357178</t>
   </si>
   <si>
     <t xml:space="preserve">25.3991413116455</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7672462463379</t>
+    <t xml:space="preserve">25.7672443389893</t>
   </si>
   <si>
     <t xml:space="preserve">25.0310382843018</t>
@@ -1238,61 +1238,61 @@
     <t xml:space="preserve">27.6077632904053</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5525894165039</t>
+    <t xml:space="preserve">30.5525913238525</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6323337554932</t>
+    <t xml:space="preserve">29.6323318481445</t>
   </si>
   <si>
     <t xml:space="preserve">30.0004329681396</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3931121826172</t>
+    <t xml:space="preserve">32.3931083679199</t>
   </si>
   <si>
-    <t xml:space="preserve">32.2090530395508</t>
+    <t xml:space="preserve">32.209056854248</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2887954711914</t>
+    <t xml:space="preserve">31.28879737854</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6569042205811</t>
+    <t xml:space="preserve">31.6569023132324</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0250053405762</t>
+    <t xml:space="preserve">32.0250015258789</t>
   </si>
   <si>
     <t xml:space="preserve">32.0337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5990676879883</t>
+    <t xml:space="preserve">32.5990715026855</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1643753051758</t>
+    <t xml:space="preserve">33.1643714904785</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6568984985352</t>
+    <t xml:space="preserve">31.6569004058838</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4106407165527</t>
+    <t xml:space="preserve">32.4106369018555</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7875061035156</t>
+    <t xml:space="preserve">32.7875022888184</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9759368896484</t>
+    <t xml:space="preserve">32.9759407043457</t>
   </si>
   <si>
     <t xml:space="preserve">30.9031639099121</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8453350067139</t>
+    <t xml:space="preserve">31.8453369140625</t>
   </si>
   <si>
     <t xml:space="preserve">30.714729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5263004302979</t>
+    <t xml:space="preserve">30.5262985229492</t>
   </si>
   <si>
     <t xml:space="preserve">31.2800331115723</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">30.1494293212891</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3378658294678</t>
+    <t xml:space="preserve">30.3378639221191</t>
   </si>
   <si>
     <t xml:space="preserve">29.395694732666</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">28.2650909423828</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6997871398926</t>
+    <t xml:space="preserve">27.6997890472412</t>
   </si>
   <si>
     <t xml:space="preserve">28.0766563415527</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">25.2501468658447</t>
   </si>
   <si>
-    <t xml:space="preserve">24.307975769043</t>
+    <t xml:space="preserve">24.3079776763916</t>
   </si>
   <si>
     <t xml:space="preserve">23.9311103820801</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">23.7426776885986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1773738861084</t>
+    <t xml:space="preserve">23.177375793457</t>
   </si>
   <si>
     <t xml:space="preserve">22.6120719909668</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">22.2352046966553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0467720031738</t>
+    <t xml:space="preserve">22.0467700958252</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8005065917969</t>
+    <t xml:space="preserve">22.8005084991455</t>
   </si>
   <si>
     <t xml:space="preserve">22.988941192627</t>
@@ -1394,19 +1394,19 @@
     <t xml:space="preserve">25.6270160675049</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3807525634766</t>
+    <t xml:space="preserve">26.3807506561279</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1344871520996</t>
+    <t xml:space="preserve">27.134485244751</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9460544586182</t>
+    <t xml:space="preserve">26.9460525512695</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3229217529297</t>
+    <t xml:space="preserve">27.3229198455811</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1923179626465</t>
+    <t xml:space="preserve">26.1923160552979</t>
   </si>
   <si>
     <t xml:space="preserve">26.7576179504395</t>
@@ -61868,7 +61868,7 @@
     </row>
     <row r="2302">
       <c r="A2302" s="1" t="n">
-        <v>46009.5767361111</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B2302" t="n">
         <v>250</v>
@@ -61889,6 +61889,32 @@
         <v>540</v>
       </c>
       <c r="H2302" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" s="1" t="n">
+        <v>46010.6788310185</v>
+      </c>
+      <c r="B2303" t="n">
+        <v>3250</v>
+      </c>
+      <c r="C2303" t="n">
+        <v>40</v>
+      </c>
+      <c r="D2303" t="n">
+        <v>38</v>
+      </c>
+      <c r="E2303" t="n">
+        <v>38</v>
+      </c>
+      <c r="F2303" t="n">
+        <v>39.2000007629395</v>
+      </c>
+      <c r="G2303" t="s">
+        <v>537</v>
+      </c>
+      <c r="H2303" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -50,7 +50,7 @@
     <t xml:space="preserve">2.43408489227295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41060543060303</t>
+    <t xml:space="preserve">2.41060495376587</t>
   </si>
   <si>
     <t xml:space="preserve">2.45756530761719</t>
@@ -62,16 +62,16 @@
     <t xml:space="preserve">2.33233904838562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41843175888062</t>
+    <t xml:space="preserve">2.41843152046204</t>
   </si>
   <si>
     <t xml:space="preserve">2.35581874847412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37147212028503</t>
+    <t xml:space="preserve">2.37147188186646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50452494621277</t>
+    <t xml:space="preserve">2.50452470779419</t>
   </si>
   <si>
     <t xml:space="preserve">2.36364531517029</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">2.44973850250244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37303757667542</t>
+    <t xml:space="preserve">2.37303781509399</t>
   </si>
   <si>
     <t xml:space="preserve">2.34955763816833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46382641792297</t>
+    <t xml:space="preserve">2.46382665634155</t>
   </si>
   <si>
     <t xml:space="preserve">2.38712525367737</t>
@@ -95,16 +95,16 @@
     <t xml:space="preserve">2.45443439483643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34799218177795</t>
+    <t xml:space="preserve">2.34799194335938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48104500770569</t>
+    <t xml:space="preserve">2.48104524612427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3792986869812</t>
+    <t xml:space="preserve">2.37929844856262</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38555979728699</t>
+    <t xml:space="preserve">2.38556003570557</t>
   </si>
   <si>
     <t xml:space="preserve">2.4419116973877</t>
@@ -113,19 +113,19 @@
     <t xml:space="preserve">2.78002262115479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36702060699463</t>
+    <t xml:space="preserve">3.36702084541321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62529969215393</t>
+    <t xml:space="preserve">3.62529993057251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31066918373108</t>
+    <t xml:space="preserve">3.3106689453125</t>
   </si>
   <si>
     <t xml:space="preserve">3.25588202476501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20266175270081</t>
+    <t xml:space="preserve">3.20266151428223</t>
   </si>
   <si>
     <t xml:space="preserve">3.0523898601532</t>
@@ -134,16 +134,16 @@
     <t xml:space="preserve">3.09152317047119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04456305503845</t>
+    <t xml:space="preserve">3.04456329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03673648834229</t>
+    <t xml:space="preserve">3.03673672676086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03830170631409</t>
+    <t xml:space="preserve">3.03830146789551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15413641929626</t>
+    <t xml:space="preserve">3.15413665771484</t>
   </si>
   <si>
     <t xml:space="preserve">3.30910396575928</t>
@@ -152,31 +152,31 @@
     <t xml:space="preserve">3.30284190177917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3576283454895</t>
+    <t xml:space="preserve">3.35762882232666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57677483558655</t>
+    <t xml:space="preserve">3.57677555084229</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52198815345764</t>
+    <t xml:space="preserve">3.52198839187622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40458846092224</t>
+    <t xml:space="preserve">3.40458869934082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59242820739746</t>
+    <t xml:space="preserve">3.59242796897888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58460116386414</t>
+    <t xml:space="preserve">3.58460140228271</t>
   </si>
   <si>
     <t xml:space="preserve">3.67852115631104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60025453567505</t>
+    <t xml:space="preserve">3.60025429725647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59555816650391</t>
+    <t xml:space="preserve">3.59555864334106</t>
   </si>
   <si>
     <t xml:space="preserve">3.32632231712341</t>
@@ -185,52 +185,52 @@
     <t xml:space="preserve">3.29501581192017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37484741210938</t>
+    <t xml:space="preserve">3.3748471736908</t>
   </si>
   <si>
     <t xml:space="preserve">3.38267374038696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44372224807739</t>
+    <t xml:space="preserve">3.44372177124023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59086298942566</t>
+    <t xml:space="preserve">3.5908625125885</t>
   </si>
   <si>
     <t xml:space="preserve">3.47972440719604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42650294303894</t>
+    <t xml:space="preserve">3.42650270462036</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41241502761841</t>
+    <t xml:space="preserve">3.41241526603699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24022912979126</t>
+    <t xml:space="preserve">3.24022889137268</t>
   </si>
   <si>
     <t xml:space="preserve">3.21048808097839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28405833244324</t>
+    <t xml:space="preserve">3.28405809402466</t>
   </si>
   <si>
     <t xml:space="preserve">3.16196274757385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20892262458801</t>
+    <t xml:space="preserve">3.20892238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13848280906677</t>
+    <t xml:space="preserve">3.13848328590393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23240280151367</t>
+    <t xml:space="preserve">3.23240256309509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31849527359009</t>
+    <t xml:space="preserve">3.31849551200867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27623152732849</t>
+    <t xml:space="preserve">3.27623128890991</t>
   </si>
   <si>
     <t xml:space="preserve">3.18857336044312</t>
@@ -239,40 +239,40 @@
     <t xml:space="preserve">3.14317870140076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11500334739685</t>
+    <t xml:space="preserve">3.11500310897827</t>
   </si>
   <si>
     <t xml:space="preserve">3.00073385238647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97412347793579</t>
+    <t xml:space="preserve">2.97412300109863</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06021618843079</t>
+    <t xml:space="preserve">3.06021642684937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90368342399597</t>
+    <t xml:space="preserve">2.90368366241455</t>
   </si>
   <si>
     <t xml:space="preserve">2.89585709571838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82854771614075</t>
+    <t xml:space="preserve">2.82854819297791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83637428283691</t>
+    <t xml:space="preserve">2.83637452125549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90994453430176</t>
+    <t xml:space="preserve">2.90994477272034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491231918335</t>
+    <t xml:space="preserve">3.06491255760193</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13065624237061</t>
+    <t xml:space="preserve">3.13065600395203</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14474439620972</t>
+    <t xml:space="preserve">3.14474415779114</t>
   </si>
   <si>
     <t xml:space="preserve">3.213618516922</t>
@@ -281,34 +281,34 @@
     <t xml:space="preserve">3.28562355041504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35919404029846</t>
+    <t xml:space="preserve">3.35919380187988</t>
   </si>
   <si>
     <t xml:space="preserve">3.36388969421387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91332030296326</t>
+    <t xml:space="preserve">3.91332054138184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34378480911255</t>
+    <t xml:space="preserve">4.34378576278687</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7938175201416</t>
+    <t xml:space="preserve">4.79381704330444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47864818572998</t>
+    <t xml:space="preserve">5.47864866256714</t>
   </si>
   <si>
     <t xml:space="preserve">6.09303903579712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41603517532349</t>
+    <t xml:space="preserve">5.41603565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71344804763794</t>
+    <t xml:space="preserve">5.71344757080078</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56865453720093</t>
+    <t xml:space="preserve">5.56865501403809</t>
   </si>
   <si>
     <t xml:space="preserve">5.41994857788086</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">5.16558265686035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94643688201904</t>
+    <t xml:space="preserve">4.94643640518188</t>
   </si>
   <si>
     <t xml:space="preserve">4.7038106918335</t>
@@ -326,13 +326,13 @@
     <t xml:space="preserve">4.67641735076904</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00904989242554</t>
+    <t xml:space="preserve">5.00904941558838</t>
   </si>
   <si>
     <t xml:space="preserve">5.55691432952881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30646276473999</t>
+    <t xml:space="preserve">5.30646228790283</t>
   </si>
   <si>
     <t xml:space="preserve">5.22428274154663</t>
@@ -341,43 +341,43 @@
     <t xml:space="preserve">5.19688940048218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32211542129517</t>
+    <t xml:space="preserve">5.32211589813232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47082233428955</t>
+    <t xml:space="preserve">5.47082185745239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36907577514648</t>
+    <t xml:space="preserve">5.36907529830933</t>
   </si>
   <si>
     <t xml:space="preserve">5.2908091545105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17340898513794</t>
+    <t xml:space="preserve">5.1734094619751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09514284133911</t>
+    <t xml:space="preserve">5.09514331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2203688621521</t>
+    <t xml:space="preserve">5.22036933898926</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1029691696167</t>
+    <t xml:space="preserve">5.10297012329102</t>
   </si>
   <si>
     <t xml:space="preserve">4.99339628219604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15384244918823</t>
+    <t xml:space="preserve">5.15384292602539</t>
   </si>
   <si>
     <t xml:space="preserve">4.9855694770813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7585973739624</t>
+    <t xml:space="preserve">4.75859689712524</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77033710479736</t>
+    <t xml:space="preserve">4.77033662796021</t>
   </si>
   <si>
     <t xml:space="preserve">4.86425733566284</t>
@@ -386,52 +386,52 @@
     <t xml:space="preserve">4.88773679733276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83295011520386</t>
+    <t xml:space="preserve">4.83295059204102</t>
   </si>
   <si>
     <t xml:space="preserve">4.75468349456787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82903671264648</t>
+    <t xml:space="preserve">4.82903718948364</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72337675094604</t>
+    <t xml:space="preserve">4.7233772277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68815803527832</t>
+    <t xml:space="preserve">4.68815755844116</t>
   </si>
   <si>
     <t xml:space="preserve">4.78207731246948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87599658966064</t>
+    <t xml:space="preserve">4.8759970664978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03644275665283</t>
+    <t xml:space="preserve">5.03644371032715</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92687034606934</t>
+    <t xml:space="preserve">4.92686986923218</t>
   </si>
   <si>
     <t xml:space="preserve">4.81338405609131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86034345626831</t>
+    <t xml:space="preserve">4.86034393310547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00122356414795</t>
+    <t xml:space="preserve">5.00122261047363</t>
   </si>
   <si>
     <t xml:space="preserve">4.77425050735474</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82121086120605</t>
+    <t xml:space="preserve">4.82120990753174</t>
   </si>
   <si>
     <t xml:space="preserve">4.69989776611328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69598436355591</t>
+    <t xml:space="preserve">4.69598388671875</t>
   </si>
   <si>
     <t xml:space="preserve">4.90730333328247</t>
@@ -440,28 +440,28 @@
     <t xml:space="preserve">5.20471620559692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43951463699341</t>
+    <t xml:space="preserve">5.43951559066772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28298234939575</t>
+    <t xml:space="preserve">5.28298282623291</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384880065918</t>
+    <t xml:space="preserve">5.24384927749634</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36124849319458</t>
+    <t xml:space="preserve">5.36124897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40038251876831</t>
+    <t xml:space="preserve">5.40038204193115</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51778125762939</t>
+    <t xml:space="preserve">5.51778221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63518095016479</t>
+    <t xml:space="preserve">5.63518142700195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96991634368896</t>
+    <t xml:space="preserve">4.96991682052612</t>
   </si>
   <si>
     <t xml:space="preserve">4.93078374862671</t>
@@ -470,34 +470,34 @@
     <t xml:space="preserve">4.85251665115356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12644910812378</t>
+    <t xml:space="preserve">5.1264500617981</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04818296432495</t>
+    <t xml:space="preserve">5.04818248748779</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08731698989868</t>
+    <t xml:space="preserve">5.08731651306152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59604835510254</t>
+    <t xml:space="preserve">5.59604787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26159763336182</t>
+    <t xml:space="preserve">5.26159715652466</t>
   </si>
   <si>
     <t xml:space="preserve">5.42103958129883</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34131860733032</t>
+    <t xml:space="preserve">5.34131813049316</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22173643112183</t>
+    <t xml:space="preserve">5.22173690795898</t>
   </si>
   <si>
     <t xml:space="preserve">5.14201545715332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10215520858765</t>
+    <t xml:space="preserve">5.1021556854248</t>
   </si>
   <si>
     <t xml:space="preserve">5.18187618255615</t>
@@ -509,13 +509,13 @@
     <t xml:space="preserve">5.30145788192749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90285205841064</t>
+    <t xml:space="preserve">4.9028525352478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50076150894165</t>
+    <t xml:space="preserve">5.50076198577881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4608998298645</t>
+    <t xml:space="preserve">5.46090030670166</t>
   </si>
   <si>
     <t xml:space="preserve">5.580482006073</t>
@@ -524,13 +524,13 @@
     <t xml:space="preserve">5.54062128067017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62034225463867</t>
+    <t xml:space="preserve">5.62034273147583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94271230697632</t>
+    <t xml:space="preserve">4.94271278381348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98257303237915</t>
+    <t xml:space="preserve">4.98257350921631</t>
   </si>
   <si>
     <t xml:space="preserve">4.82313060760498</t>
@@ -542,16 +542,16 @@
     <t xml:space="preserve">5.02243423461914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74340915679932</t>
+    <t xml:space="preserve">4.74341011047363</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78327083587646</t>
+    <t xml:space="preserve">4.78326988220215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86299133300781</t>
+    <t xml:space="preserve">4.86299085617065</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73992395401001</t>
+    <t xml:space="preserve">5.73992443084717</t>
   </si>
   <si>
     <t xml:space="preserve">5.81964588165283</t>
@@ -560,19 +560,19 @@
     <t xml:space="preserve">5.70006418228149</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66020345687866</t>
+    <t xml:space="preserve">5.6602029800415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77978515625</t>
+    <t xml:space="preserve">5.77978467941284</t>
   </si>
   <si>
     <t xml:space="preserve">5.85950565338135</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97908782958984</t>
+    <t xml:space="preserve">5.979088306427</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29797267913818</t>
+    <t xml:space="preserve">6.29797315597534</t>
   </si>
   <si>
     <t xml:space="preserve">6.13853025436401</t>
@@ -593,10 +593,10 @@
     <t xml:space="preserve">6.25998449325562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30171775817871</t>
+    <t xml:space="preserve">6.30171823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17651891708374</t>
+    <t xml:space="preserve">6.17651844024658</t>
   </si>
   <si>
     <t xml:space="preserve">6.426917552948</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">5.96785259246826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00958490371704</t>
+    <t xml:space="preserve">6.0095853805542</t>
   </si>
   <si>
     <t xml:space="preserve">6.13478469848633</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">6.21825122833252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51038455963135</t>
+    <t xml:space="preserve">6.51038408279419</t>
   </si>
   <si>
     <t xml:space="preserve">5.84265232086182</t>
@@ -638,49 +638,49 @@
     <t xml:space="preserve">5.88438558578491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05291509628296</t>
+    <t xml:space="preserve">7.05291604995728</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09624671936035</t>
+    <t xml:space="preserve">8.09624576568604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80411386489868</t>
+    <t xml:space="preserve">7.80411529541016</t>
   </si>
   <si>
     <t xml:space="preserve">7.63718128204346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55371570587158</t>
+    <t xml:space="preserve">7.55371522903442</t>
   </si>
   <si>
     <t xml:space="preserve">7.3450493812561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17811679840088</t>
+    <t xml:space="preserve">7.17811632156372</t>
   </si>
   <si>
     <t xml:space="preserve">7.51198148727417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47024822235107</t>
+    <t xml:space="preserve">7.47024774551392</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30331563949585</t>
+    <t xml:space="preserve">7.30331611633301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851543426514</t>
+    <t xml:space="preserve">7.42851591110229</t>
   </si>
   <si>
     <t xml:space="preserve">7.2615818977356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38678216934204</t>
+    <t xml:space="preserve">7.3867826461792</t>
   </si>
   <si>
     <t xml:space="preserve">6.96944999694824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2198486328125</t>
+    <t xml:space="preserve">7.21984958648682</t>
   </si>
   <si>
     <t xml:space="preserve">7.59544801712036</t>
@@ -689,52 +689,52 @@
     <t xml:space="preserve">7.76238107681274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84584760665894</t>
+    <t xml:space="preserve">7.84584665298462</t>
   </si>
   <si>
     <t xml:space="preserve">7.67891454696655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01118278503418</t>
+    <t xml:space="preserve">7.01118326187134</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09464931488037</t>
+    <t xml:space="preserve">7.09464979171753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9277172088623</t>
+    <t xml:space="preserve">6.92771673202515</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76078414916992</t>
+    <t xml:space="preserve">6.76078367233276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8025164604187</t>
+    <t xml:space="preserve">6.80251693725586</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71904993057251</t>
+    <t xml:space="preserve">6.71905040740967</t>
   </si>
   <si>
     <t xml:space="preserve">6.8442497253418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59385061264038</t>
+    <t xml:space="preserve">6.59385108947754</t>
   </si>
   <si>
     <t xml:space="preserve">6.67731714248657</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55211687088013</t>
+    <t xml:space="preserve">6.55211639404297</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75918626785278</t>
+    <t xml:space="preserve">5.75918674468994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71745252609253</t>
+    <t xml:space="preserve">5.71745300292969</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80091857910156</t>
+    <t xml:space="preserve">5.80091905593872</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67571973800659</t>
+    <t xml:space="preserve">5.67571926116943</t>
   </si>
   <si>
     <t xml:space="preserve">5.59225273132324</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">7.47247123718262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25269222259521</t>
+    <t xml:space="preserve">7.25269269943237</t>
   </si>
   <si>
     <t xml:space="preserve">7.29664850234985</t>
@@ -776,7 +776,7 @@
     <t xml:space="preserve">7.16478109359741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07686996459961</t>
+    <t xml:space="preserve">7.07686948776245</t>
   </si>
   <si>
     <t xml:space="preserve">6.98895788192749</t>
@@ -788,13 +788,13 @@
     <t xml:space="preserve">6.94500303268433</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85709047317505</t>
+    <t xml:space="preserve">6.85709095001221</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72522401809692</t>
+    <t xml:space="preserve">6.72522449493408</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81313562393188</t>
+    <t xml:space="preserve">6.81313514709473</t>
   </si>
   <si>
     <t xml:space="preserve">6.76917934417725</t>
@@ -809,16 +809,16 @@
     <t xml:space="preserve">7.12082529067993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34060335159302</t>
+    <t xml:space="preserve">7.34060382843018</t>
   </si>
   <si>
     <t xml:space="preserve">7.5164270401001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56038188934326</t>
+    <t xml:space="preserve">7.56038284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851448059082</t>
+    <t xml:space="preserve">7.42851495742798</t>
   </si>
   <si>
     <t xml:space="preserve">7.73620557785034</t>
@@ -61943,7 +61943,7 @@
     </row>
     <row r="2305">
       <c r="A2305" s="1" t="n">
-        <v>46014.3333912037</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B2305" t="n">
         <v>250</v>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="564">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -50,19 +50,19 @@
     <t xml:space="preserve">2.43408489227295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41060495376587</t>
+    <t xml:space="preserve">2.41060519218445</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45756530761719</t>
+    <t xml:space="preserve">2.45756483078003</t>
   </si>
   <si>
     <t xml:space="preserve">2.39495182037354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233904838562</t>
+    <t xml:space="preserve">2.33233880996704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41843152046204</t>
+    <t xml:space="preserve">2.41843199729919</t>
   </si>
   <si>
     <t xml:space="preserve">2.35581874847412</t>
@@ -71,16 +71,16 @@
     <t xml:space="preserve">2.37147188186646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50452470779419</t>
+    <t xml:space="preserve">2.50452518463135</t>
   </si>
   <si>
     <t xml:space="preserve">2.36364531517029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44973850250244</t>
+    <t xml:space="preserve">2.44973826408386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37303781509399</t>
+    <t xml:space="preserve">2.37303733825684</t>
   </si>
   <si>
     <t xml:space="preserve">2.34955763816833</t>
@@ -89,94 +89,94 @@
     <t xml:space="preserve">2.46382665634155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38712525367737</t>
+    <t xml:space="preserve">2.38712549209595</t>
   </si>
   <si>
     <t xml:space="preserve">2.45443439483643</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34799194335938</t>
+    <t xml:space="preserve">2.3479917049408</t>
   </si>
   <si>
     <t xml:space="preserve">2.48104524612427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37929844856262</t>
+    <t xml:space="preserve">2.37929916381836</t>
   </si>
   <si>
     <t xml:space="preserve">2.38556003570557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4419116973877</t>
+    <t xml:space="preserve">2.44191193580627</t>
   </si>
   <si>
     <t xml:space="preserve">2.78002262115479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36702084541321</t>
+    <t xml:space="preserve">3.36702060699463</t>
   </si>
   <si>
     <t xml:space="preserve">3.62529993057251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3106689453125</t>
+    <t xml:space="preserve">3.31066870689392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25588202476501</t>
+    <t xml:space="preserve">3.25588250160217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20266151428223</t>
+    <t xml:space="preserve">3.20266127586365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0523898601532</t>
+    <t xml:space="preserve">3.05239009857178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09152317047119</t>
+    <t xml:space="preserve">3.09152269363403</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04456329345703</t>
+    <t xml:space="preserve">3.04456305503845</t>
   </si>
   <si>
     <t xml:space="preserve">3.03673672676086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03830146789551</t>
+    <t xml:space="preserve">3.03830218315125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15413665771484</t>
+    <t xml:space="preserve">3.15413618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30910396575928</t>
+    <t xml:space="preserve">3.3091037273407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30284190177917</t>
+    <t xml:space="preserve">3.30284214019775</t>
   </si>
   <si>
     <t xml:space="preserve">3.35762882232666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57677555084229</t>
+    <t xml:space="preserve">3.57677507400513</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52198839187622</t>
+    <t xml:space="preserve">3.52198791503906</t>
   </si>
   <si>
     <t xml:space="preserve">3.40458869934082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59242796897888</t>
+    <t xml:space="preserve">3.59242844581604</t>
   </si>
   <si>
     <t xml:space="preserve">3.58460140228271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67852115631104</t>
+    <t xml:space="preserve">3.67852067947388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60025429725647</t>
+    <t xml:space="preserve">3.60025477409363</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59555864334106</t>
+    <t xml:space="preserve">3.59555888175964</t>
   </si>
   <si>
     <t xml:space="preserve">3.32632231712341</t>
@@ -185,19 +185,19 @@
     <t xml:space="preserve">3.29501581192017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3748471736908</t>
+    <t xml:space="preserve">3.37484741210938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38267374038696</t>
+    <t xml:space="preserve">3.38267350196838</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44372177124023</t>
+    <t xml:space="preserve">3.44372224807739</t>
   </si>
   <si>
     <t xml:space="preserve">3.5908625125885</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47972440719604</t>
+    <t xml:space="preserve">3.47972464561462</t>
   </si>
   <si>
     <t xml:space="preserve">3.42650270462036</t>
@@ -206,46 +206,46 @@
     <t xml:space="preserve">3.41241526603699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24022889137268</t>
+    <t xml:space="preserve">3.2402286529541</t>
   </si>
   <si>
     <t xml:space="preserve">3.21048808097839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28405809402466</t>
+    <t xml:space="preserve">3.28405857086182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16196274757385</t>
+    <t xml:space="preserve">3.16196250915527</t>
   </si>
   <si>
     <t xml:space="preserve">3.20892238616943</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13848328590393</t>
+    <t xml:space="preserve">3.13848304748535</t>
   </si>
   <si>
     <t xml:space="preserve">3.23240256309509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31849551200867</t>
+    <t xml:space="preserve">3.31849527359009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27623128890991</t>
+    <t xml:space="preserve">3.27623176574707</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18857336044312</t>
+    <t xml:space="preserve">3.18857312202454</t>
   </si>
   <si>
     <t xml:space="preserve">3.14317870140076</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11500310897827</t>
+    <t xml:space="preserve">3.11500334739685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00073385238647</t>
+    <t xml:space="preserve">3.00073409080505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97412300109863</t>
+    <t xml:space="preserve">2.97412323951721</t>
   </si>
   <si>
     <t xml:space="preserve">3.06021642684937</t>
@@ -257,16 +257,16 @@
     <t xml:space="preserve">2.89585709571838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82854819297791</t>
+    <t xml:space="preserve">2.82854795455933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83637452125549</t>
+    <t xml:space="preserve">2.83637428283691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90994477272034</t>
+    <t xml:space="preserve">2.90994501113892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491255760193</t>
+    <t xml:space="preserve">3.06491208076477</t>
   </si>
   <si>
     <t xml:space="preserve">3.13065600395203</t>
@@ -278,16 +278,16 @@
     <t xml:space="preserve">3.213618516922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28562355041504</t>
+    <t xml:space="preserve">3.28562378883362</t>
   </si>
   <si>
     <t xml:space="preserve">3.35919380187988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36388969421387</t>
+    <t xml:space="preserve">3.36388945579529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91332054138184</t>
+    <t xml:space="preserve">3.91332030296326</t>
   </si>
   <si>
     <t xml:space="preserve">4.34378576278687</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">5.47864866256714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09303903579712</t>
+    <t xml:space="preserve">6.09303951263428</t>
   </si>
   <si>
     <t xml:space="preserve">5.41603565216064</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">5.71344757080078</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56865501403809</t>
+    <t xml:space="preserve">5.56865406036377</t>
   </si>
   <si>
     <t xml:space="preserve">5.41994857788086</t>
@@ -317,22 +317,22 @@
     <t xml:space="preserve">5.16558265686035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94643640518188</t>
+    <t xml:space="preserve">4.9464373588562</t>
   </si>
   <si>
     <t xml:space="preserve">4.7038106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67641735076904</t>
+    <t xml:space="preserve">4.6764178276062</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00904941558838</t>
+    <t xml:space="preserve">5.0090503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55691432952881</t>
+    <t xml:space="preserve">5.55691480636597</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30646228790283</t>
+    <t xml:space="preserve">5.30646276473999</t>
   </si>
   <si>
     <t xml:space="preserve">5.22428274154663</t>
@@ -344,13 +344,13 @@
     <t xml:space="preserve">5.32211589813232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47082185745239</t>
+    <t xml:space="preserve">5.47082138061523</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36907529830933</t>
+    <t xml:space="preserve">5.36907482147217</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2908091545105</t>
+    <t xml:space="preserve">5.29080867767334</t>
   </si>
   <si>
     <t xml:space="preserve">5.1734094619751</t>
@@ -359,25 +359,25 @@
     <t xml:space="preserve">5.09514331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22036933898926</t>
+    <t xml:space="preserve">5.2203688621521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10297012329102</t>
+    <t xml:space="preserve">5.1029691696167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99339628219604</t>
+    <t xml:space="preserve">4.9933967590332</t>
   </si>
   <si>
     <t xml:space="preserve">5.15384292602539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9855694770813</t>
+    <t xml:space="preserve">4.98556995391846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75859689712524</t>
+    <t xml:space="preserve">4.75859832763672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77033662796021</t>
+    <t xml:space="preserve">4.77033710479736</t>
   </si>
   <si>
     <t xml:space="preserve">4.86425733566284</t>
@@ -386,16 +386,16 @@
     <t xml:space="preserve">4.88773679733276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83295059204102</t>
+    <t xml:space="preserve">4.83295106887817</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75468349456787</t>
+    <t xml:space="preserve">4.75468397140503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82903718948364</t>
+    <t xml:space="preserve">4.82903671264648</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7233772277832</t>
+    <t xml:space="preserve">4.72337675094604</t>
   </si>
   <si>
     <t xml:space="preserve">4.68815755844116</t>
@@ -404,46 +404,46 @@
     <t xml:space="preserve">4.78207731246948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8759970664978</t>
+    <t xml:space="preserve">4.87599658966064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03644371032715</t>
+    <t xml:space="preserve">5.03644323348999</t>
   </si>
   <si>
     <t xml:space="preserve">4.92686986923218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81338405609131</t>
+    <t xml:space="preserve">4.81338357925415</t>
   </si>
   <si>
     <t xml:space="preserve">4.86034393310547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00122261047363</t>
+    <t xml:space="preserve">5.00122308731079</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77425050735474</t>
+    <t xml:space="preserve">4.77425098419189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82120990753174</t>
+    <t xml:space="preserve">4.8212103843689</t>
   </si>
   <si>
     <t xml:space="preserve">4.69989776611328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69598388671875</t>
+    <t xml:space="preserve">4.69598340988159</t>
   </si>
   <si>
     <t xml:space="preserve">4.90730333328247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20471620559692</t>
+    <t xml:space="preserve">5.20471572875977</t>
   </si>
   <si>
     <t xml:space="preserve">5.43951559066772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28298282623291</t>
+    <t xml:space="preserve">5.28298187255859</t>
   </si>
   <si>
     <t xml:space="preserve">5.24384927749634</t>
@@ -452,13 +452,13 @@
     <t xml:space="preserve">5.36124897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40038204193115</t>
+    <t xml:space="preserve">5.40038251876831</t>
   </si>
   <si>
     <t xml:space="preserve">5.51778221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63518142700195</t>
+    <t xml:space="preserve">5.63518095016479</t>
   </si>
   <si>
     <t xml:space="preserve">4.96991682052612</t>
@@ -470,40 +470,40 @@
     <t xml:space="preserve">4.85251665115356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1264500617981</t>
+    <t xml:space="preserve">5.12644910812378</t>
   </si>
   <si>
     <t xml:space="preserve">5.04818248748779</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08731651306152</t>
+    <t xml:space="preserve">5.08731555938721</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59604787826538</t>
+    <t xml:space="preserve">5.59604835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26159715652466</t>
+    <t xml:space="preserve">5.26159763336182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42103958129883</t>
+    <t xml:space="preserve">5.42104005813599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34131813049316</t>
+    <t xml:space="preserve">5.34131908416748</t>
   </si>
   <si>
     <t xml:space="preserve">5.22173690795898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14201545715332</t>
+    <t xml:space="preserve">5.14201498031616</t>
   </si>
   <si>
     <t xml:space="preserve">5.1021556854248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18187618255615</t>
+    <t xml:space="preserve">5.18187570571899</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38117933273315</t>
+    <t xml:space="preserve">5.381178855896</t>
   </si>
   <si>
     <t xml:space="preserve">5.30145788192749</t>
@@ -512,10 +512,10 @@
     <t xml:space="preserve">4.9028525352478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50076198577881</t>
+    <t xml:space="preserve">5.50076150894165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46090030670166</t>
+    <t xml:space="preserve">5.4608998298645</t>
   </si>
   <si>
     <t xml:space="preserve">5.580482006073</t>
@@ -527,55 +527,55 @@
     <t xml:space="preserve">5.62034273147583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94271278381348</t>
+    <t xml:space="preserve">4.94271183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98257350921631</t>
+    <t xml:space="preserve">4.98257303237915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82313060760498</t>
+    <t xml:space="preserve">4.82313108444214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06229400634766</t>
+    <t xml:space="preserve">5.06229448318481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02243423461914</t>
+    <t xml:space="preserve">5.02243375778198</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74341011047363</t>
+    <t xml:space="preserve">4.74340915679932</t>
   </si>
   <si>
     <t xml:space="preserve">4.78326988220215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86299085617065</t>
+    <t xml:space="preserve">4.86299180984497</t>
   </si>
   <si>
     <t xml:space="preserve">5.73992443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81964588165283</t>
+    <t xml:space="preserve">5.81964540481567</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70006418228149</t>
+    <t xml:space="preserve">5.70006322860718</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6602029800415</t>
+    <t xml:space="preserve">5.66020345687866</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77978467941284</t>
+    <t xml:space="preserve">5.77978515625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85950565338135</t>
+    <t xml:space="preserve">5.85950660705566</t>
   </si>
   <si>
     <t xml:space="preserve">5.979088306427</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29797315597534</t>
+    <t xml:space="preserve">6.29797220230103</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13853025436401</t>
+    <t xml:space="preserve">6.13852977752686</t>
   </si>
   <si>
     <t xml:space="preserve">6.05880880355835</t>
@@ -584,52 +584,52 @@
     <t xml:space="preserve">6.21825170516968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0986704826355</t>
+    <t xml:space="preserve">6.09867000579834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38518524169922</t>
+    <t xml:space="preserve">6.38518476486206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25998449325562</t>
+    <t xml:space="preserve">6.25998497009277</t>
   </si>
   <si>
     <t xml:space="preserve">6.30171823501587</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17651844024658</t>
+    <t xml:space="preserve">6.17651796340942</t>
   </si>
   <si>
     <t xml:space="preserve">6.426917552948</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34345102310181</t>
+    <t xml:space="preserve">6.34345054626465</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46865081787109</t>
+    <t xml:space="preserve">6.46865034103394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96785259246826</t>
+    <t xml:space="preserve">5.96785163879395</t>
   </si>
   <si>
     <t xml:space="preserve">6.0095853805542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13478469848633</t>
+    <t xml:space="preserve">6.13478517532349</t>
   </si>
   <si>
     <t xml:space="preserve">6.05131864547729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92611885070801</t>
+    <t xml:space="preserve">5.92611837387085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09305191040039</t>
+    <t xml:space="preserve">6.09305143356323</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825122833252</t>
+    <t xml:space="preserve">6.21825075149536</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51038408279419</t>
+    <t xml:space="preserve">6.51038455963135</t>
   </si>
   <si>
     <t xml:space="preserve">5.84265232086182</t>
@@ -641,37 +641,37 @@
     <t xml:space="preserve">7.05291604995728</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09624576568604</t>
+    <t xml:space="preserve">8.09624671936035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80411529541016</t>
+    <t xml:space="preserve">7.804114818573</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63718128204346</t>
+    <t xml:space="preserve">7.63718175888062</t>
   </si>
   <si>
     <t xml:space="preserve">7.55371522903442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3450493812561</t>
+    <t xml:space="preserve">7.34504890441895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17811632156372</t>
+    <t xml:space="preserve">7.17811679840088</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51198148727417</t>
+    <t xml:space="preserve">7.51198101043701</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47024774551392</t>
+    <t xml:space="preserve">7.47024822235107</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30331611633301</t>
+    <t xml:space="preserve">7.30331516265869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851591110229</t>
+    <t xml:space="preserve">7.42851448059082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2615818977356</t>
+    <t xml:space="preserve">7.26158237457275</t>
   </si>
   <si>
     <t xml:space="preserve">7.3867826461792</t>
@@ -680,55 +680,55 @@
     <t xml:space="preserve">6.96944999694824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21984958648682</t>
+    <t xml:space="preserve">7.2198486328125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544801712036</t>
+    <t xml:space="preserve">7.59544849395752</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76238107681274</t>
+    <t xml:space="preserve">7.76238203048706</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84584665298462</t>
+    <t xml:space="preserve">7.84584760665894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67891454696655</t>
+    <t xml:space="preserve">7.67891502380371</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01118326187134</t>
+    <t xml:space="preserve">7.01118230819702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09464979171753</t>
+    <t xml:space="preserve">7.09464931488037</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92771673202515</t>
+    <t xml:space="preserve">6.92771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76078367233276</t>
+    <t xml:space="preserve">6.76078414916992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80251693725586</t>
+    <t xml:space="preserve">6.80251598358154</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71905040740967</t>
+    <t xml:space="preserve">6.71904993057251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8442497253418</t>
+    <t xml:space="preserve">6.84424924850464</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59385108947754</t>
+    <t xml:space="preserve">6.59385013580322</t>
   </si>
   <si>
     <t xml:space="preserve">6.67731714248657</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55211639404297</t>
+    <t xml:space="preserve">6.55211734771729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75918674468994</t>
+    <t xml:space="preserve">5.75918626785278</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71745300292969</t>
+    <t xml:space="preserve">5.71745204925537</t>
   </si>
   <si>
     <t xml:space="preserve">5.80091905593872</t>
@@ -740,10 +740,10 @@
     <t xml:space="preserve">5.59225273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6339864730835</t>
+    <t xml:space="preserve">5.63398599624634</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46705293655396</t>
+    <t xml:space="preserve">5.46705341339111</t>
   </si>
   <si>
     <t xml:space="preserve">5.5505199432373</t>
@@ -758,22 +758,22 @@
     <t xml:space="preserve">5.38358688354492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13638305664062</t>
+    <t xml:space="preserve">7.13638401031494</t>
   </si>
   <si>
     <t xml:space="preserve">7.47247123718262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25269269943237</t>
+    <t xml:space="preserve">7.25269222259521</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29664850234985</t>
+    <t xml:space="preserve">7.29664754867554</t>
   </si>
   <si>
     <t xml:space="preserve">7.20873641967773</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16478109359741</t>
+    <t xml:space="preserve">7.16478061676025</t>
   </si>
   <si>
     <t xml:space="preserve">7.07686948776245</t>
@@ -785,13 +785,13 @@
     <t xml:space="preserve">7.03291368484497</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94500303268433</t>
+    <t xml:space="preserve">6.94500255584717</t>
   </si>
   <si>
     <t xml:space="preserve">6.85709095001221</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72522449493408</t>
+    <t xml:space="preserve">6.72522401809692</t>
   </si>
   <si>
     <t xml:space="preserve">6.81313514709473</t>
@@ -800,13 +800,13 @@
     <t xml:space="preserve">6.76917934417725</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90104579925537</t>
+    <t xml:space="preserve">6.90104675292969</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63731241226196</t>
+    <t xml:space="preserve">6.63731288909912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12082529067993</t>
+    <t xml:space="preserve">7.12082576751709</t>
   </si>
   <si>
     <t xml:space="preserve">7.34060382843018</t>
@@ -818,25 +818,25 @@
     <t xml:space="preserve">7.56038284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851495742798</t>
+    <t xml:space="preserve">7.42851543426514</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73620557785034</t>
+    <t xml:space="preserve">7.7362060546875</t>
   </si>
   <si>
     <t xml:space="preserve">7.69224977493286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829349517822</t>
+    <t xml:space="preserve">7.64829397201538</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78247404098511</t>
+    <t xml:space="preserve">7.78247451782227</t>
   </si>
   <si>
     <t xml:space="preserve">7.82720136642456</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73774719238281</t>
+    <t xml:space="preserve">7.73774671554565</t>
   </si>
   <si>
     <t xml:space="preserve">7.69302082061768</t>
@@ -848,19 +848,19 @@
     <t xml:space="preserve">7.60356712341309</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91665554046631</t>
+    <t xml:space="preserve">7.91665458679199</t>
   </si>
   <si>
     <t xml:space="preserve">7.87192869186401</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96138143539429</t>
+    <t xml:space="preserve">7.96138048171997</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2297420501709</t>
+    <t xml:space="preserve">8.22974300384521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76646614074707</t>
+    <t xml:space="preserve">8.76646518707275</t>
   </si>
   <si>
     <t xml:space="preserve">8.58755779266357</t>
@@ -881,10 +881,10 @@
     <t xml:space="preserve">8.27446937561035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45337581634521</t>
+    <t xml:space="preserve">8.45337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67701053619385</t>
+    <t xml:space="preserve">8.67701148986816</t>
   </si>
   <si>
     <t xml:space="preserve">8.49810314178467</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">8.85591888427734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03482723236084</t>
+    <t xml:space="preserve">9.03482627868652</t>
   </si>
   <si>
     <t xml:space="preserve">10.3766326904297</t>
@@ -911,31 +911,31 @@
     <t xml:space="preserve">10.734447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0922622680664</t>
+    <t xml:space="preserve">11.0922613143921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9133539199829</t>
+    <t xml:space="preserve">10.9133548736572</t>
   </si>
   <si>
-    <t xml:space="preserve">11.181715965271</t>
+    <t xml:space="preserve">11.1817150115967</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3606224060059</t>
+    <t xml:space="preserve">11.3606233596802</t>
   </si>
   <si>
     <t xml:space="preserve">11.6289844512939</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5395307540894</t>
+    <t xml:space="preserve">11.539529800415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2711706161499</t>
+    <t xml:space="preserve">11.2711696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5555400848389</t>
+    <t xml:space="preserve">10.5555391311646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2871780395508</t>
+    <t xml:space="preserve">10.2871789932251</t>
   </si>
   <si>
     <t xml:space="preserve">11.0028085708618</t>
@@ -944,13 +944,13 @@
     <t xml:space="preserve">10.6449928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.46608543396</t>
+    <t xml:space="preserve">10.4660863876343</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1082715988159</t>
+    <t xml:space="preserve">10.1082706451416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1977252960205</t>
+    <t xml:space="preserve">10.1977243423462</t>
   </si>
   <si>
     <t xml:space="preserve">9.75045585632324</t>
@@ -959,22 +959,22 @@
     <t xml:space="preserve">10.018816947937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6129760742188</t>
+    <t xml:space="preserve">12.6129751205444</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9707899093628</t>
+    <t xml:space="preserve">12.9707908630371</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0442342758179</t>
+    <t xml:space="preserve">14.0442352294922</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7758741378784</t>
+    <t xml:space="preserve">13.7758731842041</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5075130462646</t>
+    <t xml:space="preserve">13.507513999939</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2391519546509</t>
+    <t xml:space="preserve">13.2391510009766</t>
   </si>
   <si>
     <t xml:space="preserve">13.0602445602417</t>
@@ -992,19 +992,19 @@
     <t xml:space="preserve">12.702428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1496963500977</t>
+    <t xml:space="preserve">13.149697303772</t>
   </si>
   <si>
     <t xml:space="preserve">13.3286046981812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547805786133</t>
+    <t xml:space="preserve">13.9547815322876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5969667434692</t>
+    <t xml:space="preserve">13.5969657897949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6864204406738</t>
+    <t xml:space="preserve">13.6864194869995</t>
   </si>
   <si>
     <t xml:space="preserve">13.865327835083</t>
@@ -1019,13 +1019,13 @@
     <t xml:space="preserve">15.2071342468262</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5809574127197</t>
+    <t xml:space="preserve">14.5809564590454</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7598657608032</t>
+    <t xml:space="preserve">14.7598648071289</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4915037155151</t>
+    <t xml:space="preserve">14.4915056228638</t>
   </si>
   <si>
     <t xml:space="preserve">14.5400886535645</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">14.1719846725464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8161659240723</t>
+    <t xml:space="preserve">14.8161668777466</t>
   </si>
   <si>
     <t xml:space="preserve">14.6321134567261</t>
@@ -1049,16 +1049,16 @@
     <t xml:space="preserve">15.3683223724365</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5523738861084</t>
+    <t xml:space="preserve">15.5523729324341</t>
   </si>
   <si>
-    <t xml:space="preserve">16.104528427124</t>
+    <t xml:space="preserve">16.1045265197754</t>
   </si>
   <si>
     <t xml:space="preserve">16.3806037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9204769134521</t>
+    <t xml:space="preserve">15.9204750061035</t>
   </si>
   <si>
     <t xml:space="preserve">17.2088394165039</t>
@@ -1082,25 +1082,25 @@
     <t xml:space="preserve">19.1413822174072</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6935386657715</t>
+    <t xml:space="preserve">19.6935367584229</t>
   </si>
   <si>
     <t xml:space="preserve">20.0616397857666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5340538024902</t>
+    <t xml:space="preserve">21.5340557098389</t>
   </si>
   <si>
     <t xml:space="preserve">23.3745727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">22.270263671875</t>
+    <t xml:space="preserve">22.2702617645264</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8224182128906</t>
+    <t xml:space="preserve">22.822416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6137962341309</t>
+    <t xml:space="preserve">20.6137943267822</t>
   </si>
   <si>
     <t xml:space="preserve">19.3254356384277</t>
@@ -1112,13 +1112,13 @@
     <t xml:space="preserve">22.0862102508545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0064697265625</t>
+    <t xml:space="preserve">23.0064678192139</t>
   </si>
   <si>
     <t xml:space="preserve">23.5586242675781</t>
   </si>
   <si>
-    <t xml:space="preserve">23.74267578125</t>
+    <t xml:space="preserve">23.7426738739014</t>
   </si>
   <si>
     <t xml:space="preserve">23.9267272949219</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">25.9512977600098</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5034503936768</t>
+    <t xml:space="preserve">26.5034523010254</t>
   </si>
   <si>
     <t xml:space="preserve">27.975866317749</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9206924438477</t>
+    <t xml:space="preserve">30.920690536499</t>
   </si>
   <si>
     <t xml:space="preserve">29.0801773071289</t>
@@ -1175,16 +1175,16 @@
     <t xml:space="preserve">31.4728527069092</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2336235046387</t>
+    <t xml:space="preserve">34.2336273193359</t>
   </si>
   <si>
     <t xml:space="preserve">34.7857818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8655166625977</t>
+    <t xml:space="preserve">33.8655204772949</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4974174499512</t>
+    <t xml:space="preserve">33.4974212646484</t>
   </si>
   <si>
     <t xml:space="preserve">30.1844844818115</t>
@@ -1193,10 +1193,10 @@
     <t xml:space="preserve">27.4237098693848</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6875019073486</t>
+    <t xml:space="preserve">26.6875038146973</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5831928253174</t>
+    <t xml:space="preserve">25.583194732666</t>
   </si>
   <si>
     <t xml:space="preserve">26.3194007873535</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">27.7918148040771</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8961238861084</t>
+    <t xml:space="preserve">28.896125793457</t>
   </si>
   <si>
     <t xml:space="preserve">29.4482803344727</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">28.3439693450928</t>
   </si>
   <si>
-    <t xml:space="preserve">27.055606842041</t>
+    <t xml:space="preserve">27.0556049346924</t>
   </si>
   <si>
     <t xml:space="preserve">26.8715553283691</t>
@@ -1229,7 +1229,7 @@
     <t xml:space="preserve">25.3991413116455</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7672443389893</t>
+    <t xml:space="preserve">25.7672462463379</t>
   </si>
   <si>
     <t xml:space="preserve">25.0310382843018</t>
@@ -1241,55 +1241,58 @@
     <t xml:space="preserve">30.5525894165039</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6323318481445</t>
+    <t xml:space="preserve">29.6323337554932</t>
   </si>
   <si>
     <t xml:space="preserve">30.0004329681396</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3931083679199</t>
+    <t xml:space="preserve">32.3931121826172</t>
   </si>
   <si>
-    <t xml:space="preserve">32.209056854248</t>
+    <t xml:space="preserve">32.2090530395508</t>
   </si>
   <si>
     <t xml:space="preserve">31.2887954711914</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6569004058838</t>
+    <t xml:space="preserve">31.6569042205811</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0250015258789</t>
+    <t xml:space="preserve">32.0250053405762</t>
   </si>
   <si>
     <t xml:space="preserve">32.0337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5990715026855</t>
+    <t xml:space="preserve">32.5990676879883</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1643714904785</t>
+    <t xml:space="preserve">33.1643753051758</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4106369018555</t>
+    <t xml:space="preserve">31.6568984985352</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7875022888184</t>
+    <t xml:space="preserve">32.4106407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9759407043457</t>
+    <t xml:space="preserve">32.7875061035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9759368896484</t>
   </si>
   <si>
     <t xml:space="preserve">30.9031639099121</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8453369140625</t>
+    <t xml:space="preserve">31.8453350067139</t>
   </si>
   <si>
     <t xml:space="preserve">30.714729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5262985229492</t>
+    <t xml:space="preserve">30.5263004302979</t>
   </si>
   <si>
     <t xml:space="preserve">31.2800331115723</t>
@@ -1298,7 +1301,7 @@
     <t xml:space="preserve">30.1494293212891</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3378639221191</t>
+    <t xml:space="preserve">30.3378658294678</t>
   </si>
   <si>
     <t xml:space="preserve">29.395694732666</t>
@@ -1325,7 +1328,7 @@
     <t xml:space="preserve">28.2650909423828</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6997890472412</t>
+    <t xml:space="preserve">27.6997871398926</t>
   </si>
   <si>
     <t xml:space="preserve">28.0766563415527</t>
@@ -1337,7 +1340,7 @@
     <t xml:space="preserve">25.2501468658447</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3079776763916</t>
+    <t xml:space="preserve">24.307975769043</t>
   </si>
   <si>
     <t xml:space="preserve">23.9311103820801</t>
@@ -1358,7 +1361,7 @@
     <t xml:space="preserve">23.7426776885986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.177375793457</t>
+    <t xml:space="preserve">23.1773738861084</t>
   </si>
   <si>
     <t xml:space="preserve">22.6120719909668</t>
@@ -1373,10 +1376,10 @@
     <t xml:space="preserve">22.2352046966553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0467700958252</t>
+    <t xml:space="preserve">22.0467720031738</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8005084991455</t>
+    <t xml:space="preserve">22.8005065917969</t>
   </si>
   <si>
     <t xml:space="preserve">22.988941192627</t>
@@ -1391,19 +1394,19 @@
     <t xml:space="preserve">25.6270160675049</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3807506561279</t>
+    <t xml:space="preserve">26.3807525634766</t>
   </si>
   <si>
-    <t xml:space="preserve">27.134485244751</t>
+    <t xml:space="preserve">27.1344871520996</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9460525512695</t>
+    <t xml:space="preserve">26.9460544586182</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3229198455811</t>
+    <t xml:space="preserve">27.3229217529297</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1923160552979</t>
+    <t xml:space="preserve">26.1923179626465</t>
   </si>
   <si>
     <t xml:space="preserve">26.7576179504395</t>
@@ -44671,7 +44674,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1640" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44723,7 +44726,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1642" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44749,7 +44752,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1643" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44931,7 +44934,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1650" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44957,7 +44960,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1651" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44983,7 +44986,7 @@
         <v>35</v>
       </c>
       <c r="G1652" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45009,7 +45012,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1653" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45035,7 +45038,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1654" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45061,7 +45064,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1655" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45087,7 +45090,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1656" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45113,7 +45116,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1657" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45139,7 +45142,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1658" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45165,7 +45168,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1659" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45191,7 +45194,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1660" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45217,7 +45220,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1661" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45243,7 +45246,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1662" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45269,7 +45272,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1663" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45295,7 +45298,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1664" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45321,7 +45324,7 @@
         <v>32</v>
       </c>
       <c r="G1665" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45347,7 +45350,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1666" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45373,7 +45376,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1667" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45399,7 +45402,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1668" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45425,7 +45428,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1669" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45451,7 +45454,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1670" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45477,7 +45480,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1671" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45503,7 +45506,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1672" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45529,7 +45532,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1673" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45555,7 +45558,7 @@
         <v>32</v>
       </c>
       <c r="G1674" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45581,7 +45584,7 @@
         <v>32</v>
       </c>
       <c r="G1675" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45607,7 +45610,7 @@
         <v>32</v>
       </c>
       <c r="G1676" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45633,7 +45636,7 @@
         <v>32</v>
       </c>
       <c r="G1677" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45659,7 +45662,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1678" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45685,7 +45688,7 @@
         <v>33</v>
       </c>
       <c r="G1679" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45711,7 +45714,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1680" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45737,7 +45740,7 @@
         <v>33</v>
       </c>
       <c r="G1681" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45763,7 +45766,7 @@
         <v>32</v>
       </c>
       <c r="G1682" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45789,7 +45792,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1683" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45815,7 +45818,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1684" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45841,7 +45844,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1685" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45867,7 +45870,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1686" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45893,7 +45896,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1687" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45919,7 +45922,7 @@
         <v>33</v>
       </c>
       <c r="G1688" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45945,7 +45948,7 @@
         <v>33</v>
       </c>
       <c r="G1689" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45971,7 +45974,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1690" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45997,7 +46000,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1691" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46023,7 +46026,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1692" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46127,7 +46130,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1696" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46153,7 +46156,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1697" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46179,7 +46182,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1698" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46205,7 +46208,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1699" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46231,7 +46234,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1700" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46257,7 +46260,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1701" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46283,7 +46286,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1702" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46309,7 +46312,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1703" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46335,7 +46338,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1704" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46387,7 +46390,7 @@
         <v>33</v>
       </c>
       <c r="G1706" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46413,7 +46416,7 @@
         <v>33</v>
       </c>
       <c r="G1707" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46439,7 +46442,7 @@
         <v>33</v>
       </c>
       <c r="G1708" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46465,7 +46468,7 @@
         <v>33</v>
       </c>
       <c r="G1709" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46491,7 +46494,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1710" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46517,7 +46520,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1711" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46543,7 +46546,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1712" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46569,7 +46572,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1713" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46595,7 +46598,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1714" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46621,7 +46624,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1715" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46647,7 +46650,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1716" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46673,7 +46676,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1717" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46699,7 +46702,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1718" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46725,7 +46728,7 @@
         <v>32</v>
       </c>
       <c r="G1719" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46751,7 +46754,7 @@
         <v>32</v>
       </c>
       <c r="G1720" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46777,7 +46780,7 @@
         <v>32</v>
       </c>
       <c r="G1721" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46803,7 +46806,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1722" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46829,7 +46832,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1723" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46855,7 +46858,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1724" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46881,7 +46884,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1725" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46907,7 +46910,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1726" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46933,7 +46936,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1727" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46959,7 +46962,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1728" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46985,7 +46988,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1729" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47011,7 +47014,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1730" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47037,7 +47040,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1731" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47063,7 +47066,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1732" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47089,7 +47092,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1733" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47115,7 +47118,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1734" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47141,7 +47144,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1735" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47167,7 +47170,7 @@
         <v>30</v>
       </c>
       <c r="G1736" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47193,7 +47196,7 @@
         <v>30</v>
       </c>
       <c r="G1737" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47219,7 +47222,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1738" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47245,7 +47248,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1739" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47271,7 +47274,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1740" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47297,7 +47300,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1741" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47323,7 +47326,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1742" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47349,7 +47352,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1743" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47375,7 +47378,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1744" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47401,7 +47404,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1745" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47427,7 +47430,7 @@
         <v>26</v>
       </c>
       <c r="G1746" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47453,7 +47456,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1747" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47479,7 +47482,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1748" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47505,7 +47508,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1749" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47531,7 +47534,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1750" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47557,7 +47560,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1751" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47583,7 +47586,7 @@
         <v>27</v>
       </c>
       <c r="G1752" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47609,7 +47612,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1753" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47635,7 +47638,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1754" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47661,7 +47664,7 @@
         <v>26</v>
       </c>
       <c r="G1755" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47687,7 +47690,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1756" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47713,7 +47716,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1757" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47739,7 +47742,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1758" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47765,7 +47768,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1759" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47791,7 +47794,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1760" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47817,7 +47820,7 @@
         <v>24</v>
       </c>
       <c r="G1761" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47843,7 +47846,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1762" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47869,7 +47872,7 @@
         <v>23</v>
       </c>
       <c r="G1763" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47895,7 +47898,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1764" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47921,7 +47924,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1765" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47947,7 +47950,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1766" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47973,7 +47976,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1767" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47999,7 +48002,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1768" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48025,7 +48028,7 @@
         <v>24</v>
       </c>
       <c r="G1769" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48051,7 +48054,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1770" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48077,7 +48080,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1771" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48103,7 +48106,7 @@
         <v>24</v>
       </c>
       <c r="G1772" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48129,7 +48132,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48155,7 +48158,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1774" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48181,7 +48184,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1775" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48207,7 +48210,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1776" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48233,7 +48236,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1777" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48259,7 +48262,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1778" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48285,7 +48288,7 @@
         <v>28</v>
       </c>
       <c r="G1779" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48311,7 +48314,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1780" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48337,7 +48340,7 @@
         <v>28</v>
       </c>
       <c r="G1781" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48363,7 +48366,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1782" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48389,7 +48392,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1783" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48415,7 +48418,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1784" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48441,7 +48444,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1785" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48467,7 +48470,7 @@
         <v>28</v>
       </c>
       <c r="G1786" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48493,7 +48496,7 @@
         <v>28</v>
       </c>
       <c r="G1787" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48519,7 +48522,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1788" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48545,7 +48548,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1789" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48571,7 +48574,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1790" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -48597,7 +48600,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1791" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48623,7 +48626,7 @@
         <v>28</v>
       </c>
       <c r="G1792" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48649,7 +48652,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1793" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48675,7 +48678,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1794" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -48701,7 +48704,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1795" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48727,7 +48730,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1796" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48753,7 +48756,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1797" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48779,7 +48782,7 @@
         <v>29</v>
       </c>
       <c r="G1798" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48805,7 +48808,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1799" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48831,7 +48834,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1800" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48857,7 +48860,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1801" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48883,7 +48886,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1802" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48909,7 +48912,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1803" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48935,7 +48938,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1804" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48961,7 +48964,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1805" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48987,7 +48990,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1806" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49013,7 +49016,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1807" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49039,7 +49042,7 @@
         <v>28</v>
       </c>
       <c r="G1808" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49065,7 +49068,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1809" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49091,7 +49094,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1810" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49117,7 +49120,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1811" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49143,7 +49146,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1812" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49169,7 +49172,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1813" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49195,7 +49198,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1814" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49221,7 +49224,7 @@
         <v>27</v>
       </c>
       <c r="G1815" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49247,7 +49250,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1816" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49273,7 +49276,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1817" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49299,7 +49302,7 @@
         <v>26</v>
       </c>
       <c r="G1818" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49325,7 +49328,7 @@
         <v>26</v>
       </c>
       <c r="G1819" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49351,7 +49354,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1820" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49377,7 +49380,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1821" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49403,7 +49406,7 @@
         <v>26</v>
       </c>
       <c r="G1822" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49429,7 +49432,7 @@
         <v>26</v>
       </c>
       <c r="G1823" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49455,7 +49458,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49481,7 +49484,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1825" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49507,7 +49510,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1826" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49533,7 +49536,7 @@
         <v>29</v>
       </c>
       <c r="G1827" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49559,7 +49562,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1828" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49585,7 +49588,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1829" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49611,7 +49614,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49637,7 +49640,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1831" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49663,7 +49666,7 @@
         <v>29</v>
       </c>
       <c r="G1832" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49689,7 +49692,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1833" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49715,7 +49718,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1834" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49741,7 +49744,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1835" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49767,7 +49770,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1836" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49793,7 +49796,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1837" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49819,7 +49822,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1838" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49845,7 +49848,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1839" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49871,7 +49874,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1840" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49897,7 +49900,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1841" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49923,7 +49926,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1842" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49949,7 +49952,7 @@
         <v>30</v>
       </c>
       <c r="G1843" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49975,7 +49978,7 @@
         <v>30</v>
       </c>
       <c r="G1844" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50001,7 +50004,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1845" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50027,7 +50030,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1846" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50053,7 +50056,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1847" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50079,7 +50082,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1848" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50105,7 +50108,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1849" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50131,7 +50134,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1850" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50157,7 +50160,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1851" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50183,7 +50186,7 @@
         <v>29</v>
       </c>
       <c r="G1852" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50209,7 +50212,7 @@
         <v>29</v>
       </c>
       <c r="G1853" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50235,7 +50238,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1854" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50261,7 +50264,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1855" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50287,7 +50290,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1856" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50313,7 +50316,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1857" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50339,7 +50342,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1858" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50365,7 +50368,7 @@
         <v>29</v>
       </c>
       <c r="G1859" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50391,7 +50394,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50417,7 +50420,7 @@
         <v>30</v>
       </c>
       <c r="G1861" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50443,7 +50446,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1862" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50469,7 +50472,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1863" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50495,7 +50498,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1864" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50521,7 +50524,7 @@
         <v>27</v>
       </c>
       <c r="G1865" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50547,7 +50550,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1866" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50573,7 +50576,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1867" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50599,7 +50602,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1868" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50625,7 +50628,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1869" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50651,7 +50654,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1870" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50677,7 +50680,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1871" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50703,7 +50706,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1872" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50729,7 +50732,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1873" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50755,7 +50758,7 @@
         <v>27</v>
       </c>
       <c r="G1874" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50781,7 +50784,7 @@
         <v>27</v>
       </c>
       <c r="G1875" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50807,7 +50810,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1876" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50833,7 +50836,7 @@
         <v>27</v>
       </c>
       <c r="G1877" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50859,7 +50862,7 @@
         <v>27</v>
       </c>
       <c r="G1878" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50885,7 +50888,7 @@
         <v>27</v>
       </c>
       <c r="G1879" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50911,7 +50914,7 @@
         <v>27</v>
       </c>
       <c r="G1880" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50937,7 +50940,7 @@
         <v>28</v>
       </c>
       <c r="G1881" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50963,7 +50966,7 @@
         <v>28</v>
       </c>
       <c r="G1882" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50989,7 +50992,7 @@
         <v>28</v>
       </c>
       <c r="G1883" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51015,7 +51018,7 @@
         <v>28</v>
       </c>
       <c r="G1884" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51041,7 +51044,7 @@
         <v>28</v>
       </c>
       <c r="G1885" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51067,7 +51070,7 @@
         <v>28</v>
       </c>
       <c r="G1886" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51093,7 +51096,7 @@
         <v>27</v>
       </c>
       <c r="G1887" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51119,7 +51122,7 @@
         <v>27</v>
       </c>
       <c r="G1888" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51145,7 +51148,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1889" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51171,7 +51174,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1890" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51197,7 +51200,7 @@
         <v>28</v>
       </c>
       <c r="G1891" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51223,7 +51226,7 @@
         <v>28</v>
       </c>
       <c r="G1892" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51249,7 +51252,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1893" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51275,7 +51278,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1894" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51301,7 +51304,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1895" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51327,7 +51330,7 @@
         <v>28</v>
       </c>
       <c r="G1896" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51353,7 +51356,7 @@
         <v>28</v>
       </c>
       <c r="G1897" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51379,7 +51382,7 @@
         <v>28</v>
       </c>
       <c r="G1898" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51405,7 +51408,7 @@
         <v>28</v>
       </c>
       <c r="G1899" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51431,7 +51434,7 @@
         <v>28</v>
       </c>
       <c r="G1900" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51457,7 +51460,7 @@
         <v>28</v>
       </c>
       <c r="G1901" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51483,7 +51486,7 @@
         <v>28</v>
       </c>
       <c r="G1902" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51509,7 +51512,7 @@
         <v>28</v>
       </c>
       <c r="G1903" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51535,7 +51538,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51561,7 +51564,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51587,7 +51590,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51613,7 +51616,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51639,7 +51642,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1908" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51665,7 +51668,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1909" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51691,7 +51694,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1910" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51717,7 +51720,7 @@
         <v>29</v>
       </c>
       <c r="G1911" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51743,7 +51746,7 @@
         <v>29</v>
       </c>
       <c r="G1912" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51769,7 +51772,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1913" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51795,7 +51798,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1914" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51821,7 +51824,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51847,7 +51850,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1916" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51873,7 +51876,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1917" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51899,7 +51902,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1918" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51925,7 +51928,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1919" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51951,7 +51954,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1920" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51977,7 +51980,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1921" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52003,7 +52006,7 @@
         <v>27</v>
       </c>
       <c r="G1922" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52029,7 +52032,7 @@
         <v>27</v>
       </c>
       <c r="G1923" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52055,7 +52058,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1924" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52081,7 +52084,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1925" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52107,7 +52110,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1926" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52133,7 +52136,7 @@
         <v>28</v>
       </c>
       <c r="G1927" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52159,7 +52162,7 @@
         <v>28</v>
       </c>
       <c r="G1928" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52185,7 +52188,7 @@
         <v>28</v>
       </c>
       <c r="G1929" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52211,7 +52214,7 @@
         <v>28</v>
       </c>
       <c r="G1930" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52237,7 +52240,7 @@
         <v>28</v>
       </c>
       <c r="G1931" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52263,7 +52266,7 @@
         <v>28</v>
       </c>
       <c r="G1932" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52289,7 +52292,7 @@
         <v>28</v>
       </c>
       <c r="G1933" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52315,7 +52318,7 @@
         <v>28</v>
       </c>
       <c r="G1934" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52341,7 +52344,7 @@
         <v>28</v>
       </c>
       <c r="G1935" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52367,7 +52370,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1936" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52393,7 +52396,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1937" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52419,7 +52422,7 @@
         <v>28</v>
       </c>
       <c r="G1938" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52445,7 +52448,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1939" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52471,7 +52474,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1940" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52497,7 +52500,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1941" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52523,7 +52526,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1942" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52549,7 +52552,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1943" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52575,7 +52578,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1944" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52601,7 +52604,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1945" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52627,7 +52630,7 @@
         <v>28</v>
       </c>
       <c r="G1946" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52653,7 +52656,7 @@
         <v>28</v>
       </c>
       <c r="G1947" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52679,7 +52682,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1948" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52705,7 +52708,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1949" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52731,7 +52734,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1950" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52757,7 +52760,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1951" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52783,7 +52786,7 @@
         <v>28</v>
       </c>
       <c r="G1952" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52809,7 +52812,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1953" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52835,7 +52838,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1954" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52861,7 +52864,7 @@
         <v>27</v>
       </c>
       <c r="G1955" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52887,7 +52890,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1956" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52913,7 +52916,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1957" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -52939,7 +52942,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1958" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -52965,7 +52968,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1959" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -52991,7 +52994,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1960" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53017,7 +53020,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1961" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53043,7 +53046,7 @@
         <v>28</v>
       </c>
       <c r="G1962" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53069,7 +53072,7 @@
         <v>28</v>
       </c>
       <c r="G1963" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53095,7 +53098,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1964" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53121,7 +53124,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1965" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53147,7 +53150,7 @@
         <v>27</v>
       </c>
       <c r="G1966" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53173,7 +53176,7 @@
         <v>27</v>
       </c>
       <c r="G1967" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53199,7 +53202,7 @@
         <v>27</v>
       </c>
       <c r="G1968" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53225,7 +53228,7 @@
         <v>27</v>
       </c>
       <c r="G1969" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53251,7 +53254,7 @@
         <v>27</v>
       </c>
       <c r="G1970" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53277,7 +53280,7 @@
         <v>27</v>
       </c>
       <c r="G1971" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53303,7 +53306,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1972" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53329,7 +53332,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1973" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53355,7 +53358,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1974" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53381,7 +53384,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1975" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53407,7 +53410,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1976" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53433,7 +53436,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1977" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53459,7 +53462,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1978" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53485,7 +53488,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1979" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53511,7 +53514,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1980" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53537,7 +53540,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1981" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53563,7 +53566,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1982" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53589,7 +53592,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1983" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53615,7 +53618,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1984" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53641,7 +53644,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1985" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53667,7 +53670,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1986" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53693,7 +53696,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1987" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53719,7 +53722,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1988" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53745,7 +53748,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1989" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53771,7 +53774,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1990" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53797,7 +53800,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1991" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53823,7 +53826,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1992" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53849,7 +53852,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1993" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53875,7 +53878,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1994" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53901,7 +53904,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1995" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -53927,7 +53930,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1996" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -53953,7 +53956,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1997" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -53979,7 +53982,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1998" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54005,7 +54008,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1999" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54031,7 +54034,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2000" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54057,7 +54060,7 @@
         <v>25</v>
       </c>
       <c r="G2001" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54083,7 +54086,7 @@
         <v>25</v>
       </c>
       <c r="G2002" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54109,7 +54112,7 @@
         <v>25</v>
       </c>
       <c r="G2003" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54135,7 +54138,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2004" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54161,7 +54164,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2005" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54187,7 +54190,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G2006" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54213,7 +54216,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G2007" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54239,7 +54242,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G2008" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54265,7 +54268,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G2009" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54291,7 +54294,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G2010" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54317,7 +54320,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G2011" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54343,7 +54346,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G2012" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54369,7 +54372,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G2013" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54395,7 +54398,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2014" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54421,7 +54424,7 @@
         <v>24</v>
       </c>
       <c r="G2015" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54447,7 +54450,7 @@
         <v>24</v>
       </c>
       <c r="G2016" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54473,7 +54476,7 @@
         <v>24</v>
       </c>
       <c r="G2017" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54499,7 +54502,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G2018" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54525,7 +54528,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G2019" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54551,7 +54554,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2020" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54577,7 +54580,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G2021" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54603,7 +54606,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G2022" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54629,7 +54632,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G2023" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54655,7 +54658,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G2024" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54681,7 +54684,7 @@
         <v>24</v>
       </c>
       <c r="G2025" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54707,7 +54710,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G2026" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54733,7 +54736,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2027" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54759,7 +54762,7 @@
         <v>23</v>
       </c>
       <c r="G2028" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54785,7 +54788,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2029" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54811,7 +54814,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2030" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54837,7 +54840,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2031" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54863,7 +54866,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2032" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54889,7 +54892,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2033" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54915,7 +54918,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2034" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -54941,7 +54944,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2035" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -54967,7 +54970,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2036" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -54993,7 +54996,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2037" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55019,7 +55022,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2038" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55045,7 +55048,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2039" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55071,7 +55074,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2040" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55097,7 +55100,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2041" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55123,7 +55126,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G2042" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55149,7 +55152,7 @@
         <v>22</v>
       </c>
       <c r="G2043" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55175,7 +55178,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2044" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55201,7 +55204,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G2045" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55227,7 +55230,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2046" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55253,7 +55256,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2047" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55279,7 +55282,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2048" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55305,7 +55308,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2049" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55331,7 +55334,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2050" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55357,7 +55360,7 @@
         <v>24</v>
       </c>
       <c r="G2051" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55383,7 +55386,7 @@
         <v>24</v>
       </c>
       <c r="G2052" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55409,7 +55412,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G2053" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55435,7 +55438,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G2054" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55461,7 +55464,7 @@
         <v>24</v>
       </c>
       <c r="G2055" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55487,7 +55490,7 @@
         <v>24</v>
       </c>
       <c r="G2056" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55513,7 +55516,7 @@
         <v>24</v>
       </c>
       <c r="G2057" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55539,7 +55542,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2058" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55565,7 +55568,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2059" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55591,7 +55594,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2060" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55617,7 +55620,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2061" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55643,7 +55646,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2062" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55669,7 +55672,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2063" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55695,7 +55698,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2064" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55721,7 +55724,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2065" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55747,7 +55750,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2066" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55773,7 +55776,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2067" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55799,7 +55802,7 @@
         <v>25</v>
       </c>
       <c r="G2068" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55825,7 +55828,7 @@
         <v>25</v>
       </c>
       <c r="G2069" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55851,7 +55854,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2070" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55877,7 +55880,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2071" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55903,7 +55906,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2072" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -55929,7 +55932,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G2073" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -55955,7 +55958,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G2074" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -55981,7 +55984,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2075" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56007,7 +56010,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2076" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56033,7 +56036,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2077" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56059,7 +56062,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2078" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56085,7 +56088,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2079" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56111,7 +56114,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2080" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56137,7 +56140,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2081" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56163,7 +56166,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2082" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56189,7 +56192,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2083" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56215,7 +56218,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2084" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56241,7 +56244,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2085" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56267,7 +56270,7 @@
         <v>25</v>
       </c>
       <c r="G2086" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56293,7 +56296,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2087" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56319,7 +56322,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2088" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56345,7 +56348,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2089" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56371,7 +56374,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2090" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56397,7 +56400,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2091" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56423,7 +56426,7 @@
         <v>25</v>
       </c>
       <c r="G2092" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56449,7 +56452,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2093" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56475,7 +56478,7 @@
         <v>25</v>
       </c>
       <c r="G2094" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56501,7 +56504,7 @@
         <v>25</v>
       </c>
       <c r="G2095" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56527,7 +56530,7 @@
         <v>25</v>
       </c>
       <c r="G2096" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56553,7 +56556,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2097" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56579,7 +56582,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2098" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56605,7 +56608,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2099" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56631,7 +56634,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2100" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56657,7 +56660,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G2101" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56683,7 +56686,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G2102" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56709,7 +56712,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G2103" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56735,7 +56738,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G2104" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56761,7 +56764,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G2105" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56787,7 +56790,7 @@
         <v>32</v>
       </c>
       <c r="G2106" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56813,7 +56816,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G2107" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56839,7 +56842,7 @@
         <v>32</v>
       </c>
       <c r="G2108" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56865,7 +56868,7 @@
         <v>31</v>
       </c>
       <c r="G2109" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56891,7 +56894,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G2110" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56917,7 +56920,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G2111" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -56943,7 +56946,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G2112" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -56969,7 +56972,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G2113" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -56995,7 +56998,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G2114" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57021,7 +57024,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G2115" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57047,7 +57050,7 @@
         <v>31</v>
       </c>
       <c r="G2116" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57073,7 +57076,7 @@
         <v>31</v>
       </c>
       <c r="G2117" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57099,7 +57102,7 @@
         <v>31</v>
       </c>
       <c r="G2118" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57125,7 +57128,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G2119" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57151,7 +57154,7 @@
         <v>30</v>
       </c>
       <c r="G2120" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57177,7 +57180,7 @@
         <v>30</v>
       </c>
       <c r="G2121" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57203,7 +57206,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2122" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57229,7 +57232,7 @@
         <v>29</v>
       </c>
       <c r="G2123" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57255,7 +57258,7 @@
         <v>29</v>
       </c>
       <c r="G2124" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57281,7 +57284,7 @@
         <v>29</v>
       </c>
       <c r="G2125" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57307,7 +57310,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G2126" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57333,7 +57336,7 @@
         <v>29</v>
       </c>
       <c r="G2127" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57359,7 +57362,7 @@
         <v>29</v>
       </c>
       <c r="G2128" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57385,7 +57388,7 @@
         <v>29</v>
       </c>
       <c r="G2129" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57411,7 +57414,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2130" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57437,7 +57440,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2131" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57463,7 +57466,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2132" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57489,7 +57492,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G2133" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57515,7 +57518,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G2134" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57541,7 +57544,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G2135" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57567,7 +57570,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G2136" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57593,7 +57596,7 @@
         <v>31</v>
       </c>
       <c r="G2137" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57619,7 +57622,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G2138" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57645,7 +57648,7 @@
         <v>30</v>
       </c>
       <c r="G2139" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57671,7 +57674,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G2140" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57697,7 +57700,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G2141" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57723,7 +57726,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G2142" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57749,7 +57752,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G2143" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57775,7 +57778,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G2144" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57801,7 +57804,7 @@
         <v>31</v>
       </c>
       <c r="G2145" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57827,7 +57830,7 @@
         <v>31</v>
       </c>
       <c r="G2146" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57853,7 +57856,7 @@
         <v>31</v>
       </c>
       <c r="G2147" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57879,7 +57882,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G2148" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57905,7 +57908,7 @@
         <v>32</v>
       </c>
       <c r="G2149" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -57931,7 +57934,7 @@
         <v>32</v>
       </c>
       <c r="G2150" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -57957,7 +57960,7 @@
         <v>32</v>
       </c>
       <c r="G2151" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -57983,7 +57986,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G2152" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58009,7 +58012,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G2153" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58035,7 +58038,7 @@
         <v>34</v>
       </c>
       <c r="G2154" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58061,7 +58064,7 @@
         <v>34</v>
       </c>
       <c r="G2155" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58087,7 +58090,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G2156" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -58113,7 +58116,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G2157" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -58139,7 +58142,7 @@
         <v>39</v>
       </c>
       <c r="G2158" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58165,7 +58168,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2159" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58191,7 +58194,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2160" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58217,7 +58220,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2161" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58243,7 +58246,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2162" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58269,7 +58272,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2163" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58295,7 +58298,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2164" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -58321,7 +58324,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2165" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58347,7 +58350,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2166" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58373,7 +58376,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G2167" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58399,7 +58402,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G2168" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58425,7 +58428,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2169" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58451,7 +58454,7 @@
         <v>40</v>
       </c>
       <c r="G2170" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58477,7 +58480,7 @@
         <v>40</v>
       </c>
       <c r="G2171" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58503,7 +58506,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2172" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58529,7 +58532,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2173" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58555,7 +58558,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G2174" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58581,7 +58584,7 @@
         <v>38</v>
       </c>
       <c r="G2175" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58607,7 +58610,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G2176" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58633,7 +58636,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G2177" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58659,7 +58662,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G2178" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58685,7 +58688,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G2179" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58711,7 +58714,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G2180" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58737,7 +58740,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G2181" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58763,7 +58766,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2182" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58789,7 +58792,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2183" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58815,7 +58818,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2184" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58841,7 +58844,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2185" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58867,7 +58870,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2186" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58893,7 +58896,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2187" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58919,7 +58922,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2188" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -58945,7 +58948,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2189" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -58971,7 +58974,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2190" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -58997,7 +59000,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2191" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59023,7 +59026,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2192" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59049,7 +59052,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2193" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59075,7 +59078,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2194" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59101,7 +59104,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G2195" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -59127,7 +59130,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G2196" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59153,7 +59156,7 @@
         <v>40</v>
       </c>
       <c r="G2197" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59179,7 +59182,7 @@
         <v>40</v>
       </c>
       <c r="G2198" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59205,7 +59208,7 @@
         <v>40</v>
       </c>
       <c r="G2199" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59231,7 +59234,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G2200" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59257,7 +59260,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G2201" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59283,7 +59286,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G2202" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59309,7 +59312,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G2203" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59335,7 +59338,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G2204" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59361,7 +59364,7 @@
         <v>44</v>
       </c>
       <c r="G2205" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59387,7 +59390,7 @@
         <v>44</v>
       </c>
       <c r="G2206" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59413,7 +59416,7 @@
         <v>44</v>
       </c>
       <c r="G2207" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59439,7 +59442,7 @@
         <v>44.5999984741211</v>
       </c>
       <c r="G2208" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59465,7 +59468,7 @@
         <v>44</v>
       </c>
       <c r="G2209" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59491,7 +59494,7 @@
         <v>44</v>
       </c>
       <c r="G2210" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59517,7 +59520,7 @@
         <v>44</v>
       </c>
       <c r="G2211" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59543,7 +59546,7 @@
         <v>44</v>
       </c>
       <c r="G2212" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59569,7 +59572,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2213" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59595,7 +59598,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2214" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59621,7 +59624,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2215" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59647,7 +59650,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2216" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59673,7 +59676,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2217" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59699,7 +59702,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2218" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59725,7 +59728,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G2219" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59751,7 +59754,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G2220" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59777,7 +59780,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G2221" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59803,7 +59806,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2222" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59829,7 +59832,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2223" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59855,7 +59858,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2224" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59881,7 +59884,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2225" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59907,7 +59910,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G2226" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -59933,7 +59936,7 @@
         <v>39</v>
       </c>
       <c r="G2227" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -59959,7 +59962,7 @@
         <v>39</v>
       </c>
       <c r="G2228" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -59985,7 +59988,7 @@
         <v>39</v>
       </c>
       <c r="G2229" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60011,7 +60014,7 @@
         <v>39</v>
       </c>
       <c r="G2230" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60037,7 +60040,7 @@
         <v>39</v>
       </c>
       <c r="G2231" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60063,7 +60066,7 @@
         <v>39</v>
       </c>
       <c r="G2232" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60089,7 +60092,7 @@
         <v>39</v>
       </c>
       <c r="G2233" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60115,7 +60118,7 @@
         <v>37</v>
       </c>
       <c r="G2234" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60141,7 +60144,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2235" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60167,7 +60170,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G2236" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60193,7 +60196,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2237" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60219,7 +60222,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2238" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60245,7 +60248,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G2239" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60271,7 +60274,7 @@
         <v>38</v>
       </c>
       <c r="G2240" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60297,7 +60300,7 @@
         <v>39</v>
       </c>
       <c r="G2241" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60323,7 +60326,7 @@
         <v>42</v>
       </c>
       <c r="G2242" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60349,7 +60352,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G2243" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60375,7 +60378,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G2244" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60401,7 +60404,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G2245" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60427,7 +60430,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G2246" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60453,7 +60456,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G2247" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60479,7 +60482,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G2248" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60505,7 +60508,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G2249" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60531,7 +60534,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G2250" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60557,7 +60560,7 @@
         <v>41</v>
       </c>
       <c r="G2251" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60583,7 +60586,7 @@
         <v>41</v>
       </c>
       <c r="G2252" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60609,7 +60612,7 @@
         <v>40</v>
       </c>
       <c r="G2253" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60635,7 +60638,7 @@
         <v>40</v>
       </c>
       <c r="G2254" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60661,7 +60664,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G2255" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60687,7 +60690,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2256" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60713,7 +60716,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2257" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60739,7 +60742,7 @@
         <v>38</v>
       </c>
       <c r="G2258" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60765,7 +60768,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G2259" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60791,7 +60794,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G2260" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60817,7 +60820,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2261" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60843,7 +60846,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2262" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60869,7 +60872,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G2263" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60895,7 +60898,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2264" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60921,7 +60924,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2265" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -60947,7 +60950,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2266" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -60973,7 +60976,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2267" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -60999,7 +61002,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2268" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61025,7 +61028,7 @@
         <v>40</v>
       </c>
       <c r="G2269" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61051,7 +61054,7 @@
         <v>40</v>
       </c>
       <c r="G2270" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -61077,7 +61080,7 @@
         <v>40</v>
       </c>
       <c r="G2271" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61103,7 +61106,7 @@
         <v>40</v>
       </c>
       <c r="G2272" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61129,7 +61132,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G2273" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61155,7 +61158,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2274" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61181,7 +61184,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G2275" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61207,7 +61210,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2276" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61233,7 +61236,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G2277" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61259,7 +61262,7 @@
         <v>38</v>
       </c>
       <c r="G2278" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61285,7 +61288,7 @@
         <v>38</v>
       </c>
       <c r="G2279" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61311,7 +61314,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G2280" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61337,7 +61340,7 @@
         <v>38</v>
       </c>
       <c r="G2281" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61363,7 +61366,7 @@
         <v>38</v>
       </c>
       <c r="G2282" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61389,7 +61392,7 @@
         <v>38</v>
       </c>
       <c r="G2283" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61415,7 +61418,7 @@
         <v>38</v>
       </c>
       <c r="G2284" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61441,7 +61444,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G2285" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61467,7 +61470,7 @@
         <v>37</v>
       </c>
       <c r="G2286" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61493,7 +61496,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G2287" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61519,7 +61522,7 @@
         <v>37</v>
       </c>
       <c r="G2288" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61545,7 +61548,7 @@
         <v>38</v>
       </c>
       <c r="G2289" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61571,7 +61574,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G2290" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61597,7 +61600,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G2291" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61623,7 +61626,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G2292" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61649,7 +61652,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G2293" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61675,7 +61678,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G2294" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61701,7 +61704,7 @@
         <v>38</v>
       </c>
       <c r="G2295" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61727,7 +61730,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G2296" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61753,7 +61756,7 @@
         <v>37</v>
       </c>
       <c r="G2297" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61779,7 +61782,7 @@
         <v>37</v>
       </c>
       <c r="G2298" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61805,7 +61808,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2299" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61831,7 +61834,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2300" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61857,7 +61860,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2301" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61883,7 +61886,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G2302" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61909,7 +61912,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2303" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -61935,7 +61938,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2304" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -61961,7 +61964,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2305" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">2.42625856399536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43408513069153</t>
+    <t xml:space="preserve">2.43408489227295</t>
   </si>
   <si>
     <t xml:space="preserve">2.41060543060303</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">2.45756506919861</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39495205879211</t>
+    <t xml:space="preserve">2.39495182037354</t>
   </si>
   <si>
     <t xml:space="preserve">2.33233904838562</t>
@@ -68,31 +68,31 @@
     <t xml:space="preserve">2.3558189868927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37147235870361</t>
+    <t xml:space="preserve">2.37147212028503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50452518463135</t>
+    <t xml:space="preserve">2.50452494621277</t>
   </si>
   <si>
     <t xml:space="preserve">2.36364531517029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44973874092102</t>
+    <t xml:space="preserve">2.4497389793396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37303733825684</t>
+    <t xml:space="preserve">2.37303781509399</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34955739974976</t>
+    <t xml:space="preserve">2.34955763816833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46382617950439</t>
+    <t xml:space="preserve">2.46382665634155</t>
   </si>
   <si>
     <t xml:space="preserve">2.38712525367737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45443439483643</t>
+    <t xml:space="preserve">2.45443415641785</t>
   </si>
   <si>
     <t xml:space="preserve">2.34799194335938</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">2.48104524612427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37929844856262</t>
+    <t xml:space="preserve">2.37929821014404</t>
   </si>
   <si>
     <t xml:space="preserve">2.38556027412415</t>
@@ -110,16 +110,16 @@
     <t xml:space="preserve">2.4419116973877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78002285957336</t>
+    <t xml:space="preserve">2.78002262115479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36702060699463</t>
+    <t xml:space="preserve">3.36702036857605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62529993057251</t>
+    <t xml:space="preserve">3.62530040740967</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31066942214966</t>
+    <t xml:space="preserve">3.3106689453125</t>
   </si>
   <si>
     <t xml:space="preserve">3.25588226318359</t>
@@ -128,16 +128,16 @@
     <t xml:space="preserve">3.20266127586365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0523898601532</t>
+    <t xml:space="preserve">3.05239009857178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09152293205261</t>
+    <t xml:space="preserve">3.09152340888977</t>
   </si>
   <si>
     <t xml:space="preserve">3.04456329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03673696517944</t>
+    <t xml:space="preserve">3.03673648834229</t>
   </si>
   <si>
     <t xml:space="preserve">3.03830170631409</t>
@@ -146,25 +146,25 @@
     <t xml:space="preserve">3.15413618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30910325050354</t>
+    <t xml:space="preserve">3.3091037273407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30284214019775</t>
+    <t xml:space="preserve">3.30284190177917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3576283454895</t>
+    <t xml:space="preserve">3.35762858390808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57677531242371</t>
+    <t xml:space="preserve">3.57677483558655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52198767662048</t>
+    <t xml:space="preserve">3.52198839187622</t>
   </si>
   <si>
     <t xml:space="preserve">3.40458846092224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5924277305603</t>
+    <t xml:space="preserve">3.59242796897888</t>
   </si>
   <si>
     <t xml:space="preserve">3.58460116386414</t>
@@ -173,28 +173,28 @@
     <t xml:space="preserve">3.6785204410553</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60025405883789</t>
+    <t xml:space="preserve">3.60025453567505</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59555864334106</t>
+    <t xml:space="preserve">3.59555840492249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632207870483</t>
+    <t xml:space="preserve">3.32632231712341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29501533508301</t>
+    <t xml:space="preserve">3.29501557350159</t>
   </si>
   <si>
     <t xml:space="preserve">3.37484693527222</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38267421722412</t>
+    <t xml:space="preserve">3.38267397880554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44372200965881</t>
+    <t xml:space="preserve">3.44372224807739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59086275100708</t>
+    <t xml:space="preserve">3.5908625125885</t>
   </si>
   <si>
     <t xml:space="preserve">3.47972440719604</t>
@@ -206,34 +206,34 @@
     <t xml:space="preserve">3.41241526603699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24022889137268</t>
+    <t xml:space="preserve">3.24022936820984</t>
   </si>
   <si>
     <t xml:space="preserve">3.21048784255981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28405857086182</t>
+    <t xml:space="preserve">3.28405809402466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16196250915527</t>
+    <t xml:space="preserve">3.16196274757385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20892238616943</t>
+    <t xml:space="preserve">3.20892262458801</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13848328590393</t>
+    <t xml:space="preserve">3.13848280906677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23240303993225</t>
+    <t xml:space="preserve">3.23240280151367</t>
   </si>
   <si>
     <t xml:space="preserve">3.31849527359009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27623176574707</t>
+    <t xml:space="preserve">3.27623200416565</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18857336044312</t>
+    <t xml:space="preserve">3.18857312202454</t>
   </si>
   <si>
     <t xml:space="preserve">3.14317846298218</t>
@@ -242,22 +242,22 @@
     <t xml:space="preserve">3.11500287055969</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00073385238647</t>
+    <t xml:space="preserve">3.00073409080505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97412300109863</t>
+    <t xml:space="preserve">2.97412323951721</t>
   </si>
   <si>
     <t xml:space="preserve">3.06021642684937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90368342399597</t>
+    <t xml:space="preserve">2.90368366241455</t>
   </si>
   <si>
     <t xml:space="preserve">2.8958568572998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82854795455933</t>
+    <t xml:space="preserve">2.82854771614075</t>
   </si>
   <si>
     <t xml:space="preserve">2.83637452125549</t>
@@ -266,37 +266,37 @@
     <t xml:space="preserve">2.90994501113892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491255760193</t>
+    <t xml:space="preserve">3.06491231918335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13065624237061</t>
+    <t xml:space="preserve">3.13065600395203</t>
   </si>
   <si>
     <t xml:space="preserve">3.14474415779114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21361804008484</t>
+    <t xml:space="preserve">3.21361827850342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28562378883362</t>
+    <t xml:space="preserve">3.28562355041504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35919404029846</t>
+    <t xml:space="preserve">3.35919380187988</t>
   </si>
   <si>
     <t xml:space="preserve">3.36388993263245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91332101821899</t>
+    <t xml:space="preserve">3.91332030296326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34378528594971</t>
+    <t xml:space="preserve">4.34378576278687</t>
   </si>
   <si>
     <t xml:space="preserve">4.79381704330444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47864818572998</t>
+    <t xml:space="preserve">5.47864770889282</t>
   </si>
   <si>
     <t xml:space="preserve">6.09303951263428</t>
@@ -305,43 +305,43 @@
     <t xml:space="preserve">5.41603517532349</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71344757080078</t>
+    <t xml:space="preserve">5.71344709396362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56865406036377</t>
+    <t xml:space="preserve">5.56865453720093</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41994857788086</t>
+    <t xml:space="preserve">5.41994905471802</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16558265686035</t>
+    <t xml:space="preserve">5.16558218002319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94643640518188</t>
+    <t xml:space="preserve">4.94643688201904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70381164550781</t>
+    <t xml:space="preserve">4.70381116867065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67641687393188</t>
+    <t xml:space="preserve">4.67641735076904</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0090503692627</t>
+    <t xml:space="preserve">5.00904989242554</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55691432952881</t>
+    <t xml:space="preserve">5.55691480636597</t>
   </si>
   <si>
     <t xml:space="preserve">5.30646276473999</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22428226470947</t>
+    <t xml:space="preserve">5.22428274154663</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19688940048218</t>
+    <t xml:space="preserve">5.19688987731934</t>
   </si>
   <si>
-    <t xml:space="preserve">5.32211542129517</t>
+    <t xml:space="preserve">5.32211494445801</t>
   </si>
   <si>
     <t xml:space="preserve">5.47082138061523</t>
@@ -350,10 +350,10 @@
     <t xml:space="preserve">5.36907577514648</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29080963134766</t>
+    <t xml:space="preserve">5.2908091545105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1734094619751</t>
+    <t xml:space="preserve">5.17340993881226</t>
   </si>
   <si>
     <t xml:space="preserve">5.09514331817627</t>
@@ -368,52 +368,52 @@
     <t xml:space="preserve">4.99339628219604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15384244918823</t>
+    <t xml:space="preserve">5.15384292602539</t>
   </si>
   <si>
     <t xml:space="preserve">4.9855694770813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75859689712524</t>
+    <t xml:space="preserve">4.75859642028809</t>
   </si>
   <si>
     <t xml:space="preserve">4.77033710479736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86425685882568</t>
+    <t xml:space="preserve">4.86425733566284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88773632049561</t>
+    <t xml:space="preserve">4.88773727416992</t>
   </si>
   <si>
     <t xml:space="preserve">4.83295059204102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75468397140503</t>
+    <t xml:space="preserve">4.75468349456787</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82903671264648</t>
+    <t xml:space="preserve">4.8290376663208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72337770462036</t>
+    <t xml:space="preserve">4.7233772277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68815803527832</t>
+    <t xml:space="preserve">4.68815755844116</t>
   </si>
   <si>
     <t xml:space="preserve">4.78207778930664</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87599754333496</t>
+    <t xml:space="preserve">4.87599658966064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03644275665283</t>
+    <t xml:space="preserve">5.03644323348999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92687082290649</t>
+    <t xml:space="preserve">4.92687034606934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81338405609131</t>
+    <t xml:space="preserve">4.81338357925415</t>
   </si>
   <si>
     <t xml:space="preserve">4.86034393310547</t>
@@ -443,22 +443,22 @@
     <t xml:space="preserve">5.43951511383057</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28298234939575</t>
+    <t xml:space="preserve">5.28298187255859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384927749634</t>
+    <t xml:space="preserve">5.24384880065918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36124897003174</t>
+    <t xml:space="preserve">5.36124801635742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40038204193115</t>
+    <t xml:space="preserve">5.40038156509399</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51778173446655</t>
+    <t xml:space="preserve">5.51778125762939</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63518095016479</t>
+    <t xml:space="preserve">5.63518047332764</t>
   </si>
   <si>
     <t xml:space="preserve">4.96991682052612</t>
@@ -470,40 +470,40 @@
     <t xml:space="preserve">4.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1264500617981</t>
+    <t xml:space="preserve">5.12644958496094</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04818344116211</t>
+    <t xml:space="preserve">5.04818296432495</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08731651306152</t>
+    <t xml:space="preserve">5.08731603622437</t>
   </si>
   <si>
     <t xml:space="preserve">5.59604787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2615966796875</t>
+    <t xml:space="preserve">5.26159715652466</t>
   </si>
   <si>
     <t xml:space="preserve">5.42104005813599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34131860733032</t>
+    <t xml:space="preserve">5.34131813049316</t>
   </si>
   <si>
     <t xml:space="preserve">5.22173738479614</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14201545715332</t>
+    <t xml:space="preserve">5.14201593399048</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1021556854248</t>
+    <t xml:space="preserve">5.10215520858765</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18187618255615</t>
+    <t xml:space="preserve">5.18187570571899</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38117933273315</t>
+    <t xml:space="preserve">5.381178855896</t>
   </si>
   <si>
     <t xml:space="preserve">5.30145788192749</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">4.90285205841064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50076103210449</t>
+    <t xml:space="preserve">5.50076055526733</t>
   </si>
   <si>
     <t xml:space="preserve">5.46090030670166</t>
@@ -521,22 +521,22 @@
     <t xml:space="preserve">5.580482006073</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54062175750732</t>
+    <t xml:space="preserve">5.54062128067017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62034273147583</t>
+    <t xml:space="preserve">5.62034225463867</t>
   </si>
   <si>
     <t xml:space="preserve">4.94271278381348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98257303237915</t>
+    <t xml:space="preserve">4.98257350921631</t>
   </si>
   <si>
     <t xml:space="preserve">4.82313060760498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06229400634766</t>
+    <t xml:space="preserve">5.06229448318481</t>
   </si>
   <si>
     <t xml:space="preserve">5.02243423461914</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">4.74340963363647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78327083587646</t>
+    <t xml:space="preserve">4.78327035903931</t>
   </si>
   <si>
     <t xml:space="preserve">4.86299133300781</t>
@@ -560,64 +560,64 @@
     <t xml:space="preserve">5.70006370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66020345687866</t>
+    <t xml:space="preserve">5.6602029800415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77978467941284</t>
+    <t xml:space="preserve">5.77978515625</t>
   </si>
   <si>
     <t xml:space="preserve">5.85950613021851</t>
   </si>
   <si>
-    <t xml:space="preserve">5.979088306427</t>
+    <t xml:space="preserve">5.97908782958984</t>
   </si>
   <si>
     <t xml:space="preserve">6.29797315597534</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13852977752686</t>
+    <t xml:space="preserve">6.13853073120117</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05880832672119</t>
+    <t xml:space="preserve">6.05880928039551</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825122833252</t>
+    <t xml:space="preserve">6.21825170516968</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0986704826355</t>
+    <t xml:space="preserve">6.09867000579834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38518476486206</t>
+    <t xml:space="preserve">6.3851842880249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25998497009277</t>
+    <t xml:space="preserve">6.25998449325562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30171871185303</t>
+    <t xml:space="preserve">6.30171823501587</t>
   </si>
   <si>
     <t xml:space="preserve">6.17651844024658</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42691707611084</t>
+    <t xml:space="preserve">6.426917552948</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34345149993896</t>
+    <t xml:space="preserve">6.34345102310181</t>
   </si>
   <si>
     <t xml:space="preserve">6.46865081787109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96785259246826</t>
+    <t xml:space="preserve">5.9678521156311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00958585739136</t>
+    <t xml:space="preserve">6.00958490371704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13478469848633</t>
+    <t xml:space="preserve">6.13478517532349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05131912231445</t>
+    <t xml:space="preserve">6.05131864547729</t>
   </si>
   <si>
     <t xml:space="preserve">5.92611885070801</t>
@@ -626,7 +626,10 @@
     <t xml:space="preserve">6.09305191040039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51038408279419</t>
+    <t xml:space="preserve">6.21825122833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51038455963135</t>
   </si>
   <si>
     <t xml:space="preserve">5.84265232086182</t>
@@ -635,7 +638,7 @@
     <t xml:space="preserve">5.88438558578491</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05291652679443</t>
+    <t xml:space="preserve">7.05291604995728</t>
   </si>
   <si>
     <t xml:space="preserve">8.09624671936035</t>
@@ -650,61 +653,61 @@
     <t xml:space="preserve">7.55371475219727</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3450493812561</t>
+    <t xml:space="preserve">7.34504985809326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17811632156372</t>
+    <t xml:space="preserve">7.17811679840088</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51198244094849</t>
+    <t xml:space="preserve">7.51198148727417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47024822235107</t>
+    <t xml:space="preserve">7.47024869918823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30331611633301</t>
+    <t xml:space="preserve">7.30331563949585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851495742798</t>
+    <t xml:space="preserve">7.42851448059082</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26158142089844</t>
+    <t xml:space="preserve">7.2615818977356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38678169250488</t>
+    <t xml:space="preserve">7.38678216934204</t>
   </si>
   <si>
     <t xml:space="preserve">6.96944999694824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21984767913818</t>
+    <t xml:space="preserve">7.2198486328125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544897079468</t>
+    <t xml:space="preserve">7.5954475402832</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76238107681274</t>
+    <t xml:space="preserve">7.76238059997559</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84584665298462</t>
+    <t xml:space="preserve">7.84584617614746</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67891359329224</t>
+    <t xml:space="preserve">7.67891454696655</t>
   </si>
   <si>
     <t xml:space="preserve">7.01118278503418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09464883804321</t>
+    <t xml:space="preserve">7.09464931488037</t>
   </si>
   <si>
     <t xml:space="preserve">6.92771625518799</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76078367233276</t>
+    <t xml:space="preserve">6.76078414916992</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80251598358154</t>
+    <t xml:space="preserve">6.8025164604187</t>
   </si>
   <si>
     <t xml:space="preserve">6.71905040740967</t>
@@ -713,16 +716,16 @@
     <t xml:space="preserve">6.8442497253418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59385061264038</t>
+    <t xml:space="preserve">6.59385108947754</t>
   </si>
   <si>
     <t xml:space="preserve">6.67731714248657</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55211734771729</t>
+    <t xml:space="preserve">6.55211782455444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75918626785278</t>
+    <t xml:space="preserve">5.75918579101562</t>
   </si>
   <si>
     <t xml:space="preserve">5.71745252609253</t>
@@ -731,28 +734,28 @@
     <t xml:space="preserve">5.80091905593872</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67571973800659</t>
+    <t xml:space="preserve">5.67571926116943</t>
   </si>
   <si>
     <t xml:space="preserve">5.59225273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6339864730835</t>
+    <t xml:space="preserve">5.63398599624634</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46705341339111</t>
+    <t xml:space="preserve">5.46705436706543</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55051946640015</t>
+    <t xml:space="preserve">5.5505199432373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1749210357666</t>
+    <t xml:space="preserve">5.17492055892944</t>
   </si>
   <si>
     <t xml:space="preserve">5.25838756561279</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38358640670776</t>
+    <t xml:space="preserve">5.38358736038208</t>
   </si>
   <si>
     <t xml:space="preserve">7.13638257980347</t>
@@ -761,34 +764,34 @@
     <t xml:space="preserve">7.4724702835083</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25269269943237</t>
+    <t xml:space="preserve">7.25269317626953</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2966480255127</t>
+    <t xml:space="preserve">7.29664850234985</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20873641967773</t>
+    <t xml:space="preserve">7.20873689651489</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1647801399231</t>
+    <t xml:space="preserve">7.16478061676025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07686948776245</t>
+    <t xml:space="preserve">7.07686901092529</t>
   </si>
   <si>
     <t xml:space="preserve">6.98895835876465</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03291368484497</t>
+    <t xml:space="preserve">7.03291320800781</t>
   </si>
   <si>
     <t xml:space="preserve">6.94500255584717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85709095001221</t>
+    <t xml:space="preserve">6.85709047317505</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72522401809692</t>
+    <t xml:space="preserve">6.72522354125977</t>
   </si>
   <si>
     <t xml:space="preserve">6.81313514709473</t>
@@ -806,52 +809,49 @@
     <t xml:space="preserve">7.12082529067993</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34060382843018</t>
+    <t xml:space="preserve">7.34060430526733</t>
   </si>
   <si>
     <t xml:space="preserve">7.51642656326294</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56038284301758</t>
+    <t xml:space="preserve">7.56038236618042</t>
   </si>
   <si>
     <t xml:space="preserve">7.42851543426514</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73620557785034</t>
+    <t xml:space="preserve">7.7362060546875</t>
   </si>
   <si>
     <t xml:space="preserve">7.69224977493286</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829254150391</t>
+    <t xml:space="preserve">7.64829397201538</t>
   </si>
   <si>
     <t xml:space="preserve">7.78247404098511</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82720184326172</t>
+    <t xml:space="preserve">7.8272008895874</t>
   </si>
   <si>
     <t xml:space="preserve">7.73774671554565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69302082061768</t>
+    <t xml:space="preserve">7.69302129745483</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829349517822</t>
+    <t xml:space="preserve">7.60356569290161</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60356616973877</t>
+    <t xml:space="preserve">7.91665506362915</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91665458679199</t>
+    <t xml:space="preserve">7.87192916870117</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87192869186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96138143539429</t>
+    <t xml:space="preserve">7.96138095855713</t>
   </si>
   <si>
     <t xml:space="preserve">8.2297420501709</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">8.27446937561035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45337772369385</t>
+    <t xml:space="preserve">8.45337677001953</t>
   </si>
   <si>
     <t xml:space="preserve">8.67701148986816</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">9.03482627868652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3766326904297</t>
+    <t xml:space="preserve">10.376633644104</t>
   </si>
   <si>
     <t xml:space="preserve">11.4500770568848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7344465255737</t>
+    <t xml:space="preserve">10.734447479248</t>
   </si>
   <si>
     <t xml:space="preserve">11.0922622680664</t>
@@ -929,16 +929,16 @@
     <t xml:space="preserve">11.2711696624756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5555400848389</t>
+    <t xml:space="preserve">10.5555391311646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2871789932251</t>
+    <t xml:space="preserve">10.2871780395508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0028085708618</t>
+    <t xml:space="preserve">11.0028076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6449928283691</t>
+    <t xml:space="preserve">10.6449937820435</t>
   </si>
   <si>
     <t xml:space="preserve">10.4660863876343</t>
@@ -953,16 +953,16 @@
     <t xml:space="preserve">9.75045585632324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0188159942627</t>
+    <t xml:space="preserve">10.018816947937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6129751205444</t>
+    <t xml:space="preserve">12.6129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9707908630371</t>
+    <t xml:space="preserve">12.9707899093628</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0442352294922</t>
+    <t xml:space="preserve">14.0442342758179</t>
   </si>
   <si>
     <t xml:space="preserve">13.7758731842041</t>
@@ -971,13 +971,13 @@
     <t xml:space="preserve">13.5075130462646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2391510009766</t>
+    <t xml:space="preserve">13.2391519546509</t>
   </si>
   <si>
     <t xml:space="preserve">13.0602445602417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4180593490601</t>
+    <t xml:space="preserve">13.4180603027344</t>
   </si>
   <si>
     <t xml:space="preserve">12.8813362121582</t>
@@ -986,55 +986,55 @@
     <t xml:space="preserve">12.7918825149536</t>
   </si>
   <si>
-    <t xml:space="preserve">12.702428817749</t>
+    <t xml:space="preserve">12.7024297714233</t>
   </si>
   <si>
     <t xml:space="preserve">13.149697303772</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3286046981812</t>
+    <t xml:space="preserve">13.3286037445068</t>
   </si>
   <si>
     <t xml:space="preserve">13.9547815322876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5969657897949</t>
+    <t xml:space="preserve">13.5969648361206</t>
   </si>
   <si>
     <t xml:space="preserve">13.6864204406738</t>
   </si>
   <si>
-    <t xml:space="preserve">13.865327835083</t>
+    <t xml:space="preserve">13.8653287887573</t>
   </si>
   <si>
     <t xml:space="preserve">14.4020500183105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2965869903564</t>
+    <t xml:space="preserve">15.2965879440308</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2071323394775</t>
+    <t xml:space="preserve">15.2071313858032</t>
   </si>
   <si>
     <t xml:space="preserve">14.5809564590454</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7598657608032</t>
+    <t xml:space="preserve">14.7598648071289</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4915046691895</t>
+    <t xml:space="preserve">14.4915037155151</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5400886535645</t>
+    <t xml:space="preserve">14.5400876998901</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3560371398926</t>
+    <t xml:space="preserve">14.3560361862183</t>
   </si>
   <si>
     <t xml:space="preserve">14.2640104293823</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1719837188721</t>
+    <t xml:space="preserve">14.1719846725464</t>
   </si>
   <si>
     <t xml:space="preserve">14.8161659240723</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">14.6321144104004</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3683214187622</t>
+    <t xml:space="preserve">15.3683223724365</t>
   </si>
   <si>
     <t xml:space="preserve">15.5523738861084</t>
@@ -1058,7 +1058,7 @@
     <t xml:space="preserve">15.9204750061035</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2088413238525</t>
+    <t xml:space="preserve">17.2088394165039</t>
   </si>
   <si>
     <t xml:space="preserve">17.3008632659912</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">18.4051742553711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1413822174072</t>
+    <t xml:space="preserve">19.1413803100586</t>
   </si>
   <si>
     <t xml:space="preserve">19.6935367584229</t>
@@ -1094,10 +1094,10 @@
     <t xml:space="preserve">22.2702617645264</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8224182128906</t>
+    <t xml:space="preserve">22.822416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6137943267822</t>
+    <t xml:space="preserve">20.6137962341309</t>
   </si>
   <si>
     <t xml:space="preserve">19.3254337310791</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">22.0862102508545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0064697265625</t>
+    <t xml:space="preserve">23.0064678192139</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5586242675781</t>
+    <t xml:space="preserve">23.5586261749268</t>
   </si>
   <si>
     <t xml:space="preserve">23.74267578125</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">24.6629333496094</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8469867706299</t>
+    <t xml:space="preserve">24.8469886779785</t>
   </si>
   <si>
     <t xml:space="preserve">24.2948303222656</t>
@@ -1154,16 +1154,16 @@
     <t xml:space="preserve">27.975866317749</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9206924438477</t>
+    <t xml:space="preserve">30.9206943511963</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0801773071289</t>
+    <t xml:space="preserve">29.0801753997803</t>
   </si>
   <si>
-    <t xml:space="preserve">30.7366428375244</t>
+    <t xml:space="preserve">30.736644744873</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3685417175293</t>
+    <t xml:space="preserve">30.3685398101807</t>
   </si>
   <si>
     <t xml:space="preserve">29.2642288208008</t>
@@ -1175,10 +1175,10 @@
     <t xml:space="preserve">34.2336273193359</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7857818603516</t>
+    <t xml:space="preserve">34.7857780456543</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8655166625977</t>
+    <t xml:space="preserve">33.8655204772949</t>
   </si>
   <si>
     <t xml:space="preserve">33.4974212646484</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">27.7918167114258</t>
   </si>
   <si>
-    <t xml:space="preserve">28.896125793457</t>
+    <t xml:space="preserve">28.8961238861084</t>
   </si>
   <si>
     <t xml:space="preserve">29.4482803344727</t>
@@ -1211,19 +1211,19 @@
     <t xml:space="preserve">28.5280208587646</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7120742797852</t>
+    <t xml:space="preserve">28.7120723724365</t>
   </si>
   <si>
-    <t xml:space="preserve">28.3439674377441</t>
+    <t xml:space="preserve">28.3439693450928</t>
   </si>
   <si>
     <t xml:space="preserve">27.055606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8715553283691</t>
+    <t xml:space="preserve">26.8715572357178</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3991432189941</t>
+    <t xml:space="preserve">25.3991413116455</t>
   </si>
   <si>
     <t xml:space="preserve">25.7672443389893</t>
@@ -1244,13 +1244,13 @@
     <t xml:space="preserve">30.0004329681396</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3931121826172</t>
+    <t xml:space="preserve">32.3931083679199</t>
   </si>
   <si>
     <t xml:space="preserve">32.209056854248</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2887954711914</t>
+    <t xml:space="preserve">31.28879737854</t>
   </si>
   <si>
     <t xml:space="preserve">31.6569023132324</t>
@@ -1262,34 +1262,34 @@
     <t xml:space="preserve">32.0337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5990676879883</t>
+    <t xml:space="preserve">32.5990715026855</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1643753051758</t>
+    <t xml:space="preserve">33.1643714904785</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6568984985352</t>
+    <t xml:space="preserve">31.6569004058838</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4106407165527</t>
+    <t xml:space="preserve">32.4106369018555</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7875061035156</t>
+    <t xml:space="preserve">32.7875022888184</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9759368896484</t>
+    <t xml:space="preserve">32.9759407043457</t>
   </si>
   <si>
     <t xml:space="preserve">30.9031639099121</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8453350067139</t>
+    <t xml:space="preserve">31.8453369140625</t>
   </si>
   <si>
     <t xml:space="preserve">30.714729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5263004302979</t>
+    <t xml:space="preserve">30.5262985229492</t>
   </si>
   <si>
     <t xml:space="preserve">31.2800331115723</t>
@@ -1298,7 +1298,7 @@
     <t xml:space="preserve">30.1494293212891</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3378658294678</t>
+    <t xml:space="preserve">30.3378639221191</t>
   </si>
   <si>
     <t xml:space="preserve">29.395694732666</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">28.2650909423828</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6997871398926</t>
+    <t xml:space="preserve">27.6997890472412</t>
   </si>
   <si>
     <t xml:space="preserve">28.0766563415527</t>
@@ -1337,7 +1337,7 @@
     <t xml:space="preserve">25.2501468658447</t>
   </si>
   <si>
-    <t xml:space="preserve">24.307975769043</t>
+    <t xml:space="preserve">24.3079776763916</t>
   </si>
   <si>
     <t xml:space="preserve">23.9311103820801</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">23.7426776885986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1773738861084</t>
+    <t xml:space="preserve">23.177375793457</t>
   </si>
   <si>
     <t xml:space="preserve">22.6120719909668</t>
@@ -1373,10 +1373,10 @@
     <t xml:space="preserve">22.2352046966553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0467720031738</t>
+    <t xml:space="preserve">22.0467700958252</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8005065917969</t>
+    <t xml:space="preserve">22.8005084991455</t>
   </si>
   <si>
     <t xml:space="preserve">22.988941192627</t>
@@ -1391,19 +1391,19 @@
     <t xml:space="preserve">25.6270160675049</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3807525634766</t>
+    <t xml:space="preserve">26.3807506561279</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1344871520996</t>
+    <t xml:space="preserve">27.134485244751</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9460544586182</t>
+    <t xml:space="preserve">26.9460525512695</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3229217529297</t>
+    <t xml:space="preserve">27.3229198455811</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1923179626465</t>
+    <t xml:space="preserve">26.1923160552979</t>
   </si>
   <si>
     <t xml:space="preserve">26.7576179504395</t>
@@ -18645,7 +18645,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G639" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19165,7 +19165,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G659" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -19191,7 +19191,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G660" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19295,7 +19295,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G664" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19503,7 +19503,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G672" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -19529,7 +19529,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G673" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20023,7 +20023,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G692" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20049,7 +20049,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G693" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20127,7 +20127,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G696" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20153,7 +20153,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G697" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -20283,7 +20283,7 @@
         <v>7</v>
       </c>
       <c r="G702" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -20309,7 +20309,7 @@
         <v>7</v>
       </c>
       <c r="G703" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -20335,7 +20335,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G704" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -20595,7 +20595,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G714" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -20621,7 +20621,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G715" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -20699,7 +20699,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G718" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -20751,7 +20751,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G720" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21011,7 +21011,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G730" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21037,7 +21037,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G731" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21063,7 +21063,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G732" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21089,7 +21089,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G733" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -21349,7 +21349,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G743" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -21375,7 +21375,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G744" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -21401,7 +21401,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G745" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -21427,7 +21427,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G746" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -21453,7 +21453,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G747" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -21479,7 +21479,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G748" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -21505,7 +21505,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G749" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -21531,7 +21531,7 @@
         <v>9</v>
       </c>
       <c r="G750" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -21557,7 +21557,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G751" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -21583,7 +21583,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G752" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -21609,7 +21609,7 @@
         <v>8.75</v>
       </c>
       <c r="G753" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -21635,7 +21635,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G754" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -21661,7 +21661,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G755" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -21687,7 +21687,7 @@
         <v>9</v>
       </c>
       <c r="G756" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -21713,7 +21713,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G757" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -21739,7 +21739,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G758" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -21765,7 +21765,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G759" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -21791,7 +21791,7 @@
         <v>9</v>
       </c>
       <c r="G760" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -21817,7 +21817,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G761" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -21843,7 +21843,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G762" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -21869,7 +21869,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G763" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -21895,7 +21895,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G764" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -21921,7 +21921,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G765" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -21947,7 +21947,7 @@
         <v>9</v>
       </c>
       <c r="G766" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -21973,7 +21973,7 @@
         <v>9</v>
       </c>
       <c r="G767" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -21999,7 +21999,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G768" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22025,7 +22025,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G769" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22051,7 +22051,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G770" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22077,7 +22077,7 @@
         <v>8.75</v>
       </c>
       <c r="G771" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22103,7 +22103,7 @@
         <v>8.75</v>
       </c>
       <c r="G772" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22129,7 +22129,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G773" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22155,7 +22155,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G774" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22181,7 +22181,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G775" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22207,7 +22207,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G776" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22233,7 +22233,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G777" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22259,7 +22259,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G778" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22285,7 +22285,7 @@
         <v>9</v>
       </c>
       <c r="G779" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -22311,7 +22311,7 @@
         <v>9</v>
       </c>
       <c r="G780" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -22337,7 +22337,7 @@
         <v>9</v>
       </c>
       <c r="G781" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -22363,7 +22363,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G782" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -22389,7 +22389,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G783" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -22415,7 +22415,7 @@
         <v>8.75</v>
       </c>
       <c r="G784" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -22441,7 +22441,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G785" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -22467,7 +22467,7 @@
         <v>8.75</v>
       </c>
       <c r="G786" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -22493,7 +22493,7 @@
         <v>8.75</v>
       </c>
       <c r="G787" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -22519,7 +22519,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G788" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -22545,7 +22545,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G789" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -22571,7 +22571,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G790" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -22597,7 +22597,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G791" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -22623,7 +22623,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G792" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -22649,7 +22649,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G793" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -22675,7 +22675,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G794" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -22701,7 +22701,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G795" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -22727,7 +22727,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G796" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -22753,7 +22753,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G797" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -22779,7 +22779,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G798" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -22805,7 +22805,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G799" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -22831,7 +22831,7 @@
         <v>8.75</v>
       </c>
       <c r="G800" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -22857,7 +22857,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G801" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -22883,7 +22883,7 @@
         <v>8.75</v>
       </c>
       <c r="G802" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -22909,7 +22909,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G803" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -22935,7 +22935,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G804" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -22961,7 +22961,7 @@
         <v>8.75</v>
       </c>
       <c r="G805" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -22987,7 +22987,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G806" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23013,7 +23013,7 @@
         <v>8.75</v>
       </c>
       <c r="G807" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23039,7 +23039,7 @@
         <v>8.75</v>
       </c>
       <c r="G808" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23065,7 +23065,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G809" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23091,7 +23091,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G810" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23117,7 +23117,7 @@
         <v>8.5</v>
       </c>
       <c r="G811" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23143,7 +23143,7 @@
         <v>8.5</v>
       </c>
       <c r="G812" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23169,7 +23169,7 @@
         <v>8.5</v>
       </c>
       <c r="G813" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23195,7 +23195,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G814" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23221,7 +23221,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G815" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23247,7 +23247,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G816" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23273,7 +23273,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G817" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23299,7 +23299,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G818" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -23325,7 +23325,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G819" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -23351,7 +23351,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G820" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -23377,7 +23377,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G821" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -23403,7 +23403,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G822" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -23429,7 +23429,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G823" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -23455,7 +23455,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G824" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -23481,7 +23481,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G825" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -23507,7 +23507,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G826" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -23533,7 +23533,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G827" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -23559,7 +23559,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G828" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -23585,7 +23585,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G829" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -23611,7 +23611,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G830" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -23637,7 +23637,7 @@
         <v>9</v>
       </c>
       <c r="G831" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -23663,7 +23663,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G832" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -23689,7 +23689,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G833" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -23715,7 +23715,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G834" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -23741,7 +23741,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G835" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -23767,7 +23767,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G836" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -23793,7 +23793,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G837" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -23819,7 +23819,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G838" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -23845,7 +23845,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G839" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -23871,7 +23871,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G840" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -23897,7 +23897,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G841" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -23923,7 +23923,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G842" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -23949,7 +23949,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G843" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -23975,7 +23975,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G844" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -24001,7 +24001,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G845" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24027,7 +24027,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G846" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24053,7 +24053,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G847" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24079,7 +24079,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G848" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24105,7 +24105,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G849" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24131,7 +24131,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G850" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24157,7 +24157,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G851" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24183,7 +24183,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G852" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24209,7 +24209,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G853" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24235,7 +24235,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G854" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24261,7 +24261,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G855" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24287,7 +24287,7 @@
         <v>8</v>
       </c>
       <c r="G856" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24313,7 +24313,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G857" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24339,7 +24339,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G858" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -24417,7 +24417,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G861" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24495,7 +24495,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G864" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -24937,7 +24937,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G881" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25015,7 +25015,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G884" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25041,7 +25041,7 @@
         <v>7</v>
       </c>
       <c r="G885" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25249,7 +25249,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G893" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -25977,7 +25977,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G921" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26003,7 +26003,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G922" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26029,7 +26029,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G923" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -26055,7 +26055,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G924" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26159,7 +26159,7 @@
         <v>7</v>
       </c>
       <c r="G928" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26185,7 +26185,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G929" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26211,7 +26211,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G930" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26237,7 +26237,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G931" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26263,7 +26263,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G932" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26289,7 +26289,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G933" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26315,7 +26315,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G934" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26341,7 +26341,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G935" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26419,7 +26419,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G938" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26445,7 +26445,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G939" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26705,7 +26705,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G949" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26731,7 +26731,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G950" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26757,7 +26757,7 @@
         <v>7</v>
       </c>
       <c r="G951" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -26783,7 +26783,7 @@
         <v>7</v>
       </c>
       <c r="G952" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26809,7 +26809,7 @@
         <v>7</v>
       </c>
       <c r="G953" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26835,7 +26835,7 @@
         <v>7</v>
       </c>
       <c r="G954" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26861,7 +26861,7 @@
         <v>7</v>
       </c>
       <c r="G955" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26887,7 +26887,7 @@
         <v>7</v>
       </c>
       <c r="G956" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26913,7 +26913,7 @@
         <v>7</v>
       </c>
       <c r="G957" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26939,7 +26939,7 @@
         <v>7</v>
       </c>
       <c r="G958" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26965,7 +26965,7 @@
         <v>7</v>
       </c>
       <c r="G959" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -26991,7 +26991,7 @@
         <v>7</v>
       </c>
       <c r="G960" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27017,7 +27017,7 @@
         <v>7</v>
       </c>
       <c r="G961" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27043,7 +27043,7 @@
         <v>7</v>
       </c>
       <c r="G962" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27069,7 +27069,7 @@
         <v>7</v>
       </c>
       <c r="G963" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27095,7 +27095,7 @@
         <v>7</v>
       </c>
       <c r="G964" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27121,7 +27121,7 @@
         <v>7</v>
       </c>
       <c r="G965" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27147,7 +27147,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G966" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27173,7 +27173,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G967" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27199,7 +27199,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G968" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27225,7 +27225,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G969" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -27251,7 +27251,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G970" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27277,7 +27277,7 @@
         <v>6.75</v>
       </c>
       <c r="G971" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27303,7 +27303,7 @@
         <v>6.75</v>
       </c>
       <c r="G972" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27329,7 +27329,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G973" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27355,7 +27355,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G974" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27381,7 +27381,7 @@
         <v>6.75</v>
       </c>
       <c r="G975" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27407,7 +27407,7 @@
         <v>6.75</v>
       </c>
       <c r="G976" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27433,7 +27433,7 @@
         <v>6.75</v>
       </c>
       <c r="G977" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27459,7 +27459,7 @@
         <v>6.75</v>
       </c>
       <c r="G978" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -27485,7 +27485,7 @@
         <v>6.75</v>
       </c>
       <c r="G979" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27511,7 +27511,7 @@
         <v>6.75</v>
       </c>
       <c r="G980" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27537,7 +27537,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G981" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27563,7 +27563,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G982" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -27589,7 +27589,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G983" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -27615,7 +27615,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G984" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27641,7 +27641,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G985" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -27667,7 +27667,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G986" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -27693,7 +27693,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G987" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -27719,7 +27719,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G988" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -27745,7 +27745,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G989" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -27771,7 +27771,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G990" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -27797,7 +27797,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G991" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -27823,7 +27823,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G992" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -27849,7 +27849,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G993" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -27875,7 +27875,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G994" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -27901,7 +27901,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G995" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -27927,7 +27927,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G996" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -27953,7 +27953,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G997" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -27979,7 +27979,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G998" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28005,7 +28005,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G999" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28031,7 +28031,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1000" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28057,7 +28057,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1001" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28083,7 +28083,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1002" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28109,7 +28109,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1003" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28135,7 +28135,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1004" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28161,7 +28161,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1005" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28187,7 +28187,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1006" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28213,7 +28213,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1007" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28239,7 +28239,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1008" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28265,7 +28265,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1009" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28343,7 +28343,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1012" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28369,7 +28369,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1013" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28395,7 +28395,7 @@
         <v>8</v>
       </c>
       <c r="G1014" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28551,7 +28551,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1020" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28577,7 +28577,7 @@
         <v>8.5</v>
       </c>
       <c r="G1021" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28603,7 +28603,7 @@
         <v>8.5</v>
       </c>
       <c r="G1022" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -28629,7 +28629,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1023" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -28655,7 +28655,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1024" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28681,7 +28681,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1025" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28707,7 +28707,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1026" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28733,7 +28733,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1027" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28759,7 +28759,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1028" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28785,7 +28785,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1029" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28811,7 +28811,7 @@
         <v>8.75</v>
       </c>
       <c r="G1030" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28837,7 +28837,7 @@
         <v>8.75</v>
       </c>
       <c r="G1031" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28863,7 +28863,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1032" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28889,7 +28889,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1033" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28915,7 +28915,7 @@
         <v>8.5</v>
       </c>
       <c r="G1034" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28941,7 +28941,7 @@
         <v>8.25</v>
       </c>
       <c r="G1035" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28967,7 +28967,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1036" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -28993,7 +28993,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1037" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29019,7 +29019,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1038" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29045,7 +29045,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1039" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -29071,7 +29071,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1040" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -29097,7 +29097,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1041" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -29123,7 +29123,7 @@
         <v>8</v>
       </c>
       <c r="G1042" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -29149,7 +29149,7 @@
         <v>8</v>
       </c>
       <c r="G1043" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -29175,7 +29175,7 @@
         <v>8</v>
       </c>
       <c r="G1044" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -29201,7 +29201,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1045" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -29227,7 +29227,7 @@
         <v>8</v>
       </c>
       <c r="G1046" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -29253,7 +29253,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G1047" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -29279,7 +29279,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1048" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -29305,7 +29305,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1049" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -29331,7 +29331,7 @@
         <v>7.75</v>
       </c>
       <c r="G1050" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -29357,7 +29357,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1051" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -29383,7 +29383,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G1052" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -29409,7 +29409,7 @@
         <v>7.75</v>
       </c>
       <c r="G1053" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -29435,7 +29435,7 @@
         <v>7.75</v>
       </c>
       <c r="G1054" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -29461,7 +29461,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1055" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -29487,7 +29487,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G1056" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -29513,7 +29513,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1057" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -29539,7 +29539,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1058" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -29565,7 +29565,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1059" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -29591,7 +29591,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1060" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -29617,7 +29617,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1061" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -29643,7 +29643,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1062" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -29669,7 +29669,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1063" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -29695,7 +29695,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1064" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -29721,7 +29721,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1065" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -29747,7 +29747,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1066" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -29773,7 +29773,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1067" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -29799,7 +29799,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1068" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -29825,7 +29825,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1069" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -29851,7 +29851,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1070" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -29877,7 +29877,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G1071" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -29903,7 +29903,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1072" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -29929,7 +29929,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G1073" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -29955,7 +29955,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G1074" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -29981,7 +29981,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G1075" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -30007,7 +30007,7 @@
         <v>8</v>
       </c>
       <c r="G1076" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -30033,7 +30033,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G1077" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -30059,7 +30059,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1078" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -30085,7 +30085,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1079" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -30111,7 +30111,7 @@
         <v>8.25</v>
       </c>
       <c r="G1080" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -30137,7 +30137,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G1081" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -30163,7 +30163,7 @@
         <v>8.5</v>
       </c>
       <c r="G1082" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -30189,7 +30189,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1083" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -30215,7 +30215,7 @@
         <v>8.5</v>
       </c>
       <c r="G1084" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -30241,7 +30241,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1085" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -30267,7 +30267,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1086" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -30293,7 +30293,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1087" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -30319,7 +30319,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1088" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -30345,7 +30345,7 @@
         <v>8.5</v>
       </c>
       <c r="G1089" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -30371,7 +30371,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1090" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -30397,7 +30397,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1091" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -30423,7 +30423,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1092" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -30449,7 +30449,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1093" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -30475,7 +30475,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1094" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -30501,7 +30501,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1095" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -30527,7 +30527,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1096" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -30553,7 +30553,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1097" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -30579,7 +30579,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G1098" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -30605,7 +30605,7 @@
         <v>8.75</v>
       </c>
       <c r="G1099" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -30631,7 +30631,7 @@
         <v>8.75</v>
       </c>
       <c r="G1100" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -30657,7 +30657,7 @@
         <v>8.75</v>
       </c>
       <c r="G1101" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -30683,7 +30683,7 @@
         <v>8.75</v>
       </c>
       <c r="G1102" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -30709,7 +30709,7 @@
         <v>8.75</v>
       </c>
       <c r="G1103" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -30735,7 +30735,7 @@
         <v>8.75</v>
       </c>
       <c r="G1104" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -30761,7 +30761,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1105" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -30787,7 +30787,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1106" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -30813,7 +30813,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1107" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -30839,7 +30839,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1108" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -30865,7 +30865,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1109" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -30891,7 +30891,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1110" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -30917,7 +30917,7 @@
         <v>8.75</v>
       </c>
       <c r="G1111" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -30943,7 +30943,7 @@
         <v>8.75</v>
       </c>
       <c r="G1112" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -30969,7 +30969,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1113" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -30995,7 +30995,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1114" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -31021,7 +31021,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1115" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -31047,7 +31047,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1116" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -31073,7 +31073,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1117" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -31099,7 +31099,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1118" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -31125,7 +31125,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1119" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -31151,7 +31151,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1120" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -31177,7 +31177,7 @@
         <v>8.75</v>
       </c>
       <c r="G1121" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -31203,7 +31203,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1122" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -31229,7 +31229,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1123" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -31255,7 +31255,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1124" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -31281,7 +31281,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1125" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -31307,7 +31307,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1126" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -31333,7 +31333,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1127" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -31359,7 +31359,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1128" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -31385,7 +31385,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1129" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -31411,7 +31411,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1130" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -31437,7 +31437,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1131" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -31463,7 +31463,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1132" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -31489,7 +31489,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1133" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -31515,7 +31515,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1134" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -31567,7 +31567,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1136" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -31593,7 +31593,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1137" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -31619,7 +31619,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1138" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -31645,7 +31645,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1139" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -31671,7 +31671,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1140" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -31697,7 +31697,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1141" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -31723,7 +31723,7 @@
         <v>8.75</v>
       </c>
       <c r="G1142" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -31853,7 +31853,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1147" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -31905,7 +31905,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1149" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -32035,7 +32035,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1154" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -32061,7 +32061,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1155" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -32087,7 +32087,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1156" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="562">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46539163589478</t>
+    <t xml:space="preserve">2.46539187431335</t>
   </si>
   <si>
     <t xml:space="preserve">FPE.MI</t>
@@ -50,7 +50,7 @@
     <t xml:space="preserve">2.43408489227295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41060519218445</t>
+    <t xml:space="preserve">2.41060543060303</t>
   </si>
   <si>
     <t xml:space="preserve">2.45756530761719</t>
@@ -65,25 +65,25 @@
     <t xml:space="preserve">2.41843199729919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3558189868927</t>
+    <t xml:space="preserve">2.35581874847412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37147212028503</t>
+    <t xml:space="preserve">2.37147188186646</t>
   </si>
   <si>
     <t xml:space="preserve">2.50452518463135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36364555358887</t>
+    <t xml:space="preserve">2.36364531517029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44973874092102</t>
+    <t xml:space="preserve">2.44973826408386</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37303757667542</t>
+    <t xml:space="preserve">2.37303733825684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34955716133118</t>
+    <t xml:space="preserve">2.34955763816833</t>
   </si>
   <si>
     <t xml:space="preserve">2.46382641792297</t>
@@ -98,10 +98,10 @@
     <t xml:space="preserve">2.34799218177795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48104524612427</t>
+    <t xml:space="preserve">2.48104500770569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37929844856262</t>
+    <t xml:space="preserve">2.3792986869812</t>
   </si>
   <si>
     <t xml:space="preserve">2.38556003570557</t>
@@ -113,55 +113,55 @@
     <t xml:space="preserve">2.78002262115479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36702060699463</t>
+    <t xml:space="preserve">3.36702036857605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62530016899109</t>
+    <t xml:space="preserve">3.62529993057251</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31066918373108</t>
+    <t xml:space="preserve">3.31066870689392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25588226318359</t>
+    <t xml:space="preserve">3.25588202476501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20266127586365</t>
+    <t xml:space="preserve">3.20266103744507</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05238962173462</t>
+    <t xml:space="preserve">3.05239009857178</t>
   </si>
   <si>
     <t xml:space="preserve">3.09152293205261</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04456329345703</t>
+    <t xml:space="preserve">3.04456305503845</t>
   </si>
   <si>
     <t xml:space="preserve">3.03673672676086</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03830194473267</t>
+    <t xml:space="preserve">3.03830170631409</t>
   </si>
   <si>
     <t xml:space="preserve">3.15413618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3091037273407</t>
+    <t xml:space="preserve">3.30910396575928</t>
   </si>
   <si>
     <t xml:space="preserve">3.30284190177917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35762906074524</t>
+    <t xml:space="preserve">3.35762858390808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57677531242371</t>
+    <t xml:space="preserve">3.57677459716797</t>
   </si>
   <si>
     <t xml:space="preserve">3.52198815345764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40458846092224</t>
+    <t xml:space="preserve">3.40458869934082</t>
   </si>
   <si>
     <t xml:space="preserve">3.59242796897888</t>
@@ -170,55 +170,55 @@
     <t xml:space="preserve">3.58460116386414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6785204410553</t>
+    <t xml:space="preserve">3.67852067947388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60025477409363</t>
+    <t xml:space="preserve">3.60025429725647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59555840492249</t>
+    <t xml:space="preserve">3.59555864334106</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632207870483</t>
+    <t xml:space="preserve">3.32632231712341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29501581192017</t>
+    <t xml:space="preserve">3.29501557350159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37484741210938</t>
+    <t xml:space="preserve">3.3748471736908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38267397880554</t>
+    <t xml:space="preserve">3.38267374038696</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44372177124023</t>
+    <t xml:space="preserve">3.44372200965881</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59086275100708</t>
+    <t xml:space="preserve">3.5908625125885</t>
   </si>
   <si>
     <t xml:space="preserve">3.47972440719604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42650318145752</t>
+    <t xml:space="preserve">3.42650270462036</t>
   </si>
   <si>
     <t xml:space="preserve">3.41241526603699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24022912979126</t>
+    <t xml:space="preserve">3.2402286529541</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21048784255981</t>
+    <t xml:space="preserve">3.21048808097839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28405833244324</t>
+    <t xml:space="preserve">3.28405857086182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16196250915527</t>
+    <t xml:space="preserve">3.16196298599243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20892238616943</t>
+    <t xml:space="preserve">3.20892262458801</t>
   </si>
   <si>
     <t xml:space="preserve">3.13848304748535</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">3.18857336044312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14317893981934</t>
+    <t xml:space="preserve">3.14317870140076</t>
   </si>
   <si>
     <t xml:space="preserve">3.11500310897827</t>
@@ -248,25 +248,25 @@
     <t xml:space="preserve">2.97412347793579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06021642684937</t>
+    <t xml:space="preserve">3.06021666526794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90368342399597</t>
+    <t xml:space="preserve">2.90368390083313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89585709571838</t>
+    <t xml:space="preserve">2.8958568572998</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82854795455933</t>
+    <t xml:space="preserve">2.82854843139648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83637452125549</t>
+    <t xml:space="preserve">2.83637428283691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9099452495575</t>
+    <t xml:space="preserve">2.90994501113892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491231918335</t>
+    <t xml:space="preserve">3.06491208076477</t>
   </si>
   <si>
     <t xml:space="preserve">3.13065624237061</t>
@@ -275,64 +275,64 @@
     <t xml:space="preserve">3.14474415779114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.213618516922</t>
+    <t xml:space="preserve">3.21361875534058</t>
   </si>
   <si>
     <t xml:space="preserve">3.28562355041504</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35919380187988</t>
+    <t xml:space="preserve">3.35919404029846</t>
   </si>
   <si>
     <t xml:space="preserve">3.36388969421387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9133198261261</t>
+    <t xml:space="preserve">3.91332030296326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34378576278687</t>
+    <t xml:space="preserve">4.34378528594971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79381704330444</t>
+    <t xml:space="preserve">4.7938175201416</t>
   </si>
   <si>
     <t xml:space="preserve">5.47864818572998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09303903579712</t>
+    <t xml:space="preserve">6.09303998947144</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41603517532349</t>
+    <t xml:space="preserve">5.41603469848633</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71344709396362</t>
+    <t xml:space="preserve">5.71344757080078</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56865453720093</t>
+    <t xml:space="preserve">5.56865501403809</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4199481010437</t>
+    <t xml:space="preserve">5.41994857788086</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16558218002319</t>
+    <t xml:space="preserve">5.16558265686035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9464373588562</t>
+    <t xml:space="preserve">4.94643640518188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70381116867065</t>
+    <t xml:space="preserve">4.70381021499634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67641735076904</t>
+    <t xml:space="preserve">4.6764178276062</t>
   </si>
   <si>
     <t xml:space="preserve">5.0090503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55691432952881</t>
+    <t xml:space="preserve">5.55691528320312</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30646181106567</t>
+    <t xml:space="preserve">5.30646276473999</t>
   </si>
   <si>
     <t xml:space="preserve">5.22428274154663</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">5.47082185745239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36907529830933</t>
+    <t xml:space="preserve">5.36907482147217</t>
   </si>
   <si>
     <t xml:space="preserve">5.29080867767334</t>
@@ -368,31 +368,31 @@
     <t xml:space="preserve">4.9933967590332</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15384292602539</t>
+    <t xml:space="preserve">5.15384340286255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98556995391846</t>
+    <t xml:space="preserve">4.9855694770813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75859689712524</t>
+    <t xml:space="preserve">4.7585973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77033758163452</t>
+    <t xml:space="preserve">4.77033710479736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86425733566284</t>
+    <t xml:space="preserve">4.8642578125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88773632049561</t>
+    <t xml:space="preserve">4.88773679733276</t>
   </si>
   <si>
     <t xml:space="preserve">4.83295059204102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75468349456787</t>
+    <t xml:space="preserve">4.75468301773071</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8290376663208</t>
+    <t xml:space="preserve">4.82903671264648</t>
   </si>
   <si>
     <t xml:space="preserve">4.7233772277832</t>
@@ -401,22 +401,22 @@
     <t xml:space="preserve">4.68815755844116</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78207683563232</t>
+    <t xml:space="preserve">4.78207731246948</t>
   </si>
   <si>
     <t xml:space="preserve">4.8759970664978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03644323348999</t>
+    <t xml:space="preserve">5.03644275665283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92687034606934</t>
+    <t xml:space="preserve">4.92686986923218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81338357925415</t>
+    <t xml:space="preserve">4.81338453292847</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86034393310547</t>
+    <t xml:space="preserve">4.86034345626831</t>
   </si>
   <si>
     <t xml:space="preserve">5.00122308731079</t>
@@ -425,19 +425,19 @@
     <t xml:space="preserve">4.77425098419189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8212103843689</t>
+    <t xml:space="preserve">4.82121086120605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69989728927612</t>
+    <t xml:space="preserve">4.69989824295044</t>
   </si>
   <si>
     <t xml:space="preserve">4.69598436355591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90730381011963</t>
+    <t xml:space="preserve">4.90730333328247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20471620559692</t>
+    <t xml:space="preserve">5.20471572875977</t>
   </si>
   <si>
     <t xml:space="preserve">5.43951511383057</t>
@@ -446,91 +446,91 @@
     <t xml:space="preserve">5.28298234939575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384832382202</t>
+    <t xml:space="preserve">5.24384880065918</t>
   </si>
   <si>
     <t xml:space="preserve">5.36124849319458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40038156509399</t>
+    <t xml:space="preserve">5.40038251876831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.51778125762939</t>
+    <t xml:space="preserve">5.51778221130371</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63518142700195</t>
+    <t xml:space="preserve">5.63518095016479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96991586685181</t>
+    <t xml:space="preserve">4.96991682052612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93078327178955</t>
+    <t xml:space="preserve">4.93078374862671</t>
   </si>
   <si>
     <t xml:space="preserve">4.85251665115356</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12644958496094</t>
+    <t xml:space="preserve">5.12644910812378</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04818296432495</t>
+    <t xml:space="preserve">5.04818344116211</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08731603622437</t>
+    <t xml:space="preserve">5.08731555938721</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59604740142822</t>
+    <t xml:space="preserve">5.59604835510254</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26159715652466</t>
+    <t xml:space="preserve">5.26159763336182</t>
   </si>
   <si>
     <t xml:space="preserve">5.42104005813599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34131813049316</t>
+    <t xml:space="preserve">5.34131860733032</t>
   </si>
   <si>
     <t xml:space="preserve">5.22173690795898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14201545715332</t>
+    <t xml:space="preserve">5.14201593399048</t>
   </si>
   <si>
     <t xml:space="preserve">5.1021556854248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18187570571899</t>
+    <t xml:space="preserve">5.18187618255615</t>
   </si>
   <si>
     <t xml:space="preserve">5.38117933273315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30145788192749</t>
+    <t xml:space="preserve">5.30145740509033</t>
   </si>
   <si>
     <t xml:space="preserve">4.9028525352478</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50076103210449</t>
+    <t xml:space="preserve">5.50076150894165</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46090030670166</t>
+    <t xml:space="preserve">5.4608998298645</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58048248291016</t>
+    <t xml:space="preserve">5.580482006073</t>
   </si>
   <si>
     <t xml:space="preserve">5.54062128067017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62034225463867</t>
+    <t xml:space="preserve">5.62034273147583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94271230697632</t>
+    <t xml:space="preserve">4.94271183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98257255554199</t>
+    <t xml:space="preserve">4.98257350921631</t>
   </si>
   <si>
     <t xml:space="preserve">4.82313108444214</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">5.02243375778198</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74341011047363</t>
+    <t xml:space="preserve">4.74340963363647</t>
   </si>
   <si>
     <t xml:space="preserve">4.78327035903931</t>
@@ -554,34 +554,34 @@
     <t xml:space="preserve">5.73992443084717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81964588165283</t>
+    <t xml:space="preserve">5.81964540481567</t>
   </si>
   <si>
     <t xml:space="preserve">5.70006370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6602029800415</t>
+    <t xml:space="preserve">5.66020345687866</t>
   </si>
   <si>
     <t xml:space="preserve">5.77978515625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85950565338135</t>
+    <t xml:space="preserve">5.85950613021851</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97908782958984</t>
+    <t xml:space="preserve">5.979088306427</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29797267913818</t>
+    <t xml:space="preserve">6.29797220230103</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13852977752686</t>
+    <t xml:space="preserve">6.13853025436401</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05880928039551</t>
+    <t xml:space="preserve">6.05880880355835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825075149536</t>
+    <t xml:space="preserve">6.21825170516968</t>
   </si>
   <si>
     <t xml:space="preserve">6.09867000579834</t>
@@ -590,16 +590,16 @@
     <t xml:space="preserve">6.38518476486206</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25998449325562</t>
+    <t xml:space="preserve">6.25998497009277</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30171823501587</t>
+    <t xml:space="preserve">6.30171775817871</t>
   </si>
   <si>
     <t xml:space="preserve">6.17651844024658</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42691707611084</t>
+    <t xml:space="preserve">6.42691802978516</t>
   </si>
   <si>
     <t xml:space="preserve">6.34345102310181</t>
@@ -611,46 +611,46 @@
     <t xml:space="preserve">5.9678521156311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0095853805542</t>
+    <t xml:space="preserve">6.00958490371704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13478517532349</t>
+    <t xml:space="preserve">6.13478469848633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05131864547729</t>
+    <t xml:space="preserve">6.05131816864014</t>
   </si>
   <si>
     <t xml:space="preserve">5.92611885070801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09305191040039</t>
+    <t xml:space="preserve">6.09305143356323</t>
   </si>
   <si>
     <t xml:space="preserve">6.21825122833252</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51038360595703</t>
+    <t xml:space="preserve">6.51038408279419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84265279769897</t>
+    <t xml:space="preserve">5.84265232086182</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88438558578491</t>
+    <t xml:space="preserve">5.88438606262207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05291604995728</t>
+    <t xml:space="preserve">7.05291557312012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09624767303467</t>
+    <t xml:space="preserve">8.09624576568604</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80411434173584</t>
+    <t xml:space="preserve">7.804114818573</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6371808052063</t>
+    <t xml:space="preserve">7.63718128204346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55371475219727</t>
+    <t xml:space="preserve">7.55371570587158</t>
   </si>
   <si>
     <t xml:space="preserve">7.3450493812561</t>
@@ -659,70 +659,70 @@
     <t xml:space="preserve">7.17811632156372</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51198148727417</t>
+    <t xml:space="preserve">7.51198196411133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47024917602539</t>
+    <t xml:space="preserve">7.47024822235107</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30331516265869</t>
+    <t xml:space="preserve">7.30331563949585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851591110229</t>
+    <t xml:space="preserve">7.42851495742798</t>
   </si>
   <si>
     <t xml:space="preserve">7.2615818977356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38678169250488</t>
+    <t xml:space="preserve">7.38678312301636</t>
   </si>
   <si>
     <t xml:space="preserve">6.96944999694824</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21984815597534</t>
+    <t xml:space="preserve">7.21984910964966</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59544849395752</t>
+    <t xml:space="preserve">7.59544801712036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7623815536499</t>
+    <t xml:space="preserve">7.76238107681274</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84584712982178</t>
+    <t xml:space="preserve">7.84584760665894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67891502380371</t>
+    <t xml:space="preserve">7.67891454696655</t>
   </si>
   <si>
     <t xml:space="preserve">7.01118278503418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09464931488037</t>
+    <t xml:space="preserve">7.09464979171753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92771673202515</t>
+    <t xml:space="preserve">6.9277172088623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76078414916992</t>
+    <t xml:space="preserve">6.76078319549561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8025164604187</t>
+    <t xml:space="preserve">6.80251693725586</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71905088424683</t>
+    <t xml:space="preserve">6.71905040740967</t>
   </si>
   <si>
     <t xml:space="preserve">6.8442497253418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59385061264038</t>
+    <t xml:space="preserve">6.59385013580322</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67731714248657</t>
+    <t xml:space="preserve">6.67731666564941</t>
   </si>
   <si>
-    <t xml:space="preserve">6.55211782455444</t>
+    <t xml:space="preserve">6.55211687088013</t>
   </si>
   <si>
     <t xml:space="preserve">5.75918626785278</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">5.80091905593872</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67571973800659</t>
+    <t xml:space="preserve">5.67571926116943</t>
   </si>
   <si>
     <t xml:space="preserve">5.59225225448608</t>
@@ -743,37 +743,37 @@
     <t xml:space="preserve">5.6339864730835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46705389022827</t>
+    <t xml:space="preserve">5.46705341339111</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55051946640015</t>
+    <t xml:space="preserve">5.5505199432373</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17492055892944</t>
+    <t xml:space="preserve">5.17492151260376</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25838708877563</t>
+    <t xml:space="preserve">5.25838804244995</t>
   </si>
   <si>
-    <t xml:space="preserve">5.38358688354492</t>
+    <t xml:space="preserve">5.38358736038208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13638257980347</t>
+    <t xml:space="preserve">7.13638353347778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47247076034546</t>
+    <t xml:space="preserve">7.47247123718262</t>
   </si>
   <si>
     <t xml:space="preserve">7.25269269943237</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2966480255127</t>
+    <t xml:space="preserve">7.29664850234985</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20873641967773</t>
+    <t xml:space="preserve">7.20873689651489</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16478061676025</t>
+    <t xml:space="preserve">7.16478109359741</t>
   </si>
   <si>
     <t xml:space="preserve">7.07686948776245</t>
@@ -785,19 +785,19 @@
     <t xml:space="preserve">7.03291368484497</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94500207901001</t>
+    <t xml:space="preserve">6.94500255584717</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85709095001221</t>
+    <t xml:space="preserve">6.85709047317505</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72522354125977</t>
+    <t xml:space="preserve">6.72522449493408</t>
   </si>
   <si>
     <t xml:space="preserve">6.81313514709473</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76917886734009</t>
+    <t xml:space="preserve">6.7691798210144</t>
   </si>
   <si>
     <t xml:space="preserve">6.90104627609253</t>
@@ -806,10 +806,10 @@
     <t xml:space="preserve">6.63731241226196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12082576751709</t>
+    <t xml:space="preserve">7.12082481384277</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34060430526733</t>
+    <t xml:space="preserve">7.34060382843018</t>
   </si>
   <si>
     <t xml:space="preserve">7.5164270401001</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">7.56038284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73620557785034</t>
+    <t xml:space="preserve">7.7362060546875</t>
   </si>
   <si>
     <t xml:space="preserve">7.69224977493286</t>
@@ -830,28 +830,28 @@
     <t xml:space="preserve">7.78247404098511</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8272008895874</t>
+    <t xml:space="preserve">7.82720136642456</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73774671554565</t>
+    <t xml:space="preserve">7.73774719238281</t>
   </si>
   <si>
     <t xml:space="preserve">7.69302082061768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829397201538</t>
+    <t xml:space="preserve">7.64829444885254</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60356616973877</t>
+    <t xml:space="preserve">7.60356712341309</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91665410995483</t>
+    <t xml:space="preserve">7.91665554046631</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87192821502686</t>
+    <t xml:space="preserve">7.87192869186401</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96138095855713</t>
+    <t xml:space="preserve">7.96138143539429</t>
   </si>
   <si>
     <t xml:space="preserve">8.2297420501709</t>
@@ -863,28 +863,28 @@
     <t xml:space="preserve">8.58755779266357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36392402648926</t>
+    <t xml:space="preserve">8.36392307281494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63228511810303</t>
+    <t xml:space="preserve">8.63228321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54283046722412</t>
+    <t xml:space="preserve">8.54283142089844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40864944458008</t>
+    <t xml:space="preserve">8.40865039825439</t>
   </si>
   <si>
     <t xml:space="preserve">8.27446937561035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45337677001953</t>
+    <t xml:space="preserve">8.45337581634521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67701148986816</t>
+    <t xml:space="preserve">8.67701053619385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49810409545898</t>
+    <t xml:space="preserve">8.49810314178467</t>
   </si>
   <si>
     <t xml:space="preserve">8.81119251251221</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">8.85591888427734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03482627868652</t>
+    <t xml:space="preserve">9.03482723236084</t>
   </si>
   <si>
     <t xml:space="preserve">10.3766326904297</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4500780105591</t>
+    <t xml:space="preserve">11.4500770568848</t>
   </si>
   <si>
     <t xml:space="preserve">10.734447479248</t>
@@ -911,10 +911,10 @@
     <t xml:space="preserve">11.0922622680664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9133548736572</t>
+    <t xml:space="preserve">10.9133539199829</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1817150115967</t>
+    <t xml:space="preserve">11.181715965271</t>
   </si>
   <si>
     <t xml:space="preserve">11.3606224060059</t>
@@ -926,28 +926,28 @@
     <t xml:space="preserve">11.5395307540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2711696624756</t>
+    <t xml:space="preserve">11.2711706161499</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5555391311646</t>
+    <t xml:space="preserve">10.5555400848389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2871789932251</t>
+    <t xml:space="preserve">10.2871780395508</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0028076171875</t>
+    <t xml:space="preserve">11.0028085708618</t>
   </si>
   <si>
     <t xml:space="preserve">10.6449928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4660863876343</t>
+    <t xml:space="preserve">10.46608543396</t>
   </si>
   <si>
     <t xml:space="preserve">10.1082715988159</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1977243423462</t>
+    <t xml:space="preserve">10.1977252960205</t>
   </si>
   <si>
     <t xml:space="preserve">9.75045585632324</t>
@@ -956,16 +956,16 @@
     <t xml:space="preserve">10.018816947937</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6129751205444</t>
+    <t xml:space="preserve">12.6129760742188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9707908630371</t>
+    <t xml:space="preserve">12.9707899093628</t>
   </si>
   <si>
     <t xml:space="preserve">14.0442342758179</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7758731842041</t>
+    <t xml:space="preserve">13.7758741378784</t>
   </si>
   <si>
     <t xml:space="preserve">13.5075130462646</t>
@@ -983,22 +983,22 @@
     <t xml:space="preserve">12.8813362121582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7918834686279</t>
+    <t xml:space="preserve">12.7918825149536</t>
   </si>
   <si>
     <t xml:space="preserve">12.702428817749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.149697303772</t>
+    <t xml:space="preserve">13.1496963500977</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3286037445068</t>
+    <t xml:space="preserve">13.3286046981812</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9547815322876</t>
+    <t xml:space="preserve">13.9547805786133</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5969657897949</t>
+    <t xml:space="preserve">13.5969667434692</t>
   </si>
   <si>
     <t xml:space="preserve">13.6864204406738</t>
@@ -1010,25 +1010,25 @@
     <t xml:space="preserve">14.4020500183105</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2965879440308</t>
+    <t xml:space="preserve">15.2965888977051</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2071323394775</t>
+    <t xml:space="preserve">15.2071342468262</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5809564590454</t>
+    <t xml:space="preserve">14.5809574127197</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7598648071289</t>
+    <t xml:space="preserve">14.7598657608032</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4915046691895</t>
+    <t xml:space="preserve">14.4915037155151</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5400876998901</t>
+    <t xml:space="preserve">14.5400886535645</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3560361862183</t>
+    <t xml:space="preserve">14.3560371398926</t>
   </si>
   <si>
     <t xml:space="preserve">14.2640104293823</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">14.8161659240723</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6321144104004</t>
+    <t xml:space="preserve">14.6321134567261</t>
   </si>
   <si>
     <t xml:space="preserve">15.3683223724365</t>
@@ -1052,10 +1052,10 @@
     <t xml:space="preserve">16.104528427124</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3806056976318</t>
+    <t xml:space="preserve">16.3806037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9204750061035</t>
+    <t xml:space="preserve">15.9204769134521</t>
   </si>
   <si>
     <t xml:space="preserve">17.2088394165039</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">17.4849166870117</t>
   </si>
   <si>
-    <t xml:space="preserve">17.576940536499</t>
+    <t xml:space="preserve">17.5769424438477</t>
   </si>
   <si>
     <t xml:space="preserve">17.6689682006836</t>
@@ -1076,31 +1076,31 @@
     <t xml:space="preserve">18.4051742553711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1413803100586</t>
+    <t xml:space="preserve">19.1413822174072</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6935367584229</t>
+    <t xml:space="preserve">19.6935386657715</t>
   </si>
   <si>
     <t xml:space="preserve">20.0616397857666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5340557098389</t>
+    <t xml:space="preserve">21.5340538024902</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3745708465576</t>
+    <t xml:space="preserve">23.3745727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2702617645264</t>
+    <t xml:space="preserve">22.270263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">22.822416305542</t>
+    <t xml:space="preserve">22.8224182128906</t>
   </si>
   <si>
     <t xml:space="preserve">20.6137962341309</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3254337310791</t>
+    <t xml:space="preserve">19.3254356384277</t>
   </si>
   <si>
     <t xml:space="preserve">21.902156829834</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">22.0862102508545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0064678192139</t>
+    <t xml:space="preserve">23.0064697265625</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5586261749268</t>
+    <t xml:space="preserve">23.5586242675781</t>
   </si>
   <si>
     <t xml:space="preserve">23.74267578125</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">24.6629333496094</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8469886779785</t>
+    <t xml:space="preserve">24.8469867706299</t>
   </si>
   <si>
     <t xml:space="preserve">24.2948303222656</t>
@@ -1139,25 +1139,25 @@
     <t xml:space="preserve">25.2150897979736</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4543132781982</t>
+    <t xml:space="preserve">22.4543151855469</t>
   </si>
   <si>
     <t xml:space="preserve">24.4788837432861</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9512958526611</t>
+    <t xml:space="preserve">25.9512977600098</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5034523010254</t>
+    <t xml:space="preserve">26.5034503936768</t>
   </si>
   <si>
     <t xml:space="preserve">27.975866317749</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9206943511963</t>
+    <t xml:space="preserve">30.9206924438477</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0801753997803</t>
+    <t xml:space="preserve">29.0801773071289</t>
   </si>
   <si>
     <t xml:space="preserve">30.736644744873</t>
@@ -1166,31 +1166,31 @@
     <t xml:space="preserve">30.3685398101807</t>
   </si>
   <si>
-    <t xml:space="preserve">29.2642288208008</t>
+    <t xml:space="preserve">29.2642269134521</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4728507995605</t>
+    <t xml:space="preserve">31.4728527069092</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2336273193359</t>
+    <t xml:space="preserve">34.2336235046387</t>
   </si>
   <si>
-    <t xml:space="preserve">34.7857780456543</t>
+    <t xml:space="preserve">34.7857818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8655204772949</t>
+    <t xml:space="preserve">33.8655166625977</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4974212646484</t>
+    <t xml:space="preserve">33.4974174499512</t>
   </si>
   <si>
-    <t xml:space="preserve">30.1844863891602</t>
+    <t xml:space="preserve">30.1844844818115</t>
   </si>
   <si>
     <t xml:space="preserve">27.4237098693848</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6875038146973</t>
+    <t xml:space="preserve">26.6875019073486</t>
   </si>
   <si>
     <t xml:space="preserve">25.5831928253174</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">26.3194007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7918167114258</t>
+    <t xml:space="preserve">27.7918148040771</t>
   </si>
   <si>
     <t xml:space="preserve">28.8961238861084</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">28.5280208587646</t>
   </si>
   <si>
-    <t xml:space="preserve">28.7120723724365</t>
+    <t xml:space="preserve">28.7120742797852</t>
   </si>
   <si>
     <t xml:space="preserve">28.3439693450928</t>
@@ -1220,7 +1220,7 @@
     <t xml:space="preserve">27.055606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8715572357178</t>
+    <t xml:space="preserve">26.8715553283691</t>
   </si>
   <si>
     <t xml:space="preserve">25.3991413116455</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">27.6077632904053</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5525913238525</t>
+    <t xml:space="preserve">30.5525894165039</t>
   </si>
   <si>
     <t xml:space="preserve">29.6323318481445</t>
@@ -1250,10 +1250,10 @@
     <t xml:space="preserve">32.209056854248</t>
   </si>
   <si>
-    <t xml:space="preserve">31.28879737854</t>
+    <t xml:space="preserve">31.2887954711914</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6569023132324</t>
+    <t xml:space="preserve">31.6569004058838</t>
   </si>
   <si>
     <t xml:space="preserve">32.0250015258789</t>
@@ -1266,9 +1266,6 @@
   </si>
   <si>
     <t xml:space="preserve">33.1643714904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6569004058838</t>
   </si>
   <si>
     <t xml:space="preserve">32.4106369018555</t>
@@ -44671,7 +44668,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1640" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44723,7 +44720,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1642" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44749,7 +44746,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1643" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44931,7 +44928,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1650" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44957,7 +44954,7 @@
         <v>34.7999992370605</v>
       </c>
       <c r="G1651" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44983,7 +44980,7 @@
         <v>35</v>
       </c>
       <c r="G1652" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -45009,7 +45006,7 @@
         <v>34.4000015258789</v>
       </c>
       <c r="G1653" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -45035,7 +45032,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1654" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -45061,7 +45058,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1655" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -45087,7 +45084,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1656" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -45113,7 +45110,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1657" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -45139,7 +45136,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1658" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45165,7 +45162,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1659" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45191,7 +45188,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1660" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45217,7 +45214,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1661" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45243,7 +45240,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1662" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45269,7 +45266,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G1663" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45295,7 +45292,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1664" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45321,7 +45318,7 @@
         <v>32</v>
       </c>
       <c r="G1665" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45347,7 +45344,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1666" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45373,7 +45370,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1667" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45399,7 +45396,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1668" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45425,7 +45422,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1669" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45451,7 +45448,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1670" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45477,7 +45474,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1671" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45503,7 +45500,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1672" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45529,7 +45526,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G1673" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45555,7 +45552,7 @@
         <v>32</v>
       </c>
       <c r="G1674" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45581,7 +45578,7 @@
         <v>32</v>
       </c>
       <c r="G1675" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45607,7 +45604,7 @@
         <v>32</v>
       </c>
       <c r="G1676" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45633,7 +45630,7 @@
         <v>32</v>
       </c>
       <c r="G1677" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45659,7 +45656,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1678" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45685,7 +45682,7 @@
         <v>33</v>
       </c>
       <c r="G1679" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45711,7 +45708,7 @@
         <v>32.5999984741211</v>
       </c>
       <c r="G1680" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45737,7 +45734,7 @@
         <v>33</v>
       </c>
       <c r="G1681" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45763,7 +45760,7 @@
         <v>32</v>
       </c>
       <c r="G1682" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45789,7 +45786,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1683" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45815,7 +45812,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1684" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45841,7 +45838,7 @@
         <v>33.4000015258789</v>
       </c>
       <c r="G1685" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45867,7 +45864,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1686" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45893,7 +45890,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1687" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45919,7 +45916,7 @@
         <v>33</v>
       </c>
       <c r="G1688" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45945,7 +45942,7 @@
         <v>33</v>
       </c>
       <c r="G1689" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45971,7 +45968,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1690" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45997,7 +45994,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1691" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -46023,7 +46020,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1692" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -46127,7 +46124,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1696" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46153,7 +46150,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1697" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46179,7 +46176,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1698" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46205,7 +46202,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1699" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46231,7 +46228,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G1700" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46257,7 +46254,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1701" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46283,7 +46280,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1702" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46309,7 +46306,7 @@
         <v>33.5999984741211</v>
       </c>
       <c r="G1703" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46335,7 +46332,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1704" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46387,7 +46384,7 @@
         <v>33</v>
       </c>
       <c r="G1706" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46413,7 +46410,7 @@
         <v>33</v>
       </c>
       <c r="G1707" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46439,7 +46436,7 @@
         <v>33</v>
       </c>
       <c r="G1708" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46465,7 +46462,7 @@
         <v>33</v>
       </c>
       <c r="G1709" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46491,7 +46488,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1710" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46517,7 +46514,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1711" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46543,7 +46540,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1712" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46569,7 +46566,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1713" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46595,7 +46592,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1714" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46621,7 +46618,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1715" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46647,7 +46644,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1716" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46673,7 +46670,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1717" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46699,7 +46696,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1718" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46725,7 +46722,7 @@
         <v>32</v>
       </c>
       <c r="G1719" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46751,7 +46748,7 @@
         <v>32</v>
       </c>
       <c r="G1720" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46777,7 +46774,7 @@
         <v>32</v>
       </c>
       <c r="G1721" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46803,7 +46800,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1722" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46829,7 +46826,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1723" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46855,7 +46852,7 @@
         <v>32.2000007629395</v>
       </c>
       <c r="G1724" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46881,7 +46878,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1725" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46907,7 +46904,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1726" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46933,7 +46930,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1727" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46959,7 +46956,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1728" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46985,7 +46982,7 @@
         <v>31.7999992370605</v>
       </c>
       <c r="G1729" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -47011,7 +47008,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1730" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -47037,7 +47034,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1731" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -47063,7 +47060,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G1732" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -47089,7 +47086,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1733" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -47115,7 +47112,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1734" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -47141,7 +47138,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G1735" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47167,7 +47164,7 @@
         <v>30</v>
       </c>
       <c r="G1736" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47193,7 +47190,7 @@
         <v>30</v>
       </c>
       <c r="G1737" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47219,7 +47216,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1738" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47245,7 +47242,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1739" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47271,7 +47268,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1740" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47297,7 +47294,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1741" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47323,7 +47320,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1742" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47349,7 +47346,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1743" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47375,7 +47372,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1744" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47401,7 +47398,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1745" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47427,7 +47424,7 @@
         <v>26</v>
       </c>
       <c r="G1746" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47453,7 +47450,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1747" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47479,7 +47476,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1748" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47505,7 +47502,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1749" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47531,7 +47528,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1750" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47557,7 +47554,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1751" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47583,7 +47580,7 @@
         <v>27</v>
       </c>
       <c r="G1752" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47609,7 +47606,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1753" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47635,7 +47632,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1754" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47661,7 +47658,7 @@
         <v>26</v>
       </c>
       <c r="G1755" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47687,7 +47684,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1756" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47713,7 +47710,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1757" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47739,7 +47736,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1758" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47765,7 +47762,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1759" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47791,7 +47788,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1760" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47817,7 +47814,7 @@
         <v>24</v>
       </c>
       <c r="G1761" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47843,7 +47840,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1762" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47869,7 +47866,7 @@
         <v>23</v>
       </c>
       <c r="G1763" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47895,7 +47892,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1764" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47921,7 +47918,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1765" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47947,7 +47944,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G1766" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47973,7 +47970,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G1767" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47999,7 +47996,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G1768" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -48025,7 +48022,7 @@
         <v>24</v>
       </c>
       <c r="G1769" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -48051,7 +48048,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G1770" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -48077,7 +48074,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G1771" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -48103,7 +48100,7 @@
         <v>24</v>
       </c>
       <c r="G1772" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -48129,7 +48126,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1773" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48155,7 +48152,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G1774" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48181,7 +48178,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1775" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48207,7 +48204,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1776" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48233,7 +48230,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1777" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48259,7 +48256,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1778" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48285,7 +48282,7 @@
         <v>28</v>
       </c>
       <c r="G1779" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48311,7 +48308,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1780" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48337,7 +48334,7 @@
         <v>28</v>
       </c>
       <c r="G1781" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48363,7 +48360,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1782" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48389,7 +48386,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1783" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48415,7 +48412,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1784" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48441,7 +48438,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1785" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48467,7 +48464,7 @@
         <v>28</v>
       </c>
       <c r="G1786" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48493,7 +48490,7 @@
         <v>28</v>
       </c>
       <c r="G1787" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48519,7 +48516,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1788" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48545,7 +48542,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1789" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48571,7 +48568,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1790" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -48597,7 +48594,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1791" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48623,7 +48620,7 @@
         <v>28</v>
       </c>
       <c r="G1792" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48649,7 +48646,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1793" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48675,7 +48672,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1794" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -48701,7 +48698,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1795" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48727,7 +48724,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1796" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48753,7 +48750,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1797" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48779,7 +48776,7 @@
         <v>29</v>
       </c>
       <c r="G1798" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48805,7 +48802,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1799" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48831,7 +48828,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1800" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48857,7 +48854,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1801" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48883,7 +48880,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1802" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48909,7 +48906,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1803" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48935,7 +48932,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1804" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48961,7 +48958,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1805" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48987,7 +48984,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1806" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -49013,7 +49010,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1807" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -49039,7 +49036,7 @@
         <v>28</v>
       </c>
       <c r="G1808" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -49065,7 +49062,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1809" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -49091,7 +49088,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1810" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -49117,7 +49114,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1811" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -49143,7 +49140,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1812" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49169,7 +49166,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1813" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49195,7 +49192,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1814" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49221,7 +49218,7 @@
         <v>27</v>
       </c>
       <c r="G1815" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49247,7 +49244,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1816" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49273,7 +49270,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1817" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49299,7 +49296,7 @@
         <v>26</v>
       </c>
       <c r="G1818" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49325,7 +49322,7 @@
         <v>26</v>
       </c>
       <c r="G1819" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49351,7 +49348,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1820" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49377,7 +49374,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1821" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49403,7 +49400,7 @@
         <v>26</v>
       </c>
       <c r="G1822" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49429,7 +49426,7 @@
         <v>26</v>
       </c>
       <c r="G1823" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49455,7 +49452,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1824" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49481,7 +49478,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1825" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49507,7 +49504,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1826" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49533,7 +49530,7 @@
         <v>29</v>
       </c>
       <c r="G1827" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49559,7 +49556,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1828" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49585,7 +49582,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1829" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49611,7 +49608,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1830" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49637,7 +49634,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1831" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49663,7 +49660,7 @@
         <v>29</v>
       </c>
       <c r="G1832" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49689,7 +49686,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1833" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49715,7 +49712,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1834" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49741,7 +49738,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1835" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49767,7 +49764,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1836" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49793,7 +49790,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1837" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49819,7 +49816,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1838" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49845,7 +49842,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1839" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49871,7 +49868,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1840" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49897,7 +49894,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1841" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49923,7 +49920,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1842" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49949,7 +49946,7 @@
         <v>30</v>
       </c>
       <c r="G1843" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49975,7 +49972,7 @@
         <v>30</v>
       </c>
       <c r="G1844" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -50001,7 +49998,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1845" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -50027,7 +50024,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1846" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -50053,7 +50050,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1847" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -50079,7 +50076,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G1848" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -50105,7 +50102,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G1849" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -50131,7 +50128,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1850" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50157,7 +50154,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1851" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50183,7 +50180,7 @@
         <v>29</v>
       </c>
       <c r="G1852" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50209,7 +50206,7 @@
         <v>29</v>
       </c>
       <c r="G1853" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50235,7 +50232,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1854" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50261,7 +50258,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1855" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50287,7 +50284,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1856" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50313,7 +50310,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1857" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50339,7 +50336,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1858" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50365,7 +50362,7 @@
         <v>29</v>
       </c>
       <c r="G1859" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50391,7 +50388,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1860" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50417,7 +50414,7 @@
         <v>30</v>
       </c>
       <c r="G1861" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50443,7 +50440,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1862" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50469,7 +50466,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1863" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50495,7 +50492,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1864" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50521,7 +50518,7 @@
         <v>27</v>
       </c>
       <c r="G1865" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50547,7 +50544,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1866" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50573,7 +50570,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1867" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50599,7 +50596,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1868" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50625,7 +50622,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1869" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50651,7 +50648,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1870" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50677,7 +50674,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1871" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50703,7 +50700,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1872" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50729,7 +50726,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1873" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50755,7 +50752,7 @@
         <v>27</v>
       </c>
       <c r="G1874" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50781,7 +50778,7 @@
         <v>27</v>
       </c>
       <c r="G1875" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50807,7 +50804,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1876" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50833,7 +50830,7 @@
         <v>27</v>
       </c>
       <c r="G1877" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50859,7 +50856,7 @@
         <v>27</v>
       </c>
       <c r="G1878" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50885,7 +50882,7 @@
         <v>27</v>
       </c>
       <c r="G1879" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50911,7 +50908,7 @@
         <v>27</v>
       </c>
       <c r="G1880" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50937,7 +50934,7 @@
         <v>28</v>
       </c>
       <c r="G1881" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50963,7 +50960,7 @@
         <v>28</v>
       </c>
       <c r="G1882" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50989,7 +50986,7 @@
         <v>28</v>
       </c>
       <c r="G1883" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -51015,7 +51012,7 @@
         <v>28</v>
       </c>
       <c r="G1884" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -51041,7 +51038,7 @@
         <v>28</v>
       </c>
       <c r="G1885" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -51067,7 +51064,7 @@
         <v>28</v>
       </c>
       <c r="G1886" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -51093,7 +51090,7 @@
         <v>27</v>
       </c>
       <c r="G1887" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -51119,7 +51116,7 @@
         <v>27</v>
       </c>
       <c r="G1888" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51145,7 +51142,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1889" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51171,7 +51168,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1890" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51197,7 +51194,7 @@
         <v>28</v>
       </c>
       <c r="G1891" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51223,7 +51220,7 @@
         <v>28</v>
       </c>
       <c r="G1892" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51249,7 +51246,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1893" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51275,7 +51272,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1894" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51301,7 +51298,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1895" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51327,7 +51324,7 @@
         <v>28</v>
       </c>
       <c r="G1896" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51353,7 +51350,7 @@
         <v>28</v>
       </c>
       <c r="G1897" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51379,7 +51376,7 @@
         <v>28</v>
       </c>
       <c r="G1898" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51405,7 +51402,7 @@
         <v>28</v>
       </c>
       <c r="G1899" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51431,7 +51428,7 @@
         <v>28</v>
       </c>
       <c r="G1900" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51457,7 +51454,7 @@
         <v>28</v>
       </c>
       <c r="G1901" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51483,7 +51480,7 @@
         <v>28</v>
       </c>
       <c r="G1902" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51509,7 +51506,7 @@
         <v>28</v>
       </c>
       <c r="G1903" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51535,7 +51532,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1904" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51561,7 +51558,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1905" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51587,7 +51584,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1906" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51613,7 +51610,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1907" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51639,7 +51636,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1908" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51665,7 +51662,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1909" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51691,7 +51688,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1910" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51717,7 +51714,7 @@
         <v>29</v>
       </c>
       <c r="G1911" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51743,7 +51740,7 @@
         <v>29</v>
       </c>
       <c r="G1912" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51769,7 +51766,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1913" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51795,7 +51792,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1914" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51821,7 +51818,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1915" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51847,7 +51844,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1916" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51873,7 +51870,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1917" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51899,7 +51896,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1918" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51925,7 +51922,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1919" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51951,7 +51948,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1920" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51977,7 +51974,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1921" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -52003,7 +52000,7 @@
         <v>27</v>
       </c>
       <c r="G1922" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -52029,7 +52026,7 @@
         <v>27</v>
       </c>
       <c r="G1923" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -52055,7 +52052,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1924" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -52081,7 +52078,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1925" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -52107,7 +52104,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1926" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52133,7 +52130,7 @@
         <v>28</v>
       </c>
       <c r="G1927" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52159,7 +52156,7 @@
         <v>28</v>
       </c>
       <c r="G1928" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52185,7 +52182,7 @@
         <v>28</v>
       </c>
       <c r="G1929" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52211,7 +52208,7 @@
         <v>28</v>
       </c>
       <c r="G1930" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52237,7 +52234,7 @@
         <v>28</v>
       </c>
       <c r="G1931" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52263,7 +52260,7 @@
         <v>28</v>
       </c>
       <c r="G1932" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52289,7 +52286,7 @@
         <v>28</v>
       </c>
       <c r="G1933" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52315,7 +52312,7 @@
         <v>28</v>
       </c>
       <c r="G1934" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52341,7 +52338,7 @@
         <v>28</v>
       </c>
       <c r="G1935" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52367,7 +52364,7 @@
         <v>27.6000003814697</v>
       </c>
       <c r="G1936" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52393,7 +52390,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1937" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52419,7 +52416,7 @@
         <v>28</v>
       </c>
       <c r="G1938" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52445,7 +52442,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1939" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52471,7 +52468,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1940" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52497,7 +52494,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1941" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52523,7 +52520,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1942" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52549,7 +52546,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1943" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52575,7 +52572,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1944" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52601,7 +52598,7 @@
         <v>29.3999996185303</v>
       </c>
       <c r="G1945" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52627,7 +52624,7 @@
         <v>28</v>
       </c>
       <c r="G1946" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52653,7 +52650,7 @@
         <v>28</v>
       </c>
       <c r="G1947" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52679,7 +52676,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1948" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52705,7 +52702,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1949" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52731,7 +52728,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1950" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52757,7 +52754,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G1951" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52783,7 +52780,7 @@
         <v>28</v>
       </c>
       <c r="G1952" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52809,7 +52806,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1953" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52835,7 +52832,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1954" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52861,7 +52858,7 @@
         <v>27</v>
       </c>
       <c r="G1955" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52887,7 +52884,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1956" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52913,7 +52910,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1957" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -52939,7 +52936,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1958" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -52965,7 +52962,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1959" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -52991,7 +52988,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1960" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -53017,7 +53014,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1961" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -53043,7 +53040,7 @@
         <v>28</v>
       </c>
       <c r="G1962" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -53069,7 +53066,7 @@
         <v>28</v>
       </c>
       <c r="G1963" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -53095,7 +53092,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1964" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -53121,7 +53118,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1965" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53147,7 +53144,7 @@
         <v>27</v>
       </c>
       <c r="G1966" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53173,7 +53170,7 @@
         <v>27</v>
       </c>
       <c r="G1967" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53199,7 +53196,7 @@
         <v>27</v>
       </c>
       <c r="G1968" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53225,7 +53222,7 @@
         <v>27</v>
       </c>
       <c r="G1969" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53251,7 +53248,7 @@
         <v>27</v>
       </c>
       <c r="G1970" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53277,7 +53274,7 @@
         <v>27</v>
       </c>
       <c r="G1971" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53303,7 +53300,7 @@
         <v>26.7999992370605</v>
       </c>
       <c r="G1972" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53329,7 +53326,7 @@
         <v>27.3999996185303</v>
       </c>
       <c r="G1973" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53355,7 +53352,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1974" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53381,7 +53378,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1975" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53407,7 +53404,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1976" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53433,7 +53430,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1977" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53459,7 +53456,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1978" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53485,7 +53482,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1979" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53511,7 +53508,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G1980" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53537,7 +53534,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1981" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53563,7 +53560,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1982" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53589,7 +53586,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1983" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53615,7 +53612,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1984" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53641,7 +53638,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1985" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53667,7 +53664,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1986" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53693,7 +53690,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1987" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53719,7 +53716,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1988" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53745,7 +53742,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1989" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53771,7 +53768,7 @@
         <v>26.3999996185303</v>
       </c>
       <c r="G1990" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53797,7 +53794,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1991" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53823,7 +53820,7 @@
         <v>26.6000003814697</v>
       </c>
       <c r="G1992" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53849,7 +53846,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1993" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53875,7 +53872,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1994" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53901,7 +53898,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1995" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -53927,7 +53924,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1996" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -53953,7 +53950,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1997" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -53979,7 +53976,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G1998" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -54005,7 +54002,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G1999" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -54031,7 +54028,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2000" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -54057,7 +54054,7 @@
         <v>25</v>
       </c>
       <c r="G2001" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -54083,7 +54080,7 @@
         <v>25</v>
       </c>
       <c r="G2002" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -54109,7 +54106,7 @@
         <v>25</v>
       </c>
       <c r="G2003" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -54135,7 +54132,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2004" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54161,7 +54158,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2005" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54187,7 +54184,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G2006" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54213,7 +54210,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G2007" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54239,7 +54236,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G2008" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54265,7 +54262,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G2009" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54291,7 +54288,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G2010" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54317,7 +54314,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G2011" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54343,7 +54340,7 @@
         <v>24.6000003814697</v>
       </c>
       <c r="G2012" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54369,7 +54366,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G2013" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54395,7 +54392,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2014" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54421,7 +54418,7 @@
         <v>24</v>
       </c>
       <c r="G2015" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54447,7 +54444,7 @@
         <v>24</v>
       </c>
       <c r="G2016" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54473,7 +54470,7 @@
         <v>24</v>
       </c>
       <c r="G2017" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54499,7 +54496,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G2018" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54525,7 +54522,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G2019" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54551,7 +54548,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2020" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54577,7 +54574,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G2021" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54603,7 +54600,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G2022" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54629,7 +54626,7 @@
         <v>23.6000003814697</v>
       </c>
       <c r="G2023" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54655,7 +54652,7 @@
         <v>23.3999996185303</v>
       </c>
       <c r="G2024" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54681,7 +54678,7 @@
         <v>24</v>
       </c>
       <c r="G2025" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54707,7 +54704,7 @@
         <v>24.2000007629395</v>
       </c>
       <c r="G2026" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54733,7 +54730,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2027" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54759,7 +54756,7 @@
         <v>23</v>
       </c>
       <c r="G2028" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54785,7 +54782,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2029" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54811,7 +54808,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2030" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54837,7 +54834,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2031" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54863,7 +54860,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2032" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54889,7 +54886,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2033" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54915,7 +54912,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2034" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -54941,7 +54938,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2035" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -54967,7 +54964,7 @@
         <v>23.2000007629395</v>
       </c>
       <c r="G2036" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -54993,7 +54990,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2037" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -55019,7 +55016,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G2038" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -55045,7 +55042,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2039" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -55071,7 +55068,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2040" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -55097,7 +55094,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2041" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -55123,7 +55120,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G2042" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55149,7 +55146,7 @@
         <v>22</v>
       </c>
       <c r="G2043" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55175,7 +55172,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2044" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55201,7 +55198,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G2045" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55227,7 +55224,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2046" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55253,7 +55250,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2047" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55279,7 +55276,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2048" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55305,7 +55302,7 @@
         <v>22.2000007629395</v>
       </c>
       <c r="G2049" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55331,7 +55328,7 @@
         <v>22.7999992370605</v>
       </c>
       <c r="G2050" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55357,7 +55354,7 @@
         <v>24</v>
       </c>
       <c r="G2051" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55383,7 +55380,7 @@
         <v>24</v>
       </c>
       <c r="G2052" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55409,7 +55406,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G2053" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55435,7 +55432,7 @@
         <v>24.3999996185303</v>
       </c>
       <c r="G2054" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55461,7 +55458,7 @@
         <v>24</v>
       </c>
       <c r="G2055" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55487,7 +55484,7 @@
         <v>24</v>
       </c>
       <c r="G2056" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55513,7 +55510,7 @@
         <v>24</v>
       </c>
       <c r="G2057" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55539,7 +55536,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2058" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55565,7 +55562,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2059" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55591,7 +55588,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2060" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55617,7 +55614,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2061" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55643,7 +55640,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2062" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55669,7 +55666,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2063" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55695,7 +55692,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2064" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55721,7 +55718,7 @@
         <v>23.7999992370605</v>
       </c>
       <c r="G2065" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55747,7 +55744,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2066" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55773,7 +55770,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2067" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55799,7 +55796,7 @@
         <v>25</v>
       </c>
       <c r="G2068" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55825,7 +55822,7 @@
         <v>25</v>
       </c>
       <c r="G2069" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55851,7 +55848,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2070" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55877,7 +55874,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2071" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55903,7 +55900,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2072" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -55929,7 +55926,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G2073" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -55955,7 +55952,7 @@
         <v>24.7999992370605</v>
       </c>
       <c r="G2074" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -55981,7 +55978,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2075" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -56007,7 +56004,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2076" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -56033,7 +56030,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2077" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -56059,7 +56056,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2078" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -56085,7 +56082,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2079" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -56111,7 +56108,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2080" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -56137,7 +56134,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2081" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56163,7 +56160,7 @@
         <v>25.2000007629395</v>
       </c>
       <c r="G2082" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56189,7 +56186,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2083" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56215,7 +56212,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2084" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56241,7 +56238,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2085" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56267,7 +56264,7 @@
         <v>25</v>
       </c>
       <c r="G2086" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56293,7 +56290,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2087" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56319,7 +56316,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2088" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56345,7 +56342,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2089" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56371,7 +56368,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2090" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56397,7 +56394,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2091" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56423,7 +56420,7 @@
         <v>25</v>
       </c>
       <c r="G2092" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56449,7 +56446,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G2093" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56475,7 +56472,7 @@
         <v>25</v>
       </c>
       <c r="G2094" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56501,7 +56498,7 @@
         <v>25</v>
       </c>
       <c r="G2095" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56527,7 +56524,7 @@
         <v>25</v>
       </c>
       <c r="G2096" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56553,7 +56550,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2097" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56579,7 +56576,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2098" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56605,7 +56602,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2099" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56631,7 +56628,7 @@
         <v>25.6000003814697</v>
       </c>
       <c r="G2100" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56657,7 +56654,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G2101" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56683,7 +56680,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G2102" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56709,7 +56706,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G2103" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56735,7 +56732,7 @@
         <v>27.2000007629395</v>
       </c>
       <c r="G2104" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56761,7 +56758,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G2105" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56787,7 +56784,7 @@
         <v>32</v>
       </c>
       <c r="G2106" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56813,7 +56810,7 @@
         <v>31.6000003814697</v>
       </c>
       <c r="G2107" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56839,7 +56836,7 @@
         <v>32</v>
       </c>
       <c r="G2108" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56865,7 +56862,7 @@
         <v>31</v>
       </c>
       <c r="G2109" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56891,7 +56888,7 @@
         <v>30.2000007629395</v>
       </c>
       <c r="G2110" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56917,7 +56914,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G2111" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -56943,7 +56940,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G2112" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -56969,7 +56966,7 @@
         <v>30.6000003814697</v>
       </c>
       <c r="G2113" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -56995,7 +56992,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G2114" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -57021,7 +57018,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G2115" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -57047,7 +57044,7 @@
         <v>31</v>
       </c>
       <c r="G2116" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -57073,7 +57070,7 @@
         <v>31</v>
       </c>
       <c r="G2117" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -57099,7 +57096,7 @@
         <v>31</v>
       </c>
       <c r="G2118" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -57125,7 +57122,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G2119" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57151,7 +57148,7 @@
         <v>30</v>
       </c>
       <c r="G2120" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57177,7 +57174,7 @@
         <v>30</v>
       </c>
       <c r="G2121" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57203,7 +57200,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2122" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57229,7 +57226,7 @@
         <v>29</v>
       </c>
       <c r="G2123" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57255,7 +57252,7 @@
         <v>29</v>
       </c>
       <c r="G2124" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57281,7 +57278,7 @@
         <v>29</v>
       </c>
       <c r="G2125" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57307,7 +57304,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G2126" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57333,7 +57330,7 @@
         <v>29</v>
       </c>
       <c r="G2127" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57359,7 +57356,7 @@
         <v>29</v>
       </c>
       <c r="G2128" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57385,7 +57382,7 @@
         <v>29</v>
       </c>
       <c r="G2129" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57411,7 +57408,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2130" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57437,7 +57434,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2131" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57463,7 +57460,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G2132" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57489,7 +57486,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G2133" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57515,7 +57512,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G2134" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57541,7 +57538,7 @@
         <v>31.3999996185303</v>
       </c>
       <c r="G2135" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57567,7 +57564,7 @@
         <v>30.7999992370605</v>
       </c>
       <c r="G2136" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57593,7 +57590,7 @@
         <v>31</v>
       </c>
       <c r="G2137" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57619,7 +57616,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G2138" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57645,7 +57642,7 @@
         <v>30</v>
       </c>
       <c r="G2139" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57671,7 +57668,7 @@
         <v>29.2000007629395</v>
       </c>
       <c r="G2140" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57697,7 +57694,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G2141" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57723,7 +57720,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G2142" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57749,7 +57746,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G2143" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57775,7 +57772,7 @@
         <v>31.2000007629395</v>
       </c>
       <c r="G2144" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57801,7 +57798,7 @@
         <v>31</v>
       </c>
       <c r="G2145" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57827,7 +57824,7 @@
         <v>31</v>
       </c>
       <c r="G2146" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57853,7 +57850,7 @@
         <v>31</v>
       </c>
       <c r="G2147" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57879,7 +57876,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G2148" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57905,7 +57902,7 @@
         <v>32</v>
       </c>
       <c r="G2149" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -57931,7 +57928,7 @@
         <v>32</v>
       </c>
       <c r="G2150" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -57957,7 +57954,7 @@
         <v>32</v>
       </c>
       <c r="G2151" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -57983,7 +57980,7 @@
         <v>32.4000015258789</v>
       </c>
       <c r="G2152" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -58009,7 +58006,7 @@
         <v>33.7999992370605</v>
       </c>
       <c r="G2153" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -58035,7 +58032,7 @@
         <v>34</v>
       </c>
       <c r="G2154" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -58061,7 +58058,7 @@
         <v>34</v>
       </c>
       <c r="G2155" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -58087,7 +58084,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G2156" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -58113,7 +58110,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G2157" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -58139,7 +58136,7 @@
         <v>39</v>
       </c>
       <c r="G2158" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58165,7 +58162,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2159" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58191,7 +58188,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2160" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58217,7 +58214,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2161" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58243,7 +58240,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2162" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58269,7 +58266,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2163" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58295,7 +58292,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2164" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -58321,7 +58318,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2165" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58347,7 +58344,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2166" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58373,7 +58370,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G2167" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58399,7 +58396,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G2168" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58425,7 +58422,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2169" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58451,7 +58448,7 @@
         <v>40</v>
       </c>
       <c r="G2170" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58477,7 +58474,7 @@
         <v>40</v>
       </c>
       <c r="G2171" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58503,7 +58500,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2172" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58529,7 +58526,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2173" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58555,7 +58552,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G2174" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58581,7 +58578,7 @@
         <v>38</v>
       </c>
       <c r="G2175" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58607,7 +58604,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G2176" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58633,7 +58630,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G2177" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58659,7 +58656,7 @@
         <v>35.7999992370605</v>
       </c>
       <c r="G2178" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58685,7 +58682,7 @@
         <v>36.5999984741211</v>
       </c>
       <c r="G2179" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58711,7 +58708,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G2180" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58737,7 +58734,7 @@
         <v>37.2000007629395</v>
       </c>
       <c r="G2181" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58763,7 +58760,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2182" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58789,7 +58786,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2183" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58815,7 +58812,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2184" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58841,7 +58838,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2185" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58867,7 +58864,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2186" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58893,7 +58890,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2187" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58919,7 +58916,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2188" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -58945,7 +58942,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2189" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -58971,7 +58968,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2190" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -58997,7 +58994,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2191" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -59023,7 +59020,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2192" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -59049,7 +59046,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2193" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -59075,7 +59072,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2194" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -59101,7 +59098,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G2195" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -59127,7 +59124,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G2196" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59153,7 +59150,7 @@
         <v>40</v>
       </c>
       <c r="G2197" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59179,7 +59176,7 @@
         <v>40</v>
       </c>
       <c r="G2198" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59205,7 +59202,7 @@
         <v>40</v>
       </c>
       <c r="G2199" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59231,7 +59228,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G2200" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59257,7 +59254,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G2201" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59283,7 +59280,7 @@
         <v>43.2000007629395</v>
       </c>
       <c r="G2202" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59309,7 +59306,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G2203" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59335,7 +59332,7 @@
         <v>43.7999992370605</v>
       </c>
       <c r="G2204" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59361,7 +59358,7 @@
         <v>44</v>
       </c>
       <c r="G2205" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59387,7 +59384,7 @@
         <v>44</v>
       </c>
       <c r="G2206" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59413,7 +59410,7 @@
         <v>44</v>
       </c>
       <c r="G2207" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59439,7 +59436,7 @@
         <v>44.5999984741211</v>
       </c>
       <c r="G2208" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59465,7 +59462,7 @@
         <v>44</v>
       </c>
       <c r="G2209" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59491,7 +59488,7 @@
         <v>44</v>
       </c>
       <c r="G2210" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59517,7 +59514,7 @@
         <v>44</v>
       </c>
       <c r="G2211" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59543,7 +59540,7 @@
         <v>44</v>
       </c>
       <c r="G2212" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59569,7 +59566,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2213" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59595,7 +59592,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2214" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59621,7 +59618,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2215" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59647,7 +59644,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2216" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59673,7 +59670,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2217" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59699,7 +59696,7 @@
         <v>42.7999992370605</v>
       </c>
       <c r="G2218" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59725,7 +59722,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G2219" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59751,7 +59748,7 @@
         <v>42.4000015258789</v>
       </c>
       <c r="G2220" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59777,7 +59774,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G2221" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59803,7 +59800,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2222" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59829,7 +59826,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2223" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59855,7 +59852,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2224" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59881,7 +59878,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2225" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59907,7 +59904,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G2226" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -59933,7 +59930,7 @@
         <v>39</v>
       </c>
       <c r="G2227" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -59959,7 +59956,7 @@
         <v>39</v>
       </c>
       <c r="G2228" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -59985,7 +59982,7 @@
         <v>39</v>
       </c>
       <c r="G2229" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -60011,7 +60008,7 @@
         <v>39</v>
       </c>
       <c r="G2230" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -60037,7 +60034,7 @@
         <v>39</v>
       </c>
       <c r="G2231" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -60063,7 +60060,7 @@
         <v>39</v>
       </c>
       <c r="G2232" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -60089,7 +60086,7 @@
         <v>39</v>
       </c>
       <c r="G2233" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -60115,7 +60112,7 @@
         <v>37</v>
       </c>
       <c r="G2234" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -60141,7 +60138,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2235" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60167,7 +60164,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G2236" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60193,7 +60190,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2237" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60219,7 +60216,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2238" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60245,7 +60242,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G2239" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60271,7 +60268,7 @@
         <v>38</v>
       </c>
       <c r="G2240" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60297,7 +60294,7 @@
         <v>39</v>
       </c>
       <c r="G2241" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60323,7 +60320,7 @@
         <v>42</v>
       </c>
       <c r="G2242" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60349,7 +60346,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G2243" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60375,7 +60372,7 @@
         <v>41.2000007629395</v>
       </c>
       <c r="G2244" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60401,7 +60398,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G2245" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60427,7 +60424,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G2246" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60453,7 +60450,7 @@
         <v>41.4000015258789</v>
       </c>
       <c r="G2247" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60479,7 +60476,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G2248" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60505,7 +60502,7 @@
         <v>41.7999992370605</v>
       </c>
       <c r="G2249" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60531,7 +60528,7 @@
         <v>41.5999984741211</v>
       </c>
       <c r="G2250" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60557,7 +60554,7 @@
         <v>41</v>
       </c>
       <c r="G2251" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60583,7 +60580,7 @@
         <v>41</v>
       </c>
       <c r="G2252" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60609,7 +60606,7 @@
         <v>40</v>
       </c>
       <c r="G2253" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60635,7 +60632,7 @@
         <v>40</v>
       </c>
       <c r="G2254" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60661,7 +60658,7 @@
         <v>40.2000007629395</v>
       </c>
       <c r="G2255" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60687,7 +60684,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2256" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60713,7 +60710,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2257" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60739,7 +60736,7 @@
         <v>38</v>
       </c>
       <c r="G2258" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60765,7 +60762,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G2259" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60791,7 +60788,7 @@
         <v>38.5999984741211</v>
       </c>
       <c r="G2260" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60817,7 +60814,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2261" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60843,7 +60840,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2262" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60869,7 +60866,7 @@
         <v>40.4000015258789</v>
       </c>
       <c r="G2263" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60895,7 +60892,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2264" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60921,7 +60918,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2265" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -60947,7 +60944,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2266" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -60973,7 +60970,7 @@
         <v>39.7999992370605</v>
       </c>
       <c r="G2267" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -60999,7 +60996,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2268" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -61025,7 +61022,7 @@
         <v>40</v>
       </c>
       <c r="G2269" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -61051,7 +61048,7 @@
         <v>40</v>
       </c>
       <c r="G2270" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -61077,7 +61074,7 @@
         <v>40</v>
       </c>
       <c r="G2271" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -61103,7 +61100,7 @@
         <v>40</v>
       </c>
       <c r="G2272" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -61129,7 +61126,7 @@
         <v>40.5999984741211</v>
       </c>
       <c r="G2273" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61155,7 +61152,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2274" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61181,7 +61178,7 @@
         <v>39.4000015258789</v>
       </c>
       <c r="G2275" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61207,7 +61204,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2276" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61233,7 +61230,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G2277" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61259,7 +61256,7 @@
         <v>38</v>
       </c>
       <c r="G2278" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61285,7 +61282,7 @@
         <v>38</v>
       </c>
       <c r="G2279" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61311,7 +61308,7 @@
         <v>38.7999992370605</v>
       </c>
       <c r="G2280" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61337,7 +61334,7 @@
         <v>38</v>
       </c>
       <c r="G2281" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61363,7 +61360,7 @@
         <v>38</v>
       </c>
       <c r="G2282" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61389,7 +61386,7 @@
         <v>38</v>
       </c>
       <c r="G2283" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61415,7 +61412,7 @@
         <v>38</v>
       </c>
       <c r="G2284" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61441,7 +61438,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G2285" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61467,7 +61464,7 @@
         <v>37</v>
       </c>
       <c r="G2286" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61493,7 +61490,7 @@
         <v>36.7999992370605</v>
       </c>
       <c r="G2287" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61519,7 +61516,7 @@
         <v>37</v>
       </c>
       <c r="G2288" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61545,7 +61542,7 @@
         <v>38</v>
       </c>
       <c r="G2289" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61571,7 +61568,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G2290" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61597,7 +61594,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G2291" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61623,7 +61620,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G2292" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61649,7 +61646,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G2293" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61675,7 +61672,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G2294" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61701,7 +61698,7 @@
         <v>38</v>
       </c>
       <c r="G2295" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61727,7 +61724,7 @@
         <v>37.4000015258789</v>
       </c>
       <c r="G2296" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61753,7 +61750,7 @@
         <v>37</v>
       </c>
       <c r="G2297" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61779,7 +61776,7 @@
         <v>37</v>
       </c>
       <c r="G2298" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61805,7 +61802,7 @@
         <v>37.7999992370605</v>
       </c>
       <c r="G2299" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61831,7 +61828,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2300" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61857,7 +61854,7 @@
         <v>38.4000015258789</v>
       </c>
       <c r="G2301" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61883,7 +61880,7 @@
         <v>37.5999984741211</v>
       </c>
       <c r="G2302" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61909,7 +61906,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2303" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -61935,7 +61932,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2304" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -61961,7 +61958,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2305" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -61987,7 +61984,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2306" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -62013,7 +62010,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2307" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -62039,7 +62036,7 @@
         <v>39.2000007629395</v>
       </c>
       <c r="G2308" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -62065,7 +62062,7 @@
         <v>39</v>
       </c>
       <c r="G2309" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -62073,13 +62070,13 @@
     </row>
     <row r="2310">
       <c r="A2310" s="1" t="n">
-        <v>46028.6837268519</v>
+        <v>46028.3333333333</v>
       </c>
       <c r="B2310" t="n">
-        <v>1250</v>
+        <v>2250</v>
       </c>
       <c r="C2310" t="n">
-        <v>39.4000015258789</v>
+        <v>39.5999984741211</v>
       </c>
       <c r="D2310" t="n">
         <v>39.4000015258789</v>
@@ -62091,7 +62088,7 @@
         <v>39.5999984741211</v>
       </c>
       <c r="G2310" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>

--- a/data/FPE.MI.xlsx
+++ b/data/FPE.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="562">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="563">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46539187431335</t>
+    <t xml:space="preserve">2.46539163589478</t>
   </si>
   <si>
     <t xml:space="preserve">FPE.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42625832557678</t>
+    <t xml:space="preserve">2.42625856399536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43408489227295</t>
+    <t xml:space="preserve">2.43408513069153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41060543060303</t>
+    <t xml:space="preserve">2.41060519218445</t>
   </si>
   <si>
     <t xml:space="preserve">2.45756530761719</t>
@@ -59,16 +59,16 @@
     <t xml:space="preserve">2.39495205879211</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33233857154846</t>
+    <t xml:space="preserve">2.33233904838562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41843199729919</t>
+    <t xml:space="preserve">2.41843175888062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35581874847412</t>
+    <t xml:space="preserve">2.3558189868927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37147188186646</t>
+    <t xml:space="preserve">2.37147212028503</t>
   </si>
   <si>
     <t xml:space="preserve">2.50452518463135</t>
@@ -77,10 +77,10 @@
     <t xml:space="preserve">2.36364531517029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44973826408386</t>
+    <t xml:space="preserve">2.44973850250244</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37303733825684</t>
+    <t xml:space="preserve">2.37303757667542</t>
   </si>
   <si>
     <t xml:space="preserve">2.34955763816833</t>
@@ -107,37 +107,37 @@
     <t xml:space="preserve">2.38556003570557</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44191193580627</t>
+    <t xml:space="preserve">2.4419116973877</t>
   </si>
   <si>
     <t xml:space="preserve">2.78002262115479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36702036857605</t>
+    <t xml:space="preserve">3.36702084541321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62529993057251</t>
+    <t xml:space="preserve">3.62529969215393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31066870689392</t>
+    <t xml:space="preserve">3.3106689453125</t>
   </si>
   <si>
     <t xml:space="preserve">3.25588202476501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20266103744507</t>
+    <t xml:space="preserve">3.20266151428223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05239009857178</t>
+    <t xml:space="preserve">3.0523898601532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09152293205261</t>
+    <t xml:space="preserve">3.09152317047119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04456305503845</t>
+    <t xml:space="preserve">3.04456329345703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03673672676086</t>
+    <t xml:space="preserve">3.03673696517944</t>
   </si>
   <si>
     <t xml:space="preserve">3.03830170631409</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">3.15413618087769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30910396575928</t>
+    <t xml:space="preserve">3.3091037273407</t>
   </si>
   <si>
     <t xml:space="preserve">3.30284190177917</t>
@@ -155,19 +155,19 @@
     <t xml:space="preserve">3.35762858390808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57677459716797</t>
+    <t xml:space="preserve">3.57677483558655</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52198815345764</t>
+    <t xml:space="preserve">3.52198767662048</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40458869934082</t>
+    <t xml:space="preserve">3.40458822250366</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59242796897888</t>
+    <t xml:space="preserve">3.59242844581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58460116386414</t>
+    <t xml:space="preserve">3.58460164070129</t>
   </si>
   <si>
     <t xml:space="preserve">3.67852067947388</t>
@@ -176,31 +176,31 @@
     <t xml:space="preserve">3.60025429725647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59555864334106</t>
+    <t xml:space="preserve">3.59555840492249</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32632231712341</t>
+    <t xml:space="preserve">3.32632207870483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29501557350159</t>
+    <t xml:space="preserve">3.29501581192017</t>
   </si>
   <si>
     <t xml:space="preserve">3.3748471736908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38267374038696</t>
+    <t xml:space="preserve">3.3826744556427</t>
   </si>
   <si>
     <t xml:space="preserve">3.44372200965881</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5908625125885</t>
+    <t xml:space="preserve">3.59086227416992</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47972440719604</t>
+    <t xml:space="preserve">3.47972416877747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42650270462036</t>
+    <t xml:space="preserve">3.42650318145752</t>
   </si>
   <si>
     <t xml:space="preserve">3.41241526603699</t>
@@ -212,13 +212,13 @@
     <t xml:space="preserve">3.21048808097839</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28405857086182</t>
+    <t xml:space="preserve">3.28405833244324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16196298599243</t>
+    <t xml:space="preserve">3.16196274757385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20892262458801</t>
+    <t xml:space="preserve">3.20892238616943</t>
   </si>
   <si>
     <t xml:space="preserve">3.13848304748535</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">3.23240256309509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31849503517151</t>
+    <t xml:space="preserve">3.31849527359009</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27623176574707</t>
+    <t xml:space="preserve">3.27623128890991</t>
   </si>
   <si>
     <t xml:space="preserve">3.18857336044312</t>
@@ -242,40 +242,40 @@
     <t xml:space="preserve">3.11500310897827</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00073385238647</t>
+    <t xml:space="preserve">3.00073409080505</t>
   </si>
   <si>
     <t xml:space="preserve">2.97412347793579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06021666526794</t>
+    <t xml:space="preserve">3.06021642684937</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90368390083313</t>
+    <t xml:space="preserve">2.90368366241455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8958568572998</t>
+    <t xml:space="preserve">2.89585709571838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82854843139648</t>
+    <t xml:space="preserve">2.82854819297791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83637428283691</t>
+    <t xml:space="preserve">2.83637452125549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90994501113892</t>
+    <t xml:space="preserve">2.90994477272034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06491208076477</t>
+    <t xml:space="preserve">3.06491231918335</t>
   </si>
   <si>
     <t xml:space="preserve">3.13065624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14474415779114</t>
+    <t xml:space="preserve">3.14474439620972</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21361875534058</t>
+    <t xml:space="preserve">3.21361827850342</t>
   </si>
   <si>
     <t xml:space="preserve">3.28562355041504</t>
@@ -287,85 +287,85 @@
     <t xml:space="preserve">3.36388969421387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91332030296326</t>
+    <t xml:space="preserve">3.91332006454468</t>
   </si>
   <si>
     <t xml:space="preserve">4.34378528594971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7938175201416</t>
+    <t xml:space="preserve">4.79381656646729</t>
   </si>
   <si>
     <t xml:space="preserve">5.47864818572998</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09303998947144</t>
+    <t xml:space="preserve">6.09303855895996</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41603469848633</t>
+    <t xml:space="preserve">5.41603565216064</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71344757080078</t>
+    <t xml:space="preserve">5.71344709396362</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56865501403809</t>
+    <t xml:space="preserve">5.56865406036377</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41994857788086</t>
+    <t xml:space="preserve">5.4199481010437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16558265686035</t>
+    <t xml:space="preserve">5.16558218002319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94643640518188</t>
+    <t xml:space="preserve">4.94643688201904</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70381021499634</t>
+    <t xml:space="preserve">4.70381164550781</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6764178276062</t>
+    <t xml:space="preserve">4.67641735076904</t>
   </si>
   <si>
     <t xml:space="preserve">5.0090503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55691528320312</t>
+    <t xml:space="preserve">5.55691432952881</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30646276473999</t>
+    <t xml:space="preserve">5.30646228790283</t>
   </si>
   <si>
     <t xml:space="preserve">5.22428274154663</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19688940048218</t>
+    <t xml:space="preserve">5.19688987731934</t>
   </si>
   <si>
     <t xml:space="preserve">5.32211589813232</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47082185745239</t>
+    <t xml:space="preserve">5.47082138061523</t>
   </si>
   <si>
     <t xml:space="preserve">5.36907482147217</t>
   </si>
   <si>
-    <t xml:space="preserve">5.29080867767334</t>
+    <t xml:space="preserve">5.2908091545105</t>
   </si>
   <si>
     <t xml:space="preserve">5.1734094619751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09514284133911</t>
+    <t xml:space="preserve">5.09514331817627</t>
   </si>
   <si>
-    <t xml:space="preserve">5.22036933898926</t>
+    <t xml:space="preserve">5.2203688621521</t>
   </si>
   <si>
     <t xml:space="preserve">5.10296964645386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9933967590332</t>
+    <t xml:space="preserve">4.99339628219604</t>
   </si>
   <si>
     <t xml:space="preserve">5.15384340286255</t>
@@ -377,22 +377,22 @@
     <t xml:space="preserve">4.7585973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77033710479736</t>
+    <t xml:space="preserve">4.77033615112305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8642578125</t>
+    <t xml:space="preserve">4.86425733566284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88773679733276</t>
+    <t xml:space="preserve">4.88773632049561</t>
   </si>
   <si>
     <t xml:space="preserve">4.83295059204102</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75468301773071</t>
+    <t xml:space="preserve">4.75468444824219</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82903671264648</t>
+    <t xml:space="preserve">4.82903718948364</t>
   </si>
   <si>
     <t xml:space="preserve">4.7233772277832</t>
@@ -407,46 +407,46 @@
     <t xml:space="preserve">4.8759970664978</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03644275665283</t>
+    <t xml:space="preserve">5.03644371032715</t>
   </si>
   <si>
     <t xml:space="preserve">4.92686986923218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81338453292847</t>
+    <t xml:space="preserve">4.81338405609131</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86034345626831</t>
+    <t xml:space="preserve">4.86034393310547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00122308731079</t>
+    <t xml:space="preserve">5.00122356414795</t>
   </si>
   <si>
     <t xml:space="preserve">4.77425098419189</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82121086120605</t>
+    <t xml:space="preserve">4.8212103843689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69989824295044</t>
+    <t xml:space="preserve">4.69989728927612</t>
   </si>
   <si>
     <t xml:space="preserve">4.69598436355591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90730333328247</t>
+    <t xml:space="preserve">4.90730381011963</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20471572875977</t>
+    <t xml:space="preserve">5.20471620559692</t>
   </si>
   <si>
-    <t xml:space="preserve">5.43951511383057</t>
+    <t xml:space="preserve">5.43951559066772</t>
   </si>
   <si>
     <t xml:space="preserve">5.28298234939575</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24384880065918</t>
+    <t xml:space="preserve">5.24384927749634</t>
   </si>
   <si>
     <t xml:space="preserve">5.36124849319458</t>
@@ -461,40 +461,40 @@
     <t xml:space="preserve">5.63518095016479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96991682052612</t>
+    <t xml:space="preserve">4.96991586685181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93078374862671</t>
+    <t xml:space="preserve">4.93078327178955</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85251665115356</t>
+    <t xml:space="preserve">4.85251712799072</t>
   </si>
   <si>
     <t xml:space="preserve">5.12644910812378</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04818344116211</t>
+    <t xml:space="preserve">5.04818248748779</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08731555938721</t>
+    <t xml:space="preserve">5.08731603622437</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59604835510254</t>
+    <t xml:space="preserve">5.59604787826538</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26159763336182</t>
+    <t xml:space="preserve">5.26159715652466</t>
   </si>
   <si>
     <t xml:space="preserve">5.42104005813599</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34131860733032</t>
+    <t xml:space="preserve">5.34131908416748</t>
   </si>
   <si>
     <t xml:space="preserve">5.22173690795898</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14201593399048</t>
+    <t xml:space="preserve">5.14201498031616</t>
   </si>
   <si>
     <t xml:space="preserve">5.1021556854248</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">5.38117933273315</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30145740509033</t>
+    <t xml:space="preserve">5.30145788192749</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9028525352478</t>
+    <t xml:space="preserve">4.90285205841064</t>
   </si>
   <si>
     <t xml:space="preserve">5.50076150894165</t>
@@ -518,37 +518,37 @@
     <t xml:space="preserve">5.4608998298645</t>
   </si>
   <si>
-    <t xml:space="preserve">5.580482006073</t>
+    <t xml:space="preserve">5.58048152923584</t>
   </si>
   <si>
     <t xml:space="preserve">5.54062128067017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62034273147583</t>
+    <t xml:space="preserve">5.62034320831299</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94271183013916</t>
+    <t xml:space="preserve">4.94271278381348</t>
   </si>
   <si>
     <t xml:space="preserve">4.98257350921631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82313108444214</t>
+    <t xml:space="preserve">4.8231315612793</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06229400634766</t>
+    <t xml:space="preserve">5.06229448318481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02243375778198</t>
+    <t xml:space="preserve">5.02243328094482</t>
   </si>
   <si>
     <t xml:space="preserve">4.74340963363647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78327035903931</t>
+    <t xml:space="preserve">4.78326988220215</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86299180984497</t>
+    <t xml:space="preserve">4.86299133300781</t>
   </si>
   <si>
     <t xml:space="preserve">5.73992443084717</t>
@@ -560,10 +560,10 @@
     <t xml:space="preserve">5.70006370544434</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66020345687866</t>
+    <t xml:space="preserve">5.66020250320435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77978515625</t>
+    <t xml:space="preserve">5.77978467941284</t>
   </si>
   <si>
     <t xml:space="preserve">5.85950613021851</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">5.979088306427</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29797220230103</t>
+    <t xml:space="preserve">6.29797267913818</t>
   </si>
   <si>
     <t xml:space="preserve">6.13853025436401</t>
@@ -581,25 +581,25 @@
     <t xml:space="preserve">6.05880880355835</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21825170516968</t>
+    <t xml:space="preserve">6.21825122833252</t>
   </si>
   <si>
     <t xml:space="preserve">6.09867000579834</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38518476486206</t>
+    <t xml:space="preserve">6.38518524169922</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25998497009277</t>
+    <t xml:space="preserve">6.25998449325562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30171775817871</t>
+    <t xml:space="preserve">6.30171823501587</t>
   </si>
   <si>
     <t xml:space="preserve">6.17651844024658</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42691802978516</t>
+    <t xml:space="preserve">6.426917552948</t>
   </si>
   <si>
     <t xml:space="preserve">6.34345102310181</t>
@@ -611,10 +611,10 @@
     <t xml:space="preserve">5.9678521156311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00958490371704</t>
+    <t xml:space="preserve">6.0095853805542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13478469848633</t>
+    <t xml:space="preserve">6.13478517532349</t>
   </si>
   <si>
     <t xml:space="preserve">6.05131816864014</t>
@@ -623,58 +623,55 @@
     <t xml:space="preserve">5.92611885070801</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09305143356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21825122833252</t>
+    <t xml:space="preserve">6.09305238723755</t>
   </si>
   <si>
     <t xml:space="preserve">6.51038408279419</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84265232086182</t>
+    <t xml:space="preserve">5.84265279769897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88438606262207</t>
+    <t xml:space="preserve">5.88438558578491</t>
   </si>
   <si>
     <t xml:space="preserve">7.05291557312012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09624576568604</t>
+    <t xml:space="preserve">8.09624671936035</t>
   </si>
   <si>
-    <t xml:space="preserve">7.804114818573</t>
+    <t xml:space="preserve">7.80411386489868</t>
   </si>
   <si>
     <t xml:space="preserve">7.63718128204346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55371570587158</t>
+    <t xml:space="preserve">7.55371522903442</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3450493812561</t>
+    <t xml:space="preserve">7.34504890441895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17811632156372</t>
+    <t xml:space="preserve">7.17811584472656</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51198196411133</t>
+    <t xml:space="preserve">7.51198148727417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47024822235107</t>
+    <t xml:space="preserve">7.47024869918823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30331563949585</t>
+    <t xml:space="preserve">7.30331516265869</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42851495742798</t>
+    <t xml:space="preserve">7.42851543426514</t>
   </si>
   <si>
     <t xml:space="preserve">7.2615818977356</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38678312301636</t>
+    <t xml:space="preserve">7.3867826461792</t>
   </si>
   <si>
     <t xml:space="preserve">6.96944999694824</t>
@@ -686,7 +683,7 @@
     <t xml:space="preserve">7.59544801712036</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76238107681274</t>
+    <t xml:space="preserve">7.7623815536499</t>
   </si>
   <si>
     <t xml:space="preserve">7.84584760665894</t>
@@ -698,28 +695,28 @@
     <t xml:space="preserve">7.01118278503418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09464979171753</t>
+    <t xml:space="preserve">7.09464931488037</t>
   </si>
   <si>
     <t xml:space="preserve">6.9277172088623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76078319549561</t>
+    <t xml:space="preserve">6.76078367233276</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80251693725586</t>
+    <t xml:space="preserve">6.8025164604187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71905040740967</t>
+    <t xml:space="preserve">6.71904993057251</t>
   </si>
   <si>
     <t xml:space="preserve">6.8442497253418</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59385013580322</t>
+    <t xml:space="preserve">6.59385061264038</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67731666564941</t>
+    <t xml:space="preserve">6.67731714248657</t>
   </si>
   <si>
     <t xml:space="preserve">6.55211687088013</t>
@@ -737,22 +734,22 @@
     <t xml:space="preserve">5.67571926116943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59225225448608</t>
+    <t xml:space="preserve">5.5922532081604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6339864730835</t>
+    <t xml:space="preserve">5.63398599624634</t>
   </si>
   <si>
     <t xml:space="preserve">5.46705341339111</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5505199432373</t>
+    <t xml:space="preserve">5.55052042007446</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17492151260376</t>
+    <t xml:space="preserve">5.1749210357666</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25838804244995</t>
+    <t xml:space="preserve">5.25838708877563</t>
   </si>
   <si>
     <t xml:space="preserve">5.38358736038208</t>
@@ -764,22 +761,22 @@
     <t xml:space="preserve">7.47247123718262</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25269269943237</t>
+    <t xml:space="preserve">7.25269174575806</t>
   </si>
   <si>
     <t xml:space="preserve">7.29664850234985</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20873689651489</t>
+    <t xml:space="preserve">7.20873594284058</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16478109359741</t>
+    <t xml:space="preserve">7.16478061676025</t>
   </si>
   <si>
     <t xml:space="preserve">7.07686948776245</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98895788192749</t>
+    <t xml:space="preserve">6.98895835876465</t>
   </si>
   <si>
     <t xml:space="preserve">7.03291368484497</t>
@@ -806,37 +803,40 @@
     <t xml:space="preserve">6.63731241226196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12082481384277</t>
+    <t xml:space="preserve">7.12082576751709</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34060382843018</t>
+    <t xml:space="preserve">7.34060430526733</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5164270401001</t>
+    <t xml:space="preserve">7.51642751693726</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56038284301758</t>
+    <t xml:space="preserve">7.56038188934326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42851495742798</t>
   </si>
   <si>
     <t xml:space="preserve">7.7362060546875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69224977493286</t>
+    <t xml:space="preserve">7.6922492980957</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64829349517822</t>
+    <t xml:space="preserve">7.64829254150391</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78247404098511</t>
+    <t xml:space="preserve">7.78247308731079</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82720136642456</t>
+    <t xml:space="preserve">7.8272008895874</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73774719238281</t>
+    <t xml:space="preserve">7.73774671554565</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69302082061768</t>
+    <t xml:space="preserve">7.69301986694336</t>
   </si>
   <si>
     <t xml:space="preserve">7.64829444885254</t>
@@ -857,16 +857,16 @@
     <t xml:space="preserve">8.2297420501709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76646614074707</t>
+    <t xml:space="preserve">8.76646518707275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58755779266357</t>
+    <t xml:space="preserve">8.58755683898926</t>
   </si>
   <si>
     <t xml:space="preserve">8.36392307281494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63228321075439</t>
+    <t xml:space="preserve">8.63228416442871</t>
   </si>
   <si>
     <t xml:space="preserve">8.54283142089844</t>
@@ -878,25 +878,25 @@
     <t xml:space="preserve">8.27446937561035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45337581634521</t>
+    <t xml:space="preserve">8.45337677001953</t>
   </si>
   <si>
     <t xml:space="preserve">8.67701053619385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49810314178467</t>
+    <t xml:space="preserve">8.49810409545898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81119251251221</t>
+    <t xml:space="preserve">8.81119155883789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7217378616333</t>
+    <t xml:space="preserve">8.72173881530762</t>
   </si>
   <si>
     <t xml:space="preserve">8.85591888427734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03482723236084</t>
+    <t xml:space="preserve">9.03482627868652</t>
   </si>
   <si>
     <t xml:space="preserve">10.3766326904297</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">11.4500770568848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.734447479248</t>
+    <t xml:space="preserve">10.7344465255737</t>
   </si>
   <si>
     <t xml:space="preserve">11.0922622680664</t>
@@ -926,16 +926,16 @@
     <t xml:space="preserve">11.5395307540894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2711706161499</t>
+    <t xml:space="preserve">11.2711687088013</t>
   </si>
   <si>
     <t xml:space="preserve">10.5555400848389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2871780395508</t>
+    <t xml:space="preserve">10.2871789932251</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0028085708618</t>
+    <t xml:space="preserve">11.0028095245361</t>
   </si>
   <si>
     <t xml:space="preserve">10.6449928283691</t>
@@ -950,13 +950,13 @@
     <t xml:space="preserve">10.1977252960205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75045585632324</t>
+    <t xml:space="preserve">9.75045680999756</t>
   </si>
   <si>
-    <t xml:space="preserve">10.018816947937</t>
+    <t xml:space="preserve">10.0188159942627</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6129760742188</t>
+    <t xml:space="preserve">12.6129751205444</t>
   </si>
   <si>
     <t xml:space="preserve">12.9707899093628</t>
@@ -977,19 +977,19 @@
     <t xml:space="preserve">13.0602445602417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4180593490601</t>
+    <t xml:space="preserve">13.4180583953857</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8813362121582</t>
+    <t xml:space="preserve">12.8813371658325</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7918825149536</t>
+    <t xml:space="preserve">12.7918834686279</t>
   </si>
   <si>
-    <t xml:space="preserve">12.702428817749</t>
+    <t xml:space="preserve">12.7024278640747</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1496963500977</t>
+    <t xml:space="preserve">13.149697303772</t>
   </si>
   <si>
     <t xml:space="preserve">13.3286046981812</t>
@@ -998,10 +998,10 @@
     <t xml:space="preserve">13.9547805786133</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5969667434692</t>
+    <t xml:space="preserve">13.5969657897949</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6864204406738</t>
+    <t xml:space="preserve">13.6864213943481</t>
   </si>
   <si>
     <t xml:space="preserve">13.865327835083</t>
@@ -1016,16 +1016,16 @@
     <t xml:space="preserve">15.2071342468262</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5809574127197</t>
+    <t xml:space="preserve">14.5809564590454</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7598657608032</t>
+    <t xml:space="preserve">14.7598638534546</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4915037155151</t>
+    <t xml:space="preserve">14.4915046691895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5400886535645</t>
+    <t xml:space="preserve">14.5400876998901</t>
   </si>
   <si>
     <t xml:space="preserve">14.3560371398926</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">14.1719846725464</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8161659240723</t>
+    <t xml:space="preserve">14.8161668777466</t>
   </si>
   <si>
     <t xml:space="preserve">14.6321134567261</t>
@@ -1049,22 +1049,22 @@
     <t xml:space="preserve">15.5523738861084</t>
   </si>
   <si>
-    <t xml:space="preserve">16.104528427124</t>
+    <t xml:space="preserve">16.1045265197754</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3806037902832</t>
+    <t xml:space="preserve">16.3806056976318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9204769134521</t>
+    <t xml:space="preserve">15.9204750061035</t>
   </si>
   <si>
     <t xml:space="preserve">17.2088394165039</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3008632659912</t>
+    <t xml:space="preserve">17.3008651733398</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4849166870117</t>
+    <t xml:space="preserve">17.4849147796631</t>
   </si>
   <si>
     <t xml:space="preserve">17.5769424438477</t>
@@ -1079,13 +1079,13 @@
     <t xml:space="preserve">19.1413822174072</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6935386657715</t>
+    <t xml:space="preserve">19.6935367584229</t>
   </si>
   <si>
     <t xml:space="preserve">20.0616397857666</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5340538024902</t>
+    <t xml:space="preserve">21.5340557098389</t>
   </si>
   <si>
     <t xml:space="preserve">23.3745727539062</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">22.270263671875</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8224182128906</t>
+    <t xml:space="preserve">22.822416305542</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6137962341309</t>
+    <t xml:space="preserve">20.6137943267822</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3254356384277</t>
+    <t xml:space="preserve">19.3254337310791</t>
   </si>
   <si>
     <t xml:space="preserve">21.902156829834</t>
@@ -1121,10 +1121,10 @@
     <t xml:space="preserve">23.9267272949219</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6629333496094</t>
+    <t xml:space="preserve">24.662935256958</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8469867706299</t>
+    <t xml:space="preserve">24.8469848632812</t>
   </si>
   <si>
     <t xml:space="preserve">24.2948303222656</t>
@@ -1136,28 +1136,28 @@
     <t xml:space="preserve">23.1905212402344</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2150897979736</t>
+    <t xml:space="preserve">25.215087890625</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4543151855469</t>
+    <t xml:space="preserve">22.4543132781982</t>
   </si>
   <si>
     <t xml:space="preserve">24.4788837432861</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9512977600098</t>
+    <t xml:space="preserve">25.9512958526611</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5034503936768</t>
+    <t xml:space="preserve">26.5034523010254</t>
   </si>
   <si>
     <t xml:space="preserve">27.975866317749</t>
   </si>
   <si>
-    <t xml:space="preserve">30.9206924438477</t>
+    <t xml:space="preserve">30.920690536499</t>
   </si>
   <si>
-    <t xml:space="preserve">29.0801773071289</t>
+    <t xml:space="preserve">29.0801753997803</t>
   </si>
   <si>
     <t xml:space="preserve">30.736644744873</t>
@@ -1169,16 +1169,16 @@
     <t xml:space="preserve">29.2642269134521</t>
   </si>
   <si>
-    <t xml:space="preserve">31.4728527069092</t>
+    <t xml:space="preserve">31.4728507995605</t>
   </si>
   <si>
-    <t xml:space="preserve">34.2336235046387</t>
+    <t xml:space="preserve">34.2336273193359</t>
   </si>
   <si>
     <t xml:space="preserve">34.7857818603516</t>
   </si>
   <si>
-    <t xml:space="preserve">33.8655166625977</t>
+    <t xml:space="preserve">33.8655204772949</t>
   </si>
   <si>
     <t xml:space="preserve">33.4974174499512</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">27.4237098693848</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6875019073486</t>
+    <t xml:space="preserve">26.6875038146973</t>
   </si>
   <si>
     <t xml:space="preserve">25.5831928253174</t>
@@ -1199,10 +1199,10 @@
     <t xml:space="preserve">26.3194007873535</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7918148040771</t>
+    <t xml:space="preserve">27.7918167114258</t>
   </si>
   <si>
-    <t xml:space="preserve">28.8961238861084</t>
+    <t xml:space="preserve">28.896125793457</t>
   </si>
   <si>
     <t xml:space="preserve">29.4482803344727</t>
@@ -1223,10 +1223,10 @@
     <t xml:space="preserve">26.8715553283691</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3991413116455</t>
+    <t xml:space="preserve">25.3991432189941</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7672443389893</t>
+    <t xml:space="preserve">25.7672462463379</t>
   </si>
   <si>
     <t xml:space="preserve">25.0310382843018</t>
@@ -1238,55 +1238,58 @@
     <t xml:space="preserve">30.5525894165039</t>
   </si>
   <si>
-    <t xml:space="preserve">29.6323318481445</t>
+    <t xml:space="preserve">29.6323337554932</t>
   </si>
   <si>
     <t xml:space="preserve">30.0004329681396</t>
   </si>
   <si>
-    <t xml:space="preserve">32.3931083679199</t>
+    <t xml:space="preserve">32.3931121826172</t>
   </si>
   <si>
-    <t xml:space="preserve">32.209056854248</t>
+    <t xml:space="preserve">32.2090530395508</t>
   </si>
   <si>
-    <t xml:space="preserve">31.2887954711914</t>
+    <t xml:space="preserve">31.2887992858887</t>
   </si>
   <si>
-    <t xml:space="preserve">31.6569004058838</t>
+    <t xml:space="preserve">31.6569023132324</t>
   </si>
   <si>
-    <t xml:space="preserve">32.0250015258789</t>
+    <t xml:space="preserve">32.0250053405762</t>
   </si>
   <si>
     <t xml:space="preserve">32.0337677001953</t>
   </si>
   <si>
-    <t xml:space="preserve">32.5990715026855</t>
+    <t xml:space="preserve">32.5990676879883</t>
   </si>
   <si>
-    <t xml:space="preserve">33.1643714904785</t>
+    <t xml:space="preserve">33.1643753051758</t>
   </si>
   <si>
-    <t xml:space="preserve">32.4106369018555</t>
+    <t xml:space="preserve">31.6568984985352</t>
   </si>
   <si>
-    <t xml:space="preserve">32.7875022888184</t>
+    <t xml:space="preserve">32.4106407165527</t>
   </si>
   <si>
-    <t xml:space="preserve">32.9759407043457</t>
+    <t xml:space="preserve">32.7875061035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9759368896484</t>
   </si>
   <si>
     <t xml:space="preserve">30.9031639099121</t>
   </si>
   <si>
-    <t xml:space="preserve">31.8453369140625</t>
+    <t xml:space="preserve">31.8453350067139</t>
   </si>
   <si>
     <t xml:space="preserve">30.714729309082</t>
   </si>
   <si>
-    <t xml:space="preserve">30.5262985229492</t>
+    <t xml:space="preserve">30.5263004302979</t>
   </si>
   <si>
     <t xml:space="preserve">31.2800331115723</t>
@@ -1295,7 +1298,7 @@
     <t xml:space="preserve">30.1494293212891</t>
   </si>
   <si>
-    <t xml:space="preserve">30.3378639221191</t>
+    <t xml:space="preserve">30.3378658294678</t>
   </si>
   <si>
     <t xml:space="preserve">29.395694732666</t>
@@ -1322,7 +1325,7 @@
     <t xml:space="preserve">28.2650909423828</t>
   </si>
   <si>
-    <t xml:space="preserve">27.6997890472412</t>
+    <t xml:space="preserve">27.6997871398926</t>
   </si>
   <si>
     <t xml:space="preserve">28.0766563415527</t>
@@ -1334,7 +1337,7 @@
     <t xml:space="preserve">25.2501468658447</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3079776763916</t>
+    <t xml:space="preserve">24.307975769043</t>
   </si>
   <si>
     <t xml:space="preserve">23.9311103820801</t>
@@ -1355,7 +1358,7 @@
     <t xml:space="preserve">23.7426776885986</t>
   </si>
   <si>
-    <t xml:space="preserve">23.177375793457</t>
+    <t xml:space="preserve">23.1773738861084</t>
   </si>
   <si>
     <t xml:space="preserve">22.6120719909668</t>
@@ -1370,10 +1373,10 @@
     <t xml:space="preserve">22.2352046966553</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0467700958252</t>
+    <t xml:space="preserve">22.0467720031738</t>
   </si>
   <si>
-    <t xml:space="preserve">22.8005084991455</t>
+    <t xml:space="preserve">22.8005065917969</t>
   </si>
   <si>
     <t xml:space="preserve">22.988941192627</t>
@@ -1388,19 +1391,19 @@
     <t xml:space="preserve">25.6270160675049</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3807506561279</t>
+    <t xml:space="preserve">26.3807525634766</t>
   </si>
   <si>
-    <t xml:space="preserve">27.134485244751</t>
+    <t xml:space="preserve">27.1344871520996</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9460525512695</t>
+    <t xml:space="preserve">26.9460544586182</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3229198455811</t>
+    <t xml:space="preserve">27.3229217529297</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1923160552979</t>
+    <t xml:space="preserve">26.1923179626465</t>
   </si>
   <si>
     <t xml:space="preserve">26.7576179504395</t>
@@ -18642,7 +18645,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G639" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19162,7 +19165,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G659" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -19188,7 +19191,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G660" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -19292,7 +19295,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G664" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -19500,7 +19503,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G672" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -19526,7 +19529,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G673" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20020,7 +20023,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G692" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -20046,7 +20049,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G693" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -20124,7 +20127,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G696" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -20150,7 +20153,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G697" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -20280,7 +20283,7 @@
         <v>7</v>
       </c>
       <c r="G702" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -20306,7 +20309,7 @@
         <v>7</v>
       </c>
       <c r="G703" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -20332,7 +20335,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G704" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -20592,7 +20595,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G714" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -20618,7 +20621,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G715" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -20696,7 +20699,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G718" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -20748,7 +20751,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G720" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -21008,7 +21011,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G730" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -21034,7 +21037,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G731" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -21060,7 +21063,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G732" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -21086,7 +21089,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G733" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -21346,7 +21349,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G743" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -21372,7 +21375,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G744" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -21398,7 +21401,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G745" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -21424,7 +21427,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G746" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -21450,7 +21453,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G747" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -21476,7 +21479,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G748" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -21502,7 +21505,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G749" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -21528,7 +21531,7 @@
         <v>9</v>
       </c>
       <c r="G750" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -21554,7 +21557,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G751" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -21580,7 +21583,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G752" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -21606,7 +21609,7 @@
         <v>8.75</v>
       </c>
       <c r="G753" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -21632,7 +21635,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G754" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -21658,7 +21661,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G755" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -21684,7 +21687,7 @@
         <v>9</v>
       </c>
       <c r="G756" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -21710,7 +21713,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G757" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -21736,7 +21739,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G758" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -21762,7 +21765,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G759" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -21788,7 +21791,7 @@
         <v>9</v>
       </c>
       <c r="G760" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -21814,7 +21817,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G761" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -21840,7 +21843,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G762" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -21866,7 +21869,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G763" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -21892,7 +21895,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G764" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -21918,7 +21921,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G765" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -21944,7 +21947,7 @@
         <v>9</v>
       </c>
       <c r="G766" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -21970,7 +21973,7 @@
         <v>9</v>
       </c>
       <c r="G767" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -21996,7 +21999,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G768" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -22022,7 +22025,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G769" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -22048,7 +22051,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G770" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -22074,7 +22077,7 @@
         <v>8.75</v>
       </c>
       <c r="G771" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -22100,7 +22103,7 @@
         <v>8.75</v>
       </c>
       <c r="G772" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -22126,7 +22129,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G773" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -22152,7 +22155,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G774" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -22178,7 +22181,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G775" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -22204,7 +22207,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G776" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -22230,7 +22233,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G777" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -22256,7 +22259,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G778" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -22282,7 +22285,7 @@
         <v>9</v>
       </c>
       <c r="G779" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -22308,7 +22311,7 @@
         <v>9</v>
       </c>
       <c r="G780" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -22334,7 +22337,7 @@
         <v>9</v>
       </c>
       <c r="G781" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -22360,7 +22363,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G782" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -22386,7 +22389,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G783" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -22412,7 +22415,7 @@
         <v>8.75</v>
       </c>
       <c r="G784" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -22438,7 +22441,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G785" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -22464,7 +22467,7 @@
         <v>8.75</v>
       </c>
       <c r="G786" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -22490,7 +22493,7 @@
         <v>8.75</v>
       </c>
       <c r="G787" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -22516,7 +22519,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G788" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -22542,7 +22545,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G789" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -22568,7 +22571,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G790" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -22594,7 +22597,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G791" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -22620,7 +22623,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G792" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -22646,7 +22649,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G793" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -22672,7 +22675,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G794" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -22698,7 +22701,7 @@
         <v>9.30000019073486</v>
       </c>
       <c r="G795" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -22724,7 +22727,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G796" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -22750,7 +22753,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G797" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -22776,7 +22779,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G798" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -22802,7 +22805,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G799" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -22828,7 +22831,7 @@
         <v>8.75</v>
       </c>
       <c r="G800" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -22854,7 +22857,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G801" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -22880,7 +22883,7 @@
         <v>8.75</v>
       </c>
       <c r="G802" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -22906,7 +22909,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G803" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -22932,7 +22935,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G804" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -22958,7 +22961,7 @@
         <v>8.75</v>
       </c>
       <c r="G805" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -22984,7 +22987,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G806" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -23010,7 +23013,7 @@
         <v>8.75</v>
       </c>
       <c r="G807" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -23036,7 +23039,7 @@
         <v>8.75</v>
       </c>
       <c r="G808" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -23062,7 +23065,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G809" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -23088,7 +23091,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G810" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -23114,7 +23117,7 @@
         <v>8.5</v>
       </c>
       <c r="G811" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -23140,7 +23143,7 @@
         <v>8.5</v>
       </c>
       <c r="G812" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -23166,7 +23169,7 @@
         <v>8.5</v>
       </c>
       <c r="G813" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -23192,7 +23195,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G814" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -23218,7 +23221,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G815" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -23244,7 +23247,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G816" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -23270,7 +23273,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G817" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -23296,7 +23299,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G818" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -23322,7 +23325,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G819" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -23348,7 +23351,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G820" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -23374,7 +23377,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G821" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -23400,7 +23403,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G822" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -23426,7 +23429,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G823" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -23452,7 +23455,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G824" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -23478,7 +23481,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G825" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -23504,7 +23507,7 @@
         <v>9.14999961853027</v>
       </c>
       <c r="G826" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -23530,7 +23533,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G827" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -23556,7 +23559,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G828" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -23582,7 +23585,7 @@
         <v>9.05000019073486</v>
       </c>
       <c r="G829" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -23608,7 +23611,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G830" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -23634,7 +23637,7 @@
         <v>9</v>
       </c>
       <c r="G831" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -23660,7 +23663,7 @@
         <v>8.94999980926514</v>
       </c>
       <c r="G832" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -23686,7 +23689,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G833" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -23712,7 +23715,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G834" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -23738,7 +23741,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G835" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -23764,7 +23767,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G836" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -23790,7 +23793,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G837" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -23816,7 +23819,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G838" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -23842,7 +23845,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G839" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -23868,7 +23871,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G840" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -23894,7 +23897,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G841" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -23920,7 +23923,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G842" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -23946,7 +23949,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G843" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -23972,7 +23975,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G844" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -23998,7 +24001,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G845" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -24024,7 +24027,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G846" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -24050,7 +24053,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G847" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -24076,7 +24079,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G848" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -24102,7 +24105,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G849" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -24128,7 +24131,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G850" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -24154,7 +24157,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G851" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -24180,7 +24183,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G852" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -24206,7 +24209,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G853" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -24232,7 +24235,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G854" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -24258,7 +24261,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G855" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -24284,7 +24287,7 @@
         <v>8</v>
       </c>
       <c r="G856" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -24310,7 +24313,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G857" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -24336,7 +24339,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G858" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -24414,7 +24417,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G861" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -24492,7 +24495,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G864" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -24934,7 +24937,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G881" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -25012,7 +25015,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G884" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -25038,7 +25041,7 @@
         <v>7</v>
       </c>
       <c r="G885" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -25246,7 +25249,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G893" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -25974,7 +25977,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G921" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -26000,7 +26003,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G922" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -26026,7 +26029,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G923" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -26052,7 +26055,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G924" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -26156,7 +26159,7 @@
         <v>7</v>
       </c>
       <c r="G928" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -26182,7 +26185,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G929" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -26208,7 +26211,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G930" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -26234,7 +26237,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G931" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -26260,7 +26263,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G932" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -26286,7 +26289,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G933" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -26312,7 +26315,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G934" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -26338,7 +26341,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G935" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -26416,7 +26419,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G938" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -26442,7 +26445,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G939" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -26702,7 +26705,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G949" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -26728,7 +26731,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G950" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -26754,7 +26757,7 @@
         <v>7</v>
       </c>
       <c r="G951" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -26780,7 +26783,7 @@
         <v>7</v>
       </c>
       <c r="G952" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -26806,7 +26809,7 @@
         <v>7</v>
       </c>
       <c r="G953" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -26832,7 +26835,7 @@
         <v>7</v>
       </c>
       <c r="G954" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -26858,7 +26861,7 @@
         <v>7</v>
       </c>
       <c r="G955" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -26884,7 +26887,7 @@
         <v>7</v>
       </c>
       <c r="G956" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -26910,7 +26913,7 @@
         <v>7</v>
       </c>
       <c r="G957" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -26936,7 +26939,7 @@
         <v>7</v>
       </c>
       <c r="G958" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -26962,7 +26965,7 @@
         <v>7</v>
       </c>
       <c r="G959" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -26988,7 +26991,7 @@
         <v>7</v>
       </c>
       <c r="G960" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -27014,7 +27017,7 @@
         <v>7</v>
       </c>
       <c r="G961" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -27040,7 +27043,7 @@
         <v>7</v>
       </c>
       <c r="G962" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -27066,7 +27069,7 @@
         <v>7</v>
       </c>
       <c r="G963" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -27092,7 +27095,7 @@
         <v>7</v>
       </c>
       <c r="G964" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -27118,7 +27121,7 @@
         <v>7</v>
       </c>
       <c r="G965" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -27144,7 +27147,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G966" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -27170,7 +27173,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G967" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -27196,7 +27199,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G968" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -27222,7 +27225,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G969" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -27248,7 +27251,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G970" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -27274,7 +27277,7 @@
         <v>6.75</v>
       </c>
       <c r="G971" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -27300,7 +27303,7 @@
         <v>6.75</v>
       </c>
       <c r="G972" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -27326,7 +27329,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G973" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -27352,7 +27355,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G974" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -27378,7 +27381,7 @@
         <v>6.75</v>
       </c>
       <c r="G975" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -27404,7 +27407,7 @@
         <v>6.75</v>
       </c>
       <c r="G976" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -27430,7 +27433,7 @@
         <v>6.75</v>
       </c>
       <c r="G977" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -27456,7 +27459,7 @@
         <v>6.75</v>
       </c>
       <c r="G978" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -27482,7 +27485,7 @@
         <v>6.75</v>
       </c>
       <c r="G979" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -27508,7 +27511,7 @@
         <v>6.75</v>
       </c>
       <c r="G980" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -27534,7 +27537,7 @@
         <v>6.94999980926514</v>
       </c>
       <c r="G981" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -27560,7 +27563,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G982" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -27586,7 +27589,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G983" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -27612,7 +27615,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G984" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -27638,7 +27641,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G985" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -27664,7 +27667,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G986" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -27690,7 +27693,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G987" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -27716,7 +27719,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G988" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -27742,7 +27745,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G989" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -27768,7 +27771,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G990" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -27794,7 +27797,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G991" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -27820,7 +27823,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G992" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -27846,7 +27849,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G993" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -27872,7 +27875,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G994" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -27898,7 +27901,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G995" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -27924,7 +27927,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G996" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -27950,7 +27953,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G997" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -27976,7 +27979,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G998" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -28002,7 +28005,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G999" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -28028,7 +28031,7 @@
         <v>6.44999980926514</v>
       </c>
       <c r="G1000" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -28054,7 +28057,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G1001" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -28080,7 +28083,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1002" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -28106,7 +28109,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G1003" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -28132,7 +28135,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G1004" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -28158,7 +28161,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1005" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -28184,7 +28187,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1006" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -28210,7 +28213,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1007" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -28236,7 +28239,7 @@
         <v>6.84999990463257</v>
       </c>
       <c r="G1008" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -28262,7 +28265,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G1009" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -28340,7 +28343,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1012" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -28366,7 +28369,7 @@
         <v>7.44999980926514</v>
       </c>
       <c r="G1013" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -28392,7 +28395,7 @@
         <v>8</v>
       </c>
       <c r="G1014" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -28548,7 +28551,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1020" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -28574,7 +28577,7 @@
         <v>8.5</v>
       </c>
       <c r="G1021" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -28600,7 +28603,7 @@
         <v>8.5</v>
       </c>
       <c r="G1022" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -28626,7 +28629,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1023" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -28652,7 +28655,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1024" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -28678,7 +28681,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1025" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -28704,7 +28707,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1026" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -28730,7 +28733,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G1027" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -28756,7 +28759,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1028" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -28782,7 +28785,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G1029" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -28808,7 +28811,7 @@
         <v>8.75</v>
       </c>
       <c r="G1030" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -28834,7 +28837,7 @@
         <v>8.75</v>
       </c>
       <c r="G1031" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -28860,7 +28863,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G1032" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -28886,7 +28889,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G1033" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -28912,7 +28915,7 @@
         <v>8.5</v>
       </c>
       <c r="G1034" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -28938,7 +28941,7 @@
         <v>8.25</v>
       </c>
       <c r="G1035" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -28964,7 +28967,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1036" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -28990,7 +28993,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G1037" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -29016,7 +29019,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G1038" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -29042,7 +29045,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G1039" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H1039" t="s">
   